--- a/s60_signal/position-01618-601618.xlsx
+++ b/s60_signal/position-01618-601618.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="124">
   <si>
     <t>trade_time</t>
   </si>
@@ -85,306 +85,288 @@
     <t>2020-08-17</t>
   </si>
   <si>
+    <t>2020-12-15</t>
+  </si>
+  <si>
+    <t>2021-02-22</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
     <t>2020-12-11</t>
   </si>
   <si>
-    <t>2020-12-15</t>
-  </si>
-  <si>
-    <t>2021-02-22</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
+    <t>2021-01-13</t>
+  </si>
+  <si>
+    <t>2021-01-15</t>
+  </si>
+  <si>
+    <t>2021-04-01</t>
   </si>
   <si>
     <t>2021-04-12</t>
   </si>
   <si>
-    <t>2021-01-13</t>
-  </si>
-  <si>
-    <t>2021-01-15</t>
-  </si>
-  <si>
-    <t>2021-04-01</t>
+    <t>2021-02-26</t>
+  </si>
+  <si>
+    <t>2021-02-25</t>
+  </si>
+  <si>
+    <t>2021-02-23</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>2021-04-15</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>2021-07-12</t>
+  </si>
+  <si>
+    <t>2016-12-30</t>
+  </si>
+  <si>
+    <t>2017-04-05</t>
+  </si>
+  <si>
+    <t>2017-05-04</t>
+  </si>
+  <si>
+    <t>2017-12-20</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>2020-08-12</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-07-17</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>2021-05-21</t>
+  </si>
+  <si>
+    <t>2021-05-20</t>
+  </si>
+  <si>
+    <t>2021-01-22</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>2021-01-26</t>
+  </si>
+  <si>
+    <t>2021-03-09</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>2016-12-23</t>
+  </si>
+  <si>
+    <t>2017-02-09</t>
+  </si>
+  <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
+    <t>2017-02-13</t>
+  </si>
+  <si>
+    <t>2017-02-14</t>
+  </si>
+  <si>
+    <t>2017-02-15</t>
+  </si>
+  <si>
+    <t>2017-02-16</t>
+  </si>
+  <si>
+    <t>2017-04-27</t>
+  </si>
+  <si>
+    <t>2019-12-05</t>
+  </si>
+  <si>
+    <t>2019-12-06</t>
+  </si>
+  <si>
+    <t>2019-12-20</t>
+  </si>
+  <si>
+    <t>2020-02-21</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>2020-02-27</t>
+  </si>
+  <si>
+    <t>2020-02-28</t>
+  </si>
+  <si>
+    <t>2020-11-26</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-01</t>
+  </si>
+  <si>
+    <t>2020-12-02</t>
+  </si>
+  <si>
+    <t>2020-12-14</t>
+  </si>
+  <si>
+    <t>2020-12-16</t>
+  </si>
+  <si>
+    <t>2020-12-17</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>2020-12-21</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
+    <t>2020-12-24</t>
+  </si>
+  <si>
+    <t>2020-12-28</t>
+  </si>
+  <si>
+    <t>2020-12-29</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>2021-01-05</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>2021-01-08</t>
+  </si>
+  <si>
+    <t>2021-01-11</t>
+  </si>
+  <si>
+    <t>2021-01-14</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
   </si>
   <si>
     <t>2021-03-31</t>
   </si>
   <si>
-    <t>2021-02-26</t>
-  </si>
-  <si>
-    <t>2021-02-25</t>
-  </si>
-  <si>
-    <t>2021-02-23</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>2021-04-15</t>
-  </si>
-  <si>
-    <t>2021-04-29</t>
-  </si>
-  <si>
-    <t>2021-07-12</t>
+    <t>2021-04-08</t>
+  </si>
+  <si>
+    <t>2021-04-09</t>
+  </si>
+  <si>
+    <t>2021-04-13</t>
+  </si>
+  <si>
+    <t>2021-04-14</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>2021-05-12</t>
+  </si>
+  <si>
+    <t>2021-05-13</t>
+  </si>
+  <si>
+    <t>2021-05-14</t>
   </si>
   <si>
     <t>2021-05-17</t>
   </si>
   <si>
-    <t>2016-12-30</t>
-  </si>
-  <si>
-    <t>2017-04-05</t>
-  </si>
-  <si>
-    <t>2017-05-04</t>
-  </si>
-  <si>
-    <t>2017-12-20</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>2020-08-12</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-07-17</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>2021-05-21</t>
-  </si>
-  <si>
-    <t>2021-01-22</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-26</t>
-  </si>
-  <si>
-    <t>2021-03-09</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
+    <t>2021-05-18</t>
   </si>
   <si>
     <t>2021-05-24</t>
   </si>
   <si>
-    <t>2021-07-16</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
+    <t>2021-05-25</t>
+  </si>
+  <si>
+    <t>2021-05-26</t>
+  </si>
+  <si>
+    <t>2021-05-27</t>
   </si>
   <si>
     <t>2021-05-28</t>
   </si>
   <si>
-    <t>2016-12-23</t>
-  </si>
-  <si>
-    <t>2017-02-09</t>
-  </si>
-  <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
-    <t>2017-02-13</t>
-  </si>
-  <si>
-    <t>2017-02-14</t>
-  </si>
-  <si>
-    <t>2017-02-15</t>
-  </si>
-  <si>
-    <t>2017-02-16</t>
-  </si>
-  <si>
-    <t>2017-04-27</t>
-  </si>
-  <si>
-    <t>2019-12-05</t>
-  </si>
-  <si>
-    <t>2019-12-06</t>
-  </si>
-  <si>
-    <t>2019-12-20</t>
-  </si>
-  <si>
-    <t>2020-02-21</t>
-  </si>
-  <si>
-    <t>2020-02-24</t>
-  </si>
-  <si>
-    <t>2020-02-25</t>
-  </si>
-  <si>
-    <t>2020-02-26</t>
-  </si>
-  <si>
-    <t>2020-02-27</t>
-  </si>
-  <si>
-    <t>2020-02-28</t>
-  </si>
-  <si>
-    <t>2020-11-26</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-01</t>
-  </si>
-  <si>
-    <t>2020-12-02</t>
-  </si>
-  <si>
-    <t>2020-12-14</t>
-  </si>
-  <si>
-    <t>2020-12-16</t>
-  </si>
-  <si>
-    <t>2020-12-17</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>2020-12-21</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2020-12-23</t>
-  </si>
-  <si>
-    <t>2020-12-24</t>
-  </si>
-  <si>
-    <t>2020-12-28</t>
-  </si>
-  <si>
-    <t>2020-12-29</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>2021-01-05</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>2021-01-08</t>
-  </si>
-  <si>
-    <t>2021-01-11</t>
-  </si>
-  <si>
-    <t>2021-01-14</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>2021-04-08</t>
-  </si>
-  <si>
-    <t>2021-04-09</t>
-  </si>
-  <si>
-    <t>2021-04-13</t>
-  </si>
-  <si>
-    <t>2021-04-14</t>
-  </si>
-  <si>
-    <t>2021-04-23</t>
-  </si>
-  <si>
-    <t>2021-04-26</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>2021-05-10</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>2021-05-12</t>
-  </si>
-  <si>
-    <t>2021-05-13</t>
-  </si>
-  <si>
-    <t>2021-05-14</t>
-  </si>
-  <si>
-    <t>2021-05-18</t>
-  </si>
-  <si>
-    <t>2021-05-20</t>
-  </si>
-  <si>
-    <t>2021-05-25</t>
-  </si>
-  <si>
-    <t>2021-05-26</t>
-  </si>
-  <si>
-    <t>2021-05-27</t>
-  </si>
-  <si>
     <t>2021-05-31</t>
   </si>
   <si>
@@ -404,48 +386,6 @@
   </si>
   <si>
     <t>2021-06-08</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>2021-06-10</t>
-  </si>
-  <si>
-    <t>2021-06-11</t>
-  </si>
-  <si>
-    <t>2021-06-15</t>
-  </si>
-  <si>
-    <t>2021-06-16</t>
-  </si>
-  <si>
-    <t>2021-06-17</t>
-  </si>
-  <si>
-    <t>2021-06-18</t>
-  </si>
-  <si>
-    <t>2021-06-21</t>
-  </si>
-  <si>
-    <t>2021-06-22</t>
-  </si>
-  <si>
-    <t>2021-06-23</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>2021-06-25</t>
-  </si>
-  <si>
-    <t>2021-06-28</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
   </si>
 </sst>
 </file>
@@ -803,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P151"/>
+  <dimension ref="A1:P132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -864,7 +804,7 @@
         <v>2.241636620202809</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E2">
         <v>2.083673377356266</v>
@@ -900,7 +840,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -914,7 +854,7 @@
         <v>2.291018963074085</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3">
         <v>2.748932188801797</v>
@@ -950,7 +890,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -964,7 +904,7 @@
         <v>0.1640886968569069</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E4">
         <v>0.8087275807852619</v>
@@ -1000,7 +940,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1014,7 +954,7 @@
         <v>0.1567937244930127</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E5">
         <v>0.8087275807852619</v>
@@ -1050,7 +990,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1064,7 +1004,7 @@
         <v>0.06008199184724816</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E6">
         <v>0.7118353409391309</v>
@@ -1100,7 +1040,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1114,7 +1054,7 @@
         <v>0.05109309920632388</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E7">
         <v>0.7118353409391309</v>
@@ -1150,7 +1090,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1164,7 +1104,7 @@
         <v>-0.0569506423664734</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8">
         <v>0.6028081963621785</v>
@@ -1200,7 +1140,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1214,7 +1154,7 @@
         <v>-0.06784560396853312</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E9">
         <v>0.6028081963621785</v>
@@ -1250,7 +1190,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1264,7 +1204,7 @@
         <v>-0.1396452470657845</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E10">
         <v>0.5257702258605397</v>
@@ -1300,7 +1240,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1314,7 +1254,7 @@
         <v>-0.1518870263339567</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E11">
         <v>0.5257702258605397</v>
@@ -1350,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1364,7 +1304,7 @@
         <v>-0.2479133877986754</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E12">
         <v>0.424908049151723</v>
@@ -1400,7 +1340,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1414,7 +1354,7 @@
         <v>-0.2619184918344848</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E13">
         <v>0.424908049151723</v>
@@ -1450,7 +1390,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1464,7 +1404,7 @@
         <v>-0.3399965939203824</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E14">
         <v>0.3391236942630966</v>
@@ -1500,7 +1440,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1514,7 +1454,7 @@
         <v>0.9756011105228968</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E15">
         <v>0.8107654111102569</v>
@@ -1550,7 +1490,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1564,7 +1504,7 @@
         <v>1.301145679016073</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E16">
         <v>1.173416666670367</v>
@@ -1600,7 +1540,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1614,7 +1554,7 @@
         <v>1.296277364845049</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E17">
         <v>1.230890933009092</v>
@@ -1650,7 +1590,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1664,7 +1604,7 @@
         <v>0.4435035626339812</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E18">
         <v>0.9439906537348826</v>
@@ -1700,7 +1640,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1714,7 +1654,7 @@
         <v>0.4423533289773536</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E19">
         <v>0.9439906537348826</v>
@@ -1750,7 +1690,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1764,7 +1704,7 @@
         <v>1.507350128118183</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E20">
         <v>1.202821457299868</v>
@@ -1800,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -1814,7 +1754,7 @@
         <v>1.54125697476493</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E21">
         <v>1.238224194239853</v>
@@ -1850,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -1864,7 +1804,7 @@
         <v>1.573438797246031</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E22">
         <v>1.271825803006885</v>
@@ -1900,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -1914,7 +1854,7 @@
         <v>1.613400857289038</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E23">
         <v>1.313550895110613</v>
@@ -1950,7 +1890,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -1964,7 +1904,7 @@
         <v>1.593400857289038</v>
       </c>
       <c r="D24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E24">
         <v>1.363275825771058</v>
@@ -2000,7 +1940,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2014,7 +1954,7 @@
         <v>1.645344720184119</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E25">
         <v>1.346904046074595</v>
@@ -2050,7 +1990,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2064,7 +2004,7 @@
         <v>1.625344720184119</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E26">
         <v>1.394045281942056</v>
@@ -2100,7 +2040,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2114,7 +2054,7 @@
         <v>1.68180858461344</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E27">
         <v>1.384976610405209</v>
@@ -2150,7 +2090,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2164,7 +2104,7 @@
         <v>1.66180858461344</v>
       </c>
       <c r="D28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E28">
         <v>1.429168563120298</v>
@@ -2200,7 +2140,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2214,7 +2154,7 @@
         <v>1.710614904938503</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E29">
         <v>1.415053797803437</v>
@@ -2250,7 +2190,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2264,7 +2204,7 @@
         <v>1.690614904938503</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E30">
         <v>1.456915827551058</v>
@@ -2300,7 +2240,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2311,10 +2251,10 @@
         <v>23</v>
       </c>
       <c r="C31">
-        <v>2.275802866177917</v>
+        <v>2.268334662646267</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E31">
         <v>2.649848972127444</v>
@@ -2323,22 +2263,22 @@
         <v>1</v>
       </c>
       <c r="G31">
-        <v>0.002944197133822083</v>
+        <v>0.002931665337353733</v>
       </c>
       <c r="H31">
         <v>0.003470151027872556</v>
       </c>
       <c r="I31">
-        <v>0.3740461059495268</v>
+        <v>0.3815143094811773</v>
       </c>
       <c r="J31">
         <v>0.2531796468349111</v>
       </c>
       <c r="K31">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="L31">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="M31">
         <v>1.62</v>
@@ -2350,7 +2290,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2361,37 +2301,37 @@
         <v>24</v>
       </c>
       <c r="C32">
-        <v>2.268334662646267</v>
+        <v>2.967686812279704</v>
       </c>
       <c r="D32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E32">
-        <v>2.649848972127444</v>
+        <v>2.601744839228811</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G32">
-        <v>0.002931665337353733</v>
+        <v>0.004132313187720295</v>
       </c>
       <c r="H32">
-        <v>0.003470151027872556</v>
+        <v>0.003518255160771189</v>
       </c>
       <c r="I32">
-        <v>0.3815143094811773</v>
+        <v>0.3659419730508935</v>
       </c>
       <c r="J32">
         <v>0.2531796468349111</v>
       </c>
       <c r="K32">
-        <v>1.31</v>
+        <v>2.3</v>
       </c>
       <c r="L32">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="M32">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="N32">
         <v>3.06</v>
@@ -2400,7 +2340,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2411,10 +2351,10 @@
         <v>25</v>
       </c>
       <c r="C33">
-        <v>2.967686812279704</v>
+        <v>2.94857711339348</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E33">
         <v>2.601744839228811</v>
@@ -2423,22 +2363,22 @@
         <v>-1</v>
       </c>
       <c r="G33">
-        <v>0.004132313187720295</v>
+        <v>0.00397142288660652</v>
       </c>
       <c r="H33">
         <v>0.003518255160771189</v>
       </c>
       <c r="I33">
-        <v>0.3659419730508935</v>
+        <v>0.3468322741646688</v>
       </c>
       <c r="J33">
         <v>0.2531796468349111</v>
       </c>
       <c r="K33">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="L33">
-        <v>3.55</v>
+        <v>3.46</v>
       </c>
       <c r="M33">
         <v>1.81</v>
@@ -2450,48 +2390,48 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B34" t="s">
         <v>26</v>
       </c>
       <c r="C34">
-        <v>2.94857711339348</v>
+        <v>2.276798754456807</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E34">
-        <v>2.601744839228811</v>
+        <v>2.651071198651537</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>0.00397142288660652</v>
+        <v>0.002943201245543193</v>
       </c>
       <c r="H34">
-        <v>0.003518255160771189</v>
+        <v>0.003468928801348464</v>
       </c>
       <c r="I34">
-        <v>0.3468322741646688</v>
+        <v>0.3742724441947294</v>
       </c>
       <c r="J34">
-        <v>0.2531796468349111</v>
+        <v>0.2524251860175702</v>
       </c>
       <c r="K34">
-        <v>2.02</v>
+        <v>1.32</v>
       </c>
       <c r="L34">
-        <v>3.46</v>
+        <v>2.61</v>
       </c>
       <c r="M34">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="N34">
         <v>3.06</v>
@@ -2500,48 +2440,48 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C35">
-        <v>2.936045316925131</v>
+        <v>2.269323006316983</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E35">
-        <v>2.601744839228811</v>
+        <v>2.651071198651537</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>0.00396395468307487</v>
+        <v>0.002930676993683017</v>
       </c>
       <c r="H35">
-        <v>0.003518255160771189</v>
+        <v>0.003468928801348464</v>
       </c>
       <c r="I35">
-        <v>0.3343004776963197</v>
+        <v>0.3817481923345531</v>
       </c>
       <c r="J35">
-        <v>0.2531796468349111</v>
+        <v>0.2524251860175702</v>
       </c>
       <c r="K35">
-        <v>2.03</v>
+        <v>1.31</v>
       </c>
       <c r="L35">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="M35">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="N35">
         <v>3.06</v>
@@ -2550,48 +2490,48 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C36">
-        <v>2.276798754456807</v>
+        <v>2.969422072159588</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E36">
-        <v>2.651071198651537</v>
+        <v>2.603110413308198</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G36">
-        <v>0.002943201245543193</v>
+        <v>0.004130577927840411</v>
       </c>
       <c r="H36">
-        <v>0.003468928801348464</v>
+        <v>0.003516889586691802</v>
       </c>
       <c r="I36">
-        <v>0.3742724441947294</v>
+        <v>0.3663116588513904</v>
       </c>
       <c r="J36">
         <v>0.2524251860175702</v>
       </c>
       <c r="K36">
-        <v>1.32</v>
+        <v>2.3</v>
       </c>
       <c r="L36">
-        <v>2.61</v>
+        <v>3.55</v>
       </c>
       <c r="M36">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="N36">
         <v>3.06</v>
@@ -2600,98 +2540,98 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B37" t="s">
         <v>25</v>
       </c>
       <c r="C37">
-        <v>2.969422072159588</v>
+        <v>2.950101124244508</v>
       </c>
       <c r="D37" t="s">
         <v>51</v>
       </c>
       <c r="E37">
-        <v>2.603110413308198</v>
+        <v>2.610586161448022</v>
       </c>
       <c r="F37">
         <v>-1</v>
       </c>
       <c r="G37">
-        <v>0.004130577927840411</v>
+        <v>0.003969898875755492</v>
       </c>
       <c r="H37">
-        <v>0.003516889586691802</v>
+        <v>0.003529413838551978</v>
       </c>
       <c r="I37">
-        <v>0.3663116588513904</v>
+        <v>0.339514962796486</v>
       </c>
       <c r="J37">
         <v>0.2524251860175702</v>
       </c>
       <c r="K37">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="L37">
-        <v>3.55</v>
+        <v>3.46</v>
       </c>
       <c r="M37">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="N37">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="O37">
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B38" t="s">
         <v>26</v>
       </c>
       <c r="C38">
-        <v>2.950101124244508</v>
+        <v>2.277619541489629</v>
       </c>
       <c r="D38" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E38">
-        <v>2.603110413308198</v>
+        <v>2.652078528191817</v>
       </c>
       <c r="F38">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>0.003969898875755492</v>
+        <v>0.002942380458510371</v>
       </c>
       <c r="H38">
-        <v>0.003516889586691802</v>
+        <v>0.003467921471808183</v>
       </c>
       <c r="I38">
-        <v>0.3469907109363102</v>
+        <v>0.3744589867021886</v>
       </c>
       <c r="J38">
-        <v>0.2524251860175702</v>
+        <v>0.2518033776593721</v>
       </c>
       <c r="K38">
-        <v>2.02</v>
+        <v>1.32</v>
       </c>
       <c r="L38">
-        <v>3.46</v>
+        <v>2.61</v>
       </c>
       <c r="M38">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="N38">
         <v>3.06</v>
@@ -2700,45 +2640,45 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:16">
       <c r="A39" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C39">
-        <v>2.937576872384333</v>
+        <v>2.970852231383444</v>
       </c>
       <c r="D39" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E39">
-        <v>2.603110413308198</v>
+        <v>2.604235886436537</v>
       </c>
       <c r="F39">
         <v>-1</v>
       </c>
       <c r="G39">
-        <v>0.003962423127615668</v>
+        <v>0.004129147768616556</v>
       </c>
       <c r="H39">
-        <v>0.003516889586691802</v>
+        <v>0.003515764113563464</v>
       </c>
       <c r="I39">
-        <v>0.3344664590761348</v>
+        <v>0.3666163449469071</v>
       </c>
       <c r="J39">
-        <v>0.2524251860175702</v>
+        <v>0.2518033776593721</v>
       </c>
       <c r="K39">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="L39">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="M39">
         <v>1.81</v>
@@ -2750,98 +2690,98 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C40">
-        <v>2.277619541489629</v>
+        <v>2.951357177128068</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E40">
-        <v>2.652078528191817</v>
+        <v>2.611717852659943</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G40">
-        <v>0.002942380458510371</v>
+        <v>0.003968642822871932</v>
       </c>
       <c r="H40">
-        <v>0.003467921471808183</v>
+        <v>0.003528282147340057</v>
       </c>
       <c r="I40">
-        <v>0.3744589867021886</v>
+        <v>0.3396393244681257</v>
       </c>
       <c r="J40">
         <v>0.2518033776593721</v>
       </c>
       <c r="K40">
-        <v>1.32</v>
+        <v>2.02</v>
       </c>
       <c r="L40">
-        <v>2.61</v>
+        <v>3.46</v>
       </c>
       <c r="M40">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="N40">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="O40">
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C41">
-        <v>2.970852231383444</v>
+        <v>2.2742064249631</v>
       </c>
       <c r="D41" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E41">
-        <v>2.604235886436537</v>
+        <v>2.647889703363805</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G41">
-        <v>0.004129147768616556</v>
+        <v>0.0029457935750369</v>
       </c>
       <c r="H41">
-        <v>0.003515764113563464</v>
+        <v>0.003472110296636196</v>
       </c>
       <c r="I41">
-        <v>0.3666163449469071</v>
+        <v>0.3736832784007049</v>
       </c>
       <c r="J41">
-        <v>0.2518033776593721</v>
+        <v>0.2543890719976515</v>
       </c>
       <c r="K41">
-        <v>2.3</v>
+        <v>1.32</v>
       </c>
       <c r="L41">
-        <v>3.55</v>
+        <v>2.61</v>
       </c>
       <c r="M41">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="N41">
         <v>3.06</v>
@@ -2850,45 +2790,45 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C42">
-        <v>2.951357177128068</v>
+        <v>2.964905134405401</v>
       </c>
       <c r="D42" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E42">
-        <v>2.604235886436537</v>
+        <v>2.599555779684251</v>
       </c>
       <c r="F42">
         <v>-1</v>
       </c>
       <c r="G42">
-        <v>0.003968642822871932</v>
+        <v>0.004135094865594598</v>
       </c>
       <c r="H42">
-        <v>0.003515764113563464</v>
+        <v>0.003520444220315749</v>
       </c>
       <c r="I42">
-        <v>0.3471212906915317</v>
+        <v>0.3653493547211504</v>
       </c>
       <c r="J42">
-        <v>0.2518033776593721</v>
+        <v>0.2543890719976515</v>
       </c>
       <c r="K42">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="L42">
-        <v>3.46</v>
+        <v>3.55</v>
       </c>
       <c r="M42">
         <v>1.81</v>
@@ -2900,57 +2840,57 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C43">
-        <v>2.938839143351475</v>
+        <v>2.946134074564744</v>
       </c>
       <c r="D43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E43">
-        <v>2.604235886436537</v>
+        <v>2.607011888964274</v>
       </c>
       <c r="F43">
         <v>-1</v>
       </c>
       <c r="G43">
-        <v>0.003961160856648526</v>
+        <v>0.003973865925435256</v>
       </c>
       <c r="H43">
-        <v>0.003515764113563464</v>
+        <v>0.003532988111035726</v>
       </c>
       <c r="I43">
-        <v>0.3346032569149382</v>
+        <v>0.3391221856004698</v>
       </c>
       <c r="J43">
-        <v>0.2518033776593721</v>
+        <v>0.2543890719976515</v>
       </c>
       <c r="K43">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="L43">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="M43">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="N43">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -2961,34 +2901,34 @@
         <v>23</v>
       </c>
       <c r="C44">
-        <v>2.2742064249631</v>
+        <v>1.990887286527514</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E44">
-        <v>2.647889703363805</v>
+        <v>2.306746110056926</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44">
-        <v>0.0029457935750369</v>
+        <v>0.003209112713472486</v>
       </c>
       <c r="H44">
-        <v>0.003472110296636196</v>
+        <v>0.003813253889943074</v>
       </c>
       <c r="I44">
-        <v>0.3736832784007049</v>
+        <v>0.3158588235294117</v>
       </c>
       <c r="J44">
-        <v>0.2543890719976515</v>
+        <v>0.4649715370018978</v>
       </c>
       <c r="K44">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="L44">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="M44">
         <v>1.62</v>
@@ -3000,7 +2940,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3008,49 +2948,49 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C45">
-        <v>2.964905134405401</v>
+        <v>2.492796963946868</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E45">
-        <v>2.599555779684251</v>
+        <v>2.222096394686907</v>
       </c>
       <c r="F45">
         <v>-1</v>
       </c>
       <c r="G45">
-        <v>0.004135094865594598</v>
+        <v>0.004027203036053131</v>
       </c>
       <c r="H45">
-        <v>0.003520444220315749</v>
+        <v>0.003737903605313093</v>
       </c>
       <c r="I45">
-        <v>0.3653493547211504</v>
+        <v>0.2707005692599616</v>
       </c>
       <c r="J45">
-        <v>0.2543890719976515</v>
+        <v>0.4649715370018978</v>
       </c>
       <c r="K45">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="L45">
-        <v>3.55</v>
+        <v>3.26</v>
       </c>
       <c r="M45">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="N45">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="O45">
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3058,49 +2998,49 @@
         <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C46">
-        <v>2.946134074564744</v>
+        <v>2.502796963946869</v>
       </c>
       <c r="D46" t="s">
         <v>52</v>
       </c>
       <c r="E46">
-        <v>2.599555779684251</v>
+        <v>2.222096394686907</v>
       </c>
       <c r="F46">
         <v>-1</v>
       </c>
       <c r="G46">
-        <v>0.003973865925435256</v>
+        <v>0.004037203036053131</v>
       </c>
       <c r="H46">
-        <v>0.003520444220315749</v>
+        <v>0.003737903605313093</v>
       </c>
       <c r="I46">
-        <v>0.346578294880493</v>
+        <v>0.2807005692599618</v>
       </c>
       <c r="J46">
-        <v>0.2543890719976515</v>
+        <v>0.4649715370018978</v>
       </c>
       <c r="K46">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="L46">
-        <v>3.46</v>
+        <v>3.27</v>
       </c>
       <c r="M46">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="N46">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="O46">
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3108,187 +3048,187 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C47">
-        <v>2.933590183844768</v>
+        <v>2.504006072106261</v>
       </c>
       <c r="D47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E47">
-        <v>2.599555779684251</v>
+        <v>2.229102087286527</v>
       </c>
       <c r="F47">
         <v>-1</v>
       </c>
       <c r="G47">
-        <v>0.003966409816155233</v>
+        <v>0.004335993927893739</v>
       </c>
       <c r="H47">
-        <v>0.003520444220315749</v>
+        <v>0.003930897912713473</v>
       </c>
       <c r="I47">
-        <v>0.3340344041605166</v>
+        <v>0.2749039848197343</v>
       </c>
       <c r="J47">
-        <v>0.2543890719976515</v>
+        <v>0.4649715370018978</v>
       </c>
       <c r="K47">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="L47">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="M47">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="N47">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="O47">
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C48">
-        <v>1.990887286527514</v>
+        <v>2.506107779886148</v>
       </c>
       <c r="D48" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E48">
-        <v>2.306746110056926</v>
+        <v>2.229102087286527</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G48">
-        <v>0.003209112713472486</v>
+        <v>0.004393892220113852</v>
       </c>
       <c r="H48">
-        <v>0.003813253889943074</v>
+        <v>0.003930897912713473</v>
       </c>
       <c r="I48">
-        <v>0.3158588235294117</v>
+        <v>0.2770056925996207</v>
       </c>
       <c r="J48">
         <v>0.4649715370018978</v>
       </c>
       <c r="K48">
-        <v>1.31</v>
+        <v>2.03</v>
       </c>
       <c r="L48">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="M48">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="N48">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="O48">
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C49">
-        <v>2.492796963946868</v>
+        <v>1.934694011032936</v>
       </c>
       <c r="D49" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E49">
-        <v>2.222096394686907</v>
+        <v>2.237255189216302</v>
       </c>
       <c r="F49">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>0.004027203036053131</v>
+        <v>0.003265305988967065</v>
       </c>
       <c r="H49">
-        <v>0.003737903605313093</v>
+        <v>0.003882744810783698</v>
       </c>
       <c r="I49">
-        <v>0.2707005692599616</v>
+        <v>0.3025611781833666</v>
       </c>
       <c r="J49">
-        <v>0.4649715370018978</v>
+        <v>0.5078671671504308</v>
       </c>
       <c r="K49">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="L49">
-        <v>3.26</v>
+        <v>2.6</v>
       </c>
       <c r="M49">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="N49">
-        <v>2.98</v>
+        <v>3.06</v>
       </c>
       <c r="O49">
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C50">
-        <v>2.502796963946869</v>
+        <v>2.422019174201789</v>
       </c>
       <c r="D50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E50">
-        <v>2.222096394686907</v>
+        <v>2.152176517544798</v>
       </c>
       <c r="F50">
         <v>-1</v>
       </c>
       <c r="G50">
-        <v>0.004037203036053131</v>
+        <v>0.004097980825798211</v>
       </c>
       <c r="H50">
-        <v>0.003737903605313093</v>
+        <v>0.003807823482455202</v>
       </c>
       <c r="I50">
-        <v>0.2807005692599618</v>
+        <v>0.2698426566569911</v>
       </c>
       <c r="J50">
-        <v>0.4649715370018978</v>
+        <v>0.5078671671504308</v>
       </c>
       <c r="K50">
         <v>1.65</v>
       </c>
       <c r="L50">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="M50">
         <v>1.63</v>
@@ -3300,39 +3240,39 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C51">
-        <v>2.504006072106261</v>
+        <v>2.419501680713651</v>
       </c>
       <c r="D51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E51">
-        <v>2.229102087286527</v>
+        <v>2.150603084114712</v>
       </c>
       <c r="F51">
         <v>-1</v>
       </c>
       <c r="G51">
-        <v>0.004335993927893739</v>
+        <v>0.004420498319286349</v>
       </c>
       <c r="H51">
-        <v>0.003930897912713473</v>
+        <v>0.004009396915885288</v>
       </c>
       <c r="I51">
-        <v>0.2749039848197343</v>
+        <v>0.2688985965989392</v>
       </c>
       <c r="J51">
-        <v>0.4649715370018978</v>
+        <v>0.5078671671504308</v>
       </c>
       <c r="K51">
         <v>1.97</v>
@@ -3350,39 +3290,39 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C52">
-        <v>2.506107779886148</v>
+        <v>2.419029650684626</v>
       </c>
       <c r="D52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E52">
-        <v>2.229102087286527</v>
+        <v>2.150603084114712</v>
       </c>
       <c r="F52">
         <v>-1</v>
       </c>
       <c r="G52">
-        <v>0.004393892220113852</v>
+        <v>0.004480970349315374</v>
       </c>
       <c r="H52">
-        <v>0.003930897912713473</v>
+        <v>0.004009396915885288</v>
       </c>
       <c r="I52">
-        <v>0.2770056925996207</v>
+        <v>0.2684265665699139</v>
       </c>
       <c r="J52">
-        <v>0.4649715370018978</v>
+        <v>0.5078671671504308</v>
       </c>
       <c r="K52">
         <v>2.03</v>
@@ -3400,7 +3340,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3408,49 +3348,49 @@
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C53">
-        <v>1.934694011032936</v>
+        <v>2.361811863714594</v>
       </c>
       <c r="D53" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E53">
-        <v>2.167884562588337</v>
+        <v>2.092698992639265</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G53">
-        <v>0.003265305988967065</v>
+        <v>0.004158188136285406</v>
       </c>
       <c r="H53">
-        <v>0.003732115437411664</v>
+        <v>0.003867301007360734</v>
       </c>
       <c r="I53">
-        <v>0.2331905515554009</v>
+        <v>0.2691128710753286</v>
       </c>
       <c r="J53">
-        <v>0.5078671671504308</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K53">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="L53">
-        <v>2.6</v>
+        <v>3.26</v>
       </c>
       <c r="M53">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="N53">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="O53">
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3458,49 +3398,49 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C54">
-        <v>2.422019174201789</v>
+        <v>2.347617800919848</v>
       </c>
       <c r="D54" t="s">
         <v>53</v>
       </c>
       <c r="E54">
-        <v>2.152176517544798</v>
+        <v>2.08382770339255</v>
       </c>
       <c r="F54">
         <v>-1</v>
       </c>
       <c r="G54">
-        <v>0.004097980825798211</v>
+        <v>0.004492382199080151</v>
       </c>
       <c r="H54">
-        <v>0.003807823482455202</v>
+        <v>0.004076172296607451</v>
       </c>
       <c r="I54">
-        <v>0.2698426566569911</v>
+        <v>0.2637900975272984</v>
       </c>
       <c r="J54">
-        <v>0.5078671671504308</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K54">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="L54">
-        <v>3.26</v>
+        <v>3.42</v>
       </c>
       <c r="M54">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="N54">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="O54">
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3508,37 +3448,37 @@
         <v>2</v>
       </c>
       <c r="B55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C55">
-        <v>2.394108322356129</v>
+        <v>2.344956414145834</v>
       </c>
       <c r="D55" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E55">
-        <v>2.150603084114712</v>
+        <v>2.08382770339255</v>
       </c>
       <c r="F55">
         <v>-1</v>
       </c>
       <c r="G55">
-        <v>0.00444589167764387</v>
+        <v>0.004555043585854166</v>
       </c>
       <c r="H55">
-        <v>0.004009396915885288</v>
+        <v>0.004076172296607451</v>
       </c>
       <c r="I55">
-        <v>0.2435052382414176</v>
+        <v>0.261128710753284</v>
       </c>
       <c r="J55">
-        <v>0.5078671671504308</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K55">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="L55">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="M55">
         <v>1.83</v>
@@ -3550,145 +3490,145 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B56" t="s">
         <v>27</v>
       </c>
       <c r="C56">
-        <v>2.419029650684626</v>
+        <v>2.284943445032334</v>
       </c>
       <c r="D56" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E56">
-        <v>2.150603084114712</v>
+        <v>2.016762312365275</v>
       </c>
       <c r="F56">
         <v>-1</v>
       </c>
       <c r="G56">
-        <v>0.004480970349315374</v>
+        <v>0.004235056554967666</v>
       </c>
       <c r="H56">
-        <v>0.004009396915885288</v>
+        <v>0.003943237687634725</v>
       </c>
       <c r="I56">
-        <v>0.2684265665699139</v>
+        <v>0.2681811326670585</v>
       </c>
       <c r="J56">
-        <v>0.5078671671504308</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K56">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="L56">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="M56">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="N56">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="O56">
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C57">
-        <v>2.361811863714594</v>
+        <v>2.255841567705271</v>
       </c>
       <c r="D57" t="s">
         <v>53</v>
       </c>
       <c r="E57">
-        <v>2.092698992639265</v>
+        <v>1.998573639035861</v>
       </c>
       <c r="F57">
         <v>-1</v>
       </c>
       <c r="G57">
-        <v>0.004158188136285406</v>
+        <v>0.004584158432294728</v>
       </c>
       <c r="H57">
-        <v>0.003867301007360734</v>
+        <v>0.004161426360964139</v>
       </c>
       <c r="I57">
-        <v>0.2691128710753286</v>
+        <v>0.25726792866941</v>
       </c>
       <c r="J57">
-        <v>0.5443564462335794</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K57">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="L57">
-        <v>3.26</v>
+        <v>3.42</v>
       </c>
       <c r="M57">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="N57">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="O57">
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C58">
-        <v>2.32039997860817</v>
+        <v>2.250384965706448</v>
       </c>
       <c r="D58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E58">
-        <v>2.08382770339255</v>
+        <v>1.998573639035861</v>
       </c>
       <c r="F58">
         <v>-1</v>
       </c>
       <c r="G58">
-        <v>0.004519600021391831</v>
+        <v>0.004649615034293553</v>
       </c>
       <c r="H58">
-        <v>0.004076172296607451</v>
+        <v>0.004161426360964139</v>
       </c>
       <c r="I58">
-        <v>0.2365722752156199</v>
+        <v>0.2518113266705861</v>
       </c>
       <c r="J58">
-        <v>0.5443564462335794</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K58">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="L58">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="M58">
         <v>1.83</v>
@@ -3700,145 +3640,145 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B59" t="s">
         <v>27</v>
       </c>
       <c r="C59">
-        <v>2.344956414145834</v>
+        <v>2.206392009113778</v>
       </c>
       <c r="D59" t="s">
         <v>54</v>
       </c>
       <c r="E59">
-        <v>2.08382770339255</v>
+        <v>1.894705026964186</v>
       </c>
       <c r="F59">
         <v>-1</v>
       </c>
       <c r="G59">
-        <v>0.004555043585854166</v>
+        <v>0.004313607990886223</v>
       </c>
       <c r="H59">
-        <v>0.004076172296607451</v>
+        <v>0.003925294973035814</v>
       </c>
       <c r="I59">
-        <v>0.261128710753284</v>
+        <v>0.3116869821495918</v>
       </c>
       <c r="J59">
-        <v>0.5443564462335794</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K59">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="L59">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="M59">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="N59">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="O59">
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C60">
-        <v>2.284943445032334</v>
+        <v>2.162055913911602</v>
       </c>
       <c r="D60" t="s">
         <v>53</v>
       </c>
       <c r="E60">
-        <v>2.016762312365275</v>
+        <v>1.911452955562554</v>
       </c>
       <c r="F60">
         <v>-1</v>
       </c>
       <c r="G60">
-        <v>0.004235056554967666</v>
+        <v>0.004677944086088398</v>
       </c>
       <c r="H60">
-        <v>0.003943237687634725</v>
+        <v>0.004248547044437446</v>
       </c>
       <c r="I60">
-        <v>0.2681811326670585</v>
+        <v>0.2506029583490479</v>
       </c>
       <c r="J60">
-        <v>0.5909433666470703</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K60">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="L60">
-        <v>3.26</v>
+        <v>3.42</v>
       </c>
       <c r="M60">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="N60">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="O60">
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B61" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C61">
-        <v>2.226294399372918</v>
+        <v>2.153742896061194</v>
       </c>
       <c r="D61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E61">
-        <v>1.998573639035861</v>
+        <v>1.911452955562554</v>
       </c>
       <c r="F61">
         <v>-1</v>
       </c>
       <c r="G61">
-        <v>0.004613705600627082</v>
+        <v>0.004746257103938807</v>
       </c>
       <c r="H61">
-        <v>0.004161426360964139</v>
+        <v>0.004248547044437446</v>
       </c>
       <c r="I61">
-        <v>0.2277207603370566</v>
+        <v>0.2422899404986398</v>
       </c>
       <c r="J61">
-        <v>0.5909433666470703</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K61">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="L61">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="M61">
         <v>1.83</v>
@@ -3850,145 +3790,145 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:16">
       <c r="A62" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B62" t="s">
         <v>27</v>
       </c>
       <c r="C62">
-        <v>2.250384965706448</v>
+        <v>2.122703049542399</v>
       </c>
       <c r="D62" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="E62">
-        <v>1.998573639035861</v>
+        <v>2.1327030495424</v>
       </c>
       <c r="F62">
         <v>-1</v>
       </c>
       <c r="G62">
-        <v>0.004649615034293553</v>
+        <v>0.004397296950457601</v>
       </c>
       <c r="H62">
-        <v>0.004161426360964139</v>
+        <v>0.0044072969504576</v>
       </c>
       <c r="I62">
-        <v>0.2518113266705861</v>
+        <v>-0.01000000000000068</v>
       </c>
       <c r="J62">
-        <v>0.5909433666470703</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K62">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="L62">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="M62">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="N62">
-        <v>3.08</v>
+        <v>3.27</v>
       </c>
       <c r="O62">
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" spans="1:16">
       <c r="A63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B63" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C63">
-        <v>2.206392009113778</v>
+        <v>2.062136368241531</v>
       </c>
       <c r="D63" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E63">
-        <v>1.894705026964186</v>
+        <v>1.818634291310661</v>
       </c>
       <c r="F63">
         <v>-1</v>
       </c>
       <c r="G63">
-        <v>0.004313607990886223</v>
+        <v>0.004777863631758469</v>
       </c>
       <c r="H63">
-        <v>0.003925294973035814</v>
+        <v>0.004341365708689339</v>
       </c>
       <c r="I63">
-        <v>0.3116869821495918</v>
+        <v>0.24350207693087</v>
       </c>
       <c r="J63">
-        <v>0.6385502975068013</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K63">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="L63">
-        <v>3.26</v>
+        <v>3.42</v>
       </c>
       <c r="M63">
-        <v>1.59</v>
+        <v>1.83</v>
       </c>
       <c r="N63">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="O63">
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C64">
-        <v>2.130128399036261</v>
+        <v>2.050780115497619</v>
       </c>
       <c r="D64" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E64">
-        <v>1.911452955562554</v>
+        <v>1.818634291310661</v>
       </c>
       <c r="F64">
         <v>-1</v>
       </c>
       <c r="G64">
-        <v>0.004709871600963739</v>
+        <v>0.004849219884502381</v>
       </c>
       <c r="H64">
-        <v>0.004248547044437446</v>
+        <v>0.004341365708689339</v>
       </c>
       <c r="I64">
-        <v>0.2186754434737077</v>
+        <v>0.2321458241869578</v>
       </c>
       <c r="J64">
-        <v>0.6385502975068013</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K64">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="L64">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="M64">
         <v>1.83</v>
@@ -4000,45 +3940,45 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C65">
-        <v>2.153742896061194</v>
+        <v>1.960646887966805</v>
       </c>
       <c r="D65" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E65">
-        <v>1.911452955562554</v>
+        <v>1.724357261410788</v>
       </c>
       <c r="F65">
         <v>-1</v>
       </c>
       <c r="G65">
-        <v>0.004746257103938807</v>
+        <v>0.004879353112033196</v>
       </c>
       <c r="H65">
-        <v>0.004248547044437446</v>
+        <v>0.004435642738589212</v>
       </c>
       <c r="I65">
-        <v>0.2422899404986398</v>
+        <v>0.2362896265560166</v>
       </c>
       <c r="J65">
-        <v>0.6385502975068013</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K65">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="L65">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="M65">
         <v>1.83</v>
@@ -4050,45 +3990,45 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B66" t="s">
         <v>30</v>
       </c>
       <c r="C66">
-        <v>2.062136368241531</v>
+        <v>1.946199585062241</v>
       </c>
       <c r="D66" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E66">
-        <v>1.818634291310661</v>
+        <v>1.724357261410788</v>
       </c>
       <c r="F66">
         <v>-1</v>
       </c>
       <c r="G66">
-        <v>0.004777863631758469</v>
+        <v>0.00495380041493776</v>
       </c>
       <c r="H66">
-        <v>0.004341365708689339</v>
+        <v>0.004435642738589212</v>
       </c>
       <c r="I66">
-        <v>0.24350207693087</v>
+        <v>0.2218423236514526</v>
       </c>
       <c r="J66">
-        <v>0.6892708790652124</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K66">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="L66">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="M66">
         <v>1.83</v>
@@ -4100,45 +4040,45 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:16">
       <c r="A67" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C67">
-        <v>2.050780115497619</v>
+        <v>1.843540306843175</v>
       </c>
       <c r="D67" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E67">
-        <v>1.818634291310661</v>
+        <v>1.615572975392391</v>
       </c>
       <c r="F67">
         <v>-1</v>
       </c>
       <c r="G67">
-        <v>0.004849219884502381</v>
+        <v>0.004996459693156825</v>
       </c>
       <c r="H67">
-        <v>0.004341365708689339</v>
+        <v>0.00454442702460761</v>
       </c>
       <c r="I67">
-        <v>0.2321458241869578</v>
+        <v>0.227967331450784</v>
       </c>
       <c r="J67">
-        <v>0.6892708790652124</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K67">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="L67">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="M67">
         <v>1.83</v>
@@ -4150,45 +4090,45 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:16">
       <c r="A68" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B68" t="s">
         <v>30</v>
       </c>
       <c r="C68">
-        <v>1.960646887966805</v>
+        <v>1.825526306036369</v>
       </c>
       <c r="D68" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E68">
-        <v>1.724357261410788</v>
+        <v>1.615572975392391</v>
       </c>
       <c r="F68">
         <v>-1</v>
       </c>
       <c r="G68">
-        <v>0.004879353112033196</v>
+        <v>0.005074473693963632</v>
       </c>
       <c r="H68">
-        <v>0.004435642738589212</v>
+        <v>0.00454442702460761</v>
       </c>
       <c r="I68">
-        <v>0.2362896265560166</v>
+        <v>0.2099533306439776</v>
       </c>
       <c r="J68">
-        <v>0.7407883817427386</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K68">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="L68">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="M68">
         <v>1.83</v>
@@ -4200,89 +4140,89 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C69">
-        <v>1.946199585062241</v>
+        <v>1.364830842322013</v>
       </c>
       <c r="D69" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E69">
-        <v>1.724357261410788</v>
+        <v>1.554057700011381</v>
       </c>
       <c r="F69">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G69">
-        <v>0.00495380041493776</v>
+        <v>0.005255169157677987</v>
       </c>
       <c r="H69">
-        <v>0.004435642738589212</v>
+        <v>0.004645942299988619</v>
       </c>
       <c r="I69">
-        <v>0.2218423236514526</v>
+        <v>0.1892268576893685</v>
       </c>
       <c r="J69">
-        <v>0.7407883817427386</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K69">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="L69">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="M69">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="N69">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="O69">
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B70" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C70">
-        <v>1.843540306843175</v>
+        <v>1.746644873089242</v>
       </c>
       <c r="D70" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E70">
-        <v>1.615572975392391</v>
+        <v>1.552668119243339</v>
       </c>
       <c r="F70">
         <v>-1</v>
       </c>
       <c r="G70">
-        <v>0.004996459693156825</v>
+        <v>0.005093355126910757</v>
       </c>
       <c r="H70">
-        <v>0.00454442702460761</v>
+        <v>0.004967331880756661</v>
       </c>
       <c r="I70">
-        <v>0.227967331450784</v>
+        <v>0.1939767538459036</v>
       </c>
       <c r="J70">
-        <v>0.8002333467801142</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K70">
         <v>1.97</v>
@@ -4291,166 +4231,166 @@
         <v>3.42</v>
       </c>
       <c r="M70">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="N70">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="O70">
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C71">
-        <v>1.825526306036369</v>
+        <v>1.253223538131198</v>
       </c>
       <c r="D71" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E71">
-        <v>1.615572975392391</v>
+        <v>1.465356698427415</v>
       </c>
       <c r="F71">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G71">
-        <v>0.005074473693963632</v>
+        <v>0.005366776461868803</v>
       </c>
       <c r="H71">
-        <v>0.00454442702460761</v>
+        <v>0.004734643301572585</v>
       </c>
       <c r="I71">
-        <v>0.2099533306439776</v>
+        <v>0.2121331602962171</v>
       </c>
       <c r="J71">
-        <v>0.8002333467801142</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K71">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="L71">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="M71">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="N71">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="O71">
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C72">
-        <v>1.364830842322013</v>
+        <v>1.650633349396707</v>
       </c>
       <c r="D72" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E72">
-        <v>1.554057700011381</v>
+        <v>1.454707122988519</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G72">
-        <v>0.005255169157677987</v>
+        <v>0.005189366650603293</v>
       </c>
       <c r="H72">
-        <v>0.004645942299988619</v>
+        <v>0.005065292877011481</v>
       </c>
       <c r="I72">
-        <v>0.1892268576893685</v>
+        <v>0.1959262264081887</v>
       </c>
       <c r="J72">
-        <v>0.8494188461475927</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K72">
-        <v>2.29</v>
+        <v>1.97</v>
       </c>
       <c r="L72">
-        <v>3.31</v>
+        <v>3.42</v>
       </c>
       <c r="M72">
-        <v>1.82</v>
+        <v>2.01</v>
       </c>
       <c r="N72">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="O72">
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C73">
-        <v>1.746644873089242</v>
+        <v>1.142741567826858</v>
       </c>
       <c r="D73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E73">
-        <v>1.525563511549905</v>
+        <v>1.377550067006499</v>
       </c>
       <c r="F73">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>0.005093355126910757</v>
+        <v>0.005477258432173141</v>
       </c>
       <c r="H73">
-        <v>0.004634436488450095</v>
+        <v>0.004822449932993502</v>
       </c>
       <c r="I73">
-        <v>0.221081361539337</v>
+        <v>0.2348084991796402</v>
       </c>
       <c r="J73">
-        <v>0.8494188461475927</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K73">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="L73">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="M73">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="N73">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="O73">
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4458,31 +4398,31 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C74">
-        <v>1.253223538131198</v>
+        <v>1.02473295176371</v>
       </c>
       <c r="D74" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E74">
-        <v>1.465356698427415</v>
+        <v>1.28376155991701</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74">
-        <v>0.005366776461868803</v>
+        <v>0.005595267048236289</v>
       </c>
       <c r="H74">
-        <v>0.004734643301572585</v>
+        <v>0.004916238440082991</v>
       </c>
       <c r="I74">
-        <v>0.2121331602962171</v>
+        <v>0.2590286081532995</v>
       </c>
       <c r="J74">
-        <v>0.898155660204717</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K74">
         <v>2.29</v>
@@ -4500,57 +4440,57 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C75">
-        <v>1.650633349396707</v>
+        <v>0.9555784956116042</v>
       </c>
       <c r="D75" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E75">
-        <v>1.454707122988519</v>
+        <v>1.228800376424943</v>
       </c>
       <c r="F75">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G75">
-        <v>0.005189366650603293</v>
+        <v>0.005664421504388396</v>
       </c>
       <c r="H75">
-        <v>0.005065292877011481</v>
+        <v>0.004971199623575057</v>
       </c>
       <c r="I75">
-        <v>0.1959262264081887</v>
+        <v>0.2732218808133391</v>
       </c>
       <c r="J75">
-        <v>0.898155660204717</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K75">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="L75">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="M75">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="N75">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="O75">
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4561,34 +4501,34 @@
         <v>32</v>
       </c>
       <c r="C76">
-        <v>1.142741567826858</v>
+        <v>0.95505474527386</v>
       </c>
       <c r="D76" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E76">
-        <v>1.377550067006499</v>
+        <v>1.172750932925077</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76">
-        <v>0.005477258432173141</v>
+        <v>0.00580494525472614</v>
       </c>
       <c r="H76">
-        <v>0.004822449932993502</v>
+        <v>0.005027249067074924</v>
       </c>
       <c r="I76">
-        <v>0.2348084991796402</v>
+        <v>0.2176961876512167</v>
       </c>
       <c r="J76">
-        <v>0.9464010620843414</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K76">
         <v>2.29</v>
       </c>
       <c r="L76">
-        <v>3.31</v>
+        <v>3.38</v>
       </c>
       <c r="M76">
         <v>1.82</v>
@@ -4600,7 +4540,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4611,34 +4551,34 @@
         <v>32</v>
       </c>
       <c r="C77">
-        <v>1.02473295176371</v>
+        <v>0.8997461387005035</v>
       </c>
       <c r="D77" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E77">
-        <v>1.28376155991701</v>
+        <v>1.128793874425728</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77">
-        <v>0.005595267048236289</v>
+        <v>0.005860253861299496</v>
       </c>
       <c r="H77">
-        <v>0.004916238440082991</v>
+        <v>0.005071206125574273</v>
       </c>
       <c r="I77">
-        <v>0.2590286081532995</v>
+        <v>0.2290477357252241</v>
       </c>
       <c r="J77">
-        <v>0.9979332088368078</v>
+        <v>1.083080288777073</v>
       </c>
       <c r="K77">
         <v>2.29</v>
       </c>
       <c r="L77">
-        <v>3.31</v>
+        <v>3.38</v>
       </c>
       <c r="M77">
         <v>1.82</v>
@@ -4650,7 +4590,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4661,34 +4601,34 @@
         <v>32</v>
       </c>
       <c r="C78">
-        <v>0.9555784956116042</v>
+        <v>0.9004291893178089</v>
       </c>
       <c r="D78" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E78">
-        <v>1.228800376424943</v>
+        <v>1.129336735615027</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="G78">
-        <v>0.005664421504388396</v>
+        <v>0.005859570810682191</v>
       </c>
       <c r="H78">
-        <v>0.004971199623575057</v>
+        <v>0.005070663264384973</v>
       </c>
       <c r="I78">
-        <v>0.2732218808133391</v>
+        <v>0.2289075462972185</v>
       </c>
       <c r="J78">
-        <v>1.028131661304976</v>
+        <v>1.082782013398337</v>
       </c>
       <c r="K78">
         <v>2.29</v>
       </c>
       <c r="L78">
-        <v>3.31</v>
+        <v>3.38</v>
       </c>
       <c r="M78">
         <v>1.82</v>
@@ -4700,7 +4640,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4708,31 +4648,31 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C79">
-        <v>0.95505474527386</v>
+        <v>0.8995341152947529</v>
       </c>
       <c r="D79" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E79">
-        <v>1.172750932925077</v>
+        <v>1.128625366740808</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="G79">
-        <v>0.00580494525472614</v>
+        <v>0.005860465884705247</v>
       </c>
       <c r="H79">
-        <v>0.005027249067074924</v>
+        <v>0.005071374633259193</v>
       </c>
       <c r="I79">
-        <v>0.2176961876512167</v>
+        <v>0.2290912514460552</v>
       </c>
       <c r="J79">
-        <v>1.058928058832376</v>
+        <v>1.083172875417138</v>
       </c>
       <c r="K79">
         <v>2.29</v>
@@ -4750,7 +4690,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -4758,31 +4698,31 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C80">
-        <v>0.8997461387005035</v>
+        <v>0.8942975364165378</v>
       </c>
       <c r="D80" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E80">
-        <v>1.128793874425728</v>
+        <v>1.124463544226244</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80">
-        <v>0.005860253861299496</v>
+        <v>0.005865702463583462</v>
       </c>
       <c r="H80">
-        <v>0.005071206125574273</v>
+        <v>0.005075536455773756</v>
       </c>
       <c r="I80">
-        <v>0.2290477357252241</v>
+        <v>0.2301660078097063</v>
       </c>
       <c r="J80">
-        <v>1.083080288777073</v>
+        <v>1.085459591084481</v>
       </c>
       <c r="K80">
         <v>2.29</v>
@@ -4800,7 +4740,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -4808,31 +4748,31 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C81">
-        <v>0.9004291893178089</v>
+        <v>0.823882990348408</v>
       </c>
       <c r="D81" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E81">
-        <v>1.129336735615027</v>
+        <v>1.068500891892621</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="G81">
-        <v>0.005859570810682191</v>
+        <v>0.005936117009651592</v>
       </c>
       <c r="H81">
-        <v>0.005070663264384973</v>
+        <v>0.005131499108107379</v>
       </c>
       <c r="I81">
-        <v>0.2289075462972185</v>
+        <v>0.2446179015442134</v>
       </c>
       <c r="J81">
-        <v>1.082782013398337</v>
+        <v>1.1162083011579</v>
       </c>
       <c r="K81">
         <v>2.29</v>
@@ -4850,7 +4790,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -4858,31 +4798,31 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C82">
-        <v>0.8995341152947529</v>
+        <v>0.7552208383877499</v>
       </c>
       <c r="D82" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E82">
-        <v>1.128625366740808</v>
+        <v>1.013930971993758</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82">
-        <v>0.005860465884705247</v>
+        <v>0.00600477916161225</v>
       </c>
       <c r="H82">
-        <v>0.005071374633259193</v>
+        <v>0.005186069028006243</v>
       </c>
       <c r="I82">
-        <v>0.2290912514460552</v>
+        <v>0.2587101336060078</v>
       </c>
       <c r="J82">
-        <v>1.083172875417138</v>
+        <v>1.146191773629804</v>
       </c>
       <c r="K82">
         <v>2.29</v>
@@ -4900,7 +4840,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -4908,31 +4848,31 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C83">
-        <v>0.8942975364165378</v>
+        <v>0.7164672131147527</v>
       </c>
       <c r="D83" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E83">
-        <v>1.124463544226244</v>
+        <v>0.9831311475409823</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83">
-        <v>0.005865702463583462</v>
+        <v>0.006043532786885248</v>
       </c>
       <c r="H83">
-        <v>0.005075536455773756</v>
+        <v>0.005216868852459018</v>
       </c>
       <c r="I83">
-        <v>0.2301660078097063</v>
+        <v>0.2666639344262296</v>
       </c>
       <c r="J83">
-        <v>1.085459591084481</v>
+        <v>1.163114754098361</v>
       </c>
       <c r="K83">
         <v>2.29</v>
@@ -4950,7 +4890,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -4958,31 +4898,31 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C84">
-        <v>0.823882990348408</v>
+        <v>0.6498239504652852</v>
       </c>
       <c r="D84" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E84">
-        <v>1.068500891892621</v>
+        <v>0.9301657597584363</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84">
-        <v>0.005936117009651592</v>
+        <v>0.006110176049534715</v>
       </c>
       <c r="H84">
-        <v>0.005131499108107379</v>
+        <v>0.005269834240241564</v>
       </c>
       <c r="I84">
-        <v>0.2446179015442134</v>
+        <v>0.2803418092931511</v>
       </c>
       <c r="J84">
-        <v>1.1162083011579</v>
+        <v>1.192216615517343</v>
       </c>
       <c r="K84">
         <v>2.29</v>
@@ -5000,7 +4940,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5011,78 +4951,78 @@
         <v>33</v>
       </c>
       <c r="C85">
-        <v>0.7552208383877499</v>
+        <v>0.5205928926738919</v>
       </c>
       <c r="D85" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="E85">
-        <v>1.013930971993758</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85">
-        <v>0.00600477916161225</v>
+        <v>0.006459407107326108</v>
       </c>
       <c r="H85">
-        <v>0.005186069028006243</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I85">
-        <v>0.2587101336060078</v>
+        <v>-0.1165511301853397</v>
       </c>
       <c r="J85">
-        <v>1.146191773629804</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K85">
+        <v>2.34</v>
+      </c>
+      <c r="L85">
+        <v>3.49</v>
+      </c>
+      <c r="M85">
         <v>2.29</v>
       </c>
-      <c r="L85">
-        <v>3.38</v>
-      </c>
-      <c r="M85">
-        <v>1.82</v>
-      </c>
       <c r="N85">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="O85">
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B86" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C86">
-        <v>0.7164672131147527</v>
+        <v>0.474041762488552</v>
       </c>
       <c r="D86" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="E86">
-        <v>0.9831311475409823</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86">
-        <v>0.006043532786885248</v>
+        <v>0.006285958237511447</v>
       </c>
       <c r="H86">
-        <v>0.005216868852459018</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I86">
-        <v>0.2666639344262296</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J86">
-        <v>1.163114754098361</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K86">
         <v>2.29</v>
@@ -5091,16 +5031,16 @@
         <v>3.38</v>
       </c>
       <c r="M86">
-        <v>1.82</v>
+        <v>2.29</v>
       </c>
       <c r="N86">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="O86">
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5111,40 +5051,40 @@
         <v>33</v>
       </c>
       <c r="C87">
-        <v>0.6498239504652852</v>
+        <v>0.3774746016246668</v>
       </c>
       <c r="D87" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="E87">
-        <v>0.9301657597584363</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87">
-        <v>0.006110176049534715</v>
+        <v>0.006602525398375333</v>
       </c>
       <c r="H87">
-        <v>0.005269834240241564</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I87">
-        <v>0.2803418092931511</v>
+        <v>-0.1134930470432627</v>
       </c>
       <c r="J87">
-        <v>1.192216615517343</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K87">
+        <v>2.34</v>
+      </c>
+      <c r="L87">
+        <v>3.49</v>
+      </c>
+      <c r="M87">
         <v>2.29</v>
       </c>
-      <c r="L87">
-        <v>3.38</v>
-      </c>
-      <c r="M87">
-        <v>1.82</v>
-      </c>
       <c r="N87">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="O87">
         <v>1</v>
@@ -5155,40 +5095,40 @@
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C88">
-        <v>0.5205928926738919</v>
+        <v>0.333981554581404</v>
       </c>
       <c r="D88" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E88">
-        <v>0.4040417624885522</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88">
-        <v>0.006459407107326108</v>
+        <v>0.006426018445418596</v>
       </c>
       <c r="H88">
-        <v>0.006215958237511448</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I88">
-        <v>-0.1165511301853397</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J88">
-        <v>1.268977396293209</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K88">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="L88">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="M88">
         <v>2.29</v>
@@ -5200,45 +5140,45 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>102</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89" spans="1:16">
       <c r="A89" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B89" t="s">
         <v>33</v>
       </c>
       <c r="C89">
-        <v>0.474041762488552</v>
+        <v>0.2442505289553791</v>
       </c>
       <c r="D89" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E89">
-        <v>0.4040417624885522</v>
+        <v>0.1336041501315459</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89">
-        <v>0.006285958237511447</v>
+        <v>0.006735749471044622</v>
       </c>
       <c r="H89">
-        <v>0.006215958237511448</v>
+        <v>0.006486395849868455</v>
       </c>
       <c r="I89">
-        <v>-0.06999999999999984</v>
+        <v>-0.1106463788238332</v>
       </c>
       <c r="J89">
-        <v>1.268977396293209</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K89">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="L89">
-        <v>3.38</v>
+        <v>3.49</v>
       </c>
       <c r="M89">
         <v>2.29</v>
@@ -5250,45 +5190,45 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B90" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C90">
-        <v>0.3774746016246668</v>
+        <v>0.2036041501315458</v>
       </c>
       <c r="D90" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E90">
-        <v>0.2639815545814042</v>
+        <v>0.1336041501315459</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90">
-        <v>0.006602525398375333</v>
+        <v>0.006556395849868454</v>
       </c>
       <c r="H90">
-        <v>0.006356018445418596</v>
+        <v>0.006486395849868455</v>
       </c>
       <c r="I90">
-        <v>-0.1134930470432627</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J90">
-        <v>1.330139059134758</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K90">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="L90">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="M90">
         <v>2.29</v>
@@ -5300,57 +5240,57 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>29</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B91" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C91">
-        <v>0.333981554581404</v>
+        <v>0.2977942894248136</v>
       </c>
       <c r="D91" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E91">
-        <v>0.2639815545814042</v>
+        <v>0.5755281891875166</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="G91">
-        <v>0.006426018445418596</v>
+        <v>0.006262205710575186</v>
       </c>
       <c r="H91">
-        <v>0.006356018445418596</v>
+        <v>0.005624471810812484</v>
       </c>
       <c r="I91">
-        <v>-0.06999999999999984</v>
+        <v>0.277733899762703</v>
       </c>
       <c r="J91">
-        <v>1.330139059134758</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K91">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="L91">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="M91">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="N91">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="O91">
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>29</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5358,49 +5298,49 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C92">
-        <v>0.2442505289553791</v>
+        <v>1.851150997400674</v>
       </c>
       <c r="D92" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E92">
-        <v>0.1336041501315459</v>
+        <v>1.622642804691997</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G92">
-        <v>0.006735749471044622</v>
+        <v>0.004988849002599325</v>
       </c>
       <c r="H92">
-        <v>0.006486395849868455</v>
+        <v>0.004537357195308004</v>
       </c>
       <c r="I92">
-        <v>-0.1106463788238332</v>
+        <v>0.2285081927086774</v>
       </c>
       <c r="J92">
-        <v>1.387072423523342</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K92">
-        <v>2.34</v>
+        <v>1.97</v>
       </c>
       <c r="L92">
-        <v>3.49</v>
+        <v>3.42</v>
       </c>
       <c r="M92">
-        <v>2.29</v>
+        <v>1.83</v>
       </c>
       <c r="N92">
-        <v>3.31</v>
+        <v>3.08</v>
       </c>
       <c r="O92">
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5408,99 +5348,99 @@
         <v>1</v>
       </c>
       <c r="B93" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C93">
-        <v>0.2036041501315458</v>
+        <v>1.833368794275822</v>
       </c>
       <c r="D93" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E93">
-        <v>0.1336041501315459</v>
+        <v>1.622642804691997</v>
       </c>
       <c r="F93">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G93">
-        <v>0.006556395849868454</v>
+        <v>0.005066631205724178</v>
       </c>
       <c r="H93">
-        <v>0.006486395849868455</v>
+        <v>0.004537357195308004</v>
       </c>
       <c r="I93">
-        <v>-0.06999999999999984</v>
+        <v>0.2107259895838252</v>
       </c>
       <c r="J93">
-        <v>1.387072423523342</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K93">
-        <v>2.29</v>
+        <v>2.03</v>
       </c>
       <c r="L93">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="M93">
-        <v>2.29</v>
+        <v>1.83</v>
       </c>
       <c r="N93">
-        <v>3.31</v>
+        <v>3.08</v>
       </c>
       <c r="O93">
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="94" spans="1:16">
       <c r="A94" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C94">
-        <v>0.2977942894248136</v>
+        <v>1.825554329597634</v>
       </c>
       <c r="D94" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E94">
-        <v>0.5755281891875166</v>
+        <v>1.61559823801166</v>
       </c>
       <c r="F94">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G94">
-        <v>0.006262205710575186</v>
+        <v>0.005074445670402367</v>
       </c>
       <c r="H94">
-        <v>0.005624471810812484</v>
+        <v>0.00454440176198834</v>
       </c>
       <c r="I94">
-        <v>0.277733899762703</v>
+        <v>0.2099560915859742</v>
       </c>
       <c r="J94">
-        <v>1.387072423523342</v>
+        <v>0.8002195420701311</v>
       </c>
       <c r="K94">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="L94">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="M94">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="N94">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="O94">
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>103</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5511,34 +5451,34 @@
         <v>30</v>
       </c>
       <c r="C95">
-        <v>1.851150997400674</v>
+        <v>1.814964366537685</v>
       </c>
       <c r="D95" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E95">
-        <v>1.622642804691997</v>
+        <v>1.606051621065991</v>
       </c>
       <c r="F95">
         <v>-1</v>
       </c>
       <c r="G95">
-        <v>0.004988849002599325</v>
+        <v>0.005085035633462316</v>
       </c>
       <c r="H95">
-        <v>0.004537357195308004</v>
+        <v>0.004553948378934009</v>
       </c>
       <c r="I95">
-        <v>0.2285081927086774</v>
+        <v>0.2089127454716935</v>
       </c>
       <c r="J95">
-        <v>0.7963700520808761</v>
+        <v>0.8054362726415348</v>
       </c>
       <c r="K95">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="L95">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="M95">
         <v>1.83</v>
@@ -5550,39 +5490,39 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96" spans="1:16">
       <c r="A96" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C96">
-        <v>1.833368794275822</v>
+        <v>1.80276175127278</v>
       </c>
       <c r="D96" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E96">
-        <v>1.622642804691997</v>
+        <v>1.595051233906003</v>
       </c>
       <c r="F96">
         <v>-1</v>
       </c>
       <c r="G96">
-        <v>0.005066631205724178</v>
+        <v>0.005097238248727221</v>
       </c>
       <c r="H96">
-        <v>0.004537357195308004</v>
+        <v>0.004564948766093997</v>
       </c>
       <c r="I96">
-        <v>0.2107259895838252</v>
+        <v>0.2077105173667766</v>
       </c>
       <c r="J96">
-        <v>0.7963700520808761</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K96">
         <v>2.03</v>
@@ -5600,45 +5540,45 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97" spans="1:16">
       <c r="A97" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B97" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C97">
-        <v>1.825554329597634</v>
+        <v>1.766532803009457</v>
       </c>
       <c r="D97" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E97">
-        <v>1.61559823801166</v>
+        <v>1.595051233906003</v>
       </c>
       <c r="F97">
         <v>-1</v>
       </c>
       <c r="G97">
-        <v>0.005074445670402367</v>
+        <v>0.005093467196990544</v>
       </c>
       <c r="H97">
-        <v>0.00454440176198834</v>
+        <v>0.004564948766093997</v>
       </c>
       <c r="I97">
-        <v>0.2099560915859742</v>
+        <v>0.1714815691034541</v>
       </c>
       <c r="J97">
-        <v>0.8002195420701311</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K97">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="L97">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="M97">
         <v>1.83</v>
@@ -5650,7 +5590,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5658,31 +5598,31 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C98">
-        <v>1.814964366537685</v>
+        <v>1.799355758249058</v>
       </c>
       <c r="D98" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E98">
-        <v>1.606051621065991</v>
+        <v>1.591980806697426</v>
       </c>
       <c r="F98">
         <v>-1</v>
       </c>
       <c r="G98">
-        <v>0.005085035633462316</v>
+        <v>0.005100644241750943</v>
       </c>
       <c r="H98">
-        <v>0.004553948378934009</v>
+        <v>0.004568019193302574</v>
       </c>
       <c r="I98">
-        <v>0.2089127454716935</v>
+        <v>0.2073749515516314</v>
       </c>
       <c r="J98">
-        <v>0.8054362726415348</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K98">
         <v>2.03</v>
@@ -5700,7 +5640,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5708,31 +5648,31 @@
         <v>1</v>
       </c>
       <c r="B99" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C99">
-        <v>1.778855641084854</v>
+        <v>1.763093253404221</v>
       </c>
       <c r="D99" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E99">
-        <v>1.606051621065991</v>
+        <v>1.591980806697426</v>
       </c>
       <c r="F99">
         <v>-1</v>
       </c>
       <c r="G99">
-        <v>0.005081144358915147</v>
+        <v>0.00509690674659578</v>
       </c>
       <c r="H99">
-        <v>0.004553948378934009</v>
+        <v>0.004568019193302574</v>
       </c>
       <c r="I99">
-        <v>0.1728040200188627</v>
+        <v>0.1711124467067946</v>
       </c>
       <c r="J99">
-        <v>0.8054362726415348</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K99">
         <v>2.05</v>
@@ -5750,7 +5690,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -5758,37 +5698,37 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C100">
-        <v>1.80276175127278</v>
+        <v>1.758945050051923</v>
       </c>
       <c r="D100" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E100">
-        <v>1.595051233906003</v>
+        <v>1.588277776387814</v>
       </c>
       <c r="F100">
         <v>-1</v>
       </c>
       <c r="G100">
-        <v>0.005097238248727221</v>
+        <v>0.005101054949948077</v>
       </c>
       <c r="H100">
-        <v>0.004564948766093997</v>
+        <v>0.004571722223612186</v>
       </c>
       <c r="I100">
-        <v>0.2077105173667766</v>
+        <v>0.1706672736641091</v>
       </c>
       <c r="J100">
-        <v>0.8114474131661186</v>
+        <v>0.8151487560722326</v>
       </c>
       <c r="K100">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="L100">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="M100">
         <v>1.83</v>
@@ -5800,39 +5740,39 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C101">
-        <v>1.766532803009457</v>
+        <v>1.750849917183753</v>
       </c>
       <c r="D101" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E101">
-        <v>1.595051233906003</v>
+        <v>1.571905533403557</v>
       </c>
       <c r="F101">
         <v>-1</v>
       </c>
       <c r="G101">
-        <v>0.005093467196990544</v>
+        <v>0.005109150082816248</v>
       </c>
       <c r="H101">
-        <v>0.004564948766093997</v>
+        <v>0.004668094466596443</v>
       </c>
       <c r="I101">
-        <v>0.1714815691034541</v>
+        <v>0.1789443837801954</v>
       </c>
       <c r="J101">
-        <v>0.8114474131661186</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K101">
         <v>2.05</v>
@@ -5841,10 +5781,10 @@
         <v>3.43</v>
       </c>
       <c r="M101">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="N101">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="O101">
         <v>1</v>
@@ -5858,43 +5798,43 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C102">
-        <v>1.799355758249058</v>
+        <v>1.732368893145465</v>
       </c>
       <c r="D102" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E102">
-        <v>1.591980806697426</v>
+        <v>1.574988827473004</v>
       </c>
       <c r="F102">
         <v>-1</v>
       </c>
       <c r="G102">
-        <v>0.005100644241750943</v>
+        <v>0.005067631106854534</v>
       </c>
       <c r="H102">
-        <v>0.004568019193302574</v>
+        <v>0.004665011172526996</v>
       </c>
       <c r="I102">
-        <v>0.2073749515516314</v>
+        <v>0.1573800656724604</v>
       </c>
       <c r="J102">
-        <v>0.8131252422418436</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K102">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="L102">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="M102">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="N102">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="O102">
         <v>1</v>
@@ -5908,31 +5848,31 @@
         <v>1</v>
       </c>
       <c r="B103" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C103">
-        <v>1.763093253404221</v>
+        <v>1.754194230856962</v>
       </c>
       <c r="D103" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E103">
-        <v>1.591980806697426</v>
+        <v>1.574988827473004</v>
       </c>
       <c r="F103">
         <v>-1</v>
       </c>
       <c r="G103">
-        <v>0.00509690674659578</v>
+        <v>0.005105805769143037</v>
       </c>
       <c r="H103">
-        <v>0.004568019193302574</v>
+        <v>0.004665011172526996</v>
       </c>
       <c r="I103">
-        <v>0.1711124467067946</v>
+        <v>0.1792054033839581</v>
       </c>
       <c r="J103">
-        <v>0.8131252422418436</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K103">
         <v>2.05</v>
@@ -5941,10 +5881,10 @@
         <v>3.43</v>
       </c>
       <c r="M103">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="N103">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="O103">
         <v>1</v>
@@ -5958,31 +5898,31 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C104">
-        <v>1.758945050051923</v>
+        <v>1.755052845867249</v>
       </c>
       <c r="D104" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E104">
-        <v>1.579368851023481</v>
+        <v>1.57578042862883</v>
       </c>
       <c r="F104">
         <v>-1</v>
       </c>
       <c r="G104">
-        <v>0.005101054949948077</v>
+        <v>0.005104947154132751</v>
       </c>
       <c r="H104">
-        <v>0.00466063114897652</v>
+        <v>0.00466421957137117</v>
       </c>
       <c r="I104">
-        <v>0.1795761990284428</v>
+        <v>0.1792724172384195</v>
       </c>
       <c r="J104">
-        <v>0.8151487560722326</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K104">
         <v>2.05</v>
@@ -6000,7 +5940,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6011,40 +5951,40 @@
         <v>37</v>
       </c>
       <c r="C105">
-        <v>1.72904089319749</v>
+        <v>1.740014143224429</v>
       </c>
       <c r="D105" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E105">
-        <v>1.571905533403557</v>
+        <v>1.823363933674754</v>
       </c>
       <c r="F105">
         <v>-1</v>
       </c>
       <c r="G105">
-        <v>0.00507095910680251</v>
+        <v>0.005079985856775571</v>
       </c>
       <c r="H105">
-        <v>0.004668094466596443</v>
+        <v>0.005336636066325246</v>
       </c>
       <c r="I105">
-        <v>0.1571353597939327</v>
+        <v>-0.0833497904503242</v>
       </c>
       <c r="J105">
-        <v>0.8190976013737793</v>
+        <v>0.7877291777243258</v>
       </c>
       <c r="K105">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="L105">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="M105">
-        <v>1.89</v>
+        <v>2.23</v>
       </c>
       <c r="N105">
-        <v>3.12</v>
+        <v>3.58</v>
       </c>
       <c r="O105">
         <v>1</v>
@@ -6061,40 +6001,40 @@
         <v>37</v>
       </c>
       <c r="C106">
-        <v>1.732368893145465</v>
+        <v>1.740936473690798</v>
       </c>
       <c r="D106" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E106">
-        <v>1.574988827473004</v>
+        <v>1.824334120910604</v>
       </c>
       <c r="F106">
         <v>-1</v>
       </c>
       <c r="G106">
-        <v>0.005067631106854534</v>
+        <v>0.005079063526309202</v>
       </c>
       <c r="H106">
-        <v>0.004665011172526996</v>
+        <v>0.005335665879089396</v>
       </c>
       <c r="I106">
-        <v>0.1573800656724604</v>
+        <v>-0.08339764721980569</v>
       </c>
       <c r="J106">
-        <v>0.8174662288502623</v>
+        <v>0.7872941161835857</v>
       </c>
       <c r="K106">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="L106">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="M106">
-        <v>1.89</v>
+        <v>2.23</v>
       </c>
       <c r="N106">
-        <v>3.12</v>
+        <v>3.58</v>
       </c>
       <c r="O106">
         <v>1</v>
@@ -6108,43 +6048,43 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C107">
-        <v>1.697534484639878</v>
+        <v>1.737999731721985</v>
       </c>
       <c r="D107" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E107">
-        <v>1.561011377500918</v>
+        <v>1.821245000820767</v>
       </c>
       <c r="F107">
         <v>-1</v>
       </c>
       <c r="G107">
-        <v>0.004842465515360122</v>
+        <v>0.005082000268278016</v>
       </c>
       <c r="H107">
-        <v>0.004478988622499082</v>
+        <v>0.005338754999179234</v>
       </c>
       <c r="I107">
-        <v>0.1365231071389603</v>
+        <v>-0.08324526909878238</v>
       </c>
       <c r="J107">
-        <v>0.8105492347217125</v>
+        <v>0.7886793718292525</v>
       </c>
       <c r="K107">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="L107">
-        <v>3.27</v>
+        <v>3.41</v>
       </c>
       <c r="M107">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="N107">
-        <v>3.02</v>
+        <v>3.58</v>
       </c>
       <c r="O107">
         <v>1</v>
@@ -6158,43 +6098,43 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C108">
-        <v>1.703024477239647</v>
+        <v>1.735312288398669</v>
       </c>
       <c r="D108" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E108">
-        <v>1.566105185067714</v>
+        <v>1.818418114683505</v>
       </c>
       <c r="F108">
         <v>-1</v>
       </c>
       <c r="G108">
-        <v>0.004836975522760354</v>
+        <v>0.005084687711601332</v>
       </c>
       <c r="H108">
-        <v>0.004473894814932287</v>
+        <v>0.005341581885316495</v>
       </c>
       <c r="I108">
-        <v>0.1369192921719335</v>
+        <v>-0.08310582628483654</v>
       </c>
       <c r="J108">
-        <v>0.8077193416290479</v>
+        <v>0.7899470337742129</v>
       </c>
       <c r="K108">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="L108">
-        <v>3.27</v>
+        <v>3.41</v>
       </c>
       <c r="M108">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="N108">
-        <v>3.02</v>
+        <v>3.58</v>
       </c>
       <c r="O108">
         <v>1</v>
@@ -6208,43 +6148,43 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C109">
-        <v>1.706762500295012</v>
+        <v>1.734303254574541</v>
       </c>
       <c r="D109" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E109">
-        <v>1.56957345388197</v>
+        <v>1.817356725330768</v>
       </c>
       <c r="F109">
         <v>-1</v>
       </c>
       <c r="G109">
-        <v>0.004833237499704988</v>
+        <v>0.005085696745425459</v>
       </c>
       <c r="H109">
-        <v>0.004470426546118031</v>
+        <v>0.005342643274669232</v>
       </c>
       <c r="I109">
-        <v>0.1371890464130423</v>
+        <v>-0.08305347075622627</v>
       </c>
       <c r="J109">
-        <v>0.8057925256211278</v>
+        <v>0.7904229931252164</v>
       </c>
       <c r="K109">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="L109">
-        <v>3.27</v>
+        <v>3.41</v>
       </c>
       <c r="M109">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="N109">
-        <v>3.02</v>
+        <v>3.58</v>
       </c>
       <c r="O109">
         <v>1</v>
@@ -6261,40 +6201,40 @@
         <v>38</v>
       </c>
       <c r="C110">
-        <v>1.711603744119008</v>
+        <v>1.720598225993867</v>
       </c>
       <c r="D110" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E110">
-        <v>1.574065329594956</v>
+        <v>1.567308310528363</v>
       </c>
       <c r="F110">
         <v>-1</v>
       </c>
       <c r="G110">
-        <v>0.004828396255880993</v>
+        <v>0.004679401774006134</v>
       </c>
       <c r="H110">
-        <v>0.004465934670405044</v>
+        <v>0.004652691689471636</v>
       </c>
       <c r="I110">
-        <v>0.1375384145240521</v>
+        <v>0.1532899154655032</v>
       </c>
       <c r="J110">
-        <v>0.8032970391139135</v>
+        <v>0.791123943318788</v>
       </c>
       <c r="K110">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="L110">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="M110">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="N110">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="O110">
         <v>1</v>
@@ -6305,52 +6245,52 @@
     </row>
     <row r="111" spans="1:16">
       <c r="A111" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B111" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C111">
-        <v>1.702699397711841</v>
+        <v>1.732817240164169</v>
       </c>
       <c r="D111" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E111">
-        <v>1.58060202641754</v>
+        <v>1.815793606399103</v>
       </c>
       <c r="F111">
         <v>-1</v>
       </c>
       <c r="G111">
-        <v>0.004697300602288159</v>
+        <v>0.005087182759835831</v>
       </c>
       <c r="H111">
-        <v>0.00479939797358246</v>
+        <v>0.005344206393600897</v>
       </c>
       <c r="I111">
-        <v>0.1220973712943008</v>
+        <v>-0.08297636623493343</v>
       </c>
       <c r="J111">
-        <v>0.8006955092450049</v>
+        <v>0.791123943318788</v>
       </c>
       <c r="K111">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="L111">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="M111">
-        <v>2.01</v>
+        <v>2.23</v>
       </c>
       <c r="N111">
-        <v>3.19</v>
+        <v>3.58</v>
       </c>
       <c r="O111">
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6358,31 +6298,31 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C112">
-        <v>1.706549065306413</v>
+        <v>1.719739270136877</v>
       </c>
       <c r="D112" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E112">
-        <v>1.584739904420262</v>
+        <v>1.566412607896743</v>
       </c>
       <c r="F112">
         <v>-1</v>
       </c>
       <c r="G112">
-        <v>0.004693450934693588</v>
+        <v>0.004680260729863123</v>
       </c>
       <c r="H112">
-        <v>0.004795260095579738</v>
+        <v>0.004653587392103257</v>
       </c>
       <c r="I112">
-        <v>0.1218091608861507</v>
+        <v>0.1533266622401337</v>
       </c>
       <c r="J112">
-        <v>0.7986368634725065</v>
+        <v>0.7915832780016702</v>
       </c>
       <c r="K112">
         <v>1.87</v>
@@ -6391,66 +6331,66 @@
         <v>3.2</v>
       </c>
       <c r="M112">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="N112">
-        <v>3.19</v>
+        <v>3.11</v>
       </c>
       <c r="O112">
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="113" spans="1:16">
       <c r="A113" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B113" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C113">
-        <v>1.715081561736875</v>
+        <v>1.731843450636459</v>
       </c>
       <c r="D113" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E113">
-        <v>1.59391119737493</v>
+        <v>1.814769290056276</v>
       </c>
       <c r="F113">
         <v>-1</v>
       </c>
       <c r="G113">
-        <v>0.004684918438263125</v>
+        <v>0.005088156549363541</v>
       </c>
       <c r="H113">
-        <v>0.00478608880262507</v>
+        <v>0.005345230709943724</v>
       </c>
       <c r="I113">
-        <v>0.1211703643619453</v>
+        <v>-0.08292583941981624</v>
       </c>
       <c r="J113">
-        <v>0.7940740311567515</v>
+        <v>0.7915832780016702</v>
       </c>
       <c r="K113">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="L113">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="M113">
-        <v>2.01</v>
+        <v>2.23</v>
       </c>
       <c r="N113">
-        <v>3.19</v>
+        <v>3.58</v>
       </c>
       <c r="O113">
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6458,31 +6398,31 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C114">
-        <v>1.724215665563157</v>
+        <v>1.720624811893301</v>
       </c>
       <c r="D114" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E114">
-        <v>1.603729137851308</v>
+        <v>1.567336033792479</v>
       </c>
       <c r="F114">
         <v>-1</v>
       </c>
       <c r="G114">
-        <v>0.004675784334436843</v>
+        <v>0.004679375188106701</v>
       </c>
       <c r="H114">
-        <v>0.004776270862148693</v>
+        <v>0.004652663966207521</v>
       </c>
       <c r="I114">
-        <v>0.1204865277118492</v>
+        <v>0.1532887781008216</v>
       </c>
       <c r="J114">
-        <v>0.7891894836560657</v>
+        <v>0.7911097262602672</v>
       </c>
       <c r="K114">
         <v>1.87</v>
@@ -6491,66 +6431,66 @@
         <v>3.2</v>
       </c>
       <c r="M114">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="N114">
-        <v>3.19</v>
+        <v>3.11</v>
       </c>
       <c r="O114">
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>112</v>
+        <v>50</v>
       </c>
     </row>
     <row r="115" spans="1:16">
       <c r="A115" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B115" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C115">
-        <v>1.726739382920171</v>
+        <v>1.732847380328234</v>
       </c>
       <c r="D115" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E115">
-        <v>1.573712190745633</v>
+        <v>1.815825310439604</v>
       </c>
       <c r="F115">
         <v>-1</v>
       </c>
       <c r="G115">
-        <v>0.00467326061707983</v>
+        <v>0.005087152619671767</v>
       </c>
       <c r="H115">
-        <v>0.004646287809254367</v>
+        <v>0.005344174689560396</v>
       </c>
       <c r="I115">
-        <v>0.1530271921745383</v>
+        <v>-0.08297793011137067</v>
       </c>
       <c r="J115">
-        <v>0.7878399021817268</v>
+        <v>0.7911097262602672</v>
       </c>
       <c r="K115">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="L115">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="M115">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="N115">
-        <v>3.11</v>
+        <v>3.58</v>
       </c>
       <c r="O115">
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6558,31 +6498,31 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C116">
-        <v>1.726946437655511</v>
+        <v>1.721822046417237</v>
       </c>
       <c r="D116" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E116">
-        <v>1.573928103437565</v>
+        <v>1.568584486905675</v>
       </c>
       <c r="F116">
         <v>-1</v>
       </c>
       <c r="G116">
-        <v>0.004673053562344489</v>
+        <v>0.004678177953582763</v>
       </c>
       <c r="H116">
-        <v>0.004646071896562435</v>
+        <v>0.004651415513094326</v>
       </c>
       <c r="I116">
-        <v>0.1530183342179463</v>
+        <v>0.1532375595115623</v>
       </c>
       <c r="J116">
-        <v>0.7877291777243258</v>
+        <v>0.7904694938945258</v>
       </c>
       <c r="K116">
         <v>1.87</v>
@@ -6600,57 +6540,57 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="117" spans="1:16">
       <c r="A117" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B117" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C117">
-        <v>1.727760002736695</v>
+        <v>1.734204672943605</v>
       </c>
       <c r="D117" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E117">
-        <v>1.574776473442008</v>
+        <v>1.817253028615208</v>
       </c>
       <c r="F117">
         <v>-1</v>
       </c>
       <c r="G117">
-        <v>0.004672239997263306</v>
+        <v>0.005085795327056396</v>
       </c>
       <c r="H117">
-        <v>0.004645223526557992</v>
+        <v>0.005342746971384794</v>
       </c>
       <c r="I117">
-        <v>0.1529835292946871</v>
+        <v>-0.08304835567160218</v>
       </c>
       <c r="J117">
-        <v>0.7872941161835857</v>
+        <v>0.7904694938945258</v>
       </c>
       <c r="K117">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="L117">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="M117">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="N117">
-        <v>3.11</v>
+        <v>3.58</v>
       </c>
       <c r="O117">
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6658,49 +6598,49 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C118">
-        <v>1.706716749552468</v>
+        <v>1.72428138280355</v>
       </c>
       <c r="D118" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E118">
-        <v>1.579395987242713</v>
+        <v>1.571149035543809</v>
       </c>
       <c r="F118">
         <v>-1</v>
       </c>
       <c r="G118">
-        <v>0.004593283250447533</v>
+        <v>0.00467571861719645</v>
       </c>
       <c r="H118">
-        <v>0.004560604012757288</v>
+        <v>0.004648850964456191</v>
       </c>
       <c r="I118">
-        <v>0.1273207623097552</v>
+        <v>0.1531323472597415</v>
       </c>
       <c r="J118">
-        <v>0.7886793718292525</v>
+        <v>0.7891543407467646</v>
       </c>
       <c r="K118">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="L118">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="M118">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="N118">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="O118">
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6708,49 +6648,49 @@
         <v>1</v>
       </c>
       <c r="B119" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C119">
-        <v>1.725169574679298</v>
+        <v>1.736992797616859</v>
       </c>
       <c r="D119" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E119">
-        <v>1.572075224932957</v>
+        <v>1.820185820134715</v>
       </c>
       <c r="F119">
         <v>-1</v>
       </c>
       <c r="G119">
-        <v>0.004674830425320703</v>
+        <v>0.005083007202383142</v>
       </c>
       <c r="H119">
-        <v>0.004647924775067042</v>
+        <v>0.005339814179865285</v>
       </c>
       <c r="I119">
-        <v>0.1530943497463404</v>
+        <v>-0.08319302251785587</v>
       </c>
       <c r="J119">
-        <v>0.7886793718292525</v>
+        <v>0.7891543407467646</v>
       </c>
       <c r="K119">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="L119">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="M119">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="N119">
-        <v>3.11</v>
+        <v>3.58</v>
       </c>
       <c r="O119">
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -6758,49 +6698,49 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C120">
-        <v>1.70439692819319</v>
+        <v>1.727206229285669</v>
       </c>
       <c r="D120" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E120">
-        <v>1.577000106166737</v>
+        <v>1.574199009148157</v>
       </c>
       <c r="F120">
         <v>-1</v>
       </c>
       <c r="G120">
-        <v>0.00459560307180681</v>
+        <v>0.004672793770714332</v>
       </c>
       <c r="H120">
-        <v>0.004562999893833262</v>
+        <v>0.004645800990851843</v>
       </c>
       <c r="I120">
-        <v>0.1273968220264527</v>
+        <v>0.1530072201375119</v>
       </c>
       <c r="J120">
-        <v>0.7899470337742129</v>
+        <v>0.7875902517188939</v>
       </c>
       <c r="K120">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="L120">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="M120">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="N120">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="O120">
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -6808,49 +6748,49 @@
         <v>1</v>
       </c>
       <c r="B121" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C121">
-        <v>1.722799046842222</v>
+        <v>1.740308666355945</v>
       </c>
       <c r="D121" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E121">
-        <v>1.569603284140285</v>
+        <v>1.823673738666867</v>
       </c>
       <c r="F121">
         <v>-1</v>
       </c>
       <c r="G121">
-        <v>0.004677200953157779</v>
+        <v>0.005079691333644055</v>
       </c>
       <c r="H121">
-        <v>0.004650396715859715</v>
+        <v>0.005336326261333134</v>
       </c>
       <c r="I121">
-        <v>0.1531957627019371</v>
+        <v>-0.08336507231092183</v>
       </c>
       <c r="J121">
-        <v>0.7899470337742129</v>
+        <v>0.7875902517188939</v>
       </c>
       <c r="K121">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="L121">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="M121">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="N121">
-        <v>3.11</v>
+        <v>3.58</v>
       </c>
       <c r="O121">
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -6858,31 +6798,31 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C122">
-        <v>1.721909002855845</v>
+        <v>1.728676249745893</v>
       </c>
       <c r="D122" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E122">
-        <v>1.568675163405828</v>
+        <v>1.57573191818422</v>
       </c>
       <c r="F122">
         <v>-1</v>
       </c>
       <c r="G122">
-        <v>0.004678090997144155</v>
+        <v>0.004671323750254107</v>
       </c>
       <c r="H122">
-        <v>0.004651324836594172</v>
+        <v>0.00464426808181578</v>
       </c>
       <c r="I122">
-        <v>0.1532338394500175</v>
+        <v>0.1529443315616732</v>
       </c>
       <c r="J122">
-        <v>0.7904229931252164</v>
+        <v>0.7868041445209126</v>
       </c>
       <c r="K122">
         <v>1.87</v>
@@ -6900,57 +6840,57 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
     </row>
     <row r="123" spans="1:16">
       <c r="A123" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B123" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C123">
-        <v>1.720598225993867</v>
+        <v>1.741975213615665</v>
       </c>
       <c r="D123" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E123">
-        <v>1.567308310528363</v>
+        <v>1.825426757718365</v>
       </c>
       <c r="F123">
         <v>-1</v>
       </c>
       <c r="G123">
-        <v>0.004679401774006134</v>
+        <v>0.005078024786384335</v>
       </c>
       <c r="H123">
-        <v>0.004652691689471636</v>
+        <v>0.005334573242281635</v>
       </c>
       <c r="I123">
-        <v>0.1532899154655032</v>
+        <v>-0.08345154410269973</v>
       </c>
       <c r="J123">
-        <v>0.791123943318788</v>
+        <v>0.7868041445209126</v>
       </c>
       <c r="K123">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="L123">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="M123">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="N123">
-        <v>3.11</v>
+        <v>3.58</v>
       </c>
       <c r="O123">
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -6958,31 +6898,31 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C124">
-        <v>1.719739270136877</v>
+        <v>1.731283335374008</v>
       </c>
       <c r="D124" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E124">
-        <v>1.566412607896743</v>
+        <v>1.578450536887334</v>
       </c>
       <c r="F124">
         <v>-1</v>
       </c>
       <c r="G124">
-        <v>0.004680260729863123</v>
+        <v>0.004668716664625992</v>
       </c>
       <c r="H124">
-        <v>0.004653587392103257</v>
+        <v>0.004641549463112665</v>
       </c>
       <c r="I124">
-        <v>0.1533266622401337</v>
+        <v>0.1528327984866735</v>
       </c>
       <c r="J124">
-        <v>0.7915832780016702</v>
+        <v>0.7854099810834182</v>
       </c>
       <c r="K124">
         <v>1.87</v>
@@ -7000,57 +6940,57 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="125" spans="1:16">
       <c r="A125" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B125" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C125">
-        <v>1.720624811893301</v>
+        <v>1.744930840103154</v>
       </c>
       <c r="D125" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E125">
-        <v>1.567336033792479</v>
+        <v>1.828535742183977</v>
       </c>
       <c r="F125">
         <v>-1</v>
       </c>
       <c r="G125">
-        <v>0.004679375188106701</v>
+        <v>0.005075069159896847</v>
       </c>
       <c r="H125">
-        <v>0.004652663966207521</v>
+        <v>0.005331464257816023</v>
       </c>
       <c r="I125">
-        <v>0.1532887781008216</v>
+        <v>-0.08360490208082383</v>
       </c>
       <c r="J125">
-        <v>0.7911097262602672</v>
+        <v>0.7854099810834182</v>
       </c>
       <c r="K125">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="L125">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="M125">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="N125">
-        <v>3.11</v>
+        <v>3.58</v>
       </c>
       <c r="O125">
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>52</v>
+        <v>116</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7058,49 +6998,49 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C126">
-        <v>1.721822046417237</v>
+        <v>1.748898482014188</v>
       </c>
       <c r="D126" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E126">
-        <v>1.568584486905675</v>
+        <v>1.832709252307377</v>
       </c>
       <c r="F126">
         <v>-1</v>
       </c>
       <c r="G126">
-        <v>0.004678177953582763</v>
+        <v>0.005071101517985812</v>
       </c>
       <c r="H126">
-        <v>0.004651415513094326</v>
+        <v>0.005327290747692623</v>
       </c>
       <c r="I126">
-        <v>0.1532375595115623</v>
+        <v>-0.08381077029318895</v>
       </c>
       <c r="J126">
-        <v>0.7904694938945258</v>
+        <v>0.7835384518800999</v>
       </c>
       <c r="K126">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="L126">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="M126">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="N126">
-        <v>3.11</v>
+        <v>3.58</v>
       </c>
       <c r="O126">
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7108,49 +7048,49 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C127">
-        <v>1.72428138280355</v>
+        <v>1.749965012157894</v>
       </c>
       <c r="D127" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E127">
-        <v>1.571149035543809</v>
+        <v>1.833831121279294</v>
       </c>
       <c r="F127">
         <v>-1</v>
       </c>
       <c r="G127">
-        <v>0.00467571861719645</v>
+        <v>0.005070034987842107</v>
       </c>
       <c r="H127">
-        <v>0.004648850964456191</v>
+        <v>0.005326168878720706</v>
       </c>
       <c r="I127">
-        <v>0.1531323472597415</v>
+        <v>-0.08386610912140013</v>
       </c>
       <c r="J127">
-        <v>0.7891543407467646</v>
+        <v>0.783035371623635</v>
       </c>
       <c r="K127">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="L127">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="M127">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="N127">
-        <v>3.11</v>
+        <v>3.58</v>
       </c>
       <c r="O127">
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7158,49 +7098,49 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C128">
-        <v>1.727206229285669</v>
+        <v>1.751367516070874</v>
       </c>
       <c r="D128" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E128">
-        <v>1.574199009148157</v>
+        <v>1.835306396621721</v>
       </c>
       <c r="F128">
         <v>-1</v>
       </c>
       <c r="G128">
-        <v>0.004672793770714332</v>
+        <v>0.005068632483929126</v>
       </c>
       <c r="H128">
-        <v>0.004645800990851843</v>
+        <v>0.005324693603378279</v>
       </c>
       <c r="I128">
-        <v>0.1530072201375119</v>
+        <v>-0.08393888055084719</v>
       </c>
       <c r="J128">
-        <v>0.7875902517188939</v>
+        <v>0.7823738131741161</v>
       </c>
       <c r="K128">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="L128">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="M128">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="N128">
-        <v>3.11</v>
+        <v>3.58</v>
       </c>
       <c r="O128">
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7208,49 +7148,49 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C129">
-        <v>1.728676249745893</v>
+        <v>1.754470592394443</v>
       </c>
       <c r="D129" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E129">
-        <v>1.57573191818422</v>
+        <v>1.838570481622456</v>
       </c>
       <c r="F129">
         <v>-1</v>
       </c>
       <c r="G129">
-        <v>0.004671323750254107</v>
+        <v>0.005065529407605558</v>
       </c>
       <c r="H129">
-        <v>0.00464426808181578</v>
+        <v>0.005321429518377544</v>
       </c>
       <c r="I129">
-        <v>0.1529443315616732</v>
+        <v>-0.08409988922801359</v>
       </c>
       <c r="J129">
-        <v>0.7868041445209126</v>
+        <v>0.7809100979271496</v>
       </c>
       <c r="K129">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="L129">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="M129">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="N129">
-        <v>3.11</v>
+        <v>3.58</v>
       </c>
       <c r="O129">
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7258,49 +7198,49 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C130">
-        <v>1.731283335374008</v>
+        <v>1.756079279241895</v>
       </c>
       <c r="D130" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E130">
-        <v>1.578450536887334</v>
+        <v>1.840262638070484</v>
       </c>
       <c r="F130">
         <v>-1</v>
       </c>
       <c r="G130">
-        <v>0.004668716664625992</v>
+        <v>0.005063920720758106</v>
       </c>
       <c r="H130">
-        <v>0.004641549463112665</v>
+        <v>0.005319737361929516</v>
       </c>
       <c r="I130">
-        <v>0.1528327984866735</v>
+        <v>-0.08418335882858896</v>
       </c>
       <c r="J130">
-        <v>0.7854099810834182</v>
+        <v>0.7801512833764644</v>
       </c>
       <c r="K130">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="L130">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="M130">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="N130">
-        <v>3.11</v>
+        <v>3.58</v>
       </c>
       <c r="O130">
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>63</v>
+        <v>121</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7308,49 +7248,49 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C131">
-        <v>1.734783094984213</v>
+        <v>1.756919146594669</v>
       </c>
       <c r="D131" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E131">
-        <v>1.582100018833805</v>
+        <v>1.841146083446279</v>
       </c>
       <c r="F131">
         <v>-1</v>
       </c>
       <c r="G131">
-        <v>0.004665216905015787</v>
+        <v>0.005063080853405332</v>
       </c>
       <c r="H131">
-        <v>0.004637899981166194</v>
+        <v>0.005318853916553721</v>
       </c>
       <c r="I131">
-        <v>0.1526830761504081</v>
+        <v>-0.0842269368516102</v>
       </c>
       <c r="J131">
-        <v>0.7835384518800999</v>
+        <v>0.7797551195308166</v>
       </c>
       <c r="K131">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="L131">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="M131">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="N131">
-        <v>3.11</v>
+        <v>3.58</v>
       </c>
       <c r="O131">
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7358,999 +7298,49 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C132">
-        <v>1.735723855063803</v>
+        <v>1.758227892855127</v>
       </c>
       <c r="D132" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E132">
-        <v>1.583081025333912</v>
+        <v>1.842522736352327</v>
       </c>
       <c r="F132">
         <v>-1</v>
       </c>
       <c r="G132">
-        <v>0.004664276144936198</v>
+        <v>0.005061772107144873</v>
       </c>
       <c r="H132">
-        <v>0.004636918974666088</v>
+        <v>0.005317477263647673</v>
       </c>
       <c r="I132">
-        <v>0.152642829729891</v>
+        <v>-0.08429484349719996</v>
       </c>
       <c r="J132">
-        <v>0.783035371623635</v>
+        <v>0.7791377863890909</v>
       </c>
       <c r="K132">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="L132">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="M132">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="N132">
-        <v>3.11</v>
+        <v>3.58</v>
       </c>
       <c r="O132">
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16">
-      <c r="A133" s="1">
-        <v>0</v>
-      </c>
-      <c r="B133" t="s">
-        <v>39</v>
-      </c>
-      <c r="C133">
-        <v>1.736960969364403</v>
-      </c>
-      <c r="D133" t="s">
-        <v>62</v>
-      </c>
-      <c r="E133">
-        <v>1.584371064310473</v>
-      </c>
-      <c r="F133">
-        <v>-1</v>
-      </c>
-      <c r="G133">
-        <v>0.004663039030635597</v>
-      </c>
-      <c r="H133">
-        <v>0.004635628935689527</v>
-      </c>
-      <c r="I133">
-        <v>0.1525899050539294</v>
-      </c>
-      <c r="J133">
-        <v>0.7823738131741161</v>
-      </c>
-      <c r="K133">
-        <v>1.87</v>
-      </c>
-      <c r="L133">
-        <v>3.2</v>
-      </c>
-      <c r="M133">
-        <v>1.95</v>
-      </c>
-      <c r="N133">
-        <v>3.11</v>
-      </c>
-      <c r="O133">
-        <v>1</v>
-      </c>
-      <c r="P133" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16">
-      <c r="A134" s="1">
-        <v>0</v>
-      </c>
-      <c r="B134" t="s">
-        <v>39</v>
-      </c>
-      <c r="C134">
-        <v>1.73969811687623</v>
-      </c>
-      <c r="D134" t="s">
-        <v>62</v>
-      </c>
-      <c r="E134">
-        <v>1.587225309042058</v>
-      </c>
-      <c r="F134">
-        <v>-1</v>
-      </c>
-      <c r="G134">
-        <v>0.004660301883123771</v>
-      </c>
-      <c r="H134">
-        <v>0.004632774690957941</v>
-      </c>
-      <c r="I134">
-        <v>0.1524728078341722</v>
-      </c>
-      <c r="J134">
-        <v>0.7809100979271496</v>
-      </c>
-      <c r="K134">
-        <v>1.87</v>
-      </c>
-      <c r="L134">
-        <v>3.2</v>
-      </c>
-      <c r="M134">
-        <v>1.95</v>
-      </c>
-      <c r="N134">
-        <v>3.11</v>
-      </c>
-      <c r="O134">
-        <v>1</v>
-      </c>
-      <c r="P134" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16">
-      <c r="A135" s="1">
-        <v>0</v>
-      </c>
-      <c r="B135" t="s">
-        <v>39</v>
-      </c>
-      <c r="C135">
-        <v>1.741117100086012</v>
-      </c>
-      <c r="D135" t="s">
-        <v>62</v>
-      </c>
-      <c r="E135">
-        <v>1.588704997415894</v>
-      </c>
-      <c r="F135">
-        <v>-1</v>
-      </c>
-      <c r="G135">
-        <v>0.004658882899913989</v>
-      </c>
-      <c r="H135">
-        <v>0.004631295002584105</v>
-      </c>
-      <c r="I135">
-        <v>0.1524121026701173</v>
-      </c>
-      <c r="J135">
-        <v>0.7801512833764644</v>
-      </c>
-      <c r="K135">
-        <v>1.87</v>
-      </c>
-      <c r="L135">
-        <v>3.2</v>
-      </c>
-      <c r="M135">
-        <v>1.95</v>
-      </c>
-      <c r="N135">
-        <v>3.11</v>
-      </c>
-      <c r="O135">
-        <v>1</v>
-      </c>
-      <c r="P135" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="136" spans="1:16">
-      <c r="A136" s="1">
-        <v>0</v>
-      </c>
-      <c r="B136" t="s">
-        <v>39</v>
-      </c>
-      <c r="C136">
-        <v>1.741857926477373</v>
-      </c>
-      <c r="D136" t="s">
-        <v>62</v>
-      </c>
-      <c r="E136">
-        <v>1.589477516914908</v>
-      </c>
-      <c r="F136">
-        <v>-1</v>
-      </c>
-      <c r="G136">
-        <v>0.004658142073522628</v>
-      </c>
-      <c r="H136">
-        <v>0.004630522483085092</v>
-      </c>
-      <c r="I136">
-        <v>0.1523804095624655</v>
-      </c>
-      <c r="J136">
-        <v>0.7797551195308166</v>
-      </c>
-      <c r="K136">
-        <v>1.87</v>
-      </c>
-      <c r="L136">
-        <v>3.2</v>
-      </c>
-      <c r="M136">
-        <v>1.95</v>
-      </c>
-      <c r="N136">
-        <v>3.11</v>
-      </c>
-      <c r="O136">
-        <v>1</v>
-      </c>
-      <c r="P136" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16">
-      <c r="A137" s="1">
-        <v>0</v>
-      </c>
-      <c r="B137" t="s">
-        <v>39</v>
-      </c>
-      <c r="C137">
-        <v>1.7430123394524</v>
-      </c>
-      <c r="D137" t="s">
-        <v>62</v>
-      </c>
-      <c r="E137">
-        <v>1.590681316541273</v>
-      </c>
-      <c r="F137">
-        <v>-1</v>
-      </c>
-      <c r="G137">
-        <v>0.004656987660547601</v>
-      </c>
-      <c r="H137">
-        <v>0.004629318683458727</v>
-      </c>
-      <c r="I137">
-        <v>0.1523310229111274</v>
-      </c>
-      <c r="J137">
-        <v>0.7791377863890909</v>
-      </c>
-      <c r="K137">
-        <v>1.87</v>
-      </c>
-      <c r="L137">
-        <v>3.2</v>
-      </c>
-      <c r="M137">
-        <v>1.95</v>
-      </c>
-      <c r="N137">
-        <v>3.11</v>
-      </c>
-      <c r="O137">
-        <v>1</v>
-      </c>
-      <c r="P137" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="138" spans="1:16">
-      <c r="A138" s="1">
-        <v>0</v>
-      </c>
-      <c r="B138" t="s">
-        <v>39</v>
-      </c>
-      <c r="C138">
-        <v>1.745259534195844</v>
-      </c>
-      <c r="D138" t="s">
-        <v>62</v>
-      </c>
-      <c r="E138">
-        <v>1.593024647958233</v>
-      </c>
-      <c r="F138">
-        <v>-1</v>
-      </c>
-      <c r="G138">
-        <v>0.004654740465804157</v>
-      </c>
-      <c r="H138">
-        <v>0.004626975352041767</v>
-      </c>
-      <c r="I138">
-        <v>0.1522348862376111</v>
-      </c>
-      <c r="J138">
-        <v>0.777936077970137</v>
-      </c>
-      <c r="K138">
-        <v>1.87</v>
-      </c>
-      <c r="L138">
-        <v>3.2</v>
-      </c>
-      <c r="M138">
-        <v>1.95</v>
-      </c>
-      <c r="N138">
-        <v>3.11</v>
-      </c>
-      <c r="O138">
-        <v>1</v>
-      </c>
-      <c r="P138" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16">
-      <c r="A139" s="1">
-        <v>0</v>
-      </c>
-      <c r="B139" t="s">
-        <v>39</v>
-      </c>
-      <c r="C139">
-        <v>1.746411489484559</v>
-      </c>
-      <c r="D139" t="s">
-        <v>62</v>
-      </c>
-      <c r="E139">
-        <v>1.594225884756626</v>
-      </c>
-      <c r="F139">
-        <v>-1</v>
-      </c>
-      <c r="G139">
-        <v>0.004653588510515442</v>
-      </c>
-      <c r="H139">
-        <v>0.004625774115243374</v>
-      </c>
-      <c r="I139">
-        <v>0.1521856047279335</v>
-      </c>
-      <c r="J139">
-        <v>0.7773200590991663</v>
-      </c>
-      <c r="K139">
-        <v>1.87</v>
-      </c>
-      <c r="L139">
-        <v>3.2</v>
-      </c>
-      <c r="M139">
-        <v>1.95</v>
-      </c>
-      <c r="N139">
-        <v>3.11</v>
-      </c>
-      <c r="O139">
-        <v>1</v>
-      </c>
-      <c r="P139" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="140" spans="1:16">
-      <c r="A140" s="1">
-        <v>0</v>
-      </c>
-      <c r="B140" t="s">
-        <v>39</v>
-      </c>
-      <c r="C140">
-        <v>1.748527788884446</v>
-      </c>
-      <c r="D140" t="s">
-        <v>62</v>
-      </c>
-      <c r="E140">
-        <v>1.596432721029235</v>
-      </c>
-      <c r="F140">
-        <v>-1</v>
-      </c>
-      <c r="G140">
-        <v>0.004651472211115554</v>
-      </c>
-      <c r="H140">
-        <v>0.004623567278970764</v>
-      </c>
-      <c r="I140">
-        <v>0.1520950678552111</v>
-      </c>
-      <c r="J140">
-        <v>0.7761883481901358</v>
-      </c>
-      <c r="K140">
-        <v>1.87</v>
-      </c>
-      <c r="L140">
-        <v>3.2</v>
-      </c>
-      <c r="M140">
-        <v>1.95</v>
-      </c>
-      <c r="N140">
-        <v>3.11</v>
-      </c>
-      <c r="O140">
-        <v>1</v>
-      </c>
-      <c r="P140" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="141" spans="1:16">
-      <c r="A141" s="1">
-        <v>0</v>
-      </c>
-      <c r="B141" t="s">
-        <v>39</v>
-      </c>
-      <c r="C141">
-        <v>1.750999132580348</v>
-      </c>
-      <c r="D141" t="s">
-        <v>62</v>
-      </c>
-      <c r="E141">
-        <v>1.599009790658651</v>
-      </c>
-      <c r="F141">
-        <v>-1</v>
-      </c>
-      <c r="G141">
-        <v>0.004649000867419653</v>
-      </c>
-      <c r="H141">
-        <v>0.004620990209341349</v>
-      </c>
-      <c r="I141">
-        <v>0.1519893419216964</v>
-      </c>
-      <c r="J141">
-        <v>0.7748667740212044</v>
-      </c>
-      <c r="K141">
-        <v>1.87</v>
-      </c>
-      <c r="L141">
-        <v>3.2</v>
-      </c>
-      <c r="M141">
-        <v>1.95</v>
-      </c>
-      <c r="N141">
-        <v>3.11</v>
-      </c>
-      <c r="O141">
-        <v>1</v>
-      </c>
-      <c r="P141" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16">
-      <c r="A142" s="1">
-        <v>0</v>
-      </c>
-      <c r="B142" t="s">
-        <v>39</v>
-      </c>
-      <c r="C142">
-        <v>1.753450334202255</v>
-      </c>
-      <c r="D142" t="s">
-        <v>62</v>
-      </c>
-      <c r="E142">
-        <v>1.601565856521068</v>
-      </c>
-      <c r="F142">
-        <v>-1</v>
-      </c>
-      <c r="G142">
-        <v>0.004646549665797745</v>
-      </c>
-      <c r="H142">
-        <v>0.004618434143478931</v>
-      </c>
-      <c r="I142">
-        <v>0.1518844776811872</v>
-      </c>
-      <c r="J142">
-        <v>0.7735559710148369</v>
-      </c>
-      <c r="K142">
-        <v>1.87</v>
-      </c>
-      <c r="L142">
-        <v>3.2</v>
-      </c>
-      <c r="M142">
-        <v>1.95</v>
-      </c>
-      <c r="N142">
-        <v>3.11</v>
-      </c>
-      <c r="O142">
-        <v>1</v>
-      </c>
-      <c r="P142" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16">
-      <c r="A143" s="1">
-        <v>0</v>
-      </c>
-      <c r="B143" t="s">
-        <v>39</v>
-      </c>
-      <c r="C143">
-        <v>1.754939802540862</v>
-      </c>
-      <c r="D143" t="s">
-        <v>62</v>
-      </c>
-      <c r="E143">
-        <v>1.60311904543031</v>
-      </c>
-      <c r="F143">
-        <v>-1</v>
-      </c>
-      <c r="G143">
-        <v>0.004645060197459139</v>
-      </c>
-      <c r="H143">
-        <v>0.00461688095456969</v>
-      </c>
-      <c r="I143">
-        <v>0.1518207571105517</v>
-      </c>
-      <c r="J143">
-        <v>0.7727594638818923</v>
-      </c>
-      <c r="K143">
-        <v>1.87</v>
-      </c>
-      <c r="L143">
-        <v>3.2</v>
-      </c>
-      <c r="M143">
-        <v>1.95</v>
-      </c>
-      <c r="N143">
-        <v>3.11</v>
-      </c>
-      <c r="O143">
-        <v>1</v>
-      </c>
-      <c r="P143" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16">
-      <c r="A144" s="1">
-        <v>0</v>
-      </c>
-      <c r="B144" t="s">
-        <v>39</v>
-      </c>
-      <c r="C144">
-        <v>1.755568315849489</v>
-      </c>
-      <c r="D144" t="s">
-        <v>62</v>
-      </c>
-      <c r="E144">
-        <v>1.603774447008826</v>
-      </c>
-      <c r="F144">
-        <v>-1</v>
-      </c>
-      <c r="G144">
-        <v>0.004644431684150511</v>
-      </c>
-      <c r="H144">
-        <v>0.004616225552991174</v>
-      </c>
-      <c r="I144">
-        <v>0.1517938688406637</v>
-      </c>
-      <c r="J144">
-        <v>0.7724233605082945</v>
-      </c>
-      <c r="K144">
-        <v>1.87</v>
-      </c>
-      <c r="L144">
-        <v>3.2</v>
-      </c>
-      <c r="M144">
-        <v>1.95</v>
-      </c>
-      <c r="N144">
-        <v>3.11</v>
-      </c>
-      <c r="O144">
-        <v>1</v>
-      </c>
-      <c r="P144" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16">
-      <c r="A145" s="1">
-        <v>0</v>
-      </c>
-      <c r="B145" t="s">
-        <v>39</v>
-      </c>
-      <c r="C145">
-        <v>1.755871060200726</v>
-      </c>
-      <c r="D145" t="s">
-        <v>62</v>
-      </c>
-      <c r="E145">
-        <v>1.604090142990061</v>
-      </c>
-      <c r="F145">
-        <v>-1</v>
-      </c>
-      <c r="G145">
-        <v>0.004644128939799275</v>
-      </c>
-      <c r="H145">
-        <v>0.004615909857009939</v>
-      </c>
-      <c r="I145">
-        <v>0.1517809172106643</v>
-      </c>
-      <c r="J145">
-        <v>0.7722614651333018</v>
-      </c>
-      <c r="K145">
-        <v>1.87</v>
-      </c>
-      <c r="L145">
-        <v>3.2</v>
-      </c>
-      <c r="M145">
-        <v>1.95</v>
-      </c>
-      <c r="N145">
-        <v>3.11</v>
-      </c>
-      <c r="O145">
-        <v>1</v>
-      </c>
-      <c r="P145" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16">
-      <c r="A146" s="1">
-        <v>0</v>
-      </c>
-      <c r="B146" t="s">
-        <v>39</v>
-      </c>
-      <c r="C146">
-        <v>1.755021860709565</v>
-      </c>
-      <c r="D146" t="s">
-        <v>62</v>
-      </c>
-      <c r="E146">
-        <v>1.603204614108905</v>
-      </c>
-      <c r="F146">
-        <v>-1</v>
-      </c>
-      <c r="G146">
-        <v>0.004644978139290435</v>
-      </c>
-      <c r="H146">
-        <v>0.004616795385891095</v>
-      </c>
-      <c r="I146">
-        <v>0.1518172466006604</v>
-      </c>
-      <c r="J146">
-        <v>0.772715582508254</v>
-      </c>
-      <c r="K146">
-        <v>1.87</v>
-      </c>
-      <c r="L146">
-        <v>3.2</v>
-      </c>
-      <c r="M146">
-        <v>1.95</v>
-      </c>
-      <c r="N146">
-        <v>3.11</v>
-      </c>
-      <c r="O146">
-        <v>1</v>
-      </c>
-      <c r="P146" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16">
-      <c r="A147" s="1">
-        <v>0</v>
-      </c>
-      <c r="B147" t="s">
-        <v>39</v>
-      </c>
-      <c r="C147">
-        <v>1.753276827162878</v>
-      </c>
-      <c r="D147" t="s">
-        <v>61</v>
-      </c>
-      <c r="E147">
-        <v>1.634966001388976</v>
-      </c>
-      <c r="F147">
-        <v>-1</v>
-      </c>
-      <c r="G147">
-        <v>0.004646723172837122</v>
-      </c>
-      <c r="H147">
-        <v>0.004745033998611024</v>
-      </c>
-      <c r="I147">
-        <v>0.1183108257739021</v>
-      </c>
-      <c r="J147">
-        <v>0.7736487555278725</v>
-      </c>
-      <c r="K147">
-        <v>1.87</v>
-      </c>
-      <c r="L147">
-        <v>3.2</v>
-      </c>
-      <c r="M147">
-        <v>2.01</v>
-      </c>
-      <c r="N147">
-        <v>3.19</v>
-      </c>
-      <c r="O147">
-        <v>1</v>
-      </c>
-      <c r="P147" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16">
-      <c r="A148" s="1">
-        <v>0</v>
-      </c>
-      <c r="B148" t="s">
-        <v>39</v>
-      </c>
-      <c r="C148">
-        <v>1.751466054533885</v>
-      </c>
-      <c r="D148" t="s">
-        <v>61</v>
-      </c>
-      <c r="E148">
-        <v>1.633019662894711</v>
-      </c>
-      <c r="F148">
-        <v>-1</v>
-      </c>
-      <c r="G148">
-        <v>0.004648533945466115</v>
-      </c>
-      <c r="H148">
-        <v>0.004746980337105289</v>
-      </c>
-      <c r="I148">
-        <v>0.1184463916391745</v>
-      </c>
-      <c r="J148">
-        <v>0.7746170831369599</v>
-      </c>
-      <c r="K148">
-        <v>1.87</v>
-      </c>
-      <c r="L148">
-        <v>3.2</v>
-      </c>
-      <c r="M148">
-        <v>2.01</v>
-      </c>
-      <c r="N148">
-        <v>3.19</v>
-      </c>
-      <c r="O148">
-        <v>1</v>
-      </c>
-      <c r="P148" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16">
-      <c r="A149" s="1">
-        <v>0</v>
-      </c>
-      <c r="B149" t="s">
-        <v>39</v>
-      </c>
-      <c r="C149">
-        <v>1.748327094900906</v>
-      </c>
-      <c r="D149" t="s">
-        <v>61</v>
-      </c>
-      <c r="E149">
-        <v>1.629645700936268</v>
-      </c>
-      <c r="F149">
-        <v>-1</v>
-      </c>
-      <c r="G149">
-        <v>0.004651672905099095</v>
-      </c>
-      <c r="H149">
-        <v>0.004750354299063732</v>
-      </c>
-      <c r="I149">
-        <v>0.1186813939646381</v>
-      </c>
-      <c r="J149">
-        <v>0.7762956711759863</v>
-      </c>
-      <c r="K149">
-        <v>1.87</v>
-      </c>
-      <c r="L149">
-        <v>3.2</v>
-      </c>
-      <c r="M149">
-        <v>2.01</v>
-      </c>
-      <c r="N149">
-        <v>3.19</v>
-      </c>
-      <c r="O149">
-        <v>1</v>
-      </c>
-      <c r="P149" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16">
-      <c r="A150" s="1">
-        <v>0</v>
-      </c>
-      <c r="B150" t="s">
-        <v>39</v>
-      </c>
-      <c r="C150">
-        <v>1.745110555324242</v>
-      </c>
-      <c r="D150" t="s">
-        <v>61</v>
-      </c>
-      <c r="E150">
-        <v>1.626188350910014</v>
-      </c>
-      <c r="F150">
-        <v>-1</v>
-      </c>
-      <c r="G150">
-        <v>0.004654889444675759</v>
-      </c>
-      <c r="H150">
-        <v>0.004753811649089986</v>
-      </c>
-      <c r="I150">
-        <v>0.118922204414228</v>
-      </c>
-      <c r="J150">
-        <v>0.7780157458159134</v>
-      </c>
-      <c r="K150">
-        <v>1.87</v>
-      </c>
-      <c r="L150">
-        <v>3.2</v>
-      </c>
-      <c r="M150">
-        <v>2.01</v>
-      </c>
-      <c r="N150">
-        <v>3.19</v>
-      </c>
-      <c r="O150">
-        <v>1</v>
-      </c>
-      <c r="P150" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="151" spans="1:16">
-      <c r="A151" s="1">
-        <v>0</v>
-      </c>
-      <c r="B151" t="s">
-        <v>39</v>
-      </c>
-      <c r="C151">
-        <v>1.743382145937803</v>
-      </c>
-      <c r="D151" t="s">
-        <v>61</v>
-      </c>
-      <c r="E151">
-        <v>1.624330541890366</v>
-      </c>
-      <c r="F151">
-        <v>-1</v>
-      </c>
-      <c r="G151">
-        <v>0.004656617854062197</v>
-      </c>
-      <c r="H151">
-        <v>0.004755669458109634</v>
-      </c>
-      <c r="I151">
-        <v>0.1190516040474372</v>
-      </c>
-      <c r="J151">
-        <v>0.7789400289102656</v>
-      </c>
-      <c r="K151">
-        <v>1.87</v>
-      </c>
-      <c r="L151">
-        <v>3.2</v>
-      </c>
-      <c r="M151">
-        <v>2.01</v>
-      </c>
-      <c r="N151">
-        <v>3.19</v>
-      </c>
-      <c r="O151">
-        <v>1</v>
-      </c>
-      <c r="P151" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01618-601618.xlsx
+++ b/s60_signal/position-01618-601618.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="142">
   <si>
     <t>trade_time</t>
   </si>
@@ -85,273 +85,300 @@
     <t>2020-08-17</t>
   </si>
   <si>
+    <t>2021-02-22</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>2021-01-13</t>
+  </si>
+  <si>
+    <t>2021-01-15</t>
+  </si>
+  <si>
+    <t>2021-04-01</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>2021-02-26</t>
+  </si>
+  <si>
+    <t>2021-02-25</t>
+  </si>
+  <si>
+    <t>2021-02-23</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>2016-12-30</t>
+  </si>
+  <si>
+    <t>2017-04-05</t>
+  </si>
+  <si>
+    <t>2017-05-04</t>
+  </si>
+  <si>
+    <t>2017-12-20</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>2020-08-12</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-07-17</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>2021-01-22</t>
+  </si>
+  <si>
+    <t>2021-01-26</t>
+  </si>
+  <si>
+    <t>2021-03-12</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>2021-03-09</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>2016-12-23</t>
+  </si>
+  <si>
+    <t>2017-02-09</t>
+  </si>
+  <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
+    <t>2017-02-13</t>
+  </si>
+  <si>
+    <t>2017-02-14</t>
+  </si>
+  <si>
+    <t>2017-02-15</t>
+  </si>
+  <si>
+    <t>2017-02-16</t>
+  </si>
+  <si>
+    <t>2017-04-27</t>
+  </si>
+  <si>
+    <t>2019-12-05</t>
+  </si>
+  <si>
+    <t>2019-12-06</t>
+  </si>
+  <si>
+    <t>2019-12-20</t>
+  </si>
+  <si>
+    <t>2020-02-21</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>2020-02-27</t>
+  </si>
+  <si>
+    <t>2020-02-28</t>
+  </si>
+  <si>
+    <t>2020-11-26</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-01</t>
+  </si>
+  <si>
+    <t>2020-12-02</t>
+  </si>
+  <si>
+    <t>2020-12-11</t>
+  </si>
+  <si>
+    <t>2020-12-14</t>
+  </si>
+  <si>
     <t>2020-12-15</t>
   </si>
   <si>
-    <t>2021-02-22</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>2020-12-11</t>
-  </si>
-  <si>
-    <t>2021-01-13</t>
-  </si>
-  <si>
-    <t>2021-01-15</t>
-  </si>
-  <si>
-    <t>2021-04-01</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>2021-02-26</t>
-  </si>
-  <si>
-    <t>2021-02-25</t>
-  </si>
-  <si>
-    <t>2021-02-23</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
+    <t>2020-12-16</t>
+  </si>
+  <si>
+    <t>2020-12-17</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>2020-12-21</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
+    <t>2020-12-24</t>
+  </si>
+  <si>
+    <t>2020-12-28</t>
+  </si>
+  <si>
+    <t>2020-12-29</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>2021-01-05</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>2021-01-08</t>
+  </si>
+  <si>
+    <t>2021-01-11</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>2021-01-14</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>2021-04-08</t>
+  </si>
+  <si>
+    <t>2021-04-09</t>
+  </si>
+  <si>
+    <t>2021-04-13</t>
+  </si>
+  <si>
+    <t>2021-04-14</t>
   </si>
   <si>
     <t>2021-04-15</t>
   </si>
   <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>2021-07-12</t>
-  </si>
-  <si>
-    <t>2016-12-30</t>
-  </si>
-  <si>
-    <t>2017-04-05</t>
-  </si>
-  <si>
-    <t>2017-05-04</t>
-  </si>
-  <si>
-    <t>2017-12-20</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>2020-08-12</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-07-17</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
+    <t>2021-04-16</t>
+  </si>
+  <si>
+    <t>2021-04-20</t>
+  </si>
+  <si>
+    <t>2021-04-22</t>
+  </si>
+  <si>
+    <t>2021-04-23</t>
+  </si>
+  <si>
+    <t>2021-04-26</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>2021-04-29</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>2021-05-10</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>2021-05-12</t>
+  </si>
+  <si>
+    <t>2021-05-13</t>
+  </si>
+  <si>
+    <t>2021-05-14</t>
+  </si>
+  <si>
+    <t>2021-05-17</t>
+  </si>
+  <si>
+    <t>2021-05-18</t>
+  </si>
+  <si>
+    <t>2021-05-20</t>
   </si>
   <si>
     <t>2021-05-21</t>
   </si>
   <si>
-    <t>2021-05-20</t>
-  </si>
-  <si>
-    <t>2021-01-22</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>2021-01-26</t>
-  </si>
-  <si>
-    <t>2021-03-09</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>2016-12-23</t>
-  </si>
-  <si>
-    <t>2017-02-09</t>
-  </si>
-  <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
-    <t>2017-02-13</t>
-  </si>
-  <si>
-    <t>2017-02-14</t>
-  </si>
-  <si>
-    <t>2017-02-15</t>
-  </si>
-  <si>
-    <t>2017-02-16</t>
-  </si>
-  <si>
-    <t>2017-04-27</t>
-  </si>
-  <si>
-    <t>2019-12-05</t>
-  </si>
-  <si>
-    <t>2019-12-06</t>
-  </si>
-  <si>
-    <t>2019-12-20</t>
-  </si>
-  <si>
-    <t>2020-02-21</t>
-  </si>
-  <si>
-    <t>2020-02-24</t>
-  </si>
-  <si>
-    <t>2020-02-25</t>
-  </si>
-  <si>
-    <t>2020-02-26</t>
-  </si>
-  <si>
-    <t>2020-02-27</t>
-  </si>
-  <si>
-    <t>2020-02-28</t>
-  </si>
-  <si>
-    <t>2020-11-26</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-01</t>
-  </si>
-  <si>
-    <t>2020-12-02</t>
-  </si>
-  <si>
-    <t>2020-12-14</t>
-  </si>
-  <si>
-    <t>2020-12-16</t>
-  </si>
-  <si>
-    <t>2020-12-17</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>2020-12-21</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2020-12-23</t>
-  </si>
-  <si>
-    <t>2020-12-24</t>
-  </si>
-  <si>
-    <t>2020-12-28</t>
-  </si>
-  <si>
-    <t>2020-12-29</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>2021-01-05</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-08</t>
-  </si>
-  <si>
-    <t>2021-01-11</t>
-  </si>
-  <si>
-    <t>2021-01-14</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>2021-04-08</t>
-  </si>
-  <si>
-    <t>2021-04-09</t>
-  </si>
-  <si>
-    <t>2021-04-13</t>
-  </si>
-  <si>
-    <t>2021-04-14</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>2021-05-12</t>
-  </si>
-  <si>
-    <t>2021-05-13</t>
-  </si>
-  <si>
-    <t>2021-05-14</t>
-  </si>
-  <si>
-    <t>2021-05-17</t>
-  </si>
-  <si>
-    <t>2021-05-18</t>
-  </si>
-  <si>
     <t>2021-05-24</t>
   </si>
   <si>
@@ -386,6 +413,33 @@
   </si>
   <si>
     <t>2021-06-08</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>2021-06-10</t>
+  </si>
+  <si>
+    <t>2021-06-11</t>
+  </si>
+  <si>
+    <t>2021-06-15</t>
+  </si>
+  <si>
+    <t>2021-06-16</t>
+  </si>
+  <si>
+    <t>2021-06-17</t>
+  </si>
+  <si>
+    <t>2021-06-18</t>
+  </si>
+  <si>
+    <t>2021-06-21</t>
+  </si>
+  <si>
+    <t>2021-06-22</t>
   </si>
 </sst>
 </file>
@@ -743,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P132"/>
+  <dimension ref="A1:P143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -804,7 +858,7 @@
         <v>2.241636620202809</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E2">
         <v>2.083673377356266</v>
@@ -840,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -854,7 +908,7 @@
         <v>2.291018963074085</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E3">
         <v>2.748932188801797</v>
@@ -890,7 +944,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -904,7 +958,7 @@
         <v>0.1640886968569069</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E4">
         <v>0.8087275807852619</v>
@@ -940,7 +994,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -954,7 +1008,7 @@
         <v>0.1567937244930127</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E5">
         <v>0.8087275807852619</v>
@@ -990,7 +1044,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1004,7 +1058,7 @@
         <v>0.06008199184724816</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E6">
         <v>0.7118353409391309</v>
@@ -1040,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1054,7 +1108,7 @@
         <v>0.05109309920632388</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>0.7118353409391309</v>
@@ -1090,7 +1144,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1104,7 +1158,7 @@
         <v>-0.0569506423664734</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E8">
         <v>0.6028081963621785</v>
@@ -1140,7 +1194,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1154,7 +1208,7 @@
         <v>-0.06784560396853312</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E9">
         <v>0.6028081963621785</v>
@@ -1190,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1204,7 +1258,7 @@
         <v>-0.1396452470657845</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E10">
         <v>0.5257702258605397</v>
@@ -1240,7 +1294,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1254,7 +1308,7 @@
         <v>-0.1518870263339567</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>0.5257702258605397</v>
@@ -1290,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1304,7 +1358,7 @@
         <v>-0.2479133877986754</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E12">
         <v>0.424908049151723</v>
@@ -1340,7 +1394,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1354,7 +1408,7 @@
         <v>-0.2619184918344848</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E13">
         <v>0.424908049151723</v>
@@ -1390,7 +1444,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1404,7 +1458,7 @@
         <v>-0.3399965939203824</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E14">
         <v>0.3391236942630966</v>
@@ -1440,7 +1494,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1454,7 +1508,7 @@
         <v>0.9756011105228968</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E15">
         <v>0.8107654111102569</v>
@@ -1490,7 +1544,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1504,7 +1558,7 @@
         <v>1.301145679016073</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E16">
         <v>1.173416666670367</v>
@@ -1540,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1554,7 +1608,7 @@
         <v>1.296277364845049</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E17">
         <v>1.230890933009092</v>
@@ -1590,7 +1644,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1604,7 +1658,7 @@
         <v>0.4435035626339812</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E18">
         <v>0.9439906537348826</v>
@@ -1640,7 +1694,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1654,7 +1708,7 @@
         <v>0.4423533289773536</v>
       </c>
       <c r="D19" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E19">
         <v>0.9439906537348826</v>
@@ -1690,7 +1744,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1704,7 +1758,7 @@
         <v>1.507350128118183</v>
       </c>
       <c r="D20" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E20">
         <v>1.202821457299868</v>
@@ -1740,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -1754,7 +1808,7 @@
         <v>1.54125697476493</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E21">
         <v>1.238224194239853</v>
@@ -1790,7 +1844,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -1804,7 +1858,7 @@
         <v>1.573438797246031</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E22">
         <v>1.271825803006885</v>
@@ -1840,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -1854,7 +1908,7 @@
         <v>1.613400857289038</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E23">
         <v>1.313550895110613</v>
@@ -1890,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -1904,7 +1958,7 @@
         <v>1.593400857289038</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E24">
         <v>1.363275825771058</v>
@@ -1940,7 +1994,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -1954,7 +2008,7 @@
         <v>1.645344720184119</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E25">
         <v>1.346904046074595</v>
@@ -1990,7 +2044,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2004,7 +2058,7 @@
         <v>1.625344720184119</v>
       </c>
       <c r="D26" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E26">
         <v>1.394045281942056</v>
@@ -2040,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2054,7 +2108,7 @@
         <v>1.68180858461344</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E27">
         <v>1.384976610405209</v>
@@ -2090,7 +2144,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2104,7 +2158,7 @@
         <v>1.66180858461344</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E28">
         <v>1.429168563120298</v>
@@ -2140,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2154,7 +2208,7 @@
         <v>1.710614904938503</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E29">
         <v>1.415053797803437</v>
@@ -2190,7 +2244,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2204,7 +2258,7 @@
         <v>1.690614904938503</v>
       </c>
       <c r="D30" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E30">
         <v>1.456915827551058</v>
@@ -2240,7 +2294,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2251,37 +2305,37 @@
         <v>23</v>
       </c>
       <c r="C31">
-        <v>2.268334662646267</v>
+        <v>2.967686812279704</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E31">
-        <v>2.649848972127444</v>
+        <v>2.601744839228811</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G31">
-        <v>0.002931665337353733</v>
+        <v>0.004132313187720295</v>
       </c>
       <c r="H31">
-        <v>0.003470151027872556</v>
+        <v>0.003518255160771189</v>
       </c>
       <c r="I31">
-        <v>0.3815143094811773</v>
+        <v>0.3659419730508935</v>
       </c>
       <c r="J31">
         <v>0.2531796468349111</v>
       </c>
       <c r="K31">
-        <v>1.31</v>
+        <v>2.3</v>
       </c>
       <c r="L31">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="M31">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="N31">
         <v>3.06</v>
@@ -2290,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2301,84 +2355,84 @@
         <v>24</v>
       </c>
       <c r="C32">
-        <v>2.967686812279704</v>
+        <v>3.015409387558148</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E32">
-        <v>2.601744839228811</v>
+        <v>3.294391900570977</v>
       </c>
       <c r="F32">
         <v>-1</v>
       </c>
       <c r="G32">
-        <v>0.004132313187720295</v>
+        <v>0.004144590612441852</v>
       </c>
       <c r="H32">
-        <v>0.003518255160771189</v>
+        <v>0.004585608099429023</v>
       </c>
       <c r="I32">
-        <v>0.3659419730508935</v>
+        <v>-0.2789825130128283</v>
       </c>
       <c r="J32">
         <v>0.2531796468349111</v>
       </c>
       <c r="K32">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="L32">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="M32">
-        <v>1.81</v>
+        <v>2.55</v>
       </c>
       <c r="N32">
-        <v>3.06</v>
+        <v>3.94</v>
       </c>
       <c r="O32">
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C33">
-        <v>2.94857711339348</v>
+        <v>2.969422072159588</v>
       </c>
       <c r="D33" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E33">
-        <v>2.601744839228811</v>
+        <v>2.603110413308198</v>
       </c>
       <c r="F33">
         <v>-1</v>
       </c>
       <c r="G33">
-        <v>0.00397142288660652</v>
+        <v>0.004130577927840411</v>
       </c>
       <c r="H33">
-        <v>0.003518255160771189</v>
+        <v>0.003516889586691802</v>
       </c>
       <c r="I33">
-        <v>0.3468322741646688</v>
+        <v>0.3663116588513904</v>
       </c>
       <c r="J33">
-        <v>0.2531796468349111</v>
+        <v>0.2524251860175702</v>
       </c>
       <c r="K33">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="L33">
-        <v>3.46</v>
+        <v>3.55</v>
       </c>
       <c r="M33">
         <v>1.81</v>
@@ -2390,98 +2444,98 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C34">
-        <v>2.276798754456807</v>
+        <v>3.017091835180818</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E34">
-        <v>2.651071198651537</v>
+        <v>3.296315775655196</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G34">
-        <v>0.002943201245543193</v>
+        <v>0.004142908164819182</v>
       </c>
       <c r="H34">
-        <v>0.003468928801348464</v>
+        <v>0.004583684224344804</v>
       </c>
       <c r="I34">
-        <v>0.3742724441947294</v>
+        <v>-0.2792239404743775</v>
       </c>
       <c r="J34">
         <v>0.2524251860175702</v>
       </c>
       <c r="K34">
-        <v>1.32</v>
+        <v>2.23</v>
       </c>
       <c r="L34">
-        <v>2.61</v>
+        <v>3.58</v>
       </c>
       <c r="M34">
-        <v>1.62</v>
+        <v>2.55</v>
       </c>
       <c r="N34">
-        <v>3.06</v>
+        <v>3.94</v>
       </c>
       <c r="O34">
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B35" t="s">
         <v>23</v>
       </c>
       <c r="C35">
-        <v>2.269323006316983</v>
+        <v>2.970852231383444</v>
       </c>
       <c r="D35" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E35">
-        <v>2.651071198651537</v>
+        <v>2.604235886436537</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G35">
-        <v>0.002930676993683017</v>
+        <v>0.004129147768616556</v>
       </c>
       <c r="H35">
-        <v>0.003468928801348464</v>
+        <v>0.003515764113563464</v>
       </c>
       <c r="I35">
-        <v>0.3817481923345531</v>
+        <v>0.3666163449469071</v>
       </c>
       <c r="J35">
-        <v>0.2524251860175702</v>
+        <v>0.2518033776593721</v>
       </c>
       <c r="K35">
-        <v>1.31</v>
+        <v>2.3</v>
       </c>
       <c r="L35">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="M35">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="N35">
         <v>3.06</v>
@@ -2490,257 +2544,257 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B36" t="s">
         <v>24</v>
       </c>
       <c r="C36">
-        <v>2.969422072159588</v>
+        <v>3.0184784678196</v>
       </c>
       <c r="D36" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E36">
-        <v>2.603110413308198</v>
+        <v>3.297901386968601</v>
       </c>
       <c r="F36">
         <v>-1</v>
       </c>
       <c r="G36">
-        <v>0.004130577927840411</v>
+        <v>0.0041415215321804</v>
       </c>
       <c r="H36">
-        <v>0.003516889586691802</v>
+        <v>0.004582098613031399</v>
       </c>
       <c r="I36">
-        <v>0.3663116588513904</v>
+        <v>-0.2794229191490007</v>
       </c>
       <c r="J36">
-        <v>0.2524251860175702</v>
+        <v>0.2518033776593721</v>
       </c>
       <c r="K36">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="L36">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="M36">
-        <v>1.81</v>
+        <v>2.55</v>
       </c>
       <c r="N36">
-        <v>3.06</v>
+        <v>3.94</v>
       </c>
       <c r="O36">
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C37">
-        <v>2.950101124244508</v>
+        <v>2.964905134405401</v>
       </c>
       <c r="D37" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E37">
-        <v>2.610586161448022</v>
+        <v>2.599555779684251</v>
       </c>
       <c r="F37">
         <v>-1</v>
       </c>
       <c r="G37">
-        <v>0.003969898875755492</v>
+        <v>0.004135094865594598</v>
       </c>
       <c r="H37">
-        <v>0.003529413838551978</v>
+        <v>0.003520444220315749</v>
       </c>
       <c r="I37">
-        <v>0.339514962796486</v>
+        <v>0.3653493547211504</v>
       </c>
       <c r="J37">
-        <v>0.2524251860175702</v>
+        <v>0.2543890719976515</v>
       </c>
       <c r="K37">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="L37">
-        <v>3.46</v>
+        <v>3.55</v>
       </c>
       <c r="M37">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="N37">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="O37">
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C38">
-        <v>2.277619541489629</v>
+        <v>3.012712369445237</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E38">
-        <v>2.652078528191817</v>
+        <v>3.291307866405988</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G38">
-        <v>0.002942380458510371</v>
+        <v>0.004147287630554762</v>
       </c>
       <c r="H38">
-        <v>0.003467921471808183</v>
+        <v>0.004588692133594012</v>
       </c>
       <c r="I38">
-        <v>0.3744589867021886</v>
+        <v>-0.2785954969607514</v>
       </c>
       <c r="J38">
-        <v>0.2518033776593721</v>
+        <v>0.2543890719976515</v>
       </c>
       <c r="K38">
-        <v>1.32</v>
+        <v>2.23</v>
       </c>
       <c r="L38">
-        <v>2.61</v>
+        <v>3.58</v>
       </c>
       <c r="M38">
-        <v>1.62</v>
+        <v>2.55</v>
       </c>
       <c r="N38">
-        <v>3.06</v>
+        <v>3.94</v>
       </c>
       <c r="O38">
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:16">
       <c r="A39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C39">
-        <v>2.970852231383444</v>
+        <v>2.520757495256166</v>
       </c>
       <c r="D39" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E39">
-        <v>2.604235886436537</v>
+        <v>2.229102087286527</v>
       </c>
       <c r="F39">
         <v>-1</v>
       </c>
       <c r="G39">
-        <v>0.004129147768616556</v>
+        <v>0.004399242504743834</v>
       </c>
       <c r="H39">
-        <v>0.003515764113563464</v>
+        <v>0.003930897912713473</v>
       </c>
       <c r="I39">
-        <v>0.3666163449469071</v>
+        <v>0.2916554079696394</v>
       </c>
       <c r="J39">
-        <v>0.2518033776593721</v>
+        <v>0.4649715370018978</v>
       </c>
       <c r="K39">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="L39">
-        <v>3.55</v>
+        <v>3.46</v>
       </c>
       <c r="M39">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="N39">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="O39">
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C40">
-        <v>2.951357177128068</v>
+        <v>2.543113472485768</v>
       </c>
       <c r="D40" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E40">
-        <v>2.611717852659943</v>
+        <v>2.754322580645161</v>
       </c>
       <c r="F40">
         <v>-1</v>
       </c>
       <c r="G40">
-        <v>0.003968642822871932</v>
+        <v>0.004616886527514233</v>
       </c>
       <c r="H40">
-        <v>0.003528282147340057</v>
+        <v>0.005125677419354839</v>
       </c>
       <c r="I40">
-        <v>0.3396393244681257</v>
+        <v>-0.2112091081593928</v>
       </c>
       <c r="J40">
-        <v>0.2518033776593721</v>
+        <v>0.4649715370018978</v>
       </c>
       <c r="K40">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="L40">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="M40">
-        <v>1.82</v>
+        <v>2.55</v>
       </c>
       <c r="N40">
-        <v>3.07</v>
+        <v>3.94</v>
       </c>
       <c r="O40">
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -2751,46 +2805,46 @@
         <v>26</v>
       </c>
       <c r="C41">
-        <v>2.2742064249631</v>
+        <v>2.422019174201789</v>
       </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E41">
-        <v>2.647889703363805</v>
+        <v>2.152176517544798</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G41">
-        <v>0.0029457935750369</v>
+        <v>0.004097980825798211</v>
       </c>
       <c r="H41">
-        <v>0.003472110296636196</v>
+        <v>0.003807823482455202</v>
       </c>
       <c r="I41">
-        <v>0.3736832784007049</v>
+        <v>0.2698426566569911</v>
       </c>
       <c r="J41">
-        <v>0.2543890719976515</v>
+        <v>0.5078671671504308</v>
       </c>
       <c r="K41">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="L41">
-        <v>2.61</v>
+        <v>3.26</v>
       </c>
       <c r="M41">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="N41">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="O41">
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -2798,49 +2852,49 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C42">
-        <v>2.964905134405401</v>
+        <v>2.432019174201789</v>
       </c>
       <c r="D42" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E42">
-        <v>2.599555779684251</v>
+        <v>2.152176517544798</v>
       </c>
       <c r="F42">
         <v>-1</v>
       </c>
       <c r="G42">
-        <v>0.004135094865594598</v>
+        <v>0.004107980825798211</v>
       </c>
       <c r="H42">
-        <v>0.003520444220315749</v>
+        <v>0.003807823482455202</v>
       </c>
       <c r="I42">
-        <v>0.3653493547211504</v>
+        <v>0.2798426566569914</v>
       </c>
       <c r="J42">
-        <v>0.2543890719976515</v>
+        <v>0.5078671671504308</v>
       </c>
       <c r="K42">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="L42">
-        <v>3.55</v>
+        <v>3.27</v>
       </c>
       <c r="M42">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="N42">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="O42">
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -2848,187 +2902,187 @@
         <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C43">
-        <v>2.946134074564744</v>
+        <v>2.419501680713651</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E43">
-        <v>2.607011888964274</v>
+        <v>2.150603084114712</v>
       </c>
       <c r="F43">
         <v>-1</v>
       </c>
       <c r="G43">
-        <v>0.003973865925435256</v>
+        <v>0.004420498319286349</v>
       </c>
       <c r="H43">
-        <v>0.003532988111035726</v>
+        <v>0.004009396915885288</v>
       </c>
       <c r="I43">
-        <v>0.3391221856004698</v>
+        <v>0.2688985965989392</v>
       </c>
       <c r="J43">
-        <v>0.2543890719976515</v>
+        <v>0.5078671671504308</v>
       </c>
       <c r="K43">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="L43">
-        <v>3.46</v>
+        <v>3.42</v>
       </c>
       <c r="M43">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="N43">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C44">
-        <v>1.990887286527514</v>
+        <v>2.419029650684626</v>
       </c>
       <c r="D44" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E44">
-        <v>2.306746110056926</v>
+        <v>2.150603084114712</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G44">
-        <v>0.003209112713472486</v>
+        <v>0.004480970349315374</v>
       </c>
       <c r="H44">
-        <v>0.003813253889943074</v>
+        <v>0.004009396915885288</v>
       </c>
       <c r="I44">
-        <v>0.3158588235294117</v>
+        <v>0.2684265665699139</v>
       </c>
       <c r="J44">
-        <v>0.4649715370018978</v>
+        <v>0.5078671671504308</v>
       </c>
       <c r="K44">
-        <v>1.31</v>
+        <v>2.03</v>
       </c>
       <c r="L44">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="M44">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="N44">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="O44">
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C45">
-        <v>2.492796963946868</v>
+        <v>2.44745621725454</v>
       </c>
       <c r="D45" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E45">
-        <v>2.222096394686907</v>
+        <v>2.644938723766401</v>
       </c>
       <c r="F45">
         <v>-1</v>
       </c>
       <c r="G45">
-        <v>0.004027203036053131</v>
+        <v>0.004712543782745461</v>
       </c>
       <c r="H45">
-        <v>0.003737903605313093</v>
+        <v>0.005235061276233599</v>
       </c>
       <c r="I45">
-        <v>0.2707005692599616</v>
+        <v>-0.1974825065118617</v>
       </c>
       <c r="J45">
-        <v>0.4649715370018978</v>
+        <v>0.5078671671504308</v>
       </c>
       <c r="K45">
-        <v>1.65</v>
+        <v>2.23</v>
       </c>
       <c r="L45">
-        <v>3.26</v>
+        <v>3.58</v>
       </c>
       <c r="M45">
-        <v>1.63</v>
+        <v>2.55</v>
       </c>
       <c r="N45">
-        <v>2.98</v>
+        <v>3.94</v>
       </c>
       <c r="O45">
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C46">
-        <v>2.502796963946869</v>
+        <v>2.361811863714594</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E46">
-        <v>2.222096394686907</v>
+        <v>2.092698992639265</v>
       </c>
       <c r="F46">
         <v>-1</v>
       </c>
       <c r="G46">
-        <v>0.004037203036053131</v>
+        <v>0.004158188136285406</v>
       </c>
       <c r="H46">
-        <v>0.003737903605313093</v>
+        <v>0.003867301007360734</v>
       </c>
       <c r="I46">
-        <v>0.2807005692599618</v>
+        <v>0.2691128710753286</v>
       </c>
       <c r="J46">
-        <v>0.4649715370018978</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K46">
         <v>1.65</v>
       </c>
       <c r="L46">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="M46">
         <v>1.63</v>
@@ -3040,39 +3094,39 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C47">
-        <v>2.504006072106261</v>
+        <v>2.347617800919848</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E47">
-        <v>2.229102087286527</v>
+        <v>2.08382770339255</v>
       </c>
       <c r="F47">
         <v>-1</v>
       </c>
       <c r="G47">
-        <v>0.004335993927893739</v>
+        <v>0.004492382199080151</v>
       </c>
       <c r="H47">
-        <v>0.003930897912713473</v>
+        <v>0.004076172296607451</v>
       </c>
       <c r="I47">
-        <v>0.2749039848197343</v>
+        <v>0.2637900975272984</v>
       </c>
       <c r="J47">
-        <v>0.4649715370018978</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K47">
         <v>1.97</v>
@@ -3090,39 +3144,39 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C48">
-        <v>2.506107779886148</v>
+        <v>2.344956414145834</v>
       </c>
       <c r="D48" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E48">
-        <v>2.229102087286527</v>
+        <v>2.08382770339255</v>
       </c>
       <c r="F48">
         <v>-1</v>
       </c>
       <c r="G48">
-        <v>0.004393892220113852</v>
+        <v>0.004555043585854166</v>
       </c>
       <c r="H48">
-        <v>0.003930897912713473</v>
+        <v>0.004076172296607451</v>
       </c>
       <c r="I48">
-        <v>0.2770056925996207</v>
+        <v>0.261128710753284</v>
       </c>
       <c r="J48">
-        <v>0.4649715370018978</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K48">
         <v>2.03</v>
@@ -3140,89 +3194,89 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C49">
-        <v>1.934694011032936</v>
+        <v>2.366085124899118</v>
       </c>
       <c r="D49" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E49">
-        <v>2.237255189216302</v>
+        <v>2.551891062104373</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G49">
-        <v>0.003265305988967065</v>
+        <v>0.004793914875100881</v>
       </c>
       <c r="H49">
-        <v>0.003882744810783698</v>
+        <v>0.005328108937895627</v>
       </c>
       <c r="I49">
-        <v>0.3025611781833666</v>
+        <v>-0.1858059372052545</v>
       </c>
       <c r="J49">
-        <v>0.5078671671504308</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K49">
-        <v>1.31</v>
+        <v>2.23</v>
       </c>
       <c r="L49">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="M49">
-        <v>1.62</v>
+        <v>2.55</v>
       </c>
       <c r="N49">
-        <v>3.06</v>
+        <v>3.94</v>
       </c>
       <c r="O49">
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C50">
-        <v>2.422019174201789</v>
+        <v>2.284943445032334</v>
       </c>
       <c r="D50" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E50">
-        <v>2.152176517544798</v>
+        <v>2.016762312365275</v>
       </c>
       <c r="F50">
         <v>-1</v>
       </c>
       <c r="G50">
-        <v>0.004097980825798211</v>
+        <v>0.004235056554967666</v>
       </c>
       <c r="H50">
-        <v>0.003807823482455202</v>
+        <v>0.003943237687634725</v>
       </c>
       <c r="I50">
-        <v>0.2698426566569911</v>
+        <v>0.2681811326670585</v>
       </c>
       <c r="J50">
-        <v>0.5078671671504308</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K50">
         <v>1.65</v>
@@ -3240,39 +3294,39 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C51">
-        <v>2.419501680713651</v>
+        <v>2.255841567705271</v>
       </c>
       <c r="D51" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E51">
-        <v>2.150603084114712</v>
+        <v>1.998573639035861</v>
       </c>
       <c r="F51">
         <v>-1</v>
       </c>
       <c r="G51">
-        <v>0.004420498319286349</v>
+        <v>0.004584158432294728</v>
       </c>
       <c r="H51">
-        <v>0.004009396915885288</v>
+        <v>0.004161426360964139</v>
       </c>
       <c r="I51">
-        <v>0.2688985965989392</v>
+        <v>0.25726792866941</v>
       </c>
       <c r="J51">
-        <v>0.5078671671504308</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K51">
         <v>1.97</v>
@@ -3290,39 +3344,39 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C52">
-        <v>2.419029650684626</v>
+        <v>2.250384965706448</v>
       </c>
       <c r="D52" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E52">
-        <v>2.150603084114712</v>
+        <v>1.998573639035861</v>
       </c>
       <c r="F52">
         <v>-1</v>
       </c>
       <c r="G52">
-        <v>0.004480970349315374</v>
+        <v>0.004649615034293553</v>
       </c>
       <c r="H52">
-        <v>0.004009396915885288</v>
+        <v>0.004161426360964139</v>
       </c>
       <c r="I52">
-        <v>0.2684265665699139</v>
+        <v>0.2518113266705861</v>
       </c>
       <c r="J52">
-        <v>0.5078671671504308</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K52">
         <v>2.03</v>
@@ -3340,145 +3394,145 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:16">
       <c r="A53" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C53">
-        <v>2.361811863714594</v>
+        <v>2.262196292377033</v>
       </c>
       <c r="D53" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E53">
-        <v>2.092698992639265</v>
+        <v>2.433094415049971</v>
       </c>
       <c r="F53">
         <v>-1</v>
       </c>
       <c r="G53">
-        <v>0.004158188136285406</v>
+        <v>0.004897803707622967</v>
       </c>
       <c r="H53">
-        <v>0.003867301007360734</v>
+        <v>0.005446905584950029</v>
       </c>
       <c r="I53">
-        <v>0.2691128710753286</v>
+        <v>-0.1708981226729378</v>
       </c>
       <c r="J53">
-        <v>0.5443564462335794</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K53">
-        <v>1.65</v>
+        <v>2.23</v>
       </c>
       <c r="L53">
-        <v>3.26</v>
+        <v>3.58</v>
       </c>
       <c r="M53">
-        <v>1.63</v>
+        <v>2.55</v>
       </c>
       <c r="N53">
-        <v>2.98</v>
+        <v>3.94</v>
       </c>
       <c r="O53">
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C54">
-        <v>2.347617800919848</v>
+        <v>2.206392009113778</v>
       </c>
       <c r="D54" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E54">
-        <v>2.08382770339255</v>
+        <v>1.939163015063914</v>
       </c>
       <c r="F54">
         <v>-1</v>
       </c>
       <c r="G54">
-        <v>0.004492382199080151</v>
+        <v>0.004313607990886223</v>
       </c>
       <c r="H54">
-        <v>0.004076172296607451</v>
+        <v>0.004020836984936086</v>
       </c>
       <c r="I54">
-        <v>0.2637900975272984</v>
+        <v>0.2672289940498638</v>
       </c>
       <c r="J54">
-        <v>0.5443564462335794</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K54">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="L54">
-        <v>3.42</v>
+        <v>3.26</v>
       </c>
       <c r="M54">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="N54">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="O54">
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:16">
       <c r="A55" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C55">
-        <v>2.344956414145834</v>
+        <v>2.162055913911602</v>
       </c>
       <c r="D55" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E55">
-        <v>2.08382770339255</v>
+        <v>1.911452955562554</v>
       </c>
       <c r="F55">
         <v>-1</v>
       </c>
       <c r="G55">
-        <v>0.004555043585854166</v>
+        <v>0.004677944086088398</v>
       </c>
       <c r="H55">
-        <v>0.004076172296607451</v>
+        <v>0.004248547044437446</v>
       </c>
       <c r="I55">
-        <v>0.261128710753284</v>
+        <v>0.2506029583490479</v>
       </c>
       <c r="J55">
-        <v>0.5443564462335794</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K55">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="L55">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="M55">
         <v>1.83</v>
@@ -3490,245 +3544,245 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C56">
-        <v>2.284943445032334</v>
+        <v>2.153742896061194</v>
       </c>
       <c r="D56" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E56">
-        <v>2.016762312365275</v>
+        <v>1.911452955562554</v>
       </c>
       <c r="F56">
         <v>-1</v>
       </c>
       <c r="G56">
-        <v>0.004235056554967666</v>
+        <v>0.004746257103938807</v>
       </c>
       <c r="H56">
-        <v>0.003943237687634725</v>
+        <v>0.004248547044437446</v>
       </c>
       <c r="I56">
-        <v>0.2681811326670585</v>
+        <v>0.2422899404986398</v>
       </c>
       <c r="J56">
-        <v>0.5909433666470703</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K56">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="L56">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="M56">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="N56">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="O56">
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C57">
-        <v>2.255841567705271</v>
+        <v>2.156032836559834</v>
       </c>
       <c r="D57" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E57">
-        <v>1.998573639035861</v>
+        <v>2.311696741357657</v>
       </c>
       <c r="F57">
         <v>-1</v>
       </c>
       <c r="G57">
-        <v>0.004584158432294728</v>
+        <v>0.005003967163440167</v>
       </c>
       <c r="H57">
-        <v>0.004161426360964139</v>
+        <v>0.005568303258642344</v>
       </c>
       <c r="I57">
-        <v>0.25726792866941</v>
+        <v>-0.155663904797823</v>
       </c>
       <c r="J57">
-        <v>0.5909433666470703</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K57">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="L57">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="M57">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="N57">
-        <v>3.08</v>
+        <v>3.94</v>
       </c>
       <c r="O57">
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C58">
-        <v>2.250384965706448</v>
+        <v>2.122703049542399</v>
       </c>
       <c r="D58" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E58">
-        <v>1.998573639035861</v>
+        <v>1.814059302286312</v>
       </c>
       <c r="F58">
         <v>-1</v>
       </c>
       <c r="G58">
-        <v>0.004649615034293553</v>
+        <v>0.004397296950457601</v>
       </c>
       <c r="H58">
-        <v>0.004161426360964139</v>
+        <v>0.004005940697713688</v>
       </c>
       <c r="I58">
-        <v>0.2518113266705861</v>
+        <v>0.3086437472560868</v>
       </c>
       <c r="J58">
-        <v>0.5909433666470703</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K58">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="L58">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="M58">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="N58">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="O58">
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B59" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C59">
-        <v>2.206392009113778</v>
+        <v>2.062136368241531</v>
       </c>
       <c r="D59" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E59">
-        <v>1.894705026964186</v>
+        <v>1.818634291310661</v>
       </c>
       <c r="F59">
         <v>-1</v>
       </c>
       <c r="G59">
-        <v>0.004313607990886223</v>
+        <v>0.004777863631758469</v>
       </c>
       <c r="H59">
-        <v>0.003925294973035814</v>
+        <v>0.004341365708689339</v>
       </c>
       <c r="I59">
-        <v>0.3116869821495918</v>
+        <v>0.24350207693087</v>
       </c>
       <c r="J59">
-        <v>0.6385502975068013</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K59">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="L59">
-        <v>3.26</v>
+        <v>3.42</v>
       </c>
       <c r="M59">
-        <v>1.59</v>
+        <v>1.83</v>
       </c>
       <c r="N59">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="O59">
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B60" t="s">
         <v>29</v>
       </c>
       <c r="C60">
-        <v>2.162055913911602</v>
+        <v>2.050780115497619</v>
       </c>
       <c r="D60" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E60">
-        <v>1.911452955562554</v>
+        <v>1.818634291310661</v>
       </c>
       <c r="F60">
         <v>-1</v>
       </c>
       <c r="G60">
-        <v>0.004677944086088398</v>
+        <v>0.004849219884502381</v>
       </c>
       <c r="H60">
-        <v>0.004248547044437446</v>
+        <v>0.004341365708689339</v>
       </c>
       <c r="I60">
-        <v>0.2506029583490479</v>
+        <v>0.2321458241869578</v>
       </c>
       <c r="J60">
-        <v>0.6385502975068013</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K60">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="L60">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="M60">
         <v>1.83</v>
@@ -3740,57 +3794,57 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B61" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C61">
-        <v>2.153742896061194</v>
+        <v>2.042925939684576</v>
       </c>
       <c r="D61" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E61">
-        <v>1.911452955562554</v>
+        <v>2.182359258383708</v>
       </c>
       <c r="F61">
         <v>-1</v>
       </c>
       <c r="G61">
-        <v>0.004746257103938807</v>
+        <v>0.005117074060315425</v>
       </c>
       <c r="H61">
-        <v>0.004248547044437446</v>
+        <v>0.005697640741616292</v>
       </c>
       <c r="I61">
-        <v>0.2422899404986398</v>
+        <v>-0.1394333186991319</v>
       </c>
       <c r="J61">
-        <v>0.6385502975068013</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K61">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="L61">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="M61">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="N61">
-        <v>3.08</v>
+        <v>3.94</v>
       </c>
       <c r="O61">
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -3798,49 +3852,49 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C62">
-        <v>2.122703049542399</v>
+        <v>1.960646887966805</v>
       </c>
       <c r="D62" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E62">
-        <v>2.1327030495424</v>
+        <v>1.724357261410788</v>
       </c>
       <c r="F62">
         <v>-1</v>
       </c>
       <c r="G62">
-        <v>0.004397296950457601</v>
+        <v>0.004879353112033196</v>
       </c>
       <c r="H62">
-        <v>0.0044072969504576</v>
+        <v>0.004435642738589212</v>
       </c>
       <c r="I62">
-        <v>-0.01000000000000068</v>
+        <v>0.2362896265560166</v>
       </c>
       <c r="J62">
-        <v>0.6892708790652124</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K62">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="L62">
-        <v>3.26</v>
+        <v>3.42</v>
       </c>
       <c r="M62">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="N62">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="O62">
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -3851,34 +3905,34 @@
         <v>29</v>
       </c>
       <c r="C63">
-        <v>2.062136368241531</v>
+        <v>1.946199585062241</v>
       </c>
       <c r="D63" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E63">
-        <v>1.818634291310661</v>
+        <v>1.724357261410788</v>
       </c>
       <c r="F63">
         <v>-1</v>
       </c>
       <c r="G63">
-        <v>0.004777863631758469</v>
+        <v>0.00495380041493776</v>
       </c>
       <c r="H63">
-        <v>0.004341365708689339</v>
+        <v>0.004435642738589212</v>
       </c>
       <c r="I63">
-        <v>0.24350207693087</v>
+        <v>0.2218423236514526</v>
       </c>
       <c r="J63">
-        <v>0.6892708790652124</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K63">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="L63">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="M63">
         <v>1.83</v>
@@ -3890,45 +3944,45 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C64">
-        <v>2.050780115497619</v>
+        <v>1.843540306843175</v>
       </c>
       <c r="D64" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E64">
-        <v>1.818634291310661</v>
+        <v>1.615572975392391</v>
       </c>
       <c r="F64">
         <v>-1</v>
       </c>
       <c r="G64">
-        <v>0.004849219884502381</v>
+        <v>0.004996459693156825</v>
       </c>
       <c r="H64">
-        <v>0.004341365708689339</v>
+        <v>0.00454442702460761</v>
       </c>
       <c r="I64">
-        <v>0.2321458241869578</v>
+        <v>0.227967331450784</v>
       </c>
       <c r="J64">
-        <v>0.6892708790652124</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K64">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="L64">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="M64">
         <v>1.83</v>
@@ -3940,7 +3994,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -3948,49 +4002,49 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C65">
-        <v>1.960646887966805</v>
+        <v>1.364830842322013</v>
       </c>
       <c r="D65" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E65">
-        <v>1.724357261410788</v>
+        <v>1.598575134626953</v>
       </c>
       <c r="F65">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G65">
-        <v>0.004879353112033196</v>
+        <v>0.005255169157677987</v>
       </c>
       <c r="H65">
-        <v>0.004435642738589212</v>
+        <v>0.004741424865373047</v>
       </c>
       <c r="I65">
-        <v>0.2362896265560166</v>
+        <v>0.2337442923049406</v>
       </c>
       <c r="J65">
-        <v>0.7407883817427386</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K65">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="L65">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="M65">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="N65">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="O65">
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -3998,49 +4052,49 @@
         <v>1</v>
       </c>
       <c r="B66" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C66">
-        <v>1.946199585062241</v>
+        <v>1.746644873089242</v>
       </c>
       <c r="D66" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E66">
-        <v>1.724357261410788</v>
+        <v>1.552668119243339</v>
       </c>
       <c r="F66">
         <v>-1</v>
       </c>
       <c r="G66">
-        <v>0.00495380041493776</v>
+        <v>0.005093355126910757</v>
       </c>
       <c r="H66">
-        <v>0.004435642738589212</v>
+        <v>0.004967331880756661</v>
       </c>
       <c r="I66">
-        <v>0.2218423236514526</v>
+        <v>0.1939767538459036</v>
       </c>
       <c r="J66">
-        <v>0.7407883817427386</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K66">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="L66">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="M66">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="N66">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="O66">
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4048,49 +4102,49 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C67">
-        <v>1.843540306843175</v>
+        <v>1.253223538131198</v>
       </c>
       <c r="D67" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E67">
-        <v>1.615572975392391</v>
+        <v>1.465356698427415</v>
       </c>
       <c r="F67">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G67">
-        <v>0.004996459693156825</v>
+        <v>0.005366776461868803</v>
       </c>
       <c r="H67">
-        <v>0.00454442702460761</v>
+        <v>0.004734643301572585</v>
       </c>
       <c r="I67">
-        <v>0.227967331450784</v>
+        <v>0.2121331602962171</v>
       </c>
       <c r="J67">
-        <v>0.8002333467801142</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K67">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="L67">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="M67">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="N67">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="O67">
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4098,49 +4152,49 @@
         <v>1</v>
       </c>
       <c r="B68" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C68">
-        <v>1.825526306036369</v>
+        <v>1.650633349396707</v>
       </c>
       <c r="D68" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E68">
-        <v>1.615572975392391</v>
+        <v>1.454707122988519</v>
       </c>
       <c r="F68">
         <v>-1</v>
       </c>
       <c r="G68">
-        <v>0.005074473693963632</v>
+        <v>0.005189366650603293</v>
       </c>
       <c r="H68">
-        <v>0.00454442702460761</v>
+        <v>0.005065292877011481</v>
       </c>
       <c r="I68">
-        <v>0.2099533306439776</v>
+        <v>0.1959262264081887</v>
       </c>
       <c r="J68">
-        <v>0.8002333467801142</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K68">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="L68">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="M68">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="N68">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="O68">
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4148,31 +4202,31 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C69">
-        <v>1.364830842322013</v>
+        <v>1.142741567826858</v>
       </c>
       <c r="D69" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E69">
-        <v>1.554057700011381</v>
+        <v>1.377550067006499</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69">
-        <v>0.005255169157677987</v>
+        <v>0.005477258432173141</v>
       </c>
       <c r="H69">
-        <v>0.004645942299988619</v>
+        <v>0.004822449932993502</v>
       </c>
       <c r="I69">
-        <v>0.1892268576893685</v>
+        <v>0.2348084991796402</v>
       </c>
       <c r="J69">
-        <v>0.8494188461475927</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K69">
         <v>2.29</v>
@@ -4190,57 +4244,57 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C70">
-        <v>1.746644873089242</v>
+        <v>1.02473295176371</v>
       </c>
       <c r="D70" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E70">
-        <v>1.552668119243339</v>
+        <v>1.28376155991701</v>
       </c>
       <c r="F70">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G70">
-        <v>0.005093355126910757</v>
+        <v>0.005595267048236289</v>
       </c>
       <c r="H70">
-        <v>0.004967331880756661</v>
+        <v>0.004916238440082991</v>
       </c>
       <c r="I70">
-        <v>0.1939767538459036</v>
+        <v>0.2590286081532995</v>
       </c>
       <c r="J70">
-        <v>0.8494188461475927</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K70">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="L70">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="M70">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="N70">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="O70">
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4251,34 +4305,34 @@
         <v>31</v>
       </c>
       <c r="C71">
-        <v>1.253223538131198</v>
+        <v>1.025578495611604</v>
       </c>
       <c r="D71" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E71">
-        <v>1.465356698427415</v>
+        <v>1.228800376424943</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71">
-        <v>0.005366776461868803</v>
+        <v>0.005734421504388396</v>
       </c>
       <c r="H71">
-        <v>0.004734643301572585</v>
+        <v>0.004971199623575057</v>
       </c>
       <c r="I71">
-        <v>0.2121331602962171</v>
+        <v>0.2032218808133393</v>
       </c>
       <c r="J71">
-        <v>0.898155660204717</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K71">
         <v>2.29</v>
       </c>
       <c r="L71">
-        <v>3.31</v>
+        <v>3.38</v>
       </c>
       <c r="M71">
         <v>1.82</v>
@@ -4290,57 +4344,57 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C72">
-        <v>1.650633349396707</v>
+        <v>0.95505474527386</v>
       </c>
       <c r="D72" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E72">
-        <v>1.454707122988519</v>
+        <v>1.172750932925077</v>
       </c>
       <c r="F72">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G72">
-        <v>0.005189366650603293</v>
+        <v>0.00580494525472614</v>
       </c>
       <c r="H72">
-        <v>0.005065292877011481</v>
+        <v>0.005027249067074924</v>
       </c>
       <c r="I72">
-        <v>0.1959262264081887</v>
+        <v>0.2176961876512167</v>
       </c>
       <c r="J72">
-        <v>0.898155660204717</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K72">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="L72">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="M72">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="N72">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="O72">
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4351,34 +4405,34 @@
         <v>31</v>
       </c>
       <c r="C73">
-        <v>1.142741567826858</v>
+        <v>0.8997461387005035</v>
       </c>
       <c r="D73" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E73">
-        <v>1.377550067006499</v>
+        <v>1.128793874425728</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73">
-        <v>0.005477258432173141</v>
+        <v>0.005860253861299496</v>
       </c>
       <c r="H73">
-        <v>0.004822449932993502</v>
+        <v>0.005071206125574273</v>
       </c>
       <c r="I73">
-        <v>0.2348084991796402</v>
+        <v>0.2290477357252241</v>
       </c>
       <c r="J73">
-        <v>0.9464010620843414</v>
+        <v>1.083080288777073</v>
       </c>
       <c r="K73">
         <v>2.29</v>
       </c>
       <c r="L73">
-        <v>3.31</v>
+        <v>3.38</v>
       </c>
       <c r="M73">
         <v>1.82</v>
@@ -4390,7 +4444,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4401,34 +4455,34 @@
         <v>31</v>
       </c>
       <c r="C74">
-        <v>1.02473295176371</v>
+        <v>0.9004291893178089</v>
       </c>
       <c r="D74" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E74">
-        <v>1.28376155991701</v>
+        <v>1.129336735615027</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74">
-        <v>0.005595267048236289</v>
+        <v>0.005859570810682191</v>
       </c>
       <c r="H74">
-        <v>0.004916238440082991</v>
+        <v>0.005070663264384973</v>
       </c>
       <c r="I74">
-        <v>0.2590286081532995</v>
+        <v>0.2289075462972185</v>
       </c>
       <c r="J74">
-        <v>0.9979332088368078</v>
+        <v>1.082782013398337</v>
       </c>
       <c r="K74">
         <v>2.29</v>
       </c>
       <c r="L74">
-        <v>3.31</v>
+        <v>3.38</v>
       </c>
       <c r="M74">
         <v>1.82</v>
@@ -4440,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4451,34 +4505,34 @@
         <v>31</v>
       </c>
       <c r="C75">
-        <v>0.9555784956116042</v>
+        <v>0.8995341152947529</v>
       </c>
       <c r="D75" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E75">
-        <v>1.228800376424943</v>
+        <v>1.128625366740808</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75">
-        <v>0.005664421504388396</v>
+        <v>0.005860465884705247</v>
       </c>
       <c r="H75">
-        <v>0.004971199623575057</v>
+        <v>0.005071374633259193</v>
       </c>
       <c r="I75">
-        <v>0.2732218808133391</v>
+        <v>0.2290912514460552</v>
       </c>
       <c r="J75">
-        <v>1.028131661304976</v>
+        <v>1.083172875417138</v>
       </c>
       <c r="K75">
         <v>2.29</v>
       </c>
       <c r="L75">
-        <v>3.31</v>
+        <v>3.38</v>
       </c>
       <c r="M75">
         <v>1.82</v>
@@ -4490,7 +4544,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4498,31 +4552,31 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C76">
-        <v>0.95505474527386</v>
+        <v>0.8942975364165378</v>
       </c>
       <c r="D76" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E76">
-        <v>1.172750932925077</v>
+        <v>1.124463544226244</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76">
-        <v>0.00580494525472614</v>
+        <v>0.005865702463583462</v>
       </c>
       <c r="H76">
-        <v>0.005027249067074924</v>
+        <v>0.005075536455773756</v>
       </c>
       <c r="I76">
-        <v>0.2176961876512167</v>
+        <v>0.2301660078097063</v>
       </c>
       <c r="J76">
-        <v>1.058928058832376</v>
+        <v>1.085459591084481</v>
       </c>
       <c r="K76">
         <v>2.29</v>
@@ -4540,7 +4594,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4548,31 +4602,31 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C77">
-        <v>0.8997461387005035</v>
+        <v>0.823882990348408</v>
       </c>
       <c r="D77" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E77">
-        <v>1.128793874425728</v>
+        <v>1.068500891892621</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77">
-        <v>0.005860253861299496</v>
+        <v>0.005936117009651592</v>
       </c>
       <c r="H77">
-        <v>0.005071206125574273</v>
+        <v>0.005131499108107379</v>
       </c>
       <c r="I77">
-        <v>0.2290477357252241</v>
+        <v>0.2446179015442134</v>
       </c>
       <c r="J77">
-        <v>1.083080288777073</v>
+        <v>1.1162083011579</v>
       </c>
       <c r="K77">
         <v>2.29</v>
@@ -4590,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4598,31 +4652,31 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C78">
-        <v>0.9004291893178089</v>
+        <v>0.7552208383877499</v>
       </c>
       <c r="D78" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E78">
-        <v>1.129336735615027</v>
+        <v>1.013930971993758</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="G78">
-        <v>0.005859570810682191</v>
+        <v>0.00600477916161225</v>
       </c>
       <c r="H78">
-        <v>0.005070663264384973</v>
+        <v>0.005186069028006243</v>
       </c>
       <c r="I78">
-        <v>0.2289075462972185</v>
+        <v>0.2587101336060078</v>
       </c>
       <c r="J78">
-        <v>1.082782013398337</v>
+        <v>1.146191773629804</v>
       </c>
       <c r="K78">
         <v>2.29</v>
@@ -4640,7 +4694,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4648,31 +4702,31 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C79">
-        <v>0.8995341152947529</v>
+        <v>0.7164672131147527</v>
       </c>
       <c r="D79" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E79">
-        <v>1.128625366740808</v>
+        <v>0.9831311475409823</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="G79">
-        <v>0.005860465884705247</v>
+        <v>0.006043532786885248</v>
       </c>
       <c r="H79">
-        <v>0.005071374633259193</v>
+        <v>0.005216868852459018</v>
       </c>
       <c r="I79">
-        <v>0.2290912514460552</v>
+        <v>0.2666639344262296</v>
       </c>
       <c r="J79">
-        <v>1.083172875417138</v>
+        <v>1.163114754098361</v>
       </c>
       <c r="K79">
         <v>2.29</v>
@@ -4690,7 +4744,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -4698,31 +4752,31 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C80">
-        <v>0.8942975364165378</v>
+        <v>0.6498239504652852</v>
       </c>
       <c r="D80" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E80">
-        <v>1.124463544226244</v>
+        <v>0.9301657597584363</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80">
-        <v>0.005865702463583462</v>
+        <v>0.006110176049534715</v>
       </c>
       <c r="H80">
-        <v>0.005075536455773756</v>
+        <v>0.005269834240241564</v>
       </c>
       <c r="I80">
-        <v>0.2301660078097063</v>
+        <v>0.2803418092931511</v>
       </c>
       <c r="J80">
-        <v>1.085459591084481</v>
+        <v>1.192216615517343</v>
       </c>
       <c r="K80">
         <v>2.29</v>
@@ -4740,7 +4794,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -4751,78 +4805,78 @@
         <v>32</v>
       </c>
       <c r="C81">
-        <v>0.823882990348408</v>
+        <v>0.5205928926738919</v>
       </c>
       <c r="D81" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="E81">
-        <v>1.068500891892621</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="G81">
-        <v>0.005936117009651592</v>
+        <v>0.006459407107326108</v>
       </c>
       <c r="H81">
-        <v>0.005131499108107379</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I81">
-        <v>0.2446179015442134</v>
+        <v>-0.1165511301853397</v>
       </c>
       <c r="J81">
-        <v>1.1162083011579</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K81">
+        <v>2.34</v>
+      </c>
+      <c r="L81">
+        <v>3.49</v>
+      </c>
+      <c r="M81">
         <v>2.29</v>
       </c>
-      <c r="L81">
-        <v>3.38</v>
-      </c>
-      <c r="M81">
-        <v>1.82</v>
-      </c>
       <c r="N81">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="O81">
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="82" spans="1:16">
       <c r="A82" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C82">
-        <v>0.7552208383877499</v>
+        <v>0.474041762488552</v>
       </c>
       <c r="D82" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="E82">
-        <v>1.013930971993758</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82">
-        <v>0.00600477916161225</v>
+        <v>0.006285958237511447</v>
       </c>
       <c r="H82">
-        <v>0.005186069028006243</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I82">
-        <v>0.2587101336060078</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J82">
-        <v>1.146191773629804</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K82">
         <v>2.29</v>
@@ -4831,16 +4885,16 @@
         <v>3.38</v>
       </c>
       <c r="M82">
-        <v>1.82</v>
+        <v>2.29</v>
       </c>
       <c r="N82">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="O82">
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -4851,78 +4905,78 @@
         <v>32</v>
       </c>
       <c r="C83">
-        <v>0.7164672131147527</v>
+        <v>0.3774746016246668</v>
       </c>
       <c r="D83" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="E83">
-        <v>0.9831311475409823</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83">
-        <v>0.006043532786885248</v>
+        <v>0.006602525398375333</v>
       </c>
       <c r="H83">
-        <v>0.005216868852459018</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I83">
-        <v>0.2666639344262296</v>
+        <v>-0.1134930470432627</v>
       </c>
       <c r="J83">
-        <v>1.163114754098361</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K83">
+        <v>2.34</v>
+      </c>
+      <c r="L83">
+        <v>3.49</v>
+      </c>
+      <c r="M83">
         <v>2.29</v>
       </c>
-      <c r="L83">
-        <v>3.38</v>
-      </c>
-      <c r="M83">
-        <v>1.82</v>
-      </c>
       <c r="N83">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="O83">
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B84" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C84">
-        <v>0.6498239504652852</v>
+        <v>0.333981554581404</v>
       </c>
       <c r="D84" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="E84">
-        <v>0.9301657597584363</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84">
-        <v>0.006110176049534715</v>
+        <v>0.006426018445418596</v>
       </c>
       <c r="H84">
-        <v>0.005269834240241564</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I84">
-        <v>0.2803418092931511</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J84">
-        <v>1.192216615517343</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K84">
         <v>2.29</v>
@@ -4931,10 +4985,10 @@
         <v>3.38</v>
       </c>
       <c r="M84">
-        <v>1.82</v>
+        <v>2.29</v>
       </c>
       <c r="N84">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="O84">
         <v>1</v>
@@ -4948,31 +5002,31 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C85">
-        <v>0.5205928926738919</v>
+        <v>0.2442505289553791</v>
       </c>
       <c r="D85" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E85">
-        <v>0.4040417624885522</v>
+        <v>0.1336041501315459</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85">
-        <v>0.006459407107326108</v>
+        <v>0.006735749471044622</v>
       </c>
       <c r="H85">
-        <v>0.006215958237511448</v>
+        <v>0.006486395849868455</v>
       </c>
       <c r="I85">
-        <v>-0.1165511301853397</v>
+        <v>-0.1106463788238332</v>
       </c>
       <c r="J85">
-        <v>1.268977396293209</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K85">
         <v>2.34</v>
@@ -4990,7 +5044,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -4998,31 +5052,31 @@
         <v>1</v>
       </c>
       <c r="B86" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C86">
-        <v>0.474041762488552</v>
+        <v>0.2036041501315458</v>
       </c>
       <c r="D86" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E86">
-        <v>0.4040417624885522</v>
+        <v>0.1336041501315459</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86">
-        <v>0.006285958237511447</v>
+        <v>0.006556395849868454</v>
       </c>
       <c r="H86">
-        <v>0.006215958237511448</v>
+        <v>0.006486395849868455</v>
       </c>
       <c r="I86">
         <v>-0.06999999999999984</v>
       </c>
       <c r="J86">
-        <v>1.268977396293209</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K86">
         <v>2.29</v>
@@ -5040,257 +5094,257 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B87" t="s">
         <v>33</v>
       </c>
       <c r="C87">
-        <v>0.3774746016246668</v>
+        <v>0.2977942894248136</v>
       </c>
       <c r="D87" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="E87">
-        <v>0.2639815545814042</v>
+        <v>0.5755281891875166</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87">
-        <v>0.006602525398375333</v>
+        <v>0.006262205710575186</v>
       </c>
       <c r="H87">
-        <v>0.006356018445418596</v>
+        <v>0.005624471810812484</v>
       </c>
       <c r="I87">
-        <v>-0.1134930470432627</v>
+        <v>0.277733899762703</v>
       </c>
       <c r="J87">
-        <v>1.330139059134758</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K87">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="L87">
-        <v>3.49</v>
+        <v>3.28</v>
       </c>
       <c r="M87">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="N87">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="O87">
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C88">
-        <v>0.333981554581404</v>
+        <v>1.851150997400674</v>
       </c>
       <c r="D88" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E88">
-        <v>0.2639815545814042</v>
+        <v>1.622642804691997</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G88">
-        <v>0.006426018445418596</v>
+        <v>0.004988849002599325</v>
       </c>
       <c r="H88">
-        <v>0.006356018445418596</v>
+        <v>0.004537357195308004</v>
       </c>
       <c r="I88">
-        <v>-0.06999999999999984</v>
+        <v>0.2285081927086774</v>
       </c>
       <c r="J88">
-        <v>1.330139059134758</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K88">
-        <v>2.29</v>
+        <v>1.97</v>
       </c>
       <c r="L88">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="M88">
-        <v>2.29</v>
+        <v>1.83</v>
       </c>
       <c r="N88">
-        <v>3.31</v>
+        <v>3.08</v>
       </c>
       <c r="O88">
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
     </row>
     <row r="89" spans="1:16">
       <c r="A89" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B89" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C89">
-        <v>0.2442505289553791</v>
+        <v>1.833368794275822</v>
       </c>
       <c r="D89" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E89">
-        <v>0.1336041501315459</v>
+        <v>1.622642804691997</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G89">
-        <v>0.006735749471044622</v>
+        <v>0.005066631205724178</v>
       </c>
       <c r="H89">
-        <v>0.006486395849868455</v>
+        <v>0.004537357195308004</v>
       </c>
       <c r="I89">
-        <v>-0.1106463788238332</v>
+        <v>0.2107259895838252</v>
       </c>
       <c r="J89">
-        <v>1.387072423523342</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K89">
-        <v>2.34</v>
+        <v>2.03</v>
       </c>
       <c r="L89">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="M89">
-        <v>2.29</v>
+        <v>1.83</v>
       </c>
       <c r="N89">
-        <v>3.31</v>
+        <v>3.08</v>
       </c>
       <c r="O89">
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C90">
-        <v>0.2036041501315458</v>
+        <v>1.825554329597634</v>
       </c>
       <c r="D90" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E90">
-        <v>0.1336041501315459</v>
+        <v>1.61559823801166</v>
       </c>
       <c r="F90">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G90">
-        <v>0.006556395849868454</v>
+        <v>0.005074445670402367</v>
       </c>
       <c r="H90">
-        <v>0.006486395849868455</v>
+        <v>0.00454440176198834</v>
       </c>
       <c r="I90">
-        <v>-0.06999999999999984</v>
+        <v>0.2099560915859742</v>
       </c>
       <c r="J90">
-        <v>1.387072423523342</v>
+        <v>0.8002195420701311</v>
       </c>
       <c r="K90">
-        <v>2.29</v>
+        <v>2.03</v>
       </c>
       <c r="L90">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="M90">
-        <v>2.29</v>
+        <v>1.83</v>
       </c>
       <c r="N90">
-        <v>3.31</v>
+        <v>3.08</v>
       </c>
       <c r="O90">
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C91">
-        <v>0.2977942894248136</v>
+        <v>1.814964366537685</v>
       </c>
       <c r="D91" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E91">
-        <v>0.5755281891875166</v>
+        <v>1.606051621065991</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G91">
-        <v>0.006262205710575186</v>
+        <v>0.005085035633462316</v>
       </c>
       <c r="H91">
-        <v>0.005624471810812484</v>
+        <v>0.004553948378934009</v>
       </c>
       <c r="I91">
-        <v>0.277733899762703</v>
+        <v>0.2089127454716935</v>
       </c>
       <c r="J91">
-        <v>1.387072423523342</v>
+        <v>0.8054362726415348</v>
       </c>
       <c r="K91">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="L91">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="M91">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="N91">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="O91">
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5301,34 +5355,34 @@
         <v>29</v>
       </c>
       <c r="C92">
-        <v>1.851150997400674</v>
+        <v>1.80276175127278</v>
       </c>
       <c r="D92" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E92">
-        <v>1.622642804691997</v>
+        <v>1.595051233906003</v>
       </c>
       <c r="F92">
         <v>-1</v>
       </c>
       <c r="G92">
-        <v>0.004988849002599325</v>
+        <v>0.005097238248727221</v>
       </c>
       <c r="H92">
-        <v>0.004537357195308004</v>
+        <v>0.004564948766093997</v>
       </c>
       <c r="I92">
-        <v>0.2285081927086774</v>
+        <v>0.2077105173667766</v>
       </c>
       <c r="J92">
-        <v>0.7963700520808761</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K92">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="L92">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="M92">
         <v>1.83</v>
@@ -5340,39 +5394,39 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="93" spans="1:16">
       <c r="A93" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C93">
-        <v>1.833368794275822</v>
+        <v>1.799355758249058</v>
       </c>
       <c r="D93" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E93">
-        <v>1.622642804691997</v>
+        <v>1.591980806697426</v>
       </c>
       <c r="F93">
         <v>-1</v>
       </c>
       <c r="G93">
-        <v>0.005066631205724178</v>
+        <v>0.005100644241750943</v>
       </c>
       <c r="H93">
-        <v>0.004537357195308004</v>
+        <v>0.004568019193302574</v>
       </c>
       <c r="I93">
-        <v>0.2107259895838252</v>
+        <v>0.2073749515516314</v>
       </c>
       <c r="J93">
-        <v>0.7963700520808761</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K93">
         <v>2.03</v>
@@ -5390,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5398,37 +5452,37 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C94">
-        <v>1.825554329597634</v>
+        <v>1.750849917183753</v>
       </c>
       <c r="D94" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E94">
-        <v>1.61559823801166</v>
+        <v>1.581051389485984</v>
       </c>
       <c r="F94">
         <v>-1</v>
       </c>
       <c r="G94">
-        <v>0.005074445670402367</v>
+        <v>0.005109150082816248</v>
       </c>
       <c r="H94">
-        <v>0.00454440176198834</v>
+        <v>0.004578948610514017</v>
       </c>
       <c r="I94">
-        <v>0.2099560915859742</v>
+        <v>0.1697985276977689</v>
       </c>
       <c r="J94">
-        <v>0.8002195420701311</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K94">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="L94">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="M94">
         <v>1.83</v>
@@ -5440,57 +5494,57 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>29</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95" spans="1:16">
       <c r="A95" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B95" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C95">
-        <v>1.814964366537685</v>
+        <v>1.753412348936472</v>
       </c>
       <c r="D95" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E95">
-        <v>1.606051621065991</v>
+        <v>1.851301116496863</v>
       </c>
       <c r="F95">
         <v>-1</v>
       </c>
       <c r="G95">
-        <v>0.005085035633462316</v>
+        <v>0.005406587651063528</v>
       </c>
       <c r="H95">
-        <v>0.004553948378934009</v>
+        <v>0.006028698883503138</v>
       </c>
       <c r="I95">
-        <v>0.2089127454716935</v>
+        <v>-0.09788876756039033</v>
       </c>
       <c r="J95">
-        <v>0.8054362726415348</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K95">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="L95">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="M95">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="N95">
-        <v>3.08</v>
+        <v>3.94</v>
       </c>
       <c r="O95">
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5498,37 +5552,37 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C96">
-        <v>1.80276175127278</v>
+        <v>1.754194230856962</v>
       </c>
       <c r="D96" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E96">
-        <v>1.595051233906003</v>
+        <v>1.58403680120402</v>
       </c>
       <c r="F96">
         <v>-1</v>
       </c>
       <c r="G96">
-        <v>0.005097238248727221</v>
+        <v>0.005105805769143037</v>
       </c>
       <c r="H96">
-        <v>0.004564948766093997</v>
+        <v>0.00457596319879598</v>
       </c>
       <c r="I96">
-        <v>0.2077105173667766</v>
+        <v>0.1701574296529424</v>
       </c>
       <c r="J96">
-        <v>0.8114474131661186</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K96">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="L96">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="M96">
         <v>1.83</v>
@@ -5540,7 +5594,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5548,49 +5602,49 @@
         <v>1</v>
       </c>
       <c r="B97" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C97">
-        <v>1.766532803009457</v>
+        <v>1.757050309663915</v>
       </c>
       <c r="D97" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E97">
-        <v>1.595051233906003</v>
+        <v>1.855461116431831</v>
       </c>
       <c r="F97">
         <v>-1</v>
       </c>
       <c r="G97">
-        <v>0.005093467196990544</v>
+        <v>0.005402949690336085</v>
       </c>
       <c r="H97">
-        <v>0.004564948766093997</v>
+        <v>0.006024538883568169</v>
       </c>
       <c r="I97">
-        <v>0.1714815691034541</v>
+        <v>-0.09841080676791614</v>
       </c>
       <c r="J97">
-        <v>0.8114474131661186</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K97">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="L97">
-        <v>3.43</v>
+        <v>3.58</v>
       </c>
       <c r="M97">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="N97">
-        <v>3.08</v>
+        <v>3.94</v>
       </c>
       <c r="O97">
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5598,37 +5652,37 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C98">
-        <v>1.799355758249058</v>
+        <v>1.755052845867249</v>
       </c>
       <c r="D98" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E98">
-        <v>1.591980806697426</v>
+        <v>1.584803272164423</v>
       </c>
       <c r="F98">
         <v>-1</v>
       </c>
       <c r="G98">
-        <v>0.005100644241750943</v>
+        <v>0.005104947154132751</v>
       </c>
       <c r="H98">
-        <v>0.004568019193302574</v>
+        <v>0.004575196727835578</v>
       </c>
       <c r="I98">
-        <v>0.2073749515516314</v>
+        <v>0.1702495737028269</v>
       </c>
       <c r="J98">
-        <v>0.8131252422418436</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K98">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="L98">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="M98">
         <v>1.83</v>
@@ -5640,7 +5694,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5648,49 +5702,49 @@
         <v>1</v>
       </c>
       <c r="B99" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C99">
-        <v>1.763093253404221</v>
+        <v>1.757984315260471</v>
       </c>
       <c r="D99" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E99">
-        <v>1.591980806697426</v>
+        <v>1.85652914973731</v>
       </c>
       <c r="F99">
         <v>-1</v>
       </c>
       <c r="G99">
-        <v>0.00509690674659578</v>
+        <v>0.005402015684739529</v>
       </c>
       <c r="H99">
-        <v>0.004568019193302574</v>
+        <v>0.006023470850262691</v>
       </c>
       <c r="I99">
-        <v>0.1711124467067946</v>
+        <v>-0.09854483447683893</v>
       </c>
       <c r="J99">
-        <v>0.8131252422418436</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K99">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="L99">
-        <v>3.43</v>
+        <v>3.58</v>
       </c>
       <c r="M99">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="N99">
-        <v>3.08</v>
+        <v>3.94</v>
       </c>
       <c r="O99">
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -5698,31 +5752,31 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C100">
-        <v>1.758945050051923</v>
+        <v>1.753786160185185</v>
       </c>
       <c r="D100" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E100">
-        <v>1.588277776387814</v>
+        <v>1.574612606219512</v>
       </c>
       <c r="F100">
         <v>-1</v>
       </c>
       <c r="G100">
-        <v>0.005101054949948077</v>
+        <v>0.005106213839814816</v>
       </c>
       <c r="H100">
-        <v>0.004571722223612186</v>
+        <v>0.004665387393780488</v>
       </c>
       <c r="I100">
-        <v>0.1706672736641091</v>
+        <v>0.1791735539656729</v>
       </c>
       <c r="J100">
-        <v>0.8151487560722326</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K100">
         <v>2.05</v>
@@ -5731,66 +5785,66 @@
         <v>3.43</v>
       </c>
       <c r="M100">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="N100">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="O100">
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B101" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C101">
-        <v>1.750849917183753</v>
+        <v>1.756606408396567</v>
       </c>
       <c r="D101" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E101">
-        <v>1.571905533403557</v>
+        <v>1.854953516327912</v>
       </c>
       <c r="F101">
         <v>-1</v>
       </c>
       <c r="G101">
-        <v>0.005109150082816248</v>
+        <v>0.005403393591603433</v>
       </c>
       <c r="H101">
-        <v>0.004668094466596443</v>
+        <v>0.006025046483672087</v>
       </c>
       <c r="I101">
-        <v>0.1789443837801954</v>
+        <v>-0.09834710793134582</v>
       </c>
       <c r="J101">
-        <v>0.8190976013737793</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K101">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="L101">
-        <v>3.43</v>
+        <v>3.58</v>
       </c>
       <c r="M101">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="N101">
-        <v>3.12</v>
+        <v>3.94</v>
       </c>
       <c r="O101">
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -5798,99 +5852,99 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C102">
-        <v>1.732368893145465</v>
+        <v>1.755683380438077</v>
       </c>
       <c r="D102" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E102">
-        <v>1.574988827473004</v>
+        <v>1.853898035926949</v>
       </c>
       <c r="F102">
         <v>-1</v>
       </c>
       <c r="G102">
-        <v>0.005067631106854534</v>
+        <v>0.005404316619561924</v>
       </c>
       <c r="H102">
-        <v>0.004665011172526996</v>
+        <v>0.00602610196407305</v>
       </c>
       <c r="I102">
-        <v>0.1573800656724604</v>
+        <v>-0.09821465548887209</v>
       </c>
       <c r="J102">
-        <v>0.8174662288502623</v>
+        <v>0.8180792015972748</v>
       </c>
       <c r="K102">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="L102">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="M102">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="N102">
-        <v>3.12</v>
+        <v>3.94</v>
       </c>
       <c r="O102">
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
     </row>
     <row r="103" spans="1:16">
       <c r="A103" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C103">
-        <v>1.754194230856962</v>
+        <v>1.753286997752252</v>
       </c>
       <c r="D103" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E103">
-        <v>1.574988827473004</v>
+        <v>1.851157777698763</v>
       </c>
       <c r="F103">
         <v>-1</v>
       </c>
       <c r="G103">
-        <v>0.005105805769143037</v>
+        <v>0.005406713002247748</v>
       </c>
       <c r="H103">
-        <v>0.004665011172526996</v>
+        <v>0.006028842222301236</v>
       </c>
       <c r="I103">
-        <v>0.1792054033839581</v>
+        <v>-0.0978707799465115</v>
       </c>
       <c r="J103">
-        <v>0.8174662288502623</v>
+        <v>0.8191538126671517</v>
       </c>
       <c r="K103">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="L103">
-        <v>3.43</v>
+        <v>3.58</v>
       </c>
       <c r="M103">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="N103">
-        <v>3.12</v>
+        <v>3.94</v>
       </c>
       <c r="O103">
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -5898,49 +5952,49 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C104">
-        <v>1.755052845867249</v>
+        <v>1.759765740315211</v>
       </c>
       <c r="D104" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E104">
-        <v>1.57578042862883</v>
+        <v>1.858566205293179</v>
       </c>
       <c r="F104">
         <v>-1</v>
       </c>
       <c r="G104">
-        <v>0.005104947154132751</v>
+        <v>0.005400234259684789</v>
       </c>
       <c r="H104">
-        <v>0.00466421957137117</v>
+        <v>0.006021433794706822</v>
       </c>
       <c r="I104">
-        <v>0.1792724172384195</v>
+        <v>-0.09880046497796746</v>
       </c>
       <c r="J104">
-        <v>0.8170473922598784</v>
+        <v>0.8162485469438515</v>
       </c>
       <c r="K104">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="L104">
-        <v>3.43</v>
+        <v>3.58</v>
       </c>
       <c r="M104">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="N104">
-        <v>3.12</v>
+        <v>3.94</v>
       </c>
       <c r="O104">
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -5948,49 +6002,49 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C105">
-        <v>1.740014143224429</v>
+        <v>1.768370582676801</v>
       </c>
       <c r="D105" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E105">
-        <v>1.823363933674754</v>
+        <v>1.868405823240289</v>
       </c>
       <c r="F105">
         <v>-1</v>
       </c>
       <c r="G105">
-        <v>0.005079985856775571</v>
+        <v>0.005391629417323198</v>
       </c>
       <c r="H105">
-        <v>0.005336636066325246</v>
+        <v>0.006011594176759711</v>
       </c>
       <c r="I105">
-        <v>-0.0833497904503242</v>
+        <v>-0.1000352405634874</v>
       </c>
       <c r="J105">
-        <v>0.7877291777243258</v>
+        <v>0.8123898732391025</v>
       </c>
       <c r="K105">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L105">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M105">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N105">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O105">
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -5998,49 +6052,49 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C106">
-        <v>1.740936473690798</v>
+        <v>1.772475206570581</v>
       </c>
       <c r="D106" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E106">
-        <v>1.824334120910604</v>
+        <v>1.873099451459633</v>
       </c>
       <c r="F106">
         <v>-1</v>
       </c>
       <c r="G106">
-        <v>0.005079063526309202</v>
+        <v>0.005387524793429419</v>
       </c>
       <c r="H106">
-        <v>0.005335665879089396</v>
+        <v>0.006006900548540367</v>
       </c>
       <c r="I106">
-        <v>-0.08339764721980569</v>
+        <v>-0.1006242448890518</v>
       </c>
       <c r="J106">
-        <v>0.7872941161835857</v>
+        <v>0.8105492347217125</v>
       </c>
       <c r="K106">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L106">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M106">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N106">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O106">
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6048,49 +6102,49 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C107">
-        <v>1.737999731721985</v>
+        <v>1.778785868167223</v>
       </c>
       <c r="D107" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E107">
-        <v>1.821245000820767</v>
+        <v>1.880315678845928</v>
       </c>
       <c r="F107">
         <v>-1</v>
       </c>
       <c r="G107">
-        <v>0.005082000268278016</v>
+        <v>0.005381214131832777</v>
       </c>
       <c r="H107">
-        <v>0.005338754999179234</v>
+        <v>0.005999684321154073</v>
       </c>
       <c r="I107">
-        <v>-0.08324526909878238</v>
+        <v>-0.1015298106787046</v>
       </c>
       <c r="J107">
-        <v>0.7886793718292525</v>
+        <v>0.8077193416290479</v>
       </c>
       <c r="K107">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L107">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M107">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N107">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O107">
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6098,49 +6152,49 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C108">
-        <v>1.735312288398669</v>
+        <v>1.783082667864885</v>
       </c>
       <c r="D108" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E108">
-        <v>1.818418114683505</v>
+        <v>1.885229059666124</v>
       </c>
       <c r="F108">
         <v>-1</v>
       </c>
       <c r="G108">
-        <v>0.005084687711601332</v>
+        <v>0.005376917332135115</v>
       </c>
       <c r="H108">
-        <v>0.005341581885316495</v>
+        <v>0.005994770940333876</v>
       </c>
       <c r="I108">
-        <v>-0.08310582628483654</v>
+        <v>-0.1021463918012393</v>
       </c>
       <c r="J108">
-        <v>0.7899470337742129</v>
+        <v>0.8057925256211278</v>
       </c>
       <c r="K108">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L108">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M108">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N108">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O108">
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6148,49 +6202,49 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C109">
-        <v>1.734303254574541</v>
+        <v>1.788647602775973</v>
       </c>
       <c r="D109" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E109">
-        <v>1.817356725330768</v>
+        <v>1.891592550259521</v>
       </c>
       <c r="F109">
         <v>-1</v>
       </c>
       <c r="G109">
-        <v>0.005085696745425459</v>
+        <v>0.005371352397224027</v>
       </c>
       <c r="H109">
-        <v>0.005342643274669232</v>
+        <v>0.00598840744974048</v>
       </c>
       <c r="I109">
-        <v>-0.08305347075622627</v>
+        <v>-0.1029449474835478</v>
       </c>
       <c r="J109">
-        <v>0.7904229931252164</v>
+        <v>0.8032970391139135</v>
       </c>
       <c r="K109">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L109">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M109">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N109">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O109">
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6198,99 +6252,99 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C110">
-        <v>1.720598225993867</v>
+        <v>1.794449014383639</v>
       </c>
       <c r="D110" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E110">
-        <v>1.567308310528363</v>
+        <v>1.898226451425238</v>
       </c>
       <c r="F110">
         <v>-1</v>
       </c>
       <c r="G110">
-        <v>0.004679401774006134</v>
+        <v>0.005365550985616361</v>
       </c>
       <c r="H110">
-        <v>0.004652691689471636</v>
+        <v>0.005981773548574762</v>
       </c>
       <c r="I110">
-        <v>0.1532899154655032</v>
+        <v>-0.1037774370415987</v>
       </c>
       <c r="J110">
-        <v>0.791123943318788</v>
+        <v>0.8006955092450049</v>
       </c>
       <c r="K110">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="L110">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="M110">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="N110">
-        <v>3.11</v>
+        <v>3.94</v>
       </c>
       <c r="O110">
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="111" spans="1:16">
       <c r="A111" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C111">
-        <v>1.732817240164169</v>
+        <v>1.799039794456311</v>
       </c>
       <c r="D111" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E111">
-        <v>1.815793606399103</v>
+        <v>1.903475998145109</v>
       </c>
       <c r="F111">
         <v>-1</v>
       </c>
       <c r="G111">
-        <v>0.005087182759835831</v>
+        <v>0.005360960205543689</v>
       </c>
       <c r="H111">
-        <v>0.005344206393600897</v>
+        <v>0.005976524001854891</v>
       </c>
       <c r="I111">
-        <v>-0.08297636623493343</v>
+        <v>-0.104436203688798</v>
       </c>
       <c r="J111">
-        <v>0.791123943318788</v>
+        <v>0.7986368634725065</v>
       </c>
       <c r="K111">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L111">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M111">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N111">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O111">
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6298,99 +6352,99 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C112">
-        <v>1.719739270136877</v>
+        <v>1.809214910520444</v>
       </c>
       <c r="D112" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E112">
-        <v>1.566412607896743</v>
+        <v>1.915111220550284</v>
       </c>
       <c r="F112">
         <v>-1</v>
       </c>
       <c r="G112">
-        <v>0.004680260729863123</v>
+        <v>0.005350785089479557</v>
       </c>
       <c r="H112">
-        <v>0.004653587392103257</v>
+        <v>0.005964888779449715</v>
       </c>
       <c r="I112">
-        <v>0.1533266622401337</v>
+        <v>-0.1058963100298396</v>
       </c>
       <c r="J112">
-        <v>0.7915832780016702</v>
+        <v>0.7940740311567515</v>
       </c>
       <c r="K112">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="L112">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="M112">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="N112">
-        <v>3.11</v>
+        <v>3.94</v>
       </c>
       <c r="O112">
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="113" spans="1:16">
       <c r="A113" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C113">
-        <v>1.731843450636459</v>
+        <v>1.820107451446974</v>
       </c>
       <c r="D113" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E113">
-        <v>1.814769290056276</v>
+        <v>1.927566816677033</v>
       </c>
       <c r="F113">
         <v>-1</v>
       </c>
       <c r="G113">
-        <v>0.005088156549363541</v>
+        <v>0.005339892548553027</v>
       </c>
       <c r="H113">
-        <v>0.005345230709943724</v>
+        <v>0.005952433183322967</v>
       </c>
       <c r="I113">
-        <v>-0.08292583941981624</v>
+        <v>-0.1074593652300591</v>
       </c>
       <c r="J113">
-        <v>0.7915832780016702</v>
+        <v>0.7891894836560657</v>
       </c>
       <c r="K113">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L113">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M113">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N113">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O113">
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6398,99 +6452,99 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C114">
-        <v>1.720624811893301</v>
+        <v>1.823117018134749</v>
       </c>
       <c r="D114" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E114">
-        <v>1.567336033792479</v>
+        <v>1.931008249436597</v>
       </c>
       <c r="F114">
         <v>-1</v>
       </c>
       <c r="G114">
-        <v>0.004679375188106701</v>
+        <v>0.005336882981865252</v>
       </c>
       <c r="H114">
-        <v>0.004652663966207521</v>
+        <v>0.005948991750563403</v>
       </c>
       <c r="I114">
-        <v>0.1532887781008216</v>
+        <v>-0.1078912313018474</v>
       </c>
       <c r="J114">
-        <v>0.7911097262602672</v>
+        <v>0.7878399021817268</v>
       </c>
       <c r="K114">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="L114">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="M114">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="N114">
-        <v>3.11</v>
+        <v>3.94</v>
       </c>
       <c r="O114">
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>50</v>
+        <v>112</v>
       </c>
     </row>
     <row r="115" spans="1:16">
       <c r="A115" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C115">
-        <v>1.732847380328234</v>
+        <v>1.823363933674754</v>
       </c>
       <c r="D115" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E115">
-        <v>1.815825310439604</v>
+        <v>1.931290596802969</v>
       </c>
       <c r="F115">
         <v>-1</v>
       </c>
       <c r="G115">
-        <v>0.005087152619671767</v>
+        <v>0.005336636066325246</v>
       </c>
       <c r="H115">
-        <v>0.005344174689560396</v>
+        <v>0.00594870940319703</v>
       </c>
       <c r="I115">
-        <v>-0.08297793011137067</v>
+        <v>-0.1079266631282159</v>
       </c>
       <c r="J115">
-        <v>0.7911097262602672</v>
+        <v>0.7877291777243258</v>
       </c>
       <c r="K115">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L115">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M115">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N115">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O115">
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>50</v>
+        <v>113</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6498,99 +6552,99 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C116">
-        <v>1.721822046417237</v>
+        <v>1.824334120910604</v>
       </c>
       <c r="D116" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E116">
-        <v>1.568584486905675</v>
+        <v>1.932400003731856</v>
       </c>
       <c r="F116">
         <v>-1</v>
       </c>
       <c r="G116">
-        <v>0.004678177953582763</v>
+        <v>0.005335665879089396</v>
       </c>
       <c r="H116">
-        <v>0.004651415513094326</v>
+        <v>0.005947599996268144</v>
       </c>
       <c r="I116">
-        <v>0.1532375595115623</v>
+        <v>-0.1080658828212524</v>
       </c>
       <c r="J116">
-        <v>0.7904694938945258</v>
+        <v>0.7872941161835857</v>
       </c>
       <c r="K116">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="L116">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="M116">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="N116">
-        <v>3.11</v>
+        <v>3.94</v>
       </c>
       <c r="O116">
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="117" spans="1:16">
       <c r="A117" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C117">
-        <v>1.734204672943605</v>
+        <v>1.821245000820767</v>
       </c>
       <c r="D117" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E117">
-        <v>1.817253028615208</v>
+        <v>1.928867601835406</v>
       </c>
       <c r="F117">
         <v>-1</v>
       </c>
       <c r="G117">
-        <v>0.005085795327056396</v>
+        <v>0.005338754999179234</v>
       </c>
       <c r="H117">
-        <v>0.005342746971384794</v>
+        <v>0.005951132398164594</v>
       </c>
       <c r="I117">
-        <v>-0.08304835567160218</v>
+        <v>-0.1076226010146393</v>
       </c>
       <c r="J117">
-        <v>0.7904694938945258</v>
+        <v>0.7886793718292525</v>
       </c>
       <c r="K117">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L117">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M117">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N117">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O117">
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6598,99 +6652,99 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C118">
-        <v>1.72428138280355</v>
+        <v>1.818418114683505</v>
       </c>
       <c r="D118" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E118">
-        <v>1.571149035543809</v>
+        <v>1.925635063875757</v>
       </c>
       <c r="F118">
         <v>-1</v>
       </c>
       <c r="G118">
-        <v>0.00467571861719645</v>
+        <v>0.005341581885316495</v>
       </c>
       <c r="H118">
-        <v>0.004648850964456191</v>
+        <v>0.005954364936124243</v>
       </c>
       <c r="I118">
-        <v>0.1531323472597415</v>
+        <v>-0.1072169491922517</v>
       </c>
       <c r="J118">
-        <v>0.7891543407467646</v>
+        <v>0.7899470337742129</v>
       </c>
       <c r="K118">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="L118">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="M118">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="N118">
-        <v>3.11</v>
+        <v>3.94</v>
       </c>
       <c r="O118">
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="119" spans="1:16">
       <c r="A119" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C119">
-        <v>1.736992797616859</v>
+        <v>1.817356725330768</v>
       </c>
       <c r="D119" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E119">
-        <v>1.820185820134715</v>
+        <v>1.924421367530698</v>
       </c>
       <c r="F119">
         <v>-1</v>
       </c>
       <c r="G119">
-        <v>0.005083007202383142</v>
+        <v>0.005342643274669232</v>
       </c>
       <c r="H119">
-        <v>0.005339814179865285</v>
+        <v>0.005955578632469301</v>
       </c>
       <c r="I119">
-        <v>-0.08319302251785587</v>
+        <v>-0.1070646421999308</v>
       </c>
       <c r="J119">
-        <v>0.7891543407467646</v>
+        <v>0.7904229931252164</v>
       </c>
       <c r="K119">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L119">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M119">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N119">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O119">
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -6698,99 +6752,99 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C120">
-        <v>1.727206229285669</v>
+        <v>1.815793606399103</v>
       </c>
       <c r="D120" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E120">
-        <v>1.574199009148157</v>
+        <v>1.922633944537091</v>
       </c>
       <c r="F120">
         <v>-1</v>
       </c>
       <c r="G120">
-        <v>0.004672793770714332</v>
+        <v>0.005344206393600897</v>
       </c>
       <c r="H120">
-        <v>0.004645800990851843</v>
+        <v>0.00595736605546291</v>
       </c>
       <c r="I120">
-        <v>0.1530072201375119</v>
+        <v>-0.1068403381379877</v>
       </c>
       <c r="J120">
-        <v>0.7875902517188939</v>
+        <v>0.791123943318788</v>
       </c>
       <c r="K120">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="L120">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="M120">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="N120">
-        <v>3.11</v>
+        <v>3.94</v>
       </c>
       <c r="O120">
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="121" spans="1:16">
       <c r="A121" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C121">
-        <v>1.740308666355945</v>
+        <v>1.814769290056276</v>
       </c>
       <c r="D121" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E121">
-        <v>1.823673738666867</v>
+        <v>1.921462641095741</v>
       </c>
       <c r="F121">
         <v>-1</v>
       </c>
       <c r="G121">
-        <v>0.005079691333644055</v>
+        <v>0.005345230709943724</v>
       </c>
       <c r="H121">
-        <v>0.005336326261333134</v>
+        <v>0.005958537358904259</v>
       </c>
       <c r="I121">
-        <v>-0.08336507231092183</v>
+        <v>-0.1066933510394659</v>
       </c>
       <c r="J121">
-        <v>0.7875902517188939</v>
+        <v>0.7915832780016702</v>
       </c>
       <c r="K121">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L121">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M121">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N121">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O121">
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -6798,99 +6852,99 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C122">
-        <v>1.728676249745893</v>
+        <v>1.815825310439604</v>
       </c>
       <c r="D122" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E122">
-        <v>1.57573191818422</v>
+        <v>1.922670198036319</v>
       </c>
       <c r="F122">
         <v>-1</v>
       </c>
       <c r="G122">
-        <v>0.004671323750254107</v>
+        <v>0.005344174689560396</v>
       </c>
       <c r="H122">
-        <v>0.00464426808181578</v>
+        <v>0.005957329801963681</v>
       </c>
       <c r="I122">
-        <v>0.1529443315616732</v>
+        <v>-0.1068448875967143</v>
       </c>
       <c r="J122">
-        <v>0.7868041445209126</v>
+        <v>0.7911097262602672</v>
       </c>
       <c r="K122">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="L122">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="M122">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="N122">
-        <v>3.11</v>
+        <v>3.94</v>
       </c>
       <c r="O122">
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="123" spans="1:16">
       <c r="A123" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C123">
-        <v>1.741975213615665</v>
+        <v>1.817253028615208</v>
       </c>
       <c r="D123" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E123">
-        <v>1.825426757718365</v>
+        <v>1.924302790568959</v>
       </c>
       <c r="F123">
         <v>-1</v>
       </c>
       <c r="G123">
-        <v>0.005078024786384335</v>
+        <v>0.005342746971384794</v>
       </c>
       <c r="H123">
-        <v>0.005334573242281635</v>
+        <v>0.00595569720943104</v>
       </c>
       <c r="I123">
-        <v>-0.08345154410269973</v>
+        <v>-0.1070497619537516</v>
       </c>
       <c r="J123">
-        <v>0.7868041445209126</v>
+        <v>0.7904694938945258</v>
       </c>
       <c r="K123">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L123">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M123">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N123">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O123">
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -6898,99 +6952,99 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C124">
-        <v>1.731283335374008</v>
+        <v>1.820185820134715</v>
       </c>
       <c r="D124" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E124">
-        <v>1.578450536887334</v>
+        <v>1.92765643109575</v>
       </c>
       <c r="F124">
         <v>-1</v>
       </c>
       <c r="G124">
-        <v>0.004668716664625992</v>
+        <v>0.005339814179865285</v>
       </c>
       <c r="H124">
-        <v>0.004641549463112665</v>
+        <v>0.005952343568904249</v>
       </c>
       <c r="I124">
-        <v>0.1528327984866735</v>
+        <v>-0.1074706109610355</v>
       </c>
       <c r="J124">
-        <v>0.7854099810834182</v>
+        <v>0.7891543407467646</v>
       </c>
       <c r="K124">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="L124">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="M124">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="N124">
-        <v>3.11</v>
+        <v>3.94</v>
       </c>
       <c r="O124">
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="125" spans="1:16">
       <c r="A125" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C125">
-        <v>1.744930840103154</v>
+        <v>1.823673738666867</v>
       </c>
       <c r="D125" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E125">
-        <v>1.828535742183977</v>
+        <v>1.931644858116821</v>
       </c>
       <c r="F125">
         <v>-1</v>
       </c>
       <c r="G125">
-        <v>0.005075069159896847</v>
+        <v>0.005336326261333134</v>
       </c>
       <c r="H125">
-        <v>0.005331464257816023</v>
+        <v>0.005948355141883179</v>
       </c>
       <c r="I125">
-        <v>-0.08360490208082383</v>
+        <v>-0.1079711194499537</v>
       </c>
       <c r="J125">
-        <v>0.7854099810834182</v>
+        <v>0.7875902517188939</v>
       </c>
       <c r="K125">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L125">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M125">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N125">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O125">
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -6998,49 +7052,49 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C126">
-        <v>1.748898482014188</v>
+        <v>1.825426757718365</v>
       </c>
       <c r="D126" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E126">
-        <v>1.832709252307377</v>
+        <v>1.933649431471673</v>
       </c>
       <c r="F126">
         <v>-1</v>
       </c>
       <c r="G126">
-        <v>0.005071101517985812</v>
+        <v>0.005334573242281635</v>
       </c>
       <c r="H126">
-        <v>0.005327290747692623</v>
+        <v>0.005946350568528327</v>
       </c>
       <c r="I126">
-        <v>-0.08381077029318895</v>
+        <v>-0.1082226737533081</v>
       </c>
       <c r="J126">
-        <v>0.7835384518800999</v>
+        <v>0.7868041445209126</v>
       </c>
       <c r="K126">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L126">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M126">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N126">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O126">
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7048,49 +7102,49 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C127">
-        <v>1.749965012157894</v>
+        <v>1.828535742183977</v>
       </c>
       <c r="D127" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E127">
-        <v>1.833831121279294</v>
+        <v>1.937204548237283</v>
       </c>
       <c r="F127">
         <v>-1</v>
       </c>
       <c r="G127">
-        <v>0.005070034987842107</v>
+        <v>0.005331464257816023</v>
       </c>
       <c r="H127">
-        <v>0.005326168878720706</v>
+        <v>0.005942795451762716</v>
       </c>
       <c r="I127">
-        <v>-0.08386610912140013</v>
+        <v>-0.1086688060533061</v>
       </c>
       <c r="J127">
-        <v>0.783035371623635</v>
+        <v>0.7854099810834182</v>
       </c>
       <c r="K127">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L127">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M127">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N127">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O127">
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7098,49 +7152,49 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C128">
-        <v>1.751367516070874</v>
+        <v>1.832709252307377</v>
       </c>
       <c r="D128" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E128">
-        <v>1.835306396621721</v>
+        <v>1.941976947705745</v>
       </c>
       <c r="F128">
         <v>-1</v>
       </c>
       <c r="G128">
-        <v>0.005068632483929126</v>
+        <v>0.005327290747692623</v>
       </c>
       <c r="H128">
-        <v>0.005324693603378279</v>
+        <v>0.005938023052294255</v>
       </c>
       <c r="I128">
-        <v>-0.08393888055084719</v>
+        <v>-0.109267695398368</v>
       </c>
       <c r="J128">
-        <v>0.7823738131741161</v>
+        <v>0.7835384518800999</v>
       </c>
       <c r="K128">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L128">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M128">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N128">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O128">
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7148,49 +7202,49 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C129">
-        <v>1.754470592394443</v>
+        <v>1.833831121279294</v>
       </c>
       <c r="D129" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E129">
-        <v>1.838570481622456</v>
+        <v>1.943259802359731</v>
       </c>
       <c r="F129">
         <v>-1</v>
       </c>
       <c r="G129">
-        <v>0.005065529407605558</v>
+        <v>0.005326168878720706</v>
       </c>
       <c r="H129">
-        <v>0.005321429518377544</v>
+        <v>0.005936740197640269</v>
       </c>
       <c r="I129">
-        <v>-0.08409988922801359</v>
+        <v>-0.1094286810804368</v>
       </c>
       <c r="J129">
-        <v>0.7809100979271496</v>
+        <v>0.783035371623635</v>
       </c>
       <c r="K129">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L129">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M129">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N129">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O129">
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7198,49 +7252,49 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C130">
-        <v>1.756079279241895</v>
+        <v>1.835306396621721</v>
       </c>
       <c r="D130" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E130">
-        <v>1.840262638070484</v>
+        <v>1.944946776406004</v>
       </c>
       <c r="F130">
         <v>-1</v>
       </c>
       <c r="G130">
-        <v>0.005063920720758106</v>
+        <v>0.005324693603378279</v>
       </c>
       <c r="H130">
-        <v>0.005319737361929516</v>
+        <v>0.005935053223593996</v>
       </c>
       <c r="I130">
-        <v>-0.08418335882858896</v>
+        <v>-0.1096403797842829</v>
       </c>
       <c r="J130">
-        <v>0.7801512833764644</v>
+        <v>0.7823738131741161</v>
       </c>
       <c r="K130">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L130">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M130">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N130">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O130">
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7248,49 +7302,49 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C131">
-        <v>1.756919146594669</v>
+        <v>1.838570481622456</v>
       </c>
       <c r="D131" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E131">
-        <v>1.841146083446279</v>
+        <v>1.948679250285769</v>
       </c>
       <c r="F131">
         <v>-1</v>
       </c>
       <c r="G131">
-        <v>0.005063080853405332</v>
+        <v>0.005321429518377544</v>
       </c>
       <c r="H131">
-        <v>0.005318853916553721</v>
+        <v>0.005931320749714232</v>
       </c>
       <c r="I131">
-        <v>-0.0842269368516102</v>
+        <v>-0.1101087686633122</v>
       </c>
       <c r="J131">
-        <v>0.7797551195308166</v>
+        <v>0.7809100979271496</v>
       </c>
       <c r="K131">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="L131">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="M131">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="N131">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="O131">
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7298,49 +7352,599 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C132">
-        <v>1.758227892855127</v>
+        <v>1.840262638070484</v>
       </c>
       <c r="D132" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E132">
+        <v>1.950614227390016</v>
+      </c>
+      <c r="F132">
+        <v>-1</v>
+      </c>
+      <c r="G132">
+        <v>0.005319737361929516</v>
+      </c>
+      <c r="H132">
+        <v>0.005929385772609984</v>
+      </c>
+      <c r="I132">
+        <v>-0.1103515893195315</v>
+      </c>
+      <c r="J132">
+        <v>0.7801512833764644</v>
+      </c>
+      <c r="K132">
+        <v>2.23</v>
+      </c>
+      <c r="L132">
+        <v>3.58</v>
+      </c>
+      <c r="M132">
+        <v>2.55</v>
+      </c>
+      <c r="N132">
+        <v>3.94</v>
+      </c>
+      <c r="O132">
+        <v>1</v>
+      </c>
+      <c r="P132" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16">
+      <c r="A133" s="1">
+        <v>0</v>
+      </c>
+      <c r="B133" t="s">
+        <v>24</v>
+      </c>
+      <c r="C133">
+        <v>1.841146083446279</v>
+      </c>
+      <c r="D133" t="s">
+        <v>45</v>
+      </c>
+      <c r="E133">
+        <v>1.951624445196418</v>
+      </c>
+      <c r="F133">
+        <v>-1</v>
+      </c>
+      <c r="G133">
+        <v>0.005318853916553721</v>
+      </c>
+      <c r="H133">
+        <v>0.005928375554803582</v>
+      </c>
+      <c r="I133">
+        <v>-0.1104783617501388</v>
+      </c>
+      <c r="J133">
+        <v>0.7797551195308166</v>
+      </c>
+      <c r="K133">
+        <v>2.23</v>
+      </c>
+      <c r="L133">
+        <v>3.58</v>
+      </c>
+      <c r="M133">
+        <v>2.55</v>
+      </c>
+      <c r="N133">
+        <v>3.94</v>
+      </c>
+      <c r="O133">
+        <v>1</v>
+      </c>
+      <c r="P133" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16">
+      <c r="A134" s="1">
+        <v>0</v>
+      </c>
+      <c r="B134" t="s">
+        <v>24</v>
+      </c>
+      <c r="C134">
         <v>1.842522736352327</v>
       </c>
-      <c r="F132">
-        <v>-1</v>
-      </c>
-      <c r="G132">
-        <v>0.005061772107144873</v>
-      </c>
-      <c r="H132">
+      <c r="D134" t="s">
+        <v>45</v>
+      </c>
+      <c r="E134">
+        <v>1.953198644707818</v>
+      </c>
+      <c r="F134">
+        <v>-1</v>
+      </c>
+      <c r="G134">
         <v>0.005317477263647673</v>
       </c>
-      <c r="I132">
-        <v>-0.08429484349719996</v>
-      </c>
-      <c r="J132">
+      <c r="H134">
+        <v>0.005926801355292182</v>
+      </c>
+      <c r="I134">
+        <v>-0.1106759083554909</v>
+      </c>
+      <c r="J134">
         <v>0.7791377863890909</v>
       </c>
-      <c r="K132">
-        <v>2.12</v>
-      </c>
-      <c r="L132">
-        <v>3.41</v>
-      </c>
-      <c r="M132">
+      <c r="K134">
         <v>2.23</v>
       </c>
-      <c r="N132">
+      <c r="L134">
         <v>3.58</v>
       </c>
-      <c r="O132">
-        <v>1</v>
-      </c>
-      <c r="P132" t="s">
-        <v>123</v>
+      <c r="M134">
+        <v>2.55</v>
+      </c>
+      <c r="N134">
+        <v>3.94</v>
+      </c>
+      <c r="O134">
+        <v>1</v>
+      </c>
+      <c r="P134" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16">
+      <c r="A135" s="1">
+        <v>0</v>
+      </c>
+      <c r="B135" t="s">
+        <v>24</v>
+      </c>
+      <c r="C135">
+        <v>1.845202546126595</v>
+      </c>
+      <c r="D135" t="s">
+        <v>45</v>
+      </c>
+      <c r="E135">
+        <v>1.956263001176151</v>
+      </c>
+      <c r="F135">
+        <v>-1</v>
+      </c>
+      <c r="G135">
+        <v>0.005314797453873405</v>
+      </c>
+      <c r="H135">
+        <v>0.00592373699882385</v>
+      </c>
+      <c r="I135">
+        <v>-0.1110604550495562</v>
+      </c>
+      <c r="J135">
+        <v>0.777936077970137</v>
+      </c>
+      <c r="K135">
+        <v>2.23</v>
+      </c>
+      <c r="L135">
+        <v>3.58</v>
+      </c>
+      <c r="M135">
+        <v>2.55</v>
+      </c>
+      <c r="N135">
+        <v>3.94</v>
+      </c>
+      <c r="O135">
+        <v>1</v>
+      </c>
+      <c r="P135" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16">
+      <c r="A136" s="1">
+        <v>0</v>
+      </c>
+      <c r="B136" t="s">
+        <v>24</v>
+      </c>
+      <c r="C136">
+        <v>1.846576268208859</v>
+      </c>
+      <c r="D136" t="s">
+        <v>45</v>
+      </c>
+      <c r="E136">
+        <v>1.957833849297126</v>
+      </c>
+      <c r="F136">
+        <v>-1</v>
+      </c>
+      <c r="G136">
+        <v>0.005313423731791141</v>
+      </c>
+      <c r="H136">
+        <v>0.005922166150702874</v>
+      </c>
+      <c r="I136">
+        <v>-0.1112575810882668</v>
+      </c>
+      <c r="J136">
+        <v>0.7773200590991663</v>
+      </c>
+      <c r="K136">
+        <v>2.23</v>
+      </c>
+      <c r="L136">
+        <v>3.58</v>
+      </c>
+      <c r="M136">
+        <v>2.55</v>
+      </c>
+      <c r="N136">
+        <v>3.94</v>
+      </c>
+      <c r="O136">
+        <v>1</v>
+      </c>
+      <c r="P136" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16">
+      <c r="A137" s="1">
+        <v>0</v>
+      </c>
+      <c r="B137" t="s">
+        <v>24</v>
+      </c>
+      <c r="C137">
+        <v>1.849099983535997</v>
+      </c>
+      <c r="D137" t="s">
+        <v>45</v>
+      </c>
+      <c r="E137">
+        <v>1.960719712115154</v>
+      </c>
+      <c r="F137">
+        <v>-1</v>
+      </c>
+      <c r="G137">
+        <v>0.005310900016464003</v>
+      </c>
+      <c r="H137">
+        <v>0.005919280287884846</v>
+      </c>
+      <c r="I137">
+        <v>-0.1116197285791567</v>
+      </c>
+      <c r="J137">
+        <v>0.7761883481901358</v>
+      </c>
+      <c r="K137">
+        <v>2.23</v>
+      </c>
+      <c r="L137">
+        <v>3.58</v>
+      </c>
+      <c r="M137">
+        <v>2.55</v>
+      </c>
+      <c r="N137">
+        <v>3.94</v>
+      </c>
+      <c r="O137">
+        <v>1</v>
+      </c>
+      <c r="P137" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16">
+      <c r="A138" s="1">
+        <v>0</v>
+      </c>
+      <c r="B138" t="s">
+        <v>24</v>
+      </c>
+      <c r="C138">
+        <v>1.852047093932714</v>
+      </c>
+      <c r="D138" t="s">
+        <v>45</v>
+      </c>
+      <c r="E138">
+        <v>1.964089726245929</v>
+      </c>
+      <c r="F138">
+        <v>-1</v>
+      </c>
+      <c r="G138">
+        <v>0.005307952906067286</v>
+      </c>
+      <c r="H138">
+        <v>0.005915910273754071</v>
+      </c>
+      <c r="I138">
+        <v>-0.1120426323132147</v>
+      </c>
+      <c r="J138">
+        <v>0.7748667740212044</v>
+      </c>
+      <c r="K138">
+        <v>2.23</v>
+      </c>
+      <c r="L138">
+        <v>3.58</v>
+      </c>
+      <c r="M138">
+        <v>2.55</v>
+      </c>
+      <c r="N138">
+        <v>3.94</v>
+      </c>
+      <c r="O138">
+        <v>1</v>
+      </c>
+      <c r="P138" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16">
+      <c r="A139" s="1">
+        <v>0</v>
+      </c>
+      <c r="B139" t="s">
+        <v>24</v>
+      </c>
+      <c r="C139">
+        <v>1.854970184636914</v>
+      </c>
+      <c r="D139" t="s">
+        <v>45</v>
+      </c>
+      <c r="E139">
+        <v>1.967432273912166</v>
+      </c>
+      <c r="F139">
+        <v>-1</v>
+      </c>
+      <c r="G139">
+        <v>0.005305029815363087</v>
+      </c>
+      <c r="H139">
+        <v>0.005912567726087834</v>
+      </c>
+      <c r="I139">
+        <v>-0.1124620892752521</v>
+      </c>
+      <c r="J139">
+        <v>0.7735559710148369</v>
+      </c>
+      <c r="K139">
+        <v>2.23</v>
+      </c>
+      <c r="L139">
+        <v>3.58</v>
+      </c>
+      <c r="M139">
+        <v>2.55</v>
+      </c>
+      <c r="N139">
+        <v>3.94</v>
+      </c>
+      <c r="O139">
+        <v>1</v>
+      </c>
+      <c r="P139" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16">
+      <c r="A140" s="1">
+        <v>0</v>
+      </c>
+      <c r="B140" t="s">
+        <v>24</v>
+      </c>
+      <c r="C140">
+        <v>1.85674639554338</v>
+      </c>
+      <c r="D140" t="s">
+        <v>45</v>
+      </c>
+      <c r="E140">
+        <v>1.969463367101175</v>
+      </c>
+      <c r="F140">
+        <v>-1</v>
+      </c>
+      <c r="G140">
+        <v>0.00530325360445662</v>
+      </c>
+      <c r="H140">
+        <v>0.005910536632898825</v>
+      </c>
+      <c r="I140">
+        <v>-0.1127169715577945</v>
+      </c>
+      <c r="J140">
+        <v>0.7727594638818923</v>
+      </c>
+      <c r="K140">
+        <v>2.23</v>
+      </c>
+      <c r="L140">
+        <v>3.58</v>
+      </c>
+      <c r="M140">
+        <v>2.55</v>
+      </c>
+      <c r="N140">
+        <v>3.94</v>
+      </c>
+      <c r="O140">
+        <v>1</v>
+      </c>
+      <c r="P140" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16">
+      <c r="A141" s="1">
+        <v>0</v>
+      </c>
+      <c r="B141" t="s">
+        <v>24</v>
+      </c>
+      <c r="C141">
+        <v>1.857495906066503</v>
+      </c>
+      <c r="D141" t="s">
+        <v>45</v>
+      </c>
+      <c r="E141">
+        <v>1.970320430703849</v>
+      </c>
+      <c r="F141">
+        <v>-1</v>
+      </c>
+      <c r="G141">
+        <v>0.005302504093933497</v>
+      </c>
+      <c r="H141">
+        <v>0.00590967956929615</v>
+      </c>
+      <c r="I141">
+        <v>-0.1128245246373458</v>
+      </c>
+      <c r="J141">
+        <v>0.7724233605082945</v>
+      </c>
+      <c r="K141">
+        <v>2.23</v>
+      </c>
+      <c r="L141">
+        <v>3.58</v>
+      </c>
+      <c r="M141">
+        <v>2.55</v>
+      </c>
+      <c r="N141">
+        <v>3.94</v>
+      </c>
+      <c r="O141">
+        <v>1</v>
+      </c>
+      <c r="P141" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16">
+      <c r="A142" s="1">
+        <v>0</v>
+      </c>
+      <c r="B142" t="s">
+        <v>24</v>
+      </c>
+      <c r="C142">
+        <v>1.857856932752737</v>
+      </c>
+      <c r="D142" t="s">
+        <v>45</v>
+      </c>
+      <c r="E142">
+        <v>1.97073326391008</v>
+      </c>
+      <c r="F142">
+        <v>-1</v>
+      </c>
+      <c r="G142">
+        <v>0.005302143067247263</v>
+      </c>
+      <c r="H142">
+        <v>0.00590926673608992</v>
+      </c>
+      <c r="I142">
+        <v>-0.1128763311573433</v>
+      </c>
+      <c r="J142">
+        <v>0.7722614651333018</v>
+      </c>
+      <c r="K142">
+        <v>2.23</v>
+      </c>
+      <c r="L142">
+        <v>3.58</v>
+      </c>
+      <c r="M142">
+        <v>2.55</v>
+      </c>
+      <c r="N142">
+        <v>3.94</v>
+      </c>
+      <c r="O142">
+        <v>1</v>
+      </c>
+      <c r="P142" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16">
+      <c r="A143" s="1">
+        <v>0</v>
+      </c>
+      <c r="B143" t="s">
+        <v>24</v>
+      </c>
+      <c r="C143">
+        <v>1.856844251006594</v>
+      </c>
+      <c r="D143" t="s">
+        <v>45</v>
+      </c>
+      <c r="E143">
+        <v>1.969575264603952</v>
+      </c>
+      <c r="F143">
+        <v>-1</v>
+      </c>
+      <c r="G143">
+        <v>0.005303155748993407</v>
+      </c>
+      <c r="H143">
+        <v>0.005910424735396047</v>
+      </c>
+      <c r="I143">
+        <v>-0.1127310135973587</v>
+      </c>
+      <c r="J143">
+        <v>0.772715582508254</v>
+      </c>
+      <c r="K143">
+        <v>2.23</v>
+      </c>
+      <c r="L143">
+        <v>3.58</v>
+      </c>
+      <c r="M143">
+        <v>2.55</v>
+      </c>
+      <c r="N143">
+        <v>3.94</v>
+      </c>
+      <c r="O143">
+        <v>1</v>
+      </c>
+      <c r="P143" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01618-601618.xlsx
+++ b/s60_signal/position-01618-601618.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="153">
   <si>
     <t>trade_time</t>
   </si>
@@ -85,270 +85,261 @@
     <t>2020-08-17</t>
   </si>
   <si>
-    <t>2021-02-22</t>
-  </si>
-  <si>
     <t>2021-07-22</t>
   </si>
   <si>
+    <t>2021-01-13</t>
+  </si>
+  <si>
+    <t>2021-01-15</t>
+  </si>
+  <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
+    <t>2021-02-26</t>
+  </si>
+  <si>
+    <t>2021-07-26</t>
+  </si>
+  <si>
+    <t>2021-02-25</t>
+  </si>
+  <si>
+    <t>2021-02-23</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>2016-12-30</t>
+  </si>
+  <si>
+    <t>2017-04-05</t>
+  </si>
+  <si>
+    <t>2017-05-04</t>
+  </si>
+  <si>
+    <t>2017-12-20</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>2020-08-12</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-07-17</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>2021-01-22</t>
+  </si>
+  <si>
+    <t>2021-01-26</t>
+  </si>
+  <si>
+    <t>2021-03-12</t>
+  </si>
+  <si>
+    <t>2021-07-29</t>
+  </si>
+  <si>
+    <t>2021-03-09</t>
+  </si>
+  <si>
+    <t>2016-12-23</t>
+  </si>
+  <si>
+    <t>2017-02-09</t>
+  </si>
+  <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
+    <t>2017-02-13</t>
+  </si>
+  <si>
+    <t>2017-02-14</t>
+  </si>
+  <si>
+    <t>2017-02-15</t>
+  </si>
+  <si>
+    <t>2017-02-16</t>
+  </si>
+  <si>
+    <t>2017-04-27</t>
+  </si>
+  <si>
+    <t>2019-12-05</t>
+  </si>
+  <si>
+    <t>2019-12-06</t>
+  </si>
+  <si>
+    <t>2019-12-20</t>
+  </si>
+  <si>
+    <t>2020-02-21</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>2020-02-27</t>
+  </si>
+  <si>
+    <t>2020-02-28</t>
+  </si>
+  <si>
+    <t>2020-11-26</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-01</t>
+  </si>
+  <si>
+    <t>2020-12-16</t>
+  </si>
+  <si>
+    <t>2020-12-17</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>2020-12-21</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
+    <t>2020-12-24</t>
+  </si>
+  <si>
+    <t>2020-12-28</t>
+  </si>
+  <si>
+    <t>2020-12-29</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>2021-01-05</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>2021-01-08</t>
+  </si>
+  <si>
+    <t>2021-01-11</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>2021-01-14</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>2021-04-01</t>
+  </si>
+  <si>
     <t>2021-04-07</t>
   </si>
   <si>
-    <t>2021-01-13</t>
-  </si>
-  <si>
-    <t>2021-01-15</t>
-  </si>
-  <si>
-    <t>2021-04-01</t>
+    <t>2021-04-08</t>
+  </si>
+  <si>
+    <t>2021-04-09</t>
   </si>
   <si>
     <t>2021-04-12</t>
   </si>
   <si>
-    <t>2021-02-26</t>
-  </si>
-  <si>
-    <t>2021-02-25</t>
-  </si>
-  <si>
-    <t>2021-02-23</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
+    <t>2021-04-13</t>
+  </si>
+  <si>
+    <t>2021-04-14</t>
+  </si>
+  <si>
+    <t>2021-04-15</t>
+  </si>
+  <si>
+    <t>2021-04-16</t>
   </si>
   <si>
     <t>2021-04-19</t>
   </si>
   <si>
-    <t>2016-12-30</t>
-  </si>
-  <si>
-    <t>2017-04-05</t>
-  </si>
-  <si>
-    <t>2017-05-04</t>
-  </si>
-  <si>
-    <t>2017-12-20</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>2020-08-12</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-07-17</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>2021-07-23</t>
+    <t>2021-04-20</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>2021-04-22</t>
+  </si>
+  <si>
+    <t>2021-04-23</t>
+  </si>
+  <si>
+    <t>2021-04-26</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>2021-04-29</t>
   </si>
   <si>
     <t>2021-04-30</t>
   </si>
   <si>
-    <t>2021-01-22</t>
-  </si>
-  <si>
-    <t>2021-01-26</t>
-  </si>
-  <si>
-    <t>2021-03-12</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2021-03-09</t>
-  </si>
-  <si>
     <t>2021-05-06</t>
   </si>
   <si>
-    <t>2016-12-23</t>
-  </si>
-  <si>
-    <t>2017-02-09</t>
-  </si>
-  <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
-    <t>2017-02-13</t>
-  </si>
-  <si>
-    <t>2017-02-14</t>
-  </si>
-  <si>
-    <t>2017-02-15</t>
-  </si>
-  <si>
-    <t>2017-02-16</t>
-  </si>
-  <si>
-    <t>2017-04-27</t>
-  </si>
-  <si>
-    <t>2019-12-05</t>
-  </si>
-  <si>
-    <t>2019-12-06</t>
-  </si>
-  <si>
-    <t>2019-12-20</t>
-  </si>
-  <si>
-    <t>2020-02-21</t>
-  </si>
-  <si>
-    <t>2020-02-24</t>
-  </si>
-  <si>
-    <t>2020-02-25</t>
-  </si>
-  <si>
-    <t>2020-02-26</t>
-  </si>
-  <si>
-    <t>2020-02-27</t>
-  </si>
-  <si>
-    <t>2020-02-28</t>
-  </si>
-  <si>
-    <t>2020-11-26</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-01</t>
-  </si>
-  <si>
-    <t>2020-12-02</t>
-  </si>
-  <si>
-    <t>2020-12-11</t>
-  </si>
-  <si>
-    <t>2020-12-14</t>
-  </si>
-  <si>
-    <t>2020-12-15</t>
-  </si>
-  <si>
-    <t>2020-12-16</t>
-  </si>
-  <si>
-    <t>2020-12-17</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>2020-12-21</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2020-12-23</t>
-  </si>
-  <si>
-    <t>2020-12-24</t>
-  </si>
-  <si>
-    <t>2020-12-28</t>
-  </si>
-  <si>
-    <t>2020-12-29</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>2021-01-05</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-08</t>
-  </si>
-  <si>
-    <t>2021-01-11</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>2021-01-14</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>2021-04-08</t>
-  </si>
-  <si>
-    <t>2021-04-09</t>
-  </si>
-  <si>
-    <t>2021-04-13</t>
-  </si>
-  <si>
-    <t>2021-04-14</t>
-  </si>
-  <si>
-    <t>2021-04-15</t>
-  </si>
-  <si>
-    <t>2021-04-16</t>
-  </si>
-  <si>
-    <t>2021-04-20</t>
-  </si>
-  <si>
-    <t>2021-04-22</t>
-  </si>
-  <si>
-    <t>2021-04-23</t>
-  </si>
-  <si>
-    <t>2021-04-26</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>2021-04-29</t>
-  </si>
-  <si>
     <t>2021-05-07</t>
   </si>
   <si>
@@ -440,6 +431,48 @@
   </si>
   <si>
     <t>2021-06-22</t>
+  </si>
+  <si>
+    <t>2021-06-23</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>2021-06-25</t>
+  </si>
+  <si>
+    <t>2021-06-28</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>2021-07-05</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>2021-07-07</t>
+  </si>
+  <si>
+    <t>2021-07-08</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>2021-07-12</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
   </si>
 </sst>
 </file>
@@ -797,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P143"/>
+  <dimension ref="A1:P132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -858,7 +891,7 @@
         <v>2.241636620202809</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E2">
         <v>2.083673377356266</v>
@@ -894,7 +927,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -908,7 +941,7 @@
         <v>2.291018963074085</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E3">
         <v>2.748932188801797</v>
@@ -944,7 +977,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -958,7 +991,7 @@
         <v>0.1640886968569069</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E4">
         <v>0.8087275807852619</v>
@@ -994,7 +1027,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1008,7 +1041,7 @@
         <v>0.1567937244930127</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E5">
         <v>0.8087275807852619</v>
@@ -1044,7 +1077,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1058,7 +1091,7 @@
         <v>0.06008199184724816</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E6">
         <v>0.7118353409391309</v>
@@ -1094,7 +1127,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1108,7 +1141,7 @@
         <v>0.05109309920632388</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E7">
         <v>0.7118353409391309</v>
@@ -1144,7 +1177,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1158,7 +1191,7 @@
         <v>-0.0569506423664734</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E8">
         <v>0.6028081963621785</v>
@@ -1194,7 +1227,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1208,7 +1241,7 @@
         <v>-0.06784560396853312</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E9">
         <v>0.6028081963621785</v>
@@ -1244,7 +1277,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1258,7 +1291,7 @@
         <v>-0.1396452470657845</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E10">
         <v>0.5257702258605397</v>
@@ -1294,7 +1327,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1308,7 +1341,7 @@
         <v>-0.1518870263339567</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E11">
         <v>0.5257702258605397</v>
@@ -1344,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1358,7 +1391,7 @@
         <v>-0.2479133877986754</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <v>0.424908049151723</v>
@@ -1394,7 +1427,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1408,7 +1441,7 @@
         <v>-0.2619184918344848</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E13">
         <v>0.424908049151723</v>
@@ -1444,7 +1477,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1458,7 +1491,7 @@
         <v>-0.3399965939203824</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E14">
         <v>0.3391236942630966</v>
@@ -1494,7 +1527,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1508,7 +1541,7 @@
         <v>0.9756011105228968</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E15">
         <v>0.8107654111102569</v>
@@ -1544,7 +1577,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1558,7 +1591,7 @@
         <v>1.301145679016073</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E16">
         <v>1.173416666670367</v>
@@ -1594,7 +1627,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1608,7 +1641,7 @@
         <v>1.296277364845049</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E17">
         <v>1.230890933009092</v>
@@ -1644,7 +1677,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1658,7 +1691,7 @@
         <v>0.4435035626339812</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E18">
         <v>0.9439906537348826</v>
@@ -1694,7 +1727,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1708,7 +1741,7 @@
         <v>0.4423533289773536</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E19">
         <v>0.9439906537348826</v>
@@ -1744,7 +1777,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1758,7 +1791,7 @@
         <v>1.507350128118183</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E20">
         <v>1.202821457299868</v>
@@ -1794,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -1808,7 +1841,7 @@
         <v>1.54125697476493</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E21">
         <v>1.238224194239853</v>
@@ -1844,7 +1877,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -1858,7 +1891,7 @@
         <v>1.573438797246031</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E22">
         <v>1.271825803006885</v>
@@ -1894,7 +1927,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -1908,7 +1941,7 @@
         <v>1.613400857289038</v>
       </c>
       <c r="D23" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E23">
         <v>1.313550895110613</v>
@@ -1944,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -1958,7 +1991,7 @@
         <v>1.593400857289038</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E24">
         <v>1.363275825771058</v>
@@ -1994,7 +2027,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2008,7 +2041,7 @@
         <v>1.645344720184119</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E25">
         <v>1.346904046074595</v>
@@ -2044,7 +2077,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2058,7 +2091,7 @@
         <v>1.625344720184119</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E26">
         <v>1.394045281942056</v>
@@ -2094,7 +2127,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2108,7 +2141,7 @@
         <v>1.68180858461344</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E27">
         <v>1.384976610405209</v>
@@ -2144,7 +2177,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2158,7 +2191,7 @@
         <v>1.66180858461344</v>
       </c>
       <c r="D28" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E28">
         <v>1.429168563120298</v>
@@ -2194,7 +2227,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2208,7 +2241,7 @@
         <v>1.710614904938503</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E29">
         <v>1.415053797803437</v>
@@ -2244,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2258,7 +2291,7 @@
         <v>1.690614904938503</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E30">
         <v>1.456915827551058</v>
@@ -2294,7 +2327,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2305,78 +2338,78 @@
         <v>23</v>
       </c>
       <c r="C31">
-        <v>2.967686812279704</v>
+        <v>3.015409387558148</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E31">
-        <v>2.601744839228811</v>
+        <v>3.294391900570977</v>
       </c>
       <c r="F31">
         <v>-1</v>
       </c>
       <c r="G31">
-        <v>0.004132313187720295</v>
+        <v>0.004144590612441852</v>
       </c>
       <c r="H31">
-        <v>0.003518255160771189</v>
+        <v>0.004585608099429023</v>
       </c>
       <c r="I31">
-        <v>0.3659419730508935</v>
+        <v>-0.2789825130128283</v>
       </c>
       <c r="J31">
         <v>0.2531796468349111</v>
       </c>
       <c r="K31">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="L31">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="M31">
-        <v>1.81</v>
+        <v>2.55</v>
       </c>
       <c r="N31">
-        <v>3.06</v>
+        <v>3.94</v>
       </c>
       <c r="O31">
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C32">
-        <v>3.015409387558148</v>
+        <v>3.017091835180818</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="E32">
-        <v>3.294391900570977</v>
+        <v>3.296315775655196</v>
       </c>
       <c r="F32">
         <v>-1</v>
       </c>
       <c r="G32">
-        <v>0.004144590612441852</v>
+        <v>0.004142908164819182</v>
       </c>
       <c r="H32">
-        <v>0.004585608099429023</v>
+        <v>0.004583684224344804</v>
       </c>
       <c r="I32">
-        <v>-0.2789825130128283</v>
+        <v>-0.2792239404743775</v>
       </c>
       <c r="J32">
-        <v>0.2531796468349111</v>
+        <v>0.2524251860175702</v>
       </c>
       <c r="K32">
         <v>2.23</v>
@@ -2394,7 +2427,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2405,196 +2438,196 @@
         <v>23</v>
       </c>
       <c r="C33">
-        <v>2.969422072159588</v>
+        <v>3.0184784678196</v>
       </c>
       <c r="D33" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E33">
-        <v>2.603110413308198</v>
+        <v>3.297901386968601</v>
       </c>
       <c r="F33">
         <v>-1</v>
       </c>
       <c r="G33">
-        <v>0.004130577927840411</v>
+        <v>0.0041415215321804</v>
       </c>
       <c r="H33">
-        <v>0.003516889586691802</v>
+        <v>0.004582098613031399</v>
       </c>
       <c r="I33">
-        <v>0.3663116588513904</v>
+        <v>-0.2794229191490007</v>
       </c>
       <c r="J33">
-        <v>0.2524251860175702</v>
+        <v>0.2518033776593721</v>
       </c>
       <c r="K33">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="L33">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="M33">
-        <v>1.81</v>
+        <v>2.55</v>
       </c>
       <c r="N33">
-        <v>3.06</v>
+        <v>3.94</v>
       </c>
       <c r="O33">
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>
       </c>
       <c r="C34">
-        <v>3.017091835180818</v>
+        <v>2.284943445032334</v>
       </c>
       <c r="D34" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E34">
-        <v>3.296315775655196</v>
+        <v>2.033577409367039</v>
       </c>
       <c r="F34">
         <v>-1</v>
       </c>
       <c r="G34">
-        <v>0.004142908164819182</v>
+        <v>0.004235056554967666</v>
       </c>
       <c r="H34">
-        <v>0.004583684224344804</v>
+        <v>0.004066422590632961</v>
       </c>
       <c r="I34">
-        <v>-0.2792239404743775</v>
+        <v>0.2513660356652947</v>
       </c>
       <c r="J34">
-        <v>0.2524251860175702</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K34">
-        <v>2.23</v>
+        <v>1.65</v>
       </c>
       <c r="L34">
-        <v>3.58</v>
+        <v>3.26</v>
       </c>
       <c r="M34">
-        <v>2.55</v>
+        <v>1.72</v>
       </c>
       <c r="N34">
-        <v>3.94</v>
+        <v>3.05</v>
       </c>
       <c r="O34">
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C35">
-        <v>2.970852231383444</v>
+        <v>2.294943445032334</v>
       </c>
       <c r="D35" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E35">
-        <v>2.604235886436537</v>
+        <v>2.033577409367039</v>
       </c>
       <c r="F35">
         <v>-1</v>
       </c>
       <c r="G35">
-        <v>0.004129147768616556</v>
+        <v>0.004245056554967665</v>
       </c>
       <c r="H35">
-        <v>0.003515764113563464</v>
+        <v>0.004066422590632961</v>
       </c>
       <c r="I35">
-        <v>0.3666163449469071</v>
+        <v>0.2613660356652949</v>
       </c>
       <c r="J35">
-        <v>0.2518033776593721</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K35">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="L35">
-        <v>3.55</v>
+        <v>3.27</v>
       </c>
       <c r="M35">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="N35">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="O35">
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B36" t="s">
         <v>24</v>
       </c>
       <c r="C36">
-        <v>3.0184784678196</v>
+        <v>2.206392009113778</v>
       </c>
       <c r="D36" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E36">
-        <v>3.297901386968601</v>
+        <v>1.939163015063914</v>
       </c>
       <c r="F36">
         <v>-1</v>
       </c>
       <c r="G36">
-        <v>0.0041415215321804</v>
+        <v>0.004313607990886223</v>
       </c>
       <c r="H36">
-        <v>0.004582098613031399</v>
+        <v>0.004020836984936086</v>
       </c>
       <c r="I36">
-        <v>-0.2794229191490007</v>
+        <v>0.2672289940498638</v>
       </c>
       <c r="J36">
-        <v>0.2518033776593721</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K36">
-        <v>2.23</v>
+        <v>1.65</v>
       </c>
       <c r="L36">
-        <v>3.58</v>
+        <v>3.26</v>
       </c>
       <c r="M36">
-        <v>2.55</v>
+        <v>1.63</v>
       </c>
       <c r="N36">
-        <v>3.94</v>
+        <v>2.98</v>
       </c>
       <c r="O36">
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2602,643 +2635,643 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C37">
-        <v>2.964905134405401</v>
+        <v>2.122703049542399</v>
       </c>
       <c r="D37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E37">
-        <v>2.599555779684251</v>
+        <v>1.814059302286312</v>
       </c>
       <c r="F37">
         <v>-1</v>
       </c>
       <c r="G37">
-        <v>0.004135094865594598</v>
+        <v>0.004397296950457601</v>
       </c>
       <c r="H37">
-        <v>0.003520444220315749</v>
+        <v>0.004005940697713688</v>
       </c>
       <c r="I37">
-        <v>0.3653493547211504</v>
+        <v>0.3086437472560868</v>
       </c>
       <c r="J37">
-        <v>0.2543890719976515</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K37">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="L37">
-        <v>3.55</v>
+        <v>3.26</v>
       </c>
       <c r="M37">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="N37">
-        <v>3.06</v>
+        <v>2.91</v>
       </c>
       <c r="O37">
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B38" t="s">
         <v>24</v>
       </c>
       <c r="C38">
-        <v>3.012712369445237</v>
+        <v>2.037699170124481</v>
       </c>
       <c r="D38" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E38">
-        <v>3.291307866405988</v>
+        <v>1.732146473029046</v>
       </c>
       <c r="F38">
         <v>-1</v>
       </c>
       <c r="G38">
-        <v>0.004147287630554762</v>
+        <v>0.004482300829875518</v>
       </c>
       <c r="H38">
-        <v>0.004588692133594012</v>
+        <v>0.004087853526970955</v>
       </c>
       <c r="I38">
-        <v>-0.2785954969607514</v>
+        <v>0.3055526970954354</v>
       </c>
       <c r="J38">
-        <v>0.2543890719976515</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K38">
-        <v>2.23</v>
+        <v>1.65</v>
       </c>
       <c r="L38">
-        <v>3.58</v>
+        <v>3.26</v>
       </c>
       <c r="M38">
-        <v>2.55</v>
+        <v>1.59</v>
       </c>
       <c r="N38">
-        <v>3.94</v>
+        <v>2.91</v>
       </c>
       <c r="O38">
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:16">
       <c r="A39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C39">
-        <v>2.520757495256166</v>
+        <v>2.050989626556016</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E39">
-        <v>2.229102087286527</v>
+        <v>2.158029045643153</v>
       </c>
       <c r="F39">
         <v>-1</v>
       </c>
       <c r="G39">
-        <v>0.004399242504743834</v>
+        <v>0.005829010373443984</v>
       </c>
       <c r="H39">
-        <v>0.003930897912713473</v>
+        <v>0.005861970954356846</v>
       </c>
       <c r="I39">
-        <v>0.2916554079696394</v>
+        <v>-0.1070394190871369</v>
       </c>
       <c r="J39">
-        <v>0.4649715370018978</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K39">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="L39">
-        <v>3.46</v>
+        <v>3.94</v>
       </c>
       <c r="M39">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="N39">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="O39">
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B40" t="s">
         <v>24</v>
       </c>
       <c r="C40">
-        <v>2.543113472485768</v>
+        <v>1.939614977812812</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E40">
-        <v>2.754322580645161</v>
+        <v>1.637628978619619</v>
       </c>
       <c r="F40">
         <v>-1</v>
       </c>
       <c r="G40">
-        <v>0.004616886527514233</v>
+        <v>0.004580385022187188</v>
       </c>
       <c r="H40">
-        <v>0.005125677419354839</v>
+        <v>0.004182371021380382</v>
       </c>
       <c r="I40">
-        <v>-0.2112091081593928</v>
+        <v>0.301985999193193</v>
       </c>
       <c r="J40">
-        <v>0.4649715370018978</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K40">
-        <v>2.23</v>
+        <v>1.65</v>
       </c>
       <c r="L40">
-        <v>3.58</v>
+        <v>3.26</v>
       </c>
       <c r="M40">
-        <v>2.55</v>
+        <v>1.59</v>
       </c>
       <c r="N40">
-        <v>3.94</v>
+        <v>2.91</v>
       </c>
       <c r="O40">
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" t="s">
         <v>26</v>
       </c>
       <c r="C41">
-        <v>2.422019174201789</v>
+        <v>1.899404965710709</v>
       </c>
       <c r="D41" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E41">
-        <v>2.152176517544798</v>
+        <v>2.009416633049714</v>
       </c>
       <c r="F41">
         <v>-1</v>
       </c>
       <c r="G41">
-        <v>0.004097980825798211</v>
+        <v>0.005980595034289291</v>
       </c>
       <c r="H41">
-        <v>0.003807823482455202</v>
+        <v>0.006010583366950286</v>
       </c>
       <c r="I41">
-        <v>0.2698426566569911</v>
+        <v>-0.1100116673390055</v>
       </c>
       <c r="J41">
-        <v>0.5078671671504308</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K41">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="L41">
-        <v>3.26</v>
+        <v>3.94</v>
       </c>
       <c r="M41">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="N41">
-        <v>2.98</v>
+        <v>4.01</v>
       </c>
       <c r="O41">
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B42" t="s">
         <v>27</v>
       </c>
       <c r="C42">
-        <v>2.432019174201789</v>
+        <v>1.364830842322013</v>
       </c>
       <c r="D42" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E42">
-        <v>2.152176517544798</v>
+        <v>1.598575134626953</v>
       </c>
       <c r="F42">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G42">
-        <v>0.004107980825798211</v>
+        <v>0.005255169157677987</v>
       </c>
       <c r="H42">
-        <v>0.003807823482455202</v>
+        <v>0.004741424865373047</v>
       </c>
       <c r="I42">
-        <v>0.2798426566569914</v>
+        <v>0.2337442923049406</v>
       </c>
       <c r="J42">
-        <v>0.5078671671504308</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K42">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="L42">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="M42">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="N42">
-        <v>2.98</v>
+        <v>3.17</v>
       </c>
       <c r="O42">
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43">
+        <v>1.773981942323639</v>
+      </c>
+      <c r="D43" t="s">
         <v>28</v>
       </c>
-      <c r="C43">
-        <v>2.419501680713651</v>
-      </c>
-      <c r="D43" t="s">
-        <v>46</v>
-      </c>
       <c r="E43">
-        <v>2.150603084114712</v>
+        <v>1.886452884631018</v>
       </c>
       <c r="F43">
         <v>-1</v>
       </c>
       <c r="G43">
-        <v>0.004420498319286349</v>
+        <v>0.006106018057676361</v>
       </c>
       <c r="H43">
-        <v>0.004009396915885288</v>
+        <v>0.006133547115368982</v>
       </c>
       <c r="I43">
-        <v>0.2688985965989392</v>
+        <v>-0.1124709423073793</v>
       </c>
       <c r="J43">
-        <v>0.5078671671504308</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K43">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="L43">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="M43">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="N43">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C44">
-        <v>2.419029650684626</v>
+        <v>1.253223538131198</v>
       </c>
       <c r="D44" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E44">
-        <v>2.150603084114712</v>
+        <v>1.508412028621273</v>
       </c>
       <c r="F44">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G44">
-        <v>0.004480970349315374</v>
+        <v>0.005366776461868803</v>
       </c>
       <c r="H44">
-        <v>0.004009396915885288</v>
+        <v>0.004831587971378727</v>
       </c>
       <c r="I44">
-        <v>0.2684265665699139</v>
+        <v>0.2551884904900752</v>
       </c>
       <c r="J44">
-        <v>0.5078671671504308</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K44">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="L44">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="M44">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="N44">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="O44">
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C45">
-        <v>2.44745621725454</v>
+        <v>1.142741567826858</v>
       </c>
       <c r="D45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E45">
-        <v>2.644938723766401</v>
+        <v>1.419158035143968</v>
       </c>
       <c r="F45">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>0.004712543782745461</v>
+        <v>0.005477258432173141</v>
       </c>
       <c r="H45">
-        <v>0.005235061276233599</v>
+        <v>0.004920841964856031</v>
       </c>
       <c r="I45">
-        <v>-0.1974825065118617</v>
+        <v>0.2764164673171099</v>
       </c>
       <c r="J45">
-        <v>0.5078671671504308</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K45">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="L45">
-        <v>3.58</v>
+        <v>3.31</v>
       </c>
       <c r="M45">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="N45">
-        <v>3.94</v>
+        <v>3.17</v>
       </c>
       <c r="O45">
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C46">
-        <v>2.361811863714594</v>
+        <v>1.643997344789146</v>
       </c>
       <c r="D46" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E46">
-        <v>2.092698992639265</v>
+        <v>1.473813546585172</v>
       </c>
       <c r="F46">
         <v>-1</v>
       </c>
       <c r="G46">
-        <v>0.004158188136285406</v>
+        <v>0.006376002655210854</v>
       </c>
       <c r="H46">
-        <v>0.003867301007360734</v>
+        <v>0.005846186453414829</v>
       </c>
       <c r="I46">
-        <v>0.2691128710753286</v>
+        <v>0.1701837982039747</v>
       </c>
       <c r="J46">
-        <v>0.5443564462335794</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K46">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="L46">
-        <v>3.26</v>
+        <v>4.01</v>
       </c>
       <c r="M46">
-        <v>1.63</v>
+        <v>2.31</v>
       </c>
       <c r="N46">
-        <v>2.98</v>
+        <v>3.66</v>
       </c>
       <c r="O46">
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C47">
-        <v>2.347617800919848</v>
+        <v>1.02473295176371</v>
       </c>
       <c r="D47" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E47">
-        <v>2.08382770339255</v>
+        <v>1.323823563651905</v>
       </c>
       <c r="F47">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G47">
-        <v>0.004492382199080151</v>
+        <v>0.005595267048236289</v>
       </c>
       <c r="H47">
-        <v>0.004076172296607451</v>
+        <v>0.005016176436348095</v>
       </c>
       <c r="I47">
-        <v>0.2637900975272984</v>
+        <v>0.2990906118881951</v>
       </c>
       <c r="J47">
-        <v>0.5443564462335794</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K47">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="L47">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="M47">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="N47">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="O47">
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C48">
-        <v>2.344956414145834</v>
+        <v>1.51516697790798</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E48">
-        <v>2.08382770339255</v>
+        <v>1.354774287586974</v>
       </c>
       <c r="F48">
         <v>-1</v>
       </c>
       <c r="G48">
-        <v>0.004555043585854166</v>
+        <v>0.00650483302209202</v>
       </c>
       <c r="H48">
-        <v>0.004076172296607451</v>
+        <v>0.005965225712413026</v>
       </c>
       <c r="I48">
-        <v>0.261128710753284</v>
+        <v>0.160392690321006</v>
       </c>
       <c r="J48">
-        <v>0.5443564462335794</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K48">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="L48">
-        <v>3.45</v>
+        <v>4.01</v>
       </c>
       <c r="M48">
-        <v>1.83</v>
+        <v>2.31</v>
       </c>
       <c r="N48">
-        <v>3.08</v>
+        <v>3.66</v>
       </c>
       <c r="O48">
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C49">
-        <v>2.366085124899118</v>
+        <v>1.025578495611604</v>
       </c>
       <c r="D49" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E49">
-        <v>2.551891062104373</v>
+        <v>1.228800376424943</v>
       </c>
       <c r="F49">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>0.004793914875100881</v>
+        <v>0.005734421504388396</v>
       </c>
       <c r="H49">
-        <v>0.005328108937895627</v>
+        <v>0.004971199623575057</v>
       </c>
       <c r="I49">
-        <v>-0.1858059372052545</v>
+        <v>0.2032218808133393</v>
       </c>
       <c r="J49">
-        <v>0.5443564462335794</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K49">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="L49">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="M49">
-        <v>2.55</v>
+        <v>1.82</v>
       </c>
       <c r="N49">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="O49">
         <v>1</v>
@@ -3249,96 +3282,96 @@
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C50">
-        <v>2.284943445032334</v>
+        <v>1.439670846737559</v>
       </c>
       <c r="D50" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E50">
-        <v>2.016762312365275</v>
+        <v>1.285015862385505</v>
       </c>
       <c r="F50">
         <v>-1</v>
       </c>
       <c r="G50">
-        <v>0.004235056554967666</v>
+        <v>0.00658032915326244</v>
       </c>
       <c r="H50">
-        <v>0.003943237687634725</v>
+        <v>0.006034984137614496</v>
       </c>
       <c r="I50">
-        <v>0.2681811326670585</v>
+        <v>0.1546549843520544</v>
       </c>
       <c r="J50">
-        <v>0.5909433666470703</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K50">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="L50">
-        <v>3.26</v>
+        <v>4.01</v>
       </c>
       <c r="M50">
-        <v>1.63</v>
+        <v>2.31</v>
       </c>
       <c r="N50">
-        <v>2.98</v>
+        <v>3.66</v>
       </c>
       <c r="O50">
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C51">
-        <v>2.255841567705271</v>
+        <v>0.95505474527386</v>
       </c>
       <c r="D51" t="s">
         <v>46</v>
       </c>
       <c r="E51">
-        <v>1.998573639035861</v>
+        <v>1.172750932925077</v>
       </c>
       <c r="F51">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>0.004584158432294728</v>
+        <v>0.00580494525472614</v>
       </c>
       <c r="H51">
-        <v>0.004161426360964139</v>
+        <v>0.005027249067074924</v>
       </c>
       <c r="I51">
-        <v>0.25726792866941</v>
+        <v>0.2176961876512167</v>
       </c>
       <c r="J51">
-        <v>0.5909433666470703</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K51">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="L51">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="M51">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="N51">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="O51">
         <v>1</v>
@@ -3349,102 +3382,102 @@
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B52" t="s">
         <v>29</v>
       </c>
       <c r="C52">
-        <v>2.250384965706448</v>
+        <v>0.8997461387005035</v>
       </c>
       <c r="D52" t="s">
         <v>46</v>
       </c>
       <c r="E52">
-        <v>1.998573639035861</v>
+        <v>1.128793874425728</v>
       </c>
       <c r="F52">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>0.004649615034293553</v>
+        <v>0.005860253861299496</v>
       </c>
       <c r="H52">
-        <v>0.004161426360964139</v>
+        <v>0.005071206125574273</v>
       </c>
       <c r="I52">
-        <v>0.2518113266705861</v>
+        <v>0.2290477357252241</v>
       </c>
       <c r="J52">
-        <v>0.5909433666470703</v>
+        <v>1.083080288777073</v>
       </c>
       <c r="K52">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="L52">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="M52">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="N52">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="O52">
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" spans="1:16">
       <c r="A53" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C53">
-        <v>2.262196292377033</v>
+        <v>0.9004291893178089</v>
       </c>
       <c r="D53" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E53">
-        <v>2.433094415049971</v>
+        <v>1.129336735615027</v>
       </c>
       <c r="F53">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G53">
-        <v>0.004897803707622967</v>
+        <v>0.005859570810682191</v>
       </c>
       <c r="H53">
-        <v>0.005446905584950029</v>
+        <v>0.005070663264384973</v>
       </c>
       <c r="I53">
-        <v>-0.1708981226729378</v>
+        <v>0.2289075462972185</v>
       </c>
       <c r="J53">
-        <v>0.5909433666470703</v>
+        <v>1.082782013398337</v>
       </c>
       <c r="K53">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="L53">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="M53">
-        <v>2.55</v>
+        <v>1.82</v>
       </c>
       <c r="N53">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="O53">
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3452,199 +3485,199 @@
         <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C54">
-        <v>2.206392009113778</v>
+        <v>0.8995341152947529</v>
       </c>
       <c r="D54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E54">
-        <v>1.939163015063914</v>
+        <v>1.128625366740808</v>
       </c>
       <c r="F54">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G54">
-        <v>0.004313607990886223</v>
+        <v>0.005860465884705247</v>
       </c>
       <c r="H54">
-        <v>0.004020836984936086</v>
+        <v>0.005071374633259193</v>
       </c>
       <c r="I54">
-        <v>0.2672289940498638</v>
+        <v>0.2290912514460552</v>
       </c>
       <c r="J54">
-        <v>0.6385502975068013</v>
+        <v>1.083172875417138</v>
       </c>
       <c r="K54">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="L54">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="M54">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="N54">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O54">
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:16">
       <c r="A55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C55">
-        <v>2.162055913911602</v>
+        <v>0.8942975364165378</v>
       </c>
       <c r="D55" t="s">
         <v>46</v>
       </c>
       <c r="E55">
-        <v>1.911452955562554</v>
+        <v>1.124463544226244</v>
       </c>
       <c r="F55">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G55">
-        <v>0.004677944086088398</v>
+        <v>0.005865702463583462</v>
       </c>
       <c r="H55">
-        <v>0.004248547044437446</v>
+        <v>0.005075536455773756</v>
       </c>
       <c r="I55">
-        <v>0.2506029583490479</v>
+        <v>0.2301660078097063</v>
       </c>
       <c r="J55">
-        <v>0.6385502975068013</v>
+        <v>1.085459591084481</v>
       </c>
       <c r="K55">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="L55">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="M55">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="N55">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="O55">
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B56" t="s">
         <v>29</v>
       </c>
       <c r="C56">
-        <v>2.153742896061194</v>
+        <v>0.823882990348408</v>
       </c>
       <c r="D56" t="s">
         <v>46</v>
       </c>
       <c r="E56">
-        <v>1.911452955562554</v>
+        <v>1.068500891892621</v>
       </c>
       <c r="F56">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>0.004746257103938807</v>
+        <v>0.005936117009651592</v>
       </c>
       <c r="H56">
-        <v>0.004248547044437446</v>
+        <v>0.005131499108107379</v>
       </c>
       <c r="I56">
-        <v>0.2422899404986398</v>
+        <v>0.2446179015442134</v>
       </c>
       <c r="J56">
-        <v>0.6385502975068013</v>
+        <v>1.1162083011579</v>
       </c>
       <c r="K56">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="L56">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="M56">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="N56">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="O56">
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C57">
-        <v>2.156032836559834</v>
+        <v>0.7552208383877499</v>
       </c>
       <c r="D57" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E57">
-        <v>2.311696741357657</v>
+        <v>1.013930971993758</v>
       </c>
       <c r="F57">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G57">
-        <v>0.005003967163440167</v>
+        <v>0.00600477916161225</v>
       </c>
       <c r="H57">
-        <v>0.005568303258642344</v>
+        <v>0.005186069028006243</v>
       </c>
       <c r="I57">
-        <v>-0.155663904797823</v>
+        <v>0.2587101336060078</v>
       </c>
       <c r="J57">
-        <v>0.6385502975068013</v>
+        <v>1.146191773629804</v>
       </c>
       <c r="K57">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="L57">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="M57">
-        <v>2.55</v>
+        <v>1.82</v>
       </c>
       <c r="N57">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="O57">
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3652,199 +3685,199 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C58">
-        <v>2.122703049542399</v>
+        <v>0.7164672131147527</v>
       </c>
       <c r="D58" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E58">
-        <v>1.814059302286312</v>
+        <v>0.9831311475409823</v>
       </c>
       <c r="F58">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G58">
-        <v>0.004397296950457601</v>
+        <v>0.006043532786885248</v>
       </c>
       <c r="H58">
-        <v>0.004005940697713688</v>
+        <v>0.005216868852459018</v>
       </c>
       <c r="I58">
-        <v>0.3086437472560868</v>
+        <v>0.2666639344262296</v>
       </c>
       <c r="J58">
-        <v>0.6892708790652124</v>
+        <v>1.163114754098361</v>
       </c>
       <c r="K58">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="L58">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="M58">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="N58">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="O58">
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C59">
-        <v>2.062136368241531</v>
+        <v>0.6498239504652852</v>
       </c>
       <c r="D59" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E59">
-        <v>1.818634291310661</v>
+        <v>0.5798239504652853</v>
       </c>
       <c r="F59">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>0.004777863631758469</v>
+        <v>0.006110176049534715</v>
       </c>
       <c r="H59">
-        <v>0.004341365708689339</v>
+        <v>0.006040176049534715</v>
       </c>
       <c r="I59">
-        <v>0.24350207693087</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J59">
-        <v>0.6892708790652124</v>
+        <v>1.192216615517343</v>
       </c>
       <c r="K59">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="L59">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="M59">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="N59">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="O59">
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C60">
-        <v>2.050780115497619</v>
+        <v>0.5205928926738919</v>
       </c>
       <c r="D60" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E60">
-        <v>1.818634291310661</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F60">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G60">
-        <v>0.004849219884502381</v>
+        <v>0.006459407107326108</v>
       </c>
       <c r="H60">
-        <v>0.004341365708689339</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I60">
-        <v>0.2321458241869578</v>
+        <v>-0.1165511301853397</v>
       </c>
       <c r="J60">
-        <v>0.6892708790652124</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K60">
-        <v>2.03</v>
+        <v>2.34</v>
       </c>
       <c r="L60">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="M60">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="N60">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="O60">
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C61">
-        <v>2.042925939684576</v>
+        <v>0.474041762488552</v>
       </c>
       <c r="D61" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E61">
-        <v>2.182359258383708</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F61">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G61">
-        <v>0.005117074060315425</v>
+        <v>0.006285958237511447</v>
       </c>
       <c r="H61">
-        <v>0.005697640741616292</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I61">
-        <v>-0.1394333186991319</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J61">
-        <v>0.6892708790652124</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K61">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="L61">
-        <v>3.58</v>
+        <v>3.38</v>
       </c>
       <c r="M61">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="N61">
-        <v>3.94</v>
+        <v>3.31</v>
       </c>
       <c r="O61">
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -3852,49 +3885,49 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C62">
-        <v>1.960646887966805</v>
+        <v>0.3774746016246668</v>
       </c>
       <c r="D62" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E62">
-        <v>1.724357261410788</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F62">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G62">
-        <v>0.004879353112033196</v>
+        <v>0.006602525398375333</v>
       </c>
       <c r="H62">
-        <v>0.004435642738589212</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I62">
-        <v>0.2362896265560166</v>
+        <v>-0.1134930470432627</v>
       </c>
       <c r="J62">
-        <v>0.7407883817427386</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K62">
-        <v>1.97</v>
+        <v>2.34</v>
       </c>
       <c r="L62">
-        <v>3.42</v>
+        <v>3.49</v>
       </c>
       <c r="M62">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="N62">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="O62">
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -3905,46 +3938,46 @@
         <v>29</v>
       </c>
       <c r="C63">
-        <v>1.946199585062241</v>
+        <v>0.333981554581404</v>
       </c>
       <c r="D63" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E63">
-        <v>1.724357261410788</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F63">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>0.00495380041493776</v>
+        <v>0.006426018445418596</v>
       </c>
       <c r="H63">
-        <v>0.004435642738589212</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I63">
-        <v>0.2218423236514526</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J63">
-        <v>0.7407883817427386</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K63">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="L63">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="M63">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="N63">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="O63">
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -3952,149 +3985,149 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C64">
-        <v>1.843540306843175</v>
+        <v>0.2442505289553791</v>
       </c>
       <c r="D64" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E64">
-        <v>1.615572975392391</v>
+        <v>0.1336041501315459</v>
       </c>
       <c r="F64">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>0.004996459693156825</v>
+        <v>0.006735749471044622</v>
       </c>
       <c r="H64">
-        <v>0.00454442702460761</v>
+        <v>0.006486395849868455</v>
       </c>
       <c r="I64">
-        <v>0.227967331450784</v>
+        <v>-0.1106463788238332</v>
       </c>
       <c r="J64">
-        <v>0.8002333467801142</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K64">
-        <v>1.97</v>
+        <v>2.34</v>
       </c>
       <c r="L64">
-        <v>3.42</v>
+        <v>3.49</v>
       </c>
       <c r="M64">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="N64">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="O64">
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C65">
-        <v>1.364830842322013</v>
+        <v>0.2036041501315458</v>
       </c>
       <c r="D65" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="E65">
-        <v>1.598575134626953</v>
+        <v>0.1336041501315459</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
       <c r="G65">
-        <v>0.005255169157677987</v>
+        <v>0.006556395849868454</v>
       </c>
       <c r="H65">
-        <v>0.004741424865373047</v>
+        <v>0.006486395849868455</v>
       </c>
       <c r="I65">
-        <v>0.2337442923049406</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J65">
-        <v>0.8494188461475927</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K65">
         <v>2.29</v>
       </c>
       <c r="L65">
+        <v>3.38</v>
+      </c>
+      <c r="M65">
+        <v>2.29</v>
+      </c>
+      <c r="N65">
         <v>3.31</v>
       </c>
-      <c r="M65">
-        <v>1.85</v>
-      </c>
-      <c r="N65">
-        <v>3.17</v>
-      </c>
       <c r="O65">
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C66">
-        <v>1.746644873089242</v>
+        <v>0.2977942894248136</v>
       </c>
       <c r="D66" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E66">
-        <v>1.552668119243339</v>
+        <v>0.5755281891875166</v>
       </c>
       <c r="F66">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G66">
-        <v>0.005093355126910757</v>
+        <v>0.006262205710575186</v>
       </c>
       <c r="H66">
-        <v>0.004967331880756661</v>
+        <v>0.005624471810812484</v>
       </c>
       <c r="I66">
-        <v>0.1939767538459036</v>
+        <v>0.277733899762703</v>
       </c>
       <c r="J66">
-        <v>0.8494188461475927</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K66">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="L66">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="M66">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="N66">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="O66">
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4102,99 +4135,99 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C67">
-        <v>1.253223538131198</v>
+        <v>1.909256367193766</v>
       </c>
       <c r="D67" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E67">
-        <v>1.465356698427415</v>
+        <v>2.01907486979781</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G67">
-        <v>0.005366776461868803</v>
+        <v>0.005970743632806234</v>
       </c>
       <c r="H67">
-        <v>0.004734643301572585</v>
+        <v>0.00600092513020219</v>
       </c>
       <c r="I67">
-        <v>0.2121331602962171</v>
+        <v>-0.1098185026040435</v>
       </c>
       <c r="J67">
-        <v>0.898155660204717</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K67">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L67">
-        <v>3.31</v>
+        <v>3.94</v>
       </c>
       <c r="M67">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="N67">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="O67">
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="1:16">
       <c r="A68" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68">
+        <v>1.899440167721166</v>
+      </c>
+      <c r="D68" t="s">
         <v>28</v>
       </c>
-      <c r="C68">
-        <v>1.650633349396707</v>
-      </c>
-      <c r="D68" t="s">
-        <v>50</v>
-      </c>
       <c r="E68">
-        <v>1.454707122988519</v>
+        <v>2.009451144824672</v>
       </c>
       <c r="F68">
         <v>-1</v>
       </c>
       <c r="G68">
-        <v>0.005189366650603293</v>
+        <v>0.005980559832278834</v>
       </c>
       <c r="H68">
-        <v>0.005065292877011481</v>
+        <v>0.006010548855175328</v>
       </c>
       <c r="I68">
-        <v>0.1959262264081887</v>
+        <v>-0.1100109771035065</v>
       </c>
       <c r="J68">
-        <v>0.898155660204717</v>
+        <v>0.8002195420701311</v>
       </c>
       <c r="K68">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="L68">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="M68">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="N68">
-        <v>3.26</v>
+        <v>4.01</v>
       </c>
       <c r="O68">
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4202,49 +4235,49 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C69">
-        <v>1.142741567826858</v>
+        <v>1.886137504764086</v>
       </c>
       <c r="D69" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E69">
-        <v>1.377550067006499</v>
+        <v>1.996409318396163</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G69">
-        <v>0.005477258432173141</v>
+        <v>0.005993862495235914</v>
       </c>
       <c r="H69">
-        <v>0.004822449932993502</v>
+        <v>0.006023590681603837</v>
       </c>
       <c r="I69">
-        <v>0.2348084991796402</v>
+        <v>-0.1102718136320764</v>
       </c>
       <c r="J69">
-        <v>0.9464010620843414</v>
+        <v>0.8054362726415348</v>
       </c>
       <c r="K69">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L69">
-        <v>3.31</v>
+        <v>3.94</v>
       </c>
       <c r="M69">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="N69">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="O69">
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4252,49 +4285,49 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C70">
-        <v>1.02473295176371</v>
+        <v>1.870809096426398</v>
       </c>
       <c r="D70" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E70">
-        <v>1.28376155991701</v>
+        <v>1.981381467084703</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G70">
-        <v>0.005595267048236289</v>
+        <v>0.006009190903573602</v>
       </c>
       <c r="H70">
-        <v>0.004916238440082991</v>
+        <v>0.006038618532915297</v>
       </c>
       <c r="I70">
-        <v>0.2590286081532995</v>
+        <v>-0.1105723706583053</v>
       </c>
       <c r="J70">
-        <v>0.9979332088368078</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K70">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L70">
-        <v>3.31</v>
+        <v>3.94</v>
       </c>
       <c r="M70">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="N70">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="O70">
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4302,49 +4335,49 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C71">
-        <v>1.025578495611604</v>
+        <v>1.866530632283299</v>
       </c>
       <c r="D71" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E71">
-        <v>1.228800376424943</v>
+        <v>1.977186894395391</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G71">
-        <v>0.005734421504388396</v>
+        <v>0.0060134693677167</v>
       </c>
       <c r="H71">
-        <v>0.004971199623575057</v>
+        <v>0.006042813105604609</v>
       </c>
       <c r="I71">
-        <v>0.2032218808133393</v>
+        <v>-0.1106562621120917</v>
       </c>
       <c r="J71">
-        <v>1.028131661304976</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K71">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L71">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="M71">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="N71">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="O71">
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4352,49 +4385,49 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C72">
-        <v>0.95505474527386</v>
+        <v>1.861370672015807</v>
       </c>
       <c r="D72" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E72">
-        <v>1.172750932925077</v>
+        <v>1.972128109819418</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G72">
-        <v>0.00580494525472614</v>
+        <v>0.006018629327984194</v>
       </c>
       <c r="H72">
-        <v>0.005027249067074924</v>
+        <v>0.006047871890180582</v>
       </c>
       <c r="I72">
-        <v>0.2176961876512167</v>
+        <v>-0.1107574378036111</v>
       </c>
       <c r="J72">
-        <v>1.058928058832376</v>
+        <v>0.8151487560722326</v>
       </c>
       <c r="K72">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L72">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="M72">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="N72">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="O72">
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4402,49 +4435,49 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C73">
-        <v>0.8997461387005035</v>
+        <v>1.851301116496863</v>
       </c>
       <c r="D73" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E73">
-        <v>1.128793874425728</v>
+        <v>1.962255996565552</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G73">
-        <v>0.005860253861299496</v>
+        <v>0.006028698883503138</v>
       </c>
       <c r="H73">
-        <v>0.005071206125574273</v>
+        <v>0.006057744003434448</v>
       </c>
       <c r="I73">
-        <v>0.2290477357252241</v>
+        <v>-0.110954880068689</v>
       </c>
       <c r="J73">
-        <v>1.083080288777073</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K73">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L73">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="M73">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="N73">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="O73">
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4452,49 +4485,49 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C74">
-        <v>0.9004291893178089</v>
+        <v>1.855461116431831</v>
       </c>
       <c r="D74" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E74">
-        <v>1.129336735615027</v>
+        <v>1.966334427874344</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G74">
-        <v>0.005859570810682191</v>
+        <v>0.006024538883568169</v>
       </c>
       <c r="H74">
-        <v>0.005070663264384973</v>
+        <v>0.006053665572125656</v>
       </c>
       <c r="I74">
-        <v>0.2289075462972185</v>
+        <v>-0.1108733114425124</v>
       </c>
       <c r="J74">
-        <v>1.082782013398337</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K74">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L74">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="M74">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="N74">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="O74">
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4502,49 +4535,49 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C75">
-        <v>0.8995341152947529</v>
+        <v>1.85652914973731</v>
       </c>
       <c r="D75" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E75">
-        <v>1.128625366740808</v>
+        <v>1.967381519350304</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G75">
-        <v>0.005860465884705247</v>
+        <v>0.006023470850262691</v>
       </c>
       <c r="H75">
-        <v>0.005071374633259193</v>
+        <v>0.006052618480649696</v>
       </c>
       <c r="I75">
-        <v>0.2290912514460552</v>
+        <v>-0.1108523696129935</v>
       </c>
       <c r="J75">
-        <v>1.083172875417138</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K75">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L75">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="M75">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="N75">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="O75">
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4552,49 +4585,49 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C76">
-        <v>0.8942975364165378</v>
+        <v>1.854953516327912</v>
       </c>
       <c r="D76" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E76">
-        <v>1.124463544226244</v>
+        <v>1.965836780713639</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G76">
-        <v>0.005865702463583462</v>
+        <v>0.006025046483672087</v>
       </c>
       <c r="H76">
-        <v>0.005075536455773756</v>
+        <v>0.00605416321928636</v>
       </c>
       <c r="I76">
-        <v>0.2301660078097063</v>
+        <v>-0.1108832643857269</v>
       </c>
       <c r="J76">
-        <v>1.085459591084481</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K76">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L76">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="M76">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="N76">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="O76">
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4602,49 +4635,49 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C77">
-        <v>0.823882990348408</v>
+        <v>1.853898035926949</v>
       </c>
       <c r="D77" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E77">
-        <v>1.068500891892621</v>
+        <v>1.964801996006813</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G77">
-        <v>0.005936117009651592</v>
+        <v>0.00602610196407305</v>
       </c>
       <c r="H77">
-        <v>0.005131499108107379</v>
+        <v>0.006055198003993187</v>
       </c>
       <c r="I77">
-        <v>0.2446179015442134</v>
+        <v>-0.1109039600798636</v>
       </c>
       <c r="J77">
-        <v>1.1162083011579</v>
+        <v>0.8180792015972748</v>
       </c>
       <c r="K77">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L77">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="M77">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="N77">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="O77">
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4652,49 +4685,49 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C78">
-        <v>0.7552208383877499</v>
+        <v>1.851157777698763</v>
       </c>
       <c r="D78" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E78">
-        <v>1.013930971993758</v>
+        <v>1.96211546833212</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G78">
-        <v>0.00600477916161225</v>
+        <v>0.006028842222301236</v>
       </c>
       <c r="H78">
-        <v>0.005186069028006243</v>
+        <v>0.006057884531667879</v>
       </c>
       <c r="I78">
-        <v>0.2587101336060078</v>
+        <v>-0.1109576906333571</v>
       </c>
       <c r="J78">
-        <v>1.146191773629804</v>
+        <v>0.8191538126671517</v>
       </c>
       <c r="K78">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L78">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="M78">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="N78">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="O78">
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4702,49 +4735,49 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C79">
-        <v>0.7164672131147527</v>
+        <v>1.858566205293179</v>
       </c>
       <c r="D79" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E79">
-        <v>0.9831311475409823</v>
+        <v>1.969378632640371</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G79">
-        <v>0.006043532786885248</v>
+        <v>0.006021433794706822</v>
       </c>
       <c r="H79">
-        <v>0.005216868852459018</v>
+        <v>0.006050621367359629</v>
       </c>
       <c r="I79">
-        <v>0.2666639344262296</v>
+        <v>-0.1108124273471924</v>
       </c>
       <c r="J79">
-        <v>1.163114754098361</v>
+        <v>0.8162485469438515</v>
       </c>
       <c r="K79">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L79">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="M79">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="N79">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="O79">
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -4752,49 +4785,49 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C80">
-        <v>0.6498239504652852</v>
+        <v>1.868405823240289</v>
       </c>
       <c r="D80" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E80">
-        <v>0.9301657597584363</v>
+        <v>1.979025316902244</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G80">
-        <v>0.006110176049534715</v>
+        <v>0.006011594176759711</v>
       </c>
       <c r="H80">
-        <v>0.005269834240241564</v>
+        <v>0.006040974683097756</v>
       </c>
       <c r="I80">
-        <v>0.2803418092931511</v>
+        <v>-0.1106194936619547</v>
       </c>
       <c r="J80">
-        <v>1.192216615517343</v>
+        <v>0.8123898732391025</v>
       </c>
       <c r="K80">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L80">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="M80">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="N80">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="O80">
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>26</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -4802,99 +4835,99 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C81">
-        <v>0.5205928926738919</v>
+        <v>1.873099451459633</v>
       </c>
       <c r="D81" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E81">
-        <v>0.4040417624885522</v>
+        <v>1.983626913195719</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G81">
-        <v>0.006459407107326108</v>
+        <v>0.006006900548540367</v>
       </c>
       <c r="H81">
-        <v>0.006215958237511448</v>
+        <v>0.00603637308680428</v>
       </c>
       <c r="I81">
-        <v>-0.1165511301853397</v>
+        <v>-0.1105274617360856</v>
       </c>
       <c r="J81">
-        <v>1.268977396293209</v>
+        <v>0.8105492347217125</v>
       </c>
       <c r="K81">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="L81">
-        <v>3.49</v>
+        <v>3.94</v>
       </c>
       <c r="M81">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="N81">
-        <v>3.31</v>
+        <v>4.01</v>
       </c>
       <c r="O81">
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="1:16">
       <c r="A82" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C82">
-        <v>0.474041762488552</v>
+        <v>1.880315678845928</v>
       </c>
       <c r="D82" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E82">
-        <v>0.4040417624885522</v>
+        <v>1.99070164592738</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G82">
-        <v>0.006285958237511447</v>
+        <v>0.005999684321154073</v>
       </c>
       <c r="H82">
-        <v>0.006215958237511448</v>
+        <v>0.006029298354072619</v>
       </c>
       <c r="I82">
-        <v>-0.06999999999999984</v>
+        <v>-0.1103859670814522</v>
       </c>
       <c r="J82">
-        <v>1.268977396293209</v>
+        <v>0.8077193416290479</v>
       </c>
       <c r="K82">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L82">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="M82">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="N82">
-        <v>3.31</v>
+        <v>4.01</v>
       </c>
       <c r="O82">
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -4902,99 +4935,99 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C83">
-        <v>0.3774746016246668</v>
+        <v>1.885229059666124</v>
       </c>
       <c r="D83" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E83">
-        <v>0.2639815545814042</v>
+        <v>1.995518685947181</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G83">
-        <v>0.006602525398375333</v>
+        <v>0.005994770940333876</v>
       </c>
       <c r="H83">
-        <v>0.006356018445418596</v>
+        <v>0.006024481314052819</v>
       </c>
       <c r="I83">
-        <v>-0.1134930470432627</v>
+        <v>-0.1102896262810562</v>
       </c>
       <c r="J83">
-        <v>1.330139059134758</v>
+        <v>0.8057925256211278</v>
       </c>
       <c r="K83">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="L83">
-        <v>3.49</v>
+        <v>3.94</v>
       </c>
       <c r="M83">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="N83">
-        <v>3.31</v>
+        <v>4.01</v>
       </c>
       <c r="O83">
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C84">
-        <v>0.333981554581404</v>
+        <v>1.891592550259521</v>
       </c>
       <c r="D84" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E84">
-        <v>0.2639815545814042</v>
+        <v>2.001757402215216</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G84">
-        <v>0.006426018445418596</v>
+        <v>0.00598840744974048</v>
       </c>
       <c r="H84">
-        <v>0.006356018445418596</v>
+        <v>0.006018242597784784</v>
       </c>
       <c r="I84">
-        <v>-0.06999999999999984</v>
+        <v>-0.1101648519556955</v>
       </c>
       <c r="J84">
-        <v>1.330139059134758</v>
+        <v>0.8032970391139135</v>
       </c>
       <c r="K84">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L84">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="M84">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="N84">
-        <v>3.31</v>
+        <v>4.01</v>
       </c>
       <c r="O84">
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5002,149 +5035,149 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C85">
-        <v>0.2442505289553791</v>
+        <v>1.898226451425238</v>
       </c>
       <c r="D85" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E85">
-        <v>0.1336041501315459</v>
+        <v>2.008261226887488</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G85">
-        <v>0.006735749471044622</v>
+        <v>0.005981773548574762</v>
       </c>
       <c r="H85">
-        <v>0.006486395849868455</v>
+        <v>0.006011738773112512</v>
       </c>
       <c r="I85">
-        <v>-0.1106463788238332</v>
+        <v>-0.1100347754622497</v>
       </c>
       <c r="J85">
-        <v>1.387072423523342</v>
+        <v>0.8006955092450049</v>
       </c>
       <c r="K85">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="L85">
-        <v>3.49</v>
+        <v>3.94</v>
       </c>
       <c r="M85">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="N85">
-        <v>3.31</v>
+        <v>4.01</v>
       </c>
       <c r="O85">
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C86">
-        <v>0.2036041501315458</v>
+        <v>1.903475998145109</v>
       </c>
       <c r="D86" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E86">
-        <v>0.1336041501315459</v>
+        <v>2.013407841318734</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G86">
-        <v>0.006556395849868454</v>
+        <v>0.005976524001854891</v>
       </c>
       <c r="H86">
-        <v>0.006486395849868455</v>
+        <v>0.006006592158681266</v>
       </c>
       <c r="I86">
-        <v>-0.06999999999999984</v>
+        <v>-0.1099318431736251</v>
       </c>
       <c r="J86">
-        <v>1.387072423523342</v>
+        <v>0.7986368634725065</v>
       </c>
       <c r="K86">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L86">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="M86">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="N86">
-        <v>3.31</v>
+        <v>4.01</v>
       </c>
       <c r="O86">
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C87">
-        <v>0.2977942894248136</v>
+        <v>1.915111220550284</v>
       </c>
       <c r="D87" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E87">
-        <v>0.5755281891875166</v>
+        <v>2.024814922108121</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G87">
-        <v>0.006262205710575186</v>
+        <v>0.005964888779449715</v>
       </c>
       <c r="H87">
-        <v>0.005624471810812484</v>
+        <v>0.005995185077891879</v>
       </c>
       <c r="I87">
-        <v>0.277733899762703</v>
+        <v>-0.1097037015578373</v>
       </c>
       <c r="J87">
-        <v>1.387072423523342</v>
+        <v>0.7940740311567515</v>
       </c>
       <c r="K87">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="L87">
-        <v>3.28</v>
+        <v>3.94</v>
       </c>
       <c r="M87">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="N87">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="O87">
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5152,99 +5185,99 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88">
+        <v>1.927566816677033</v>
+      </c>
+      <c r="D88" t="s">
         <v>28</v>
       </c>
-      <c r="C88">
-        <v>1.851150997400674</v>
-      </c>
-      <c r="D88" t="s">
-        <v>46</v>
-      </c>
       <c r="E88">
-        <v>1.622642804691997</v>
+        <v>2.037026290859836</v>
       </c>
       <c r="F88">
         <v>-1</v>
       </c>
       <c r="G88">
-        <v>0.004988849002599325</v>
+        <v>0.005952433183322967</v>
       </c>
       <c r="H88">
-        <v>0.004537357195308004</v>
+        <v>0.005982973709140164</v>
       </c>
       <c r="I88">
-        <v>0.2285081927086774</v>
+        <v>-0.109459474182803</v>
       </c>
       <c r="J88">
-        <v>0.7963700520808761</v>
+        <v>0.7891894836560657</v>
       </c>
       <c r="K88">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="L88">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="M88">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="N88">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="O88">
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
     </row>
     <row r="89" spans="1:16">
       <c r="A89" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C89">
-        <v>1.833368794275822</v>
+        <v>1.931008249436597</v>
       </c>
       <c r="D89" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E89">
-        <v>1.622642804691997</v>
+        <v>2.040400244545683</v>
       </c>
       <c r="F89">
         <v>-1</v>
       </c>
       <c r="G89">
-        <v>0.005066631205724178</v>
+        <v>0.005948991750563403</v>
       </c>
       <c r="H89">
-        <v>0.004537357195308004</v>
+        <v>0.005979599755454317</v>
       </c>
       <c r="I89">
-        <v>0.2107259895838252</v>
+        <v>-0.1093919951090863</v>
       </c>
       <c r="J89">
-        <v>0.7963700520808761</v>
+        <v>0.7878399021817268</v>
       </c>
       <c r="K89">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="L89">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="M89">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="N89">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="O89">
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5252,49 +5285,49 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C90">
-        <v>1.825554329597634</v>
+        <v>1.931290596802969</v>
       </c>
       <c r="D90" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E90">
-        <v>1.61559823801166</v>
+        <v>2.040677055689185</v>
       </c>
       <c r="F90">
         <v>-1</v>
       </c>
       <c r="G90">
-        <v>0.005074445670402367</v>
+        <v>0.00594870940319703</v>
       </c>
       <c r="H90">
-        <v>0.00454440176198834</v>
+        <v>0.005979322944310814</v>
       </c>
       <c r="I90">
-        <v>0.2099560915859742</v>
+        <v>-0.1093864588862159</v>
       </c>
       <c r="J90">
-        <v>0.8002195420701311</v>
+        <v>0.7877291777243258</v>
       </c>
       <c r="K90">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="L90">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="M90">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="N90">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="O90">
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5302,49 +5335,49 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C91">
-        <v>1.814964366537685</v>
+        <v>1.932400003731856</v>
       </c>
       <c r="D91" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E91">
-        <v>1.606051621065991</v>
+        <v>2.041764709541035</v>
       </c>
       <c r="F91">
         <v>-1</v>
       </c>
       <c r="G91">
-        <v>0.005085035633462316</v>
+        <v>0.005947599996268144</v>
       </c>
       <c r="H91">
-        <v>0.004553948378934009</v>
+        <v>0.005978235290458964</v>
       </c>
       <c r="I91">
-        <v>0.2089127454716935</v>
+        <v>-0.1093647058091789</v>
       </c>
       <c r="J91">
-        <v>0.8054362726415348</v>
+        <v>0.7872941161835857</v>
       </c>
       <c r="K91">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="L91">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="M91">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="N91">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="O91">
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>25</v>
+        <v>111</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5352,49 +5385,49 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C92">
-        <v>1.80276175127278</v>
+        <v>1.928867601835406</v>
       </c>
       <c r="D92" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E92">
-        <v>1.595051233906003</v>
+        <v>2.038301570426869</v>
       </c>
       <c r="F92">
         <v>-1</v>
       </c>
       <c r="G92">
-        <v>0.005097238248727221</v>
+        <v>0.005951132398164594</v>
       </c>
       <c r="H92">
-        <v>0.004564948766093997</v>
+        <v>0.005981698429573131</v>
       </c>
       <c r="I92">
-        <v>0.2077105173667766</v>
+        <v>-0.1094339685914623</v>
       </c>
       <c r="J92">
-        <v>0.8114474131661186</v>
+        <v>0.7886793718292525</v>
       </c>
       <c r="K92">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="L92">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="M92">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="N92">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="O92">
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5402,49 +5435,49 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C93">
-        <v>1.799355758249058</v>
+        <v>1.925635063875757</v>
       </c>
       <c r="D93" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E93">
-        <v>1.591980806697426</v>
+        <v>2.035132415564467</v>
       </c>
       <c r="F93">
         <v>-1</v>
       </c>
       <c r="G93">
-        <v>0.005100644241750943</v>
+        <v>0.005954364936124243</v>
       </c>
       <c r="H93">
-        <v>0.004568019193302574</v>
+        <v>0.005984867584435533</v>
       </c>
       <c r="I93">
-        <v>0.2073749515516314</v>
+        <v>-0.1094973516887103</v>
       </c>
       <c r="J93">
-        <v>0.8131252422418436</v>
+        <v>0.7899470337742129</v>
       </c>
       <c r="K93">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="L93">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="M93">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="N93">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="O93">
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5452,99 +5485,99 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C94">
-        <v>1.750849917183753</v>
+        <v>1.924421367530698</v>
       </c>
       <c r="D94" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E94">
-        <v>1.581051389485984</v>
+        <v>2.033942517186959</v>
       </c>
       <c r="F94">
         <v>-1</v>
       </c>
       <c r="G94">
-        <v>0.005109150082816248</v>
+        <v>0.005955578632469301</v>
       </c>
       <c r="H94">
-        <v>0.004578948610514017</v>
+        <v>0.005986057482813041</v>
       </c>
       <c r="I94">
-        <v>0.1697985276977689</v>
+        <v>-0.1095211496562603</v>
       </c>
       <c r="J94">
-        <v>0.8190976013737793</v>
+        <v>0.7904229931252164</v>
       </c>
       <c r="K94">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="L94">
-        <v>3.43</v>
+        <v>3.94</v>
       </c>
       <c r="M94">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="N94">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="O94">
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
     </row>
     <row r="95" spans="1:16">
       <c r="A95" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C95">
-        <v>1.753412348936472</v>
+        <v>1.922633944537091</v>
       </c>
       <c r="D95" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E95">
-        <v>1.851301116496863</v>
+        <v>2.03219014170303</v>
       </c>
       <c r="F95">
         <v>-1</v>
       </c>
       <c r="G95">
-        <v>0.005406587651063528</v>
+        <v>0.00595736605546291</v>
       </c>
       <c r="H95">
-        <v>0.006028698883503138</v>
+        <v>0.00598780985829697</v>
       </c>
       <c r="I95">
-        <v>-0.09788876756039033</v>
+        <v>-0.1095561971659391</v>
       </c>
       <c r="J95">
-        <v>0.8190976013737793</v>
+        <v>0.791123943318788</v>
       </c>
       <c r="K95">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L95">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M95">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="N95">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="O95">
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5552,99 +5585,99 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C96">
-        <v>1.754194230856962</v>
+        <v>1.921462641095741</v>
       </c>
       <c r="D96" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E96">
-        <v>1.58403680120402</v>
+        <v>2.031041804995824</v>
       </c>
       <c r="F96">
         <v>-1</v>
       </c>
       <c r="G96">
-        <v>0.005105805769143037</v>
+        <v>0.005958537358904259</v>
       </c>
       <c r="H96">
-        <v>0.00457596319879598</v>
+        <v>0.005988958195004175</v>
       </c>
       <c r="I96">
-        <v>0.1701574296529424</v>
+        <v>-0.1095791639000829</v>
       </c>
       <c r="J96">
-        <v>0.8174662288502623</v>
+        <v>0.7915832780016702</v>
       </c>
       <c r="K96">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="L96">
-        <v>3.43</v>
+        <v>3.94</v>
       </c>
       <c r="M96">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="N96">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="O96">
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="97" spans="1:16">
       <c r="A97" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C97">
-        <v>1.757050309663915</v>
+        <v>1.922670198036319</v>
       </c>
       <c r="D97" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E97">
-        <v>1.855461116431831</v>
+        <v>2.032225684349332</v>
       </c>
       <c r="F97">
         <v>-1</v>
       </c>
       <c r="G97">
-        <v>0.005402949690336085</v>
+        <v>0.005957329801963681</v>
       </c>
       <c r="H97">
-        <v>0.006024538883568169</v>
+        <v>0.005987774315650668</v>
       </c>
       <c r="I97">
-        <v>-0.09841080676791614</v>
+        <v>-0.1095554863130133</v>
       </c>
       <c r="J97">
-        <v>0.8174662288502623</v>
+        <v>0.7911097262602672</v>
       </c>
       <c r="K97">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L97">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M97">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="N97">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="O97">
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5652,99 +5685,99 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C98">
-        <v>1.755052845867249</v>
+        <v>1.924302790568959</v>
       </c>
       <c r="D98" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E98">
-        <v>1.584803272164423</v>
+        <v>2.033826265263685</v>
       </c>
       <c r="F98">
         <v>-1</v>
       </c>
       <c r="G98">
-        <v>0.005104947154132751</v>
+        <v>0.00595569720943104</v>
       </c>
       <c r="H98">
-        <v>0.004575196727835578</v>
+        <v>0.005986173734736314</v>
       </c>
       <c r="I98">
-        <v>0.1702495737028269</v>
+        <v>-0.109523474694726</v>
       </c>
       <c r="J98">
-        <v>0.8170473922598784</v>
+        <v>0.7904694938945258</v>
       </c>
       <c r="K98">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="L98">
-        <v>3.43</v>
+        <v>3.94</v>
       </c>
       <c r="M98">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="N98">
-        <v>3.08</v>
+        <v>4.01</v>
       </c>
       <c r="O98">
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C99">
-        <v>1.757984315260471</v>
+        <v>1.92765643109575</v>
       </c>
       <c r="D99" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E99">
-        <v>1.85652914973731</v>
+        <v>2.037114148133088</v>
       </c>
       <c r="F99">
         <v>-1</v>
       </c>
       <c r="G99">
-        <v>0.005402015684739529</v>
+        <v>0.005952343568904249</v>
       </c>
       <c r="H99">
-        <v>0.006023470850262691</v>
+        <v>0.005982885851866911</v>
       </c>
       <c r="I99">
-        <v>-0.09854483447683893</v>
+        <v>-0.1094577170373379</v>
       </c>
       <c r="J99">
-        <v>0.8170473922598784</v>
+        <v>0.7891543407467646</v>
       </c>
       <c r="K99">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L99">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M99">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="N99">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="O99">
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -5752,99 +5785,99 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C100">
-        <v>1.753786160185185</v>
+        <v>1.931644858116821</v>
       </c>
       <c r="D100" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="E100">
-        <v>1.574612606219512</v>
+        <v>2.041024370702765</v>
       </c>
       <c r="F100">
         <v>-1</v>
       </c>
       <c r="G100">
-        <v>0.005106213839814816</v>
+        <v>0.005948355141883179</v>
       </c>
       <c r="H100">
-        <v>0.004665387393780488</v>
+        <v>0.005978975629297235</v>
       </c>
       <c r="I100">
-        <v>0.1791735539656729</v>
+        <v>-0.1093795125859445</v>
       </c>
       <c r="J100">
-        <v>0.8176652877145442</v>
+        <v>0.7875902517188939</v>
       </c>
       <c r="K100">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="L100">
-        <v>3.43</v>
+        <v>3.94</v>
       </c>
       <c r="M100">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="N100">
-        <v>3.12</v>
+        <v>4.01</v>
       </c>
       <c r="O100">
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C101">
-        <v>1.756606408396567</v>
+        <v>1.933649431471673</v>
       </c>
       <c r="D101" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E101">
-        <v>1.854953516327912</v>
+        <v>2.042989638697718</v>
       </c>
       <c r="F101">
         <v>-1</v>
       </c>
       <c r="G101">
-        <v>0.005403393591603433</v>
+        <v>0.005946350568528327</v>
       </c>
       <c r="H101">
-        <v>0.006025046483672087</v>
+        <v>0.005977010361302281</v>
       </c>
       <c r="I101">
-        <v>-0.09834710793134582</v>
+        <v>-0.1093402072260452</v>
       </c>
       <c r="J101">
-        <v>0.8176652877145442</v>
+        <v>0.7868041445209126</v>
       </c>
       <c r="K101">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L101">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M101">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="N101">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="O101">
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -5852,49 +5885,49 @@
         <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C102">
-        <v>1.755683380438077</v>
+        <v>1.937204548237283</v>
       </c>
       <c r="D102" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E102">
-        <v>1.853898035926949</v>
+        <v>2.046475047291454</v>
       </c>
       <c r="F102">
         <v>-1</v>
       </c>
       <c r="G102">
-        <v>0.005404316619561924</v>
+        <v>0.005942795451762716</v>
       </c>
       <c r="H102">
-        <v>0.00602610196407305</v>
+        <v>0.005973524952708546</v>
       </c>
       <c r="I102">
-        <v>-0.09821465548887209</v>
+        <v>-0.1092704990541709</v>
       </c>
       <c r="J102">
-        <v>0.8180792015972748</v>
+        <v>0.7854099810834182</v>
       </c>
       <c r="K102">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L102">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M102">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="N102">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="O102">
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -5902,49 +5935,49 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C103">
-        <v>1.753286997752252</v>
+        <v>1.941976947705745</v>
       </c>
       <c r="D103" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E103">
-        <v>1.851157777698763</v>
+        <v>2.05115387029975</v>
       </c>
       <c r="F103">
         <v>-1</v>
       </c>
       <c r="G103">
-        <v>0.005406713002247748</v>
+        <v>0.005938023052294255</v>
       </c>
       <c r="H103">
-        <v>0.006028842222301236</v>
+        <v>0.00596884612970025</v>
       </c>
       <c r="I103">
-        <v>-0.0978707799465115</v>
+        <v>-0.1091769225940049</v>
       </c>
       <c r="J103">
-        <v>0.8191538126671517</v>
+        <v>0.7835384518800999</v>
       </c>
       <c r="K103">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L103">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M103">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="N103">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="O103">
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -5952,49 +5985,49 @@
         <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C104">
-        <v>1.759765740315211</v>
+        <v>1.943259802359731</v>
       </c>
       <c r="D104" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E104">
-        <v>1.858566205293179</v>
+        <v>2.052411570940913</v>
       </c>
       <c r="F104">
         <v>-1</v>
       </c>
       <c r="G104">
-        <v>0.005400234259684789</v>
+        <v>0.005936740197640269</v>
       </c>
       <c r="H104">
-        <v>0.006021433794706822</v>
+        <v>0.005967588429059087</v>
       </c>
       <c r="I104">
-        <v>-0.09880046497796746</v>
+        <v>-0.1091517685811818</v>
       </c>
       <c r="J104">
-        <v>0.8162485469438515</v>
+        <v>0.783035371623635</v>
       </c>
       <c r="K104">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L104">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M104">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="N104">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="O104">
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6002,49 +6035,49 @@
         <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C105">
-        <v>1.768370582676801</v>
+        <v>1.944946776406004</v>
       </c>
       <c r="D105" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E105">
-        <v>1.868405823240289</v>
+        <v>2.054065467064709</v>
       </c>
       <c r="F105">
         <v>-1</v>
       </c>
       <c r="G105">
-        <v>0.005391629417323198</v>
+        <v>0.005935053223593996</v>
       </c>
       <c r="H105">
-        <v>0.006011594176759711</v>
+        <v>0.005965934532935291</v>
       </c>
       <c r="I105">
-        <v>-0.1000352405634874</v>
+        <v>-0.1091186906587052</v>
       </c>
       <c r="J105">
-        <v>0.8123898732391025</v>
+        <v>0.7823738131741161</v>
       </c>
       <c r="K105">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L105">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M105">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="N105">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="O105">
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6052,49 +6085,49 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C106">
-        <v>1.772475206570581</v>
+        <v>1.948679250285769</v>
       </c>
       <c r="D106" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E106">
-        <v>1.873099451459633</v>
+        <v>2.057724755182126</v>
       </c>
       <c r="F106">
         <v>-1</v>
       </c>
       <c r="G106">
-        <v>0.005387524793429419</v>
+        <v>0.005931320749714232</v>
       </c>
       <c r="H106">
-        <v>0.006006900548540367</v>
+        <v>0.005962275244817874</v>
       </c>
       <c r="I106">
-        <v>-0.1006242448890518</v>
+        <v>-0.1090455048963574</v>
       </c>
       <c r="J106">
-        <v>0.8105492347217125</v>
+        <v>0.7809100979271496</v>
       </c>
       <c r="K106">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L106">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M106">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="N106">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="O106">
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6102,49 +6135,49 @@
         <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C107">
-        <v>1.778785868167223</v>
+        <v>1.950614227390016</v>
       </c>
       <c r="D107" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E107">
-        <v>1.880315678845928</v>
+        <v>2.059621791558839</v>
       </c>
       <c r="F107">
         <v>-1</v>
       </c>
       <c r="G107">
-        <v>0.005381214131832777</v>
+        <v>0.005929385772609984</v>
       </c>
       <c r="H107">
-        <v>0.005999684321154073</v>
+        <v>0.005960378208441161</v>
       </c>
       <c r="I107">
-        <v>-0.1015298106787046</v>
+        <v>-0.1090075641688231</v>
       </c>
       <c r="J107">
-        <v>0.8077193416290479</v>
+        <v>0.7801512833764644</v>
       </c>
       <c r="K107">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L107">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M107">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="N107">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="O107">
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6152,49 +6185,49 @@
         <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C108">
-        <v>1.783082667864885</v>
+        <v>1.951624445196418</v>
       </c>
       <c r="D108" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E108">
-        <v>1.885229059666124</v>
+        <v>2.060612201172958</v>
       </c>
       <c r="F108">
         <v>-1</v>
       </c>
       <c r="G108">
-        <v>0.005376917332135115</v>
+        <v>0.005928375554803582</v>
       </c>
       <c r="H108">
-        <v>0.005994770940333876</v>
+        <v>0.005959387798827042</v>
       </c>
       <c r="I108">
-        <v>-0.1021463918012393</v>
+        <v>-0.1089877559765402</v>
       </c>
       <c r="J108">
-        <v>0.8057925256211278</v>
+        <v>0.7797551195308166</v>
       </c>
       <c r="K108">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L108">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M108">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="N108">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="O108">
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6202,49 +6235,49 @@
         <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C109">
-        <v>1.788647602775973</v>
+        <v>1.953198644707818</v>
       </c>
       <c r="D109" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E109">
-        <v>1.891592550259521</v>
+        <v>2.062155534027272</v>
       </c>
       <c r="F109">
         <v>-1</v>
       </c>
       <c r="G109">
-        <v>0.005371352397224027</v>
+        <v>0.005926801355292182</v>
       </c>
       <c r="H109">
-        <v>0.00598840744974048</v>
+        <v>0.005957844465972727</v>
       </c>
       <c r="I109">
-        <v>-0.1029449474835478</v>
+        <v>-0.1089568893194541</v>
       </c>
       <c r="J109">
-        <v>0.8032970391139135</v>
+        <v>0.7791377863890909</v>
       </c>
       <c r="K109">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L109">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M109">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="N109">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="O109">
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6252,49 +6285,49 @@
         <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C110">
-        <v>1.794449014383639</v>
+        <v>1.956263001176151</v>
       </c>
       <c r="D110" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E110">
-        <v>1.898226451425238</v>
+        <v>2.065159805074657</v>
       </c>
       <c r="F110">
         <v>-1</v>
       </c>
       <c r="G110">
-        <v>0.005365550985616361</v>
+        <v>0.00592373699882385</v>
       </c>
       <c r="H110">
-        <v>0.005981773548574762</v>
+        <v>0.005954840194925343</v>
       </c>
       <c r="I110">
-        <v>-0.1037774370415987</v>
+        <v>-0.1088968038985063</v>
       </c>
       <c r="J110">
-        <v>0.8006955092450049</v>
+        <v>0.777936077970137</v>
       </c>
       <c r="K110">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L110">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M110">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="N110">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="O110">
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6302,49 +6335,49 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C111">
-        <v>1.799039794456311</v>
+        <v>1.957833849297126</v>
       </c>
       <c r="D111" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E111">
-        <v>1.903475998145109</v>
+        <v>2.066699852252084</v>
       </c>
       <c r="F111">
         <v>-1</v>
       </c>
       <c r="G111">
-        <v>0.005360960205543689</v>
+        <v>0.005922166150702874</v>
       </c>
       <c r="H111">
-        <v>0.005976524001854891</v>
+        <v>0.005953300147747916</v>
       </c>
       <c r="I111">
-        <v>-0.104436203688798</v>
+        <v>-0.108866002954958</v>
       </c>
       <c r="J111">
-        <v>0.7986368634725065</v>
+        <v>0.7773200590991663</v>
       </c>
       <c r="K111">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L111">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M111">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="N111">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="O111">
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>46</v>
+        <v>131</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6352,49 +6385,49 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C112">
-        <v>1.809214910520444</v>
+        <v>1.960719712115154</v>
       </c>
       <c r="D112" t="s">
         <v>45</v>
       </c>
       <c r="E112">
-        <v>1.915111220550284</v>
+        <v>1.867004915680786</v>
       </c>
       <c r="F112">
         <v>-1</v>
       </c>
       <c r="G112">
-        <v>0.005350785089479557</v>
+        <v>0.005919280287884846</v>
       </c>
       <c r="H112">
-        <v>0.005964888779449715</v>
+        <v>0.005452995084319214</v>
       </c>
       <c r="I112">
-        <v>-0.1058963100298396</v>
+        <v>0.09371479643436742</v>
       </c>
       <c r="J112">
-        <v>0.7940740311567515</v>
+        <v>0.7761883481901358</v>
       </c>
       <c r="K112">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L112">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M112">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N112">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O112">
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6402,49 +6435,49 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C113">
-        <v>1.820107451446974</v>
+        <v>1.964089726245929</v>
       </c>
       <c r="D113" t="s">
         <v>45</v>
       </c>
       <c r="E113">
-        <v>1.927566816677033</v>
+        <v>1.870057752011018</v>
       </c>
       <c r="F113">
         <v>-1</v>
       </c>
       <c r="G113">
-        <v>0.005339892548553027</v>
+        <v>0.005915910273754071</v>
       </c>
       <c r="H113">
-        <v>0.005952433183322967</v>
+        <v>0.005449942247988983</v>
       </c>
       <c r="I113">
-        <v>-0.1074593652300591</v>
+        <v>0.09403197423491094</v>
       </c>
       <c r="J113">
-        <v>0.7891894836560657</v>
+        <v>0.7748667740212044</v>
       </c>
       <c r="K113">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L113">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M113">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N113">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O113">
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6452,49 +6485,49 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C114">
-        <v>1.823117018134749</v>
+        <v>1.967432273912166</v>
       </c>
       <c r="D114" t="s">
         <v>45</v>
       </c>
       <c r="E114">
-        <v>1.931008249436597</v>
+        <v>1.873085706955727</v>
       </c>
       <c r="F114">
         <v>-1</v>
       </c>
       <c r="G114">
-        <v>0.005336882981865252</v>
+        <v>0.005912567726087834</v>
       </c>
       <c r="H114">
-        <v>0.005948991750563403</v>
+        <v>0.005446914293044273</v>
       </c>
       <c r="I114">
-        <v>-0.1078912313018474</v>
+        <v>0.09434656695643917</v>
       </c>
       <c r="J114">
-        <v>0.7878399021817268</v>
+        <v>0.7735559710148369</v>
       </c>
       <c r="K114">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L114">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M114">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N114">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O114">
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6502,49 +6535,49 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C115">
-        <v>1.823363933674754</v>
+        <v>1.969463367101175</v>
       </c>
       <c r="D115" t="s">
         <v>45</v>
       </c>
       <c r="E115">
-        <v>1.931290596802969</v>
+        <v>1.874925638432829</v>
       </c>
       <c r="F115">
         <v>-1</v>
       </c>
       <c r="G115">
-        <v>0.005336636066325246</v>
+        <v>0.005910536632898825</v>
       </c>
       <c r="H115">
-        <v>0.00594870940319703</v>
+        <v>0.005445074361567171</v>
       </c>
       <c r="I115">
-        <v>-0.1079266631282159</v>
+        <v>0.09453772866834598</v>
       </c>
       <c r="J115">
-        <v>0.7877291777243258</v>
+        <v>0.7727594638818923</v>
       </c>
       <c r="K115">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L115">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M115">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N115">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O115">
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6552,49 +6585,49 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C116">
-        <v>1.824334120910604</v>
+        <v>1.970320430703849</v>
       </c>
       <c r="D116" t="s">
         <v>45</v>
       </c>
       <c r="E116">
-        <v>1.932400003731856</v>
+        <v>1.87570203722584</v>
       </c>
       <c r="F116">
         <v>-1</v>
       </c>
       <c r="G116">
-        <v>0.005335665879089396</v>
+        <v>0.00590967956929615</v>
       </c>
       <c r="H116">
-        <v>0.005947599996268144</v>
+        <v>0.005444297962774161</v>
       </c>
       <c r="I116">
-        <v>-0.1080658828212524</v>
+        <v>0.09461839347800938</v>
       </c>
       <c r="J116">
-        <v>0.7872941161835857</v>
+        <v>0.7724233605082945</v>
       </c>
       <c r="K116">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="L116">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="M116">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N116">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O116">
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6602,49 +6635,49 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C117">
-        <v>1.821245000820767</v>
+        <v>2.079346337166745</v>
       </c>
       <c r="D117" t="s">
         <v>45</v>
       </c>
       <c r="E117">
-        <v>1.928867601835406</v>
+        <v>1.876076015542073</v>
       </c>
       <c r="F117">
         <v>-1</v>
       </c>
       <c r="G117">
-        <v>0.005338754999179234</v>
+        <v>0.005940653662833254</v>
       </c>
       <c r="H117">
-        <v>0.005951132398164594</v>
+        <v>0.005443923984457927</v>
       </c>
       <c r="I117">
-        <v>-0.1076226010146393</v>
+        <v>0.2032703216246725</v>
       </c>
       <c r="J117">
-        <v>0.7886793718292525</v>
+        <v>0.7722614651333018</v>
       </c>
       <c r="K117">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L117">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="M117">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N117">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O117">
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6652,49 +6685,49 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C118">
-        <v>1.818418114683505</v>
+        <v>2.078211043729365</v>
       </c>
       <c r="D118" t="s">
         <v>45</v>
       </c>
       <c r="E118">
-        <v>1.925635063875757</v>
+        <v>1.875027004405933</v>
       </c>
       <c r="F118">
         <v>-1</v>
       </c>
       <c r="G118">
-        <v>0.005341581885316495</v>
+        <v>0.005941788956270636</v>
       </c>
       <c r="H118">
-        <v>0.005954364936124243</v>
+        <v>0.005444972995594067</v>
       </c>
       <c r="I118">
-        <v>-0.1072169491922517</v>
+        <v>0.2031840393234312</v>
       </c>
       <c r="J118">
-        <v>0.7899470337742129</v>
+        <v>0.772715582508254</v>
       </c>
       <c r="K118">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L118">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="M118">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N118">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O118">
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6702,49 +6735,49 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C119">
-        <v>1.817356725330768</v>
+        <v>2.075878111180319</v>
       </c>
       <c r="D119" t="s">
         <v>45</v>
       </c>
       <c r="E119">
-        <v>1.924421367530698</v>
+        <v>1.872871374730615</v>
       </c>
       <c r="F119">
         <v>-1</v>
       </c>
       <c r="G119">
-        <v>0.005342643274669232</v>
+        <v>0.005944121888819681</v>
       </c>
       <c r="H119">
-        <v>0.005955578632469301</v>
+        <v>0.005447128625269386</v>
       </c>
       <c r="I119">
-        <v>-0.1070646421999308</v>
+        <v>0.2030067364497039</v>
       </c>
       <c r="J119">
-        <v>0.7904229931252164</v>
+        <v>0.7736487555278725</v>
       </c>
       <c r="K119">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L119">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="M119">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N119">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O119">
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -6752,49 +6785,49 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C120">
-        <v>1.815793606399103</v>
+        <v>2.0734572921576</v>
       </c>
       <c r="D120" t="s">
         <v>45</v>
       </c>
       <c r="E120">
-        <v>1.922633944537091</v>
+        <v>1.870634537953623</v>
       </c>
       <c r="F120">
         <v>-1</v>
       </c>
       <c r="G120">
-        <v>0.005344206393600897</v>
+        <v>0.005946542707842399</v>
       </c>
       <c r="H120">
-        <v>0.00595736605546291</v>
+        <v>0.005449365462046377</v>
       </c>
       <c r="I120">
-        <v>-0.1068403381379877</v>
+        <v>0.2028227542039773</v>
       </c>
       <c r="J120">
-        <v>0.791123943318788</v>
+        <v>0.7746170831369599</v>
       </c>
       <c r="K120">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L120">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="M120">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N120">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O120">
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -6802,49 +6835,49 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C121">
-        <v>1.814769290056276</v>
+        <v>2.069260822060034</v>
       </c>
       <c r="D121" t="s">
         <v>45</v>
       </c>
       <c r="E121">
-        <v>1.921462641095741</v>
+        <v>1.866756999583472</v>
       </c>
       <c r="F121">
         <v>-1</v>
       </c>
       <c r="G121">
-        <v>0.005345230709943724</v>
+        <v>0.005950739177939966</v>
       </c>
       <c r="H121">
-        <v>0.005958537358904259</v>
+        <v>0.005453243000416529</v>
       </c>
       <c r="I121">
-        <v>-0.1066933510394659</v>
+        <v>0.2025038224765623</v>
       </c>
       <c r="J121">
-        <v>0.7915832780016702</v>
+        <v>0.7762956711759863</v>
       </c>
       <c r="K121">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L121">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="M121">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N121">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O121">
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -6852,49 +6885,49 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C122">
-        <v>1.815825310439604</v>
+        <v>2.064960635460216</v>
       </c>
       <c r="D122" t="s">
         <v>45</v>
       </c>
       <c r="E122">
-        <v>1.922670198036319</v>
+        <v>1.86278362716524</v>
       </c>
       <c r="F122">
         <v>-1</v>
       </c>
       <c r="G122">
-        <v>0.005344174689560396</v>
+        <v>0.005955039364539783</v>
       </c>
       <c r="H122">
-        <v>0.005957329801963681</v>
+        <v>0.00545721637283476</v>
       </c>
       <c r="I122">
-        <v>-0.1068448875967143</v>
+        <v>0.2021770082949759</v>
       </c>
       <c r="J122">
-        <v>0.7911097262602672</v>
+        <v>0.7780157458159134</v>
       </c>
       <c r="K122">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L122">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="M122">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N122">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O122">
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -6902,49 +6935,49 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C123">
-        <v>1.817253028615208</v>
+        <v>2.062649927724336</v>
       </c>
       <c r="D123" t="s">
         <v>45</v>
       </c>
       <c r="E123">
-        <v>1.924302790568959</v>
+        <v>1.860648533217287</v>
       </c>
       <c r="F123">
         <v>-1</v>
       </c>
       <c r="G123">
-        <v>0.005342746971384794</v>
+        <v>0.005957350072275664</v>
       </c>
       <c r="H123">
-        <v>0.00595569720943104</v>
+        <v>0.005459351466782713</v>
       </c>
       <c r="I123">
-        <v>-0.1070497619537516</v>
+        <v>0.2020013945070493</v>
       </c>
       <c r="J123">
-        <v>0.7904694938945258</v>
+        <v>0.7789400289102656</v>
       </c>
       <c r="K123">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L123">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="M123">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N123">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O123">
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -6952,49 +6985,49 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C124">
-        <v>1.820185820134715</v>
+        <v>2.060340111638369</v>
       </c>
       <c r="D124" t="s">
         <v>45</v>
       </c>
       <c r="E124">
-        <v>1.92765643109575</v>
+        <v>1.858514263153853</v>
       </c>
       <c r="F124">
         <v>-1</v>
       </c>
       <c r="G124">
-        <v>0.005339814179865285</v>
+        <v>0.00595965988836163</v>
       </c>
       <c r="H124">
-        <v>0.005952343568904249</v>
+        <v>0.005461485736846147</v>
       </c>
       <c r="I124">
-        <v>-0.1074706109610355</v>
+        <v>0.2018258484845159</v>
       </c>
       <c r="J124">
-        <v>0.7891543407467646</v>
+        <v>0.7798639553446522</v>
       </c>
       <c r="K124">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L124">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="M124">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N124">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O124">
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7002,49 +7035,49 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C125">
-        <v>1.823673738666867</v>
+        <v>2.058086897870289</v>
       </c>
       <c r="D125" t="s">
         <v>45</v>
       </c>
       <c r="E125">
-        <v>1.931644858116821</v>
+        <v>1.856432293632148</v>
       </c>
       <c r="F125">
         <v>-1</v>
       </c>
       <c r="G125">
-        <v>0.005336326261333134</v>
+        <v>0.00596191310212971</v>
       </c>
       <c r="H125">
-        <v>0.005948355141883179</v>
+        <v>0.005463567706367853</v>
       </c>
       <c r="I125">
-        <v>-0.1079711194499537</v>
+        <v>0.2016546042381415</v>
       </c>
       <c r="J125">
-        <v>0.7875902517188939</v>
+        <v>0.7807652408518843</v>
       </c>
       <c r="K125">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L125">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="M125">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N125">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O125">
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7052,49 +7085,49 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C126">
-        <v>1.825426757718365</v>
+        <v>2.054455475290532</v>
       </c>
       <c r="D126" t="s">
         <v>45</v>
       </c>
       <c r="E126">
-        <v>1.933649431471673</v>
+        <v>1.853076859168452</v>
       </c>
       <c r="F126">
         <v>-1</v>
       </c>
       <c r="G126">
-        <v>0.005334573242281635</v>
+        <v>0.005965544524709467</v>
       </c>
       <c r="H126">
-        <v>0.005946350568528327</v>
+        <v>0.005466923140831549</v>
       </c>
       <c r="I126">
-        <v>-0.1082226737533081</v>
+        <v>0.2013786161220803</v>
       </c>
       <c r="J126">
-        <v>0.7868041445209126</v>
+        <v>0.7822178098837871</v>
       </c>
       <c r="K126">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L126">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="M126">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N126">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O126">
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7102,49 +7135,49 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C127">
-        <v>1.828535742183977</v>
+        <v>2.051743125354167</v>
       </c>
       <c r="D127" t="s">
         <v>45</v>
       </c>
       <c r="E127">
-        <v>1.937204548237283</v>
+        <v>1.85057064782725</v>
       </c>
       <c r="F127">
         <v>-1</v>
       </c>
       <c r="G127">
-        <v>0.005331464257816023</v>
+        <v>0.005968256874645833</v>
       </c>
       <c r="H127">
-        <v>0.005942795451762716</v>
+        <v>0.00546942935217275</v>
       </c>
       <c r="I127">
-        <v>-0.1086688060533061</v>
+        <v>0.2011724775269164</v>
       </c>
       <c r="J127">
-        <v>0.7854099810834182</v>
+        <v>0.7833027498583333</v>
       </c>
       <c r="K127">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L127">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="M127">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N127">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O127">
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7152,49 +7185,49 @@
         <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C128">
-        <v>1.832709252307377</v>
+        <v>2.049665109064402</v>
       </c>
       <c r="D128" t="s">
         <v>45</v>
       </c>
       <c r="E128">
-        <v>1.941976947705745</v>
+        <v>1.848650560775508</v>
       </c>
       <c r="F128">
         <v>-1</v>
       </c>
       <c r="G128">
-        <v>0.005327290747692623</v>
+        <v>0.005970334890935598</v>
       </c>
       <c r="H128">
-        <v>0.005938023052294255</v>
+        <v>0.005471349439224492</v>
       </c>
       <c r="I128">
-        <v>-0.109267695398368</v>
+        <v>0.2010145482888941</v>
       </c>
       <c r="J128">
-        <v>0.7835384518800999</v>
+        <v>0.784133956374239</v>
       </c>
       <c r="K128">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L128">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="M128">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N128">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O128">
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7202,49 +7235,49 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C129">
-        <v>1.833831121279294</v>
+        <v>2.045876432573801</v>
       </c>
       <c r="D129" t="s">
         <v>45</v>
       </c>
       <c r="E129">
-        <v>1.943259802359731</v>
+        <v>1.845149823698192</v>
       </c>
       <c r="F129">
         <v>-1</v>
       </c>
       <c r="G129">
-        <v>0.005326168878720706</v>
+        <v>0.005974123567426199</v>
       </c>
       <c r="H129">
-        <v>0.005936740197640269</v>
+        <v>0.005474850176301808</v>
       </c>
       <c r="I129">
-        <v>-0.1094286810804368</v>
+        <v>0.2007266088756083</v>
       </c>
       <c r="J129">
-        <v>0.783035371623635</v>
+        <v>0.7856494269704796</v>
       </c>
       <c r="K129">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L129">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="M129">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N129">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O129">
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7252,49 +7285,49 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C130">
-        <v>1.835306396621721</v>
+        <v>2.040113864426065</v>
       </c>
       <c r="D130" t="s">
         <v>45</v>
       </c>
       <c r="E130">
-        <v>1.944946776406004</v>
+        <v>1.839825210729684</v>
       </c>
       <c r="F130">
         <v>-1</v>
       </c>
       <c r="G130">
-        <v>0.005324693603378279</v>
+        <v>0.005979886135573935</v>
       </c>
       <c r="H130">
-        <v>0.005935053223593996</v>
+        <v>0.005480174789270317</v>
       </c>
       <c r="I130">
-        <v>-0.1096403797842829</v>
+        <v>0.2002886536963808</v>
       </c>
       <c r="J130">
-        <v>0.7823738131741161</v>
+        <v>0.7879544542295741</v>
       </c>
       <c r="K130">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L130">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="M130">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N130">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O130">
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7302,49 +7335,49 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C131">
-        <v>1.838570481622456</v>
+        <v>2.03513888559835</v>
       </c>
       <c r="D131" t="s">
         <v>45</v>
       </c>
       <c r="E131">
-        <v>1.948679250285769</v>
+        <v>1.835228330292875</v>
       </c>
       <c r="F131">
         <v>-1</v>
       </c>
       <c r="G131">
-        <v>0.005321429518377544</v>
+        <v>0.00598486111440165</v>
       </c>
       <c r="H131">
-        <v>0.005931320749714232</v>
+        <v>0.005484771669707125</v>
       </c>
       <c r="I131">
-        <v>-0.1101087686633122</v>
+        <v>0.1999105553054743</v>
       </c>
       <c r="J131">
-        <v>0.7809100979271496</v>
+        <v>0.78994444576066</v>
       </c>
       <c r="K131">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L131">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="M131">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N131">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O131">
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7352,599 +7385,49 @@
         <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C132">
-        <v>1.840262638070484</v>
+        <v>2.027039654230626</v>
       </c>
       <c r="D132" t="s">
         <v>45</v>
       </c>
       <c r="E132">
-        <v>1.950614227390016</v>
+        <v>1.827744640509099</v>
       </c>
       <c r="F132">
         <v>-1</v>
       </c>
       <c r="G132">
-        <v>0.005319737361929516</v>
+        <v>0.005992960345769374</v>
       </c>
       <c r="H132">
-        <v>0.005929385772609984</v>
+        <v>0.005492255359490901</v>
       </c>
       <c r="I132">
-        <v>-0.1103515893195315</v>
+        <v>0.199295013721527</v>
       </c>
       <c r="J132">
-        <v>0.7801512833764644</v>
+        <v>0.7931841383077493</v>
       </c>
       <c r="K132">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="L132">
-        <v>3.58</v>
+        <v>4.01</v>
       </c>
       <c r="M132">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="N132">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="O132">
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16">
-      <c r="A133" s="1">
-        <v>0</v>
-      </c>
-      <c r="B133" t="s">
-        <v>24</v>
-      </c>
-      <c r="C133">
-        <v>1.841146083446279</v>
-      </c>
-      <c r="D133" t="s">
-        <v>45</v>
-      </c>
-      <c r="E133">
-        <v>1.951624445196418</v>
-      </c>
-      <c r="F133">
-        <v>-1</v>
-      </c>
-      <c r="G133">
-        <v>0.005318853916553721</v>
-      </c>
-      <c r="H133">
-        <v>0.005928375554803582</v>
-      </c>
-      <c r="I133">
-        <v>-0.1104783617501388</v>
-      </c>
-      <c r="J133">
-        <v>0.7797551195308166</v>
-      </c>
-      <c r="K133">
-        <v>2.23</v>
-      </c>
-      <c r="L133">
-        <v>3.58</v>
-      </c>
-      <c r="M133">
-        <v>2.55</v>
-      </c>
-      <c r="N133">
-        <v>3.94</v>
-      </c>
-      <c r="O133">
-        <v>1</v>
-      </c>
-      <c r="P133" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16">
-      <c r="A134" s="1">
-        <v>0</v>
-      </c>
-      <c r="B134" t="s">
-        <v>24</v>
-      </c>
-      <c r="C134">
-        <v>1.842522736352327</v>
-      </c>
-      <c r="D134" t="s">
-        <v>45</v>
-      </c>
-      <c r="E134">
-        <v>1.953198644707818</v>
-      </c>
-      <c r="F134">
-        <v>-1</v>
-      </c>
-      <c r="G134">
-        <v>0.005317477263647673</v>
-      </c>
-      <c r="H134">
-        <v>0.005926801355292182</v>
-      </c>
-      <c r="I134">
-        <v>-0.1106759083554909</v>
-      </c>
-      <c r="J134">
-        <v>0.7791377863890909</v>
-      </c>
-      <c r="K134">
-        <v>2.23</v>
-      </c>
-      <c r="L134">
-        <v>3.58</v>
-      </c>
-      <c r="M134">
-        <v>2.55</v>
-      </c>
-      <c r="N134">
-        <v>3.94</v>
-      </c>
-      <c r="O134">
-        <v>1</v>
-      </c>
-      <c r="P134" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16">
-      <c r="A135" s="1">
-        <v>0</v>
-      </c>
-      <c r="B135" t="s">
-        <v>24</v>
-      </c>
-      <c r="C135">
-        <v>1.845202546126595</v>
-      </c>
-      <c r="D135" t="s">
-        <v>45</v>
-      </c>
-      <c r="E135">
-        <v>1.956263001176151</v>
-      </c>
-      <c r="F135">
-        <v>-1</v>
-      </c>
-      <c r="G135">
-        <v>0.005314797453873405</v>
-      </c>
-      <c r="H135">
-        <v>0.00592373699882385</v>
-      </c>
-      <c r="I135">
-        <v>-0.1110604550495562</v>
-      </c>
-      <c r="J135">
-        <v>0.777936077970137</v>
-      </c>
-      <c r="K135">
-        <v>2.23</v>
-      </c>
-      <c r="L135">
-        <v>3.58</v>
-      </c>
-      <c r="M135">
-        <v>2.55</v>
-      </c>
-      <c r="N135">
-        <v>3.94</v>
-      </c>
-      <c r="O135">
-        <v>1</v>
-      </c>
-      <c r="P135" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="136" spans="1:16">
-      <c r="A136" s="1">
-        <v>0</v>
-      </c>
-      <c r="B136" t="s">
-        <v>24</v>
-      </c>
-      <c r="C136">
-        <v>1.846576268208859</v>
-      </c>
-      <c r="D136" t="s">
-        <v>45</v>
-      </c>
-      <c r="E136">
-        <v>1.957833849297126</v>
-      </c>
-      <c r="F136">
-        <v>-1</v>
-      </c>
-      <c r="G136">
-        <v>0.005313423731791141</v>
-      </c>
-      <c r="H136">
-        <v>0.005922166150702874</v>
-      </c>
-      <c r="I136">
-        <v>-0.1112575810882668</v>
-      </c>
-      <c r="J136">
-        <v>0.7773200590991663</v>
-      </c>
-      <c r="K136">
-        <v>2.23</v>
-      </c>
-      <c r="L136">
-        <v>3.58</v>
-      </c>
-      <c r="M136">
-        <v>2.55</v>
-      </c>
-      <c r="N136">
-        <v>3.94</v>
-      </c>
-      <c r="O136">
-        <v>1</v>
-      </c>
-      <c r="P136" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16">
-      <c r="A137" s="1">
-        <v>0</v>
-      </c>
-      <c r="B137" t="s">
-        <v>24</v>
-      </c>
-      <c r="C137">
-        <v>1.849099983535997</v>
-      </c>
-      <c r="D137" t="s">
-        <v>45</v>
-      </c>
-      <c r="E137">
-        <v>1.960719712115154</v>
-      </c>
-      <c r="F137">
-        <v>-1</v>
-      </c>
-      <c r="G137">
-        <v>0.005310900016464003</v>
-      </c>
-      <c r="H137">
-        <v>0.005919280287884846</v>
-      </c>
-      <c r="I137">
-        <v>-0.1116197285791567</v>
-      </c>
-      <c r="J137">
-        <v>0.7761883481901358</v>
-      </c>
-      <c r="K137">
-        <v>2.23</v>
-      </c>
-      <c r="L137">
-        <v>3.58</v>
-      </c>
-      <c r="M137">
-        <v>2.55</v>
-      </c>
-      <c r="N137">
-        <v>3.94</v>
-      </c>
-      <c r="O137">
-        <v>1</v>
-      </c>
-      <c r="P137" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="138" spans="1:16">
-      <c r="A138" s="1">
-        <v>0</v>
-      </c>
-      <c r="B138" t="s">
-        <v>24</v>
-      </c>
-      <c r="C138">
-        <v>1.852047093932714</v>
-      </c>
-      <c r="D138" t="s">
-        <v>45</v>
-      </c>
-      <c r="E138">
-        <v>1.964089726245929</v>
-      </c>
-      <c r="F138">
-        <v>-1</v>
-      </c>
-      <c r="G138">
-        <v>0.005307952906067286</v>
-      </c>
-      <c r="H138">
-        <v>0.005915910273754071</v>
-      </c>
-      <c r="I138">
-        <v>-0.1120426323132147</v>
-      </c>
-      <c r="J138">
-        <v>0.7748667740212044</v>
-      </c>
-      <c r="K138">
-        <v>2.23</v>
-      </c>
-      <c r="L138">
-        <v>3.58</v>
-      </c>
-      <c r="M138">
-        <v>2.55</v>
-      </c>
-      <c r="N138">
-        <v>3.94</v>
-      </c>
-      <c r="O138">
-        <v>1</v>
-      </c>
-      <c r="P138" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16">
-      <c r="A139" s="1">
-        <v>0</v>
-      </c>
-      <c r="B139" t="s">
-        <v>24</v>
-      </c>
-      <c r="C139">
-        <v>1.854970184636914</v>
-      </c>
-      <c r="D139" t="s">
-        <v>45</v>
-      </c>
-      <c r="E139">
-        <v>1.967432273912166</v>
-      </c>
-      <c r="F139">
-        <v>-1</v>
-      </c>
-      <c r="G139">
-        <v>0.005305029815363087</v>
-      </c>
-      <c r="H139">
-        <v>0.005912567726087834</v>
-      </c>
-      <c r="I139">
-        <v>-0.1124620892752521</v>
-      </c>
-      <c r="J139">
-        <v>0.7735559710148369</v>
-      </c>
-      <c r="K139">
-        <v>2.23</v>
-      </c>
-      <c r="L139">
-        <v>3.58</v>
-      </c>
-      <c r="M139">
-        <v>2.55</v>
-      </c>
-      <c r="N139">
-        <v>3.94</v>
-      </c>
-      <c r="O139">
-        <v>1</v>
-      </c>
-      <c r="P139" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="140" spans="1:16">
-      <c r="A140" s="1">
-        <v>0</v>
-      </c>
-      <c r="B140" t="s">
-        <v>24</v>
-      </c>
-      <c r="C140">
-        <v>1.85674639554338</v>
-      </c>
-      <c r="D140" t="s">
-        <v>45</v>
-      </c>
-      <c r="E140">
-        <v>1.969463367101175</v>
-      </c>
-      <c r="F140">
-        <v>-1</v>
-      </c>
-      <c r="G140">
-        <v>0.00530325360445662</v>
-      </c>
-      <c r="H140">
-        <v>0.005910536632898825</v>
-      </c>
-      <c r="I140">
-        <v>-0.1127169715577945</v>
-      </c>
-      <c r="J140">
-        <v>0.7727594638818923</v>
-      </c>
-      <c r="K140">
-        <v>2.23</v>
-      </c>
-      <c r="L140">
-        <v>3.58</v>
-      </c>
-      <c r="M140">
-        <v>2.55</v>
-      </c>
-      <c r="N140">
-        <v>3.94</v>
-      </c>
-      <c r="O140">
-        <v>1</v>
-      </c>
-      <c r="P140" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="141" spans="1:16">
-      <c r="A141" s="1">
-        <v>0</v>
-      </c>
-      <c r="B141" t="s">
-        <v>24</v>
-      </c>
-      <c r="C141">
-        <v>1.857495906066503</v>
-      </c>
-      <c r="D141" t="s">
-        <v>45</v>
-      </c>
-      <c r="E141">
-        <v>1.970320430703849</v>
-      </c>
-      <c r="F141">
-        <v>-1</v>
-      </c>
-      <c r="G141">
-        <v>0.005302504093933497</v>
-      </c>
-      <c r="H141">
-        <v>0.00590967956929615</v>
-      </c>
-      <c r="I141">
-        <v>-0.1128245246373458</v>
-      </c>
-      <c r="J141">
-        <v>0.7724233605082945</v>
-      </c>
-      <c r="K141">
-        <v>2.23</v>
-      </c>
-      <c r="L141">
-        <v>3.58</v>
-      </c>
-      <c r="M141">
-        <v>2.55</v>
-      </c>
-      <c r="N141">
-        <v>3.94</v>
-      </c>
-      <c r="O141">
-        <v>1</v>
-      </c>
-      <c r="P141" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16">
-      <c r="A142" s="1">
-        <v>0</v>
-      </c>
-      <c r="B142" t="s">
-        <v>24</v>
-      </c>
-      <c r="C142">
-        <v>1.857856932752737</v>
-      </c>
-      <c r="D142" t="s">
-        <v>45</v>
-      </c>
-      <c r="E142">
-        <v>1.97073326391008</v>
-      </c>
-      <c r="F142">
-        <v>-1</v>
-      </c>
-      <c r="G142">
-        <v>0.005302143067247263</v>
-      </c>
-      <c r="H142">
-        <v>0.00590926673608992</v>
-      </c>
-      <c r="I142">
-        <v>-0.1128763311573433</v>
-      </c>
-      <c r="J142">
-        <v>0.7722614651333018</v>
-      </c>
-      <c r="K142">
-        <v>2.23</v>
-      </c>
-      <c r="L142">
-        <v>3.58</v>
-      </c>
-      <c r="M142">
-        <v>2.55</v>
-      </c>
-      <c r="N142">
-        <v>3.94</v>
-      </c>
-      <c r="O142">
-        <v>1</v>
-      </c>
-      <c r="P142" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16">
-      <c r="A143" s="1">
-        <v>0</v>
-      </c>
-      <c r="B143" t="s">
-        <v>24</v>
-      </c>
-      <c r="C143">
-        <v>1.856844251006594</v>
-      </c>
-      <c r="D143" t="s">
-        <v>45</v>
-      </c>
-      <c r="E143">
-        <v>1.969575264603952</v>
-      </c>
-      <c r="F143">
-        <v>-1</v>
-      </c>
-      <c r="G143">
-        <v>0.005303155748993407</v>
-      </c>
-      <c r="H143">
-        <v>0.005910424735396047</v>
-      </c>
-      <c r="I143">
-        <v>-0.1127310135973587</v>
-      </c>
-      <c r="J143">
-        <v>0.772715582508254</v>
-      </c>
-      <c r="K143">
-        <v>2.23</v>
-      </c>
-      <c r="L143">
-        <v>3.58</v>
-      </c>
-      <c r="M143">
-        <v>2.55</v>
-      </c>
-      <c r="N143">
-        <v>3.94</v>
-      </c>
-      <c r="O143">
-        <v>1</v>
-      </c>
-      <c r="P143" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01618-601618.xlsx
+++ b/s60_signal/position-01618-601618.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="154">
   <si>
     <t>trade_time</t>
   </si>
@@ -151,12 +151,18 @@
     <t>2021-03-12</t>
   </si>
   <si>
-    <t>2021-07-29</t>
+    <t>2021-07-30</t>
   </si>
   <si>
     <t>2021-03-09</t>
   </si>
   <si>
+    <t>2021-07-28</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
     <t>2016-12-23</t>
   </si>
   <si>
@@ -211,12 +217,6 @@
     <t>2020-11-26</t>
   </si>
   <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-01</t>
-  </si>
-  <si>
     <t>2020-12-16</t>
   </si>
   <si>
@@ -473,6 +473,9 @@
   </si>
   <si>
     <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
   </si>
 </sst>
 </file>
@@ -830,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P132"/>
+  <dimension ref="A1:P134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -927,7 +930,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -977,7 +980,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1027,7 +1030,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1077,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1127,7 +1130,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1177,7 +1180,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1227,7 +1230,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1277,7 +1280,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1327,7 +1330,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1377,7 +1380,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1427,7 +1430,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1477,7 +1480,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1527,7 +1530,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1577,7 +1580,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1627,7 +1630,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1677,7 +1680,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1727,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1777,7 +1780,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1827,7 +1830,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -1877,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -1927,7 +1930,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -1977,7 +1980,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2027,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2077,7 +2080,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2127,7 +2130,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2177,7 +2180,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2227,7 +2230,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2377,7 +2380,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2385,99 +2388,99 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C32">
-        <v>3.017091835180818</v>
+        <v>2.284943445032334</v>
       </c>
       <c r="D32" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E32">
-        <v>3.296315775655196</v>
+        <v>2.033577409367039</v>
       </c>
       <c r="F32">
         <v>-1</v>
       </c>
       <c r="G32">
-        <v>0.004142908164819182</v>
+        <v>0.004235056554967666</v>
       </c>
       <c r="H32">
-        <v>0.004583684224344804</v>
+        <v>0.004066422590632961</v>
       </c>
       <c r="I32">
-        <v>-0.2792239404743775</v>
+        <v>0.2513660356652947</v>
       </c>
       <c r="J32">
-        <v>0.2524251860175702</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K32">
-        <v>2.23</v>
+        <v>1.65</v>
       </c>
       <c r="L32">
-        <v>3.58</v>
+        <v>3.26</v>
       </c>
       <c r="M32">
-        <v>2.55</v>
+        <v>1.72</v>
       </c>
       <c r="N32">
-        <v>3.94</v>
+        <v>3.05</v>
       </c>
       <c r="O32">
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C33">
-        <v>3.0184784678196</v>
+        <v>2.294943445032334</v>
       </c>
       <c r="D33" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E33">
-        <v>3.297901386968601</v>
+        <v>2.033577409367039</v>
       </c>
       <c r="F33">
         <v>-1</v>
       </c>
       <c r="G33">
-        <v>0.0041415215321804</v>
+        <v>0.004245056554967665</v>
       </c>
       <c r="H33">
-        <v>0.004582098613031399</v>
+        <v>0.004066422590632961</v>
       </c>
       <c r="I33">
-        <v>-0.2794229191490007</v>
+        <v>0.2613660356652949</v>
       </c>
       <c r="J33">
-        <v>0.2518033776593721</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K33">
-        <v>2.23</v>
+        <v>1.65</v>
       </c>
       <c r="L33">
-        <v>3.58</v>
+        <v>3.27</v>
       </c>
       <c r="M33">
-        <v>2.55</v>
+        <v>1.72</v>
       </c>
       <c r="N33">
-        <v>3.94</v>
+        <v>3.05</v>
       </c>
       <c r="O33">
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2488,28 +2491,28 @@
         <v>24</v>
       </c>
       <c r="C34">
-        <v>2.284943445032334</v>
+        <v>2.206392009113778</v>
       </c>
       <c r="D34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E34">
-        <v>2.033577409367039</v>
+        <v>1.939163015063914</v>
       </c>
       <c r="F34">
         <v>-1</v>
       </c>
       <c r="G34">
-        <v>0.004235056554967666</v>
+        <v>0.004313607990886223</v>
       </c>
       <c r="H34">
-        <v>0.004066422590632961</v>
+        <v>0.004020836984936086</v>
       </c>
       <c r="I34">
-        <v>0.2513660356652947</v>
+        <v>0.2672289940498638</v>
       </c>
       <c r="J34">
-        <v>0.5909433666470703</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K34">
         <v>1.65</v>
@@ -2518,116 +2521,116 @@
         <v>3.26</v>
       </c>
       <c r="M34">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="N34">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="O34">
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C35">
-        <v>2.294943445032334</v>
+        <v>2.122703049542399</v>
       </c>
       <c r="D35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E35">
-        <v>2.033577409367039</v>
+        <v>1.856488467123704</v>
       </c>
       <c r="F35">
         <v>-1</v>
       </c>
       <c r="G35">
-        <v>0.004245056554967665</v>
+        <v>0.004397296950457601</v>
       </c>
       <c r="H35">
-        <v>0.004066422590632961</v>
+        <v>0.004103511532876296</v>
       </c>
       <c r="I35">
-        <v>0.2613660356652949</v>
+        <v>0.2662145824186952</v>
       </c>
       <c r="J35">
-        <v>0.5909433666470703</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K35">
         <v>1.65</v>
       </c>
       <c r="L35">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="M35">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="N35">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="O35">
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C36">
-        <v>2.206392009113778</v>
+        <v>2.182359258383708</v>
       </c>
       <c r="D36" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E36">
-        <v>1.939163015063914</v>
+        <v>2.286822802336969</v>
       </c>
       <c r="F36">
         <v>-1</v>
       </c>
       <c r="G36">
-        <v>0.004313607990886223</v>
+        <v>0.005697640741616292</v>
       </c>
       <c r="H36">
-        <v>0.004020836984936086</v>
+        <v>0.005733177197663031</v>
       </c>
       <c r="I36">
-        <v>0.2672289940498638</v>
+        <v>-0.1044635439532606</v>
       </c>
       <c r="J36">
-        <v>0.6385502975068013</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K36">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="L36">
-        <v>3.26</v>
+        <v>3.94</v>
       </c>
       <c r="M36">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="N36">
-        <v>2.98</v>
+        <v>4.01</v>
       </c>
       <c r="O36">
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2638,28 +2641,28 @@
         <v>24</v>
       </c>
       <c r="C37">
-        <v>2.122703049542399</v>
+        <v>2.037699170124481</v>
       </c>
       <c r="D37" t="s">
         <v>43</v>
       </c>
       <c r="E37">
-        <v>1.814059302286312</v>
+        <v>1.732146473029046</v>
       </c>
       <c r="F37">
         <v>-1</v>
       </c>
       <c r="G37">
-        <v>0.004397296950457601</v>
+        <v>0.004482300829875518</v>
       </c>
       <c r="H37">
-        <v>0.004005940697713688</v>
+        <v>0.004087853526970955</v>
       </c>
       <c r="I37">
-        <v>0.3086437472560868</v>
+        <v>0.3055526970954354</v>
       </c>
       <c r="J37">
-        <v>0.6892708790652124</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K37">
         <v>1.65</v>
@@ -2677,51 +2680,51 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C38">
-        <v>2.037699170124481</v>
+        <v>2.050989626556016</v>
       </c>
       <c r="D38" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E38">
-        <v>1.732146473029046</v>
+        <v>2.158029045643153</v>
       </c>
       <c r="F38">
         <v>-1</v>
       </c>
       <c r="G38">
-        <v>0.004482300829875518</v>
+        <v>0.005829010373443984</v>
       </c>
       <c r="H38">
-        <v>0.004087853526970955</v>
+        <v>0.005861970954356846</v>
       </c>
       <c r="I38">
-        <v>0.3055526970954354</v>
+        <v>-0.1070394190871369</v>
       </c>
       <c r="J38">
         <v>0.7407883817427386</v>
       </c>
       <c r="K38">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="L38">
-        <v>3.26</v>
+        <v>3.94</v>
       </c>
       <c r="M38">
-        <v>1.59</v>
+        <v>2.5</v>
       </c>
       <c r="N38">
-        <v>2.91</v>
+        <v>4.01</v>
       </c>
       <c r="O38">
         <v>1</v>
@@ -2732,96 +2735,96 @@
     </row>
     <row r="39" spans="1:16">
       <c r="A39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C39">
-        <v>2.050989626556016</v>
+        <v>1.939614977812812</v>
       </c>
       <c r="D39" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E39">
-        <v>2.158029045643153</v>
+        <v>1.637628978619619</v>
       </c>
       <c r="F39">
         <v>-1</v>
       </c>
       <c r="G39">
-        <v>0.005829010373443984</v>
+        <v>0.004580385022187188</v>
       </c>
       <c r="H39">
-        <v>0.005861970954356846</v>
+        <v>0.004182371021380382</v>
       </c>
       <c r="I39">
-        <v>-0.1070394190871369</v>
+        <v>0.301985999193193</v>
       </c>
       <c r="J39">
-        <v>0.7407883817427386</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K39">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="L39">
-        <v>3.94</v>
+        <v>3.26</v>
       </c>
       <c r="M39">
-        <v>2.5</v>
+        <v>1.59</v>
       </c>
       <c r="N39">
-        <v>4.01</v>
+        <v>2.91</v>
       </c>
       <c r="O39">
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C40">
-        <v>1.939614977812812</v>
+        <v>1.899404965710709</v>
       </c>
       <c r="D40" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E40">
-        <v>1.637628978619619</v>
+        <v>2.009416633049714</v>
       </c>
       <c r="F40">
         <v>-1</v>
       </c>
       <c r="G40">
-        <v>0.004580385022187188</v>
+        <v>0.005980595034289291</v>
       </c>
       <c r="H40">
-        <v>0.004182371021380382</v>
+        <v>0.006010583366950286</v>
       </c>
       <c r="I40">
-        <v>0.301985999193193</v>
+        <v>-0.1100116673390055</v>
       </c>
       <c r="J40">
         <v>0.8002333467801142</v>
       </c>
       <c r="K40">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="L40">
-        <v>3.26</v>
+        <v>3.94</v>
       </c>
       <c r="M40">
-        <v>1.59</v>
+        <v>2.5</v>
       </c>
       <c r="N40">
-        <v>2.91</v>
+        <v>4.01</v>
       </c>
       <c r="O40">
         <v>1</v>
@@ -2832,96 +2835,96 @@
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C41">
-        <v>1.899404965710709</v>
+        <v>1.364830842322013</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="E41">
-        <v>2.009416633049714</v>
+        <v>1.598575134626953</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G41">
-        <v>0.005980595034289291</v>
+        <v>0.005255169157677987</v>
       </c>
       <c r="H41">
-        <v>0.006010583366950286</v>
+        <v>0.004741424865373047</v>
       </c>
       <c r="I41">
-        <v>-0.1100116673390055</v>
+        <v>0.2337442923049406</v>
       </c>
       <c r="J41">
-        <v>0.8002333467801142</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K41">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="L41">
-        <v>3.94</v>
+        <v>3.31</v>
       </c>
       <c r="M41">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="N41">
-        <v>4.01</v>
+        <v>3.17</v>
       </c>
       <c r="O41">
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C42">
-        <v>1.364830842322013</v>
+        <v>1.773981942323639</v>
       </c>
       <c r="D42" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E42">
-        <v>1.598575134626953</v>
+        <v>1.886452884631018</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G42">
-        <v>0.005255169157677987</v>
+        <v>0.006106018057676361</v>
       </c>
       <c r="H42">
-        <v>0.004741424865373047</v>
+        <v>0.006133547115368982</v>
       </c>
       <c r="I42">
-        <v>0.2337442923049406</v>
+        <v>-0.1124709423073793</v>
       </c>
       <c r="J42">
         <v>0.8494188461475927</v>
       </c>
       <c r="K42">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L42">
-        <v>3.31</v>
+        <v>3.94</v>
       </c>
       <c r="M42">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="N42">
-        <v>3.17</v>
+        <v>4.01</v>
       </c>
       <c r="O42">
         <v>1</v>
@@ -2932,52 +2935,52 @@
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C43">
-        <v>1.773981942323639</v>
+        <v>1.253223538131198</v>
       </c>
       <c r="D43" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="E43">
-        <v>1.886452884631018</v>
+        <v>1.508412028621273</v>
       </c>
       <c r="F43">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>0.006106018057676361</v>
+        <v>0.005366776461868803</v>
       </c>
       <c r="H43">
-        <v>0.006133547115368982</v>
+        <v>0.004831587971378727</v>
       </c>
       <c r="I43">
-        <v>-0.1124709423073793</v>
+        <v>0.2551884904900752</v>
       </c>
       <c r="J43">
-        <v>0.8494188461475927</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K43">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="L43">
-        <v>3.94</v>
+        <v>3.31</v>
       </c>
       <c r="M43">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="N43">
-        <v>4.01</v>
+        <v>3.17</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -2988,28 +2991,28 @@
         <v>27</v>
       </c>
       <c r="C44">
-        <v>1.253223538131198</v>
+        <v>1.142741567826858</v>
       </c>
       <c r="D44" t="s">
         <v>44</v>
       </c>
       <c r="E44">
-        <v>1.508412028621273</v>
+        <v>1.419158035143968</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44">
-        <v>0.005366776461868803</v>
+        <v>0.005477258432173141</v>
       </c>
       <c r="H44">
-        <v>0.004831587971378727</v>
+        <v>0.004920841964856031</v>
       </c>
       <c r="I44">
-        <v>0.2551884904900752</v>
+        <v>0.2764164673171099</v>
       </c>
       <c r="J44">
-        <v>0.898155660204717</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K44">
         <v>2.29</v>
@@ -3027,51 +3030,51 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C45">
-        <v>1.142741567826858</v>
+        <v>1.643997344789146</v>
       </c>
       <c r="D45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E45">
-        <v>1.419158035143968</v>
+        <v>1.497029482860111</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G45">
-        <v>0.005477258432173141</v>
+        <v>0.006376002655210854</v>
       </c>
       <c r="H45">
-        <v>0.004920841964856031</v>
+        <v>0.00598297051713989</v>
       </c>
       <c r="I45">
-        <v>0.2764164673171099</v>
+        <v>0.1469678619290353</v>
       </c>
       <c r="J45">
         <v>0.9464010620843414</v>
       </c>
       <c r="K45">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="L45">
-        <v>3.31</v>
+        <v>4.01</v>
       </c>
       <c r="M45">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="N45">
-        <v>3.17</v>
+        <v>3.74</v>
       </c>
       <c r="O45">
         <v>1</v>
@@ -3082,96 +3085,96 @@
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46">
-        <v>1.643997344789146</v>
+        <v>1.02473295176371</v>
       </c>
       <c r="D46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E46">
-        <v>1.473813546585172</v>
+        <v>1.323823563651905</v>
       </c>
       <c r="F46">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G46">
-        <v>0.006376002655210854</v>
+        <v>0.005595267048236289</v>
       </c>
       <c r="H46">
-        <v>0.005846186453414829</v>
+        <v>0.005016176436348095</v>
       </c>
       <c r="I46">
-        <v>0.1701837982039747</v>
+        <v>0.2990906118881951</v>
       </c>
       <c r="J46">
-        <v>0.9464010620843414</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K46">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="L46">
-        <v>4.01</v>
+        <v>3.31</v>
       </c>
       <c r="M46">
-        <v>2.31</v>
+        <v>1.85</v>
       </c>
       <c r="N46">
-        <v>3.66</v>
+        <v>3.17</v>
       </c>
       <c r="O46">
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C47">
-        <v>1.02473295176371</v>
+        <v>1.51516697790798</v>
       </c>
       <c r="D47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E47">
-        <v>1.323823563651905</v>
+        <v>1.374898295056766</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G47">
-        <v>0.005595267048236289</v>
+        <v>0.00650483302209202</v>
       </c>
       <c r="H47">
-        <v>0.005016176436348095</v>
+        <v>0.006105101704943235</v>
       </c>
       <c r="I47">
-        <v>0.2990906118881951</v>
+        <v>0.1402686828512145</v>
       </c>
       <c r="J47">
         <v>0.9979332088368078</v>
       </c>
       <c r="K47">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="L47">
-        <v>3.31</v>
+        <v>4.01</v>
       </c>
       <c r="M47">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="N47">
-        <v>3.17</v>
+        <v>3.74</v>
       </c>
       <c r="O47">
         <v>1</v>
@@ -3182,96 +3185,96 @@
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C48">
-        <v>1.51516697790798</v>
+        <v>1.025578495611604</v>
       </c>
       <c r="D48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E48">
-        <v>1.354774287586974</v>
+        <v>1.267956426585794</v>
       </c>
       <c r="F48">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>0.00650483302209202</v>
+        <v>0.005734421504388396</v>
       </c>
       <c r="H48">
-        <v>0.005965225712413026</v>
+        <v>0.005072043573414206</v>
       </c>
       <c r="I48">
-        <v>0.160392690321006</v>
+        <v>0.2423779309741898</v>
       </c>
       <c r="J48">
-        <v>0.9979332088368078</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K48">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="L48">
-        <v>4.01</v>
+        <v>3.38</v>
       </c>
       <c r="M48">
-        <v>2.31</v>
+        <v>1.85</v>
       </c>
       <c r="N48">
-        <v>3.66</v>
+        <v>3.17</v>
       </c>
       <c r="O48">
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C49">
-        <v>1.025578495611604</v>
+        <v>1.439670846737559</v>
       </c>
       <c r="D49" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E49">
-        <v>1.228800376424943</v>
+        <v>1.303327962707206</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G49">
-        <v>0.005734421504388396</v>
+        <v>0.00658032915326244</v>
       </c>
       <c r="H49">
-        <v>0.004971199623575057</v>
+        <v>0.006176672037292795</v>
       </c>
       <c r="I49">
-        <v>0.2032218808133393</v>
+        <v>0.1363428840303529</v>
       </c>
       <c r="J49">
         <v>1.028131661304976</v>
       </c>
       <c r="K49">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="L49">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="M49">
-        <v>1.82</v>
+        <v>2.37</v>
       </c>
       <c r="N49">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="O49">
         <v>1</v>
@@ -3282,52 +3285,52 @@
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C50">
-        <v>1.439670846737559</v>
+        <v>0.95505474527386</v>
       </c>
       <c r="D50" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E50">
-        <v>1.285015862385505</v>
+        <v>1.172750932925077</v>
       </c>
       <c r="F50">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G50">
-        <v>0.00658032915326244</v>
+        <v>0.00580494525472614</v>
       </c>
       <c r="H50">
-        <v>0.006034984137614496</v>
+        <v>0.005027249067074924</v>
       </c>
       <c r="I50">
-        <v>0.1546549843520544</v>
+        <v>0.2176961876512167</v>
       </c>
       <c r="J50">
-        <v>1.028131661304976</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K50">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="L50">
-        <v>4.01</v>
+        <v>3.38</v>
       </c>
       <c r="M50">
-        <v>2.31</v>
+        <v>1.82</v>
       </c>
       <c r="N50">
-        <v>3.66</v>
+        <v>3.1</v>
       </c>
       <c r="O50">
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3338,28 +3341,28 @@
         <v>29</v>
       </c>
       <c r="C51">
-        <v>0.95505474527386</v>
+        <v>0.8997461387005035</v>
       </c>
       <c r="D51" t="s">
         <v>46</v>
       </c>
       <c r="E51">
-        <v>1.172750932925077</v>
+        <v>1.128793874425728</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="G51">
-        <v>0.00580494525472614</v>
+        <v>0.005860253861299496</v>
       </c>
       <c r="H51">
-        <v>0.005027249067074924</v>
+        <v>0.005071206125574273</v>
       </c>
       <c r="I51">
-        <v>0.2176961876512167</v>
+        <v>0.2290477357252241</v>
       </c>
       <c r="J51">
-        <v>1.058928058832376</v>
+        <v>1.083080288777073</v>
       </c>
       <c r="K51">
         <v>2.29</v>
@@ -3377,7 +3380,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3388,28 +3391,28 @@
         <v>29</v>
       </c>
       <c r="C52">
-        <v>0.8997461387005035</v>
+        <v>0.9004291893178089</v>
       </c>
       <c r="D52" t="s">
         <v>46</v>
       </c>
       <c r="E52">
-        <v>1.128793874425728</v>
+        <v>1.129336735615027</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52">
-        <v>0.005860253861299496</v>
+        <v>0.005859570810682191</v>
       </c>
       <c r="H52">
-        <v>0.005071206125574273</v>
+        <v>0.005070663264384973</v>
       </c>
       <c r="I52">
-        <v>0.2290477357252241</v>
+        <v>0.2289075462972185</v>
       </c>
       <c r="J52">
-        <v>1.083080288777073</v>
+        <v>1.082782013398337</v>
       </c>
       <c r="K52">
         <v>2.29</v>
@@ -3427,7 +3430,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3438,28 +3441,28 @@
         <v>29</v>
       </c>
       <c r="C53">
-        <v>0.9004291893178089</v>
+        <v>0.8995341152947529</v>
       </c>
       <c r="D53" t="s">
         <v>46</v>
       </c>
       <c r="E53">
-        <v>1.129336735615027</v>
+        <v>1.128625366740808</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53">
-        <v>0.005859570810682191</v>
+        <v>0.005860465884705247</v>
       </c>
       <c r="H53">
-        <v>0.005070663264384973</v>
+        <v>0.005071374633259193</v>
       </c>
       <c r="I53">
-        <v>0.2289075462972185</v>
+        <v>0.2290912514460552</v>
       </c>
       <c r="J53">
-        <v>1.082782013398337</v>
+        <v>1.083172875417138</v>
       </c>
       <c r="K53">
         <v>2.29</v>
@@ -3477,7 +3480,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3488,28 +3491,28 @@
         <v>29</v>
       </c>
       <c r="C54">
-        <v>0.8995341152947529</v>
+        <v>0.8942975364165378</v>
       </c>
       <c r="D54" t="s">
         <v>46</v>
       </c>
       <c r="E54">
-        <v>1.128625366740808</v>
+        <v>1.124463544226244</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54">
-        <v>0.005860465884705247</v>
+        <v>0.005865702463583462</v>
       </c>
       <c r="H54">
-        <v>0.005071374633259193</v>
+        <v>0.005075536455773756</v>
       </c>
       <c r="I54">
-        <v>0.2290912514460552</v>
+        <v>0.2301660078097063</v>
       </c>
       <c r="J54">
-        <v>1.083172875417138</v>
+        <v>1.085459591084481</v>
       </c>
       <c r="K54">
         <v>2.29</v>
@@ -3527,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3538,28 +3541,28 @@
         <v>29</v>
       </c>
       <c r="C55">
-        <v>0.8942975364165378</v>
+        <v>0.823882990348408</v>
       </c>
       <c r="D55" t="s">
         <v>46</v>
       </c>
       <c r="E55">
-        <v>1.124463544226244</v>
+        <v>1.068500891892621</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55">
-        <v>0.005865702463583462</v>
+        <v>0.005936117009651592</v>
       </c>
       <c r="H55">
-        <v>0.005075536455773756</v>
+        <v>0.005131499108107379</v>
       </c>
       <c r="I55">
-        <v>0.2301660078097063</v>
+        <v>0.2446179015442134</v>
       </c>
       <c r="J55">
-        <v>1.085459591084481</v>
+        <v>1.1162083011579</v>
       </c>
       <c r="K55">
         <v>2.29</v>
@@ -3577,7 +3580,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3588,28 +3591,28 @@
         <v>29</v>
       </c>
       <c r="C56">
-        <v>0.823882990348408</v>
+        <v>0.7552208383877499</v>
       </c>
       <c r="D56" t="s">
         <v>46</v>
       </c>
       <c r="E56">
-        <v>1.068500891892621</v>
+        <v>1.013930971993758</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="G56">
-        <v>0.005936117009651592</v>
+        <v>0.00600477916161225</v>
       </c>
       <c r="H56">
-        <v>0.005131499108107379</v>
+        <v>0.005186069028006243</v>
       </c>
       <c r="I56">
-        <v>0.2446179015442134</v>
+        <v>0.2587101336060078</v>
       </c>
       <c r="J56">
-        <v>1.1162083011579</v>
+        <v>1.146191773629804</v>
       </c>
       <c r="K56">
         <v>2.29</v>
@@ -3627,7 +3630,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3638,28 +3641,28 @@
         <v>29</v>
       </c>
       <c r="C57">
-        <v>0.7552208383877499</v>
+        <v>0.7164672131147527</v>
       </c>
       <c r="D57" t="s">
         <v>46</v>
       </c>
       <c r="E57">
-        <v>1.013930971993758</v>
+        <v>0.9831311475409823</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57">
-        <v>0.00600477916161225</v>
+        <v>0.006043532786885248</v>
       </c>
       <c r="H57">
-        <v>0.005186069028006243</v>
+        <v>0.005216868852459018</v>
       </c>
       <c r="I57">
-        <v>0.2587101336060078</v>
+        <v>0.2666639344262296</v>
       </c>
       <c r="J57">
-        <v>1.146191773629804</v>
+        <v>1.163114754098361</v>
       </c>
       <c r="K57">
         <v>2.29</v>
@@ -3677,7 +3680,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3688,28 +3691,28 @@
         <v>29</v>
       </c>
       <c r="C58">
-        <v>0.7164672131147527</v>
+        <v>0.6498239504652852</v>
       </c>
       <c r="D58" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E58">
-        <v>0.9831311475409823</v>
+        <v>0.5798239504652853</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58">
-        <v>0.006043532786885248</v>
+        <v>0.006110176049534715</v>
       </c>
       <c r="H58">
-        <v>0.005216868852459018</v>
+        <v>0.006040176049534715</v>
       </c>
       <c r="I58">
-        <v>0.2666639344262296</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J58">
-        <v>1.163114754098361</v>
+        <v>1.192216615517343</v>
       </c>
       <c r="K58">
         <v>2.29</v>
@@ -3718,16 +3721,16 @@
         <v>3.38</v>
       </c>
       <c r="M58">
-        <v>1.82</v>
+        <v>2.29</v>
       </c>
       <c r="N58">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="O58">
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3735,37 +3738,37 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C59">
-        <v>0.6498239504652852</v>
+        <v>0.5205928926738919</v>
       </c>
       <c r="D59" t="s">
         <v>27</v>
       </c>
       <c r="E59">
-        <v>0.5798239504652853</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59">
-        <v>0.006110176049534715</v>
+        <v>0.006459407107326108</v>
       </c>
       <c r="H59">
-        <v>0.006040176049534715</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I59">
-        <v>-0.06999999999999984</v>
+        <v>-0.1165511301853397</v>
       </c>
       <c r="J59">
-        <v>1.192216615517343</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K59">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="L59">
-        <v>3.38</v>
+        <v>3.49</v>
       </c>
       <c r="M59">
         <v>2.29</v>
@@ -3777,18 +3780,18 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C60">
-        <v>0.5205928926738919</v>
+        <v>0.474041762488552</v>
       </c>
       <c r="D60" t="s">
         <v>27</v>
@@ -3800,22 +3803,22 @@
         <v>1</v>
       </c>
       <c r="G60">
-        <v>0.006459407107326108</v>
+        <v>0.006285958237511447</v>
       </c>
       <c r="H60">
         <v>0.006215958237511448</v>
       </c>
       <c r="I60">
-        <v>-0.1165511301853397</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J60">
         <v>1.268977396293209</v>
       </c>
       <c r="K60">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="L60">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="M60">
         <v>2.29</v>
@@ -3832,40 +3835,40 @@
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C61">
-        <v>0.474041762488552</v>
+        <v>0.3774746016246668</v>
       </c>
       <c r="D61" t="s">
         <v>27</v>
       </c>
       <c r="E61">
-        <v>0.4040417624885522</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61">
-        <v>0.006285958237511447</v>
+        <v>0.006602525398375333</v>
       </c>
       <c r="H61">
-        <v>0.006215958237511448</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I61">
-        <v>-0.06999999999999984</v>
+        <v>-0.1134930470432627</v>
       </c>
       <c r="J61">
-        <v>1.268977396293209</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K61">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="L61">
-        <v>3.38</v>
+        <v>3.49</v>
       </c>
       <c r="M61">
         <v>2.29</v>
@@ -3877,18 +3880,18 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62" spans="1:16">
       <c r="A62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C62">
-        <v>0.3774746016246668</v>
+        <v>0.333981554581404</v>
       </c>
       <c r="D62" t="s">
         <v>27</v>
@@ -3900,22 +3903,22 @@
         <v>1</v>
       </c>
       <c r="G62">
-        <v>0.006602525398375333</v>
+        <v>0.006426018445418596</v>
       </c>
       <c r="H62">
         <v>0.006356018445418596</v>
       </c>
       <c r="I62">
-        <v>-0.1134930470432627</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J62">
         <v>1.330139059134758</v>
       </c>
       <c r="K62">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="L62">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="M62">
         <v>2.29</v>
@@ -3932,40 +3935,40 @@
     </row>
     <row r="63" spans="1:16">
       <c r="A63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C63">
-        <v>0.333981554581404</v>
+        <v>0.2442505289553791</v>
       </c>
       <c r="D63" t="s">
         <v>27</v>
       </c>
       <c r="E63">
-        <v>0.2639815545814042</v>
+        <v>0.1336041501315459</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63">
-        <v>0.006426018445418596</v>
+        <v>0.006735749471044622</v>
       </c>
       <c r="H63">
-        <v>0.006356018445418596</v>
+        <v>0.006486395849868455</v>
       </c>
       <c r="I63">
-        <v>-0.06999999999999984</v>
+        <v>-0.1106463788238332</v>
       </c>
       <c r="J63">
-        <v>1.330139059134758</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K63">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="L63">
-        <v>3.38</v>
+        <v>3.49</v>
       </c>
       <c r="M63">
         <v>2.29</v>
@@ -3977,18 +3980,18 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C64">
-        <v>0.2442505289553791</v>
+        <v>0.2036041501315458</v>
       </c>
       <c r="D64" t="s">
         <v>27</v>
@@ -4000,22 +4003,22 @@
         <v>1</v>
       </c>
       <c r="G64">
-        <v>0.006735749471044622</v>
+        <v>0.006556395849868454</v>
       </c>
       <c r="H64">
         <v>0.006486395849868455</v>
       </c>
       <c r="I64">
-        <v>-0.1106463788238332</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J64">
         <v>1.387072423523342</v>
       </c>
       <c r="K64">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="L64">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="M64">
         <v>2.29</v>
@@ -4032,46 +4035,46 @@
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B65" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C65">
-        <v>0.2036041501315458</v>
+        <v>0.2977942894248136</v>
       </c>
       <c r="D65" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="E65">
-        <v>0.1336041501315459</v>
+        <v>0.5755281891875166</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
       <c r="G65">
-        <v>0.006556395849868454</v>
+        <v>0.006262205710575186</v>
       </c>
       <c r="H65">
-        <v>0.006486395849868455</v>
+        <v>0.005624471810812484</v>
       </c>
       <c r="I65">
-        <v>-0.06999999999999984</v>
+        <v>0.277733899762703</v>
       </c>
       <c r="J65">
         <v>1.387072423523342</v>
       </c>
       <c r="K65">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="L65">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="M65">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="N65">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="O65">
         <v>1</v>
@@ -4082,52 +4085,52 @@
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C66">
-        <v>0.2977942894248136</v>
+        <v>1.909256367193766</v>
       </c>
       <c r="D66" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E66">
-        <v>0.5755281891875166</v>
+        <v>2.01907486979781</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G66">
-        <v>0.006262205710575186</v>
+        <v>0.005970743632806234</v>
       </c>
       <c r="H66">
-        <v>0.005624471810812484</v>
+        <v>0.00600092513020219</v>
       </c>
       <c r="I66">
-        <v>0.277733899762703</v>
+        <v>-0.1098185026040435</v>
       </c>
       <c r="J66">
-        <v>1.387072423523342</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K66">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="L66">
-        <v>3.28</v>
+        <v>3.94</v>
       </c>
       <c r="M66">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="N66">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="O66">
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4138,28 +4141,28 @@
         <v>26</v>
       </c>
       <c r="C67">
-        <v>1.909256367193766</v>
+        <v>1.899440167721166</v>
       </c>
       <c r="D67" t="s">
         <v>28</v>
       </c>
       <c r="E67">
-        <v>2.01907486979781</v>
+        <v>2.009451144824672</v>
       </c>
       <c r="F67">
         <v>-1</v>
       </c>
       <c r="G67">
-        <v>0.005970743632806234</v>
+        <v>0.005980559832278834</v>
       </c>
       <c r="H67">
-        <v>0.00600092513020219</v>
+        <v>0.006010548855175328</v>
       </c>
       <c r="I67">
-        <v>-0.1098185026040435</v>
+        <v>-0.1100109771035065</v>
       </c>
       <c r="J67">
-        <v>0.7963700520808761</v>
+        <v>0.8002195420701311</v>
       </c>
       <c r="K67">
         <v>2.55</v>
@@ -4177,7 +4180,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4188,28 +4191,28 @@
         <v>26</v>
       </c>
       <c r="C68">
-        <v>1.899440167721166</v>
+        <v>1.886137504764086</v>
       </c>
       <c r="D68" t="s">
         <v>28</v>
       </c>
       <c r="E68">
-        <v>2.009451144824672</v>
+        <v>1.996409318396163</v>
       </c>
       <c r="F68">
         <v>-1</v>
       </c>
       <c r="G68">
-        <v>0.005980559832278834</v>
+        <v>0.005993862495235914</v>
       </c>
       <c r="H68">
-        <v>0.006010548855175328</v>
+        <v>0.006023590681603837</v>
       </c>
       <c r="I68">
-        <v>-0.1100109771035065</v>
+        <v>-0.1102718136320764</v>
       </c>
       <c r="J68">
-        <v>0.8002195420701311</v>
+        <v>0.8054362726415348</v>
       </c>
       <c r="K68">
         <v>2.55</v>
@@ -4227,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4238,28 +4241,28 @@
         <v>26</v>
       </c>
       <c r="C69">
-        <v>1.886137504764086</v>
+        <v>1.870809096426398</v>
       </c>
       <c r="D69" t="s">
         <v>28</v>
       </c>
       <c r="E69">
-        <v>1.996409318396163</v>
+        <v>1.981381467084703</v>
       </c>
       <c r="F69">
         <v>-1</v>
       </c>
       <c r="G69">
-        <v>0.005993862495235914</v>
+        <v>0.006009190903573602</v>
       </c>
       <c r="H69">
-        <v>0.006023590681603837</v>
+        <v>0.006038618532915297</v>
       </c>
       <c r="I69">
-        <v>-0.1102718136320764</v>
+        <v>-0.1105723706583053</v>
       </c>
       <c r="J69">
-        <v>0.8054362726415348</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K69">
         <v>2.55</v>
@@ -4277,7 +4280,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4288,28 +4291,28 @@
         <v>26</v>
       </c>
       <c r="C70">
-        <v>1.870809096426398</v>
+        <v>1.866530632283299</v>
       </c>
       <c r="D70" t="s">
         <v>28</v>
       </c>
       <c r="E70">
-        <v>1.981381467084703</v>
+        <v>1.977186894395391</v>
       </c>
       <c r="F70">
         <v>-1</v>
       </c>
       <c r="G70">
-        <v>0.006009190903573602</v>
+        <v>0.0060134693677167</v>
       </c>
       <c r="H70">
-        <v>0.006038618532915297</v>
+        <v>0.006042813105604609</v>
       </c>
       <c r="I70">
-        <v>-0.1105723706583053</v>
+        <v>-0.1106562621120917</v>
       </c>
       <c r="J70">
-        <v>0.8114474131661186</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K70">
         <v>2.55</v>
@@ -4327,7 +4330,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4338,28 +4341,28 @@
         <v>26</v>
       </c>
       <c r="C71">
-        <v>1.866530632283299</v>
+        <v>1.861370672015807</v>
       </c>
       <c r="D71" t="s">
         <v>28</v>
       </c>
       <c r="E71">
-        <v>1.977186894395391</v>
+        <v>1.972128109819418</v>
       </c>
       <c r="F71">
         <v>-1</v>
       </c>
       <c r="G71">
-        <v>0.0060134693677167</v>
+        <v>0.006018629327984194</v>
       </c>
       <c r="H71">
-        <v>0.006042813105604609</v>
+        <v>0.006047871890180582</v>
       </c>
       <c r="I71">
-        <v>-0.1106562621120917</v>
+        <v>-0.1107574378036111</v>
       </c>
       <c r="J71">
-        <v>0.8131252422418436</v>
+        <v>0.8151487560722326</v>
       </c>
       <c r="K71">
         <v>2.55</v>
@@ -4377,7 +4380,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4388,28 +4391,28 @@
         <v>26</v>
       </c>
       <c r="C72">
-        <v>1.861370672015807</v>
+        <v>1.851301116496863</v>
       </c>
       <c r="D72" t="s">
         <v>28</v>
       </c>
       <c r="E72">
-        <v>1.972128109819418</v>
+        <v>1.962255996565552</v>
       </c>
       <c r="F72">
         <v>-1</v>
       </c>
       <c r="G72">
-        <v>0.006018629327984194</v>
+        <v>0.006028698883503138</v>
       </c>
       <c r="H72">
-        <v>0.006047871890180582</v>
+        <v>0.006057744003434448</v>
       </c>
       <c r="I72">
-        <v>-0.1107574378036111</v>
+        <v>-0.110954880068689</v>
       </c>
       <c r="J72">
-        <v>0.8151487560722326</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K72">
         <v>2.55</v>
@@ -4427,7 +4430,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4438,28 +4441,28 @@
         <v>26</v>
       </c>
       <c r="C73">
-        <v>1.851301116496863</v>
+        <v>1.855461116431831</v>
       </c>
       <c r="D73" t="s">
         <v>28</v>
       </c>
       <c r="E73">
-        <v>1.962255996565552</v>
+        <v>1.966334427874344</v>
       </c>
       <c r="F73">
         <v>-1</v>
       </c>
       <c r="G73">
-        <v>0.006028698883503138</v>
+        <v>0.006024538883568169</v>
       </c>
       <c r="H73">
-        <v>0.006057744003434448</v>
+        <v>0.006053665572125656</v>
       </c>
       <c r="I73">
-        <v>-0.110954880068689</v>
+        <v>-0.1108733114425124</v>
       </c>
       <c r="J73">
-        <v>0.8190976013737793</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K73">
         <v>2.55</v>
@@ -4477,7 +4480,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4488,28 +4491,28 @@
         <v>26</v>
       </c>
       <c r="C74">
-        <v>1.855461116431831</v>
+        <v>1.85652914973731</v>
       </c>
       <c r="D74" t="s">
         <v>28</v>
       </c>
       <c r="E74">
-        <v>1.966334427874344</v>
+        <v>1.967381519350304</v>
       </c>
       <c r="F74">
         <v>-1</v>
       </c>
       <c r="G74">
-        <v>0.006024538883568169</v>
+        <v>0.006023470850262691</v>
       </c>
       <c r="H74">
-        <v>0.006053665572125656</v>
+        <v>0.006052618480649696</v>
       </c>
       <c r="I74">
-        <v>-0.1108733114425124</v>
+        <v>-0.1108523696129935</v>
       </c>
       <c r="J74">
-        <v>0.8174662288502623</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K74">
         <v>2.55</v>
@@ -4527,7 +4530,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4538,28 +4541,28 @@
         <v>26</v>
       </c>
       <c r="C75">
-        <v>1.85652914973731</v>
+        <v>1.854953516327912</v>
       </c>
       <c r="D75" t="s">
         <v>28</v>
       </c>
       <c r="E75">
-        <v>1.967381519350304</v>
+        <v>1.965836780713639</v>
       </c>
       <c r="F75">
         <v>-1</v>
       </c>
       <c r="G75">
-        <v>0.006023470850262691</v>
+        <v>0.006025046483672087</v>
       </c>
       <c r="H75">
-        <v>0.006052618480649696</v>
+        <v>0.00605416321928636</v>
       </c>
       <c r="I75">
-        <v>-0.1108523696129935</v>
+        <v>-0.1108832643857269</v>
       </c>
       <c r="J75">
-        <v>0.8170473922598784</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K75">
         <v>2.55</v>
@@ -4577,7 +4580,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4588,28 +4591,28 @@
         <v>26</v>
       </c>
       <c r="C76">
-        <v>1.854953516327912</v>
+        <v>1.853898035926949</v>
       </c>
       <c r="D76" t="s">
         <v>28</v>
       </c>
       <c r="E76">
-        <v>1.965836780713639</v>
+        <v>1.964801996006813</v>
       </c>
       <c r="F76">
         <v>-1</v>
       </c>
       <c r="G76">
-        <v>0.006025046483672087</v>
+        <v>0.00602610196407305</v>
       </c>
       <c r="H76">
-        <v>0.00605416321928636</v>
+        <v>0.006055198003993187</v>
       </c>
       <c r="I76">
-        <v>-0.1108832643857269</v>
+        <v>-0.1109039600798636</v>
       </c>
       <c r="J76">
-        <v>0.8176652877145442</v>
+        <v>0.8180792015972748</v>
       </c>
       <c r="K76">
         <v>2.55</v>
@@ -4627,7 +4630,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4638,28 +4641,28 @@
         <v>26</v>
       </c>
       <c r="C77">
-        <v>1.853898035926949</v>
+        <v>1.851157777698763</v>
       </c>
       <c r="D77" t="s">
         <v>28</v>
       </c>
       <c r="E77">
-        <v>1.964801996006813</v>
+        <v>1.96211546833212</v>
       </c>
       <c r="F77">
         <v>-1</v>
       </c>
       <c r="G77">
-        <v>0.00602610196407305</v>
+        <v>0.006028842222301236</v>
       </c>
       <c r="H77">
-        <v>0.006055198003993187</v>
+        <v>0.006057884531667879</v>
       </c>
       <c r="I77">
-        <v>-0.1109039600798636</v>
+        <v>-0.1109576906333571</v>
       </c>
       <c r="J77">
-        <v>0.8180792015972748</v>
+        <v>0.8191538126671517</v>
       </c>
       <c r="K77">
         <v>2.55</v>
@@ -4677,7 +4680,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4688,28 +4691,28 @@
         <v>26</v>
       </c>
       <c r="C78">
-        <v>1.851157777698763</v>
+        <v>1.858566205293179</v>
       </c>
       <c r="D78" t="s">
         <v>28</v>
       </c>
       <c r="E78">
-        <v>1.96211546833212</v>
+        <v>1.969378632640371</v>
       </c>
       <c r="F78">
         <v>-1</v>
       </c>
       <c r="G78">
-        <v>0.006028842222301236</v>
+        <v>0.006021433794706822</v>
       </c>
       <c r="H78">
-        <v>0.006057884531667879</v>
+        <v>0.006050621367359629</v>
       </c>
       <c r="I78">
-        <v>-0.1109576906333571</v>
+        <v>-0.1108124273471924</v>
       </c>
       <c r="J78">
-        <v>0.8191538126671517</v>
+        <v>0.8162485469438515</v>
       </c>
       <c r="K78">
         <v>2.55</v>
@@ -4727,7 +4730,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4738,28 +4741,28 @@
         <v>26</v>
       </c>
       <c r="C79">
-        <v>1.858566205293179</v>
+        <v>1.868405823240289</v>
       </c>
       <c r="D79" t="s">
         <v>28</v>
       </c>
       <c r="E79">
-        <v>1.969378632640371</v>
+        <v>1.979025316902244</v>
       </c>
       <c r="F79">
         <v>-1</v>
       </c>
       <c r="G79">
-        <v>0.006021433794706822</v>
+        <v>0.006011594176759711</v>
       </c>
       <c r="H79">
-        <v>0.006050621367359629</v>
+        <v>0.006040974683097756</v>
       </c>
       <c r="I79">
-        <v>-0.1108124273471924</v>
+        <v>-0.1106194936619547</v>
       </c>
       <c r="J79">
-        <v>0.8162485469438515</v>
+        <v>0.8123898732391025</v>
       </c>
       <c r="K79">
         <v>2.55</v>
@@ -4777,7 +4780,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -4788,28 +4791,28 @@
         <v>26</v>
       </c>
       <c r="C80">
-        <v>1.868405823240289</v>
+        <v>1.873099451459633</v>
       </c>
       <c r="D80" t="s">
         <v>28</v>
       </c>
       <c r="E80">
-        <v>1.979025316902244</v>
+        <v>1.983626913195719</v>
       </c>
       <c r="F80">
         <v>-1</v>
       </c>
       <c r="G80">
-        <v>0.006011594176759711</v>
+        <v>0.006006900548540367</v>
       </c>
       <c r="H80">
-        <v>0.006040974683097756</v>
+        <v>0.00603637308680428</v>
       </c>
       <c r="I80">
-        <v>-0.1106194936619547</v>
+        <v>-0.1105274617360856</v>
       </c>
       <c r="J80">
-        <v>0.8123898732391025</v>
+        <v>0.8105492347217125</v>
       </c>
       <c r="K80">
         <v>2.55</v>
@@ -4827,7 +4830,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -4838,28 +4841,28 @@
         <v>26</v>
       </c>
       <c r="C81">
-        <v>1.873099451459633</v>
+        <v>1.880315678845928</v>
       </c>
       <c r="D81" t="s">
         <v>28</v>
       </c>
       <c r="E81">
-        <v>1.983626913195719</v>
+        <v>1.99070164592738</v>
       </c>
       <c r="F81">
         <v>-1</v>
       </c>
       <c r="G81">
-        <v>0.006006900548540367</v>
+        <v>0.005999684321154073</v>
       </c>
       <c r="H81">
-        <v>0.00603637308680428</v>
+        <v>0.006029298354072619</v>
       </c>
       <c r="I81">
-        <v>-0.1105274617360856</v>
+        <v>-0.1103859670814522</v>
       </c>
       <c r="J81">
-        <v>0.8105492347217125</v>
+        <v>0.8077193416290479</v>
       </c>
       <c r="K81">
         <v>2.55</v>
@@ -4877,7 +4880,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -4888,28 +4891,28 @@
         <v>26</v>
       </c>
       <c r="C82">
-        <v>1.880315678845928</v>
+        <v>1.885229059666124</v>
       </c>
       <c r="D82" t="s">
         <v>28</v>
       </c>
       <c r="E82">
-        <v>1.99070164592738</v>
+        <v>1.995518685947181</v>
       </c>
       <c r="F82">
         <v>-1</v>
       </c>
       <c r="G82">
-        <v>0.005999684321154073</v>
+        <v>0.005994770940333876</v>
       </c>
       <c r="H82">
-        <v>0.006029298354072619</v>
+        <v>0.006024481314052819</v>
       </c>
       <c r="I82">
-        <v>-0.1103859670814522</v>
+        <v>-0.1102896262810562</v>
       </c>
       <c r="J82">
-        <v>0.8077193416290479</v>
+        <v>0.8057925256211278</v>
       </c>
       <c r="K82">
         <v>2.55</v>
@@ -4927,7 +4930,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -4938,28 +4941,28 @@
         <v>26</v>
       </c>
       <c r="C83">
-        <v>1.885229059666124</v>
+        <v>1.891592550259521</v>
       </c>
       <c r="D83" t="s">
         <v>28</v>
       </c>
       <c r="E83">
-        <v>1.995518685947181</v>
+        <v>2.001757402215216</v>
       </c>
       <c r="F83">
         <v>-1</v>
       </c>
       <c r="G83">
-        <v>0.005994770940333876</v>
+        <v>0.00598840744974048</v>
       </c>
       <c r="H83">
-        <v>0.006024481314052819</v>
+        <v>0.006018242597784784</v>
       </c>
       <c r="I83">
-        <v>-0.1102896262810562</v>
+        <v>-0.1101648519556955</v>
       </c>
       <c r="J83">
-        <v>0.8057925256211278</v>
+        <v>0.8032970391139135</v>
       </c>
       <c r="K83">
         <v>2.55</v>
@@ -4977,7 +4980,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -4988,28 +4991,28 @@
         <v>26</v>
       </c>
       <c r="C84">
-        <v>1.891592550259521</v>
+        <v>1.898226451425238</v>
       </c>
       <c r="D84" t="s">
         <v>28</v>
       </c>
       <c r="E84">
-        <v>2.001757402215216</v>
+        <v>2.008261226887488</v>
       </c>
       <c r="F84">
         <v>-1</v>
       </c>
       <c r="G84">
-        <v>0.00598840744974048</v>
+        <v>0.005981773548574762</v>
       </c>
       <c r="H84">
-        <v>0.006018242597784784</v>
+        <v>0.006011738773112512</v>
       </c>
       <c r="I84">
-        <v>-0.1101648519556955</v>
+        <v>-0.1100347754622497</v>
       </c>
       <c r="J84">
-        <v>0.8032970391139135</v>
+        <v>0.8006955092450049</v>
       </c>
       <c r="K84">
         <v>2.55</v>
@@ -5027,7 +5030,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5038,28 +5041,28 @@
         <v>26</v>
       </c>
       <c r="C85">
-        <v>1.898226451425238</v>
+        <v>1.903475998145109</v>
       </c>
       <c r="D85" t="s">
         <v>28</v>
       </c>
       <c r="E85">
-        <v>2.008261226887488</v>
+        <v>2.013407841318734</v>
       </c>
       <c r="F85">
         <v>-1</v>
       </c>
       <c r="G85">
-        <v>0.005981773548574762</v>
+        <v>0.005976524001854891</v>
       </c>
       <c r="H85">
-        <v>0.006011738773112512</v>
+        <v>0.006006592158681266</v>
       </c>
       <c r="I85">
-        <v>-0.1100347754622497</v>
+        <v>-0.1099318431736251</v>
       </c>
       <c r="J85">
-        <v>0.8006955092450049</v>
+        <v>0.7986368634725065</v>
       </c>
       <c r="K85">
         <v>2.55</v>
@@ -5077,7 +5080,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5088,28 +5091,28 @@
         <v>26</v>
       </c>
       <c r="C86">
-        <v>1.903475998145109</v>
+        <v>1.915111220550284</v>
       </c>
       <c r="D86" t="s">
         <v>28</v>
       </c>
       <c r="E86">
-        <v>2.013407841318734</v>
+        <v>2.024814922108121</v>
       </c>
       <c r="F86">
         <v>-1</v>
       </c>
       <c r="G86">
-        <v>0.005976524001854891</v>
+        <v>0.005964888779449715</v>
       </c>
       <c r="H86">
-        <v>0.006006592158681266</v>
+        <v>0.005995185077891879</v>
       </c>
       <c r="I86">
-        <v>-0.1099318431736251</v>
+        <v>-0.1097037015578373</v>
       </c>
       <c r="J86">
-        <v>0.7986368634725065</v>
+        <v>0.7940740311567515</v>
       </c>
       <c r="K86">
         <v>2.55</v>
@@ -5127,7 +5130,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5138,28 +5141,28 @@
         <v>26</v>
       </c>
       <c r="C87">
-        <v>1.915111220550284</v>
+        <v>1.927566816677033</v>
       </c>
       <c r="D87" t="s">
         <v>28</v>
       </c>
       <c r="E87">
-        <v>2.024814922108121</v>
+        <v>2.037026290859836</v>
       </c>
       <c r="F87">
         <v>-1</v>
       </c>
       <c r="G87">
-        <v>0.005964888779449715</v>
+        <v>0.005952433183322967</v>
       </c>
       <c r="H87">
-        <v>0.005995185077891879</v>
+        <v>0.005982973709140164</v>
       </c>
       <c r="I87">
-        <v>-0.1097037015578373</v>
+        <v>-0.109459474182803</v>
       </c>
       <c r="J87">
-        <v>0.7940740311567515</v>
+        <v>0.7891894836560657</v>
       </c>
       <c r="K87">
         <v>2.55</v>
@@ -5177,7 +5180,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5188,28 +5191,28 @@
         <v>26</v>
       </c>
       <c r="C88">
-        <v>1.927566816677033</v>
+        <v>1.931008249436597</v>
       </c>
       <c r="D88" t="s">
         <v>28</v>
       </c>
       <c r="E88">
-        <v>2.037026290859836</v>
+        <v>2.040400244545683</v>
       </c>
       <c r="F88">
         <v>-1</v>
       </c>
       <c r="G88">
-        <v>0.005952433183322967</v>
+        <v>0.005948991750563403</v>
       </c>
       <c r="H88">
-        <v>0.005982973709140164</v>
+        <v>0.005979599755454317</v>
       </c>
       <c r="I88">
-        <v>-0.109459474182803</v>
+        <v>-0.1093919951090863</v>
       </c>
       <c r="J88">
-        <v>0.7891894836560657</v>
+        <v>0.7878399021817268</v>
       </c>
       <c r="K88">
         <v>2.55</v>
@@ -5227,7 +5230,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5238,28 +5241,28 @@
         <v>26</v>
       </c>
       <c r="C89">
-        <v>1.931008249436597</v>
+        <v>1.931290596802969</v>
       </c>
       <c r="D89" t="s">
         <v>28</v>
       </c>
       <c r="E89">
-        <v>2.040400244545683</v>
+        <v>2.040677055689185</v>
       </c>
       <c r="F89">
         <v>-1</v>
       </c>
       <c r="G89">
-        <v>0.005948991750563403</v>
+        <v>0.00594870940319703</v>
       </c>
       <c r="H89">
-        <v>0.005979599755454317</v>
+        <v>0.005979322944310814</v>
       </c>
       <c r="I89">
-        <v>-0.1093919951090863</v>
+        <v>-0.1093864588862159</v>
       </c>
       <c r="J89">
-        <v>0.7878399021817268</v>
+        <v>0.7877291777243258</v>
       </c>
       <c r="K89">
         <v>2.55</v>
@@ -5277,7 +5280,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5288,28 +5291,28 @@
         <v>26</v>
       </c>
       <c r="C90">
-        <v>1.931290596802969</v>
+        <v>1.932400003731856</v>
       </c>
       <c r="D90" t="s">
         <v>28</v>
       </c>
       <c r="E90">
-        <v>2.040677055689185</v>
+        <v>2.041764709541035</v>
       </c>
       <c r="F90">
         <v>-1</v>
       </c>
       <c r="G90">
-        <v>0.00594870940319703</v>
+        <v>0.005947599996268144</v>
       </c>
       <c r="H90">
-        <v>0.005979322944310814</v>
+        <v>0.005978235290458964</v>
       </c>
       <c r="I90">
-        <v>-0.1093864588862159</v>
+        <v>-0.1093647058091789</v>
       </c>
       <c r="J90">
-        <v>0.7877291777243258</v>
+        <v>0.7872941161835857</v>
       </c>
       <c r="K90">
         <v>2.55</v>
@@ -5327,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5338,28 +5341,28 @@
         <v>26</v>
       </c>
       <c r="C91">
-        <v>1.932400003731856</v>
+        <v>1.928867601835406</v>
       </c>
       <c r="D91" t="s">
         <v>28</v>
       </c>
       <c r="E91">
-        <v>2.041764709541035</v>
+        <v>2.038301570426869</v>
       </c>
       <c r="F91">
         <v>-1</v>
       </c>
       <c r="G91">
-        <v>0.005947599996268144</v>
+        <v>0.005951132398164594</v>
       </c>
       <c r="H91">
-        <v>0.005978235290458964</v>
+        <v>0.005981698429573131</v>
       </c>
       <c r="I91">
-        <v>-0.1093647058091789</v>
+        <v>-0.1094339685914623</v>
       </c>
       <c r="J91">
-        <v>0.7872941161835857</v>
+        <v>0.7886793718292525</v>
       </c>
       <c r="K91">
         <v>2.55</v>
@@ -5377,7 +5380,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5388,28 +5391,28 @@
         <v>26</v>
       </c>
       <c r="C92">
-        <v>1.928867601835406</v>
+        <v>1.925635063875757</v>
       </c>
       <c r="D92" t="s">
         <v>28</v>
       </c>
       <c r="E92">
-        <v>2.038301570426869</v>
+        <v>2.035132415564467</v>
       </c>
       <c r="F92">
         <v>-1</v>
       </c>
       <c r="G92">
-        <v>0.005951132398164594</v>
+        <v>0.005954364936124243</v>
       </c>
       <c r="H92">
-        <v>0.005981698429573131</v>
+        <v>0.005984867584435533</v>
       </c>
       <c r="I92">
-        <v>-0.1094339685914623</v>
+        <v>-0.1094973516887103</v>
       </c>
       <c r="J92">
-        <v>0.7886793718292525</v>
+        <v>0.7899470337742129</v>
       </c>
       <c r="K92">
         <v>2.55</v>
@@ -5427,7 +5430,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5438,28 +5441,28 @@
         <v>26</v>
       </c>
       <c r="C93">
-        <v>1.925635063875757</v>
+        <v>1.924421367530698</v>
       </c>
       <c r="D93" t="s">
         <v>28</v>
       </c>
       <c r="E93">
-        <v>2.035132415564467</v>
+        <v>2.033942517186959</v>
       </c>
       <c r="F93">
         <v>-1</v>
       </c>
       <c r="G93">
-        <v>0.005954364936124243</v>
+        <v>0.005955578632469301</v>
       </c>
       <c r="H93">
-        <v>0.005984867584435533</v>
+        <v>0.005986057482813041</v>
       </c>
       <c r="I93">
-        <v>-0.1094973516887103</v>
+        <v>-0.1095211496562603</v>
       </c>
       <c r="J93">
-        <v>0.7899470337742129</v>
+        <v>0.7904229931252164</v>
       </c>
       <c r="K93">
         <v>2.55</v>
@@ -5477,7 +5480,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5488,28 +5491,28 @@
         <v>26</v>
       </c>
       <c r="C94">
-        <v>1.924421367530698</v>
+        <v>1.922633944537091</v>
       </c>
       <c r="D94" t="s">
         <v>28</v>
       </c>
       <c r="E94">
-        <v>2.033942517186959</v>
+        <v>2.03219014170303</v>
       </c>
       <c r="F94">
         <v>-1</v>
       </c>
       <c r="G94">
-        <v>0.005955578632469301</v>
+        <v>0.00595736605546291</v>
       </c>
       <c r="H94">
-        <v>0.005986057482813041</v>
+        <v>0.00598780985829697</v>
       </c>
       <c r="I94">
-        <v>-0.1095211496562603</v>
+        <v>-0.1095561971659391</v>
       </c>
       <c r="J94">
-        <v>0.7904229931252164</v>
+        <v>0.791123943318788</v>
       </c>
       <c r="K94">
         <v>2.55</v>
@@ -5527,7 +5530,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5538,28 +5541,28 @@
         <v>26</v>
       </c>
       <c r="C95">
-        <v>1.922633944537091</v>
+        <v>1.921462641095741</v>
       </c>
       <c r="D95" t="s">
         <v>28</v>
       </c>
       <c r="E95">
-        <v>2.03219014170303</v>
+        <v>2.031041804995824</v>
       </c>
       <c r="F95">
         <v>-1</v>
       </c>
       <c r="G95">
-        <v>0.00595736605546291</v>
+        <v>0.005958537358904259</v>
       </c>
       <c r="H95">
-        <v>0.00598780985829697</v>
+        <v>0.005988958195004175</v>
       </c>
       <c r="I95">
-        <v>-0.1095561971659391</v>
+        <v>-0.1095791639000829</v>
       </c>
       <c r="J95">
-        <v>0.791123943318788</v>
+        <v>0.7915832780016702</v>
       </c>
       <c r="K95">
         <v>2.55</v>
@@ -5577,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5588,28 +5591,28 @@
         <v>26</v>
       </c>
       <c r="C96">
-        <v>1.921462641095741</v>
+        <v>1.922670198036319</v>
       </c>
       <c r="D96" t="s">
         <v>28</v>
       </c>
       <c r="E96">
-        <v>2.031041804995824</v>
+        <v>2.032225684349332</v>
       </c>
       <c r="F96">
         <v>-1</v>
       </c>
       <c r="G96">
-        <v>0.005958537358904259</v>
+        <v>0.005957329801963681</v>
       </c>
       <c r="H96">
-        <v>0.005988958195004175</v>
+        <v>0.005987774315650668</v>
       </c>
       <c r="I96">
-        <v>-0.1095791639000829</v>
+        <v>-0.1095554863130133</v>
       </c>
       <c r="J96">
-        <v>0.7915832780016702</v>
+        <v>0.7911097262602672</v>
       </c>
       <c r="K96">
         <v>2.55</v>
@@ -5627,7 +5630,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5638,28 +5641,28 @@
         <v>26</v>
       </c>
       <c r="C97">
-        <v>1.922670198036319</v>
+        <v>1.924302790568959</v>
       </c>
       <c r="D97" t="s">
         <v>28</v>
       </c>
       <c r="E97">
-        <v>2.032225684349332</v>
+        <v>2.033826265263685</v>
       </c>
       <c r="F97">
         <v>-1</v>
       </c>
       <c r="G97">
-        <v>0.005957329801963681</v>
+        <v>0.00595569720943104</v>
       </c>
       <c r="H97">
-        <v>0.005987774315650668</v>
+        <v>0.005986173734736314</v>
       </c>
       <c r="I97">
-        <v>-0.1095554863130133</v>
+        <v>-0.109523474694726</v>
       </c>
       <c r="J97">
-        <v>0.7911097262602672</v>
+        <v>0.7904694938945258</v>
       </c>
       <c r="K97">
         <v>2.55</v>
@@ -5677,7 +5680,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5688,28 +5691,28 @@
         <v>26</v>
       </c>
       <c r="C98">
-        <v>1.924302790568959</v>
+        <v>1.92765643109575</v>
       </c>
       <c r="D98" t="s">
         <v>28</v>
       </c>
       <c r="E98">
-        <v>2.033826265263685</v>
+        <v>2.037114148133088</v>
       </c>
       <c r="F98">
         <v>-1</v>
       </c>
       <c r="G98">
-        <v>0.00595569720943104</v>
+        <v>0.005952343568904249</v>
       </c>
       <c r="H98">
-        <v>0.005986173734736314</v>
+        <v>0.005982885851866911</v>
       </c>
       <c r="I98">
-        <v>-0.109523474694726</v>
+        <v>-0.1094577170373379</v>
       </c>
       <c r="J98">
-        <v>0.7904694938945258</v>
+        <v>0.7891543407467646</v>
       </c>
       <c r="K98">
         <v>2.55</v>
@@ -5727,7 +5730,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5738,28 +5741,28 @@
         <v>26</v>
       </c>
       <c r="C99">
-        <v>1.92765643109575</v>
+        <v>1.931644858116821</v>
       </c>
       <c r="D99" t="s">
         <v>28</v>
       </c>
       <c r="E99">
-        <v>2.037114148133088</v>
+        <v>2.041024370702765</v>
       </c>
       <c r="F99">
         <v>-1</v>
       </c>
       <c r="G99">
-        <v>0.005952343568904249</v>
+        <v>0.005948355141883179</v>
       </c>
       <c r="H99">
-        <v>0.005982885851866911</v>
+        <v>0.005978975629297235</v>
       </c>
       <c r="I99">
-        <v>-0.1094577170373379</v>
+        <v>-0.1093795125859445</v>
       </c>
       <c r="J99">
-        <v>0.7891543407467646</v>
+        <v>0.7875902517188939</v>
       </c>
       <c r="K99">
         <v>2.55</v>
@@ -5777,7 +5780,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -5788,28 +5791,28 @@
         <v>26</v>
       </c>
       <c r="C100">
-        <v>1.931644858116821</v>
+        <v>1.933649431471673</v>
       </c>
       <c r="D100" t="s">
         <v>28</v>
       </c>
       <c r="E100">
-        <v>2.041024370702765</v>
+        <v>2.042989638697718</v>
       </c>
       <c r="F100">
         <v>-1</v>
       </c>
       <c r="G100">
-        <v>0.005948355141883179</v>
+        <v>0.005946350568528327</v>
       </c>
       <c r="H100">
-        <v>0.005978975629297235</v>
+        <v>0.005977010361302281</v>
       </c>
       <c r="I100">
-        <v>-0.1093795125859445</v>
+        <v>-0.1093402072260452</v>
       </c>
       <c r="J100">
-        <v>0.7875902517188939</v>
+        <v>0.7868041445209126</v>
       </c>
       <c r="K100">
         <v>2.55</v>
@@ -5827,7 +5830,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -5838,28 +5841,28 @@
         <v>26</v>
       </c>
       <c r="C101">
-        <v>1.933649431471673</v>
+        <v>1.937204548237283</v>
       </c>
       <c r="D101" t="s">
         <v>28</v>
       </c>
       <c r="E101">
-        <v>2.042989638697718</v>
+        <v>2.046475047291454</v>
       </c>
       <c r="F101">
         <v>-1</v>
       </c>
       <c r="G101">
-        <v>0.005946350568528327</v>
+        <v>0.005942795451762716</v>
       </c>
       <c r="H101">
-        <v>0.005977010361302281</v>
+        <v>0.005973524952708546</v>
       </c>
       <c r="I101">
-        <v>-0.1093402072260452</v>
+        <v>-0.1092704990541709</v>
       </c>
       <c r="J101">
-        <v>0.7868041445209126</v>
+        <v>0.7854099810834182</v>
       </c>
       <c r="K101">
         <v>2.55</v>
@@ -5877,7 +5880,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -5888,28 +5891,28 @@
         <v>26</v>
       </c>
       <c r="C102">
-        <v>1.937204548237283</v>
+        <v>1.941976947705745</v>
       </c>
       <c r="D102" t="s">
         <v>28</v>
       </c>
       <c r="E102">
-        <v>2.046475047291454</v>
+        <v>2.05115387029975</v>
       </c>
       <c r="F102">
         <v>-1</v>
       </c>
       <c r="G102">
-        <v>0.005942795451762716</v>
+        <v>0.005938023052294255</v>
       </c>
       <c r="H102">
-        <v>0.005973524952708546</v>
+        <v>0.00596884612970025</v>
       </c>
       <c r="I102">
-        <v>-0.1092704990541709</v>
+        <v>-0.1091769225940049</v>
       </c>
       <c r="J102">
-        <v>0.7854099810834182</v>
+        <v>0.7835384518800999</v>
       </c>
       <c r="K102">
         <v>2.55</v>
@@ -5927,7 +5930,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -5938,28 +5941,28 @@
         <v>26</v>
       </c>
       <c r="C103">
-        <v>1.941976947705745</v>
+        <v>1.943259802359731</v>
       </c>
       <c r="D103" t="s">
         <v>28</v>
       </c>
       <c r="E103">
-        <v>2.05115387029975</v>
+        <v>2.052411570940913</v>
       </c>
       <c r="F103">
         <v>-1</v>
       </c>
       <c r="G103">
-        <v>0.005938023052294255</v>
+        <v>0.005936740197640269</v>
       </c>
       <c r="H103">
-        <v>0.00596884612970025</v>
+        <v>0.005967588429059087</v>
       </c>
       <c r="I103">
-        <v>-0.1091769225940049</v>
+        <v>-0.1091517685811818</v>
       </c>
       <c r="J103">
-        <v>0.7835384518800999</v>
+        <v>0.783035371623635</v>
       </c>
       <c r="K103">
         <v>2.55</v>
@@ -5977,7 +5980,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -5988,28 +5991,28 @@
         <v>26</v>
       </c>
       <c r="C104">
-        <v>1.943259802359731</v>
+        <v>1.944946776406004</v>
       </c>
       <c r="D104" t="s">
         <v>28</v>
       </c>
       <c r="E104">
-        <v>2.052411570940913</v>
+        <v>2.054065467064709</v>
       </c>
       <c r="F104">
         <v>-1</v>
       </c>
       <c r="G104">
-        <v>0.005936740197640269</v>
+        <v>0.005935053223593996</v>
       </c>
       <c r="H104">
-        <v>0.005967588429059087</v>
+        <v>0.005965934532935291</v>
       </c>
       <c r="I104">
-        <v>-0.1091517685811818</v>
+        <v>-0.1091186906587052</v>
       </c>
       <c r="J104">
-        <v>0.783035371623635</v>
+        <v>0.7823738131741161</v>
       </c>
       <c r="K104">
         <v>2.55</v>
@@ -6027,7 +6030,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6038,28 +6041,28 @@
         <v>26</v>
       </c>
       <c r="C105">
-        <v>1.944946776406004</v>
+        <v>1.948679250285769</v>
       </c>
       <c r="D105" t="s">
         <v>28</v>
       </c>
       <c r="E105">
-        <v>2.054065467064709</v>
+        <v>2.057724755182126</v>
       </c>
       <c r="F105">
         <v>-1</v>
       </c>
       <c r="G105">
-        <v>0.005935053223593996</v>
+        <v>0.005931320749714232</v>
       </c>
       <c r="H105">
-        <v>0.005965934532935291</v>
+        <v>0.005962275244817874</v>
       </c>
       <c r="I105">
-        <v>-0.1091186906587052</v>
+        <v>-0.1090455048963574</v>
       </c>
       <c r="J105">
-        <v>0.7823738131741161</v>
+        <v>0.7809100979271496</v>
       </c>
       <c r="K105">
         <v>2.55</v>
@@ -6077,7 +6080,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6088,28 +6091,28 @@
         <v>26</v>
       </c>
       <c r="C106">
-        <v>1.948679250285769</v>
+        <v>1.950614227390016</v>
       </c>
       <c r="D106" t="s">
         <v>28</v>
       </c>
       <c r="E106">
-        <v>2.057724755182126</v>
+        <v>2.059621791558839</v>
       </c>
       <c r="F106">
         <v>-1</v>
       </c>
       <c r="G106">
-        <v>0.005931320749714232</v>
+        <v>0.005929385772609984</v>
       </c>
       <c r="H106">
-        <v>0.005962275244817874</v>
+        <v>0.005960378208441161</v>
       </c>
       <c r="I106">
-        <v>-0.1090455048963574</v>
+        <v>-0.1090075641688231</v>
       </c>
       <c r="J106">
-        <v>0.7809100979271496</v>
+        <v>0.7801512833764644</v>
       </c>
       <c r="K106">
         <v>2.55</v>
@@ -6127,7 +6130,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6138,28 +6141,28 @@
         <v>26</v>
       </c>
       <c r="C107">
-        <v>1.950614227390016</v>
+        <v>1.951624445196418</v>
       </c>
       <c r="D107" t="s">
         <v>28</v>
       </c>
       <c r="E107">
-        <v>2.059621791558839</v>
+        <v>2.060612201172958</v>
       </c>
       <c r="F107">
         <v>-1</v>
       </c>
       <c r="G107">
-        <v>0.005929385772609984</v>
+        <v>0.005928375554803582</v>
       </c>
       <c r="H107">
-        <v>0.005960378208441161</v>
+        <v>0.005959387798827042</v>
       </c>
       <c r="I107">
-        <v>-0.1090075641688231</v>
+        <v>-0.1089877559765402</v>
       </c>
       <c r="J107">
-        <v>0.7801512833764644</v>
+        <v>0.7797551195308166</v>
       </c>
       <c r="K107">
         <v>2.55</v>
@@ -6177,7 +6180,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6188,28 +6191,28 @@
         <v>26</v>
       </c>
       <c r="C108">
-        <v>1.951624445196418</v>
+        <v>1.953198644707818</v>
       </c>
       <c r="D108" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E108">
-        <v>2.060612201172958</v>
+        <v>1.893443446257855</v>
       </c>
       <c r="F108">
         <v>-1</v>
       </c>
       <c r="G108">
-        <v>0.005928375554803582</v>
+        <v>0.005926801355292182</v>
       </c>
       <c r="H108">
-        <v>0.005959387798827042</v>
+        <v>0.005586556553742145</v>
       </c>
       <c r="I108">
-        <v>-0.1089877559765402</v>
+        <v>0.05975519844996358</v>
       </c>
       <c r="J108">
-        <v>0.7797551195308166</v>
+        <v>0.7791377863890909</v>
       </c>
       <c r="K108">
         <v>2.55</v>
@@ -6218,16 +6221,16 @@
         <v>3.94</v>
       </c>
       <c r="M108">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="N108">
-        <v>4.01</v>
+        <v>3.74</v>
       </c>
       <c r="O108">
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6238,28 +6241,28 @@
         <v>26</v>
       </c>
       <c r="C109">
-        <v>1.953198644707818</v>
+        <v>1.956263001176151</v>
       </c>
       <c r="D109" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E109">
-        <v>2.062155534027272</v>
+        <v>1.896291495210775</v>
       </c>
       <c r="F109">
         <v>-1</v>
       </c>
       <c r="G109">
-        <v>0.005926801355292182</v>
+        <v>0.00592373699882385</v>
       </c>
       <c r="H109">
-        <v>0.005957844465972727</v>
+        <v>0.005583708504789225</v>
       </c>
       <c r="I109">
-        <v>-0.1089568893194541</v>
+        <v>0.05997150596537537</v>
       </c>
       <c r="J109">
-        <v>0.7791377863890909</v>
+        <v>0.777936077970137</v>
       </c>
       <c r="K109">
         <v>2.55</v>
@@ -6268,16 +6271,16 @@
         <v>3.94</v>
       </c>
       <c r="M109">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="N109">
-        <v>4.01</v>
+        <v>3.74</v>
       </c>
       <c r="O109">
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6288,28 +6291,28 @@
         <v>26</v>
       </c>
       <c r="C110">
-        <v>1.956263001176151</v>
+        <v>1.957833849297126</v>
       </c>
       <c r="D110" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E110">
-        <v>2.065159805074657</v>
+        <v>1.897751459934976</v>
       </c>
       <c r="F110">
         <v>-1</v>
       </c>
       <c r="G110">
-        <v>0.00592373699882385</v>
+        <v>0.005922166150702874</v>
       </c>
       <c r="H110">
-        <v>0.005954840194925343</v>
+        <v>0.005582248540065025</v>
       </c>
       <c r="I110">
-        <v>-0.1088968038985063</v>
+        <v>0.06008238936215005</v>
       </c>
       <c r="J110">
-        <v>0.777936077970137</v>
+        <v>0.7773200590991663</v>
       </c>
       <c r="K110">
         <v>2.55</v>
@@ -6318,16 +6321,16 @@
         <v>3.94</v>
       </c>
       <c r="M110">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="N110">
-        <v>4.01</v>
+        <v>3.74</v>
       </c>
       <c r="O110">
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6338,28 +6341,28 @@
         <v>26</v>
       </c>
       <c r="C111">
-        <v>1.957833849297126</v>
+        <v>1.960719712115154</v>
       </c>
       <c r="D111" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E111">
-        <v>2.066699852252084</v>
+        <v>1.900433614789378</v>
       </c>
       <c r="F111">
         <v>-1</v>
       </c>
       <c r="G111">
-        <v>0.005922166150702874</v>
+        <v>0.005919280287884846</v>
       </c>
       <c r="H111">
-        <v>0.005953300147747916</v>
+        <v>0.005579566385210622</v>
       </c>
       <c r="I111">
-        <v>-0.108866002954958</v>
+        <v>0.0602860973257755</v>
       </c>
       <c r="J111">
-        <v>0.7773200590991663</v>
+        <v>0.7761883481901358</v>
       </c>
       <c r="K111">
         <v>2.55</v>
@@ -6368,16 +6371,16 @@
         <v>3.94</v>
       </c>
       <c r="M111">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="N111">
-        <v>4.01</v>
+        <v>3.74</v>
       </c>
       <c r="O111">
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6388,28 +6391,28 @@
         <v>26</v>
       </c>
       <c r="C112">
-        <v>1.960719712115154</v>
+        <v>1.964089726245929</v>
       </c>
       <c r="D112" t="s">
         <v>45</v>
       </c>
       <c r="E112">
-        <v>1.867004915680786</v>
+        <v>1.903565745569746</v>
       </c>
       <c r="F112">
         <v>-1</v>
       </c>
       <c r="G112">
-        <v>0.005919280287884846</v>
+        <v>0.005915910273754071</v>
       </c>
       <c r="H112">
-        <v>0.005452995084319214</v>
+        <v>0.005576434254430255</v>
       </c>
       <c r="I112">
-        <v>0.09371479643436742</v>
+        <v>0.06052398067618325</v>
       </c>
       <c r="J112">
-        <v>0.7761883481901358</v>
+        <v>0.7748667740212044</v>
       </c>
       <c r="K112">
         <v>2.55</v>
@@ -6418,16 +6421,16 @@
         <v>3.94</v>
       </c>
       <c r="M112">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N112">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O112">
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6435,49 +6438,49 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C113">
-        <v>1.964089726245929</v>
+        <v>2.076110072462908</v>
       </c>
       <c r="D113" t="s">
         <v>45</v>
       </c>
       <c r="E113">
-        <v>1.870057752011018</v>
+        <v>1.906672348694837</v>
       </c>
       <c r="F113">
         <v>-1</v>
       </c>
       <c r="G113">
-        <v>0.005915910273754071</v>
+        <v>0.005943889927537092</v>
       </c>
       <c r="H113">
-        <v>0.005449942247988983</v>
+        <v>0.005573327651305164</v>
       </c>
       <c r="I113">
-        <v>0.09403197423491094</v>
+        <v>0.1694377237680709</v>
       </c>
       <c r="J113">
-        <v>0.7748667740212044</v>
+        <v>0.7735559710148369</v>
       </c>
       <c r="K113">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="L113">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="M113">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N113">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O113">
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6485,49 +6488,49 @@
         <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C114">
-        <v>1.967432273912166</v>
+        <v>2.078101340295269</v>
       </c>
       <c r="D114" t="s">
         <v>45</v>
       </c>
       <c r="E114">
-        <v>1.873085706955727</v>
+        <v>1.908560070599915</v>
       </c>
       <c r="F114">
         <v>-1</v>
       </c>
       <c r="G114">
-        <v>0.005912567726087834</v>
+        <v>0.00594189865970473</v>
       </c>
       <c r="H114">
-        <v>0.005446914293044273</v>
+        <v>0.005571439929400086</v>
       </c>
       <c r="I114">
-        <v>0.09434656695643917</v>
+        <v>0.1695412696953538</v>
       </c>
       <c r="J114">
-        <v>0.7735559710148369</v>
+        <v>0.7727594638818923</v>
       </c>
       <c r="K114">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="L114">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="M114">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N114">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O114">
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6535,49 +6538,49 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C115">
-        <v>1.969463367101175</v>
+        <v>2.078941598729263</v>
       </c>
       <c r="D115" t="s">
         <v>45</v>
       </c>
       <c r="E115">
-        <v>1.874925638432829</v>
+        <v>1.909356635595342</v>
       </c>
       <c r="F115">
         <v>-1</v>
       </c>
       <c r="G115">
-        <v>0.005910536632898825</v>
+        <v>0.005941058401270736</v>
       </c>
       <c r="H115">
-        <v>0.005445074361567171</v>
+        <v>0.005570643364404658</v>
       </c>
       <c r="I115">
-        <v>0.09453772866834598</v>
+        <v>0.1695849631339212</v>
       </c>
       <c r="J115">
-        <v>0.7727594638818923</v>
+        <v>0.7724233605082945</v>
       </c>
       <c r="K115">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="L115">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="M115">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N115">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O115">
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6585,49 +6588,49 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C116">
-        <v>1.970320430703849</v>
+        <v>2.079346337166745</v>
       </c>
       <c r="D116" t="s">
         <v>45</v>
       </c>
       <c r="E116">
-        <v>1.87570203722584</v>
+        <v>1.909740327634075</v>
       </c>
       <c r="F116">
         <v>-1</v>
       </c>
       <c r="G116">
-        <v>0.00590967956929615</v>
+        <v>0.005940653662833254</v>
       </c>
       <c r="H116">
-        <v>0.005444297962774161</v>
+        <v>0.005570259672365926</v>
       </c>
       <c r="I116">
-        <v>0.09461839347800938</v>
+        <v>0.1696060095326706</v>
       </c>
       <c r="J116">
-        <v>0.7724233605082945</v>
+        <v>0.7722614651333018</v>
       </c>
       <c r="K116">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="L116">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="M116">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N116">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O116">
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6638,28 +6641,28 @@
         <v>28</v>
       </c>
       <c r="C117">
-        <v>2.079346337166745</v>
+        <v>2.078211043729365</v>
       </c>
       <c r="D117" t="s">
         <v>45</v>
       </c>
       <c r="E117">
-        <v>1.876076015542073</v>
+        <v>1.908664069455438</v>
       </c>
       <c r="F117">
         <v>-1</v>
       </c>
       <c r="G117">
-        <v>0.005940653662833254</v>
+        <v>0.005941788956270636</v>
       </c>
       <c r="H117">
-        <v>0.005443923984457927</v>
+        <v>0.005571335930544562</v>
       </c>
       <c r="I117">
-        <v>0.2032703216246725</v>
+        <v>0.1695469742739264</v>
       </c>
       <c r="J117">
-        <v>0.7722614651333018</v>
+        <v>0.772715582508254</v>
       </c>
       <c r="K117">
         <v>2.5</v>
@@ -6668,16 +6671,16 @@
         <v>4.01</v>
       </c>
       <c r="M117">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N117">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O117">
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6688,28 +6691,28 @@
         <v>28</v>
       </c>
       <c r="C118">
-        <v>2.078211043729365</v>
+        <v>2.075878111180319</v>
       </c>
       <c r="D118" t="s">
         <v>45</v>
       </c>
       <c r="E118">
-        <v>1.875027004405933</v>
+        <v>1.906452449398942</v>
       </c>
       <c r="F118">
         <v>-1</v>
       </c>
       <c r="G118">
-        <v>0.005941788956270636</v>
+        <v>0.005944121888819681</v>
       </c>
       <c r="H118">
-        <v>0.005444972995594067</v>
+        <v>0.005573547550601058</v>
       </c>
       <c r="I118">
-        <v>0.2031840393234312</v>
+        <v>0.1694256617813763</v>
       </c>
       <c r="J118">
-        <v>0.772715582508254</v>
+        <v>0.7736487555278725</v>
       </c>
       <c r="K118">
         <v>2.5</v>
@@ -6718,16 +6721,16 @@
         <v>4.01</v>
       </c>
       <c r="M118">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N118">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O118">
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6738,28 +6741,28 @@
         <v>28</v>
       </c>
       <c r="C119">
-        <v>2.075878111180319</v>
+        <v>2.0734572921576</v>
       </c>
       <c r="D119" t="s">
         <v>45</v>
       </c>
       <c r="E119">
-        <v>1.872871374730615</v>
+        <v>1.904157512965405</v>
       </c>
       <c r="F119">
         <v>-1</v>
       </c>
       <c r="G119">
-        <v>0.005944121888819681</v>
+        <v>0.005946542707842399</v>
       </c>
       <c r="H119">
-        <v>0.005447128625269386</v>
+        <v>0.005575842487034596</v>
       </c>
       <c r="I119">
-        <v>0.2030067364497039</v>
+        <v>0.1692997791921951</v>
       </c>
       <c r="J119">
-        <v>0.7736487555278725</v>
+        <v>0.7746170831369599</v>
       </c>
       <c r="K119">
         <v>2.5</v>
@@ -6768,16 +6771,16 @@
         <v>4.01</v>
       </c>
       <c r="M119">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N119">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O119">
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -6788,28 +6791,28 @@
         <v>28</v>
       </c>
       <c r="C120">
-        <v>2.0734572921576</v>
+        <v>2.069260822060034</v>
       </c>
       <c r="D120" t="s">
         <v>45</v>
       </c>
       <c r="E120">
-        <v>1.870634537953623</v>
+        <v>1.900179259312913</v>
       </c>
       <c r="F120">
         <v>-1</v>
       </c>
       <c r="G120">
-        <v>0.005946542707842399</v>
+        <v>0.005950739177939966</v>
       </c>
       <c r="H120">
-        <v>0.005449365462046377</v>
+        <v>0.005579820740687088</v>
       </c>
       <c r="I120">
-        <v>0.2028227542039773</v>
+        <v>0.1690815627471216</v>
       </c>
       <c r="J120">
-        <v>0.7746170831369599</v>
+        <v>0.7762956711759863</v>
       </c>
       <c r="K120">
         <v>2.5</v>
@@ -6818,16 +6821,16 @@
         <v>4.01</v>
       </c>
       <c r="M120">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N120">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O120">
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -6838,28 +6841,28 @@
         <v>28</v>
       </c>
       <c r="C121">
-        <v>2.069260822060034</v>
+        <v>2.064960635460216</v>
       </c>
       <c r="D121" t="s">
         <v>45</v>
       </c>
       <c r="E121">
-        <v>1.866756999583472</v>
+        <v>1.896102682416285</v>
       </c>
       <c r="F121">
         <v>-1</v>
       </c>
       <c r="G121">
-        <v>0.005950739177939966</v>
+        <v>0.005955039364539783</v>
       </c>
       <c r="H121">
-        <v>0.005453243000416529</v>
+        <v>0.005583897317583715</v>
       </c>
       <c r="I121">
-        <v>0.2025038224765623</v>
+        <v>0.1688579530439307</v>
       </c>
       <c r="J121">
-        <v>0.7762956711759863</v>
+        <v>0.7780157458159134</v>
       </c>
       <c r="K121">
         <v>2.5</v>
@@ -6868,16 +6871,16 @@
         <v>4.01</v>
       </c>
       <c r="M121">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N121">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O121">
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -6888,28 +6891,28 @@
         <v>28</v>
       </c>
       <c r="C122">
-        <v>2.064960635460216</v>
+        <v>2.062649927724336</v>
       </c>
       <c r="D122" t="s">
         <v>45</v>
       </c>
       <c r="E122">
-        <v>1.86278362716524</v>
+        <v>1.893912131482671</v>
       </c>
       <c r="F122">
         <v>-1</v>
       </c>
       <c r="G122">
-        <v>0.005955039364539783</v>
+        <v>0.005957350072275664</v>
       </c>
       <c r="H122">
-        <v>0.00545721637283476</v>
+        <v>0.00558608786851733</v>
       </c>
       <c r="I122">
-        <v>0.2021770082949759</v>
+        <v>0.1687377962416654</v>
       </c>
       <c r="J122">
-        <v>0.7780157458159134</v>
+        <v>0.7789400289102656</v>
       </c>
       <c r="K122">
         <v>2.5</v>
@@ -6918,16 +6921,16 @@
         <v>4.01</v>
       </c>
       <c r="M122">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N122">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O122">
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -6938,28 +6941,28 @@
         <v>28</v>
       </c>
       <c r="C123">
-        <v>2.062649927724336</v>
+        <v>2.060340111638369</v>
       </c>
       <c r="D123" t="s">
         <v>45</v>
       </c>
       <c r="E123">
-        <v>1.860648533217287</v>
+        <v>1.891722425833174</v>
       </c>
       <c r="F123">
         <v>-1</v>
       </c>
       <c r="G123">
-        <v>0.005957350072275664</v>
+        <v>0.00595965988836163</v>
       </c>
       <c r="H123">
-        <v>0.005459351466782713</v>
+        <v>0.005588277574166826</v>
       </c>
       <c r="I123">
-        <v>0.2020013945070493</v>
+        <v>0.1686176858051949</v>
       </c>
       <c r="J123">
-        <v>0.7789400289102656</v>
+        <v>0.7798639553446522</v>
       </c>
       <c r="K123">
         <v>2.5</v>
@@ -6968,16 +6971,16 @@
         <v>4.01</v>
       </c>
       <c r="M123">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N123">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O123">
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -6988,28 +6991,28 @@
         <v>28</v>
       </c>
       <c r="C124">
-        <v>2.060340111638369</v>
+        <v>2.058086897870289</v>
       </c>
       <c r="D124" t="s">
         <v>45</v>
       </c>
       <c r="E124">
-        <v>1.858514263153853</v>
+        <v>1.889586379181034</v>
       </c>
       <c r="F124">
         <v>-1</v>
       </c>
       <c r="G124">
-        <v>0.00595965988836163</v>
+        <v>0.00596191310212971</v>
       </c>
       <c r="H124">
-        <v>0.005461485736846147</v>
+        <v>0.005590413620818966</v>
       </c>
       <c r="I124">
-        <v>0.2018258484845159</v>
+        <v>0.1685005186892548</v>
       </c>
       <c r="J124">
-        <v>0.7798639553446522</v>
+        <v>0.7807652408518843</v>
       </c>
       <c r="K124">
         <v>2.5</v>
@@ -7018,16 +7021,16 @@
         <v>4.01</v>
       </c>
       <c r="M124">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N124">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O124">
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7038,28 +7041,28 @@
         <v>28</v>
       </c>
       <c r="C125">
-        <v>2.058086897870289</v>
+        <v>2.054455475290532</v>
       </c>
       <c r="D125" t="s">
         <v>45</v>
       </c>
       <c r="E125">
-        <v>1.856432293632148</v>
+        <v>1.886143790575425</v>
       </c>
       <c r="F125">
         <v>-1</v>
       </c>
       <c r="G125">
-        <v>0.00596191310212971</v>
+        <v>0.005965544524709467</v>
       </c>
       <c r="H125">
-        <v>0.005463567706367853</v>
+        <v>0.005593856209424576</v>
       </c>
       <c r="I125">
-        <v>0.2016546042381415</v>
+        <v>0.1683116847151074</v>
       </c>
       <c r="J125">
-        <v>0.7807652408518843</v>
+        <v>0.7822178098837871</v>
       </c>
       <c r="K125">
         <v>2.5</v>
@@ -7068,16 +7071,16 @@
         <v>4.01</v>
       </c>
       <c r="M125">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N125">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O125">
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7088,28 +7091,28 @@
         <v>28</v>
       </c>
       <c r="C126">
-        <v>2.054455475290532</v>
+        <v>2.051743125354167</v>
       </c>
       <c r="D126" t="s">
         <v>45</v>
       </c>
       <c r="E126">
-        <v>1.853076859168452</v>
+        <v>1.88357248283575</v>
       </c>
       <c r="F126">
         <v>-1</v>
       </c>
       <c r="G126">
-        <v>0.005965544524709467</v>
+        <v>0.005968256874645833</v>
       </c>
       <c r="H126">
-        <v>0.005466923140831549</v>
+        <v>0.005596427517164251</v>
       </c>
       <c r="I126">
-        <v>0.2013786161220803</v>
+        <v>0.1681706425184164</v>
       </c>
       <c r="J126">
-        <v>0.7822178098837871</v>
+        <v>0.7833027498583333</v>
       </c>
       <c r="K126">
         <v>2.5</v>
@@ -7118,16 +7121,16 @@
         <v>4.01</v>
       </c>
       <c r="M126">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N126">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O126">
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7138,28 +7141,28 @@
         <v>28</v>
       </c>
       <c r="C127">
-        <v>2.051743125354167</v>
+        <v>2.049665109064402</v>
       </c>
       <c r="D127" t="s">
         <v>45</v>
       </c>
       <c r="E127">
-        <v>1.85057064782725</v>
+        <v>1.881602523393054</v>
       </c>
       <c r="F127">
         <v>-1</v>
       </c>
       <c r="G127">
-        <v>0.005968256874645833</v>
+        <v>0.005970334890935598</v>
       </c>
       <c r="H127">
-        <v>0.00546942935217275</v>
+        <v>0.005598397476606946</v>
       </c>
       <c r="I127">
-        <v>0.2011724775269164</v>
+        <v>0.1680625856713482</v>
       </c>
       <c r="J127">
-        <v>0.7833027498583333</v>
+        <v>0.784133956374239</v>
       </c>
       <c r="K127">
         <v>2.5</v>
@@ -7168,16 +7171,16 @@
         <v>4.01</v>
       </c>
       <c r="M127">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N127">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O127">
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7188,28 +7191,28 @@
         <v>28</v>
       </c>
       <c r="C128">
-        <v>2.049665109064402</v>
+        <v>2.045876432573801</v>
       </c>
       <c r="D128" t="s">
         <v>45</v>
       </c>
       <c r="E128">
-        <v>1.848650560775508</v>
+        <v>1.878010858079963</v>
       </c>
       <c r="F128">
         <v>-1</v>
       </c>
       <c r="G128">
-        <v>0.005970334890935598</v>
+        <v>0.005974123567426199</v>
       </c>
       <c r="H128">
-        <v>0.005471349439224492</v>
+        <v>0.005601989141920037</v>
       </c>
       <c r="I128">
-        <v>0.2010145482888941</v>
+        <v>0.1678655744938371</v>
       </c>
       <c r="J128">
-        <v>0.784133956374239</v>
+        <v>0.7856494269704796</v>
       </c>
       <c r="K128">
         <v>2.5</v>
@@ -7218,16 +7221,16 @@
         <v>4.01</v>
       </c>
       <c r="M128">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N128">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O128">
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7238,28 +7241,28 @@
         <v>28</v>
       </c>
       <c r="C129">
-        <v>2.045876432573801</v>
+        <v>2.040113864426065</v>
       </c>
       <c r="D129" t="s">
         <v>45</v>
       </c>
       <c r="E129">
-        <v>1.845149823698192</v>
+        <v>1.87254794347591</v>
       </c>
       <c r="F129">
         <v>-1</v>
       </c>
       <c r="G129">
-        <v>0.005974123567426199</v>
+        <v>0.005979886135573935</v>
       </c>
       <c r="H129">
-        <v>0.005474850176301808</v>
+        <v>0.005607452056524091</v>
       </c>
       <c r="I129">
-        <v>0.2007266088756083</v>
+        <v>0.1675659209501552</v>
       </c>
       <c r="J129">
-        <v>0.7856494269704796</v>
+        <v>0.7879544542295741</v>
       </c>
       <c r="K129">
         <v>2.5</v>
@@ -7268,16 +7271,16 @@
         <v>4.01</v>
       </c>
       <c r="M129">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N129">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O129">
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7288,28 +7291,28 @@
         <v>28</v>
       </c>
       <c r="C130">
-        <v>2.040113864426065</v>
+        <v>2.03513888559835</v>
       </c>
       <c r="D130" t="s">
         <v>45</v>
       </c>
       <c r="E130">
-        <v>1.839825210729684</v>
+        <v>1.867831663547236</v>
       </c>
       <c r="F130">
         <v>-1</v>
       </c>
       <c r="G130">
-        <v>0.005979886135573935</v>
+        <v>0.00598486111440165</v>
       </c>
       <c r="H130">
-        <v>0.005480174789270317</v>
+        <v>0.005612168336452765</v>
       </c>
       <c r="I130">
-        <v>0.2002886536963808</v>
+        <v>0.1673072220511138</v>
       </c>
       <c r="J130">
-        <v>0.7879544542295741</v>
+        <v>0.78994444576066</v>
       </c>
       <c r="K130">
         <v>2.5</v>
@@ -7318,16 +7321,16 @@
         <v>4.01</v>
       </c>
       <c r="M130">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N130">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O130">
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7338,28 +7341,28 @@
         <v>28</v>
       </c>
       <c r="C131">
-        <v>2.03513888559835</v>
+        <v>2.027039654230626</v>
       </c>
       <c r="D131" t="s">
         <v>45</v>
       </c>
       <c r="E131">
-        <v>1.835228330292875</v>
+        <v>1.860153592210634</v>
       </c>
       <c r="F131">
         <v>-1</v>
       </c>
       <c r="G131">
-        <v>0.00598486111440165</v>
+        <v>0.005992960345769374</v>
       </c>
       <c r="H131">
-        <v>0.005484771669707125</v>
+        <v>0.005619846407789366</v>
       </c>
       <c r="I131">
-        <v>0.1999105553054743</v>
+        <v>0.1668860620199919</v>
       </c>
       <c r="J131">
-        <v>0.78994444576066</v>
+        <v>0.7931841383077493</v>
       </c>
       <c r="K131">
         <v>2.5</v>
@@ -7368,16 +7371,16 @@
         <v>4.01</v>
       </c>
       <c r="M131">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="N131">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="O131">
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7388,28 +7391,28 @@
         <v>28</v>
       </c>
       <c r="C132">
-        <v>2.027039654230626</v>
+        <v>2.014982057940606</v>
       </c>
       <c r="D132" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E132">
-        <v>1.827744640509099</v>
+        <v>1.820543636841833</v>
       </c>
       <c r="F132">
         <v>-1</v>
       </c>
       <c r="G132">
-        <v>0.005992960345769374</v>
+        <v>0.006005017942059394</v>
       </c>
       <c r="H132">
-        <v>0.005492255359490901</v>
+        <v>0.005459456363158167</v>
       </c>
       <c r="I132">
-        <v>0.199295013721527</v>
+        <v>0.1944384210987726</v>
       </c>
       <c r="J132">
-        <v>0.7931841383077493</v>
+        <v>0.7980071768237574</v>
       </c>
       <c r="K132">
         <v>2.5</v>
@@ -7418,16 +7421,116 @@
         <v>4.01</v>
       </c>
       <c r="M132">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="N132">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="O132">
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>152</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16">
+      <c r="A133" s="1">
+        <v>0</v>
+      </c>
+      <c r="B133" t="s">
+        <v>28</v>
+      </c>
+      <c r="C133">
+        <v>2.006007199100977</v>
+      </c>
+      <c r="D133" t="s">
+        <v>47</v>
+      </c>
+      <c r="E133">
+        <v>1.812358565580092</v>
+      </c>
+      <c r="F133">
+        <v>-1</v>
+      </c>
+      <c r="G133">
+        <v>0.006013992800899023</v>
+      </c>
+      <c r="H133">
+        <v>0.005467641434419909</v>
+      </c>
+      <c r="I133">
+        <v>0.1936486335208853</v>
+      </c>
+      <c r="J133">
+        <v>0.8015971203596091</v>
+      </c>
+      <c r="K133">
+        <v>2.5</v>
+      </c>
+      <c r="L133">
+        <v>4.01</v>
+      </c>
+      <c r="M133">
+        <v>2.28</v>
+      </c>
+      <c r="N133">
+        <v>3.64</v>
+      </c>
+      <c r="O133">
+        <v>1</v>
+      </c>
+      <c r="P133" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16">
+      <c r="A134" s="1">
+        <v>0</v>
+      </c>
+      <c r="B134" t="s">
+        <v>28</v>
+      </c>
+      <c r="C134">
+        <v>1.989657960367918</v>
+      </c>
+      <c r="D134" t="s">
+        <v>48</v>
+      </c>
+      <c r="E134">
+        <v>1.848261741440824</v>
+      </c>
+      <c r="F134">
+        <v>-1</v>
+      </c>
+      <c r="G134">
+        <v>0.006030342039632082</v>
+      </c>
+      <c r="H134">
+        <v>0.005371738258559176</v>
+      </c>
+      <c r="I134">
+        <v>0.1413962189270934</v>
+      </c>
+      <c r="J134">
+        <v>0.8081368158528327</v>
+      </c>
+      <c r="K134">
+        <v>2.5</v>
+      </c>
+      <c r="L134">
+        <v>4.01</v>
+      </c>
+      <c r="M134">
+        <v>2.18</v>
+      </c>
+      <c r="N134">
+        <v>3.61</v>
+      </c>
+      <c r="O134">
+        <v>1</v>
+      </c>
+      <c r="P134" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01618-601618.xlsx
+++ b/s60_signal/position-01618-601618.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="148">
   <si>
     <t>trade_time</t>
   </si>
@@ -88,13 +88,22 @@
     <t>2021-07-22</t>
   </si>
   <si>
+    <t>2021-07-29</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
+    <t>2021-01-15</t>
+  </si>
+  <si>
     <t>2021-01-13</t>
   </si>
   <si>
-    <t>2021-01-15</t>
-  </si>
-  <si>
-    <t>2021-07-23</t>
+    <t>2021-08-03</t>
   </si>
   <si>
     <t>2021-02-26</t>
@@ -148,21 +157,15 @@
     <t>2021-01-26</t>
   </si>
   <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
     <t>2021-03-12</t>
   </si>
   <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
     <t>2021-03-09</t>
   </si>
   <si>
-    <t>2021-07-28</t>
-  </si>
-  <si>
-    <t>2021-07-27</t>
-  </si>
-  <si>
     <t>2016-12-23</t>
   </si>
   <si>
@@ -217,6 +220,18 @@
     <t>2020-11-26</t>
   </si>
   <si>
+    <t>2020-12-02</t>
+  </si>
+  <si>
+    <t>2020-12-11</t>
+  </si>
+  <si>
+    <t>2020-12-14</t>
+  </si>
+  <si>
+    <t>2020-12-15</t>
+  </si>
+  <si>
     <t>2020-12-16</t>
   </si>
   <si>
@@ -443,39 +458,6 @@
   </si>
   <si>
     <t>2021-06-28</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>2021-07-05</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>2021-07-07</t>
-  </si>
-  <si>
-    <t>2021-07-08</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>2021-07-12</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
   </si>
 </sst>
 </file>
@@ -833,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P134"/>
+  <dimension ref="A1:P186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -894,7 +876,7 @@
         <v>2.241636620202809</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E2">
         <v>2.083673377356266</v>
@@ -930,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -944,7 +926,7 @@
         <v>2.291018963074085</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3">
         <v>2.748932188801797</v>
@@ -980,7 +962,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -994,7 +976,7 @@
         <v>0.1640886968569069</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E4">
         <v>0.8087275807852619</v>
@@ -1030,7 +1012,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1044,7 +1026,7 @@
         <v>0.1567937244930127</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E5">
         <v>0.8087275807852619</v>
@@ -1080,7 +1062,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1094,7 +1076,7 @@
         <v>0.06008199184724816</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E6">
         <v>0.7118353409391309</v>
@@ -1130,7 +1112,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1144,7 +1126,7 @@
         <v>0.05109309920632388</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>0.7118353409391309</v>
@@ -1180,7 +1162,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1194,7 +1176,7 @@
         <v>-0.0569506423664734</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E8">
         <v>0.6028081963621785</v>
@@ -1230,7 +1212,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1244,7 +1226,7 @@
         <v>-0.06784560396853312</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E9">
         <v>0.6028081963621785</v>
@@ -1280,7 +1262,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1294,7 +1276,7 @@
         <v>-0.1396452470657845</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E10">
         <v>0.5257702258605397</v>
@@ -1330,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1344,7 +1326,7 @@
         <v>-0.1518870263339567</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>0.5257702258605397</v>
@@ -1380,7 +1362,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1394,7 +1376,7 @@
         <v>-0.2479133877986754</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E12">
         <v>0.424908049151723</v>
@@ -1430,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1444,7 +1426,7 @@
         <v>-0.2619184918344848</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E13">
         <v>0.424908049151723</v>
@@ -1480,7 +1462,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1494,7 +1476,7 @@
         <v>-0.3399965939203824</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E14">
         <v>0.3391236942630966</v>
@@ -1530,7 +1512,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1544,7 +1526,7 @@
         <v>0.9756011105228968</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E15">
         <v>0.8107654111102569</v>
@@ -1580,7 +1562,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1594,7 +1576,7 @@
         <v>1.301145679016073</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E16">
         <v>1.173416666670367</v>
@@ -1630,7 +1612,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1644,7 +1626,7 @@
         <v>1.296277364845049</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E17">
         <v>1.230890933009092</v>
@@ -1680,7 +1662,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1694,7 +1676,7 @@
         <v>0.4435035626339812</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E18">
         <v>0.9439906537348826</v>
@@ -1730,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1744,7 +1726,7 @@
         <v>0.4423533289773536</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E19">
         <v>0.9439906537348826</v>
@@ -1780,7 +1762,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1794,7 +1776,7 @@
         <v>1.507350128118183</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E20">
         <v>1.202821457299868</v>
@@ -1830,7 +1812,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -1844,7 +1826,7 @@
         <v>1.54125697476493</v>
       </c>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E21">
         <v>1.238224194239853</v>
@@ -1880,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -1894,7 +1876,7 @@
         <v>1.573438797246031</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E22">
         <v>1.271825803006885</v>
@@ -1930,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -1944,7 +1926,7 @@
         <v>1.613400857289038</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E23">
         <v>1.313550895110613</v>
@@ -1980,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -1994,7 +1976,7 @@
         <v>1.593400857289038</v>
       </c>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E24">
         <v>1.363275825771058</v>
@@ -2030,7 +2012,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2044,7 +2026,7 @@
         <v>1.645344720184119</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E25">
         <v>1.346904046074595</v>
@@ -2080,7 +2062,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2094,7 +2076,7 @@
         <v>1.625344720184119</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E26">
         <v>1.394045281942056</v>
@@ -2130,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2144,7 +2126,7 @@
         <v>1.68180858461344</v>
       </c>
       <c r="D27" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E27">
         <v>1.384976610405209</v>
@@ -2180,7 +2162,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2194,7 +2176,7 @@
         <v>1.66180858461344</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E28">
         <v>1.429168563120298</v>
@@ -2230,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2244,7 +2226,7 @@
         <v>1.710614904938503</v>
       </c>
       <c r="D29" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E29">
         <v>1.415053797803437</v>
@@ -2280,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2294,7 +2276,7 @@
         <v>1.690614904938503</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E30">
         <v>1.456915827551058</v>
@@ -2330,7 +2312,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2380,7 +2362,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2391,96 +2373,96 @@
         <v>24</v>
       </c>
       <c r="C32">
-        <v>2.284943445032334</v>
+        <v>3.072361243685425</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E32">
-        <v>2.033577409367039</v>
+        <v>3.272185680805519</v>
       </c>
       <c r="F32">
         <v>-1</v>
       </c>
       <c r="G32">
-        <v>0.004235056554967666</v>
+        <v>0.004247638756314576</v>
       </c>
       <c r="H32">
-        <v>0.004066422590632961</v>
+        <v>0.004467814319194481</v>
       </c>
       <c r="I32">
-        <v>0.2513660356652947</v>
+        <v>-0.1998244371200939</v>
       </c>
       <c r="J32">
-        <v>0.5909433666470703</v>
+        <v>0.2543890719976515</v>
       </c>
       <c r="K32">
-        <v>1.65</v>
+        <v>2.31</v>
       </c>
       <c r="L32">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="M32">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="N32">
-        <v>3.05</v>
+        <v>3.87</v>
       </c>
       <c r="O32">
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B33" t="s">
         <v>25</v>
       </c>
       <c r="C33">
-        <v>2.294943445032334</v>
+        <v>2.638017457305502</v>
       </c>
       <c r="D33" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E33">
-        <v>2.033577409367039</v>
+        <v>2.77731688804554</v>
       </c>
       <c r="F33">
         <v>-1</v>
       </c>
       <c r="G33">
-        <v>0.004245056554967665</v>
+        <v>0.004841982542694498</v>
       </c>
       <c r="H33">
-        <v>0.004066422590632961</v>
+        <v>0.00496268311195446</v>
       </c>
       <c r="I33">
-        <v>0.2613660356652949</v>
+        <v>-0.1392994307400377</v>
       </c>
       <c r="J33">
-        <v>0.5909433666470703</v>
+        <v>0.4649715370018978</v>
       </c>
       <c r="K33">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="L33">
-        <v>3.27</v>
+        <v>3.74</v>
       </c>
       <c r="M33">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="N33">
-        <v>3.05</v>
+        <v>3.87</v>
       </c>
       <c r="O33">
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2488,49 +2470,49 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C34">
-        <v>2.206392009113778</v>
+        <v>2.536354813853479</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E34">
-        <v>1.939163015063914</v>
+        <v>2.676512157196488</v>
       </c>
       <c r="F34">
         <v>-1</v>
       </c>
       <c r="G34">
-        <v>0.004313607990886223</v>
+        <v>0.004943645186146522</v>
       </c>
       <c r="H34">
-        <v>0.004020836984936086</v>
+        <v>0.005063487842803513</v>
       </c>
       <c r="I34">
-        <v>0.2672289940498638</v>
+        <v>-0.1401573433430086</v>
       </c>
       <c r="J34">
-        <v>0.6385502975068013</v>
+        <v>0.5078671671504308</v>
       </c>
       <c r="K34">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="L34">
-        <v>3.26</v>
+        <v>3.74</v>
       </c>
       <c r="M34">
-        <v>1.63</v>
+        <v>2.35</v>
       </c>
       <c r="N34">
-        <v>2.98</v>
+        <v>3.87</v>
       </c>
       <c r="O34">
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2538,49 +2520,49 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C35">
-        <v>2.122703049542399</v>
+        <v>2.551891062104373</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E35">
-        <v>1.856488467123704</v>
+        <v>2.649108884416052</v>
       </c>
       <c r="F35">
         <v>-1</v>
       </c>
       <c r="G35">
-        <v>0.004397296950457601</v>
+        <v>0.005328108937895627</v>
       </c>
       <c r="H35">
-        <v>0.004103511532876296</v>
+        <v>0.005370891115583948</v>
       </c>
       <c r="I35">
-        <v>0.2662145824186952</v>
+        <v>-0.09721782231167886</v>
       </c>
       <c r="J35">
-        <v>0.6892708790652124</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K35">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="L35">
-        <v>3.26</v>
+        <v>3.94</v>
       </c>
       <c r="M35">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="N35">
-        <v>2.98</v>
+        <v>4.01</v>
       </c>
       <c r="O35">
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2588,49 +2570,49 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C36">
-        <v>2.182359258383708</v>
+        <v>2.449875222426417</v>
       </c>
       <c r="D36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E36">
-        <v>2.286822802336969</v>
+        <v>2.590762351351088</v>
       </c>
       <c r="F36">
         <v>-1</v>
       </c>
       <c r="G36">
-        <v>0.005697640741616292</v>
+        <v>0.005030124777573583</v>
       </c>
       <c r="H36">
-        <v>0.005733177197663031</v>
+        <v>0.005149237648648912</v>
       </c>
       <c r="I36">
-        <v>-0.1044635439532606</v>
+        <v>-0.1408871289246711</v>
       </c>
       <c r="J36">
-        <v>0.6892708790652124</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K36">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="L36">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
       <c r="M36">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="N36">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="O36">
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2638,49 +2620,49 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C37">
-        <v>2.037699170124481</v>
+        <v>2.433094415049971</v>
       </c>
       <c r="D37" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E37">
-        <v>1.732146473029046</v>
+        <v>2.532641583382324</v>
       </c>
       <c r="F37">
         <v>-1</v>
       </c>
       <c r="G37">
-        <v>0.004482300829875518</v>
+        <v>0.005446905584950029</v>
       </c>
       <c r="H37">
-        <v>0.004087853526970955</v>
+        <v>0.005487358416617676</v>
       </c>
       <c r="I37">
-        <v>0.3055526970954354</v>
+        <v>-0.09954716833235322</v>
       </c>
       <c r="J37">
-        <v>0.7407883817427386</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K37">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="L37">
-        <v>3.26</v>
+        <v>3.94</v>
       </c>
       <c r="M37">
-        <v>1.59</v>
+        <v>2.5</v>
       </c>
       <c r="N37">
-        <v>2.91</v>
+        <v>4.01</v>
       </c>
       <c r="O37">
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2688,49 +2670,49 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C38">
-        <v>2.050989626556016</v>
+        <v>2.339464221046444</v>
       </c>
       <c r="D38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E38">
-        <v>2.158029045643153</v>
+        <v>2.481283088379385</v>
       </c>
       <c r="F38">
         <v>-1</v>
       </c>
       <c r="G38">
-        <v>0.005829010373443984</v>
+        <v>0.005140535778953557</v>
       </c>
       <c r="H38">
-        <v>0.005861970954356846</v>
+        <v>0.005258716911620615</v>
       </c>
       <c r="I38">
-        <v>-0.1070394190871369</v>
+        <v>-0.1418188673329412</v>
       </c>
       <c r="J38">
-        <v>0.7407883817427386</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K38">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="L38">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
       <c r="M38">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="N38">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="O38">
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2738,49 +2720,49 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C39">
-        <v>1.939614977812812</v>
+        <v>2.216392009113778</v>
       </c>
       <c r="D39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E39">
-        <v>1.637628978619619</v>
+        <v>1.951693488288302</v>
       </c>
       <c r="F39">
         <v>-1</v>
       </c>
       <c r="G39">
-        <v>0.004580385022187188</v>
+        <v>0.004323607990886222</v>
       </c>
       <c r="H39">
-        <v>0.004182371021380382</v>
+        <v>0.004148306511711698</v>
       </c>
       <c r="I39">
-        <v>0.301985999193193</v>
+        <v>0.2646985208254764</v>
       </c>
       <c r="J39">
-        <v>0.8002333467801142</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K39">
         <v>1.65</v>
       </c>
       <c r="L39">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="M39">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="N39">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="O39">
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -2791,28 +2773,28 @@
         <v>26</v>
       </c>
       <c r="C40">
-        <v>1.899404965710709</v>
+        <v>2.311696741357657</v>
       </c>
       <c r="D40" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E40">
-        <v>2.009416633049714</v>
+        <v>2.413624256232997</v>
       </c>
       <c r="F40">
         <v>-1</v>
       </c>
       <c r="G40">
-        <v>0.005980595034289291</v>
+        <v>0.005568303258642344</v>
       </c>
       <c r="H40">
-        <v>0.006010583366950286</v>
+        <v>0.005606375743767004</v>
       </c>
       <c r="I40">
-        <v>-0.1100116673390055</v>
+        <v>-0.10192751487534</v>
       </c>
       <c r="J40">
-        <v>0.8002333467801142</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K40">
         <v>2.55</v>
@@ -2830,201 +2812,201 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C41">
-        <v>1.364830842322013</v>
+        <v>2.226635794908881</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E41">
-        <v>1.598575134626953</v>
+        <v>2.369406800859017</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G41">
-        <v>0.005255169157677987</v>
+        <v>0.005253364205091119</v>
       </c>
       <c r="H41">
-        <v>0.004741424865373047</v>
+        <v>0.005370593199140983</v>
       </c>
       <c r="I41">
-        <v>0.2337442923049406</v>
+        <v>-0.1427710059501361</v>
       </c>
       <c r="J41">
-        <v>0.8494188461475927</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K41">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="L41">
-        <v>3.31</v>
+        <v>3.74</v>
       </c>
       <c r="M41">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="N41">
-        <v>3.17</v>
+        <v>3.87</v>
       </c>
       <c r="O41">
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C42">
-        <v>1.773981942323639</v>
+        <v>2.122703049542399</v>
       </c>
       <c r="D42" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E42">
-        <v>1.886452884631018</v>
+        <v>1.856488467123704</v>
       </c>
       <c r="F42">
         <v>-1</v>
       </c>
       <c r="G42">
-        <v>0.006106018057676361</v>
+        <v>0.004397296950457601</v>
       </c>
       <c r="H42">
-        <v>0.006133547115368982</v>
+        <v>0.004103511532876296</v>
       </c>
       <c r="I42">
-        <v>-0.1124709423073793</v>
+        <v>0.2662145824186952</v>
       </c>
       <c r="J42">
-        <v>0.8494188461475927</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K42">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="L42">
-        <v>3.94</v>
+        <v>3.26</v>
       </c>
       <c r="M42">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="N42">
-        <v>4.01</v>
+        <v>2.98</v>
       </c>
       <c r="O42">
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C43">
-        <v>1.253223538131198</v>
+        <v>2.182359258383708</v>
       </c>
       <c r="D43" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E43">
-        <v>1.508412028621273</v>
+        <v>2.286822802336969</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G43">
-        <v>0.005366776461868803</v>
+        <v>0.005697640741616292</v>
       </c>
       <c r="H43">
-        <v>0.004831587971378727</v>
+        <v>0.005733177197663031</v>
       </c>
       <c r="I43">
-        <v>0.2551884904900752</v>
+        <v>-0.1044635439532606</v>
       </c>
       <c r="J43">
-        <v>0.898155660204717</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K43">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L43">
-        <v>3.31</v>
+        <v>3.94</v>
       </c>
       <c r="M43">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="N43">
-        <v>3.17</v>
+        <v>4.01</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C44">
-        <v>1.142741567826858</v>
+        <v>2.106428016615447</v>
       </c>
       <c r="D44" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E44">
-        <v>1.419158035143968</v>
+        <v>2.250213434196751</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G44">
-        <v>0.005477258432173141</v>
+        <v>0.005373571983384554</v>
       </c>
       <c r="H44">
-        <v>0.004920841964856031</v>
+        <v>0.00548978656580325</v>
       </c>
       <c r="I44">
-        <v>0.2764164673171099</v>
+        <v>-0.1437854175813045</v>
       </c>
       <c r="J44">
-        <v>0.9464010620843414</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K44">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="L44">
-        <v>3.31</v>
+        <v>3.74</v>
       </c>
       <c r="M44">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="N44">
-        <v>3.17</v>
+        <v>3.87</v>
       </c>
       <c r="O44">
         <v>1</v>
@@ -3035,96 +3017,96 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B45" t="s">
         <v>28</v>
       </c>
       <c r="C45">
-        <v>1.643997344789146</v>
+        <v>2.037699170124481</v>
       </c>
       <c r="D45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E45">
-        <v>1.497029482860111</v>
+        <v>1.732146473029046</v>
       </c>
       <c r="F45">
         <v>-1</v>
       </c>
       <c r="G45">
-        <v>0.006376002655210854</v>
+        <v>0.004482300829875518</v>
       </c>
       <c r="H45">
-        <v>0.00598297051713989</v>
+        <v>0.004087853526970955</v>
       </c>
       <c r="I45">
-        <v>0.1469678619290353</v>
+        <v>0.3055526970954354</v>
       </c>
       <c r="J45">
-        <v>0.9464010620843414</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K45">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="L45">
-        <v>4.01</v>
+        <v>3.26</v>
       </c>
       <c r="M45">
-        <v>2.37</v>
+        <v>1.59</v>
       </c>
       <c r="N45">
-        <v>3.74</v>
+        <v>2.91</v>
       </c>
       <c r="O45">
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C46">
-        <v>1.02473295176371</v>
+        <v>2.050989626556016</v>
       </c>
       <c r="D46" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E46">
-        <v>1.323823563651905</v>
+        <v>2.158029045643153</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G46">
-        <v>0.005595267048236289</v>
+        <v>0.005829010373443984</v>
       </c>
       <c r="H46">
-        <v>0.005016176436348095</v>
+        <v>0.005861970954356846</v>
       </c>
       <c r="I46">
-        <v>0.2990906118881951</v>
+        <v>-0.1070394190871369</v>
       </c>
       <c r="J46">
-        <v>0.9979332088368078</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K46">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L46">
-        <v>3.31</v>
+        <v>3.94</v>
       </c>
       <c r="M46">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="N46">
-        <v>3.17</v>
+        <v>4.01</v>
       </c>
       <c r="O46">
         <v>1</v>
@@ -3135,96 +3117,96 @@
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B47" t="s">
         <v>28</v>
       </c>
       <c r="C47">
-        <v>1.51516697790798</v>
+        <v>1.939614977812812</v>
       </c>
       <c r="D47" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E47">
-        <v>1.374898295056766</v>
+        <v>1.637628978619619</v>
       </c>
       <c r="F47">
         <v>-1</v>
       </c>
       <c r="G47">
-        <v>0.00650483302209202</v>
+        <v>0.004580385022187188</v>
       </c>
       <c r="H47">
-        <v>0.006105101704943235</v>
+        <v>0.004182371021380382</v>
       </c>
       <c r="I47">
-        <v>0.1402686828512145</v>
+        <v>0.301985999193193</v>
       </c>
       <c r="J47">
-        <v>0.9979332088368078</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K47">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="L47">
-        <v>4.01</v>
+        <v>3.26</v>
       </c>
       <c r="M47">
-        <v>2.37</v>
+        <v>1.59</v>
       </c>
       <c r="N47">
-        <v>3.74</v>
+        <v>2.91</v>
       </c>
       <c r="O47">
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C48">
-        <v>1.025578495611604</v>
+        <v>1.899404965710709</v>
       </c>
       <c r="D48" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E48">
-        <v>1.267956426585794</v>
+        <v>2.009416633049714</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G48">
-        <v>0.005734421504388396</v>
+        <v>0.005980595034289291</v>
       </c>
       <c r="H48">
-        <v>0.005072043573414206</v>
+        <v>0.006010583366950286</v>
       </c>
       <c r="I48">
-        <v>0.2423779309741898</v>
+        <v>-0.1100116673390055</v>
       </c>
       <c r="J48">
-        <v>1.028131661304976</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K48">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="L48">
-        <v>3.38</v>
+        <v>3.94</v>
       </c>
       <c r="M48">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="N48">
-        <v>3.17</v>
+        <v>4.01</v>
       </c>
       <c r="O48">
         <v>1</v>
@@ -3235,96 +3217,96 @@
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B49" t="s">
         <v>28</v>
       </c>
       <c r="C49">
-        <v>1.439670846737559</v>
+        <v>1.858458903856472</v>
       </c>
       <c r="D49" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E49">
-        <v>1.303327962707206</v>
+        <v>1.559424034625328</v>
       </c>
       <c r="F49">
         <v>-1</v>
       </c>
       <c r="G49">
-        <v>0.00658032915326244</v>
+        <v>0.004661541096143528</v>
       </c>
       <c r="H49">
-        <v>0.006176672037292795</v>
+        <v>0.004260575965374673</v>
       </c>
       <c r="I49">
-        <v>0.1363428840303529</v>
+        <v>0.2990348692311444</v>
       </c>
       <c r="J49">
-        <v>1.028131661304976</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K49">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="L49">
-        <v>4.01</v>
+        <v>3.26</v>
       </c>
       <c r="M49">
-        <v>2.37</v>
+        <v>1.59</v>
       </c>
       <c r="N49">
-        <v>3.74</v>
+        <v>2.91</v>
       </c>
       <c r="O49">
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B50" t="s">
         <v>29</v>
       </c>
       <c r="C50">
-        <v>0.95505474527386</v>
+        <v>1.873865711553157</v>
       </c>
       <c r="D50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E50">
-        <v>1.172750932925077</v>
+        <v>1.851819219244965</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G50">
-        <v>0.00580494525472614</v>
+        <v>0.005866134288446843</v>
       </c>
       <c r="H50">
-        <v>0.005027249067074924</v>
+        <v>0.005708180780755035</v>
       </c>
       <c r="I50">
-        <v>0.2176961876512167</v>
+        <v>0.02204649230819267</v>
       </c>
       <c r="J50">
-        <v>1.058928058832376</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K50">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="L50">
-        <v>3.38</v>
+        <v>3.87</v>
       </c>
       <c r="M50">
-        <v>1.82</v>
+        <v>2.27</v>
       </c>
       <c r="N50">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="O50">
         <v>1</v>
@@ -3338,43 +3320,43 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C51">
-        <v>0.8997461387005035</v>
+        <v>1.778043160662217</v>
       </c>
       <c r="D51" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E51">
-        <v>1.128793874425728</v>
+        <v>1.788043160662217</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G51">
-        <v>0.005860253861299496</v>
+        <v>0.004741956839337784</v>
       </c>
       <c r="H51">
-        <v>0.005071206125574273</v>
+        <v>0.004751956839337783</v>
       </c>
       <c r="I51">
-        <v>0.2290477357252241</v>
+        <v>-0.01000000000000023</v>
       </c>
       <c r="J51">
-        <v>1.083080288777073</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K51">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="L51">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="M51">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="N51">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="O51">
         <v>1</v>
@@ -3385,152 +3367,152 @@
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C52">
-        <v>0.9004291893178089</v>
+        <v>1.253223538131198</v>
       </c>
       <c r="D52" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E52">
-        <v>1.129336735615027</v>
+        <v>1.508412028621273</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52">
-        <v>0.005859570810682191</v>
+        <v>0.005366776461868803</v>
       </c>
       <c r="H52">
-        <v>0.005070663264384973</v>
+        <v>0.004831587971378727</v>
       </c>
       <c r="I52">
-        <v>0.2289075462972185</v>
+        <v>0.2551884904900752</v>
       </c>
       <c r="J52">
-        <v>1.082782013398337</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K52">
         <v>2.29</v>
       </c>
       <c r="L52">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="M52">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="N52">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="O52">
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" spans="1:16">
       <c r="A53" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C53">
-        <v>0.8995341152947529</v>
+        <v>1.764610849488207</v>
       </c>
       <c r="D53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E53">
-        <v>1.128625366740808</v>
+        <v>1.741186651335292</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G53">
-        <v>0.005860465884705247</v>
+        <v>0.006255389150511792</v>
       </c>
       <c r="H53">
-        <v>0.005071374633259193</v>
+        <v>0.005818813348664707</v>
       </c>
       <c r="I53">
-        <v>0.2290912514460552</v>
+        <v>0.02342419815291485</v>
       </c>
       <c r="J53">
-        <v>1.083172875417138</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K53">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="L53">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="M53">
-        <v>1.82</v>
+        <v>2.27</v>
       </c>
       <c r="N53">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="O53">
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B54" t="s">
         <v>29</v>
       </c>
       <c r="C54">
-        <v>0.8942975364165378</v>
+        <v>1.759334198518915</v>
       </c>
       <c r="D54" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E54">
-        <v>1.124463544226244</v>
+        <v>1.741186651335292</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G54">
-        <v>0.005865702463583462</v>
+        <v>0.005980665801481085</v>
       </c>
       <c r="H54">
-        <v>0.005075536455773756</v>
+        <v>0.005818813348664707</v>
       </c>
       <c r="I54">
-        <v>0.2301660078097063</v>
+        <v>0.01814754718362277</v>
       </c>
       <c r="J54">
-        <v>1.085459591084481</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K54">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="L54">
-        <v>3.38</v>
+        <v>3.87</v>
       </c>
       <c r="M54">
-        <v>1.82</v>
+        <v>2.27</v>
       </c>
       <c r="N54">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="O54">
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3538,149 +3520,149 @@
         <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C55">
-        <v>0.823882990348408</v>
+        <v>1.142741567826858</v>
       </c>
       <c r="D55" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E55">
-        <v>1.068500891892621</v>
+        <v>1.419158035143968</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55">
-        <v>0.005936117009651592</v>
+        <v>0.005477258432173141</v>
       </c>
       <c r="H55">
-        <v>0.005131499108107379</v>
+        <v>0.004920841964856031</v>
       </c>
       <c r="I55">
-        <v>0.2446179015442134</v>
+        <v>0.2764164673171099</v>
       </c>
       <c r="J55">
-        <v>1.1162083011579</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K55">
         <v>2.29</v>
       </c>
       <c r="L55">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="M55">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="N55">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="O55">
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C56">
-        <v>0.7552208383877499</v>
+        <v>1.643997344789146</v>
       </c>
       <c r="D56" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E56">
-        <v>1.013930971993758</v>
+        <v>1.631669589068545</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G56">
-        <v>0.00600477916161225</v>
+        <v>0.006376002655210854</v>
       </c>
       <c r="H56">
-        <v>0.005186069028006243</v>
+        <v>0.005928330410931455</v>
       </c>
       <c r="I56">
-        <v>0.2587101336060078</v>
+        <v>0.01232775572060163</v>
       </c>
       <c r="J56">
-        <v>1.146191773629804</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K56">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="L56">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="M56">
-        <v>1.82</v>
+        <v>2.27</v>
       </c>
       <c r="N56">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="O56">
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B57" t="s">
         <v>29</v>
       </c>
       <c r="C57">
-        <v>0.7164672131147527</v>
+        <v>1.645957504101798</v>
       </c>
       <c r="D57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E57">
-        <v>0.9831311475409823</v>
+        <v>1.631669589068545</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G57">
-        <v>0.006043532786885248</v>
+        <v>0.006094042495898203</v>
       </c>
       <c r="H57">
-        <v>0.005216868852459018</v>
+        <v>0.005928330410931455</v>
       </c>
       <c r="I57">
-        <v>0.2666639344262296</v>
+        <v>0.01428791503325311</v>
       </c>
       <c r="J57">
-        <v>1.163114754098361</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K57">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="L57">
-        <v>3.38</v>
+        <v>3.87</v>
       </c>
       <c r="M57">
-        <v>1.82</v>
+        <v>2.27</v>
       </c>
       <c r="N57">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="O57">
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3688,149 +3670,149 @@
         <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C58">
-        <v>0.6498239504652852</v>
+        <v>1.02473295176371</v>
       </c>
       <c r="D58" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="E58">
-        <v>0.5798239504652853</v>
+        <v>1.323823563651905</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58">
-        <v>0.006110176049534715</v>
+        <v>0.005595267048236289</v>
       </c>
       <c r="H58">
-        <v>0.006040176049534715</v>
+        <v>0.005016176436348095</v>
       </c>
       <c r="I58">
-        <v>-0.06999999999999984</v>
+        <v>0.2990906118881951</v>
       </c>
       <c r="J58">
-        <v>1.192216615517343</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K58">
         <v>2.29</v>
       </c>
       <c r="L58">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="M58">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="N58">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="O58">
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C59">
-        <v>0.5205928926738919</v>
+        <v>1.51516697790798</v>
       </c>
       <c r="D59" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E59">
-        <v>0.4040417624885522</v>
+        <v>1.514691615940446</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G59">
-        <v>0.006459407107326108</v>
+        <v>0.00650483302209202</v>
       </c>
       <c r="H59">
-        <v>0.006215958237511448</v>
+        <v>0.006045308384059553</v>
       </c>
       <c r="I59">
-        <v>-0.1165511301853397</v>
+        <v>0.0004753619675339493</v>
       </c>
       <c r="J59">
-        <v>1.268977396293209</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K59">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="L59">
-        <v>3.49</v>
+        <v>4.01</v>
       </c>
       <c r="M59">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="N59">
-        <v>3.31</v>
+        <v>3.78</v>
       </c>
       <c r="O59">
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B60" t="s">
         <v>29</v>
       </c>
       <c r="C60">
-        <v>0.474041762488552</v>
+        <v>1.524856959233502</v>
       </c>
       <c r="D60" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E60">
-        <v>0.4040417624885522</v>
+        <v>1.514691615940446</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G60">
-        <v>0.006285958237511447</v>
+        <v>0.006215143040766499</v>
       </c>
       <c r="H60">
-        <v>0.006215958237511448</v>
+        <v>0.006045308384059553</v>
       </c>
       <c r="I60">
-        <v>-0.06999999999999984</v>
+        <v>0.01016534329305552</v>
       </c>
       <c r="J60">
-        <v>1.268977396293209</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K60">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="L60">
-        <v>3.38</v>
+        <v>3.87</v>
       </c>
       <c r="M60">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="N60">
-        <v>3.31</v>
+        <v>3.78</v>
       </c>
       <c r="O60">
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -3838,49 +3820,49 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C61">
-        <v>0.3774746016246668</v>
+        <v>1.025578495611604</v>
       </c>
       <c r="D61" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="E61">
-        <v>0.2639815545814042</v>
+        <v>1.267956426585794</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61">
-        <v>0.006602525398375333</v>
+        <v>0.005734421504388396</v>
       </c>
       <c r="H61">
-        <v>0.006356018445418596</v>
+        <v>0.005072043573414206</v>
       </c>
       <c r="I61">
-        <v>-0.1134930470432627</v>
+        <v>0.2423779309741898</v>
       </c>
       <c r="J61">
-        <v>1.330139059134758</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K61">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="L61">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="M61">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="N61">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="O61">
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -3888,131 +3870,131 @@
         <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C62">
-        <v>0.333981554581404</v>
+        <v>1.439670846737559</v>
       </c>
       <c r="D62" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E62">
-        <v>0.2639815545814042</v>
+        <v>1.446141128837704</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G62">
-        <v>0.006426018445418596</v>
+        <v>0.00658032915326244</v>
       </c>
       <c r="H62">
-        <v>0.006356018445418596</v>
+        <v>0.006113858871162297</v>
       </c>
       <c r="I62">
-        <v>-0.06999999999999984</v>
+        <v>-0.006470282100144331</v>
       </c>
       <c r="J62">
-        <v>1.330139059134758</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K62">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="L62">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="M62">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="N62">
-        <v>3.31</v>
+        <v>3.78</v>
       </c>
       <c r="O62">
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63" spans="1:16">
       <c r="A63" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B63" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C63">
-        <v>0.2442505289553791</v>
+        <v>1.453890595933306</v>
       </c>
       <c r="D63" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E63">
-        <v>0.1336041501315459</v>
+        <v>1.446141128837704</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G63">
-        <v>0.006735749471044622</v>
+        <v>0.006286109404066695</v>
       </c>
       <c r="H63">
-        <v>0.006486395849868455</v>
+        <v>0.006113858871162297</v>
       </c>
       <c r="I63">
-        <v>-0.1106463788238332</v>
+        <v>0.007749467095602203</v>
       </c>
       <c r="J63">
-        <v>1.387072423523342</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K63">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="L63">
-        <v>3.49</v>
+        <v>3.87</v>
       </c>
       <c r="M63">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="N63">
-        <v>3.31</v>
+        <v>3.78</v>
       </c>
       <c r="O63">
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C64">
-        <v>0.2036041501315458</v>
+        <v>0.95505474527386</v>
       </c>
       <c r="D64" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="E64">
-        <v>0.1336041501315459</v>
+        <v>1.210983091160105</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64">
-        <v>0.006556395849868454</v>
+        <v>0.00580494525472614</v>
       </c>
       <c r="H64">
-        <v>0.006486395849868455</v>
+        <v>0.005129016908839895</v>
       </c>
       <c r="I64">
-        <v>-0.06999999999999984</v>
+        <v>0.2559283458862451</v>
       </c>
       <c r="J64">
-        <v>1.387072423523342</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K64">
         <v>2.29</v>
@@ -4021,54 +4003,54 @@
         <v>3.38</v>
       </c>
       <c r="M64">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="N64">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="O64">
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C65">
-        <v>0.2977942894248136</v>
+        <v>0.8997461387005035</v>
       </c>
       <c r="D65" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E65">
-        <v>0.5755281891875166</v>
+        <v>1.128793874425728</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
       <c r="G65">
-        <v>0.006262205710575186</v>
+        <v>0.005860253861299496</v>
       </c>
       <c r="H65">
-        <v>0.005624471810812484</v>
+        <v>0.005071206125574273</v>
       </c>
       <c r="I65">
-        <v>0.277733899762703</v>
+        <v>0.2290477357252241</v>
       </c>
       <c r="J65">
-        <v>1.387072423523342</v>
+        <v>1.083080288777073</v>
       </c>
       <c r="K65">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="L65">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="M65">
         <v>1.82</v>
@@ -4080,7 +4062,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4088,49 +4070,49 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C66">
-        <v>1.909256367193766</v>
+        <v>0.9004291893178089</v>
       </c>
       <c r="D66" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E66">
-        <v>2.01907486979781</v>
+        <v>1.129336735615027</v>
       </c>
       <c r="F66">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G66">
-        <v>0.005970743632806234</v>
+        <v>0.005859570810682191</v>
       </c>
       <c r="H66">
-        <v>0.00600092513020219</v>
+        <v>0.005070663264384973</v>
       </c>
       <c r="I66">
-        <v>-0.1098185026040435</v>
+        <v>0.2289075462972185</v>
       </c>
       <c r="J66">
-        <v>0.7963700520808761</v>
+        <v>1.082782013398337</v>
       </c>
       <c r="K66">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="L66">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="M66">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="N66">
-        <v>4.01</v>
+        <v>3.1</v>
       </c>
       <c r="O66">
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4138,49 +4120,49 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C67">
-        <v>1.899440167721166</v>
+        <v>0.8995341152947529</v>
       </c>
       <c r="D67" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E67">
-        <v>2.009451144824672</v>
+        <v>1.128625366740808</v>
       </c>
       <c r="F67">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G67">
-        <v>0.005980559832278834</v>
+        <v>0.005860465884705247</v>
       </c>
       <c r="H67">
-        <v>0.006010548855175328</v>
+        <v>0.005071374633259193</v>
       </c>
       <c r="I67">
-        <v>-0.1100109771035065</v>
+        <v>0.2290912514460552</v>
       </c>
       <c r="J67">
-        <v>0.8002195420701311</v>
+        <v>1.083172875417138</v>
       </c>
       <c r="K67">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="L67">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="M67">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="N67">
-        <v>4.01</v>
+        <v>3.1</v>
       </c>
       <c r="O67">
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4188,49 +4170,49 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C68">
-        <v>1.886137504764086</v>
+        <v>0.8942975364165378</v>
       </c>
       <c r="D68" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E68">
-        <v>1.996409318396163</v>
+        <v>1.124463544226244</v>
       </c>
       <c r="F68">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G68">
-        <v>0.005993862495235914</v>
+        <v>0.005865702463583462</v>
       </c>
       <c r="H68">
-        <v>0.006023590681603837</v>
+        <v>0.005075536455773756</v>
       </c>
       <c r="I68">
-        <v>-0.1102718136320764</v>
+        <v>0.2301660078097063</v>
       </c>
       <c r="J68">
-        <v>0.8054362726415348</v>
+        <v>1.085459591084481</v>
       </c>
       <c r="K68">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="L68">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="M68">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="N68">
-        <v>4.01</v>
+        <v>3.1</v>
       </c>
       <c r="O68">
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4238,49 +4220,49 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C69">
-        <v>1.870809096426398</v>
+        <v>0.823882990348408</v>
       </c>
       <c r="D69" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E69">
-        <v>1.981381467084703</v>
+        <v>1.068500891892621</v>
       </c>
       <c r="F69">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G69">
-        <v>0.006009190903573602</v>
+        <v>0.005936117009651592</v>
       </c>
       <c r="H69">
-        <v>0.006038618532915297</v>
+        <v>0.005131499108107379</v>
       </c>
       <c r="I69">
-        <v>-0.1105723706583053</v>
+        <v>0.2446179015442134</v>
       </c>
       <c r="J69">
-        <v>0.8114474131661186</v>
+        <v>1.1162083011579</v>
       </c>
       <c r="K69">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="L69">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="M69">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="N69">
-        <v>4.01</v>
+        <v>3.1</v>
       </c>
       <c r="O69">
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4288,49 +4270,49 @@
         <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C70">
-        <v>1.866530632283299</v>
+        <v>0.7552208383877499</v>
       </c>
       <c r="D70" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E70">
-        <v>1.977186894395391</v>
+        <v>1.013930971993758</v>
       </c>
       <c r="F70">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G70">
-        <v>0.0060134693677167</v>
+        <v>0.00600477916161225</v>
       </c>
       <c r="H70">
-        <v>0.006042813105604609</v>
+        <v>0.005186069028006243</v>
       </c>
       <c r="I70">
-        <v>-0.1106562621120917</v>
+        <v>0.2587101336060078</v>
       </c>
       <c r="J70">
-        <v>0.8131252422418436</v>
+        <v>1.146191773629804</v>
       </c>
       <c r="K70">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="L70">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="M70">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="N70">
-        <v>4.01</v>
+        <v>3.1</v>
       </c>
       <c r="O70">
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4338,49 +4320,49 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C71">
-        <v>1.861370672015807</v>
+        <v>0.7164672131147527</v>
       </c>
       <c r="D71" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E71">
-        <v>1.972128109819418</v>
+        <v>0.9831311475409823</v>
       </c>
       <c r="F71">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G71">
-        <v>0.006018629327984194</v>
+        <v>0.006043532786885248</v>
       </c>
       <c r="H71">
-        <v>0.006047871890180582</v>
+        <v>0.005216868852459018</v>
       </c>
       <c r="I71">
-        <v>-0.1107574378036111</v>
+        <v>0.2666639344262296</v>
       </c>
       <c r="J71">
-        <v>0.8151487560722326</v>
+        <v>1.163114754098361</v>
       </c>
       <c r="K71">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="L71">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="M71">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="N71">
-        <v>4.01</v>
+        <v>3.1</v>
       </c>
       <c r="O71">
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4388,49 +4370,49 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C72">
-        <v>1.851301116496863</v>
+        <v>0.6498239504652852</v>
       </c>
       <c r="D72" t="s">
+        <v>30</v>
+      </c>
+      <c r="E72">
+        <v>0.5798239504652853</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72">
+        <v>0.006110176049534715</v>
+      </c>
+      <c r="H72">
+        <v>0.006040176049534715</v>
+      </c>
+      <c r="I72">
+        <v>-0.06999999999999984</v>
+      </c>
+      <c r="J72">
+        <v>1.192216615517343</v>
+      </c>
+      <c r="K72">
+        <v>2.29</v>
+      </c>
+      <c r="L72">
+        <v>3.38</v>
+      </c>
+      <c r="M72">
+        <v>2.29</v>
+      </c>
+      <c r="N72">
+        <v>3.31</v>
+      </c>
+      <c r="O72">
+        <v>1</v>
+      </c>
+      <c r="P72" t="s">
         <v>28</v>
-      </c>
-      <c r="E72">
-        <v>1.962255996565552</v>
-      </c>
-      <c r="F72">
-        <v>-1</v>
-      </c>
-      <c r="G72">
-        <v>0.006028698883503138</v>
-      </c>
-      <c r="H72">
-        <v>0.006057744003434448</v>
-      </c>
-      <c r="I72">
-        <v>-0.110954880068689</v>
-      </c>
-      <c r="J72">
-        <v>0.8190976013737793</v>
-      </c>
-      <c r="K72">
-        <v>2.55</v>
-      </c>
-      <c r="L72">
-        <v>3.94</v>
-      </c>
-      <c r="M72">
-        <v>2.5</v>
-      </c>
-      <c r="N72">
-        <v>4.01</v>
-      </c>
-      <c r="O72">
-        <v>1</v>
-      </c>
-      <c r="P72" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4438,99 +4420,99 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C73">
-        <v>1.855461116431831</v>
+        <v>0.5205928926738919</v>
       </c>
       <c r="D73" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E73">
-        <v>1.966334427874344</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F73">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>0.006024538883568169</v>
+        <v>0.006459407107326108</v>
       </c>
       <c r="H73">
-        <v>0.006053665572125656</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I73">
-        <v>-0.1108733114425124</v>
+        <v>-0.1165511301853397</v>
       </c>
       <c r="J73">
-        <v>0.8174662288502623</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K73">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="L73">
-        <v>3.94</v>
+        <v>3.49</v>
       </c>
       <c r="M73">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="N73">
-        <v>4.01</v>
+        <v>3.31</v>
       </c>
       <c r="O73">
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="74" spans="1:16">
       <c r="A74" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C74">
-        <v>1.85652914973731</v>
+        <v>0.474041762488552</v>
       </c>
       <c r="D74" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E74">
-        <v>1.967381519350304</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F74">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G74">
-        <v>0.006023470850262691</v>
+        <v>0.006285958237511447</v>
       </c>
       <c r="H74">
-        <v>0.006052618480649696</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I74">
-        <v>-0.1108523696129935</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J74">
-        <v>0.8170473922598784</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K74">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="L74">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="M74">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="N74">
-        <v>4.01</v>
+        <v>3.31</v>
       </c>
       <c r="O74">
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4538,99 +4520,99 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C75">
-        <v>1.854953516327912</v>
+        <v>0.3774746016246668</v>
       </c>
       <c r="D75" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E75">
-        <v>1.965836780713639</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F75">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G75">
-        <v>0.006025046483672087</v>
+        <v>0.006602525398375333</v>
       </c>
       <c r="H75">
-        <v>0.00605416321928636</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I75">
-        <v>-0.1108832643857269</v>
+        <v>-0.1134930470432627</v>
       </c>
       <c r="J75">
-        <v>0.8176652877145442</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K75">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="L75">
-        <v>3.94</v>
+        <v>3.49</v>
       </c>
       <c r="M75">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="N75">
-        <v>4.01</v>
+        <v>3.31</v>
       </c>
       <c r="O75">
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B76" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C76">
-        <v>1.853898035926949</v>
+        <v>0.333981554581404</v>
       </c>
       <c r="D76" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E76">
-        <v>1.964801996006813</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F76">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G76">
-        <v>0.00602610196407305</v>
+        <v>0.006426018445418596</v>
       </c>
       <c r="H76">
-        <v>0.006055198003993187</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I76">
-        <v>-0.1109039600798636</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J76">
-        <v>0.8180792015972748</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K76">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="L76">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="M76">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="N76">
-        <v>4.01</v>
+        <v>3.31</v>
       </c>
       <c r="O76">
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4638,99 +4620,99 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C77">
-        <v>1.851157777698763</v>
+        <v>0.2442505289553791</v>
       </c>
       <c r="D77" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E77">
-        <v>1.96211546833212</v>
+        <v>0.1336041501315459</v>
       </c>
       <c r="F77">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>0.006028842222301236</v>
+        <v>0.006735749471044622</v>
       </c>
       <c r="H77">
-        <v>0.006057884531667879</v>
+        <v>0.006486395849868455</v>
       </c>
       <c r="I77">
-        <v>-0.1109576906333571</v>
+        <v>-0.1106463788238332</v>
       </c>
       <c r="J77">
-        <v>0.8191538126671517</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K77">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="L77">
-        <v>3.94</v>
+        <v>3.49</v>
       </c>
       <c r="M77">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="N77">
-        <v>4.01</v>
+        <v>3.31</v>
       </c>
       <c r="O77">
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B78" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C78">
-        <v>1.858566205293179</v>
+        <v>0.2977942894248136</v>
       </c>
       <c r="D78" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E78">
-        <v>1.969378632640371</v>
+        <v>0.5755281891875166</v>
       </c>
       <c r="F78">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G78">
-        <v>0.006021433794706822</v>
+        <v>0.006262205710575186</v>
       </c>
       <c r="H78">
-        <v>0.006050621367359629</v>
+        <v>0.005624471810812484</v>
       </c>
       <c r="I78">
-        <v>-0.1108124273471924</v>
+        <v>0.277733899762703</v>
       </c>
       <c r="J78">
-        <v>0.8162485469438515</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K78">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="L78">
-        <v>3.94</v>
+        <v>3.28</v>
       </c>
       <c r="M78">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="N78">
-        <v>4.01</v>
+        <v>3.1</v>
       </c>
       <c r="O78">
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4738,99 +4720,99 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C79">
-        <v>1.868405823240289</v>
+        <v>2.01907486979781</v>
       </c>
       <c r="D79" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E79">
-        <v>1.979025316902244</v>
+        <v>1.972239981776411</v>
       </c>
       <c r="F79">
         <v>-1</v>
       </c>
       <c r="G79">
-        <v>0.006011594176759711</v>
+        <v>0.00600092513020219</v>
       </c>
       <c r="H79">
-        <v>0.006040974683097756</v>
+        <v>0.005587760018223588</v>
       </c>
       <c r="I79">
-        <v>-0.1106194936619547</v>
+        <v>0.04683488802139846</v>
       </c>
       <c r="J79">
-        <v>0.8123898732391025</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K79">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="L79">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="M79">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N79">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O79">
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B80" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C80">
-        <v>1.873099451459633</v>
+        <v>1.998530377609941</v>
       </c>
       <c r="D80" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E80">
-        <v>1.983626913195719</v>
+        <v>1.972239981776411</v>
       </c>
       <c r="F80">
         <v>-1</v>
       </c>
       <c r="G80">
-        <v>0.006006900548540367</v>
+        <v>0.005741469622390059</v>
       </c>
       <c r="H80">
-        <v>0.00603637308680428</v>
+        <v>0.005587760018223588</v>
       </c>
       <c r="I80">
-        <v>-0.1105274617360856</v>
+        <v>0.0262903958335301</v>
       </c>
       <c r="J80">
-        <v>0.8105492347217125</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K80">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L80">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M80">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N80">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O80">
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -4841,28 +4823,28 @@
         <v>26</v>
       </c>
       <c r="C81">
-        <v>1.880315678845928</v>
+        <v>1.899440167721166</v>
       </c>
       <c r="D81" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E81">
-        <v>1.99070164592738</v>
+        <v>1.963501639500802</v>
       </c>
       <c r="F81">
         <v>-1</v>
       </c>
       <c r="G81">
-        <v>0.005999684321154073</v>
+        <v>0.005980559832278834</v>
       </c>
       <c r="H81">
-        <v>0.006029298354072619</v>
+        <v>0.005596498360499197</v>
       </c>
       <c r="I81">
-        <v>-0.1103859670814522</v>
+        <v>-0.06406147177963639</v>
       </c>
       <c r="J81">
-        <v>0.8077193416290479</v>
+        <v>0.8002195420701311</v>
       </c>
       <c r="K81">
         <v>2.55</v>
@@ -4871,66 +4853,66 @@
         <v>3.94</v>
       </c>
       <c r="M81">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N81">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O81">
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="82" spans="1:16">
       <c r="A82" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C82">
-        <v>1.885229059666124</v>
+        <v>1.989484076135192</v>
       </c>
       <c r="D82" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E82">
-        <v>1.995518685947181</v>
+        <v>1.963501639500802</v>
       </c>
       <c r="F82">
         <v>-1</v>
       </c>
       <c r="G82">
-        <v>0.005994770940333876</v>
+        <v>0.005750515923864809</v>
       </c>
       <c r="H82">
-        <v>0.006024481314052819</v>
+        <v>0.005596498360499197</v>
       </c>
       <c r="I82">
-        <v>-0.1102896262810562</v>
+        <v>0.02598243663438993</v>
       </c>
       <c r="J82">
-        <v>0.8057925256211278</v>
+        <v>0.8002195420701311</v>
       </c>
       <c r="K82">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L82">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M82">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N82">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O82">
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -4941,28 +4923,28 @@
         <v>26</v>
       </c>
       <c r="C83">
-        <v>1.891592550259521</v>
+        <v>1.886137504764086</v>
       </c>
       <c r="D83" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E83">
-        <v>2.001757402215216</v>
+        <v>1.951659661103716</v>
       </c>
       <c r="F83">
         <v>-1</v>
       </c>
       <c r="G83">
-        <v>0.00598840744974048</v>
+        <v>0.005993862495235914</v>
       </c>
       <c r="H83">
-        <v>0.006018242597784784</v>
+        <v>0.005608340338896283</v>
       </c>
       <c r="I83">
-        <v>-0.1101648519556955</v>
+        <v>-0.06552215633962954</v>
       </c>
       <c r="J83">
-        <v>0.8032970391139135</v>
+        <v>0.8054362726415348</v>
       </c>
       <c r="K83">
         <v>2.55</v>
@@ -4971,66 +4953,66 @@
         <v>3.94</v>
       </c>
       <c r="M83">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N83">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O83">
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B84" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C84">
-        <v>1.898226451425238</v>
+        <v>1.977224759292393</v>
       </c>
       <c r="D84" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E84">
-        <v>2.008261226887488</v>
+        <v>1.951659661103716</v>
       </c>
       <c r="F84">
         <v>-1</v>
       </c>
       <c r="G84">
-        <v>0.005981773548574762</v>
+        <v>0.005762775240707607</v>
       </c>
       <c r="H84">
-        <v>0.006011738773112512</v>
+        <v>0.005608340338896283</v>
       </c>
       <c r="I84">
-        <v>-0.1100347754622497</v>
+        <v>0.02556509818867747</v>
       </c>
       <c r="J84">
-        <v>0.8006955092450049</v>
+        <v>0.8054362726415348</v>
       </c>
       <c r="K84">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L84">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M84">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N84">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O84">
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5041,28 +5023,28 @@
         <v>26</v>
       </c>
       <c r="C85">
-        <v>1.903475998145109</v>
+        <v>1.870809096426398</v>
       </c>
       <c r="D85" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E85">
-        <v>2.013407841318734</v>
+        <v>1.981381467084703</v>
       </c>
       <c r="F85">
         <v>-1</v>
       </c>
       <c r="G85">
-        <v>0.005976524001854891</v>
+        <v>0.006009190903573602</v>
       </c>
       <c r="H85">
-        <v>0.006006592158681266</v>
+        <v>0.006038618532915297</v>
       </c>
       <c r="I85">
-        <v>-0.1099318431736251</v>
+        <v>-0.1105723706583053</v>
       </c>
       <c r="J85">
-        <v>0.7986368634725065</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K85">
         <v>2.55</v>
@@ -5080,57 +5062,57 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B86" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C86">
-        <v>1.915111220550284</v>
+        <v>1.963098579059621</v>
       </c>
       <c r="D86" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E86">
-        <v>2.024814922108121</v>
+        <v>1.938014372112911</v>
       </c>
       <c r="F86">
         <v>-1</v>
       </c>
       <c r="G86">
-        <v>0.005964888779449715</v>
+        <v>0.005776901420940379</v>
       </c>
       <c r="H86">
-        <v>0.005995185077891879</v>
+        <v>0.005621985627887089</v>
       </c>
       <c r="I86">
-        <v>-0.1097037015578373</v>
+        <v>0.02508420694671076</v>
       </c>
       <c r="J86">
-        <v>0.7940740311567515</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K86">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L86">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M86">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N86">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O86">
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5141,28 +5123,28 @@
         <v>26</v>
       </c>
       <c r="C87">
-        <v>1.927566816677033</v>
+        <v>1.866530632283299</v>
       </c>
       <c r="D87" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E87">
-        <v>2.037026290859836</v>
+        <v>1.977186894395391</v>
       </c>
       <c r="F87">
         <v>-1</v>
       </c>
       <c r="G87">
-        <v>0.005952433183322967</v>
+        <v>0.0060134693677167</v>
       </c>
       <c r="H87">
-        <v>0.005982973709140164</v>
+        <v>0.006042813105604609</v>
       </c>
       <c r="I87">
-        <v>-0.109459474182803</v>
+        <v>-0.1106562621120917</v>
       </c>
       <c r="J87">
-        <v>0.7891894836560657</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K87">
         <v>2.55</v>
@@ -5180,57 +5162,57 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C88">
-        <v>1.931008249436597</v>
+        <v>1.959155680731668</v>
       </c>
       <c r="D88" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E88">
-        <v>2.040400244545683</v>
+        <v>1.934205700111015</v>
       </c>
       <c r="F88">
         <v>-1</v>
       </c>
       <c r="G88">
-        <v>0.005948991750563403</v>
+        <v>0.005780844319268333</v>
       </c>
       <c r="H88">
-        <v>0.005979599755454317</v>
+        <v>0.005625794299888985</v>
       </c>
       <c r="I88">
-        <v>-0.1093919951090863</v>
+        <v>0.02494998062065279</v>
       </c>
       <c r="J88">
-        <v>0.7878399021817268</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K88">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L88">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M88">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N88">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O88">
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5241,28 +5223,28 @@
         <v>26</v>
       </c>
       <c r="C89">
-        <v>1.931290596802969</v>
+        <v>1.861370672015807</v>
       </c>
       <c r="D89" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E89">
-        <v>2.040677055689185</v>
+        <v>1.972128109819418</v>
       </c>
       <c r="F89">
         <v>-1</v>
       </c>
       <c r="G89">
-        <v>0.00594870940319703</v>
+        <v>0.006018629327984194</v>
       </c>
       <c r="H89">
-        <v>0.005979322944310814</v>
+        <v>0.006047871890180582</v>
       </c>
       <c r="I89">
-        <v>-0.1093864588862159</v>
+        <v>-0.1107574378036111</v>
       </c>
       <c r="J89">
-        <v>0.7877291777243258</v>
+        <v>0.8151487560722326</v>
       </c>
       <c r="K89">
         <v>2.55</v>
@@ -5280,57 +5262,57 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B90" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C90">
-        <v>1.932400003731856</v>
+        <v>1.954400423230253</v>
       </c>
       <c r="D90" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E90">
-        <v>2.041764709541035</v>
+        <v>1.929612323716032</v>
       </c>
       <c r="F90">
         <v>-1</v>
       </c>
       <c r="G90">
-        <v>0.005947599996268144</v>
+        <v>0.005785599576769747</v>
       </c>
       <c r="H90">
-        <v>0.005978235290458964</v>
+        <v>0.005630387676283969</v>
       </c>
       <c r="I90">
-        <v>-0.1093647058091789</v>
+        <v>0.02478809951422156</v>
       </c>
       <c r="J90">
-        <v>0.7872941161835857</v>
+        <v>0.8151487560722326</v>
       </c>
       <c r="K90">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L90">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M90">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N90">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O90">
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5341,28 +5323,28 @@
         <v>26</v>
       </c>
       <c r="C91">
-        <v>1.928867601835406</v>
+        <v>1.851301116496863</v>
       </c>
       <c r="D91" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E91">
-        <v>2.038301570426869</v>
+        <v>1.962255996565552</v>
       </c>
       <c r="F91">
         <v>-1</v>
       </c>
       <c r="G91">
-        <v>0.005951132398164594</v>
+        <v>0.006028698883503138</v>
       </c>
       <c r="H91">
-        <v>0.005981698429573131</v>
+        <v>0.006057744003434448</v>
       </c>
       <c r="I91">
-        <v>-0.1094339685914623</v>
+        <v>-0.110954880068689</v>
       </c>
       <c r="J91">
-        <v>0.7886793718292525</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K91">
         <v>2.55</v>
@@ -5380,57 +5362,57 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B92" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C92">
-        <v>1.925635063875757</v>
+        <v>1.945120636771619</v>
       </c>
       <c r="D92" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E92">
-        <v>2.035132415564467</v>
+        <v>1.920648444881521</v>
       </c>
       <c r="F92">
         <v>-1</v>
       </c>
       <c r="G92">
-        <v>0.005954364936124243</v>
+        <v>0.005794879363228382</v>
       </c>
       <c r="H92">
-        <v>0.005984867584435533</v>
+        <v>0.005639351555118479</v>
       </c>
       <c r="I92">
-        <v>-0.1094973516887103</v>
+        <v>0.02447219189009786</v>
       </c>
       <c r="J92">
-        <v>0.7899470337742129</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K92">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L92">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M92">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N92">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O92">
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5441,28 +5423,28 @@
         <v>26</v>
       </c>
       <c r="C93">
-        <v>1.924421367530698</v>
+        <v>1.855461116431831</v>
       </c>
       <c r="D93" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E93">
-        <v>2.033942517186959</v>
+        <v>1.966334427874344</v>
       </c>
       <c r="F93">
         <v>-1</v>
       </c>
       <c r="G93">
-        <v>0.005955578632469301</v>
+        <v>0.006024538883568169</v>
       </c>
       <c r="H93">
-        <v>0.005986057482813041</v>
+        <v>0.006053665572125656</v>
       </c>
       <c r="I93">
-        <v>-0.1095211496562603</v>
+        <v>-0.1108733114425124</v>
       </c>
       <c r="J93">
-        <v>0.7904229931252164</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K93">
         <v>2.55</v>
@@ -5480,57 +5462,57 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:16">
       <c r="A94" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B94" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C94">
-        <v>1.922633944537091</v>
+        <v>1.948954362201884</v>
       </c>
       <c r="D94" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E94">
-        <v>2.03219014170303</v>
+        <v>1.924351660509904</v>
       </c>
       <c r="F94">
         <v>-1</v>
       </c>
       <c r="G94">
-        <v>0.00595736605546291</v>
+        <v>0.005791045637798117</v>
       </c>
       <c r="H94">
-        <v>0.00598780985829697</v>
+        <v>0.005635648339490096</v>
       </c>
       <c r="I94">
-        <v>-0.1095561971659391</v>
+        <v>0.02460270169197942</v>
       </c>
       <c r="J94">
-        <v>0.791123943318788</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K94">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L94">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M94">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N94">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O94">
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5541,28 +5523,28 @@
         <v>26</v>
       </c>
       <c r="C95">
-        <v>1.921462641095741</v>
+        <v>1.85652914973731</v>
       </c>
       <c r="D95" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E95">
-        <v>2.031041804995824</v>
+        <v>1.967381519350304</v>
       </c>
       <c r="F95">
         <v>-1</v>
       </c>
       <c r="G95">
-        <v>0.005958537358904259</v>
+        <v>0.006023470850262691</v>
       </c>
       <c r="H95">
-        <v>0.005988958195004175</v>
+        <v>0.006052618480649696</v>
       </c>
       <c r="I95">
-        <v>-0.1095791639000829</v>
+        <v>-0.1108523696129935</v>
       </c>
       <c r="J95">
-        <v>0.7915832780016702</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K95">
         <v>2.55</v>
@@ -5580,57 +5562,57 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96" spans="1:16">
       <c r="A96" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B96" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C96">
-        <v>1.922670198036319</v>
+        <v>1.949938628189286</v>
       </c>
       <c r="D96" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E96">
-        <v>2.032225684349332</v>
+        <v>1.925302419570076</v>
       </c>
       <c r="F96">
         <v>-1</v>
       </c>
       <c r="G96">
-        <v>0.005957329801963681</v>
+        <v>0.005790061371810714</v>
       </c>
       <c r="H96">
-        <v>0.005987774315650668</v>
+        <v>0.005634697580429924</v>
       </c>
       <c r="I96">
-        <v>-0.1095554863130133</v>
+        <v>0.02463620861921001</v>
       </c>
       <c r="J96">
-        <v>0.7911097262602672</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K96">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L96">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M96">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N96">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O96">
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5641,28 +5623,28 @@
         <v>26</v>
       </c>
       <c r="C97">
-        <v>1.924302790568959</v>
+        <v>1.854953516327912</v>
       </c>
       <c r="D97" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E97">
-        <v>2.033826265263685</v>
+        <v>1.965836780713639</v>
       </c>
       <c r="F97">
         <v>-1</v>
       </c>
       <c r="G97">
-        <v>0.00595569720943104</v>
+        <v>0.006025046483672087</v>
       </c>
       <c r="H97">
-        <v>0.005986173734736314</v>
+        <v>0.00605416321928636</v>
       </c>
       <c r="I97">
-        <v>-0.109523474694726</v>
+        <v>-0.1108832643857269</v>
       </c>
       <c r="J97">
-        <v>0.7904694938945258</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K97">
         <v>2.55</v>
@@ -5680,57 +5662,57 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="1:16">
       <c r="A98" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B98" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C98">
-        <v>1.92765643109575</v>
+        <v>1.948486573870821</v>
       </c>
       <c r="D98" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E98">
-        <v>2.037114148133088</v>
+        <v>1.923899796887985</v>
       </c>
       <c r="F98">
         <v>-1</v>
       </c>
       <c r="G98">
-        <v>0.005952343568904249</v>
+        <v>0.00579151342612918</v>
       </c>
       <c r="H98">
-        <v>0.005982885851866911</v>
+        <v>0.005636100203112015</v>
       </c>
       <c r="I98">
-        <v>-0.1094577170373379</v>
+        <v>0.02458677698283673</v>
       </c>
       <c r="J98">
-        <v>0.7891543407467646</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K98">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L98">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M98">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N98">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O98">
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5741,28 +5723,28 @@
         <v>26</v>
       </c>
       <c r="C99">
-        <v>1.931644858116821</v>
+        <v>1.853898035926949</v>
       </c>
       <c r="D99" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E99">
-        <v>2.041024370702765</v>
+        <v>1.964801996006813</v>
       </c>
       <c r="F99">
         <v>-1</v>
       </c>
       <c r="G99">
-        <v>0.005948355141883179</v>
+        <v>0.00602610196407305</v>
       </c>
       <c r="H99">
-        <v>0.005978975629297235</v>
+        <v>0.006055198003993187</v>
       </c>
       <c r="I99">
-        <v>-0.1093795125859445</v>
+        <v>-0.1109039600798636</v>
       </c>
       <c r="J99">
-        <v>0.7875902517188939</v>
+        <v>0.8180792015972748</v>
       </c>
       <c r="K99">
         <v>2.55</v>
@@ -5780,57 +5762,57 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:16">
       <c r="A100" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B100" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C100">
-        <v>1.933649431471673</v>
+        <v>1.947513876246404</v>
       </c>
       <c r="D100" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E100">
-        <v>2.042989638697718</v>
+        <v>1.922960212374186</v>
       </c>
       <c r="F100">
         <v>-1</v>
       </c>
       <c r="G100">
-        <v>0.005946350568528327</v>
+        <v>0.005792486123753596</v>
       </c>
       <c r="H100">
-        <v>0.005977010361302281</v>
+        <v>0.005637039787625813</v>
       </c>
       <c r="I100">
-        <v>-0.1093402072260452</v>
+        <v>0.02455366387221836</v>
       </c>
       <c r="J100">
-        <v>0.7868041445209126</v>
+        <v>0.8180792015972748</v>
       </c>
       <c r="K100">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L100">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M100">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N100">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O100">
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -5841,28 +5823,28 @@
         <v>26</v>
       </c>
       <c r="C101">
-        <v>1.937204548237283</v>
+        <v>1.851157777698763</v>
       </c>
       <c r="D101" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E101">
-        <v>2.046475047291454</v>
+        <v>1.96211546833212</v>
       </c>
       <c r="F101">
         <v>-1</v>
       </c>
       <c r="G101">
-        <v>0.005942795451762716</v>
+        <v>0.006028842222301236</v>
       </c>
       <c r="H101">
-        <v>0.005973524952708546</v>
+        <v>0.006057884531667879</v>
       </c>
       <c r="I101">
-        <v>-0.1092704990541709</v>
+        <v>-0.1109576906333571</v>
       </c>
       <c r="J101">
-        <v>0.7854099810834182</v>
+        <v>0.8191538126671517</v>
       </c>
       <c r="K101">
         <v>2.55</v>
@@ -5880,57 +5862,57 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
     </row>
     <row r="102" spans="1:16">
       <c r="A102" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B102" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C102">
-        <v>1.941976947705745</v>
+        <v>1.944988540232194</v>
       </c>
       <c r="D102" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E102">
-        <v>2.05115387029975</v>
+        <v>1.920520845245565</v>
       </c>
       <c r="F102">
         <v>-1</v>
       </c>
       <c r="G102">
-        <v>0.005938023052294255</v>
+        <v>0.005795011459767806</v>
       </c>
       <c r="H102">
-        <v>0.00596884612970025</v>
+        <v>0.005639479154754435</v>
       </c>
       <c r="I102">
-        <v>-0.1091769225940049</v>
+        <v>0.02446769498662826</v>
       </c>
       <c r="J102">
-        <v>0.7835384518800999</v>
+        <v>0.8191538126671517</v>
       </c>
       <c r="K102">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L102">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M102">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N102">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O102">
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -5941,28 +5923,28 @@
         <v>26</v>
       </c>
       <c r="C103">
-        <v>1.943259802359731</v>
+        <v>1.858566205293179</v>
       </c>
       <c r="D103" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E103">
-        <v>2.052411570940913</v>
+        <v>1.969378632640371</v>
       </c>
       <c r="F103">
         <v>-1</v>
       </c>
       <c r="G103">
-        <v>0.005936740197640269</v>
+        <v>0.006021433794706822</v>
       </c>
       <c r="H103">
-        <v>0.005967588429059087</v>
+        <v>0.006050621367359629</v>
       </c>
       <c r="I103">
-        <v>-0.1091517685811818</v>
+        <v>-0.1108124273471924</v>
       </c>
       <c r="J103">
-        <v>0.783035371623635</v>
+        <v>0.8162485469438515</v>
       </c>
       <c r="K103">
         <v>2.55</v>
@@ -5980,57 +5962,57 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
     </row>
     <row r="104" spans="1:16">
       <c r="A104" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B104" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C104">
-        <v>1.944946776406004</v>
+        <v>1.951815914681949</v>
       </c>
       <c r="D104" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E104">
-        <v>2.054065467064709</v>
+        <v>1.927115798437457</v>
       </c>
       <c r="F104">
         <v>-1</v>
       </c>
       <c r="G104">
-        <v>0.005935053223593996</v>
+        <v>0.005788184085318051</v>
       </c>
       <c r="H104">
-        <v>0.005965934532935291</v>
+        <v>0.005632884201562542</v>
       </c>
       <c r="I104">
-        <v>-0.1091186906587052</v>
+        <v>0.02470011624449198</v>
       </c>
       <c r="J104">
-        <v>0.7823738131741161</v>
+        <v>0.8162485469438515</v>
       </c>
       <c r="K104">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L104">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M104">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N104">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O104">
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6041,28 +6023,28 @@
         <v>26</v>
       </c>
       <c r="C105">
-        <v>1.948679250285769</v>
+        <v>1.868405823240289</v>
       </c>
       <c r="D105" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E105">
-        <v>2.057724755182126</v>
+        <v>1.979025316902244</v>
       </c>
       <c r="F105">
         <v>-1</v>
       </c>
       <c r="G105">
-        <v>0.005931320749714232</v>
+        <v>0.006011594176759711</v>
       </c>
       <c r="H105">
-        <v>0.005962275244817874</v>
+        <v>0.006040974683097756</v>
       </c>
       <c r="I105">
-        <v>-0.1090455048963574</v>
+        <v>-0.1106194936619547</v>
       </c>
       <c r="J105">
-        <v>0.7809100979271496</v>
+        <v>0.8123898732391025</v>
       </c>
       <c r="K105">
         <v>2.55</v>
@@ -6080,57 +6062,57 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
     </row>
     <row r="106" spans="1:16">
       <c r="A106" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B106" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C106">
-        <v>1.950614227390016</v>
+        <v>1.960883797888109</v>
       </c>
       <c r="D106" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E106">
-        <v>2.059621791558839</v>
+        <v>1.935874987747237</v>
       </c>
       <c r="F106">
         <v>-1</v>
       </c>
       <c r="G106">
-        <v>0.005929385772609984</v>
+        <v>0.005779116202111891</v>
       </c>
       <c r="H106">
-        <v>0.005960378208441161</v>
+        <v>0.005624125012252763</v>
       </c>
       <c r="I106">
-        <v>-0.1090075641688231</v>
+        <v>0.02500881014087186</v>
       </c>
       <c r="J106">
-        <v>0.7801512833764644</v>
+        <v>0.8123898732391025</v>
       </c>
       <c r="K106">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L106">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M106">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="N106">
-        <v>4.01</v>
+        <v>3.78</v>
       </c>
       <c r="O106">
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6141,28 +6123,28 @@
         <v>26</v>
       </c>
       <c r="C107">
-        <v>1.951624445196418</v>
+        <v>1.873099451459633</v>
       </c>
       <c r="D107" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E107">
-        <v>2.060612201172958</v>
+        <v>1.983626913195719</v>
       </c>
       <c r="F107">
         <v>-1</v>
       </c>
       <c r="G107">
-        <v>0.005928375554803582</v>
+        <v>0.006006900548540367</v>
       </c>
       <c r="H107">
-        <v>0.005959387798827042</v>
+        <v>0.00603637308680428</v>
       </c>
       <c r="I107">
-        <v>-0.1089877559765402</v>
+        <v>-0.1105274617360856</v>
       </c>
       <c r="J107">
-        <v>0.7797551195308166</v>
+        <v>0.8105492347217125</v>
       </c>
       <c r="K107">
         <v>2.55</v>
@@ -6180,57 +6162,57 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:16">
       <c r="A108" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B108" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C108">
-        <v>1.953198644707818</v>
+        <v>1.965209298403976</v>
       </c>
       <c r="D108" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E108">
-        <v>1.893443446257855</v>
+        <v>1.940053237181713</v>
       </c>
       <c r="F108">
         <v>-1</v>
       </c>
       <c r="G108">
-        <v>0.005926801355292182</v>
+        <v>0.005774790701596024</v>
       </c>
       <c r="H108">
-        <v>0.005586556553742145</v>
+        <v>0.005619946762818287</v>
       </c>
       <c r="I108">
-        <v>0.05975519844996358</v>
+        <v>0.02515606122226322</v>
       </c>
       <c r="J108">
-        <v>0.7791377863890909</v>
+        <v>0.8105492347217125</v>
       </c>
       <c r="K108">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L108">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M108">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N108">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O108">
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6241,28 +6223,28 @@
         <v>26</v>
       </c>
       <c r="C109">
-        <v>1.956263001176151</v>
+        <v>1.880315678845928</v>
       </c>
       <c r="D109" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E109">
-        <v>1.896291495210775</v>
+        <v>1.99070164592738</v>
       </c>
       <c r="F109">
         <v>-1</v>
       </c>
       <c r="G109">
-        <v>0.00592373699882385</v>
+        <v>0.005999684321154073</v>
       </c>
       <c r="H109">
-        <v>0.005583708504789225</v>
+        <v>0.006029298354072619</v>
       </c>
       <c r="I109">
-        <v>0.05997150596537537</v>
+        <v>-0.1103859670814522</v>
       </c>
       <c r="J109">
-        <v>0.777936077970137</v>
+        <v>0.8077193416290479</v>
       </c>
       <c r="K109">
         <v>2.55</v>
@@ -6271,66 +6253,66 @@
         <v>3.94</v>
       </c>
       <c r="M109">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="N109">
-        <v>3.74</v>
+        <v>4.01</v>
       </c>
       <c r="O109">
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110" spans="1:16">
       <c r="A110" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B110" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C110">
-        <v>1.957833849297126</v>
+        <v>1.971859547171738</v>
       </c>
       <c r="D110" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E110">
-        <v>1.897751459934976</v>
+        <v>1.946477094502061</v>
       </c>
       <c r="F110">
         <v>-1</v>
       </c>
       <c r="G110">
-        <v>0.005922166150702874</v>
+        <v>0.005768140452828262</v>
       </c>
       <c r="H110">
-        <v>0.005582248540065025</v>
+        <v>0.005613522905497939</v>
       </c>
       <c r="I110">
-        <v>0.06008238936215005</v>
+        <v>0.02538245266967643</v>
       </c>
       <c r="J110">
-        <v>0.7773200590991663</v>
+        <v>0.8077193416290479</v>
       </c>
       <c r="K110">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L110">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M110">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N110">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O110">
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6341,28 +6323,28 @@
         <v>26</v>
       </c>
       <c r="C111">
-        <v>1.960719712115154</v>
+        <v>1.885229059666124</v>
       </c>
       <c r="D111" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E111">
-        <v>1.900433614789378</v>
+        <v>1.995518685947181</v>
       </c>
       <c r="F111">
         <v>-1</v>
       </c>
       <c r="G111">
-        <v>0.005919280287884846</v>
+        <v>0.005994770940333876</v>
       </c>
       <c r="H111">
-        <v>0.005579566385210622</v>
+        <v>0.006024481314052819</v>
       </c>
       <c r="I111">
-        <v>0.0602860973257755</v>
+        <v>-0.1102896262810562</v>
       </c>
       <c r="J111">
-        <v>0.7761883481901358</v>
+        <v>0.8057925256211278</v>
       </c>
       <c r="K111">
         <v>2.55</v>
@@ -6371,66 +6353,66 @@
         <v>3.94</v>
       </c>
       <c r="M111">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="N111">
-        <v>3.74</v>
+        <v>4.01</v>
       </c>
       <c r="O111">
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="112" spans="1:16">
       <c r="A112" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B112" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C112">
-        <v>1.964089726245929</v>
+        <v>1.97638756479035</v>
       </c>
       <c r="D112" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E112">
-        <v>1.903565745569746</v>
+        <v>1.95085096684004</v>
       </c>
       <c r="F112">
         <v>-1</v>
       </c>
       <c r="G112">
-        <v>0.005915910273754071</v>
+        <v>0.005763612435209651</v>
       </c>
       <c r="H112">
-        <v>0.005576434254430255</v>
+        <v>0.00560914903315996</v>
       </c>
       <c r="I112">
-        <v>0.06052398067618325</v>
+        <v>0.02553659795030994</v>
       </c>
       <c r="J112">
-        <v>0.7748667740212044</v>
+        <v>0.8057925256211278</v>
       </c>
       <c r="K112">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L112">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M112">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N112">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O112">
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6438,99 +6420,99 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C113">
-        <v>2.076110072462908</v>
+        <v>1.891592550259521</v>
       </c>
       <c r="D113" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E113">
-        <v>1.906672348694837</v>
+        <v>2.001757402215216</v>
       </c>
       <c r="F113">
         <v>-1</v>
       </c>
       <c r="G113">
-        <v>0.005943889927537092</v>
+        <v>0.00598840744974048</v>
       </c>
       <c r="H113">
-        <v>0.005573327651305164</v>
+        <v>0.006018242597784784</v>
       </c>
       <c r="I113">
-        <v>0.1694377237680709</v>
+        <v>-0.1101648519556955</v>
       </c>
       <c r="J113">
-        <v>0.7735559710148369</v>
+        <v>0.8032970391139135</v>
       </c>
       <c r="K113">
+        <v>2.55</v>
+      </c>
+      <c r="L113">
+        <v>3.94</v>
+      </c>
+      <c r="M113">
         <v>2.5</v>
       </c>
-      <c r="L113">
+      <c r="N113">
         <v>4.01</v>
       </c>
-      <c r="M113">
-        <v>2.37</v>
-      </c>
-      <c r="N113">
-        <v>3.74</v>
-      </c>
       <c r="O113">
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
     </row>
     <row r="114" spans="1:16">
       <c r="A114" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B114" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C114">
-        <v>2.078101340295269</v>
+        <v>1.982251958082303</v>
       </c>
       <c r="D114" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E114">
-        <v>1.908560070599915</v>
+        <v>1.956515721211416</v>
       </c>
       <c r="F114">
         <v>-1</v>
       </c>
       <c r="G114">
-        <v>0.00594189865970473</v>
+        <v>0.005757748041917698</v>
       </c>
       <c r="H114">
-        <v>0.005571439929400086</v>
+        <v>0.005603484278788583</v>
       </c>
       <c r="I114">
-        <v>0.1695412696953538</v>
+        <v>0.02573623687088711</v>
       </c>
       <c r="J114">
-        <v>0.7727594638818923</v>
+        <v>0.8032970391139135</v>
       </c>
       <c r="K114">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L114">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M114">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N114">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O114">
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6538,99 +6520,99 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C115">
-        <v>2.078941598729263</v>
+        <v>1.898226451425238</v>
       </c>
       <c r="D115" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E115">
-        <v>1.909356635595342</v>
+        <v>2.008261226887488</v>
       </c>
       <c r="F115">
         <v>-1</v>
       </c>
       <c r="G115">
-        <v>0.005941058401270736</v>
+        <v>0.005981773548574762</v>
       </c>
       <c r="H115">
-        <v>0.005570643364404658</v>
+        <v>0.006011738773112512</v>
       </c>
       <c r="I115">
-        <v>0.1695849631339212</v>
+        <v>-0.1100347754622497</v>
       </c>
       <c r="J115">
-        <v>0.7724233605082945</v>
+        <v>0.8006955092450049</v>
       </c>
       <c r="K115">
+        <v>2.55</v>
+      </c>
+      <c r="L115">
+        <v>3.94</v>
+      </c>
+      <c r="M115">
         <v>2.5</v>
       </c>
-      <c r="L115">
+      <c r="N115">
         <v>4.01</v>
       </c>
-      <c r="M115">
-        <v>2.37</v>
-      </c>
-      <c r="N115">
-        <v>3.74</v>
-      </c>
       <c r="O115">
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
     </row>
     <row r="116" spans="1:16">
       <c r="A116" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B116" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C116">
-        <v>2.079346337166745</v>
+        <v>1.988365553274239</v>
       </c>
       <c r="D116" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E116">
-        <v>1.909740327634075</v>
+        <v>1.962421194013839</v>
       </c>
       <c r="F116">
         <v>-1</v>
       </c>
       <c r="G116">
-        <v>0.005940653662833254</v>
+        <v>0.005751634446725762</v>
       </c>
       <c r="H116">
-        <v>0.005570259672365926</v>
+        <v>0.005597578805986161</v>
       </c>
       <c r="I116">
-        <v>0.1696060095326706</v>
+        <v>0.02594435926039984</v>
       </c>
       <c r="J116">
-        <v>0.7722614651333018</v>
+        <v>0.8006955092450049</v>
       </c>
       <c r="K116">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L116">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M116">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N116">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O116">
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6638,99 +6620,99 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C117">
-        <v>2.078211043729365</v>
+        <v>1.903475998145109</v>
       </c>
       <c r="D117" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E117">
-        <v>1.908664069455438</v>
+        <v>2.013407841318734</v>
       </c>
       <c r="F117">
         <v>-1</v>
       </c>
       <c r="G117">
-        <v>0.005941788956270636</v>
+        <v>0.005976524001854891</v>
       </c>
       <c r="H117">
-        <v>0.005571335930544562</v>
+        <v>0.006006592158681266</v>
       </c>
       <c r="I117">
-        <v>0.1695469742739264</v>
+        <v>-0.1099318431736251</v>
       </c>
       <c r="J117">
-        <v>0.772715582508254</v>
+        <v>0.7986368634725065</v>
       </c>
       <c r="K117">
+        <v>2.55</v>
+      </c>
+      <c r="L117">
+        <v>3.94</v>
+      </c>
+      <c r="M117">
         <v>2.5</v>
       </c>
-      <c r="L117">
+      <c r="N117">
         <v>4.01</v>
       </c>
-      <c r="M117">
-        <v>2.37</v>
-      </c>
-      <c r="N117">
-        <v>3.74</v>
-      </c>
       <c r="O117">
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
     </row>
     <row r="118" spans="1:16">
       <c r="A118" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B118" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C118">
-        <v>2.075878111180319</v>
+        <v>1.99320337083961</v>
       </c>
       <c r="D118" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E118">
-        <v>1.906452449398942</v>
+        <v>1.96709431991741</v>
       </c>
       <c r="F118">
         <v>-1</v>
       </c>
       <c r="G118">
-        <v>0.005944121888819681</v>
+        <v>0.005746796629160391</v>
       </c>
       <c r="H118">
-        <v>0.005573547550601058</v>
+        <v>0.00559290568008259</v>
       </c>
       <c r="I118">
-        <v>0.1694256617813763</v>
+        <v>0.02610905092219973</v>
       </c>
       <c r="J118">
-        <v>0.7736487555278725</v>
+        <v>0.7986368634725065</v>
       </c>
       <c r="K118">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L118">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M118">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N118">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O118">
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6738,99 +6720,99 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C119">
-        <v>2.0734572921576</v>
+        <v>1.915111220550284</v>
       </c>
       <c r="D119" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E119">
-        <v>1.904157512965405</v>
+        <v>2.024814922108121</v>
       </c>
       <c r="F119">
         <v>-1</v>
       </c>
       <c r="G119">
-        <v>0.005946542707842399</v>
+        <v>0.005964888779449715</v>
       </c>
       <c r="H119">
-        <v>0.005575842487034596</v>
+        <v>0.005995185077891879</v>
       </c>
       <c r="I119">
-        <v>0.1692997791921951</v>
+        <v>-0.1097037015578373</v>
       </c>
       <c r="J119">
-        <v>0.7746170831369599</v>
+        <v>0.7940740311567515</v>
       </c>
       <c r="K119">
+        <v>2.55</v>
+      </c>
+      <c r="L119">
+        <v>3.94</v>
+      </c>
+      <c r="M119">
         <v>2.5</v>
       </c>
-      <c r="L119">
+      <c r="N119">
         <v>4.01</v>
       </c>
-      <c r="M119">
-        <v>2.37</v>
-      </c>
-      <c r="N119">
-        <v>3.74</v>
-      </c>
       <c r="O119">
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
     </row>
     <row r="120" spans="1:16">
       <c r="A120" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B120" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C120">
-        <v>2.069260822060034</v>
+        <v>2.003926026781634</v>
       </c>
       <c r="D120" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E120">
-        <v>1.900179259312913</v>
+        <v>1.977451949274174</v>
       </c>
       <c r="F120">
         <v>-1</v>
       </c>
       <c r="G120">
-        <v>0.005950739177939966</v>
+        <v>0.005736073973218366</v>
       </c>
       <c r="H120">
-        <v>0.005579820740687088</v>
+        <v>0.005582548050725825</v>
       </c>
       <c r="I120">
-        <v>0.1690815627471216</v>
+        <v>0.02647407750746011</v>
       </c>
       <c r="J120">
-        <v>0.7762956711759863</v>
+        <v>0.7940740311567515</v>
       </c>
       <c r="K120">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L120">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M120">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N120">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O120">
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -6838,99 +6820,99 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C121">
-        <v>2.064960635460216</v>
+        <v>1.927566816677033</v>
       </c>
       <c r="D121" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E121">
-        <v>1.896102682416285</v>
+        <v>1.988539872100731</v>
       </c>
       <c r="F121">
         <v>-1</v>
       </c>
       <c r="G121">
-        <v>0.005955039364539783</v>
+        <v>0.005952433183322967</v>
       </c>
       <c r="H121">
-        <v>0.005583897317583715</v>
+        <v>0.005571460127899269</v>
       </c>
       <c r="I121">
-        <v>0.1688579530439307</v>
+        <v>-0.06097305542369802</v>
       </c>
       <c r="J121">
-        <v>0.7780157458159134</v>
+        <v>0.7891894836560657</v>
       </c>
       <c r="K121">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="L121">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="M121">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N121">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O121">
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
     </row>
     <row r="122" spans="1:16">
       <c r="A122" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B122" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C122">
-        <v>2.062649927724336</v>
+        <v>2.015404713408246</v>
       </c>
       <c r="D122" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E122">
-        <v>1.893912131482671</v>
+        <v>1.988539872100731</v>
       </c>
       <c r="F122">
         <v>-1</v>
       </c>
       <c r="G122">
-        <v>0.005957350072275664</v>
+        <v>0.005724595286591755</v>
       </c>
       <c r="H122">
-        <v>0.00558608786851733</v>
+        <v>0.005571460127899269</v>
       </c>
       <c r="I122">
-        <v>0.1687377962416654</v>
+        <v>0.02686484130751476</v>
       </c>
       <c r="J122">
-        <v>0.7789400289102656</v>
+        <v>0.7891894836560657</v>
       </c>
       <c r="K122">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L122">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M122">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N122">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O122">
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -6938,99 +6920,99 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C123">
-        <v>2.060340111638369</v>
+        <v>1.931008249436597</v>
       </c>
       <c r="D123" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E123">
-        <v>1.891722425833174</v>
+        <v>1.99160342204748</v>
       </c>
       <c r="F123">
         <v>-1</v>
       </c>
       <c r="G123">
-        <v>0.00595965988836163</v>
+        <v>0.005948991750563403</v>
       </c>
       <c r="H123">
-        <v>0.005588277574166826</v>
+        <v>0.00556839657795252</v>
       </c>
       <c r="I123">
-        <v>0.1686176858051949</v>
+        <v>-0.06059517261088332</v>
       </c>
       <c r="J123">
-        <v>0.7798639553446522</v>
+        <v>0.7878399021817268</v>
       </c>
       <c r="K123">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="L123">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="M123">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N123">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O123">
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
     </row>
     <row r="124" spans="1:16">
       <c r="A124" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B124" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C124">
-        <v>2.058086897870289</v>
+        <v>2.018576229872942</v>
       </c>
       <c r="D124" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E124">
-        <v>1.889586379181034</v>
+        <v>1.99160342204748</v>
       </c>
       <c r="F124">
         <v>-1</v>
       </c>
       <c r="G124">
-        <v>0.00596191310212971</v>
+        <v>0.005721423770127059</v>
       </c>
       <c r="H124">
-        <v>0.005590413620818966</v>
+        <v>0.00556839657795252</v>
       </c>
       <c r="I124">
-        <v>0.1685005186892548</v>
+        <v>0.02697280782546208</v>
       </c>
       <c r="J124">
-        <v>0.7807652408518843</v>
+        <v>0.7878399021817268</v>
       </c>
       <c r="K124">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L124">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M124">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N124">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O124">
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7038,99 +7020,99 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C125">
-        <v>2.054455475290532</v>
+        <v>1.931290596802969</v>
       </c>
       <c r="D125" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E125">
-        <v>1.886143790575425</v>
+        <v>1.99185476656578</v>
       </c>
       <c r="F125">
         <v>-1</v>
       </c>
       <c r="G125">
-        <v>0.005965544524709467</v>
+        <v>0.00594870940319703</v>
       </c>
       <c r="H125">
-        <v>0.005593856209424576</v>
+        <v>0.005568145233434219</v>
       </c>
       <c r="I125">
-        <v>0.1683116847151074</v>
+        <v>-0.06056416976281076</v>
       </c>
       <c r="J125">
-        <v>0.7822178098837871</v>
+        <v>0.7877291777243258</v>
       </c>
       <c r="K125">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="L125">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="M125">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N125">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O125">
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
     </row>
     <row r="126" spans="1:16">
       <c r="A126" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B126" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C126">
-        <v>2.051743125354167</v>
+        <v>2.018836432347834</v>
       </c>
       <c r="D126" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E126">
-        <v>1.88357248283575</v>
+        <v>1.99185476656578</v>
       </c>
       <c r="F126">
         <v>-1</v>
       </c>
       <c r="G126">
-        <v>0.005968256874645833</v>
+        <v>0.005721163567652166</v>
       </c>
       <c r="H126">
-        <v>0.005596427517164251</v>
+        <v>0.005568145233434219</v>
       </c>
       <c r="I126">
-        <v>0.1681706425184164</v>
+        <v>0.02698166578205408</v>
       </c>
       <c r="J126">
-        <v>0.7833027498583333</v>
+        <v>0.7877291777243258</v>
       </c>
       <c r="K126">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L126">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M126">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N126">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O126">
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7138,99 +7120,99 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C127">
-        <v>2.049665109064402</v>
+        <v>1.932400003731856</v>
       </c>
       <c r="D127" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E127">
-        <v>1.881602523393054</v>
+        <v>1.99284235626326</v>
       </c>
       <c r="F127">
         <v>-1</v>
       </c>
       <c r="G127">
-        <v>0.005970334890935598</v>
+        <v>0.005947599996268144</v>
       </c>
       <c r="H127">
-        <v>0.005598397476606946</v>
+        <v>0.00556715764373674</v>
       </c>
       <c r="I127">
-        <v>0.1680625856713482</v>
+        <v>-0.06044235253140373</v>
       </c>
       <c r="J127">
-        <v>0.784133956374239</v>
+        <v>0.7872941161835857</v>
       </c>
       <c r="K127">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="L127">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="M127">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N127">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O127">
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
     </row>
     <row r="128" spans="1:16">
       <c r="A128" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B128" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C128">
-        <v>2.045876432573801</v>
+        <v>2.019858826968574</v>
       </c>
       <c r="D128" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E128">
-        <v>1.878010858079963</v>
+        <v>1.99284235626326</v>
       </c>
       <c r="F128">
         <v>-1</v>
       </c>
       <c r="G128">
-        <v>0.005974123567426199</v>
+        <v>0.005720141173031427</v>
       </c>
       <c r="H128">
-        <v>0.005601989141920037</v>
+        <v>0.00556715764373674</v>
       </c>
       <c r="I128">
-        <v>0.1678655744938371</v>
+        <v>0.02701647070531354</v>
       </c>
       <c r="J128">
-        <v>0.7856494269704796</v>
+        <v>0.7872941161835857</v>
       </c>
       <c r="K128">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L128">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M128">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N128">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O128">
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7238,99 +7220,99 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C129">
-        <v>2.040113864426065</v>
+        <v>1.928867601835406</v>
       </c>
       <c r="D129" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E129">
-        <v>1.87254794347591</v>
+        <v>1.989697825947597</v>
       </c>
       <c r="F129">
         <v>-1</v>
       </c>
       <c r="G129">
-        <v>0.005979886135573935</v>
+        <v>0.005951132398164594</v>
       </c>
       <c r="H129">
-        <v>0.005607452056524091</v>
+        <v>0.005570302174052403</v>
       </c>
       <c r="I129">
-        <v>0.1675659209501552</v>
+        <v>-0.0608302241121903</v>
       </c>
       <c r="J129">
-        <v>0.7879544542295741</v>
+        <v>0.7886793718292525</v>
       </c>
       <c r="K129">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="L129">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="M129">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N129">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O129">
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
     </row>
     <row r="130" spans="1:16">
       <c r="A130" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B130" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C130">
-        <v>2.03513888559835</v>
+        <v>2.016603476201257</v>
       </c>
       <c r="D130" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E130">
-        <v>1.867831663547236</v>
+        <v>1.989697825947597</v>
       </c>
       <c r="F130">
         <v>-1</v>
       </c>
       <c r="G130">
-        <v>0.00598486111440165</v>
+        <v>0.005723396523798744</v>
       </c>
       <c r="H130">
-        <v>0.005612168336452765</v>
+        <v>0.005570302174052403</v>
       </c>
       <c r="I130">
-        <v>0.1673072220511138</v>
+        <v>0.02690565025365999</v>
       </c>
       <c r="J130">
-        <v>0.78994444576066</v>
+        <v>0.7886793718292525</v>
       </c>
       <c r="K130">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L130">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M130">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N130">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O130">
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>151</v>
+        <v>117</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7338,99 +7320,99 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C131">
-        <v>2.027039654230626</v>
+        <v>1.925635063875757</v>
       </c>
       <c r="D131" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E131">
-        <v>1.860153592210634</v>
+        <v>1.986820233332536</v>
       </c>
       <c r="F131">
         <v>-1</v>
       </c>
       <c r="G131">
-        <v>0.005992960345769374</v>
+        <v>0.005954364936124243</v>
       </c>
       <c r="H131">
-        <v>0.005619846407789366</v>
+        <v>0.005573179766667463</v>
       </c>
       <c r="I131">
-        <v>0.1668860620199919</v>
+        <v>-0.06118516945677954</v>
       </c>
       <c r="J131">
-        <v>0.7931841383077493</v>
+        <v>0.7899470337742129</v>
       </c>
       <c r="K131">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="L131">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="M131">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="N131">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O131">
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="132" spans="1:16">
       <c r="A132" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B132" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C132">
-        <v>2.014982057940606</v>
+        <v>2.013624470630599</v>
       </c>
       <c r="D132" t="s">
         <v>47</v>
       </c>
       <c r="E132">
-        <v>1.820543636841833</v>
+        <v>1.986820233332536</v>
       </c>
       <c r="F132">
         <v>-1</v>
       </c>
       <c r="G132">
-        <v>0.006005017942059394</v>
+        <v>0.0057263755293694</v>
       </c>
       <c r="H132">
-        <v>0.005459456363158167</v>
+        <v>0.005573179766667463</v>
       </c>
       <c r="I132">
-        <v>0.1944384210987726</v>
+        <v>0.02680423729806303</v>
       </c>
       <c r="J132">
-        <v>0.7980071768237574</v>
+        <v>0.7899470337742129</v>
       </c>
       <c r="K132">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L132">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M132">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="N132">
-        <v>3.64</v>
+        <v>3.78</v>
       </c>
       <c r="O132">
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7438,99 +7420,2699 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C133">
-        <v>2.006007199100977</v>
+        <v>1.924421367530698</v>
       </c>
       <c r="D133" t="s">
         <v>47</v>
       </c>
       <c r="E133">
-        <v>1.812358565580092</v>
+        <v>1.985739805605759</v>
       </c>
       <c r="F133">
         <v>-1</v>
       </c>
       <c r="G133">
-        <v>0.006013992800899023</v>
+        <v>0.005955578632469301</v>
       </c>
       <c r="H133">
-        <v>0.005467641434419909</v>
+        <v>0.005574260194394241</v>
       </c>
       <c r="I133">
-        <v>0.1936486335208853</v>
+        <v>-0.06131843807506021</v>
       </c>
       <c r="J133">
-        <v>0.8015971203596091</v>
+        <v>0.7904229931252164</v>
       </c>
       <c r="K133">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="L133">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="M133">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="N133">
-        <v>3.64</v>
+        <v>3.78</v>
       </c>
       <c r="O133">
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
     </row>
     <row r="134" spans="1:16">
       <c r="A134" s="1">
+        <v>1</v>
+      </c>
+      <c r="B134" t="s">
+        <v>29</v>
+      </c>
+      <c r="C134">
+        <v>2.012505966155742</v>
+      </c>
+      <c r="D134" t="s">
+        <v>47</v>
+      </c>
+      <c r="E134">
+        <v>1.985739805605759</v>
+      </c>
+      <c r="F134">
+        <v>-1</v>
+      </c>
+      <c r="G134">
+        <v>0.00572749403384426</v>
+      </c>
+      <c r="H134">
+        <v>0.005574260194394241</v>
+      </c>
+      <c r="I134">
+        <v>0.02676616054998293</v>
+      </c>
+      <c r="J134">
+        <v>0.7904229931252164</v>
+      </c>
+      <c r="K134">
+        <v>2.35</v>
+      </c>
+      <c r="L134">
+        <v>3.87</v>
+      </c>
+      <c r="M134">
+        <v>2.27</v>
+      </c>
+      <c r="N134">
+        <v>3.78</v>
+      </c>
+      <c r="O134">
+        <v>1</v>
+      </c>
+      <c r="P134" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16">
+      <c r="A135" s="1">
         <v>0</v>
       </c>
-      <c r="B134" t="s">
-        <v>28</v>
-      </c>
-      <c r="C134">
-        <v>1.989657960367918</v>
-      </c>
-      <c r="D134" t="s">
-        <v>48</v>
-      </c>
-      <c r="E134">
-        <v>1.848261741440824</v>
-      </c>
-      <c r="F134">
-        <v>-1</v>
-      </c>
-      <c r="G134">
-        <v>0.006030342039632082</v>
-      </c>
-      <c r="H134">
-        <v>0.005371738258559176</v>
-      </c>
-      <c r="I134">
-        <v>0.1413962189270934</v>
-      </c>
-      <c r="J134">
-        <v>0.8081368158528327</v>
-      </c>
-      <c r="K134">
+      <c r="B135" t="s">
+        <v>26</v>
+      </c>
+      <c r="C135">
+        <v>1.922633944537091</v>
+      </c>
+      <c r="D135" t="s">
+        <v>47</v>
+      </c>
+      <c r="E135">
+        <v>1.984148648666351</v>
+      </c>
+      <c r="F135">
+        <v>-1</v>
+      </c>
+      <c r="G135">
+        <v>0.00595736605546291</v>
+      </c>
+      <c r="H135">
+        <v>0.005575851351333649</v>
+      </c>
+      <c r="I135">
+        <v>-0.06151470412926052</v>
+      </c>
+      <c r="J135">
+        <v>0.791123943318788</v>
+      </c>
+      <c r="K135">
+        <v>2.55</v>
+      </c>
+      <c r="L135">
+        <v>3.94</v>
+      </c>
+      <c r="M135">
+        <v>2.27</v>
+      </c>
+      <c r="N135">
+        <v>3.78</v>
+      </c>
+      <c r="O135">
+        <v>1</v>
+      </c>
+      <c r="P135" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16">
+      <c r="A136" s="1">
+        <v>1</v>
+      </c>
+      <c r="B136" t="s">
+        <v>29</v>
+      </c>
+      <c r="C136">
+        <v>2.010858733200848</v>
+      </c>
+      <c r="D136" t="s">
+        <v>47</v>
+      </c>
+      <c r="E136">
+        <v>1.984148648666351</v>
+      </c>
+      <c r="F136">
+        <v>-1</v>
+      </c>
+      <c r="G136">
+        <v>0.005729141266799152</v>
+      </c>
+      <c r="H136">
+        <v>0.005575851351333649</v>
+      </c>
+      <c r="I136">
+        <v>0.02671008453449719</v>
+      </c>
+      <c r="J136">
+        <v>0.791123943318788</v>
+      </c>
+      <c r="K136">
+        <v>2.35</v>
+      </c>
+      <c r="L136">
+        <v>3.87</v>
+      </c>
+      <c r="M136">
+        <v>2.27</v>
+      </c>
+      <c r="N136">
+        <v>3.78</v>
+      </c>
+      <c r="O136">
+        <v>1</v>
+      </c>
+      <c r="P136" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16">
+      <c r="A137" s="1">
+        <v>0</v>
+      </c>
+      <c r="B137" t="s">
+        <v>26</v>
+      </c>
+      <c r="C137">
+        <v>1.921462641095741</v>
+      </c>
+      <c r="D137" t="s">
+        <v>47</v>
+      </c>
+      <c r="E137">
+        <v>1.983105958936209</v>
+      </c>
+      <c r="F137">
+        <v>-1</v>
+      </c>
+      <c r="G137">
+        <v>0.005958537358904259</v>
+      </c>
+      <c r="H137">
+        <v>0.005576894041063791</v>
+      </c>
+      <c r="I137">
+        <v>-0.06164331784046717</v>
+      </c>
+      <c r="J137">
+        <v>0.7915832780016702</v>
+      </c>
+      <c r="K137">
+        <v>2.55</v>
+      </c>
+      <c r="L137">
+        <v>3.94</v>
+      </c>
+      <c r="M137">
+        <v>2.27</v>
+      </c>
+      <c r="N137">
+        <v>3.78</v>
+      </c>
+      <c r="O137">
+        <v>1</v>
+      </c>
+      <c r="P137" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16">
+      <c r="A138" s="1">
+        <v>1</v>
+      </c>
+      <c r="B138" t="s">
+        <v>29</v>
+      </c>
+      <c r="C138">
+        <v>2.009779296696075</v>
+      </c>
+      <c r="D138" t="s">
+        <v>47</v>
+      </c>
+      <c r="E138">
+        <v>1.983105958936209</v>
+      </c>
+      <c r="F138">
+        <v>-1</v>
+      </c>
+      <c r="G138">
+        <v>0.005730220703303925</v>
+      </c>
+      <c r="H138">
+        <v>0.005576894041063791</v>
+      </c>
+      <c r="I138">
+        <v>0.02667333775986669</v>
+      </c>
+      <c r="J138">
+        <v>0.7915832780016702</v>
+      </c>
+      <c r="K138">
+        <v>2.35</v>
+      </c>
+      <c r="L138">
+        <v>3.87</v>
+      </c>
+      <c r="M138">
+        <v>2.27</v>
+      </c>
+      <c r="N138">
+        <v>3.78</v>
+      </c>
+      <c r="O138">
+        <v>1</v>
+      </c>
+      <c r="P138" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16">
+      <c r="A139" s="1">
+        <v>0</v>
+      </c>
+      <c r="B139" t="s">
+        <v>31</v>
+      </c>
+      <c r="C139">
+        <v>2.032225684349332</v>
+      </c>
+      <c r="D139" t="s">
+        <v>47</v>
+      </c>
+      <c r="E139">
+        <v>1.984180921389193</v>
+      </c>
+      <c r="F139">
+        <v>-1</v>
+      </c>
+      <c r="G139">
+        <v>0.005987774315650668</v>
+      </c>
+      <c r="H139">
+        <v>0.005575819078610806</v>
+      </c>
+      <c r="I139">
+        <v>0.0480447629601386</v>
+      </c>
+      <c r="J139">
+        <v>0.7911097262602672</v>
+      </c>
+      <c r="K139">
         <v>2.5</v>
       </c>
-      <c r="L134">
+      <c r="L139">
         <v>4.01</v>
       </c>
-      <c r="M134">
-        <v>2.18</v>
-      </c>
-      <c r="N134">
-        <v>3.61</v>
-      </c>
-      <c r="O134">
-        <v>1</v>
-      </c>
-      <c r="P134" t="s">
-        <v>26</v>
+      <c r="M139">
+        <v>2.27</v>
+      </c>
+      <c r="N139">
+        <v>3.78</v>
+      </c>
+      <c r="O139">
+        <v>1</v>
+      </c>
+      <c r="P139" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16">
+      <c r="A140" s="1">
+        <v>1</v>
+      </c>
+      <c r="B140" t="s">
+        <v>29</v>
+      </c>
+      <c r="C140">
+        <v>2.010892143288372</v>
+      </c>
+      <c r="D140" t="s">
+        <v>47</v>
+      </c>
+      <c r="E140">
+        <v>1.984180921389193</v>
+      </c>
+      <c r="F140">
+        <v>-1</v>
+      </c>
+      <c r="G140">
+        <v>0.005729107856711628</v>
+      </c>
+      <c r="H140">
+        <v>0.005575819078610806</v>
+      </c>
+      <c r="I140">
+        <v>0.02671122189917918</v>
+      </c>
+      <c r="J140">
+        <v>0.7911097262602672</v>
+      </c>
+      <c r="K140">
+        <v>2.35</v>
+      </c>
+      <c r="L140">
+        <v>3.87</v>
+      </c>
+      <c r="M140">
+        <v>2.27</v>
+      </c>
+      <c r="N140">
+        <v>3.78</v>
+      </c>
+      <c r="O140">
+        <v>1</v>
+      </c>
+      <c r="P140" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16">
+      <c r="A141" s="1">
+        <v>0</v>
+      </c>
+      <c r="B141" t="s">
+        <v>31</v>
+      </c>
+      <c r="C141">
+        <v>2.033826265263685</v>
+      </c>
+      <c r="D141" t="s">
+        <v>47</v>
+      </c>
+      <c r="E141">
+        <v>1.985634248859426</v>
+      </c>
+      <c r="F141">
+        <v>-1</v>
+      </c>
+      <c r="G141">
+        <v>0.005986173734736314</v>
+      </c>
+      <c r="H141">
+        <v>0.005574365751140573</v>
+      </c>
+      <c r="I141">
+        <v>0.04819201640425885</v>
+      </c>
+      <c r="J141">
+        <v>0.7904694938945258</v>
+      </c>
+      <c r="K141">
+        <v>2.5</v>
+      </c>
+      <c r="L141">
+        <v>4.01</v>
+      </c>
+      <c r="M141">
+        <v>2.27</v>
+      </c>
+      <c r="N141">
+        <v>3.78</v>
+      </c>
+      <c r="O141">
+        <v>1</v>
+      </c>
+      <c r="P141" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16">
+      <c r="A142" s="1">
+        <v>1</v>
+      </c>
+      <c r="B142" t="s">
+        <v>29</v>
+      </c>
+      <c r="C142">
+        <v>2.012396689347864</v>
+      </c>
+      <c r="D142" t="s">
+        <v>47</v>
+      </c>
+      <c r="E142">
+        <v>1.985634248859426</v>
+      </c>
+      <c r="F142">
+        <v>-1</v>
+      </c>
+      <c r="G142">
+        <v>0.005727603310652135</v>
+      </c>
+      <c r="H142">
+        <v>0.005574365751140573</v>
+      </c>
+      <c r="I142">
+        <v>0.02676244048843812</v>
+      </c>
+      <c r="J142">
+        <v>0.7904694938945258</v>
+      </c>
+      <c r="K142">
+        <v>2.35</v>
+      </c>
+      <c r="L142">
+        <v>3.87</v>
+      </c>
+      <c r="M142">
+        <v>2.27</v>
+      </c>
+      <c r="N142">
+        <v>3.78</v>
+      </c>
+      <c r="O142">
+        <v>1</v>
+      </c>
+      <c r="P142" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16">
+      <c r="A143" s="1">
+        <v>0</v>
+      </c>
+      <c r="B143" t="s">
+        <v>31</v>
+      </c>
+      <c r="C143">
+        <v>2.037114148133088</v>
+      </c>
+      <c r="D143" t="s">
+        <v>47</v>
+      </c>
+      <c r="E143">
+        <v>1.988619646504844</v>
+      </c>
+      <c r="F143">
+        <v>-1</v>
+      </c>
+      <c r="G143">
+        <v>0.005982885851866911</v>
+      </c>
+      <c r="H143">
+        <v>0.005571380353495156</v>
+      </c>
+      <c r="I143">
+        <v>0.04849450162824409</v>
+      </c>
+      <c r="J143">
+        <v>0.7891543407467646</v>
+      </c>
+      <c r="K143">
+        <v>2.5</v>
+      </c>
+      <c r="L143">
+        <v>4.01</v>
+      </c>
+      <c r="M143">
+        <v>2.27</v>
+      </c>
+      <c r="N143">
+        <v>3.78</v>
+      </c>
+      <c r="O143">
+        <v>1</v>
+      </c>
+      <c r="P143" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16">
+      <c r="A144" s="1">
+        <v>1</v>
+      </c>
+      <c r="B144" t="s">
+        <v>29</v>
+      </c>
+      <c r="C144">
+        <v>2.015487299245103</v>
+      </c>
+      <c r="D144" t="s">
+        <v>47</v>
+      </c>
+      <c r="E144">
+        <v>1.988619646504844</v>
+      </c>
+      <c r="F144">
+        <v>-1</v>
+      </c>
+      <c r="G144">
+        <v>0.005724512700754897</v>
+      </c>
+      <c r="H144">
+        <v>0.005571380353495156</v>
+      </c>
+      <c r="I144">
+        <v>0.02686765274025893</v>
+      </c>
+      <c r="J144">
+        <v>0.7891543407467646</v>
+      </c>
+      <c r="K144">
+        <v>2.35</v>
+      </c>
+      <c r="L144">
+        <v>3.87</v>
+      </c>
+      <c r="M144">
+        <v>2.27</v>
+      </c>
+      <c r="N144">
+        <v>3.78</v>
+      </c>
+      <c r="O144">
+        <v>1</v>
+      </c>
+      <c r="P144" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16">
+      <c r="A145" s="1">
+        <v>0</v>
+      </c>
+      <c r="B145" t="s">
+        <v>31</v>
+      </c>
+      <c r="C145">
+        <v>2.041024370702765</v>
+      </c>
+      <c r="D145" t="s">
+        <v>47</v>
+      </c>
+      <c r="E145">
+        <v>1.992170128598111</v>
+      </c>
+      <c r="F145">
+        <v>-1</v>
+      </c>
+      <c r="G145">
+        <v>0.005978975629297235</v>
+      </c>
+      <c r="H145">
+        <v>0.005567829871401889</v>
+      </c>
+      <c r="I145">
+        <v>0.04885424210465428</v>
+      </c>
+      <c r="J145">
+        <v>0.7875902517188939</v>
+      </c>
+      <c r="K145">
+        <v>2.5</v>
+      </c>
+      <c r="L145">
+        <v>4.01</v>
+      </c>
+      <c r="M145">
+        <v>2.27</v>
+      </c>
+      <c r="N145">
+        <v>3.78</v>
+      </c>
+      <c r="O145">
+        <v>1</v>
+      </c>
+      <c r="P145" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16">
+      <c r="A146" s="1">
+        <v>1</v>
+      </c>
+      <c r="B146" t="s">
+        <v>29</v>
+      </c>
+      <c r="C146">
+        <v>2.0191629084606</v>
+      </c>
+      <c r="D146" t="s">
+        <v>47</v>
+      </c>
+      <c r="E146">
+        <v>1.992170128598111</v>
+      </c>
+      <c r="F146">
+        <v>-1</v>
+      </c>
+      <c r="G146">
+        <v>0.005720837091539401</v>
+      </c>
+      <c r="H146">
+        <v>0.005567829871401889</v>
+      </c>
+      <c r="I146">
+        <v>0.02699277986248894</v>
+      </c>
+      <c r="J146">
+        <v>0.7875902517188939</v>
+      </c>
+      <c r="K146">
+        <v>2.35</v>
+      </c>
+      <c r="L146">
+        <v>3.87</v>
+      </c>
+      <c r="M146">
+        <v>2.27</v>
+      </c>
+      <c r="N146">
+        <v>3.78</v>
+      </c>
+      <c r="O146">
+        <v>1</v>
+      </c>
+      <c r="P146" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16">
+      <c r="A147" s="1">
+        <v>0</v>
+      </c>
+      <c r="B147" t="s">
+        <v>31</v>
+      </c>
+      <c r="C147">
+        <v>2.042989638697718</v>
+      </c>
+      <c r="D147" t="s">
+        <v>47</v>
+      </c>
+      <c r="E147">
+        <v>1.993954591937528</v>
+      </c>
+      <c r="F147">
+        <v>-1</v>
+      </c>
+      <c r="G147">
+        <v>0.005977010361302281</v>
+      </c>
+      <c r="H147">
+        <v>0.005566045408062472</v>
+      </c>
+      <c r="I147">
+        <v>0.0490350467601901</v>
+      </c>
+      <c r="J147">
+        <v>0.7868041445209126</v>
+      </c>
+      <c r="K147">
+        <v>2.5</v>
+      </c>
+      <c r="L147">
+        <v>4.01</v>
+      </c>
+      <c r="M147">
+        <v>2.27</v>
+      </c>
+      <c r="N147">
+        <v>3.78</v>
+      </c>
+      <c r="O147">
+        <v>1</v>
+      </c>
+      <c r="P147" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16">
+      <c r="A148" s="1">
+        <v>1</v>
+      </c>
+      <c r="B148" t="s">
+        <v>29</v>
+      </c>
+      <c r="C148">
+        <v>2.021010260375856</v>
+      </c>
+      <c r="D148" t="s">
+        <v>47</v>
+      </c>
+      <c r="E148">
+        <v>1.993954591937528</v>
+      </c>
+      <c r="F148">
+        <v>-1</v>
+      </c>
+      <c r="G148">
+        <v>0.005718989739624145</v>
+      </c>
+      <c r="H148">
+        <v>0.005566045408062472</v>
+      </c>
+      <c r="I148">
+        <v>0.02705566843832741</v>
+      </c>
+      <c r="J148">
+        <v>0.7868041445209126</v>
+      </c>
+      <c r="K148">
+        <v>2.35</v>
+      </c>
+      <c r="L148">
+        <v>3.87</v>
+      </c>
+      <c r="M148">
+        <v>2.27</v>
+      </c>
+      <c r="N148">
+        <v>3.78</v>
+      </c>
+      <c r="O148">
+        <v>1</v>
+      </c>
+      <c r="P148" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16">
+      <c r="A149" s="1">
+        <v>0</v>
+      </c>
+      <c r="B149" t="s">
+        <v>31</v>
+      </c>
+      <c r="C149">
+        <v>2.046475047291454</v>
+      </c>
+      <c r="D149" t="s">
+        <v>47</v>
+      </c>
+      <c r="E149">
+        <v>1.99711934294064</v>
+      </c>
+      <c r="F149">
+        <v>-1</v>
+      </c>
+      <c r="G149">
+        <v>0.005973524952708546</v>
+      </c>
+      <c r="H149">
+        <v>0.00556288065705936</v>
+      </c>
+      <c r="I149">
+        <v>0.04935570435081393</v>
+      </c>
+      <c r="J149">
+        <v>0.7854099810834182</v>
+      </c>
+      <c r="K149">
+        <v>2.5</v>
+      </c>
+      <c r="L149">
+        <v>4.01</v>
+      </c>
+      <c r="M149">
+        <v>2.27</v>
+      </c>
+      <c r="N149">
+        <v>3.78</v>
+      </c>
+      <c r="O149">
+        <v>1</v>
+      </c>
+      <c r="P149" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16">
+      <c r="A150" s="1">
+        <v>1</v>
+      </c>
+      <c r="B150" t="s">
+        <v>29</v>
+      </c>
+      <c r="C150">
+        <v>2.024286544453967</v>
+      </c>
+      <c r="D150" t="s">
+        <v>47</v>
+      </c>
+      <c r="E150">
+        <v>1.99711934294064</v>
+      </c>
+      <c r="F150">
+        <v>-1</v>
+      </c>
+      <c r="G150">
+        <v>0.005715713455546033</v>
+      </c>
+      <c r="H150">
+        <v>0.00556288065705936</v>
+      </c>
+      <c r="I150">
+        <v>0.02716720151332686</v>
+      </c>
+      <c r="J150">
+        <v>0.7854099810834182</v>
+      </c>
+      <c r="K150">
+        <v>2.35</v>
+      </c>
+      <c r="L150">
+        <v>3.87</v>
+      </c>
+      <c r="M150">
+        <v>2.27</v>
+      </c>
+      <c r="N150">
+        <v>3.78</v>
+      </c>
+      <c r="O150">
+        <v>1</v>
+      </c>
+      <c r="P150" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16">
+      <c r="A151" s="1">
+        <v>0</v>
+      </c>
+      <c r="B151" t="s">
+        <v>31</v>
+      </c>
+      <c r="C151">
+        <v>2.05115387029975</v>
+      </c>
+      <c r="D151" t="s">
+        <v>47</v>
+      </c>
+      <c r="E151">
+        <v>2.001367714232173</v>
+      </c>
+      <c r="F151">
+        <v>-1</v>
+      </c>
+      <c r="G151">
+        <v>0.00596884612970025</v>
+      </c>
+      <c r="H151">
+        <v>0.005558632285767827</v>
+      </c>
+      <c r="I151">
+        <v>0.04978615606757719</v>
+      </c>
+      <c r="J151">
+        <v>0.7835384518800999</v>
+      </c>
+      <c r="K151">
+        <v>2.5</v>
+      </c>
+      <c r="L151">
+        <v>4.01</v>
+      </c>
+      <c r="M151">
+        <v>2.27</v>
+      </c>
+      <c r="N151">
+        <v>3.78</v>
+      </c>
+      <c r="O151">
+        <v>1</v>
+      </c>
+      <c r="P151" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16">
+      <c r="A152" s="1">
+        <v>1</v>
+      </c>
+      <c r="B152" t="s">
+        <v>29</v>
+      </c>
+      <c r="C152">
+        <v>2.028684638081765</v>
+      </c>
+      <c r="D152" t="s">
+        <v>47</v>
+      </c>
+      <c r="E152">
+        <v>2.001367714232173</v>
+      </c>
+      <c r="F152">
+        <v>-1</v>
+      </c>
+      <c r="G152">
+        <v>0.005711315361918235</v>
+      </c>
+      <c r="H152">
+        <v>0.005558632285767827</v>
+      </c>
+      <c r="I152">
+        <v>0.02731692384959228</v>
+      </c>
+      <c r="J152">
+        <v>0.7835384518800999</v>
+      </c>
+      <c r="K152">
+        <v>2.35</v>
+      </c>
+      <c r="L152">
+        <v>3.87</v>
+      </c>
+      <c r="M152">
+        <v>2.27</v>
+      </c>
+      <c r="N152">
+        <v>3.78</v>
+      </c>
+      <c r="O152">
+        <v>1</v>
+      </c>
+      <c r="P152" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16">
+      <c r="A153" s="1">
+        <v>0</v>
+      </c>
+      <c r="B153" t="s">
+        <v>31</v>
+      </c>
+      <c r="C153">
+        <v>2.052411570940913</v>
+      </c>
+      <c r="D153" t="s">
+        <v>47</v>
+      </c>
+      <c r="E153">
+        <v>2.002509706414348</v>
+      </c>
+      <c r="F153">
+        <v>-1</v>
+      </c>
+      <c r="G153">
+        <v>0.005967588429059087</v>
+      </c>
+      <c r="H153">
+        <v>0.005557490293585651</v>
+      </c>
+      <c r="I153">
+        <v>0.04990186452656431</v>
+      </c>
+      <c r="J153">
+        <v>0.783035371623635</v>
+      </c>
+      <c r="K153">
+        <v>2.5</v>
+      </c>
+      <c r="L153">
+        <v>4.01</v>
+      </c>
+      <c r="M153">
+        <v>2.27</v>
+      </c>
+      <c r="N153">
+        <v>3.78</v>
+      </c>
+      <c r="O153">
+        <v>1</v>
+      </c>
+      <c r="P153" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16">
+      <c r="A154" s="1">
+        <v>1</v>
+      </c>
+      <c r="B154" t="s">
+        <v>29</v>
+      </c>
+      <c r="C154">
+        <v>2.029866876684458</v>
+      </c>
+      <c r="D154" t="s">
+        <v>47</v>
+      </c>
+      <c r="E154">
+        <v>2.002509706414348</v>
+      </c>
+      <c r="F154">
+        <v>-1</v>
+      </c>
+      <c r="G154">
+        <v>0.005710133123315543</v>
+      </c>
+      <c r="H154">
+        <v>0.005557490293585651</v>
+      </c>
+      <c r="I154">
+        <v>0.02735717027010942</v>
+      </c>
+      <c r="J154">
+        <v>0.783035371623635</v>
+      </c>
+      <c r="K154">
+        <v>2.35</v>
+      </c>
+      <c r="L154">
+        <v>3.87</v>
+      </c>
+      <c r="M154">
+        <v>2.27</v>
+      </c>
+      <c r="N154">
+        <v>3.78</v>
+      </c>
+      <c r="O154">
+        <v>1</v>
+      </c>
+      <c r="P154" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16">
+      <c r="A155" s="1">
+        <v>0</v>
+      </c>
+      <c r="B155" t="s">
+        <v>31</v>
+      </c>
+      <c r="C155">
+        <v>2.054065467064709</v>
+      </c>
+      <c r="D155" t="s">
+        <v>47</v>
+      </c>
+      <c r="E155">
+        <v>2.004011444094756</v>
+      </c>
+      <c r="F155">
+        <v>-1</v>
+      </c>
+      <c r="G155">
+        <v>0.005965934532935291</v>
+      </c>
+      <c r="H155">
+        <v>0.005555988555905244</v>
+      </c>
+      <c r="I155">
+        <v>0.05005402296995332</v>
+      </c>
+      <c r="J155">
+        <v>0.7823738131741161</v>
+      </c>
+      <c r="K155">
+        <v>2.5</v>
+      </c>
+      <c r="L155">
+        <v>4.01</v>
+      </c>
+      <c r="M155">
+        <v>2.27</v>
+      </c>
+      <c r="N155">
+        <v>3.78</v>
+      </c>
+      <c r="O155">
+        <v>1</v>
+      </c>
+      <c r="P155" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16">
+      <c r="A156" s="1">
+        <v>1</v>
+      </c>
+      <c r="B156" t="s">
+        <v>29</v>
+      </c>
+      <c r="C156">
+        <v>2.031421539040827</v>
+      </c>
+      <c r="D156" t="s">
+        <v>47</v>
+      </c>
+      <c r="E156">
+        <v>2.004011444094756</v>
+      </c>
+      <c r="F156">
+        <v>-1</v>
+      </c>
+      <c r="G156">
+        <v>0.005708578460959173</v>
+      </c>
+      <c r="H156">
+        <v>0.005555988555905244</v>
+      </c>
+      <c r="I156">
+        <v>0.02741009494607116</v>
+      </c>
+      <c r="J156">
+        <v>0.7823738131741161</v>
+      </c>
+      <c r="K156">
+        <v>2.35</v>
+      </c>
+      <c r="L156">
+        <v>3.87</v>
+      </c>
+      <c r="M156">
+        <v>2.27</v>
+      </c>
+      <c r="N156">
+        <v>3.78</v>
+      </c>
+      <c r="O156">
+        <v>1</v>
+      </c>
+      <c r="P156" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16">
+      <c r="A157" s="1">
+        <v>0</v>
+      </c>
+      <c r="B157" t="s">
+        <v>31</v>
+      </c>
+      <c r="C157">
+        <v>2.057724755182126</v>
+      </c>
+      <c r="D157" t="s">
+        <v>47</v>
+      </c>
+      <c r="E157">
+        <v>2.00733407770537</v>
+      </c>
+      <c r="F157">
+        <v>-1</v>
+      </c>
+      <c r="G157">
+        <v>0.005962275244817874</v>
+      </c>
+      <c r="H157">
+        <v>0.00555266592229463</v>
+      </c>
+      <c r="I157">
+        <v>0.05039067747675574</v>
+      </c>
+      <c r="J157">
+        <v>0.7809100979271496</v>
+      </c>
+      <c r="K157">
+        <v>2.5</v>
+      </c>
+      <c r="L157">
+        <v>4.01</v>
+      </c>
+      <c r="M157">
+        <v>2.27</v>
+      </c>
+      <c r="N157">
+        <v>3.78</v>
+      </c>
+      <c r="O157">
+        <v>1</v>
+      </c>
+      <c r="P157" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16">
+      <c r="A158" s="1">
+        <v>1</v>
+      </c>
+      <c r="B158" t="s">
+        <v>29</v>
+      </c>
+      <c r="C158">
+        <v>2.034861269871199</v>
+      </c>
+      <c r="D158" t="s">
+        <v>47</v>
+      </c>
+      <c r="E158">
+        <v>2.00733407770537</v>
+      </c>
+      <c r="F158">
+        <v>-1</v>
+      </c>
+      <c r="G158">
+        <v>0.005705138730128801</v>
+      </c>
+      <c r="H158">
+        <v>0.00555266592229463</v>
+      </c>
+      <c r="I158">
+        <v>0.02752719216582822</v>
+      </c>
+      <c r="J158">
+        <v>0.7809100979271496</v>
+      </c>
+      <c r="K158">
+        <v>2.35</v>
+      </c>
+      <c r="L158">
+        <v>3.87</v>
+      </c>
+      <c r="M158">
+        <v>2.27</v>
+      </c>
+      <c r="N158">
+        <v>3.78</v>
+      </c>
+      <c r="O158">
+        <v>1</v>
+      </c>
+      <c r="P158" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16">
+      <c r="A159" s="1">
+        <v>0</v>
+      </c>
+      <c r="B159" t="s">
+        <v>31</v>
+      </c>
+      <c r="C159">
+        <v>2.059621791558839</v>
+      </c>
+      <c r="D159" t="s">
+        <v>47</v>
+      </c>
+      <c r="E159">
+        <v>2.009056586735426</v>
+      </c>
+      <c r="F159">
+        <v>-1</v>
+      </c>
+      <c r="G159">
+        <v>0.005960378208441161</v>
+      </c>
+      <c r="H159">
+        <v>0.005550943413264574</v>
+      </c>
+      <c r="I159">
+        <v>0.05056520482341309</v>
+      </c>
+      <c r="J159">
+        <v>0.7801512833764644</v>
+      </c>
+      <c r="K159">
+        <v>2.5</v>
+      </c>
+      <c r="L159">
+        <v>4.01</v>
+      </c>
+      <c r="M159">
+        <v>2.27</v>
+      </c>
+      <c r="N159">
+        <v>3.78</v>
+      </c>
+      <c r="O159">
+        <v>1</v>
+      </c>
+      <c r="P159" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16">
+      <c r="A160" s="1">
+        <v>1</v>
+      </c>
+      <c r="B160" t="s">
+        <v>29</v>
+      </c>
+      <c r="C160">
+        <v>2.036644484065309</v>
+      </c>
+      <c r="D160" t="s">
+        <v>47</v>
+      </c>
+      <c r="E160">
+        <v>2.009056586735426</v>
+      </c>
+      <c r="F160">
+        <v>-1</v>
+      </c>
+      <c r="G160">
+        <v>0.005703355515934692</v>
+      </c>
+      <c r="H160">
+        <v>0.005550943413264574</v>
+      </c>
+      <c r="I160">
+        <v>0.02758789732988287</v>
+      </c>
+      <c r="J160">
+        <v>0.7801512833764644</v>
+      </c>
+      <c r="K160">
+        <v>2.35</v>
+      </c>
+      <c r="L160">
+        <v>3.87</v>
+      </c>
+      <c r="M160">
+        <v>2.27</v>
+      </c>
+      <c r="N160">
+        <v>3.78</v>
+      </c>
+      <c r="O160">
+        <v>1</v>
+      </c>
+      <c r="P160" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16">
+      <c r="A161" s="1">
+        <v>0</v>
+      </c>
+      <c r="B161" t="s">
+        <v>31</v>
+      </c>
+      <c r="C161">
+        <v>2.060612201172958</v>
+      </c>
+      <c r="D161" t="s">
+        <v>47</v>
+      </c>
+      <c r="E161">
+        <v>2.009955878665046</v>
+      </c>
+      <c r="F161">
+        <v>-1</v>
+      </c>
+      <c r="G161">
+        <v>0.005959387798827042</v>
+      </c>
+      <c r="H161">
+        <v>0.005550044121334954</v>
+      </c>
+      <c r="I161">
+        <v>0.05065632250791197</v>
+      </c>
+      <c r="J161">
+        <v>0.7797551195308166</v>
+      </c>
+      <c r="K161">
+        <v>2.5</v>
+      </c>
+      <c r="L161">
+        <v>4.01</v>
+      </c>
+      <c r="M161">
+        <v>2.27</v>
+      </c>
+      <c r="N161">
+        <v>3.78</v>
+      </c>
+      <c r="O161">
+        <v>1</v>
+      </c>
+      <c r="P161" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16">
+      <c r="A162" s="1">
+        <v>1</v>
+      </c>
+      <c r="B162" t="s">
+        <v>29</v>
+      </c>
+      <c r="C162">
+        <v>2.037575469102581</v>
+      </c>
+      <c r="D162" t="s">
+        <v>47</v>
+      </c>
+      <c r="E162">
+        <v>2.009955878665046</v>
+      </c>
+      <c r="F162">
+        <v>-1</v>
+      </c>
+      <c r="G162">
+        <v>0.005702424530897419</v>
+      </c>
+      <c r="H162">
+        <v>0.005550044121334954</v>
+      </c>
+      <c r="I162">
+        <v>0.02761959043753492</v>
+      </c>
+      <c r="J162">
+        <v>0.7797551195308166</v>
+      </c>
+      <c r="K162">
+        <v>2.35</v>
+      </c>
+      <c r="L162">
+        <v>3.87</v>
+      </c>
+      <c r="M162">
+        <v>2.27</v>
+      </c>
+      <c r="N162">
+        <v>3.78</v>
+      </c>
+      <c r="O162">
+        <v>1</v>
+      </c>
+      <c r="P162" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16">
+      <c r="A163" s="1">
+        <v>0</v>
+      </c>
+      <c r="B163" t="s">
+        <v>31</v>
+      </c>
+      <c r="C163">
+        <v>2.062155534027272</v>
+      </c>
+      <c r="D163" t="s">
+        <v>47</v>
+      </c>
+      <c r="E163">
+        <v>2.011357224896764</v>
+      </c>
+      <c r="F163">
+        <v>-1</v>
+      </c>
+      <c r="G163">
+        <v>0.005957844465972727</v>
+      </c>
+      <c r="H163">
+        <v>0.005548642775103236</v>
+      </c>
+      <c r="I163">
+        <v>0.05079830913050865</v>
+      </c>
+      <c r="J163">
+        <v>0.7791377863890909</v>
+      </c>
+      <c r="K163">
+        <v>2.5</v>
+      </c>
+      <c r="L163">
+        <v>4.01</v>
+      </c>
+      <c r="M163">
+        <v>2.27</v>
+      </c>
+      <c r="N163">
+        <v>3.78</v>
+      </c>
+      <c r="O163">
+        <v>1</v>
+      </c>
+      <c r="P163" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16">
+      <c r="A164" s="1">
+        <v>1</v>
+      </c>
+      <c r="B164" t="s">
+        <v>29</v>
+      </c>
+      <c r="C164">
+        <v>2.039026201985636</v>
+      </c>
+      <c r="D164" t="s">
+        <v>47</v>
+      </c>
+      <c r="E164">
+        <v>2.011357224896764</v>
+      </c>
+      <c r="F164">
+        <v>-1</v>
+      </c>
+      <c r="G164">
+        <v>0.005700973798014364</v>
+      </c>
+      <c r="H164">
+        <v>0.005548642775103236</v>
+      </c>
+      <c r="I164">
+        <v>0.02766897708887273</v>
+      </c>
+      <c r="J164">
+        <v>0.7791377863890909</v>
+      </c>
+      <c r="K164">
+        <v>2.35</v>
+      </c>
+      <c r="L164">
+        <v>3.87</v>
+      </c>
+      <c r="M164">
+        <v>2.27</v>
+      </c>
+      <c r="N164">
+        <v>3.78</v>
+      </c>
+      <c r="O164">
+        <v>1</v>
+      </c>
+      <c r="P164" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16">
+      <c r="A165" s="1">
+        <v>0</v>
+      </c>
+      <c r="B165" t="s">
+        <v>31</v>
+      </c>
+      <c r="C165">
+        <v>2.065159805074657</v>
+      </c>
+      <c r="D165" t="s">
+        <v>47</v>
+      </c>
+      <c r="E165">
+        <v>2.014085103007789</v>
+      </c>
+      <c r="F165">
+        <v>-1</v>
+      </c>
+      <c r="G165">
+        <v>0.005954840194925343</v>
+      </c>
+      <c r="H165">
+        <v>0.005545914896992211</v>
+      </c>
+      <c r="I165">
+        <v>0.05107470206686848</v>
+      </c>
+      <c r="J165">
+        <v>0.777936077970137</v>
+      </c>
+      <c r="K165">
+        <v>2.5</v>
+      </c>
+      <c r="L165">
+        <v>4.01</v>
+      </c>
+      <c r="M165">
+        <v>2.27</v>
+      </c>
+      <c r="N165">
+        <v>3.78</v>
+      </c>
+      <c r="O165">
+        <v>1</v>
+      </c>
+      <c r="P165" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16">
+      <c r="A166" s="1">
+        <v>1</v>
+      </c>
+      <c r="B166" t="s">
+        <v>29</v>
+      </c>
+      <c r="C166">
+        <v>2.041850216770178</v>
+      </c>
+      <c r="D166" t="s">
+        <v>47</v>
+      </c>
+      <c r="E166">
+        <v>2.014085103007789</v>
+      </c>
+      <c r="F166">
+        <v>-1</v>
+      </c>
+      <c r="G166">
+        <v>0.005698149783229823</v>
+      </c>
+      <c r="H166">
+        <v>0.005545914896992211</v>
+      </c>
+      <c r="I166">
+        <v>0.02776511376238933</v>
+      </c>
+      <c r="J166">
+        <v>0.777936077970137</v>
+      </c>
+      <c r="K166">
+        <v>2.35</v>
+      </c>
+      <c r="L166">
+        <v>3.87</v>
+      </c>
+      <c r="M166">
+        <v>2.27</v>
+      </c>
+      <c r="N166">
+        <v>3.78</v>
+      </c>
+      <c r="O166">
+        <v>1</v>
+      </c>
+      <c r="P166" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16">
+      <c r="A167" s="1">
+        <v>0</v>
+      </c>
+      <c r="B167" t="s">
+        <v>31</v>
+      </c>
+      <c r="C167">
+        <v>2.066699852252084</v>
+      </c>
+      <c r="D167" t="s">
+        <v>47</v>
+      </c>
+      <c r="E167">
+        <v>2.015483465844892</v>
+      </c>
+      <c r="F167">
+        <v>-1</v>
+      </c>
+      <c r="G167">
+        <v>0.005953300147747916</v>
+      </c>
+      <c r="H167">
+        <v>0.005544516534155107</v>
+      </c>
+      <c r="I167">
+        <v>0.05121638640719173</v>
+      </c>
+      <c r="J167">
+        <v>0.7773200590991663</v>
+      </c>
+      <c r="K167">
+        <v>2.5</v>
+      </c>
+      <c r="L167">
+        <v>4.01</v>
+      </c>
+      <c r="M167">
+        <v>2.27</v>
+      </c>
+      <c r="N167">
+        <v>3.78</v>
+      </c>
+      <c r="O167">
+        <v>1</v>
+      </c>
+      <c r="P167" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16">
+      <c r="A168" s="1">
+        <v>1</v>
+      </c>
+      <c r="B168" t="s">
+        <v>29</v>
+      </c>
+      <c r="C168">
+        <v>2.043297861116959</v>
+      </c>
+      <c r="D168" t="s">
+        <v>47</v>
+      </c>
+      <c r="E168">
+        <v>2.015483465844892</v>
+      </c>
+      <c r="F168">
+        <v>-1</v>
+      </c>
+      <c r="G168">
+        <v>0.005696702138883041</v>
+      </c>
+      <c r="H168">
+        <v>0.005544516534155107</v>
+      </c>
+      <c r="I168">
+        <v>0.02781439527206686</v>
+      </c>
+      <c r="J168">
+        <v>0.7773200590991663</v>
+      </c>
+      <c r="K168">
+        <v>2.35</v>
+      </c>
+      <c r="L168">
+        <v>3.87</v>
+      </c>
+      <c r="M168">
+        <v>2.27</v>
+      </c>
+      <c r="N168">
+        <v>3.78</v>
+      </c>
+      <c r="O168">
+        <v>1</v>
+      </c>
+      <c r="P168" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16">
+      <c r="A169" s="1">
+        <v>0</v>
+      </c>
+      <c r="B169" t="s">
+        <v>31</v>
+      </c>
+      <c r="C169">
+        <v>2.069529129524661</v>
+      </c>
+      <c r="D169" t="s">
+        <v>47</v>
+      </c>
+      <c r="E169">
+        <v>2.018052449608391</v>
+      </c>
+      <c r="F169">
+        <v>-1</v>
+      </c>
+      <c r="G169">
+        <v>0.00595047087047534</v>
+      </c>
+      <c r="H169">
+        <v>0.005541947550391608</v>
+      </c>
+      <c r="I169">
+        <v>0.05147667991626914</v>
+      </c>
+      <c r="J169">
+        <v>0.7761883481901358</v>
+      </c>
+      <c r="K169">
+        <v>2.5</v>
+      </c>
+      <c r="L169">
+        <v>4.01</v>
+      </c>
+      <c r="M169">
+        <v>2.27</v>
+      </c>
+      <c r="N169">
+        <v>3.78</v>
+      </c>
+      <c r="O169">
+        <v>1</v>
+      </c>
+      <c r="P169" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16">
+      <c r="A170" s="1">
+        <v>1</v>
+      </c>
+      <c r="B170" t="s">
+        <v>29</v>
+      </c>
+      <c r="C170">
+        <v>2.045957381753181</v>
+      </c>
+      <c r="D170" t="s">
+        <v>47</v>
+      </c>
+      <c r="E170">
+        <v>2.018052449608391</v>
+      </c>
+      <c r="F170">
+        <v>-1</v>
+      </c>
+      <c r="G170">
+        <v>0.00569404261824682</v>
+      </c>
+      <c r="H170">
+        <v>0.005541947550391608</v>
+      </c>
+      <c r="I170">
+        <v>0.02790493214478929</v>
+      </c>
+      <c r="J170">
+        <v>0.7761883481901358</v>
+      </c>
+      <c r="K170">
+        <v>2.35</v>
+      </c>
+      <c r="L170">
+        <v>3.87</v>
+      </c>
+      <c r="M170">
+        <v>2.27</v>
+      </c>
+      <c r="N170">
+        <v>3.78</v>
+      </c>
+      <c r="O170">
+        <v>1</v>
+      </c>
+      <c r="P170" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16">
+      <c r="A171" s="1">
+        <v>0</v>
+      </c>
+      <c r="B171" t="s">
+        <v>31</v>
+      </c>
+      <c r="C171">
+        <v>2.072833064946989</v>
+      </c>
+      <c r="D171" t="s">
+        <v>47</v>
+      </c>
+      <c r="E171">
+        <v>2.021052422971866</v>
+      </c>
+      <c r="F171">
+        <v>-1</v>
+      </c>
+      <c r="G171">
+        <v>0.00594716693505301</v>
+      </c>
+      <c r="H171">
+        <v>0.005538947577028134</v>
+      </c>
+      <c r="I171">
+        <v>0.05178064197512322</v>
+      </c>
+      <c r="J171">
+        <v>0.7748667740212044</v>
+      </c>
+      <c r="K171">
+        <v>2.5</v>
+      </c>
+      <c r="L171">
+        <v>4.01</v>
+      </c>
+      <c r="M171">
+        <v>2.27</v>
+      </c>
+      <c r="N171">
+        <v>3.78</v>
+      </c>
+      <c r="O171">
+        <v>1</v>
+      </c>
+      <c r="P171" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16">
+      <c r="A172" s="1">
+        <v>1</v>
+      </c>
+      <c r="B172" t="s">
+        <v>29</v>
+      </c>
+      <c r="C172">
+        <v>2.04906308105017</v>
+      </c>
+      <c r="D172" t="s">
+        <v>47</v>
+      </c>
+      <c r="E172">
+        <v>2.021052422971866</v>
+      </c>
+      <c r="F172">
+        <v>-1</v>
+      </c>
+      <c r="G172">
+        <v>0.005690936918949831</v>
+      </c>
+      <c r="H172">
+        <v>0.005538947577028134</v>
+      </c>
+      <c r="I172">
+        <v>0.02801065807830394</v>
+      </c>
+      <c r="J172">
+        <v>0.7748667740212044</v>
+      </c>
+      <c r="K172">
+        <v>2.35</v>
+      </c>
+      <c r="L172">
+        <v>3.87</v>
+      </c>
+      <c r="M172">
+        <v>2.27</v>
+      </c>
+      <c r="N172">
+        <v>3.78</v>
+      </c>
+      <c r="O172">
+        <v>1</v>
+      </c>
+      <c r="P172" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16">
+      <c r="A173" s="1">
+        <v>0</v>
+      </c>
+      <c r="B173" t="s">
+        <v>31</v>
+      </c>
+      <c r="C173">
+        <v>2.076110072462908</v>
+      </c>
+      <c r="D173" t="s">
+        <v>47</v>
+      </c>
+      <c r="E173">
+        <v>2.02402794579632</v>
+      </c>
+      <c r="F173">
+        <v>-1</v>
+      </c>
+      <c r="G173">
+        <v>0.005943889927537092</v>
+      </c>
+      <c r="H173">
+        <v>0.005535972054203679</v>
+      </c>
+      <c r="I173">
+        <v>0.0520821266665874</v>
+      </c>
+      <c r="J173">
+        <v>0.7735559710148369</v>
+      </c>
+      <c r="K173">
+        <v>2.5</v>
+      </c>
+      <c r="L173">
+        <v>4.01</v>
+      </c>
+      <c r="M173">
+        <v>2.27</v>
+      </c>
+      <c r="N173">
+        <v>3.78</v>
+      </c>
+      <c r="O173">
+        <v>1</v>
+      </c>
+      <c r="P173" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16">
+      <c r="A174" s="1">
+        <v>1</v>
+      </c>
+      <c r="B174" t="s">
+        <v>29</v>
+      </c>
+      <c r="C174">
+        <v>2.052143468115133</v>
+      </c>
+      <c r="D174" t="s">
+        <v>47</v>
+      </c>
+      <c r="E174">
+        <v>2.02402794579632</v>
+      </c>
+      <c r="F174">
+        <v>-1</v>
+      </c>
+      <c r="G174">
+        <v>0.005687856531884867</v>
+      </c>
+      <c r="H174">
+        <v>0.005535972054203679</v>
+      </c>
+      <c r="I174">
+        <v>0.0281155223188132</v>
+      </c>
+      <c r="J174">
+        <v>0.7735559710148369</v>
+      </c>
+      <c r="K174">
+        <v>2.35</v>
+      </c>
+      <c r="L174">
+        <v>3.87</v>
+      </c>
+      <c r="M174">
+        <v>2.27</v>
+      </c>
+      <c r="N174">
+        <v>3.78</v>
+      </c>
+      <c r="O174">
+        <v>1</v>
+      </c>
+      <c r="P174" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16">
+      <c r="A175" s="1">
+        <v>0</v>
+      </c>
+      <c r="B175" t="s">
+        <v>31</v>
+      </c>
+      <c r="C175">
+        <v>2.078101340295269</v>
+      </c>
+      <c r="D175" t="s">
+        <v>47</v>
+      </c>
+      <c r="E175">
+        <v>2.025836016988104</v>
+      </c>
+      <c r="F175">
+        <v>-1</v>
+      </c>
+      <c r="G175">
+        <v>0.00594189865970473</v>
+      </c>
+      <c r="H175">
+        <v>0.005534163983011896</v>
+      </c>
+      <c r="I175">
+        <v>0.05226532330716482</v>
+      </c>
+      <c r="J175">
+        <v>0.7727594638818923</v>
+      </c>
+      <c r="K175">
+        <v>2.5</v>
+      </c>
+      <c r="L175">
+        <v>4.01</v>
+      </c>
+      <c r="M175">
+        <v>2.27</v>
+      </c>
+      <c r="N175">
+        <v>3.78</v>
+      </c>
+      <c r="O175">
+        <v>1</v>
+      </c>
+      <c r="P175" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16">
+      <c r="A176" s="1">
+        <v>1</v>
+      </c>
+      <c r="B176" t="s">
+        <v>29</v>
+      </c>
+      <c r="C176">
+        <v>2.054015259877553</v>
+      </c>
+      <c r="D176" t="s">
+        <v>47</v>
+      </c>
+      <c r="E176">
+        <v>2.025836016988104</v>
+      </c>
+      <c r="F176">
+        <v>-1</v>
+      </c>
+      <c r="G176">
+        <v>0.005685984740122448</v>
+      </c>
+      <c r="H176">
+        <v>0.005534163983011896</v>
+      </c>
+      <c r="I176">
+        <v>0.02817924288944873</v>
+      </c>
+      <c r="J176">
+        <v>0.7727594638818923</v>
+      </c>
+      <c r="K176">
+        <v>2.35</v>
+      </c>
+      <c r="L176">
+        <v>3.87</v>
+      </c>
+      <c r="M176">
+        <v>2.27</v>
+      </c>
+      <c r="N176">
+        <v>3.78</v>
+      </c>
+      <c r="O176">
+        <v>1</v>
+      </c>
+      <c r="P176" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16">
+      <c r="A177" s="1">
+        <v>0</v>
+      </c>
+      <c r="B177" t="s">
+        <v>31</v>
+      </c>
+      <c r="C177">
+        <v>2.078941598729263</v>
+      </c>
+      <c r="D177" t="s">
+        <v>47</v>
+      </c>
+      <c r="E177">
+        <v>2.026598971646171</v>
+      </c>
+      <c r="F177">
+        <v>-1</v>
+      </c>
+      <c r="G177">
+        <v>0.005941058401270736</v>
+      </c>
+      <c r="H177">
+        <v>0.005533401028353828</v>
+      </c>
+      <c r="I177">
+        <v>0.05234262708309201</v>
+      </c>
+      <c r="J177">
+        <v>0.7724233605082945</v>
+      </c>
+      <c r="K177">
+        <v>2.5</v>
+      </c>
+      <c r="L177">
+        <v>4.01</v>
+      </c>
+      <c r="M177">
+        <v>2.27</v>
+      </c>
+      <c r="N177">
+        <v>3.78</v>
+      </c>
+      <c r="O177">
+        <v>1</v>
+      </c>
+      <c r="P177" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16">
+      <c r="A178" s="1">
+        <v>1</v>
+      </c>
+      <c r="B178" t="s">
+        <v>29</v>
+      </c>
+      <c r="C178">
+        <v>2.054805102805508</v>
+      </c>
+      <c r="D178" t="s">
+        <v>47</v>
+      </c>
+      <c r="E178">
+        <v>2.026598971646171</v>
+      </c>
+      <c r="F178">
+        <v>-1</v>
+      </c>
+      <c r="G178">
+        <v>0.005685194897194492</v>
+      </c>
+      <c r="H178">
+        <v>0.005533401028353828</v>
+      </c>
+      <c r="I178">
+        <v>0.02820613115933668</v>
+      </c>
+      <c r="J178">
+        <v>0.7724233605082945</v>
+      </c>
+      <c r="K178">
+        <v>2.35</v>
+      </c>
+      <c r="L178">
+        <v>3.87</v>
+      </c>
+      <c r="M178">
+        <v>2.27</v>
+      </c>
+      <c r="N178">
+        <v>3.78</v>
+      </c>
+      <c r="O178">
+        <v>1</v>
+      </c>
+      <c r="P178" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16">
+      <c r="A179" s="1">
+        <v>0</v>
+      </c>
+      <c r="B179" t="s">
+        <v>31</v>
+      </c>
+      <c r="C179">
+        <v>2.079346337166745</v>
+      </c>
+      <c r="D179" t="s">
+        <v>47</v>
+      </c>
+      <c r="E179">
+        <v>2.026966474147405</v>
+      </c>
+      <c r="F179">
+        <v>-1</v>
+      </c>
+      <c r="G179">
+        <v>0.005940653662833254</v>
+      </c>
+      <c r="H179">
+        <v>0.005533033525852595</v>
+      </c>
+      <c r="I179">
+        <v>0.05237986301934061</v>
+      </c>
+      <c r="J179">
+        <v>0.7722614651333018</v>
+      </c>
+      <c r="K179">
+        <v>2.5</v>
+      </c>
+      <c r="L179">
+        <v>4.01</v>
+      </c>
+      <c r="M179">
+        <v>2.27</v>
+      </c>
+      <c r="N179">
+        <v>3.78</v>
+      </c>
+      <c r="O179">
+        <v>1</v>
+      </c>
+      <c r="P179" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16">
+      <c r="A180" s="1">
+        <v>1</v>
+      </c>
+      <c r="B180" t="s">
+        <v>29</v>
+      </c>
+      <c r="C180">
+        <v>2.055185556936741</v>
+      </c>
+      <c r="D180" t="s">
+        <v>47</v>
+      </c>
+      <c r="E180">
+        <v>2.026966474147405</v>
+      </c>
+      <c r="F180">
+        <v>-1</v>
+      </c>
+      <c r="G180">
+        <v>0.00568481444306326</v>
+      </c>
+      <c r="H180">
+        <v>0.005533033525852595</v>
+      </c>
+      <c r="I180">
+        <v>0.02821908278933627</v>
+      </c>
+      <c r="J180">
+        <v>0.7722614651333018</v>
+      </c>
+      <c r="K180">
+        <v>2.35</v>
+      </c>
+      <c r="L180">
+        <v>3.87</v>
+      </c>
+      <c r="M180">
+        <v>2.27</v>
+      </c>
+      <c r="N180">
+        <v>3.78</v>
+      </c>
+      <c r="O180">
+        <v>1</v>
+      </c>
+      <c r="P180" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16">
+      <c r="A181" s="1">
+        <v>0</v>
+      </c>
+      <c r="B181" t="s">
+        <v>31</v>
+      </c>
+      <c r="C181">
+        <v>2.078211043729365</v>
+      </c>
+      <c r="D181" t="s">
+        <v>47</v>
+      </c>
+      <c r="E181">
+        <v>2.025935627706263</v>
+      </c>
+      <c r="F181">
+        <v>-1</v>
+      </c>
+      <c r="G181">
+        <v>0.005941788956270636</v>
+      </c>
+      <c r="H181">
+        <v>0.005534064372293737</v>
+      </c>
+      <c r="I181">
+        <v>0.05227541602310115</v>
+      </c>
+      <c r="J181">
+        <v>0.772715582508254</v>
+      </c>
+      <c r="K181">
+        <v>2.5</v>
+      </c>
+      <c r="L181">
+        <v>4.01</v>
+      </c>
+      <c r="M181">
+        <v>2.27</v>
+      </c>
+      <c r="N181">
+        <v>3.78</v>
+      </c>
+      <c r="O181">
+        <v>1</v>
+      </c>
+      <c r="P181" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16">
+      <c r="A182" s="1">
+        <v>1</v>
+      </c>
+      <c r="B182" t="s">
+        <v>29</v>
+      </c>
+      <c r="C182">
+        <v>2.054118381105603</v>
+      </c>
+      <c r="D182" t="s">
+        <v>47</v>
+      </c>
+      <c r="E182">
+        <v>2.025935627706263</v>
+      </c>
+      <c r="F182">
+        <v>-1</v>
+      </c>
+      <c r="G182">
+        <v>0.005685881618894397</v>
+      </c>
+      <c r="H182">
+        <v>0.005534064372293737</v>
+      </c>
+      <c r="I182">
+        <v>0.02818275339933951</v>
+      </c>
+      <c r="J182">
+        <v>0.772715582508254</v>
+      </c>
+      <c r="K182">
+        <v>2.35</v>
+      </c>
+      <c r="L182">
+        <v>3.87</v>
+      </c>
+      <c r="M182">
+        <v>2.27</v>
+      </c>
+      <c r="N182">
+        <v>3.78</v>
+      </c>
+      <c r="O182">
+        <v>1</v>
+      </c>
+      <c r="P182" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16">
+      <c r="A183" s="1">
+        <v>0</v>
+      </c>
+      <c r="B183" t="s">
+        <v>31</v>
+      </c>
+      <c r="C183">
+        <v>2.075878111180319</v>
+      </c>
+      <c r="D183" t="s">
+        <v>47</v>
+      </c>
+      <c r="E183">
+        <v>2.023817324951729</v>
+      </c>
+      <c r="F183">
+        <v>-1</v>
+      </c>
+      <c r="G183">
+        <v>0.005944121888819681</v>
+      </c>
+      <c r="H183">
+        <v>0.00553618267504827</v>
+      </c>
+      <c r="I183">
+        <v>0.05206078622858934</v>
+      </c>
+      <c r="J183">
+        <v>0.7736487555278725</v>
+      </c>
+      <c r="K183">
+        <v>2.5</v>
+      </c>
+      <c r="L183">
+        <v>4.01</v>
+      </c>
+      <c r="M183">
+        <v>2.27</v>
+      </c>
+      <c r="N183">
+        <v>3.78</v>
+      </c>
+      <c r="O183">
+        <v>1</v>
+      </c>
+      <c r="P183" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16">
+      <c r="A184" s="1">
+        <v>0</v>
+      </c>
+      <c r="B184" t="s">
+        <v>31</v>
+      </c>
+      <c r="C184">
+        <v>2.0734572921576</v>
+      </c>
+      <c r="D184" t="s">
+        <v>47</v>
+      </c>
+      <c r="E184">
+        <v>2.021619221279101</v>
+      </c>
+      <c r="F184">
+        <v>-1</v>
+      </c>
+      <c r="G184">
+        <v>0.005946542707842399</v>
+      </c>
+      <c r="H184">
+        <v>0.005538380778720898</v>
+      </c>
+      <c r="I184">
+        <v>0.05183807087849912</v>
+      </c>
+      <c r="J184">
+        <v>0.7746170831369599</v>
+      </c>
+      <c r="K184">
+        <v>2.5</v>
+      </c>
+      <c r="L184">
+        <v>4.01</v>
+      </c>
+      <c r="M184">
+        <v>2.27</v>
+      </c>
+      <c r="N184">
+        <v>3.78</v>
+      </c>
+      <c r="O184">
+        <v>1</v>
+      </c>
+      <c r="P184" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16">
+      <c r="A185" s="1">
+        <v>0</v>
+      </c>
+      <c r="B185" t="s">
+        <v>31</v>
+      </c>
+      <c r="C185">
+        <v>2.069260822060034</v>
+      </c>
+      <c r="D185" t="s">
+        <v>47</v>
+      </c>
+      <c r="E185">
+        <v>2.017808826430511</v>
+      </c>
+      <c r="F185">
+        <v>-1</v>
+      </c>
+      <c r="G185">
+        <v>0.005950739177939966</v>
+      </c>
+      <c r="H185">
+        <v>0.005542191173569489</v>
+      </c>
+      <c r="I185">
+        <v>0.05145199562952296</v>
+      </c>
+      <c r="J185">
+        <v>0.7762956711759863</v>
+      </c>
+      <c r="K185">
+        <v>2.5</v>
+      </c>
+      <c r="L185">
+        <v>4.01</v>
+      </c>
+      <c r="M185">
+        <v>2.27</v>
+      </c>
+      <c r="N185">
+        <v>3.78</v>
+      </c>
+      <c r="O185">
+        <v>1</v>
+      </c>
+      <c r="P185" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16">
+      <c r="A186" s="1">
+        <v>0</v>
+      </c>
+      <c r="B186" t="s">
+        <v>31</v>
+      </c>
+      <c r="C186">
+        <v>2.064960635460216</v>
+      </c>
+      <c r="D186" t="s">
+        <v>47</v>
+      </c>
+      <c r="E186">
+        <v>2.013904256997876</v>
+      </c>
+      <c r="F186">
+        <v>-1</v>
+      </c>
+      <c r="G186">
+        <v>0.005955039364539783</v>
+      </c>
+      <c r="H186">
+        <v>0.005546095743002123</v>
+      </c>
+      <c r="I186">
+        <v>0.05105637846233968</v>
+      </c>
+      <c r="J186">
+        <v>0.7780157458159134</v>
+      </c>
+      <c r="K186">
+        <v>2.5</v>
+      </c>
+      <c r="L186">
+        <v>4.01</v>
+      </c>
+      <c r="M186">
+        <v>2.27</v>
+      </c>
+      <c r="N186">
+        <v>3.78</v>
+      </c>
+      <c r="O186">
+        <v>1</v>
+      </c>
+      <c r="P186" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01618-601618.xlsx
+++ b/s60_signal/position-01618-601618.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="147">
   <si>
     <t>trade_time</t>
   </si>
@@ -91,12 +91,12 @@
     <t>2021-07-29</t>
   </si>
   <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-07-23</t>
-  </si>
-  <si>
     <t>2021-01-15</t>
   </si>
   <si>
@@ -121,6 +121,9 @@
     <t>2021-03-03</t>
   </si>
   <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
     <t>2016-12-30</t>
   </si>
   <si>
@@ -151,13 +154,10 @@
     <t>2021-01-20</t>
   </si>
   <si>
-    <t>2021-01-22</t>
-  </si>
-  <si>
     <t>2021-01-26</t>
   </si>
   <si>
-    <t>2021-08-04</t>
+    <t>2021-08-05</t>
   </si>
   <si>
     <t>2021-03-12</t>
@@ -454,10 +454,7 @@
     <t>2021-06-24</t>
   </si>
   <si>
-    <t>2021-06-25</t>
-  </si>
-  <si>
-    <t>2021-06-28</t>
+    <t>2021-07-16</t>
   </si>
 </sst>
 </file>
@@ -815,7 +812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P186"/>
+  <dimension ref="A1:P185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -876,7 +873,7 @@
         <v>2.241636620202809</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2">
         <v>2.083673377356266</v>
@@ -926,7 +923,7 @@
         <v>2.291018963074085</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3">
         <v>2.748932188801797</v>
@@ -976,7 +973,7 @@
         <v>0.1640886968569069</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4">
         <v>0.8087275807852619</v>
@@ -1026,7 +1023,7 @@
         <v>0.1567937244930127</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5">
         <v>0.8087275807852619</v>
@@ -1076,7 +1073,7 @@
         <v>0.06008199184724816</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6">
         <v>0.7118353409391309</v>
@@ -1126,7 +1123,7 @@
         <v>0.05109309920632388</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>0.7118353409391309</v>
@@ -1176,7 +1173,7 @@
         <v>-0.0569506423664734</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>0.6028081963621785</v>
@@ -1226,7 +1223,7 @@
         <v>-0.06784560396853312</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E9">
         <v>0.6028081963621785</v>
@@ -1276,7 +1273,7 @@
         <v>-0.1396452470657845</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E10">
         <v>0.5257702258605397</v>
@@ -1326,7 +1323,7 @@
         <v>-0.1518870263339567</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>0.5257702258605397</v>
@@ -1376,7 +1373,7 @@
         <v>-0.2479133877986754</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E12">
         <v>0.424908049151723</v>
@@ -1426,7 +1423,7 @@
         <v>-0.2619184918344848</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E13">
         <v>0.424908049151723</v>
@@ -1476,7 +1473,7 @@
         <v>-0.3399965939203824</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E14">
         <v>0.3391236942630966</v>
@@ -1526,7 +1523,7 @@
         <v>0.9756011105228968</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15">
         <v>0.8107654111102569</v>
@@ -1576,7 +1573,7 @@
         <v>1.301145679016073</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E16">
         <v>1.173416666670367</v>
@@ -1626,7 +1623,7 @@
         <v>1.296277364845049</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E17">
         <v>1.230890933009092</v>
@@ -1676,7 +1673,7 @@
         <v>0.4435035626339812</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E18">
         <v>0.9439906537348826</v>
@@ -1726,7 +1723,7 @@
         <v>0.4423533289773536</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E19">
         <v>0.9439906537348826</v>
@@ -1776,7 +1773,7 @@
         <v>1.507350128118183</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E20">
         <v>1.202821457299868</v>
@@ -1826,7 +1823,7 @@
         <v>1.54125697476493</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E21">
         <v>1.238224194239853</v>
@@ -1876,7 +1873,7 @@
         <v>1.573438797246031</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E22">
         <v>1.271825803006885</v>
@@ -1926,7 +1923,7 @@
         <v>1.613400857289038</v>
       </c>
       <c r="D23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E23">
         <v>1.313550895110613</v>
@@ -1976,7 +1973,7 @@
         <v>1.593400857289038</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E24">
         <v>1.363275825771058</v>
@@ -2026,7 +2023,7 @@
         <v>1.645344720184119</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E25">
         <v>1.346904046074595</v>
@@ -2076,7 +2073,7 @@
         <v>1.625344720184119</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E26">
         <v>1.394045281942056</v>
@@ -2126,7 +2123,7 @@
         <v>1.68180858461344</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E27">
         <v>1.384976610405209</v>
@@ -2176,7 +2173,7 @@
         <v>1.66180858461344</v>
       </c>
       <c r="D28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E28">
         <v>1.429168563120298</v>
@@ -2226,7 +2223,7 @@
         <v>1.710614904938503</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E29">
         <v>1.415053797803437</v>
@@ -2262,7 +2259,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2276,7 +2273,7 @@
         <v>1.690614904938503</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E30">
         <v>1.456915827551058</v>
@@ -2312,7 +2309,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2326,7 +2323,7 @@
         <v>3.015409387558148</v>
       </c>
       <c r="D31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31">
         <v>3.294391900570977</v>
@@ -2423,40 +2420,40 @@
         <v>25</v>
       </c>
       <c r="C33">
-        <v>2.638017457305502</v>
+        <v>2.754322580645161</v>
       </c>
       <c r="D33" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E33">
-        <v>2.77731688804554</v>
+        <v>2.847571157495255</v>
       </c>
       <c r="F33">
         <v>-1</v>
       </c>
       <c r="G33">
-        <v>0.004841982542694498</v>
+        <v>0.005125677419354839</v>
       </c>
       <c r="H33">
-        <v>0.00496268311195446</v>
+        <v>0.005172428842504745</v>
       </c>
       <c r="I33">
-        <v>-0.1392994307400377</v>
+        <v>-0.0932485768500948</v>
       </c>
       <c r="J33">
         <v>0.4649715370018978</v>
       </c>
       <c r="K33">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="L33">
-        <v>3.74</v>
+        <v>3.94</v>
       </c>
       <c r="M33">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="N33">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="O33">
         <v>1</v>
@@ -2467,34 +2464,34 @@
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C34">
-        <v>2.536354813853479</v>
+        <v>2.638017457305502</v>
       </c>
       <c r="D34" t="s">
         <v>29</v>
       </c>
       <c r="E34">
-        <v>2.676512157196488</v>
+        <v>2.77731688804554</v>
       </c>
       <c r="F34">
         <v>-1</v>
       </c>
       <c r="G34">
-        <v>0.004943645186146522</v>
+        <v>0.004841982542694498</v>
       </c>
       <c r="H34">
-        <v>0.005063487842803513</v>
+        <v>0.00496268311195446</v>
       </c>
       <c r="I34">
-        <v>-0.1401573433430086</v>
+        <v>-0.1392994307400377</v>
       </c>
       <c r="J34">
-        <v>0.5078671671504308</v>
+        <v>0.4649715370018978</v>
       </c>
       <c r="K34">
         <v>2.37</v>
@@ -2512,7 +2509,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2520,31 +2517,31 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C35">
-        <v>2.551891062104373</v>
+        <v>2.644938723766401</v>
       </c>
       <c r="D35" t="s">
         <v>31</v>
       </c>
       <c r="E35">
-        <v>2.649108884416052</v>
+        <v>2.740332082123923</v>
       </c>
       <c r="F35">
         <v>-1</v>
       </c>
       <c r="G35">
-        <v>0.005328108937895627</v>
+        <v>0.005235061276233599</v>
       </c>
       <c r="H35">
-        <v>0.005370891115583948</v>
+        <v>0.005279667917876077</v>
       </c>
       <c r="I35">
-        <v>-0.09721782231167886</v>
+        <v>-0.0953933583575215</v>
       </c>
       <c r="J35">
-        <v>0.5443564462335794</v>
+        <v>0.5078671671504308</v>
       </c>
       <c r="K35">
         <v>2.55</v>
@@ -2562,7 +2559,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2570,31 +2567,31 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C36">
-        <v>2.449875222426417</v>
+        <v>2.536354813853479</v>
       </c>
       <c r="D36" t="s">
         <v>29</v>
       </c>
       <c r="E36">
-        <v>2.590762351351088</v>
+        <v>2.676512157196488</v>
       </c>
       <c r="F36">
         <v>-1</v>
       </c>
       <c r="G36">
-        <v>0.005030124777573583</v>
+        <v>0.004943645186146522</v>
       </c>
       <c r="H36">
-        <v>0.005149237648648912</v>
+        <v>0.005063487842803513</v>
       </c>
       <c r="I36">
-        <v>-0.1408871289246711</v>
+        <v>-0.1401573433430086</v>
       </c>
       <c r="J36">
-        <v>0.5443564462335794</v>
+        <v>0.5078671671504308</v>
       </c>
       <c r="K36">
         <v>2.37</v>
@@ -2612,7 +2609,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2620,31 +2617,31 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C37">
-        <v>2.433094415049971</v>
+        <v>2.551891062104373</v>
       </c>
       <c r="D37" t="s">
         <v>31</v>
       </c>
       <c r="E37">
-        <v>2.532641583382324</v>
+        <v>2.649108884416052</v>
       </c>
       <c r="F37">
         <v>-1</v>
       </c>
       <c r="G37">
-        <v>0.005446905584950029</v>
+        <v>0.005328108937895627</v>
       </c>
       <c r="H37">
-        <v>0.005487358416617676</v>
+        <v>0.005370891115583948</v>
       </c>
       <c r="I37">
-        <v>-0.09954716833235322</v>
+        <v>-0.09721782231167886</v>
       </c>
       <c r="J37">
-        <v>0.5909433666470703</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K37">
         <v>2.55</v>
@@ -2662,7 +2659,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2670,31 +2667,31 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C38">
-        <v>2.339464221046444</v>
+        <v>2.449875222426417</v>
       </c>
       <c r="D38" t="s">
         <v>29</v>
       </c>
       <c r="E38">
-        <v>2.481283088379385</v>
+        <v>2.590762351351088</v>
       </c>
       <c r="F38">
         <v>-1</v>
       </c>
       <c r="G38">
-        <v>0.005140535778953557</v>
+        <v>0.005030124777573583</v>
       </c>
       <c r="H38">
-        <v>0.005258716911620615</v>
+        <v>0.005149237648648912</v>
       </c>
       <c r="I38">
-        <v>-0.1418188673329412</v>
+        <v>-0.1408871289246711</v>
       </c>
       <c r="J38">
-        <v>0.5909433666470703</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K38">
         <v>2.37</v>
@@ -2712,7 +2709,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2720,49 +2717,49 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C39">
-        <v>2.216392009113778</v>
+        <v>2.433094415049971</v>
       </c>
       <c r="D39" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E39">
-        <v>1.951693488288302</v>
+        <v>2.532641583382324</v>
       </c>
       <c r="F39">
         <v>-1</v>
       </c>
       <c r="G39">
-        <v>0.004323607990886222</v>
+        <v>0.005446905584950029</v>
       </c>
       <c r="H39">
-        <v>0.004148306511711698</v>
+        <v>0.005487358416617676</v>
       </c>
       <c r="I39">
-        <v>0.2646985208254764</v>
+        <v>-0.09954716833235322</v>
       </c>
       <c r="J39">
-        <v>0.6385502975068013</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K39">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="L39">
-        <v>3.27</v>
+        <v>3.94</v>
       </c>
       <c r="M39">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="N39">
-        <v>3.05</v>
+        <v>4.01</v>
       </c>
       <c r="O39">
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -2773,90 +2770,90 @@
         <v>26</v>
       </c>
       <c r="C40">
-        <v>2.311696741357657</v>
+        <v>2.339464221046444</v>
       </c>
       <c r="D40" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E40">
-        <v>2.413624256232997</v>
+        <v>2.481283088379385</v>
       </c>
       <c r="F40">
         <v>-1</v>
       </c>
       <c r="G40">
-        <v>0.005568303258642344</v>
+        <v>0.005140535778953557</v>
       </c>
       <c r="H40">
-        <v>0.005606375743767004</v>
+        <v>0.005258716911620615</v>
       </c>
       <c r="I40">
-        <v>-0.10192751487534</v>
+        <v>-0.1418188673329412</v>
       </c>
       <c r="J40">
-        <v>0.6385502975068013</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K40">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="L40">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
       <c r="M40">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="N40">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="O40">
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C41">
-        <v>2.226635794908881</v>
+        <v>2.216392009113778</v>
       </c>
       <c r="D41" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E41">
-        <v>2.369406800859017</v>
+        <v>1.951693488288302</v>
       </c>
       <c r="F41">
         <v>-1</v>
       </c>
       <c r="G41">
-        <v>0.005253364205091119</v>
+        <v>0.004323607990886222</v>
       </c>
       <c r="H41">
-        <v>0.005370593199140983</v>
+        <v>0.004148306511711698</v>
       </c>
       <c r="I41">
-        <v>-0.1427710059501361</v>
+        <v>0.2646985208254764</v>
       </c>
       <c r="J41">
         <v>0.6385502975068013</v>
       </c>
       <c r="K41">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="L41">
-        <v>3.74</v>
+        <v>3.27</v>
       </c>
       <c r="M41">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="N41">
-        <v>3.87</v>
+        <v>3.05</v>
       </c>
       <c r="O41">
         <v>1</v>
@@ -2867,146 +2864,146 @@
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C42">
-        <v>2.122703049542399</v>
+        <v>2.311696741357657</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E42">
-        <v>1.856488467123704</v>
+        <v>2.413624256232997</v>
       </c>
       <c r="F42">
         <v>-1</v>
       </c>
       <c r="G42">
-        <v>0.004397296950457601</v>
+        <v>0.005568303258642344</v>
       </c>
       <c r="H42">
-        <v>0.004103511532876296</v>
+        <v>0.005606375743767004</v>
       </c>
       <c r="I42">
-        <v>0.2662145824186952</v>
+        <v>-0.10192751487534</v>
       </c>
       <c r="J42">
-        <v>0.6892708790652124</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K42">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="L42">
-        <v>3.26</v>
+        <v>3.94</v>
       </c>
       <c r="M42">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="N42">
-        <v>2.98</v>
+        <v>4.01</v>
       </c>
       <c r="O42">
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B43" t="s">
         <v>26</v>
       </c>
       <c r="C43">
-        <v>2.182359258383708</v>
+        <v>2.226635794908881</v>
       </c>
       <c r="D43" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E43">
-        <v>2.286822802336969</v>
+        <v>2.369406800859017</v>
       </c>
       <c r="F43">
         <v>-1</v>
       </c>
       <c r="G43">
-        <v>0.005697640741616292</v>
+        <v>0.005253364205091119</v>
       </c>
       <c r="H43">
-        <v>0.005733177197663031</v>
+        <v>0.005370593199140983</v>
       </c>
       <c r="I43">
-        <v>-0.1044635439532606</v>
+        <v>-0.1427710059501361</v>
       </c>
       <c r="J43">
-        <v>0.6892708790652124</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K43">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="L43">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
       <c r="M43">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="N43">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C44">
-        <v>2.106428016615447</v>
+        <v>2.122703049542399</v>
       </c>
       <c r="D44" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E44">
-        <v>2.250213434196751</v>
+        <v>1.864454088007834</v>
       </c>
       <c r="F44">
         <v>-1</v>
       </c>
       <c r="G44">
-        <v>0.005373571983384554</v>
+        <v>0.004397296950457601</v>
       </c>
       <c r="H44">
-        <v>0.00548978656580325</v>
+        <v>0.004235545911992165</v>
       </c>
       <c r="I44">
-        <v>-0.1437854175813045</v>
+        <v>0.2582489615345647</v>
       </c>
       <c r="J44">
         <v>0.6892708790652124</v>
       </c>
       <c r="K44">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="L44">
-        <v>3.74</v>
+        <v>3.26</v>
       </c>
       <c r="M44">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="N44">
-        <v>3.87</v>
+        <v>3.05</v>
       </c>
       <c r="O44">
         <v>1</v>
@@ -3017,84 +3014,84 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C45">
-        <v>2.037699170124481</v>
+        <v>2.1327030495424</v>
       </c>
       <c r="D45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E45">
-        <v>1.732146473029046</v>
+        <v>1.864454088007834</v>
       </c>
       <c r="F45">
         <v>-1</v>
       </c>
       <c r="G45">
-        <v>0.004482300829875518</v>
+        <v>0.0044072969504576</v>
       </c>
       <c r="H45">
-        <v>0.004087853526970955</v>
+        <v>0.004235545911992165</v>
       </c>
       <c r="I45">
-        <v>0.3055526970954354</v>
+        <v>0.2682489615345653</v>
       </c>
       <c r="J45">
-        <v>0.7407883817427386</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K45">
         <v>1.65</v>
       </c>
       <c r="L45">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="M45">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="N45">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="O45">
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C46">
-        <v>2.050989626556016</v>
+        <v>2.182359258383708</v>
       </c>
       <c r="D46" t="s">
         <v>31</v>
       </c>
       <c r="E46">
-        <v>2.158029045643153</v>
+        <v>2.286822802336969</v>
       </c>
       <c r="F46">
         <v>-1</v>
       </c>
       <c r="G46">
-        <v>0.005829010373443984</v>
+        <v>0.005697640741616292</v>
       </c>
       <c r="H46">
-        <v>0.005861970954356846</v>
+        <v>0.005733177197663031</v>
       </c>
       <c r="I46">
-        <v>-0.1070394190871369</v>
+        <v>-0.1044635439532606</v>
       </c>
       <c r="J46">
-        <v>0.7407883817427386</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K46">
         <v>2.55</v>
@@ -3112,401 +3109,401 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C47">
-        <v>1.939614977812812</v>
+        <v>2.106428016615447</v>
       </c>
       <c r="D47" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E47">
-        <v>1.637628978619619</v>
+        <v>2.250213434196751</v>
       </c>
       <c r="F47">
         <v>-1</v>
       </c>
       <c r="G47">
-        <v>0.004580385022187188</v>
+        <v>0.005373571983384554</v>
       </c>
       <c r="H47">
-        <v>0.004182371021380382</v>
+        <v>0.00548978656580325</v>
       </c>
       <c r="I47">
-        <v>0.301985999193193</v>
+        <v>-0.1437854175813045</v>
       </c>
       <c r="J47">
-        <v>0.8002333467801142</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K47">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="L47">
-        <v>3.26</v>
+        <v>3.74</v>
       </c>
       <c r="M47">
-        <v>1.59</v>
+        <v>2.35</v>
       </c>
       <c r="N47">
-        <v>2.91</v>
+        <v>3.87</v>
       </c>
       <c r="O47">
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C48">
-        <v>1.899404965710709</v>
+        <v>2.037699170124481</v>
       </c>
       <c r="D48" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E48">
-        <v>2.009416633049714</v>
+        <v>1.732146473029046</v>
       </c>
       <c r="F48">
         <v>-1</v>
       </c>
       <c r="G48">
-        <v>0.005980595034289291</v>
+        <v>0.004482300829875518</v>
       </c>
       <c r="H48">
-        <v>0.006010583366950286</v>
+        <v>0.004087853526970955</v>
       </c>
       <c r="I48">
-        <v>-0.1100116673390055</v>
+        <v>0.3055526970954354</v>
       </c>
       <c r="J48">
-        <v>0.8002333467801142</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K48">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="L48">
-        <v>3.94</v>
+        <v>3.26</v>
       </c>
       <c r="M48">
-        <v>2.5</v>
+        <v>1.59</v>
       </c>
       <c r="N48">
-        <v>4.01</v>
+        <v>2.91</v>
       </c>
       <c r="O48">
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C49">
-        <v>1.858458903856472</v>
+        <v>2.050989626556016</v>
       </c>
       <c r="D49" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E49">
-        <v>1.559424034625328</v>
+        <v>2.158029045643153</v>
       </c>
       <c r="F49">
         <v>-1</v>
       </c>
       <c r="G49">
-        <v>0.004661541096143528</v>
+        <v>0.005829010373443984</v>
       </c>
       <c r="H49">
-        <v>0.004260575965374673</v>
+        <v>0.005861970954356846</v>
       </c>
       <c r="I49">
-        <v>0.2990348692311444</v>
+        <v>-0.1070394190871369</v>
       </c>
       <c r="J49">
-        <v>0.8494188461475927</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K49">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="L49">
-        <v>3.26</v>
+        <v>3.94</v>
       </c>
       <c r="M49">
-        <v>1.59</v>
+        <v>2.5</v>
       </c>
       <c r="N49">
-        <v>2.91</v>
+        <v>4.01</v>
       </c>
       <c r="O49">
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C50">
-        <v>1.873865711553157</v>
+        <v>1.939614977812812</v>
       </c>
       <c r="D50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E50">
-        <v>1.851819219244965</v>
+        <v>1.637628978619619</v>
       </c>
       <c r="F50">
         <v>-1</v>
       </c>
       <c r="G50">
-        <v>0.005866134288446843</v>
+        <v>0.004580385022187188</v>
       </c>
       <c r="H50">
-        <v>0.005708180780755035</v>
+        <v>0.004182371021380382</v>
       </c>
       <c r="I50">
-        <v>0.02204649230819267</v>
+        <v>0.301985999193193</v>
       </c>
       <c r="J50">
-        <v>0.8494188461475927</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K50">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="L50">
-        <v>3.87</v>
+        <v>3.26</v>
       </c>
       <c r="M50">
-        <v>2.27</v>
+        <v>1.59</v>
       </c>
       <c r="N50">
-        <v>3.78</v>
+        <v>2.91</v>
       </c>
       <c r="O50">
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C51">
-        <v>1.778043160662217</v>
+        <v>1.899404965710709</v>
       </c>
       <c r="D51" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E51">
-        <v>1.788043160662217</v>
+        <v>2.009416633049714</v>
       </c>
       <c r="F51">
         <v>-1</v>
       </c>
       <c r="G51">
-        <v>0.004741956839337784</v>
+        <v>0.005980595034289291</v>
       </c>
       <c r="H51">
-        <v>0.004751956839337783</v>
+        <v>0.006010583366950286</v>
       </c>
       <c r="I51">
-        <v>-0.01000000000000023</v>
+        <v>-0.1100116673390055</v>
       </c>
       <c r="J51">
-        <v>0.898155660204717</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K51">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="L51">
-        <v>3.26</v>
+        <v>3.94</v>
       </c>
       <c r="M51">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="N51">
-        <v>3.27</v>
+        <v>4.01</v>
       </c>
       <c r="O51">
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C52">
-        <v>1.253223538131198</v>
+        <v>1.858458903856472</v>
       </c>
       <c r="D52" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E52">
-        <v>1.508412028621273</v>
+        <v>1.559424034625328</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G52">
-        <v>0.005366776461868803</v>
+        <v>0.004661541096143528</v>
       </c>
       <c r="H52">
-        <v>0.004831587971378727</v>
+        <v>0.004260575965374673</v>
       </c>
       <c r="I52">
-        <v>0.2551884904900752</v>
+        <v>0.2990348692311444</v>
       </c>
       <c r="J52">
-        <v>0.898155660204717</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K52">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="L52">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="M52">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="N52">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="O52">
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:16">
       <c r="A53" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C53">
-        <v>1.764610849488207</v>
+        <v>1.873865711553157</v>
       </c>
       <c r="D53" t="s">
         <v>47</v>
       </c>
       <c r="E53">
-        <v>1.741186651335292</v>
+        <v>1.779772726936772</v>
       </c>
       <c r="F53">
         <v>-1</v>
       </c>
       <c r="G53">
-        <v>0.006255389150511792</v>
+        <v>0.005866134288446843</v>
       </c>
       <c r="H53">
-        <v>0.005818813348664707</v>
+        <v>0.005500227273063228</v>
       </c>
       <c r="I53">
-        <v>0.02342419815291485</v>
+        <v>0.09409298461638493</v>
       </c>
       <c r="J53">
-        <v>0.898155660204717</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K53">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L53">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M53">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N53">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O53">
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C54">
-        <v>1.759334198518915</v>
+        <v>1.778043160662217</v>
       </c>
       <c r="D54" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="E54">
-        <v>1.741186651335292</v>
+        <v>1.788043160662217</v>
       </c>
       <c r="F54">
         <v>-1</v>
       </c>
       <c r="G54">
-        <v>0.005980665801481085</v>
+        <v>0.004741956839337784</v>
       </c>
       <c r="H54">
-        <v>0.005818813348664707</v>
+        <v>0.004751956839337783</v>
       </c>
       <c r="I54">
-        <v>0.01814754718362277</v>
+        <v>-0.01000000000000023</v>
       </c>
       <c r="J54">
         <v>0.898155660204717</v>
       </c>
       <c r="K54">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="L54">
-        <v>3.87</v>
+        <v>3.26</v>
       </c>
       <c r="M54">
-        <v>2.27</v>
+        <v>1.65</v>
       </c>
       <c r="N54">
-        <v>3.78</v>
+        <v>3.27</v>
       </c>
       <c r="O54">
         <v>1</v>
@@ -3517,34 +3514,34 @@
     </row>
     <row r="55" spans="1:16">
       <c r="A55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B55" t="s">
         <v>30</v>
       </c>
       <c r="C55">
-        <v>1.142741567826858</v>
+        <v>1.253223538131198</v>
       </c>
       <c r="D55" t="s">
         <v>48</v>
       </c>
       <c r="E55">
-        <v>1.419158035143968</v>
+        <v>1.508412028621273</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55">
-        <v>0.005477258432173141</v>
+        <v>0.005366776461868803</v>
       </c>
       <c r="H55">
-        <v>0.004920841964856031</v>
+        <v>0.004831587971378727</v>
       </c>
       <c r="I55">
-        <v>0.2764164673171099</v>
+        <v>0.2551884904900752</v>
       </c>
       <c r="J55">
-        <v>0.9464010620843414</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K55">
         <v>2.29</v>
@@ -3562,39 +3559,39 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B56" t="s">
         <v>31</v>
       </c>
       <c r="C56">
-        <v>1.643997344789146</v>
+        <v>1.764610849488207</v>
       </c>
       <c r="D56" t="s">
         <v>47</v>
       </c>
       <c r="E56">
-        <v>1.631669589068545</v>
+        <v>1.67303910415167</v>
       </c>
       <c r="F56">
         <v>-1</v>
       </c>
       <c r="G56">
-        <v>0.006376002655210854</v>
+        <v>0.006255389150511792</v>
       </c>
       <c r="H56">
-        <v>0.005928330410931455</v>
+        <v>0.005606960895848331</v>
       </c>
       <c r="I56">
-        <v>0.01232775572060163</v>
+        <v>0.09157174533653722</v>
       </c>
       <c r="J56">
-        <v>0.9464010620843414</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K56">
         <v>2.5</v>
@@ -3603,48 +3600,48 @@
         <v>4.01</v>
       </c>
       <c r="M56">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N56">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O56">
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B57" t="s">
         <v>29</v>
       </c>
       <c r="C57">
-        <v>1.645957504101798</v>
+        <v>1.759334198518915</v>
       </c>
       <c r="D57" t="s">
         <v>47</v>
       </c>
       <c r="E57">
-        <v>1.631669589068545</v>
+        <v>1.67303910415167</v>
       </c>
       <c r="F57">
         <v>-1</v>
       </c>
       <c r="G57">
-        <v>0.006094042495898203</v>
+        <v>0.005980665801481085</v>
       </c>
       <c r="H57">
-        <v>0.005928330410931455</v>
+        <v>0.005606960895848331</v>
       </c>
       <c r="I57">
-        <v>0.01428791503325311</v>
+        <v>0.08629509436724514</v>
       </c>
       <c r="J57">
-        <v>0.9464010620843414</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K57">
         <v>2.35</v>
@@ -3653,16 +3650,16 @@
         <v>3.87</v>
       </c>
       <c r="M57">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N57">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O57">
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3673,28 +3670,28 @@
         <v>30</v>
       </c>
       <c r="C58">
-        <v>1.02473295176371</v>
+        <v>1.142741567826858</v>
       </c>
       <c r="D58" t="s">
         <v>48</v>
       </c>
       <c r="E58">
-        <v>1.323823563651905</v>
+        <v>1.419158035143968</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58">
-        <v>0.005595267048236289</v>
+        <v>0.005477258432173141</v>
       </c>
       <c r="H58">
-        <v>0.005016176436348095</v>
+        <v>0.004920841964856031</v>
       </c>
       <c r="I58">
-        <v>0.2990906118881951</v>
+        <v>0.2764164673171099</v>
       </c>
       <c r="J58">
-        <v>0.9979332088368078</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K58">
         <v>2.29</v>
@@ -3712,7 +3709,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3723,28 +3720,28 @@
         <v>31</v>
       </c>
       <c r="C59">
-        <v>1.51516697790798</v>
+        <v>1.643997344789146</v>
       </c>
       <c r="D59" t="s">
         <v>47</v>
       </c>
       <c r="E59">
-        <v>1.514691615940446</v>
+        <v>1.567381674035293</v>
       </c>
       <c r="F59">
         <v>-1</v>
       </c>
       <c r="G59">
-        <v>0.00650483302209202</v>
+        <v>0.006376002655210854</v>
       </c>
       <c r="H59">
-        <v>0.006045308384059553</v>
+        <v>0.005712618325964708</v>
       </c>
       <c r="I59">
-        <v>0.0004753619675339493</v>
+        <v>0.07661567075385367</v>
       </c>
       <c r="J59">
-        <v>0.9979332088368078</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K59">
         <v>2.5</v>
@@ -3753,16 +3750,16 @@
         <v>4.01</v>
       </c>
       <c r="M59">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N59">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O59">
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -3773,28 +3770,28 @@
         <v>29</v>
       </c>
       <c r="C60">
-        <v>1.524856959233502</v>
+        <v>1.645957504101798</v>
       </c>
       <c r="D60" t="s">
         <v>47</v>
       </c>
       <c r="E60">
-        <v>1.514691615940446</v>
+        <v>1.567381674035293</v>
       </c>
       <c r="F60">
         <v>-1</v>
       </c>
       <c r="G60">
-        <v>0.006215143040766499</v>
+        <v>0.006094042495898203</v>
       </c>
       <c r="H60">
-        <v>0.006045308384059553</v>
+        <v>0.005712618325964708</v>
       </c>
       <c r="I60">
-        <v>0.01016534329305552</v>
+        <v>0.07857583006650515</v>
       </c>
       <c r="J60">
-        <v>0.9979332088368078</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K60">
         <v>2.35</v>
@@ -3803,16 +3800,16 @@
         <v>3.87</v>
       </c>
       <c r="M60">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N60">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O60">
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -3820,37 +3817,37 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C61">
-        <v>1.025578495611604</v>
+        <v>1.02473295176371</v>
       </c>
       <c r="D61" t="s">
         <v>48</v>
       </c>
       <c r="E61">
-        <v>1.267956426585794</v>
+        <v>1.323823563651905</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61">
-        <v>0.005734421504388396</v>
+        <v>0.005595267048236289</v>
       </c>
       <c r="H61">
-        <v>0.005072043573414206</v>
+        <v>0.005016176436348095</v>
       </c>
       <c r="I61">
-        <v>0.2423779309741898</v>
+        <v>0.2990906118881951</v>
       </c>
       <c r="J61">
-        <v>1.028131661304976</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K61">
         <v>2.29</v>
       </c>
       <c r="L61">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="M61">
         <v>1.85</v>
@@ -3862,7 +3859,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -3873,28 +3870,28 @@
         <v>31</v>
       </c>
       <c r="C62">
-        <v>1.439670846737559</v>
+        <v>1.51516697790798</v>
       </c>
       <c r="D62" t="s">
         <v>47</v>
       </c>
       <c r="E62">
-        <v>1.446141128837704</v>
+        <v>1.454526272647391</v>
       </c>
       <c r="F62">
         <v>-1</v>
       </c>
       <c r="G62">
-        <v>0.00658032915326244</v>
+        <v>0.00650483302209202</v>
       </c>
       <c r="H62">
-        <v>0.006113858871162297</v>
+        <v>0.005825473727352609</v>
       </c>
       <c r="I62">
-        <v>-0.006470282100144331</v>
+        <v>0.06064070526058929</v>
       </c>
       <c r="J62">
-        <v>1.028131661304976</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K62">
         <v>2.5</v>
@@ -3903,16 +3900,16 @@
         <v>4.01</v>
       </c>
       <c r="M62">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N62">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O62">
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -3923,28 +3920,28 @@
         <v>29</v>
       </c>
       <c r="C63">
-        <v>1.453890595933306</v>
+        <v>1.524856959233502</v>
       </c>
       <c r="D63" t="s">
         <v>47</v>
       </c>
       <c r="E63">
-        <v>1.446141128837704</v>
+        <v>1.454526272647391</v>
       </c>
       <c r="F63">
         <v>-1</v>
       </c>
       <c r="G63">
-        <v>0.006286109404066695</v>
+        <v>0.006215143040766499</v>
       </c>
       <c r="H63">
-        <v>0.006113858871162297</v>
+        <v>0.005825473727352609</v>
       </c>
       <c r="I63">
-        <v>0.007749467095602203</v>
+        <v>0.07033068658611086</v>
       </c>
       <c r="J63">
-        <v>1.028131661304976</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K63">
         <v>2.35</v>
@@ -3953,16 +3950,16 @@
         <v>3.87</v>
       </c>
       <c r="M63">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N63">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O63">
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -3973,28 +3970,28 @@
         <v>32</v>
       </c>
       <c r="C64">
-        <v>0.95505474527386</v>
+        <v>1.025578495611604</v>
       </c>
       <c r="D64" t="s">
         <v>48</v>
       </c>
       <c r="E64">
-        <v>1.210983091160105</v>
+        <v>1.267956426585794</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64">
-        <v>0.00580494525472614</v>
+        <v>0.005734421504388396</v>
       </c>
       <c r="H64">
-        <v>0.005129016908839895</v>
+        <v>0.005072043573414206</v>
       </c>
       <c r="I64">
-        <v>0.2559283458862451</v>
+        <v>0.2423779309741898</v>
       </c>
       <c r="J64">
-        <v>1.058928058832376</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K64">
         <v>2.29</v>
@@ -4012,57 +4009,57 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C65">
-        <v>0.8997461387005035</v>
+        <v>1.453890595933306</v>
       </c>
       <c r="D65" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E65">
-        <v>1.128793874425728</v>
+        <v>1.388391661742102</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G65">
-        <v>0.005860253861299496</v>
+        <v>0.006286109404066695</v>
       </c>
       <c r="H65">
-        <v>0.005071206125574273</v>
+        <v>0.005891608338257898</v>
       </c>
       <c r="I65">
-        <v>0.2290477357252241</v>
+        <v>0.06549893419120334</v>
       </c>
       <c r="J65">
-        <v>1.083080288777073</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K65">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="L65">
-        <v>3.38</v>
+        <v>3.87</v>
       </c>
       <c r="M65">
-        <v>1.82</v>
+        <v>2.19</v>
       </c>
       <c r="N65">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="O65">
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4073,28 +4070,28 @@
         <v>32</v>
       </c>
       <c r="C66">
-        <v>0.9004291893178089</v>
+        <v>0.95505474527386</v>
       </c>
       <c r="D66" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E66">
-        <v>1.129336735615027</v>
+        <v>1.210983091160105</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="G66">
-        <v>0.005859570810682191</v>
+        <v>0.00580494525472614</v>
       </c>
       <c r="H66">
-        <v>0.005070663264384973</v>
+        <v>0.005129016908839895</v>
       </c>
       <c r="I66">
-        <v>0.2289075462972185</v>
+        <v>0.2559283458862451</v>
       </c>
       <c r="J66">
-        <v>1.082782013398337</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K66">
         <v>2.29</v>
@@ -4103,16 +4100,16 @@
         <v>3.38</v>
       </c>
       <c r="M66">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="N66">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="O66">
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4123,28 +4120,28 @@
         <v>32</v>
       </c>
       <c r="C67">
-        <v>0.8995341152947529</v>
+        <v>0.8997461387005035</v>
       </c>
       <c r="D67" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E67">
-        <v>1.128625366740808</v>
+        <v>1.166301465762415</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="G67">
-        <v>0.005860465884705247</v>
+        <v>0.005860253861299496</v>
       </c>
       <c r="H67">
-        <v>0.005071374633259193</v>
+        <v>0.005173698534237585</v>
       </c>
       <c r="I67">
-        <v>0.2290912514460552</v>
+        <v>0.2665553270619117</v>
       </c>
       <c r="J67">
-        <v>1.083172875417138</v>
+        <v>1.083080288777073</v>
       </c>
       <c r="K67">
         <v>2.29</v>
@@ -4153,16 +4150,16 @@
         <v>3.38</v>
       </c>
       <c r="M67">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="N67">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="O67">
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4173,28 +4170,28 @@
         <v>32</v>
       </c>
       <c r="C68">
-        <v>0.8942975364165378</v>
+        <v>0.9004291893178089</v>
       </c>
       <c r="D68" t="s">
         <v>49</v>
       </c>
       <c r="E68">
-        <v>1.124463544226244</v>
+        <v>1.129336735615027</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68">
-        <v>0.005865702463583462</v>
+        <v>0.005859570810682191</v>
       </c>
       <c r="H68">
-        <v>0.005075536455773756</v>
+        <v>0.005070663264384973</v>
       </c>
       <c r="I68">
-        <v>0.2301660078097063</v>
+        <v>0.2289075462972185</v>
       </c>
       <c r="J68">
-        <v>1.085459591084481</v>
+        <v>1.082782013398337</v>
       </c>
       <c r="K68">
         <v>2.29</v>
@@ -4212,7 +4209,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4223,28 +4220,28 @@
         <v>32</v>
       </c>
       <c r="C69">
-        <v>0.823882990348408</v>
+        <v>0.8995341152947529</v>
       </c>
       <c r="D69" t="s">
         <v>49</v>
       </c>
       <c r="E69">
-        <v>1.068500891892621</v>
+        <v>1.128625366740808</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69">
-        <v>0.005936117009651592</v>
+        <v>0.005860465884705247</v>
       </c>
       <c r="H69">
-        <v>0.005131499108107379</v>
+        <v>0.005071374633259193</v>
       </c>
       <c r="I69">
-        <v>0.2446179015442134</v>
+        <v>0.2290912514460552</v>
       </c>
       <c r="J69">
-        <v>1.1162083011579</v>
+        <v>1.083172875417138</v>
       </c>
       <c r="K69">
         <v>2.29</v>
@@ -4262,7 +4259,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4273,28 +4270,28 @@
         <v>32</v>
       </c>
       <c r="C70">
-        <v>0.7552208383877499</v>
+        <v>0.8942975364165378</v>
       </c>
       <c r="D70" t="s">
         <v>49</v>
       </c>
       <c r="E70">
-        <v>1.013930971993758</v>
+        <v>1.124463544226244</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70">
-        <v>0.00600477916161225</v>
+        <v>0.005865702463583462</v>
       </c>
       <c r="H70">
-        <v>0.005186069028006243</v>
+        <v>0.005075536455773756</v>
       </c>
       <c r="I70">
-        <v>0.2587101336060078</v>
+        <v>0.2301660078097063</v>
       </c>
       <c r="J70">
-        <v>1.146191773629804</v>
+        <v>1.085459591084481</v>
       </c>
       <c r="K70">
         <v>2.29</v>
@@ -4312,7 +4309,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4323,28 +4320,28 @@
         <v>32</v>
       </c>
       <c r="C71">
-        <v>0.7164672131147527</v>
+        <v>0.823882990348408</v>
       </c>
       <c r="D71" t="s">
         <v>49</v>
       </c>
       <c r="E71">
-        <v>0.9831311475409823</v>
+        <v>1.068500891892621</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71">
-        <v>0.006043532786885248</v>
+        <v>0.005936117009651592</v>
       </c>
       <c r="H71">
-        <v>0.005216868852459018</v>
+        <v>0.005131499108107379</v>
       </c>
       <c r="I71">
-        <v>0.2666639344262296</v>
+        <v>0.2446179015442134</v>
       </c>
       <c r="J71">
-        <v>1.163114754098361</v>
+        <v>1.1162083011579</v>
       </c>
       <c r="K71">
         <v>2.29</v>
@@ -4362,7 +4359,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4373,28 +4370,28 @@
         <v>32</v>
       </c>
       <c r="C72">
-        <v>0.6498239504652852</v>
+        <v>0.7552208383877499</v>
       </c>
       <c r="D72" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E72">
-        <v>0.5798239504652853</v>
+        <v>1.013930971993758</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72">
-        <v>0.006110176049534715</v>
+        <v>0.00600477916161225</v>
       </c>
       <c r="H72">
-        <v>0.006040176049534715</v>
+        <v>0.005186069028006243</v>
       </c>
       <c r="I72">
-        <v>-0.06999999999999984</v>
+        <v>0.2587101336060078</v>
       </c>
       <c r="J72">
-        <v>1.192216615517343</v>
+        <v>1.146191773629804</v>
       </c>
       <c r="K72">
         <v>2.29</v>
@@ -4403,16 +4400,16 @@
         <v>3.38</v>
       </c>
       <c r="M72">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="N72">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="O72">
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4420,81 +4417,81 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C73">
-        <v>0.5205928926738919</v>
+        <v>0.7164672131147527</v>
       </c>
       <c r="D73" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E73">
-        <v>0.4040417624885522</v>
+        <v>0.9831311475409823</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73">
-        <v>0.006459407107326108</v>
+        <v>0.006043532786885248</v>
       </c>
       <c r="H73">
-        <v>0.006215958237511448</v>
+        <v>0.005216868852459018</v>
       </c>
       <c r="I73">
-        <v>-0.1165511301853397</v>
+        <v>0.2666639344262296</v>
       </c>
       <c r="J73">
-        <v>1.268977396293209</v>
+        <v>1.163114754098361</v>
       </c>
       <c r="K73">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="L73">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="M73">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="N73">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="O73">
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74" spans="1:16">
       <c r="A74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B74" t="s">
         <v>32</v>
       </c>
       <c r="C74">
-        <v>0.474041762488552</v>
+        <v>0.6498239504652852</v>
       </c>
       <c r="D74" t="s">
         <v>30</v>
       </c>
       <c r="E74">
-        <v>0.4040417624885522</v>
+        <v>0.5798239504652853</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74">
-        <v>0.006285958237511447</v>
+        <v>0.006110176049534715</v>
       </c>
       <c r="H74">
-        <v>0.006215958237511448</v>
+        <v>0.006040176049534715</v>
       </c>
       <c r="I74">
         <v>-0.06999999999999984</v>
       </c>
       <c r="J74">
-        <v>1.268977396293209</v>
+        <v>1.192216615517343</v>
       </c>
       <c r="K74">
         <v>2.29</v>
@@ -4512,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4523,28 +4520,28 @@
         <v>33</v>
       </c>
       <c r="C75">
-        <v>0.3774746016246668</v>
+        <v>0.5205928926738919</v>
       </c>
       <c r="D75" t="s">
         <v>30</v>
       </c>
       <c r="E75">
-        <v>0.2639815545814042</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75">
-        <v>0.006602525398375333</v>
+        <v>0.006459407107326108</v>
       </c>
       <c r="H75">
-        <v>0.006356018445418596</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I75">
-        <v>-0.1134930470432627</v>
+        <v>-0.1165511301853397</v>
       </c>
       <c r="J75">
-        <v>1.330139059134758</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K75">
         <v>2.34</v>
@@ -4562,7 +4559,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4573,28 +4570,28 @@
         <v>32</v>
       </c>
       <c r="C76">
-        <v>0.333981554581404</v>
+        <v>0.474041762488552</v>
       </c>
       <c r="D76" t="s">
         <v>30</v>
       </c>
       <c r="E76">
-        <v>0.2639815545814042</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76">
-        <v>0.006426018445418596</v>
+        <v>0.006285958237511447</v>
       </c>
       <c r="H76">
-        <v>0.006356018445418596</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I76">
         <v>-0.06999999999999984</v>
       </c>
       <c r="J76">
-        <v>1.330139059134758</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K76">
         <v>2.29</v>
@@ -4612,7 +4609,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4623,28 +4620,28 @@
         <v>33</v>
       </c>
       <c r="C77">
-        <v>0.2442505289553791</v>
+        <v>0.3774746016246668</v>
       </c>
       <c r="D77" t="s">
         <v>30</v>
       </c>
       <c r="E77">
-        <v>0.1336041501315459</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77">
-        <v>0.006735749471044622</v>
+        <v>0.006602525398375333</v>
       </c>
       <c r="H77">
-        <v>0.006486395849868455</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I77">
-        <v>-0.1106463788238332</v>
+        <v>-0.1134930470432627</v>
       </c>
       <c r="J77">
-        <v>1.387072423523342</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K77">
         <v>2.34</v>
@@ -4662,7 +4659,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4670,5149 +4667,5149 @@
         <v>1</v>
       </c>
       <c r="B78" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C78">
-        <v>0.2977942894248136</v>
+        <v>0.333981554581404</v>
       </c>
       <c r="D78" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E78">
-        <v>0.5755281891875166</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="G78">
-        <v>0.006262205710575186</v>
+        <v>0.006426018445418596</v>
       </c>
       <c r="H78">
-        <v>0.005624471810812484</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I78">
-        <v>0.277733899762703</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J78">
-        <v>1.387072423523342</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K78">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="L78">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="M78">
-        <v>1.82</v>
+        <v>2.29</v>
       </c>
       <c r="N78">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="O78">
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:16">
       <c r="A79" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B79" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C79">
-        <v>2.01907486979781</v>
+        <v>0.4202010228602702</v>
       </c>
       <c r="D79" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E79">
-        <v>1.972239981776411</v>
+        <v>0.6791469123747405</v>
       </c>
       <c r="F79">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G79">
-        <v>0.00600092513020219</v>
+        <v>0.00613979897713973</v>
       </c>
       <c r="H79">
-        <v>0.005587760018223588</v>
+        <v>0.00552085308762526</v>
       </c>
       <c r="I79">
-        <v>0.04683488802139846</v>
+        <v>0.2589458895144703</v>
       </c>
       <c r="J79">
-        <v>0.7963700520808761</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K79">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="L79">
-        <v>4.01</v>
+        <v>3.28</v>
       </c>
       <c r="M79">
-        <v>2.27</v>
+        <v>1.82</v>
       </c>
       <c r="N79">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="O79">
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C80">
-        <v>1.998530377609941</v>
+        <v>0.2442505289553791</v>
       </c>
       <c r="D80" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E80">
-        <v>1.972239981776411</v>
+        <v>0.1336041501315459</v>
       </c>
       <c r="F80">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G80">
-        <v>0.005741469622390059</v>
+        <v>0.006735749471044622</v>
       </c>
       <c r="H80">
-        <v>0.005587760018223588</v>
+        <v>0.006486395849868455</v>
       </c>
       <c r="I80">
-        <v>0.0262903958335301</v>
+        <v>-0.1106463788238332</v>
       </c>
       <c r="J80">
-        <v>0.7963700520808761</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K80">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="L80">
-        <v>3.87</v>
+        <v>3.49</v>
       </c>
       <c r="M80">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="N80">
-        <v>3.78</v>
+        <v>3.31</v>
       </c>
       <c r="O80">
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="81" spans="1:16">
       <c r="A81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B81" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C81">
-        <v>1.899440167721166</v>
+        <v>0.2977942894248136</v>
       </c>
       <c r="D81" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E81">
-        <v>1.963501639500802</v>
+        <v>0.5755281891875166</v>
       </c>
       <c r="F81">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G81">
-        <v>0.005980559832278834</v>
+        <v>0.006262205710575186</v>
       </c>
       <c r="H81">
-        <v>0.005596498360499197</v>
+        <v>0.005624471810812484</v>
       </c>
       <c r="I81">
-        <v>-0.06406147177963639</v>
+        <v>0.277733899762703</v>
       </c>
       <c r="J81">
-        <v>0.8002195420701311</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K81">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="L81">
-        <v>3.94</v>
+        <v>3.28</v>
       </c>
       <c r="M81">
-        <v>2.27</v>
+        <v>1.82</v>
       </c>
       <c r="N81">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="O81">
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82" spans="1:16">
       <c r="A82" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C82">
-        <v>1.989484076135192</v>
+        <v>2.01907486979781</v>
       </c>
       <c r="D82" t="s">
         <v>47</v>
       </c>
       <c r="E82">
-        <v>1.963501639500802</v>
+        <v>1.895949585942882</v>
       </c>
       <c r="F82">
         <v>-1</v>
       </c>
       <c r="G82">
-        <v>0.005750515923864809</v>
+        <v>0.00600092513020219</v>
       </c>
       <c r="H82">
-        <v>0.005596498360499197</v>
+        <v>0.005384050414057119</v>
       </c>
       <c r="I82">
-        <v>0.02598243663438993</v>
+        <v>0.1231252838549279</v>
       </c>
       <c r="J82">
-        <v>0.8002195420701311</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K82">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L82">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M82">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N82">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O82">
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B83" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C83">
-        <v>1.886137504764086</v>
+        <v>1.998530377609941</v>
       </c>
       <c r="D83" t="s">
         <v>47</v>
       </c>
       <c r="E83">
-        <v>1.951659661103716</v>
+        <v>1.895949585942882</v>
       </c>
       <c r="F83">
         <v>-1</v>
       </c>
       <c r="G83">
-        <v>0.005993862495235914</v>
+        <v>0.005741469622390059</v>
       </c>
       <c r="H83">
-        <v>0.005608340338896283</v>
+        <v>0.005384050414057119</v>
       </c>
       <c r="I83">
-        <v>-0.06552215633962954</v>
+        <v>0.1025807916670596</v>
       </c>
       <c r="J83">
-        <v>0.8054362726415348</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K83">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L83">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M83">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N83">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O83">
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C84">
-        <v>1.977224759292393</v>
+        <v>2.009451144824672</v>
       </c>
       <c r="D84" t="s">
         <v>47</v>
       </c>
       <c r="E84">
-        <v>1.951659661103716</v>
+        <v>1.887519202866413</v>
       </c>
       <c r="F84">
         <v>-1</v>
       </c>
       <c r="G84">
-        <v>0.005762775240707607</v>
+        <v>0.006010548855175328</v>
       </c>
       <c r="H84">
-        <v>0.005608340338896283</v>
+        <v>0.005392480797133587</v>
       </c>
       <c r="I84">
-        <v>0.02556509818867747</v>
+        <v>0.1219319419582592</v>
       </c>
       <c r="J84">
-        <v>0.8054362726415348</v>
+        <v>0.8002195420701311</v>
       </c>
       <c r="K84">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L84">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M84">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N84">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O84">
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="85" spans="1:16">
       <c r="A85" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B85" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C85">
-        <v>1.870809096426398</v>
+        <v>1.989484076135192</v>
       </c>
       <c r="D85" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E85">
-        <v>1.981381467084703</v>
+        <v>1.887519202866413</v>
       </c>
       <c r="F85">
         <v>-1</v>
       </c>
       <c r="G85">
-        <v>0.006009190903573602</v>
+        <v>0.005750515923864809</v>
       </c>
       <c r="H85">
-        <v>0.006038618532915297</v>
+        <v>0.005392480797133587</v>
       </c>
       <c r="I85">
-        <v>-0.1105723706583053</v>
+        <v>0.101964873268779</v>
       </c>
       <c r="J85">
-        <v>0.8114474131661186</v>
+        <v>0.8002195420701311</v>
       </c>
       <c r="K85">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L85">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M85">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N85">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O85">
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C86">
-        <v>1.963098579059621</v>
+        <v>1.996409318396163</v>
       </c>
       <c r="D86" t="s">
         <v>47</v>
       </c>
       <c r="E86">
-        <v>1.938014372112911</v>
+        <v>1.876094562915039</v>
       </c>
       <c r="F86">
         <v>-1</v>
       </c>
       <c r="G86">
-        <v>0.005776901420940379</v>
+        <v>0.006023590681603837</v>
       </c>
       <c r="H86">
-        <v>0.005621985627887089</v>
+        <v>0.005403905437084961</v>
       </c>
       <c r="I86">
-        <v>0.02508420694671076</v>
+        <v>0.1203147554811237</v>
       </c>
       <c r="J86">
-        <v>0.8114474131661186</v>
+        <v>0.8054362726415348</v>
       </c>
       <c r="K86">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L86">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M86">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N86">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O86">
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C87">
-        <v>1.866530632283299</v>
+        <v>1.977224759292393</v>
       </c>
       <c r="D87" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E87">
-        <v>1.977186894395391</v>
+        <v>1.876094562915039</v>
       </c>
       <c r="F87">
         <v>-1</v>
       </c>
       <c r="G87">
-        <v>0.0060134693677167</v>
+        <v>0.005762775240707607</v>
       </c>
       <c r="H87">
-        <v>0.006042813105604609</v>
+        <v>0.005403905437084961</v>
       </c>
       <c r="I87">
-        <v>-0.1106562621120917</v>
+        <v>0.1011301963773543</v>
       </c>
       <c r="J87">
-        <v>0.8131252422418436</v>
+        <v>0.8054362726415348</v>
       </c>
       <c r="K87">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L87">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M87">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N87">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O87">
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C88">
-        <v>1.959155680731668</v>
+        <v>1.870809096426398</v>
       </c>
       <c r="D88" t="s">
         <v>47</v>
       </c>
       <c r="E88">
-        <v>1.934205700111015</v>
+        <v>1.8629301651662</v>
       </c>
       <c r="F88">
         <v>-1</v>
       </c>
       <c r="G88">
-        <v>0.005780844319268333</v>
+        <v>0.006009190903573602</v>
       </c>
       <c r="H88">
-        <v>0.005625794299888985</v>
+        <v>0.0054170698348338</v>
       </c>
       <c r="I88">
-        <v>0.02494998062065279</v>
+        <v>0.007878931260197453</v>
       </c>
       <c r="J88">
-        <v>0.8131252422418436</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K88">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L88">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M88">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N88">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O88">
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="89" spans="1:16">
       <c r="A89" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B89" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C89">
-        <v>1.861370672015807</v>
+        <v>1.963098579059621</v>
       </c>
       <c r="D89" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E89">
-        <v>1.972128109819418</v>
+        <v>1.8629301651662</v>
       </c>
       <c r="F89">
         <v>-1</v>
       </c>
       <c r="G89">
-        <v>0.006018629327984194</v>
+        <v>0.005776901420940379</v>
       </c>
       <c r="H89">
-        <v>0.006047871890180582</v>
+        <v>0.0054170698348338</v>
       </c>
       <c r="I89">
-        <v>-0.1107574378036111</v>
+        <v>0.1001684138934209</v>
       </c>
       <c r="J89">
-        <v>0.8151487560722326</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K89">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L89">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M89">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N89">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O89">
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C90">
-        <v>1.954400423230253</v>
+        <v>1.866530632283299</v>
       </c>
       <c r="D90" t="s">
         <v>47</v>
       </c>
       <c r="E90">
-        <v>1.929612323716032</v>
+        <v>1.859255719490363</v>
       </c>
       <c r="F90">
         <v>-1</v>
       </c>
       <c r="G90">
-        <v>0.005785599576769747</v>
+        <v>0.0060134693677167</v>
       </c>
       <c r="H90">
-        <v>0.005630387676283969</v>
+        <v>0.005420744280509638</v>
       </c>
       <c r="I90">
-        <v>0.02478809951422156</v>
+        <v>0.00727491279293635</v>
       </c>
       <c r="J90">
-        <v>0.8151487560722326</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K90">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L90">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M90">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N90">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O90">
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B91" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C91">
-        <v>1.851301116496863</v>
+        <v>1.959155680731668</v>
       </c>
       <c r="D91" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E91">
-        <v>1.962255996565552</v>
+        <v>1.859255719490363</v>
       </c>
       <c r="F91">
         <v>-1</v>
       </c>
       <c r="G91">
-        <v>0.006028698883503138</v>
+        <v>0.005780844319268333</v>
       </c>
       <c r="H91">
-        <v>0.006057744003434448</v>
+        <v>0.005420744280509638</v>
       </c>
       <c r="I91">
-        <v>-0.110954880068689</v>
+        <v>0.09989996124130496</v>
       </c>
       <c r="J91">
-        <v>0.8190976013737793</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K91">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L91">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M91">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N91">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O91">
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C92">
-        <v>1.945120636771619</v>
+        <v>1.861370672015807</v>
       </c>
       <c r="D92" t="s">
         <v>47</v>
       </c>
       <c r="E92">
-        <v>1.920648444881521</v>
+        <v>1.854824224201811</v>
       </c>
       <c r="F92">
         <v>-1</v>
       </c>
       <c r="G92">
-        <v>0.005794879363228382</v>
+        <v>0.006018629327984194</v>
       </c>
       <c r="H92">
-        <v>0.005639351555118479</v>
+        <v>0.00542517577579819</v>
       </c>
       <c r="I92">
-        <v>0.02447219189009786</v>
+        <v>0.00654644781399627</v>
       </c>
       <c r="J92">
-        <v>0.8190976013737793</v>
+        <v>0.8151487560722326</v>
       </c>
       <c r="K92">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L92">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M92">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N92">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O92">
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:16">
       <c r="A93" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B93" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C93">
-        <v>1.855461116431831</v>
+        <v>1.954400423230253</v>
       </c>
       <c r="D93" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E93">
-        <v>1.966334427874344</v>
+        <v>1.854824224201811</v>
       </c>
       <c r="F93">
         <v>-1</v>
       </c>
       <c r="G93">
-        <v>0.006024538883568169</v>
+        <v>0.005785599576769747</v>
       </c>
       <c r="H93">
-        <v>0.006053665572125656</v>
+        <v>0.00542517577579819</v>
       </c>
       <c r="I93">
-        <v>-0.1108733114425124</v>
+        <v>0.09957619902844272</v>
       </c>
       <c r="J93">
-        <v>0.8174662288502623</v>
+        <v>0.8151487560722326</v>
       </c>
       <c r="K93">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L93">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M93">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N93">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O93">
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94" spans="1:16">
       <c r="A94" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C94">
-        <v>1.948954362201884</v>
+        <v>1.851301116496863</v>
       </c>
       <c r="D94" t="s">
         <v>47</v>
       </c>
       <c r="E94">
-        <v>1.924351660509904</v>
+        <v>1.846176252991423</v>
       </c>
       <c r="F94">
         <v>-1</v>
       </c>
       <c r="G94">
-        <v>0.005791045637798117</v>
+        <v>0.006028698883503138</v>
       </c>
       <c r="H94">
-        <v>0.005635648339490096</v>
+        <v>0.005433823747008577</v>
       </c>
       <c r="I94">
-        <v>0.02460270169197942</v>
+        <v>0.005124863505439281</v>
       </c>
       <c r="J94">
-        <v>0.8174662288502623</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K94">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L94">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M94">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N94">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O94">
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="95" spans="1:16">
       <c r="A95" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B95" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C95">
-        <v>1.85652914973731</v>
+        <v>1.945120636771619</v>
       </c>
       <c r="D95" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E95">
-        <v>1.967381519350304</v>
+        <v>1.846176252991423</v>
       </c>
       <c r="F95">
         <v>-1</v>
       </c>
       <c r="G95">
-        <v>0.006023470850262691</v>
+        <v>0.005794879363228382</v>
       </c>
       <c r="H95">
-        <v>0.006052618480649696</v>
+        <v>0.005433823747008577</v>
       </c>
       <c r="I95">
-        <v>-0.1108523696129935</v>
+        <v>0.09894438378019532</v>
       </c>
       <c r="J95">
-        <v>0.8170473922598784</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K95">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L95">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M95">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N95">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O95">
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="96" spans="1:16">
       <c r="A96" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C96">
-        <v>1.949938628189286</v>
+        <v>1.855461116431831</v>
       </c>
       <c r="D96" t="s">
         <v>47</v>
       </c>
       <c r="E96">
-        <v>1.925302419570076</v>
+        <v>1.849748958817926</v>
       </c>
       <c r="F96">
         <v>-1</v>
       </c>
       <c r="G96">
-        <v>0.005790061371810714</v>
+        <v>0.006024538883568169</v>
       </c>
       <c r="H96">
-        <v>0.005634697580429924</v>
+        <v>0.005430251041182075</v>
       </c>
       <c r="I96">
-        <v>0.02463620861921001</v>
+        <v>0.005712157613905644</v>
       </c>
       <c r="J96">
-        <v>0.8170473922598784</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K96">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L96">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M96">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N96">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O96">
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:16">
       <c r="A97" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B97" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C97">
-        <v>1.854953516327912</v>
+        <v>1.948954362201884</v>
       </c>
       <c r="D97" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E97">
-        <v>1.965836780713639</v>
+        <v>1.849748958817926</v>
       </c>
       <c r="F97">
         <v>-1</v>
       </c>
       <c r="G97">
-        <v>0.006025046483672087</v>
+        <v>0.005791045637798117</v>
       </c>
       <c r="H97">
-        <v>0.00605416321928636</v>
+        <v>0.005430251041182075</v>
       </c>
       <c r="I97">
-        <v>-0.1108832643857269</v>
+        <v>0.099205403383958</v>
       </c>
       <c r="J97">
-        <v>0.8176652877145442</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K97">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L97">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M97">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N97">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O97">
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:16">
       <c r="A98" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C98">
-        <v>1.948486573870821</v>
+        <v>1.85652914973731</v>
       </c>
       <c r="D98" t="s">
         <v>47</v>
       </c>
       <c r="E98">
-        <v>1.923899796887985</v>
+        <v>1.850666210950866</v>
       </c>
       <c r="F98">
         <v>-1</v>
       </c>
       <c r="G98">
-        <v>0.00579151342612918</v>
+        <v>0.006023470850262691</v>
       </c>
       <c r="H98">
-        <v>0.005636100203112015</v>
+        <v>0.005429333789049133</v>
       </c>
       <c r="I98">
-        <v>0.02458677698283673</v>
+        <v>0.005862938786443728</v>
       </c>
       <c r="J98">
-        <v>0.8176652877145442</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K98">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L98">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M98">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N98">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O98">
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B99" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C99">
-        <v>1.853898035926949</v>
+        <v>1.949938628189286</v>
       </c>
       <c r="D99" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E99">
-        <v>1.964801996006813</v>
+        <v>1.850666210950866</v>
       </c>
       <c r="F99">
         <v>-1</v>
       </c>
       <c r="G99">
-        <v>0.00602610196407305</v>
+        <v>0.005790061371810714</v>
       </c>
       <c r="H99">
-        <v>0.006055198003993187</v>
+        <v>0.005429333789049133</v>
       </c>
       <c r="I99">
-        <v>-0.1109039600798636</v>
+        <v>0.09927241723841917</v>
       </c>
       <c r="J99">
-        <v>0.8180792015972748</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K99">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L99">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M99">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N99">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O99">
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:16">
       <c r="A100" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C100">
-        <v>1.947513876246404</v>
+        <v>1.854953516327912</v>
       </c>
       <c r="D100" t="s">
         <v>47</v>
       </c>
       <c r="E100">
-        <v>1.922960212374186</v>
+        <v>1.849313019905148</v>
       </c>
       <c r="F100">
         <v>-1</v>
       </c>
       <c r="G100">
-        <v>0.005792486123753596</v>
+        <v>0.006025046483672087</v>
       </c>
       <c r="H100">
-        <v>0.005637039787625813</v>
+        <v>0.005430686980094852</v>
       </c>
       <c r="I100">
-        <v>0.02455366387221836</v>
+        <v>0.005640496422764096</v>
       </c>
       <c r="J100">
-        <v>0.8180792015972748</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K100">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L100">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M100">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N100">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O100">
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B101" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C101">
-        <v>1.851157777698763</v>
+        <v>1.948486573870821</v>
       </c>
       <c r="D101" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E101">
-        <v>1.96211546833212</v>
+        <v>1.849313019905148</v>
       </c>
       <c r="F101">
         <v>-1</v>
       </c>
       <c r="G101">
-        <v>0.006028842222301236</v>
+        <v>0.00579151342612918</v>
       </c>
       <c r="H101">
-        <v>0.006057884531667879</v>
+        <v>0.005430686980094852</v>
       </c>
       <c r="I101">
-        <v>-0.1109576906333571</v>
+        <v>0.09917355396567284</v>
       </c>
       <c r="J101">
-        <v>0.8191538126671517</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K101">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L101">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M101">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N101">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O101">
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:16">
       <c r="A102" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C102">
-        <v>1.944988540232194</v>
+        <v>1.853898035926949</v>
       </c>
       <c r="D102" t="s">
         <v>47</v>
       </c>
       <c r="E102">
-        <v>1.920520845245565</v>
+        <v>1.848406548501969</v>
       </c>
       <c r="F102">
         <v>-1</v>
       </c>
       <c r="G102">
-        <v>0.005795011459767806</v>
+        <v>0.00602610196407305</v>
       </c>
       <c r="H102">
-        <v>0.005639479154754435</v>
+        <v>0.005431593451498031</v>
       </c>
       <c r="I102">
-        <v>0.02446769498662826</v>
+        <v>0.005491487424980956</v>
       </c>
       <c r="J102">
-        <v>0.8191538126671517</v>
+        <v>0.8180792015972748</v>
       </c>
       <c r="K102">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L102">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M102">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N102">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O102">
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103" spans="1:16">
       <c r="A103" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B103" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C103">
-        <v>1.858566205293179</v>
+        <v>1.947513876246404</v>
       </c>
       <c r="D103" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E103">
-        <v>1.969378632640371</v>
+        <v>1.848406548501969</v>
       </c>
       <c r="F103">
         <v>-1</v>
       </c>
       <c r="G103">
-        <v>0.006021433794706822</v>
+        <v>0.005792486123753596</v>
       </c>
       <c r="H103">
-        <v>0.006050621367359629</v>
+        <v>0.005431593451498031</v>
       </c>
       <c r="I103">
-        <v>-0.1108124273471924</v>
+        <v>0.09910732774443587</v>
       </c>
       <c r="J103">
-        <v>0.8162485469438515</v>
+        <v>0.8180792015972748</v>
       </c>
       <c r="K103">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L103">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M103">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N103">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O103">
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="104" spans="1:16">
       <c r="A104" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C104">
-        <v>1.951815914681949</v>
+        <v>1.851157777698763</v>
       </c>
       <c r="D104" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E104">
-        <v>1.927115798437457</v>
+        <v>1.96211546833212</v>
       </c>
       <c r="F104">
         <v>-1</v>
       </c>
       <c r="G104">
-        <v>0.005788184085318051</v>
+        <v>0.006028842222301236</v>
       </c>
       <c r="H104">
-        <v>0.005632884201562542</v>
+        <v>0.006057884531667879</v>
       </c>
       <c r="I104">
-        <v>0.02470011624449198</v>
+        <v>-0.1109576906333571</v>
       </c>
       <c r="J104">
-        <v>0.8162485469438515</v>
+        <v>0.8191538126671517</v>
       </c>
       <c r="K104">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L104">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M104">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="N104">
-        <v>3.78</v>
+        <v>4.01</v>
       </c>
       <c r="O104">
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="105" spans="1:16">
       <c r="A105" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B105" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C105">
-        <v>1.868405823240289</v>
+        <v>1.944988540232194</v>
       </c>
       <c r="D105" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E105">
-        <v>1.979025316902244</v>
+        <v>1.846053150258938</v>
       </c>
       <c r="F105">
         <v>-1</v>
       </c>
       <c r="G105">
-        <v>0.006011594176759711</v>
+        <v>0.005795011459767806</v>
       </c>
       <c r="H105">
-        <v>0.006040974683097756</v>
+        <v>0.005433946849741062</v>
       </c>
       <c r="I105">
-        <v>-0.1106194936619547</v>
+        <v>0.09893538997325568</v>
       </c>
       <c r="J105">
-        <v>0.8123898732391025</v>
+        <v>0.8191538126671517</v>
       </c>
       <c r="K105">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L105">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M105">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N105">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O105">
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="106" spans="1:16">
       <c r="A106" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C106">
-        <v>1.960883797888109</v>
+        <v>1.858566205293179</v>
       </c>
       <c r="D106" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E106">
-        <v>1.935874987747237</v>
+        <v>1.969378632640371</v>
       </c>
       <c r="F106">
         <v>-1</v>
       </c>
       <c r="G106">
-        <v>0.005779116202111891</v>
+        <v>0.006021433794706822</v>
       </c>
       <c r="H106">
-        <v>0.005624125012252763</v>
+        <v>0.006050621367359629</v>
       </c>
       <c r="I106">
-        <v>0.02500881014087186</v>
+        <v>-0.1108124273471924</v>
       </c>
       <c r="J106">
-        <v>0.8123898732391025</v>
+        <v>0.8162485469438515</v>
       </c>
       <c r="K106">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L106">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M106">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="N106">
-        <v>3.78</v>
+        <v>4.01</v>
       </c>
       <c r="O106">
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="107" spans="1:16">
       <c r="A107" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B107" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C107">
-        <v>1.873099451459633</v>
+        <v>1.951815914681949</v>
       </c>
       <c r="D107" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E107">
-        <v>1.983626913195719</v>
+        <v>1.852415682192965</v>
       </c>
       <c r="F107">
         <v>-1</v>
       </c>
       <c r="G107">
-        <v>0.006006900548540367</v>
+        <v>0.005788184085318051</v>
       </c>
       <c r="H107">
-        <v>0.00603637308680428</v>
+        <v>0.005427584317807035</v>
       </c>
       <c r="I107">
-        <v>-0.1105274617360856</v>
+        <v>0.09940023248898355</v>
       </c>
       <c r="J107">
-        <v>0.8105492347217125</v>
+        <v>0.8162485469438515</v>
       </c>
       <c r="K107">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L107">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M107">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N107">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O107">
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="108" spans="1:16">
       <c r="A108" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C108">
-        <v>1.965209298403976</v>
+        <v>1.868405823240289</v>
       </c>
       <c r="D108" t="s">
         <v>47</v>
       </c>
       <c r="E108">
-        <v>1.940053237181713</v>
+        <v>1.860866177606366</v>
       </c>
       <c r="F108">
         <v>-1</v>
       </c>
       <c r="G108">
-        <v>0.005774790701596024</v>
+        <v>0.006011594176759711</v>
       </c>
       <c r="H108">
-        <v>0.005619946762818287</v>
+        <v>0.005419133822393635</v>
       </c>
       <c r="I108">
-        <v>0.02515606122226322</v>
+        <v>0.007539645633923175</v>
       </c>
       <c r="J108">
-        <v>0.8105492347217125</v>
+        <v>0.8123898732391025</v>
       </c>
       <c r="K108">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L108">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M108">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N108">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O108">
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="109" spans="1:16">
       <c r="A109" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B109" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C109">
-        <v>1.880315678845928</v>
+        <v>1.960883797888109</v>
       </c>
       <c r="D109" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E109">
-        <v>1.99070164592738</v>
+        <v>1.860866177606366</v>
       </c>
       <c r="F109">
         <v>-1</v>
       </c>
       <c r="G109">
-        <v>0.005999684321154073</v>
+        <v>0.005779116202111891</v>
       </c>
       <c r="H109">
-        <v>0.006029298354072619</v>
+        <v>0.005419133822393635</v>
       </c>
       <c r="I109">
-        <v>-0.1103859670814522</v>
+        <v>0.1000176202817433</v>
       </c>
       <c r="J109">
-        <v>0.8077193416290479</v>
+        <v>0.8123898732391025</v>
       </c>
       <c r="K109">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L109">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M109">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N109">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O109">
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="110" spans="1:16">
       <c r="A110" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C110">
-        <v>1.971859547171738</v>
+        <v>1.873099451459633</v>
       </c>
       <c r="D110" t="s">
         <v>47</v>
       </c>
       <c r="E110">
-        <v>1.946477094502061</v>
+        <v>1.86489717595945</v>
       </c>
       <c r="F110">
         <v>-1</v>
       </c>
       <c r="G110">
-        <v>0.005768140452828262</v>
+        <v>0.006006900548540367</v>
       </c>
       <c r="H110">
-        <v>0.005613522905497939</v>
+        <v>0.005415102824040551</v>
       </c>
       <c r="I110">
-        <v>0.02538245266967643</v>
+        <v>0.008202275500183154</v>
       </c>
       <c r="J110">
-        <v>0.8077193416290479</v>
+        <v>0.8105492347217125</v>
       </c>
       <c r="K110">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L110">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M110">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N110">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O110">
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111" spans="1:16">
       <c r="A111" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B111" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C111">
-        <v>1.885229059666124</v>
+        <v>1.965209298403976</v>
       </c>
       <c r="D111" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E111">
-        <v>1.995518685947181</v>
+        <v>1.86489717595945</v>
       </c>
       <c r="F111">
         <v>-1</v>
       </c>
       <c r="G111">
-        <v>0.005994770940333876</v>
+        <v>0.005774790701596024</v>
       </c>
       <c r="H111">
-        <v>0.006024481314052819</v>
+        <v>0.005415102824040551</v>
       </c>
       <c r="I111">
-        <v>-0.1102896262810562</v>
+        <v>0.1003121224445258</v>
       </c>
       <c r="J111">
-        <v>0.8057925256211278</v>
+        <v>0.8105492347217125</v>
       </c>
       <c r="K111">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L111">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M111">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N111">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O111">
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="112" spans="1:16">
       <c r="A112" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C112">
-        <v>1.97638756479035</v>
+        <v>1.880315678845928</v>
       </c>
       <c r="D112" t="s">
         <v>47</v>
       </c>
       <c r="E112">
-        <v>1.95085096684004</v>
+        <v>1.871094641832385</v>
       </c>
       <c r="F112">
         <v>-1</v>
       </c>
       <c r="G112">
-        <v>0.005763612435209651</v>
+        <v>0.005999684321154073</v>
       </c>
       <c r="H112">
-        <v>0.00560914903315996</v>
+        <v>0.005408905358167616</v>
       </c>
       <c r="I112">
-        <v>0.02553659795030994</v>
+        <v>0.009221037013542599</v>
       </c>
       <c r="J112">
-        <v>0.8057925256211278</v>
+        <v>0.8077193416290479</v>
       </c>
       <c r="K112">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L112">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M112">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N112">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O112">
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="113" spans="1:16">
       <c r="A113" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B113" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C113">
-        <v>1.891592550259521</v>
+        <v>1.971859547171738</v>
       </c>
       <c r="D113" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E113">
-        <v>2.001757402215216</v>
+        <v>1.871094641832385</v>
       </c>
       <c r="F113">
         <v>-1</v>
       </c>
       <c r="G113">
-        <v>0.00598840744974048</v>
+        <v>0.005768140452828262</v>
       </c>
       <c r="H113">
-        <v>0.006018242597784784</v>
+        <v>0.005408905358167616</v>
       </c>
       <c r="I113">
-        <v>-0.1101648519556955</v>
+        <v>0.1007649053393522</v>
       </c>
       <c r="J113">
-        <v>0.8032970391139135</v>
+        <v>0.8077193416290479</v>
       </c>
       <c r="K113">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L113">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M113">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N113">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O113">
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="114" spans="1:16">
       <c r="A114" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C114">
-        <v>1.982251958082303</v>
+        <v>1.885229059666124</v>
       </c>
       <c r="D114" t="s">
         <v>47</v>
       </c>
       <c r="E114">
-        <v>1.956515721211416</v>
+        <v>1.87531436888973</v>
       </c>
       <c r="F114">
         <v>-1</v>
       </c>
       <c r="G114">
-        <v>0.005757748041917698</v>
+        <v>0.005994770940333876</v>
       </c>
       <c r="H114">
-        <v>0.005603484278788583</v>
+        <v>0.00540468563111027</v>
       </c>
       <c r="I114">
-        <v>0.02573623687088711</v>
+        <v>0.009914690776394064</v>
       </c>
       <c r="J114">
-        <v>0.8032970391139135</v>
+        <v>0.8057925256211278</v>
       </c>
       <c r="K114">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L114">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M114">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N114">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O114">
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="115" spans="1:16">
       <c r="A115" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B115" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C115">
-        <v>1.898226451425238</v>
+        <v>1.97638756479035</v>
       </c>
       <c r="D115" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E115">
-        <v>2.008261226887488</v>
+        <v>1.87531436888973</v>
       </c>
       <c r="F115">
         <v>-1</v>
       </c>
       <c r="G115">
-        <v>0.005981773548574762</v>
+        <v>0.005763612435209651</v>
       </c>
       <c r="H115">
-        <v>0.006011738773112512</v>
+        <v>0.00540468563111027</v>
       </c>
       <c r="I115">
-        <v>-0.1100347754622497</v>
+        <v>0.1010731959006195</v>
       </c>
       <c r="J115">
-        <v>0.8006955092450049</v>
+        <v>0.8057925256211278</v>
       </c>
       <c r="K115">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L115">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M115">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N115">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O115">
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="116" spans="1:16">
       <c r="A116" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C116">
-        <v>1.988365553274239</v>
+        <v>1.891592550259521</v>
       </c>
       <c r="D116" t="s">
         <v>47</v>
       </c>
       <c r="E116">
-        <v>1.962421194013839</v>
+        <v>1.88077948434053</v>
       </c>
       <c r="F116">
         <v>-1</v>
       </c>
       <c r="G116">
-        <v>0.005751634446725762</v>
+        <v>0.00598840744974048</v>
       </c>
       <c r="H116">
-        <v>0.005597578805986161</v>
+        <v>0.005399220515659471</v>
       </c>
       <c r="I116">
-        <v>0.02594435926039984</v>
+        <v>0.01081306591899112</v>
       </c>
       <c r="J116">
-        <v>0.8006955092450049</v>
+        <v>0.8032970391139135</v>
       </c>
       <c r="K116">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L116">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M116">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N116">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O116">
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="117" spans="1:16">
       <c r="A117" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B117" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C117">
-        <v>1.903475998145109</v>
+        <v>1.982251958082303</v>
       </c>
       <c r="D117" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E117">
-        <v>2.013407841318734</v>
+        <v>1.88077948434053</v>
       </c>
       <c r="F117">
         <v>-1</v>
       </c>
       <c r="G117">
-        <v>0.005976524001854891</v>
+        <v>0.005757748041917698</v>
       </c>
       <c r="H117">
-        <v>0.006006592158681266</v>
+        <v>0.005399220515659471</v>
       </c>
       <c r="I117">
-        <v>-0.1099318431736251</v>
+        <v>0.1014724737417736</v>
       </c>
       <c r="J117">
-        <v>0.7986368634725065</v>
+        <v>0.8032970391139135</v>
       </c>
       <c r="K117">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L117">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M117">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N117">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O117">
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="118" spans="1:16">
       <c r="A118" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C118">
-        <v>1.99320337083961</v>
+        <v>1.898226451425238</v>
       </c>
       <c r="D118" t="s">
         <v>47</v>
       </c>
       <c r="E118">
-        <v>1.96709431991741</v>
+        <v>1.88647683475344</v>
       </c>
       <c r="F118">
         <v>-1</v>
       </c>
       <c r="G118">
-        <v>0.005746796629160391</v>
+        <v>0.005981773548574762</v>
       </c>
       <c r="H118">
-        <v>0.00559290568008259</v>
+        <v>0.00539352316524656</v>
       </c>
       <c r="I118">
-        <v>0.02610905092219973</v>
+        <v>0.0117496166717983</v>
       </c>
       <c r="J118">
-        <v>0.7986368634725065</v>
+        <v>0.8006955092450049</v>
       </c>
       <c r="K118">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L118">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M118">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N118">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O118">
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="119" spans="1:16">
       <c r="A119" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B119" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C119">
-        <v>1.915111220550284</v>
+        <v>1.988365553274239</v>
       </c>
       <c r="D119" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E119">
-        <v>2.024814922108121</v>
+        <v>1.88647683475344</v>
       </c>
       <c r="F119">
         <v>-1</v>
       </c>
       <c r="G119">
-        <v>0.005964888779449715</v>
+        <v>0.005751634446725762</v>
       </c>
       <c r="H119">
-        <v>0.005995185077891879</v>
+        <v>0.00539352316524656</v>
       </c>
       <c r="I119">
-        <v>-0.1097037015578373</v>
+        <v>0.1018887185207991</v>
       </c>
       <c r="J119">
-        <v>0.7940740311567515</v>
+        <v>0.8006955092450049</v>
       </c>
       <c r="K119">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L119">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M119">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="N119">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="O119">
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="120" spans="1:16">
       <c r="A120" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C120">
-        <v>2.003926026781634</v>
+        <v>1.903475998145109</v>
       </c>
       <c r="D120" t="s">
         <v>47</v>
       </c>
       <c r="E120">
-        <v>1.977451949274174</v>
+        <v>1.890985268995211</v>
       </c>
       <c r="F120">
         <v>-1</v>
       </c>
       <c r="G120">
-        <v>0.005736073973218366</v>
+        <v>0.005976524001854891</v>
       </c>
       <c r="H120">
-        <v>0.005582548050725825</v>
+        <v>0.00538901473100479</v>
       </c>
       <c r="I120">
-        <v>0.02647407750746011</v>
+        <v>0.01249072914989768</v>
       </c>
       <c r="J120">
-        <v>0.7940740311567515</v>
+        <v>0.7986368634725065</v>
       </c>
       <c r="K120">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L120">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M120">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N120">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O120">
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="121" spans="1:16">
       <c r="A121" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B121" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C121">
-        <v>1.927566816677033</v>
+        <v>1.99320337083961</v>
       </c>
       <c r="D121" t="s">
         <v>47</v>
       </c>
       <c r="E121">
-        <v>1.988539872100731</v>
+        <v>1.890985268995211</v>
       </c>
       <c r="F121">
         <v>-1</v>
       </c>
       <c r="G121">
-        <v>0.005952433183322967</v>
+        <v>0.005746796629160391</v>
       </c>
       <c r="H121">
-        <v>0.005571460127899269</v>
+        <v>0.00538901473100479</v>
       </c>
       <c r="I121">
-        <v>-0.06097305542369802</v>
+        <v>0.1022181018443988</v>
       </c>
       <c r="J121">
-        <v>0.7891894836560657</v>
+        <v>0.7986368634725065</v>
       </c>
       <c r="K121">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L121">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M121">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N121">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O121">
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="122" spans="1:16">
       <c r="A122" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C122">
-        <v>2.015404713408246</v>
+        <v>1.915111220550284</v>
       </c>
       <c r="D122" t="s">
         <v>47</v>
       </c>
       <c r="E122">
-        <v>1.988539872100731</v>
+        <v>1.900977871766715</v>
       </c>
       <c r="F122">
         <v>-1</v>
       </c>
       <c r="G122">
-        <v>0.005724595286591755</v>
+        <v>0.005964888779449715</v>
       </c>
       <c r="H122">
-        <v>0.005571460127899269</v>
+        <v>0.005379022128233287</v>
       </c>
       <c r="I122">
-        <v>0.02686484130751476</v>
+        <v>0.01413334878356931</v>
       </c>
       <c r="J122">
-        <v>0.7891894836560657</v>
+        <v>0.7940740311567515</v>
       </c>
       <c r="K122">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L122">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M122">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N122">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O122">
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="123" spans="1:16">
       <c r="A123" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B123" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C123">
-        <v>1.931008249436597</v>
+        <v>2.003926026781634</v>
       </c>
       <c r="D123" t="s">
         <v>47</v>
       </c>
       <c r="E123">
-        <v>1.99160342204748</v>
+        <v>1.900977871766715</v>
       </c>
       <c r="F123">
         <v>-1</v>
       </c>
       <c r="G123">
-        <v>0.005948991750563403</v>
+        <v>0.005736073973218366</v>
       </c>
       <c r="H123">
-        <v>0.00556839657795252</v>
+        <v>0.005379022128233287</v>
       </c>
       <c r="I123">
-        <v>-0.06059517261088332</v>
+        <v>0.1029481550149196</v>
       </c>
       <c r="J123">
-        <v>0.7878399021817268</v>
+        <v>0.7940740311567515</v>
       </c>
       <c r="K123">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L123">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M123">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N123">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O123">
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="124" spans="1:16">
       <c r="A124" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C124">
-        <v>2.018576229872942</v>
+        <v>1.927566816677033</v>
       </c>
       <c r="D124" t="s">
         <v>47</v>
       </c>
       <c r="E124">
-        <v>1.99160342204748</v>
+        <v>1.911675030793216</v>
       </c>
       <c r="F124">
         <v>-1</v>
       </c>
       <c r="G124">
-        <v>0.005721423770127059</v>
+        <v>0.005952433183322967</v>
       </c>
       <c r="H124">
-        <v>0.00556839657795252</v>
+        <v>0.005368324969206784</v>
       </c>
       <c r="I124">
-        <v>0.02697280782546208</v>
+        <v>0.01589178588381635</v>
       </c>
       <c r="J124">
-        <v>0.7878399021817268</v>
+        <v>0.7891894836560657</v>
       </c>
       <c r="K124">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L124">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M124">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N124">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O124">
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="125" spans="1:16">
       <c r="A125" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B125" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C125">
-        <v>1.931290596802969</v>
+        <v>2.015404713408246</v>
       </c>
       <c r="D125" t="s">
         <v>47</v>
       </c>
       <c r="E125">
-        <v>1.99185476656578</v>
+        <v>1.911675030793216</v>
       </c>
       <c r="F125">
         <v>-1</v>
       </c>
       <c r="G125">
-        <v>0.00594870940319703</v>
+        <v>0.005724595286591755</v>
       </c>
       <c r="H125">
-        <v>0.005568145233434219</v>
+        <v>0.005368324969206784</v>
       </c>
       <c r="I125">
-        <v>-0.06056416976281076</v>
+        <v>0.1037296826150291</v>
       </c>
       <c r="J125">
-        <v>0.7877291777243258</v>
+        <v>0.7891894836560657</v>
       </c>
       <c r="K125">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L125">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M125">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N125">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O125">
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="126" spans="1:16">
       <c r="A126" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C126">
-        <v>2.018836432347834</v>
+        <v>1.931008249436597</v>
       </c>
       <c r="D126" t="s">
         <v>47</v>
       </c>
       <c r="E126">
-        <v>1.99185476656578</v>
+        <v>1.914630614222018</v>
       </c>
       <c r="F126">
         <v>-1</v>
       </c>
       <c r="G126">
-        <v>0.005721163567652166</v>
+        <v>0.005948991750563403</v>
       </c>
       <c r="H126">
-        <v>0.005568145233434219</v>
+        <v>0.005365369385777982</v>
       </c>
       <c r="I126">
-        <v>0.02698166578205408</v>
+        <v>0.01637763521457813</v>
       </c>
       <c r="J126">
-        <v>0.7877291777243258</v>
+        <v>0.7878399021817268</v>
       </c>
       <c r="K126">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L126">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M126">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N126">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O126">
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="127" spans="1:16">
       <c r="A127" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B127" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C127">
-        <v>1.932400003731856</v>
+        <v>2.018576229872942</v>
       </c>
       <c r="D127" t="s">
         <v>47</v>
       </c>
       <c r="E127">
-        <v>1.99284235626326</v>
+        <v>1.914630614222018</v>
       </c>
       <c r="F127">
         <v>-1</v>
       </c>
       <c r="G127">
-        <v>0.005947599996268144</v>
+        <v>0.005721423770127059</v>
       </c>
       <c r="H127">
-        <v>0.00556715764373674</v>
+        <v>0.005365369385777982</v>
       </c>
       <c r="I127">
-        <v>-0.06044235253140373</v>
+        <v>0.1039456156509235</v>
       </c>
       <c r="J127">
-        <v>0.7872941161835857</v>
+        <v>0.7878399021817268</v>
       </c>
       <c r="K127">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L127">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M127">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N127">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O127">
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="128" spans="1:16">
       <c r="A128" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C128">
-        <v>2.019858826968574</v>
+        <v>1.931290596802969</v>
       </c>
       <c r="D128" t="s">
         <v>47</v>
       </c>
       <c r="E128">
-        <v>1.99284235626326</v>
+        <v>1.914873100783727</v>
       </c>
       <c r="F128">
         <v>-1</v>
       </c>
       <c r="G128">
-        <v>0.005720141173031427</v>
+        <v>0.00594870940319703</v>
       </c>
       <c r="H128">
-        <v>0.00556715764373674</v>
+        <v>0.005365126899216274</v>
       </c>
       <c r="I128">
-        <v>0.02701647070531354</v>
+        <v>0.01641749601924292</v>
       </c>
       <c r="J128">
-        <v>0.7872941161835857</v>
+        <v>0.7877291777243258</v>
       </c>
       <c r="K128">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L128">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M128">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N128">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O128">
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="129" spans="1:16">
       <c r="A129" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B129" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C129">
-        <v>1.928867601835406</v>
+        <v>2.018836432347834</v>
       </c>
       <c r="D129" t="s">
         <v>47</v>
       </c>
       <c r="E129">
-        <v>1.989697825947597</v>
+        <v>1.914873100783727</v>
       </c>
       <c r="F129">
         <v>-1</v>
       </c>
       <c r="G129">
-        <v>0.005951132398164594</v>
+        <v>0.005721163567652166</v>
       </c>
       <c r="H129">
-        <v>0.005570302174052403</v>
+        <v>0.005365126899216274</v>
       </c>
       <c r="I129">
-        <v>-0.0608302241121903</v>
+        <v>0.1039633315641078</v>
       </c>
       <c r="J129">
-        <v>0.7886793718292525</v>
+        <v>0.7877291777243258</v>
       </c>
       <c r="K129">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L129">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M129">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N129">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O129">
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="130" spans="1:16">
       <c r="A130" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C130">
-        <v>2.016603476201257</v>
+        <v>1.932400003731856</v>
       </c>
       <c r="D130" t="s">
         <v>47</v>
       </c>
       <c r="E130">
-        <v>1.989697825947597</v>
+        <v>1.915825885557948</v>
       </c>
       <c r="F130">
         <v>-1</v>
       </c>
       <c r="G130">
-        <v>0.005723396523798744</v>
+        <v>0.005947599996268144</v>
       </c>
       <c r="H130">
-        <v>0.005570302174052403</v>
+        <v>0.005364174114442052</v>
       </c>
       <c r="I130">
-        <v>0.02690565025365999</v>
+        <v>0.01657411817390897</v>
       </c>
       <c r="J130">
-        <v>0.7886793718292525</v>
+        <v>0.7872941161835857</v>
       </c>
       <c r="K130">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L130">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M130">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N130">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O130">
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="131" spans="1:16">
       <c r="A131" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B131" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C131">
-        <v>1.925635063875757</v>
+        <v>2.019858826968574</v>
       </c>
       <c r="D131" t="s">
         <v>47</v>
       </c>
       <c r="E131">
-        <v>1.986820233332536</v>
+        <v>1.915825885557948</v>
       </c>
       <c r="F131">
         <v>-1</v>
       </c>
       <c r="G131">
-        <v>0.005954364936124243</v>
+        <v>0.005720141173031427</v>
       </c>
       <c r="H131">
-        <v>0.005573179766667463</v>
+        <v>0.005364174114442052</v>
       </c>
       <c r="I131">
-        <v>-0.06118516945677954</v>
+        <v>0.1040329414106262</v>
       </c>
       <c r="J131">
-        <v>0.7899470337742129</v>
+        <v>0.7872941161835857</v>
       </c>
       <c r="K131">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L131">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M131">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N131">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O131">
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="132" spans="1:16">
       <c r="A132" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C132">
-        <v>2.013624470630599</v>
+        <v>2.038301570426869</v>
       </c>
       <c r="D132" t="s">
         <v>47</v>
       </c>
       <c r="E132">
-        <v>1.986820233332536</v>
+        <v>1.912792175693937</v>
       </c>
       <c r="F132">
         <v>-1</v>
       </c>
       <c r="G132">
-        <v>0.0057263755293694</v>
+        <v>0.005981698429573131</v>
       </c>
       <c r="H132">
-        <v>0.005573179766667463</v>
+        <v>0.005367207824306063</v>
       </c>
       <c r="I132">
-        <v>0.02680423729806303</v>
+        <v>0.1255093947329313</v>
       </c>
       <c r="J132">
-        <v>0.7899470337742129</v>
+        <v>0.7886793718292525</v>
       </c>
       <c r="K132">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L132">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M132">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N132">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O132">
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="133" spans="1:16">
       <c r="A133" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B133" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C133">
-        <v>1.924421367530698</v>
+        <v>2.016603476201257</v>
       </c>
       <c r="D133" t="s">
         <v>47</v>
       </c>
       <c r="E133">
-        <v>1.985739805605759</v>
+        <v>1.912792175693937</v>
       </c>
       <c r="F133">
         <v>-1</v>
       </c>
       <c r="G133">
-        <v>0.005955578632469301</v>
+        <v>0.005723396523798744</v>
       </c>
       <c r="H133">
-        <v>0.005574260194394241</v>
+        <v>0.005367207824306063</v>
       </c>
       <c r="I133">
-        <v>-0.06131843807506021</v>
+        <v>0.1038113005073193</v>
       </c>
       <c r="J133">
-        <v>0.7904229931252164</v>
+        <v>0.7886793718292525</v>
       </c>
       <c r="K133">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L133">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M133">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N133">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O133">
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="134" spans="1:16">
       <c r="A134" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C134">
-        <v>2.012505966155742</v>
+        <v>2.035132415564467</v>
       </c>
       <c r="D134" t="s">
         <v>47</v>
       </c>
       <c r="E134">
-        <v>1.985739805605759</v>
+        <v>1.910015996034474</v>
       </c>
       <c r="F134">
         <v>-1</v>
       </c>
       <c r="G134">
-        <v>0.00572749403384426</v>
+        <v>0.005984867584435533</v>
       </c>
       <c r="H134">
-        <v>0.005574260194394241</v>
+        <v>0.005369984003965526</v>
       </c>
       <c r="I134">
-        <v>0.02676616054998293</v>
+        <v>0.1251164195299934</v>
       </c>
       <c r="J134">
-        <v>0.7904229931252164</v>
+        <v>0.7899470337742129</v>
       </c>
       <c r="K134">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L134">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M134">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N134">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O134">
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="135" spans="1:16">
       <c r="A135" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B135" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C135">
-        <v>1.922633944537091</v>
+        <v>2.013624470630599</v>
       </c>
       <c r="D135" t="s">
         <v>47</v>
       </c>
       <c r="E135">
-        <v>1.984148648666351</v>
+        <v>1.910015996034474</v>
       </c>
       <c r="F135">
         <v>-1</v>
       </c>
       <c r="G135">
-        <v>0.00595736605546291</v>
+        <v>0.0057263755293694</v>
       </c>
       <c r="H135">
-        <v>0.005575851351333649</v>
+        <v>0.005369984003965526</v>
       </c>
       <c r="I135">
-        <v>-0.06151470412926052</v>
+        <v>0.1036084745961257</v>
       </c>
       <c r="J135">
-        <v>0.791123943318788</v>
+        <v>0.7899470337742129</v>
       </c>
       <c r="K135">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L135">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M135">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N135">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O135">
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="136" spans="1:16">
       <c r="A136" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C136">
-        <v>2.010858733200848</v>
+        <v>2.033942517186959</v>
       </c>
       <c r="D136" t="s">
         <v>47</v>
       </c>
       <c r="E136">
-        <v>1.984148648666351</v>
+        <v>1.908973645055776</v>
       </c>
       <c r="F136">
         <v>-1</v>
       </c>
       <c r="G136">
-        <v>0.005729141266799152</v>
+        <v>0.005986057482813041</v>
       </c>
       <c r="H136">
-        <v>0.005575851351333649</v>
+        <v>0.005371026354944224</v>
       </c>
       <c r="I136">
-        <v>0.02671008453449719</v>
+        <v>0.1249688721311824</v>
       </c>
       <c r="J136">
-        <v>0.791123943318788</v>
+        <v>0.7904229931252164</v>
       </c>
       <c r="K136">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L136">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M136">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N136">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O136">
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="137" spans="1:16">
       <c r="A137" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B137" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C137">
-        <v>1.921462641095741</v>
+        <v>2.012505966155742</v>
       </c>
       <c r="D137" t="s">
         <v>47</v>
       </c>
       <c r="E137">
-        <v>1.983105958936209</v>
+        <v>1.908973645055776</v>
       </c>
       <c r="F137">
         <v>-1</v>
       </c>
       <c r="G137">
-        <v>0.005958537358904259</v>
+        <v>0.00572749403384426</v>
       </c>
       <c r="H137">
-        <v>0.005576894041063791</v>
+        <v>0.005371026354944224</v>
       </c>
       <c r="I137">
-        <v>-0.06164331784046717</v>
+        <v>0.1035323210999652</v>
       </c>
       <c r="J137">
-        <v>0.7915832780016702</v>
+        <v>0.7904229931252164</v>
       </c>
       <c r="K137">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L137">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M137">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N137">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O137">
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="138" spans="1:16">
       <c r="A138" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C138">
-        <v>2.009779296696075</v>
+        <v>2.03219014170303</v>
       </c>
       <c r="D138" t="s">
         <v>47</v>
       </c>
       <c r="E138">
-        <v>1.983105958936209</v>
+        <v>1.907438564131855</v>
       </c>
       <c r="F138">
         <v>-1</v>
       </c>
       <c r="G138">
-        <v>0.005730220703303925</v>
+        <v>0.00598780985829697</v>
       </c>
       <c r="H138">
-        <v>0.005576894041063791</v>
+        <v>0.005372561435868146</v>
       </c>
       <c r="I138">
-        <v>0.02667333775986669</v>
+        <v>0.1247515775711752</v>
       </c>
       <c r="J138">
-        <v>0.7915832780016702</v>
+        <v>0.791123943318788</v>
       </c>
       <c r="K138">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L138">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M138">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N138">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O138">
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="139" spans="1:16">
       <c r="A139" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B139" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C139">
-        <v>2.032225684349332</v>
+        <v>2.010858733200848</v>
       </c>
       <c r="D139" t="s">
         <v>47</v>
       </c>
       <c r="E139">
-        <v>1.984180921389193</v>
+        <v>1.907438564131855</v>
       </c>
       <c r="F139">
         <v>-1</v>
       </c>
       <c r="G139">
-        <v>0.005987774315650668</v>
+        <v>0.005729141266799152</v>
       </c>
       <c r="H139">
-        <v>0.005575819078610806</v>
+        <v>0.005372561435868146</v>
       </c>
       <c r="I139">
-        <v>0.0480447629601386</v>
+        <v>0.1034201690689938</v>
       </c>
       <c r="J139">
-        <v>0.7911097262602672</v>
+        <v>0.791123943318788</v>
       </c>
       <c r="K139">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L139">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M139">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N139">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O139">
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="140" spans="1:16">
       <c r="A140" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C140">
-        <v>2.010892143288372</v>
+        <v>2.031041804995824</v>
       </c>
       <c r="D140" t="s">
         <v>47</v>
       </c>
       <c r="E140">
-        <v>1.984180921389193</v>
+        <v>1.906432621176342</v>
       </c>
       <c r="F140">
         <v>-1</v>
       </c>
       <c r="G140">
-        <v>0.005729107856711628</v>
+        <v>0.005988958195004175</v>
       </c>
       <c r="H140">
-        <v>0.005575819078610806</v>
+        <v>0.005373567378823658</v>
       </c>
       <c r="I140">
-        <v>0.02671122189917918</v>
+        <v>0.1246091838194818</v>
       </c>
       <c r="J140">
-        <v>0.7911097262602672</v>
+        <v>0.7915832780016702</v>
       </c>
       <c r="K140">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L140">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M140">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N140">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O140">
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="141" spans="1:16">
       <c r="A141" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B141" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C141">
-        <v>2.033826265263685</v>
+        <v>2.009779296696075</v>
       </c>
       <c r="D141" t="s">
         <v>47</v>
       </c>
       <c r="E141">
-        <v>1.985634248859426</v>
+        <v>1.906432621176342</v>
       </c>
       <c r="F141">
         <v>-1</v>
       </c>
       <c r="G141">
-        <v>0.005986173734736314</v>
+        <v>0.005730220703303925</v>
       </c>
       <c r="H141">
-        <v>0.005574365751140573</v>
+        <v>0.005373567378823658</v>
       </c>
       <c r="I141">
-        <v>0.04819201640425885</v>
+        <v>0.1033466755197328</v>
       </c>
       <c r="J141">
-        <v>0.7904694938945258</v>
+        <v>0.7915832780016702</v>
       </c>
       <c r="K141">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L141">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M141">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N141">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O141">
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="142" spans="1:16">
       <c r="A142" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B142" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C142">
-        <v>2.012396689347864</v>
+        <v>2.032225684349332</v>
       </c>
       <c r="D142" t="s">
         <v>47</v>
       </c>
       <c r="E142">
-        <v>1.985634248859426</v>
+        <v>1.907469699490015</v>
       </c>
       <c r="F142">
         <v>-1</v>
       </c>
       <c r="G142">
-        <v>0.005727603310652135</v>
+        <v>0.005987774315650668</v>
       </c>
       <c r="H142">
-        <v>0.005574365751140573</v>
+        <v>0.005372530300509985</v>
       </c>
       <c r="I142">
-        <v>0.02676244048843812</v>
+        <v>0.1247559848593169</v>
       </c>
       <c r="J142">
-        <v>0.7904694938945258</v>
+        <v>0.7911097262602672</v>
       </c>
       <c r="K142">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L142">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M142">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N142">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O142">
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="143" spans="1:16">
       <c r="A143" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B143" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C143">
-        <v>2.037114148133088</v>
+        <v>2.010892143288372</v>
       </c>
       <c r="D143" t="s">
         <v>47</v>
       </c>
       <c r="E143">
-        <v>1.988619646504844</v>
+        <v>1.907469699490015</v>
       </c>
       <c r="F143">
         <v>-1</v>
       </c>
       <c r="G143">
-        <v>0.005982885851866911</v>
+        <v>0.005729107856711628</v>
       </c>
       <c r="H143">
-        <v>0.005571380353495156</v>
+        <v>0.005372530300509985</v>
       </c>
       <c r="I143">
-        <v>0.04849450162824409</v>
+        <v>0.1034224437983575</v>
       </c>
       <c r="J143">
-        <v>0.7891543407467646</v>
+        <v>0.7911097262602672</v>
       </c>
       <c r="K143">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L143">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M143">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N143">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O143">
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="144" spans="1:16">
       <c r="A144" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B144" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C144">
-        <v>2.015487299245103</v>
+        <v>2.033826265263685</v>
       </c>
       <c r="D144" t="s">
         <v>47</v>
       </c>
       <c r="E144">
-        <v>1.988619646504844</v>
+        <v>1.908871808370989</v>
       </c>
       <c r="F144">
         <v>-1</v>
       </c>
       <c r="G144">
-        <v>0.005724512700754897</v>
+        <v>0.005986173734736314</v>
       </c>
       <c r="H144">
-        <v>0.005571380353495156</v>
+        <v>0.005371128191629012</v>
       </c>
       <c r="I144">
-        <v>0.02686765274025893</v>
+        <v>0.1249544568926966</v>
       </c>
       <c r="J144">
-        <v>0.7891543407467646</v>
+        <v>0.7904694938945258</v>
       </c>
       <c r="K144">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L144">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M144">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N144">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O144">
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="145" spans="1:16">
       <c r="A145" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B145" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C145">
-        <v>2.041024370702765</v>
+        <v>2.012396689347864</v>
       </c>
       <c r="D145" t="s">
         <v>47</v>
       </c>
       <c r="E145">
-        <v>1.992170128598111</v>
+        <v>1.908871808370989</v>
       </c>
       <c r="F145">
         <v>-1</v>
       </c>
       <c r="G145">
-        <v>0.005978975629297235</v>
+        <v>0.005727603310652135</v>
       </c>
       <c r="H145">
-        <v>0.005567829871401889</v>
+        <v>0.005371128191629012</v>
       </c>
       <c r="I145">
-        <v>0.04885424210465428</v>
+        <v>0.1035248809768758</v>
       </c>
       <c r="J145">
-        <v>0.7875902517188939</v>
+        <v>0.7904694938945258</v>
       </c>
       <c r="K145">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L145">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M145">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N145">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O145">
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="146" spans="1:16">
       <c r="A146" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B146" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C146">
-        <v>2.0191629084606</v>
+        <v>2.037114148133088</v>
       </c>
       <c r="D146" t="s">
         <v>47</v>
       </c>
       <c r="E146">
-        <v>1.992170128598111</v>
+        <v>1.911751993764586</v>
       </c>
       <c r="F146">
         <v>-1</v>
       </c>
       <c r="G146">
-        <v>0.005720837091539401</v>
+        <v>0.005982885851866911</v>
       </c>
       <c r="H146">
-        <v>0.005567829871401889</v>
+        <v>0.005368248006235414</v>
       </c>
       <c r="I146">
-        <v>0.02699277986248894</v>
+        <v>0.1253621543685026</v>
       </c>
       <c r="J146">
-        <v>0.7875902517188939</v>
+        <v>0.7891543407467646</v>
       </c>
       <c r="K146">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L146">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M146">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N146">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O146">
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="147" spans="1:16">
       <c r="A147" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B147" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C147">
-        <v>2.042989638697718</v>
+        <v>2.015487299245103</v>
       </c>
       <c r="D147" t="s">
         <v>47</v>
       </c>
       <c r="E147">
-        <v>1.993954591937528</v>
+        <v>1.911751993764586</v>
       </c>
       <c r="F147">
         <v>-1</v>
       </c>
       <c r="G147">
-        <v>0.005977010361302281</v>
+        <v>0.005724512700754897</v>
       </c>
       <c r="H147">
-        <v>0.005566045408062472</v>
+        <v>0.005368248006235414</v>
       </c>
       <c r="I147">
-        <v>0.0490350467601901</v>
+        <v>0.1037353054805175</v>
       </c>
       <c r="J147">
-        <v>0.7868041445209126</v>
+        <v>0.7891543407467646</v>
       </c>
       <c r="K147">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L147">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M147">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N147">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O147">
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="148" spans="1:16">
       <c r="A148" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B148" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C148">
-        <v>2.021010260375856</v>
+        <v>2.041024370702765</v>
       </c>
       <c r="D148" t="s">
         <v>47</v>
       </c>
       <c r="E148">
-        <v>1.993954591937528</v>
+        <v>1.915177348735623</v>
       </c>
       <c r="F148">
         <v>-1</v>
       </c>
       <c r="G148">
-        <v>0.005718989739624145</v>
+        <v>0.005978975629297235</v>
       </c>
       <c r="H148">
-        <v>0.005566045408062472</v>
+        <v>0.005364822651264377</v>
       </c>
       <c r="I148">
-        <v>0.02705566843832741</v>
+        <v>0.1258470219671424</v>
       </c>
       <c r="J148">
-        <v>0.7868041445209126</v>
+        <v>0.7875902517188939</v>
       </c>
       <c r="K148">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L148">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M148">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N148">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O148">
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="149" spans="1:16">
       <c r="A149" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B149" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C149">
-        <v>2.046475047291454</v>
+        <v>2.0191629084606</v>
       </c>
       <c r="D149" t="s">
         <v>47</v>
       </c>
       <c r="E149">
-        <v>1.99711934294064</v>
+        <v>1.915177348735623</v>
       </c>
       <c r="F149">
         <v>-1</v>
       </c>
       <c r="G149">
-        <v>0.005973524952708546</v>
+        <v>0.005720837091539401</v>
       </c>
       <c r="H149">
-        <v>0.00556288065705936</v>
+        <v>0.005364822651264377</v>
       </c>
       <c r="I149">
-        <v>0.04935570435081393</v>
+        <v>0.103985559724977</v>
       </c>
       <c r="J149">
-        <v>0.7854099810834182</v>
+        <v>0.7875902517188939</v>
       </c>
       <c r="K149">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L149">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M149">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N149">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O149">
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="150" spans="1:16">
       <c r="A150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B150" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C150">
-        <v>2.024286544453967</v>
+        <v>2.042989638697718</v>
       </c>
       <c r="D150" t="s">
         <v>47</v>
       </c>
       <c r="E150">
-        <v>1.99711934294064</v>
+        <v>1.916898923499202</v>
       </c>
       <c r="F150">
         <v>-1</v>
       </c>
       <c r="G150">
-        <v>0.005715713455546033</v>
+        <v>0.005977010361302281</v>
       </c>
       <c r="H150">
-        <v>0.00556288065705936</v>
+        <v>0.005363101076500799</v>
       </c>
       <c r="I150">
-        <v>0.02716720151332686</v>
+        <v>0.1260907151985167</v>
       </c>
       <c r="J150">
-        <v>0.7854099810834182</v>
+        <v>0.7868041445209126</v>
       </c>
       <c r="K150">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L150">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M150">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N150">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O150">
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="151" spans="1:16">
       <c r="A151" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B151" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C151">
-        <v>2.05115387029975</v>
+        <v>2.021010260375856</v>
       </c>
       <c r="D151" t="s">
         <v>47</v>
       </c>
       <c r="E151">
-        <v>2.001367714232173</v>
+        <v>1.916898923499202</v>
       </c>
       <c r="F151">
         <v>-1</v>
       </c>
       <c r="G151">
-        <v>0.00596884612970025</v>
+        <v>0.005718989739624145</v>
       </c>
       <c r="H151">
-        <v>0.005558632285767827</v>
+        <v>0.005363101076500799</v>
       </c>
       <c r="I151">
-        <v>0.04978615606757719</v>
+        <v>0.104111336876654</v>
       </c>
       <c r="J151">
-        <v>0.7835384518800999</v>
+        <v>0.7868041445209126</v>
       </c>
       <c r="K151">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L151">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M151">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N151">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O151">
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="152" spans="1:16">
       <c r="A152" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B152" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C152">
-        <v>2.028684638081765</v>
+        <v>2.046475047291454</v>
       </c>
       <c r="D152" t="s">
         <v>47</v>
       </c>
       <c r="E152">
-        <v>2.001367714232173</v>
+        <v>1.919952141427314</v>
       </c>
       <c r="F152">
         <v>-1</v>
       </c>
       <c r="G152">
-        <v>0.005711315361918235</v>
+        <v>0.005973524952708546</v>
       </c>
       <c r="H152">
-        <v>0.005558632285767827</v>
+        <v>0.005360047858572686</v>
       </c>
       <c r="I152">
-        <v>0.02731692384959228</v>
+        <v>0.1265229058641399</v>
       </c>
       <c r="J152">
-        <v>0.7835384518800999</v>
+        <v>0.7854099810834182</v>
       </c>
       <c r="K152">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L152">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M152">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N152">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O152">
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="153" spans="1:16">
       <c r="A153" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B153" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C153">
-        <v>2.052411570940913</v>
+        <v>2.024286544453967</v>
       </c>
       <c r="D153" t="s">
         <v>47</v>
       </c>
       <c r="E153">
-        <v>2.002509706414348</v>
+        <v>1.919952141427314</v>
       </c>
       <c r="F153">
         <v>-1</v>
       </c>
       <c r="G153">
-        <v>0.005967588429059087</v>
+        <v>0.005715713455546033</v>
       </c>
       <c r="H153">
-        <v>0.005557490293585651</v>
+        <v>0.005360047858572686</v>
       </c>
       <c r="I153">
-        <v>0.04990186452656431</v>
+        <v>0.1043344030266529</v>
       </c>
       <c r="J153">
-        <v>0.783035371623635</v>
+        <v>0.7854099810834182</v>
       </c>
       <c r="K153">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L153">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M153">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N153">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O153">
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="154" spans="1:16">
       <c r="A154" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B154" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C154">
-        <v>2.029866876684458</v>
+        <v>2.05115387029975</v>
       </c>
       <c r="D154" t="s">
         <v>47</v>
       </c>
       <c r="E154">
-        <v>2.002509706414348</v>
+        <v>1.924050790382581</v>
       </c>
       <c r="F154">
         <v>-1</v>
       </c>
       <c r="G154">
-        <v>0.005710133123315543</v>
+        <v>0.00596884612970025</v>
       </c>
       <c r="H154">
-        <v>0.005557490293585651</v>
+        <v>0.005355949209617419</v>
       </c>
       <c r="I154">
-        <v>0.02735717027010942</v>
+        <v>0.1271030799171688</v>
       </c>
       <c r="J154">
-        <v>0.783035371623635</v>
+        <v>0.7835384518800999</v>
       </c>
       <c r="K154">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L154">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M154">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N154">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O154">
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="155" spans="1:16">
       <c r="A155" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B155" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C155">
-        <v>2.054065467064709</v>
+        <v>2.028684638081765</v>
       </c>
       <c r="D155" t="s">
         <v>47</v>
       </c>
       <c r="E155">
-        <v>2.004011444094756</v>
+        <v>1.924050790382581</v>
       </c>
       <c r="F155">
         <v>-1</v>
       </c>
       <c r="G155">
-        <v>0.005965934532935291</v>
+        <v>0.005711315361918235</v>
       </c>
       <c r="H155">
-        <v>0.005555988555905244</v>
+        <v>0.005355949209617419</v>
       </c>
       <c r="I155">
-        <v>0.05005402296995332</v>
+        <v>0.1046338476991839</v>
       </c>
       <c r="J155">
-        <v>0.7823738131741161</v>
+        <v>0.7835384518800999</v>
       </c>
       <c r="K155">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L155">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M155">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N155">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O155">
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="156" spans="1:16">
       <c r="A156" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B156" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C156">
-        <v>2.031421539040827</v>
+        <v>2.052411570940913</v>
       </c>
       <c r="D156" t="s">
         <v>47</v>
       </c>
       <c r="E156">
-        <v>2.004011444094756</v>
+        <v>1.925152536144239</v>
       </c>
       <c r="F156">
         <v>-1</v>
       </c>
       <c r="G156">
-        <v>0.005708578460959173</v>
+        <v>0.005967588429059087</v>
       </c>
       <c r="H156">
-        <v>0.005555988555905244</v>
+        <v>0.00535484746385576</v>
       </c>
       <c r="I156">
-        <v>0.02741009494607116</v>
+        <v>0.1272590347966731</v>
       </c>
       <c r="J156">
-        <v>0.7823738131741161</v>
+        <v>0.783035371623635</v>
       </c>
       <c r="K156">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L156">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M156">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N156">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O156">
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="157" spans="1:16">
       <c r="A157" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B157" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C157">
-        <v>2.057724755182126</v>
+        <v>2.029866876684458</v>
       </c>
       <c r="D157" t="s">
         <v>47</v>
       </c>
       <c r="E157">
-        <v>2.00733407770537</v>
+        <v>1.925152536144239</v>
       </c>
       <c r="F157">
         <v>-1</v>
       </c>
       <c r="G157">
-        <v>0.005962275244817874</v>
+        <v>0.005710133123315543</v>
       </c>
       <c r="H157">
-        <v>0.00555266592229463</v>
+        <v>0.00535484746385576</v>
       </c>
       <c r="I157">
-        <v>0.05039067747675574</v>
+        <v>0.1047143405402182</v>
       </c>
       <c r="J157">
-        <v>0.7809100979271496</v>
+        <v>0.783035371623635</v>
       </c>
       <c r="K157">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L157">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M157">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N157">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O157">
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="158" spans="1:16">
       <c r="A158" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B158" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C158">
-        <v>2.034861269871199</v>
+        <v>2.054065467064709</v>
       </c>
       <c r="D158" t="s">
         <v>47</v>
       </c>
       <c r="E158">
-        <v>2.00733407770537</v>
+        <v>1.926601349148686</v>
       </c>
       <c r="F158">
         <v>-1</v>
       </c>
       <c r="G158">
-        <v>0.005705138730128801</v>
+        <v>0.005965934532935291</v>
       </c>
       <c r="H158">
-        <v>0.00555266592229463</v>
+        <v>0.005353398650851314</v>
       </c>
       <c r="I158">
-        <v>0.02752719216582822</v>
+        <v>0.1274641179160234</v>
       </c>
       <c r="J158">
-        <v>0.7809100979271496</v>
+        <v>0.7823738131741161</v>
       </c>
       <c r="K158">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L158">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M158">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N158">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O158">
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="159" spans="1:16">
       <c r="A159" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B159" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C159">
-        <v>2.059621791558839</v>
+        <v>2.031421539040827</v>
       </c>
       <c r="D159" t="s">
         <v>47</v>
       </c>
       <c r="E159">
-        <v>2.009056586735426</v>
+        <v>1.926601349148686</v>
       </c>
       <c r="F159">
         <v>-1</v>
       </c>
       <c r="G159">
-        <v>0.005960378208441161</v>
+        <v>0.005708578460959173</v>
       </c>
       <c r="H159">
-        <v>0.005550943413264574</v>
+        <v>0.005353398650851314</v>
       </c>
       <c r="I159">
-        <v>0.05056520482341309</v>
+        <v>0.1048201898921413</v>
       </c>
       <c r="J159">
-        <v>0.7801512833764644</v>
+        <v>0.7823738131741161</v>
       </c>
       <c r="K159">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L159">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M159">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N159">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O159">
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="160" spans="1:16">
       <c r="A160" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B160" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C160">
-        <v>2.036644484065309</v>
+        <v>2.057724755182126</v>
       </c>
       <c r="D160" t="s">
         <v>47</v>
       </c>
       <c r="E160">
-        <v>2.009056586735426</v>
+        <v>1.929806885539542</v>
       </c>
       <c r="F160">
         <v>-1</v>
       </c>
       <c r="G160">
-        <v>0.005703355515934692</v>
+        <v>0.005962275244817874</v>
       </c>
       <c r="H160">
-        <v>0.005550943413264574</v>
+        <v>0.005350193114460458</v>
       </c>
       <c r="I160">
-        <v>0.02758789732988287</v>
+        <v>0.1279178696425836</v>
       </c>
       <c r="J160">
-        <v>0.7801512833764644</v>
+        <v>0.7809100979271496</v>
       </c>
       <c r="K160">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L160">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M160">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N160">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O160">
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="161" spans="1:16">
       <c r="A161" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B161" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C161">
-        <v>2.060612201172958</v>
+        <v>2.034861269871199</v>
       </c>
       <c r="D161" t="s">
         <v>47</v>
       </c>
       <c r="E161">
-        <v>2.009955878665046</v>
+        <v>1.929806885539542</v>
       </c>
       <c r="F161">
         <v>-1</v>
       </c>
       <c r="G161">
-        <v>0.005959387798827042</v>
+        <v>0.005705138730128801</v>
       </c>
       <c r="H161">
-        <v>0.005550044121334954</v>
+        <v>0.005350193114460458</v>
       </c>
       <c r="I161">
-        <v>0.05065632250791197</v>
+        <v>0.105054384331656</v>
       </c>
       <c r="J161">
-        <v>0.7797551195308166</v>
+        <v>0.7809100979271496</v>
       </c>
       <c r="K161">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L161">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M161">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N161">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O161">
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="162" spans="1:16">
       <c r="A162" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B162" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C162">
-        <v>2.037575469102581</v>
+        <v>2.059621791558839</v>
       </c>
       <c r="D162" t="s">
         <v>47</v>
       </c>
       <c r="E162">
-        <v>2.009955878665046</v>
+        <v>1.931468689405543</v>
       </c>
       <c r="F162">
         <v>-1</v>
       </c>
       <c r="G162">
-        <v>0.005702424530897419</v>
+        <v>0.005960378208441161</v>
       </c>
       <c r="H162">
-        <v>0.005550044121334954</v>
+        <v>0.005348531310594457</v>
       </c>
       <c r="I162">
-        <v>0.02761959043753492</v>
+        <v>0.1281531021532958</v>
       </c>
       <c r="J162">
-        <v>0.7797551195308166</v>
+        <v>0.7801512833764644</v>
       </c>
       <c r="K162">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L162">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M162">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N162">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O162">
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="163" spans="1:16">
       <c r="A163" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B163" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C163">
-        <v>2.062155534027272</v>
+        <v>2.036644484065309</v>
       </c>
       <c r="D163" t="s">
         <v>47</v>
       </c>
       <c r="E163">
-        <v>2.011357224896764</v>
+        <v>1.931468689405543</v>
       </c>
       <c r="F163">
         <v>-1</v>
       </c>
       <c r="G163">
-        <v>0.005957844465972727</v>
+        <v>0.005703355515934692</v>
       </c>
       <c r="H163">
-        <v>0.005548642775103236</v>
+        <v>0.005348531310594457</v>
       </c>
       <c r="I163">
-        <v>0.05079830913050865</v>
+        <v>0.1051757946597656</v>
       </c>
       <c r="J163">
-        <v>0.7791377863890909</v>
+        <v>0.7801512833764644</v>
       </c>
       <c r="K163">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L163">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M163">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N163">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O163">
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="164" spans="1:16">
       <c r="A164" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B164" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C164">
-        <v>2.039026201985636</v>
+        <v>2.060612201172958</v>
       </c>
       <c r="D164" t="s">
         <v>47</v>
       </c>
       <c r="E164">
-        <v>2.011357224896764</v>
+        <v>1.932336288227512</v>
       </c>
       <c r="F164">
         <v>-1</v>
       </c>
       <c r="G164">
-        <v>0.005700973798014364</v>
+        <v>0.005959387798827042</v>
       </c>
       <c r="H164">
-        <v>0.005548642775103236</v>
+        <v>0.005347663711772489</v>
       </c>
       <c r="I164">
-        <v>0.02766897708887273</v>
+        <v>0.1282759129454463</v>
       </c>
       <c r="J164">
-        <v>0.7791377863890909</v>
+        <v>0.7797551195308166</v>
       </c>
       <c r="K164">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L164">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M164">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N164">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O164">
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="165" spans="1:16">
       <c r="A165" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B165" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C165">
-        <v>2.065159805074657</v>
+        <v>2.037575469102581</v>
       </c>
       <c r="D165" t="s">
         <v>47</v>
       </c>
       <c r="E165">
-        <v>2.014085103007789</v>
+        <v>1.932336288227512</v>
       </c>
       <c r="F165">
         <v>-1</v>
       </c>
       <c r="G165">
-        <v>0.005954840194925343</v>
+        <v>0.005702424530897419</v>
       </c>
       <c r="H165">
-        <v>0.005545914896992211</v>
+        <v>0.005347663711772489</v>
       </c>
       <c r="I165">
-        <v>0.05107470206686848</v>
+        <v>0.1052391808750692</v>
       </c>
       <c r="J165">
-        <v>0.777936077970137</v>
+        <v>0.7797551195308166</v>
       </c>
       <c r="K165">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L165">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M165">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N165">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O165">
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="166" spans="1:16">
       <c r="A166" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B166" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C166">
-        <v>2.041850216770178</v>
+        <v>2.062155534027272</v>
       </c>
       <c r="D166" t="s">
         <v>47</v>
       </c>
       <c r="E166">
-        <v>2.014085103007789</v>
+        <v>1.933688247807891</v>
       </c>
       <c r="F166">
         <v>-1</v>
       </c>
       <c r="G166">
-        <v>0.005698149783229823</v>
+        <v>0.005957844465972727</v>
       </c>
       <c r="H166">
-        <v>0.005545914896992211</v>
+        <v>0.005346311752192109</v>
       </c>
       <c r="I166">
-        <v>0.02776511376238933</v>
+        <v>0.1284672862193814</v>
       </c>
       <c r="J166">
-        <v>0.777936077970137</v>
+        <v>0.7791377863890909</v>
       </c>
       <c r="K166">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L166">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M166">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N166">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O166">
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="167" spans="1:16">
       <c r="A167" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B167" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C167">
-        <v>2.066699852252084</v>
+        <v>2.039026201985636</v>
       </c>
       <c r="D167" t="s">
         <v>47</v>
       </c>
       <c r="E167">
-        <v>2.015483465844892</v>
+        <v>1.933688247807891</v>
       </c>
       <c r="F167">
         <v>-1</v>
       </c>
       <c r="G167">
-        <v>0.005953300147747916</v>
+        <v>0.005700973798014364</v>
       </c>
       <c r="H167">
-        <v>0.005544516534155107</v>
+        <v>0.005346311752192109</v>
       </c>
       <c r="I167">
-        <v>0.05121638640719173</v>
+        <v>0.1053379541777455</v>
       </c>
       <c r="J167">
-        <v>0.7773200590991663</v>
+        <v>0.7791377863890909</v>
       </c>
       <c r="K167">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L167">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M167">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N167">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O167">
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="168" spans="1:16">
       <c r="A168" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B168" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C168">
-        <v>2.043297861116959</v>
+        <v>2.065159805074657</v>
       </c>
       <c r="D168" t="s">
         <v>47</v>
       </c>
       <c r="E168">
-        <v>2.015483465844892</v>
+        <v>1.9363199892454</v>
       </c>
       <c r="F168">
         <v>-1</v>
       </c>
       <c r="G168">
-        <v>0.005696702138883041</v>
+        <v>0.005954840194925343</v>
       </c>
       <c r="H168">
-        <v>0.005544516534155107</v>
+        <v>0.0053436800107546</v>
       </c>
       <c r="I168">
-        <v>0.02781439527206686</v>
+        <v>0.128839815829257</v>
       </c>
       <c r="J168">
-        <v>0.7773200590991663</v>
+        <v>0.777936077970137</v>
       </c>
       <c r="K168">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L168">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M168">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N168">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O168">
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="169" spans="1:16">
       <c r="A169" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B169" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C169">
-        <v>2.069529129524661</v>
+        <v>2.041850216770178</v>
       </c>
       <c r="D169" t="s">
         <v>47</v>
       </c>
       <c r="E169">
-        <v>2.018052449608391</v>
+        <v>1.9363199892454</v>
       </c>
       <c r="F169">
         <v>-1</v>
       </c>
       <c r="G169">
-        <v>0.00595047087047534</v>
+        <v>0.005698149783229823</v>
       </c>
       <c r="H169">
-        <v>0.005541947550391608</v>
+        <v>0.0053436800107546</v>
       </c>
       <c r="I169">
-        <v>0.05147667991626914</v>
+        <v>0.1055302275247778</v>
       </c>
       <c r="J169">
-        <v>0.7761883481901358</v>
+        <v>0.777936077970137</v>
       </c>
       <c r="K169">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L169">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M169">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N169">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O169">
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="170" spans="1:16">
       <c r="A170" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B170" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C170">
-        <v>2.045957381753181</v>
+        <v>2.066699852252084</v>
       </c>
       <c r="D170" t="s">
         <v>47</v>
       </c>
       <c r="E170">
-        <v>2.018052449608391</v>
+        <v>1.937669070572826</v>
       </c>
       <c r="F170">
         <v>-1</v>
       </c>
       <c r="G170">
-        <v>0.00569404261824682</v>
+        <v>0.005953300147747916</v>
       </c>
       <c r="H170">
-        <v>0.005541947550391608</v>
+        <v>0.005342330929427174</v>
       </c>
       <c r="I170">
-        <v>0.02790493214478929</v>
+        <v>0.129030781679258</v>
       </c>
       <c r="J170">
-        <v>0.7761883481901358</v>
+        <v>0.7773200590991663</v>
       </c>
       <c r="K170">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L170">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M170">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N170">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O170">
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="171" spans="1:16">
       <c r="A171" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B171" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C171">
-        <v>2.072833064946989</v>
+        <v>2.043297861116959</v>
       </c>
       <c r="D171" t="s">
         <v>47</v>
       </c>
       <c r="E171">
-        <v>2.021052422971866</v>
+        <v>1.937669070572826</v>
       </c>
       <c r="F171">
         <v>-1</v>
       </c>
       <c r="G171">
-        <v>0.00594716693505301</v>
+        <v>0.005696702138883041</v>
       </c>
       <c r="H171">
-        <v>0.005538947577028134</v>
+        <v>0.005342330929427174</v>
       </c>
       <c r="I171">
-        <v>0.05178064197512322</v>
+        <v>0.1056287905441331</v>
       </c>
       <c r="J171">
-        <v>0.7748667740212044</v>
+        <v>0.7773200590991663</v>
       </c>
       <c r="K171">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L171">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M171">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N171">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O171">
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="172" spans="1:16">
       <c r="A172" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B172" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C172">
-        <v>2.04906308105017</v>
+        <v>2.069529129524661</v>
       </c>
       <c r="D172" t="s">
         <v>47</v>
       </c>
       <c r="E172">
-        <v>2.021052422971866</v>
+        <v>1.940147517463603</v>
       </c>
       <c r="F172">
         <v>-1</v>
       </c>
       <c r="G172">
-        <v>0.005690936918949831</v>
+        <v>0.00595047087047534</v>
       </c>
       <c r="H172">
-        <v>0.005538947577028134</v>
+        <v>0.005339852482536397</v>
       </c>
       <c r="I172">
-        <v>0.02801065807830394</v>
+        <v>0.1293816120610578</v>
       </c>
       <c r="J172">
-        <v>0.7748667740212044</v>
+        <v>0.7761883481901358</v>
       </c>
       <c r="K172">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L172">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M172">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N172">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O172">
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="173" spans="1:16">
       <c r="A173" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B173" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C173">
-        <v>2.076110072462908</v>
+        <v>2.045957381753181</v>
       </c>
       <c r="D173" t="s">
         <v>47</v>
       </c>
       <c r="E173">
-        <v>2.02402794579632</v>
+        <v>1.940147517463603</v>
       </c>
       <c r="F173">
         <v>-1</v>
       </c>
       <c r="G173">
-        <v>0.005943889927537092</v>
+        <v>0.00569404261824682</v>
       </c>
       <c r="H173">
-        <v>0.005535972054203679</v>
+        <v>0.005339852482536397</v>
       </c>
       <c r="I173">
-        <v>0.0520821266665874</v>
+        <v>0.1058098642895779</v>
       </c>
       <c r="J173">
-        <v>0.7735559710148369</v>
+        <v>0.7761883481901358</v>
       </c>
       <c r="K173">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L173">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M173">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N173">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O173">
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="174" spans="1:16">
       <c r="A174" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B174" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C174">
-        <v>2.052143468115133</v>
+        <v>2.072833064946989</v>
       </c>
       <c r="D174" t="s">
         <v>47</v>
       </c>
       <c r="E174">
-        <v>2.02402794579632</v>
+        <v>1.943041764893563</v>
       </c>
       <c r="F174">
         <v>-1</v>
       </c>
       <c r="G174">
-        <v>0.005687856531884867</v>
+        <v>0.00594716693505301</v>
       </c>
       <c r="H174">
-        <v>0.005535972054203679</v>
+        <v>0.005336958235106438</v>
       </c>
       <c r="I174">
-        <v>0.0281155223188132</v>
+        <v>0.1297913000534263</v>
       </c>
       <c r="J174">
-        <v>0.7735559710148369</v>
+        <v>0.7748667740212044</v>
       </c>
       <c r="K174">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L174">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M174">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N174">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O174">
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="175" spans="1:16">
       <c r="A175" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B175" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C175">
-        <v>2.078101340295269</v>
+        <v>2.04906308105017</v>
       </c>
       <c r="D175" t="s">
         <v>47</v>
       </c>
       <c r="E175">
-        <v>2.025836016988104</v>
+        <v>1.943041764893563</v>
       </c>
       <c r="F175">
         <v>-1</v>
       </c>
       <c r="G175">
-        <v>0.00594189865970473</v>
+        <v>0.005690936918949831</v>
       </c>
       <c r="H175">
-        <v>0.005534163983011896</v>
+        <v>0.005336958235106438</v>
       </c>
       <c r="I175">
-        <v>0.05226532330716482</v>
+        <v>0.106021316156607</v>
       </c>
       <c r="J175">
-        <v>0.7727594638818923</v>
+        <v>0.7748667740212044</v>
       </c>
       <c r="K175">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L175">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M175">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N175">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O175">
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="176" spans="1:16">
       <c r="A176" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C176">
-        <v>2.054015259877553</v>
+        <v>2.076110072462908</v>
       </c>
       <c r="D176" t="s">
         <v>47</v>
       </c>
       <c r="E176">
-        <v>2.025836016988104</v>
+        <v>1.945912423477507</v>
       </c>
       <c r="F176">
         <v>-1</v>
       </c>
       <c r="G176">
-        <v>0.005685984740122448</v>
+        <v>0.005943889927537092</v>
       </c>
       <c r="H176">
-        <v>0.005534163983011896</v>
+        <v>0.005334087576522493</v>
       </c>
       <c r="I176">
-        <v>0.02817924288944873</v>
+        <v>0.1301976489854002</v>
       </c>
       <c r="J176">
-        <v>0.7727594638818923</v>
+        <v>0.7735559710148369</v>
       </c>
       <c r="K176">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L176">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M176">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N176">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O176">
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="177" spans="1:16">
       <c r="A177" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B177" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C177">
-        <v>2.078941598729263</v>
+        <v>2.052143468115133</v>
       </c>
       <c r="D177" t="s">
         <v>47</v>
       </c>
       <c r="E177">
-        <v>2.026598971646171</v>
+        <v>1.945912423477507</v>
       </c>
       <c r="F177">
         <v>-1</v>
       </c>
       <c r="G177">
-        <v>0.005941058401270736</v>
+        <v>0.005687856531884867</v>
       </c>
       <c r="H177">
-        <v>0.005533401028353828</v>
+        <v>0.005334087576522493</v>
       </c>
       <c r="I177">
-        <v>0.05234262708309201</v>
+        <v>0.106231044637626</v>
       </c>
       <c r="J177">
-        <v>0.7724233605082945</v>
+        <v>0.7735559710148369</v>
       </c>
       <c r="K177">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L177">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M177">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N177">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O177">
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="178" spans="1:16">
       <c r="A178" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B178" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C178">
-        <v>2.054805102805508</v>
+        <v>2.078101340295269</v>
       </c>
       <c r="D178" t="s">
         <v>47</v>
       </c>
       <c r="E178">
-        <v>2.026598971646171</v>
+        <v>1.947656774098656</v>
       </c>
       <c r="F178">
         <v>-1</v>
       </c>
       <c r="G178">
-        <v>0.005685194897194492</v>
+        <v>0.00594189865970473</v>
       </c>
       <c r="H178">
-        <v>0.005533401028353828</v>
+        <v>0.005332343225901344</v>
       </c>
       <c r="I178">
-        <v>0.02820613115933668</v>
+        <v>0.1304445661966132</v>
       </c>
       <c r="J178">
-        <v>0.7724233605082945</v>
+        <v>0.7727594638818923</v>
       </c>
       <c r="K178">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L178">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M178">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N178">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O178">
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="179" spans="1:16">
       <c r="A179" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B179" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C179">
-        <v>2.079346337166745</v>
+        <v>2.054015259877553</v>
       </c>
       <c r="D179" t="s">
         <v>47</v>
       </c>
       <c r="E179">
-        <v>2.026966474147405</v>
+        <v>1.947656774098656</v>
       </c>
       <c r="F179">
         <v>-1</v>
       </c>
       <c r="G179">
-        <v>0.005940653662833254</v>
+        <v>0.005685984740122448</v>
       </c>
       <c r="H179">
-        <v>0.005533033525852595</v>
+        <v>0.005332343225901344</v>
       </c>
       <c r="I179">
-        <v>0.05237986301934061</v>
+        <v>0.1063584857788971</v>
       </c>
       <c r="J179">
-        <v>0.7722614651333018</v>
+        <v>0.7727594638818923</v>
       </c>
       <c r="K179">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L179">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M179">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N179">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O179">
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="180" spans="1:16">
       <c r="A180" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B180" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C180">
-        <v>2.055185556936741</v>
+        <v>2.078941598729263</v>
       </c>
       <c r="D180" t="s">
         <v>47</v>
       </c>
       <c r="E180">
-        <v>2.026966474147405</v>
+        <v>1.948392840486835</v>
       </c>
       <c r="F180">
         <v>-1</v>
       </c>
       <c r="G180">
-        <v>0.00568481444306326</v>
+        <v>0.005941058401270736</v>
       </c>
       <c r="H180">
-        <v>0.005533033525852595</v>
+        <v>0.005331607159513165</v>
       </c>
       <c r="I180">
-        <v>0.02821908278933627</v>
+        <v>0.1305487582424283</v>
       </c>
       <c r="J180">
-        <v>0.7722614651333018</v>
+        <v>0.7724233605082945</v>
       </c>
       <c r="K180">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L180">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M180">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N180">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O180">
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -9823,28 +9820,28 @@
         <v>31</v>
       </c>
       <c r="C181">
-        <v>2.078211043729365</v>
+        <v>2.079346337166745</v>
       </c>
       <c r="D181" t="s">
         <v>47</v>
       </c>
       <c r="E181">
-        <v>2.025935627706263</v>
+        <v>1.948747391358069</v>
       </c>
       <c r="F181">
         <v>-1</v>
       </c>
       <c r="G181">
-        <v>0.005941788956270636</v>
+        <v>0.005940653662833254</v>
       </c>
       <c r="H181">
-        <v>0.005534064372293737</v>
+        <v>0.005331252608641931</v>
       </c>
       <c r="I181">
-        <v>0.05227541602310115</v>
+        <v>0.1305989458086763</v>
       </c>
       <c r="J181">
-        <v>0.772715582508254</v>
+        <v>0.7722614651333018</v>
       </c>
       <c r="K181">
         <v>2.5</v>
@@ -9853,60 +9850,60 @@
         <v>4.01</v>
       </c>
       <c r="M181">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N181">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O181">
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="182" spans="1:16">
       <c r="A182" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B182" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C182">
-        <v>2.054118381105603</v>
+        <v>2.078211043729365</v>
       </c>
       <c r="D182" t="s">
         <v>47</v>
       </c>
       <c r="E182">
-        <v>2.025935627706263</v>
+        <v>1.947752874306924</v>
       </c>
       <c r="F182">
         <v>-1</v>
       </c>
       <c r="G182">
-        <v>0.005685881618894397</v>
+        <v>0.005941788956270636</v>
       </c>
       <c r="H182">
-        <v>0.005534064372293737</v>
+        <v>0.005332247125693077</v>
       </c>
       <c r="I182">
-        <v>0.02818275339933951</v>
+        <v>0.1304581694224407</v>
       </c>
       <c r="J182">
         <v>0.772715582508254</v>
       </c>
       <c r="K182">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L182">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M182">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N182">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O182">
         <v>1</v>
@@ -9929,7 +9926,7 @@
         <v>47</v>
       </c>
       <c r="E183">
-        <v>2.023817324951729</v>
+        <v>1.945709225393959</v>
       </c>
       <c r="F183">
         <v>-1</v>
@@ -9938,10 +9935,10 @@
         <v>0.005944121888819681</v>
       </c>
       <c r="H183">
-        <v>0.00553618267504827</v>
+        <v>0.005334290774606041</v>
       </c>
       <c r="I183">
-        <v>0.05206078622858934</v>
+        <v>0.1301688857863592</v>
       </c>
       <c r="J183">
         <v>0.7736487555278725</v>
@@ -9953,10 +9950,10 @@
         <v>4.01</v>
       </c>
       <c r="M183">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N183">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O183">
         <v>1</v>
@@ -9979,7 +9976,7 @@
         <v>47</v>
       </c>
       <c r="E184">
-        <v>2.021619221279101</v>
+        <v>1.943588587930058</v>
       </c>
       <c r="F184">
         <v>-1</v>
@@ -9988,10 +9985,10 @@
         <v>0.005946542707842399</v>
       </c>
       <c r="H184">
-        <v>0.005538380778720898</v>
+        <v>0.005336411412069943</v>
       </c>
       <c r="I184">
-        <v>0.05183807087849912</v>
+        <v>0.1298687042275422</v>
       </c>
       <c r="J184">
         <v>0.7746170831369599</v>
@@ -10003,10 +10000,10 @@
         <v>4.01</v>
       </c>
       <c r="M184">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="N184">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="O184">
         <v>1</v>
@@ -10020,99 +10017,49 @@
         <v>0</v>
       </c>
       <c r="B185" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C185">
-        <v>2.069260822060034</v>
+        <v>1.556951287041575</v>
       </c>
       <c r="D185" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="E185">
-        <v>2.017808826430511</v>
+        <v>1.909090144592829</v>
       </c>
       <c r="F185">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G185">
-        <v>0.005950739177939966</v>
+        <v>0.004663048712958424</v>
       </c>
       <c r="H185">
-        <v>0.005542191173569489</v>
+        <v>0.00597090985540717</v>
       </c>
       <c r="I185">
-        <v>0.05145199562952296</v>
+        <v>0.3521388575512543</v>
       </c>
       <c r="J185">
-        <v>0.7762956711759863</v>
+        <v>0.7964352374145769</v>
       </c>
       <c r="K185">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="L185">
-        <v>4.01</v>
+        <v>3.11</v>
       </c>
       <c r="M185">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="N185">
-        <v>3.78</v>
+        <v>3.94</v>
       </c>
       <c r="O185">
         <v>1</v>
       </c>
       <c r="P185" t="s">
         <v>146</v>
-      </c>
-    </row>
-    <row r="186" spans="1:16">
-      <c r="A186" s="1">
-        <v>0</v>
-      </c>
-      <c r="B186" t="s">
-        <v>31</v>
-      </c>
-      <c r="C186">
-        <v>2.064960635460216</v>
-      </c>
-      <c r="D186" t="s">
-        <v>47</v>
-      </c>
-      <c r="E186">
-        <v>2.013904256997876</v>
-      </c>
-      <c r="F186">
-        <v>-1</v>
-      </c>
-      <c r="G186">
-        <v>0.005955039364539783</v>
-      </c>
-      <c r="H186">
-        <v>0.005546095743002123</v>
-      </c>
-      <c r="I186">
-        <v>0.05105637846233968</v>
-      </c>
-      <c r="J186">
-        <v>0.7780157458159134</v>
-      </c>
-      <c r="K186">
-        <v>2.5</v>
-      </c>
-      <c r="L186">
-        <v>4.01</v>
-      </c>
-      <c r="M186">
-        <v>2.27</v>
-      </c>
-      <c r="N186">
-        <v>3.78</v>
-      </c>
-      <c r="O186">
-        <v>1</v>
-      </c>
-      <c r="P186" t="s">
-        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01618-601618.xlsx
+++ b/s60_signal/position-01618-601618.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="141">
   <si>
     <t>trade_time</t>
   </si>
@@ -97,27 +97,30 @@
     <t>2021-07-30</t>
   </si>
   <si>
+    <t>2021-08-06</t>
+  </si>
+  <si>
     <t>2021-08-02</t>
   </si>
   <si>
     <t>2021-08-03</t>
   </si>
   <si>
+    <t>2021-01-13</t>
+  </si>
+  <si>
     <t>2021-01-15</t>
   </si>
   <si>
-    <t>2021-01-13</t>
-  </si>
-  <si>
-    <t>2021-08-06</t>
-  </si>
-  <si>
     <t>2021-08-10</t>
   </si>
   <si>
     <t>2021-07-26</t>
   </si>
   <si>
+    <t>2021-08-11</t>
+  </si>
+  <si>
     <t>2021-02-26</t>
   </si>
   <si>
@@ -160,7 +163,7 @@
     <t>2020-10-15</t>
   </si>
   <si>
-    <t>2021-08-11</t>
+    <t>2021-08-12</t>
   </si>
   <si>
     <t>2021-01-20</t>
@@ -430,13 +433,7 @@
     <t>2021-06-07</t>
   </si>
   <si>
-    <t>2021-06-08</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>2021-06-10</t>
+    <t>2021-07-14</t>
   </si>
   <si>
     <t>2021-07-15</t>
@@ -797,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P178"/>
+  <dimension ref="A1:P177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -858,7 +855,7 @@
         <v>2.241636620202809</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E2">
         <v>2.083673377356266</v>
@@ -894,7 +891,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -908,7 +905,7 @@
         <v>2.291018963074085</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E3">
         <v>2.748932188801797</v>
@@ -944,7 +941,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -958,7 +955,7 @@
         <v>0.1640886968569069</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>0.8087275807852619</v>
@@ -994,7 +991,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1008,7 +1005,7 @@
         <v>0.1567937244930127</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5">
         <v>0.8087275807852619</v>
@@ -1044,7 +1041,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1058,7 +1055,7 @@
         <v>0.06008199184724816</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6">
         <v>0.7118353409391309</v>
@@ -1094,7 +1091,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1108,7 +1105,7 @@
         <v>0.05109309920632388</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7">
         <v>0.7118353409391309</v>
@@ -1144,7 +1141,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1158,7 +1155,7 @@
         <v>-0.0569506423664734</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8">
         <v>0.6028081963621785</v>
@@ -1194,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1208,7 +1205,7 @@
         <v>-0.06784560396853312</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9">
         <v>0.6028081963621785</v>
@@ -1244,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1258,7 +1255,7 @@
         <v>-0.1396452470657845</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10">
         <v>0.5257702258605397</v>
@@ -1294,7 +1291,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1308,7 +1305,7 @@
         <v>-0.1518870263339567</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E11">
         <v>0.5257702258605397</v>
@@ -1344,7 +1341,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1358,7 +1355,7 @@
         <v>-0.2479133877986754</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12">
         <v>0.424908049151723</v>
@@ -1394,7 +1391,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1408,7 +1405,7 @@
         <v>-0.2619184918344848</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E13">
         <v>0.424908049151723</v>
@@ -1444,7 +1441,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1458,7 +1455,7 @@
         <v>-0.3399965939203824</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E14">
         <v>0.3391236942630966</v>
@@ -1494,7 +1491,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1508,7 +1505,7 @@
         <v>0.9756011105228968</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E15">
         <v>0.8107654111102569</v>
@@ -1544,7 +1541,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1558,7 +1555,7 @@
         <v>1.301145679016073</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E16">
         <v>1.173416666670367</v>
@@ -1594,7 +1591,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1608,7 +1605,7 @@
         <v>1.296277364845049</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E17">
         <v>1.230890933009092</v>
@@ -1644,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1658,7 +1655,7 @@
         <v>0.4435035626339812</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E18">
         <v>0.9439906537348826</v>
@@ -1694,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1708,7 +1705,7 @@
         <v>0.4423533289773536</v>
       </c>
       <c r="D19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E19">
         <v>0.9439906537348826</v>
@@ -1744,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1758,7 +1755,7 @@
         <v>1.507350128118183</v>
       </c>
       <c r="D20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E20">
         <v>1.202821457299868</v>
@@ -1794,7 +1791,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -1808,7 +1805,7 @@
         <v>1.54125697476493</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E21">
         <v>1.238224194239853</v>
@@ -1844,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -1858,7 +1855,7 @@
         <v>1.573438797246031</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E22">
         <v>1.271825803006885</v>
@@ -1894,7 +1891,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -1908,7 +1905,7 @@
         <v>1.613400857289038</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E23">
         <v>1.313550895110613</v>
@@ -1944,7 +1941,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -1958,7 +1955,7 @@
         <v>1.593400857289038</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E24">
         <v>1.363275825771058</v>
@@ -1994,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2008,7 +2005,7 @@
         <v>1.645344720184119</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E25">
         <v>1.346904046074595</v>
@@ -2044,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2058,7 +2055,7 @@
         <v>1.625344720184119</v>
       </c>
       <c r="D26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E26">
         <v>1.394045281942056</v>
@@ -2094,7 +2091,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2108,7 +2105,7 @@
         <v>1.68180858461344</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E27">
         <v>1.384976610405209</v>
@@ -2144,7 +2141,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2158,7 +2155,7 @@
         <v>1.66180858461344</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E28">
         <v>1.429168563120298</v>
@@ -2194,7 +2191,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2208,7 +2205,7 @@
         <v>1.710614904938503</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E29">
         <v>1.415053797803437</v>
@@ -2244,7 +2241,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2258,7 +2255,7 @@
         <v>1.690614904938503</v>
       </c>
       <c r="D30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E30">
         <v>1.456915827551058</v>
@@ -2294,7 +2291,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2344,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2358,7 +2355,7 @@
         <v>3.072361243685425</v>
       </c>
       <c r="D32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E32">
         <v>3.272185680805519</v>
@@ -2394,7 +2391,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2444,7 +2441,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2458,10 +2455,10 @@
         <v>2.638017457305502</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E34">
-        <v>2.657763187855787</v>
+        <v>2.715915749525616</v>
       </c>
       <c r="F34">
         <v>-1</v>
@@ -2470,10 +2467,10 @@
         <v>0.004841982542694498</v>
       </c>
       <c r="H34">
-        <v>0.004722236812144213</v>
+        <v>0.004864084250474385</v>
       </c>
       <c r="I34">
-        <v>-0.01974573055028461</v>
+        <v>-0.07789829222011369</v>
       </c>
       <c r="J34">
         <v>0.4649715370018978</v>
@@ -2485,60 +2482,60 @@
         <v>3.74</v>
       </c>
       <c r="M34">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N34">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O34">
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C35">
-        <v>2.644938723766401</v>
+        <v>2.662412903225806</v>
       </c>
       <c r="D35" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E35">
-        <v>2.740332082123923</v>
+        <v>2.715915749525616</v>
       </c>
       <c r="F35">
         <v>-1</v>
       </c>
       <c r="G35">
-        <v>0.005235061276233599</v>
+        <v>0.004717587096774194</v>
       </c>
       <c r="H35">
-        <v>0.005279667917876077</v>
+        <v>0.004864084250474385</v>
       </c>
       <c r="I35">
-        <v>-0.0953933583575215</v>
+        <v>-0.05350284629981017</v>
       </c>
       <c r="J35">
-        <v>0.5078671671504308</v>
+        <v>0.4649715370018978</v>
       </c>
       <c r="K35">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="L35">
-        <v>3.94</v>
+        <v>3.69</v>
       </c>
       <c r="M35">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="N35">
-        <v>4.01</v>
+        <v>3.79</v>
       </c>
       <c r="O35">
         <v>1</v>
@@ -2549,96 +2546,96 @@
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C36">
-        <v>2.536354813853479</v>
+        <v>2.644938723766401</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E36">
-        <v>2.562534888926043</v>
+        <v>2.740332082123923</v>
       </c>
       <c r="F36">
         <v>-1</v>
       </c>
       <c r="G36">
-        <v>0.004943645186146522</v>
+        <v>0.005235061276233599</v>
       </c>
       <c r="H36">
-        <v>0.004817465111073956</v>
+        <v>0.005279667917876077</v>
       </c>
       <c r="I36">
-        <v>-0.02618007507256426</v>
+        <v>-0.0953933583575215</v>
       </c>
       <c r="J36">
         <v>0.5078671671504308</v>
       </c>
       <c r="K36">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="L36">
-        <v>3.74</v>
+        <v>3.94</v>
       </c>
       <c r="M36">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="N36">
-        <v>3.69</v>
+        <v>4.01</v>
       </c>
       <c r="O36">
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C37">
-        <v>2.551891062104373</v>
+        <v>2.536354813853479</v>
       </c>
       <c r="D37" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E37">
-        <v>2.649108884416052</v>
+        <v>2.616826843882505</v>
       </c>
       <c r="F37">
         <v>-1</v>
       </c>
       <c r="G37">
-        <v>0.005328108937895627</v>
+        <v>0.004943645186146522</v>
       </c>
       <c r="H37">
-        <v>0.005370891115583948</v>
+        <v>0.004963173156117495</v>
       </c>
       <c r="I37">
-        <v>-0.09721782231167886</v>
+        <v>-0.08047203002902581</v>
       </c>
       <c r="J37">
-        <v>0.5443564462335794</v>
+        <v>0.5078671671504308</v>
       </c>
       <c r="K37">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="L37">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
       <c r="M37">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="N37">
-        <v>4.01</v>
+        <v>3.79</v>
       </c>
       <c r="O37">
         <v>1</v>
@@ -2649,46 +2646,46 @@
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C38">
-        <v>2.449875222426417</v>
+        <v>2.567613560597548</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E38">
-        <v>2.481528689361454</v>
+        <v>2.616826843882505</v>
       </c>
       <c r="F38">
         <v>-1</v>
       </c>
       <c r="G38">
-        <v>0.005030124777573583</v>
+        <v>0.004812386439402452</v>
       </c>
       <c r="H38">
-        <v>0.004898471310638547</v>
+        <v>0.004963173156117495</v>
       </c>
       <c r="I38">
-        <v>-0.03165346693503635</v>
+        <v>-0.04921328328495722</v>
       </c>
       <c r="J38">
-        <v>0.5443564462335794</v>
+        <v>0.5078671671504308</v>
       </c>
       <c r="K38">
-        <v>2.37</v>
+        <v>2.21</v>
       </c>
       <c r="L38">
-        <v>3.74</v>
+        <v>3.69</v>
       </c>
       <c r="M38">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N38">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O38">
         <v>1</v>
@@ -2705,28 +2702,28 @@
         <v>25</v>
       </c>
       <c r="C39">
-        <v>2.433094415049971</v>
+        <v>2.551891062104373</v>
       </c>
       <c r="D39" t="s">
         <v>33</v>
       </c>
       <c r="E39">
-        <v>2.532641583382324</v>
+        <v>2.649108884416052</v>
       </c>
       <c r="F39">
         <v>-1</v>
       </c>
       <c r="G39">
-        <v>0.005446905584950029</v>
+        <v>0.005328108937895627</v>
       </c>
       <c r="H39">
-        <v>0.005487358416617676</v>
+        <v>0.005370891115583948</v>
       </c>
       <c r="I39">
-        <v>-0.09954716833235322</v>
+        <v>-0.09721782231167886</v>
       </c>
       <c r="J39">
-        <v>0.5909433666470703</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K39">
         <v>2.55</v>
@@ -2752,31 +2749,31 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C40">
-        <v>2.343554787379973</v>
+        <v>2.454431657964081</v>
       </c>
       <c r="D40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E40">
-        <v>2.378105726043504</v>
+        <v>2.532536609200432</v>
       </c>
       <c r="F40">
         <v>-1</v>
       </c>
       <c r="G40">
-        <v>0.005156445212620027</v>
+        <v>0.005045568342035919</v>
       </c>
       <c r="H40">
-        <v>0.005001894273956496</v>
+        <v>0.005047463390799568</v>
       </c>
       <c r="I40">
-        <v>-0.03455093866353121</v>
+        <v>-0.07810495123635075</v>
       </c>
       <c r="J40">
-        <v>0.5909433666470703</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K40">
         <v>2.38</v>
@@ -2785,10 +2782,10 @@
         <v>3.75</v>
       </c>
       <c r="M40">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N40">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O40">
         <v>1</v>
@@ -2799,96 +2796,96 @@
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C41">
-        <v>2.311696741357657</v>
+        <v>2.486972253823789</v>
       </c>
       <c r="D41" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E41">
-        <v>2.413624256232997</v>
+        <v>2.532536609200432</v>
       </c>
       <c r="F41">
         <v>-1</v>
       </c>
       <c r="G41">
-        <v>0.005568303258642344</v>
+        <v>0.004893027746176211</v>
       </c>
       <c r="H41">
-        <v>0.005606375743767004</v>
+        <v>0.005047463390799568</v>
       </c>
       <c r="I41">
-        <v>-0.10192751487534</v>
+        <v>-0.0455643553766425</v>
       </c>
       <c r="J41">
-        <v>0.6385502975068013</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K41">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="L41">
-        <v>3.94</v>
+        <v>3.69</v>
       </c>
       <c r="M41">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="N41">
-        <v>4.01</v>
+        <v>3.79</v>
       </c>
       <c r="O41">
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C42">
-        <v>2.369406800859017</v>
+        <v>2.433094415049971</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E42">
-        <v>2.272418339534901</v>
+        <v>2.532641583382324</v>
       </c>
       <c r="F42">
         <v>-1</v>
       </c>
       <c r="G42">
-        <v>0.005370593199140983</v>
+        <v>0.005446905584950029</v>
       </c>
       <c r="H42">
-        <v>0.005107581660465099</v>
+        <v>0.005487358416617676</v>
       </c>
       <c r="I42">
-        <v>0.09698846132411587</v>
+        <v>-0.09954716833235322</v>
       </c>
       <c r="J42">
-        <v>0.6385502975068013</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K42">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L42">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M42">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="N42">
-        <v>3.69</v>
+        <v>4.01</v>
       </c>
       <c r="O42">
         <v>1</v>
@@ -2899,146 +2896,146 @@
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B43" t="s">
         <v>29</v>
       </c>
       <c r="C43">
-        <v>2.1327030495424</v>
+        <v>2.481283088379385</v>
       </c>
       <c r="D43" t="s">
         <v>49</v>
       </c>
       <c r="E43">
-        <v>1.864454088007834</v>
+        <v>2.424920823045268</v>
       </c>
       <c r="F43">
         <v>-1</v>
       </c>
       <c r="G43">
-        <v>0.0044072969504576</v>
+        <v>0.005258716911620615</v>
       </c>
       <c r="H43">
-        <v>0.004235545911992165</v>
+        <v>0.005155079176954733</v>
       </c>
       <c r="I43">
-        <v>0.2682489615345653</v>
+        <v>0.05636226533411737</v>
       </c>
       <c r="J43">
-        <v>0.6892708790652124</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K43">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="L43">
-        <v>3.27</v>
+        <v>3.87</v>
       </c>
       <c r="M43">
-        <v>1.72</v>
+        <v>2.31</v>
       </c>
       <c r="N43">
-        <v>3.05</v>
+        <v>3.79</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C44">
-        <v>2.182359258383708</v>
+        <v>2.384015159709975</v>
       </c>
       <c r="D44" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E44">
-        <v>2.286822802336969</v>
+        <v>2.424920823045268</v>
       </c>
       <c r="F44">
         <v>-1</v>
       </c>
       <c r="G44">
-        <v>0.005697640741616292</v>
+        <v>0.004995984840290025</v>
       </c>
       <c r="H44">
-        <v>0.005733177197663031</v>
+        <v>0.005155079176954733</v>
       </c>
       <c r="I44">
-        <v>-0.1044635439532606</v>
+        <v>-0.04090566333529289</v>
       </c>
       <c r="J44">
-        <v>0.6892708790652124</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K44">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="L44">
-        <v>3.94</v>
+        <v>3.69</v>
       </c>
       <c r="M44">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="N44">
-        <v>4.01</v>
+        <v>3.79</v>
       </c>
       <c r="O44">
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C45">
-        <v>2.250213434196751</v>
+        <v>2.311696741357657</v>
       </c>
       <c r="D45" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E45">
-        <v>2.159818648475228</v>
+        <v>2.413624256232997</v>
       </c>
       <c r="F45">
         <v>-1</v>
       </c>
       <c r="G45">
-        <v>0.00548978656580325</v>
+        <v>0.005568303258642344</v>
       </c>
       <c r="H45">
-        <v>0.005220181351524772</v>
+        <v>0.005606375743767004</v>
       </c>
       <c r="I45">
-        <v>0.09039478572152282</v>
+        <v>-0.10192751487534</v>
       </c>
       <c r="J45">
-        <v>0.6892708790652124</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K45">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L45">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M45">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="N45">
-        <v>3.69</v>
+        <v>4.01</v>
       </c>
       <c r="O45">
         <v>1</v>
@@ -3049,146 +3046,146 @@
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C46">
-        <v>2.037699170124481</v>
+        <v>2.369406800859017</v>
       </c>
       <c r="D46" t="s">
         <v>49</v>
       </c>
       <c r="E46">
-        <v>1.775843983402489</v>
+        <v>2.314948812759289</v>
       </c>
       <c r="F46">
         <v>-1</v>
       </c>
       <c r="G46">
-        <v>0.004482300829875518</v>
+        <v>0.005370593199140983</v>
       </c>
       <c r="H46">
-        <v>0.004324156016597511</v>
+        <v>0.005265051187240711</v>
       </c>
       <c r="I46">
-        <v>0.2618551867219918</v>
+        <v>0.05445798809972757</v>
       </c>
       <c r="J46">
-        <v>0.7407883817427386</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K46">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="L46">
-        <v>3.26</v>
+        <v>3.87</v>
       </c>
       <c r="M46">
-        <v>1.72</v>
+        <v>2.31</v>
       </c>
       <c r="N46">
-        <v>3.05</v>
+        <v>3.79</v>
       </c>
       <c r="O46">
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C47">
-        <v>2.050989626556016</v>
+        <v>2.278803842509969</v>
       </c>
       <c r="D47" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E47">
-        <v>2.158029045643153</v>
+        <v>2.314948812759289</v>
       </c>
       <c r="F47">
         <v>-1</v>
       </c>
       <c r="G47">
-        <v>0.005829010373443984</v>
+        <v>0.005101196157490031</v>
       </c>
       <c r="H47">
-        <v>0.005861970954356846</v>
+        <v>0.005265051187240711</v>
       </c>
       <c r="I47">
-        <v>-0.1070394190871369</v>
+        <v>-0.03614497024932017</v>
       </c>
       <c r="J47">
-        <v>0.7407883817427386</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K47">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="L47">
-        <v>3.94</v>
+        <v>3.69</v>
       </c>
       <c r="M47">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="N47">
-        <v>4.01</v>
+        <v>3.79</v>
       </c>
       <c r="O47">
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C48">
-        <v>2.129147302904564</v>
+        <v>2.182359258383708</v>
       </c>
       <c r="D48" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E48">
-        <v>2.04544979253112</v>
+        <v>2.286822802336969</v>
       </c>
       <c r="F48">
         <v>-1</v>
       </c>
       <c r="G48">
-        <v>0.005610852697095436</v>
+        <v>0.005697640741616292</v>
       </c>
       <c r="H48">
-        <v>0.005334550207468879</v>
+        <v>0.005733177197663031</v>
       </c>
       <c r="I48">
-        <v>0.08369751037344431</v>
+        <v>-0.1044635439532606</v>
       </c>
       <c r="J48">
-        <v>0.7407883817427386</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K48">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L48">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M48">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="N48">
-        <v>3.69</v>
+        <v>4.01</v>
       </c>
       <c r="O48">
         <v>1</v>
@@ -3199,46 +3196,46 @@
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C49">
-        <v>2.052857676348547</v>
+        <v>2.250213434196751</v>
       </c>
       <c r="D49" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E49">
-        <v>2.04544979253112</v>
+        <v>2.197784269359359</v>
       </c>
       <c r="F49">
         <v>-1</v>
       </c>
       <c r="G49">
-        <v>0.005327142323651453</v>
+        <v>0.00548978656580325</v>
       </c>
       <c r="H49">
-        <v>0.005334550207468879</v>
+        <v>0.005382215730640641</v>
       </c>
       <c r="I49">
-        <v>0.007407883817427408</v>
+        <v>0.0524291648373918</v>
       </c>
       <c r="J49">
-        <v>0.7407883817427386</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K49">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="L49">
-        <v>3.69</v>
+        <v>3.87</v>
       </c>
       <c r="M49">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N49">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O49">
         <v>1</v>
@@ -3249,96 +3246,96 @@
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C50">
-        <v>1.939614977812812</v>
+        <v>2.16671135726588</v>
       </c>
       <c r="D50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E50">
-        <v>1.637628978619619</v>
+        <v>2.197784269359359</v>
       </c>
       <c r="F50">
         <v>-1</v>
       </c>
       <c r="G50">
-        <v>0.004580385022187188</v>
+        <v>0.005213288642734119</v>
       </c>
       <c r="H50">
-        <v>0.004182371021380382</v>
+        <v>0.005382215730640641</v>
       </c>
       <c r="I50">
-        <v>0.301985999193193</v>
+        <v>-0.03107291209347895</v>
       </c>
       <c r="J50">
-        <v>0.8002333467801142</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K50">
-        <v>1.65</v>
+        <v>2.21</v>
       </c>
       <c r="L50">
-        <v>3.26</v>
+        <v>3.69</v>
       </c>
       <c r="M50">
-        <v>1.59</v>
+        <v>2.31</v>
       </c>
       <c r="N50">
-        <v>2.91</v>
+        <v>3.79</v>
       </c>
       <c r="O50">
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C51">
-        <v>1.899404965710709</v>
+        <v>2.037699170124481</v>
       </c>
       <c r="D51" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E51">
-        <v>2.009416633049714</v>
+        <v>1.775843983402489</v>
       </c>
       <c r="F51">
         <v>-1</v>
       </c>
       <c r="G51">
-        <v>0.005980595034289291</v>
+        <v>0.004482300829875518</v>
       </c>
       <c r="H51">
-        <v>0.006010583366950286</v>
+        <v>0.004324156016597511</v>
       </c>
       <c r="I51">
-        <v>-0.1100116673390055</v>
+        <v>0.2618551867219918</v>
       </c>
       <c r="J51">
-        <v>0.8002333467801142</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K51">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="L51">
-        <v>3.94</v>
+        <v>3.26</v>
       </c>
       <c r="M51">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="N51">
-        <v>4.01</v>
+        <v>3.05</v>
       </c>
       <c r="O51">
         <v>1</v>
@@ -3349,46 +3346,46 @@
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C52">
-        <v>1.989451635066732</v>
+        <v>2.047699170124481</v>
       </c>
       <c r="D52" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E52">
-        <v>1.913481970148146</v>
+        <v>1.775843983402489</v>
       </c>
       <c r="F52">
         <v>-1</v>
       </c>
       <c r="G52">
-        <v>0.005750548364933269</v>
+        <v>0.004492300829875518</v>
       </c>
       <c r="H52">
-        <v>0.005466518029851854</v>
+        <v>0.004324156016597511</v>
       </c>
       <c r="I52">
-        <v>0.07596966491858526</v>
+        <v>0.271855186721992</v>
       </c>
       <c r="J52">
-        <v>0.8002333467801142</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K52">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="L52">
-        <v>3.87</v>
+        <v>3.27</v>
       </c>
       <c r="M52">
-        <v>2.22</v>
+        <v>1.72</v>
       </c>
       <c r="N52">
-        <v>3.69</v>
+        <v>3.05</v>
       </c>
       <c r="O52">
         <v>1</v>
@@ -3399,46 +3396,46 @@
     </row>
     <row r="53" spans="1:16">
       <c r="A53" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C53">
-        <v>1.921484303615948</v>
+        <v>2.050989626556016</v>
       </c>
       <c r="D53" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E53">
-        <v>1.913481970148146</v>
+        <v>2.158029045643153</v>
       </c>
       <c r="F53">
         <v>-1</v>
       </c>
       <c r="G53">
-        <v>0.005458515696384052</v>
+        <v>0.005829010373443984</v>
       </c>
       <c r="H53">
-        <v>0.005466518029851854</v>
+        <v>0.005861970954356846</v>
       </c>
       <c r="I53">
-        <v>0.008002333467801215</v>
+        <v>-0.1070394190871369</v>
       </c>
       <c r="J53">
-        <v>0.8002333467801142</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K53">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="L53">
-        <v>3.69</v>
+        <v>3.94</v>
       </c>
       <c r="M53">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="N53">
-        <v>3.69</v>
+        <v>4.01</v>
       </c>
       <c r="O53">
         <v>1</v>
@@ -3449,46 +3446,46 @@
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C54">
-        <v>1.89748897055155</v>
+        <v>2.129147302904564</v>
       </c>
       <c r="D54" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E54">
-        <v>1.913481970148146</v>
+        <v>2.078778838174274</v>
       </c>
       <c r="F54">
         <v>-1</v>
       </c>
       <c r="G54">
-        <v>0.005402511029448449</v>
+        <v>0.005610852697095436</v>
       </c>
       <c r="H54">
-        <v>0.005466518029851854</v>
+        <v>0.005501221161825726</v>
       </c>
       <c r="I54">
-        <v>-0.01599299959659661</v>
+        <v>0.05036846473029044</v>
       </c>
       <c r="J54">
-        <v>0.8002333467801142</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K54">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="L54">
-        <v>3.65</v>
+        <v>3.87</v>
       </c>
       <c r="M54">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N54">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O54">
         <v>1</v>
@@ -3499,146 +3496,146 @@
     </row>
     <row r="55" spans="1:16">
       <c r="A55" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B55" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C55">
-        <v>1.858458903856472</v>
+        <v>2.052857676348547</v>
       </c>
       <c r="D55" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E55">
-        <v>1.559424034625328</v>
+        <v>2.078778838174274</v>
       </c>
       <c r="F55">
         <v>-1</v>
       </c>
       <c r="G55">
-        <v>0.004661541096143528</v>
+        <v>0.005327142323651453</v>
       </c>
       <c r="H55">
-        <v>0.004260575965374673</v>
+        <v>0.005501221161825726</v>
       </c>
       <c r="I55">
-        <v>0.2990348692311444</v>
+        <v>-0.02592116182572646</v>
       </c>
       <c r="J55">
-        <v>0.8494188461475927</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K55">
-        <v>1.65</v>
+        <v>2.21</v>
       </c>
       <c r="L55">
-        <v>3.26</v>
+        <v>3.69</v>
       </c>
       <c r="M55">
-        <v>1.59</v>
+        <v>2.31</v>
       </c>
       <c r="N55">
-        <v>2.91</v>
+        <v>3.79</v>
       </c>
       <c r="O55">
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C56">
-        <v>1.886452884631018</v>
+        <v>2.027673443983402</v>
       </c>
       <c r="D56" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E56">
-        <v>1.804290161552344</v>
+        <v>2.078778838174274</v>
       </c>
       <c r="F56">
         <v>-1</v>
       </c>
       <c r="G56">
-        <v>0.006133547115368982</v>
+        <v>0.005272326556016598</v>
       </c>
       <c r="H56">
-        <v>0.005575709838447656</v>
+        <v>0.005501221161825726</v>
       </c>
       <c r="I56">
-        <v>0.08216272307867389</v>
+        <v>-0.05110539419087168</v>
       </c>
       <c r="J56">
-        <v>0.8494188461475927</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K56">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="L56">
-        <v>4.01</v>
+        <v>3.65</v>
       </c>
       <c r="M56">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N56">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O56">
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C57">
-        <v>1.873865711553157</v>
+        <v>1.939614977812812</v>
       </c>
       <c r="D57" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E57">
-        <v>1.804290161552344</v>
+        <v>1.637628978619619</v>
       </c>
       <c r="F57">
         <v>-1</v>
       </c>
       <c r="G57">
-        <v>0.005866134288446843</v>
+        <v>0.004580385022187188</v>
       </c>
       <c r="H57">
-        <v>0.005575709838447656</v>
+        <v>0.004182371021380382</v>
       </c>
       <c r="I57">
-        <v>0.06957555000081306</v>
+        <v>0.301985999193193</v>
       </c>
       <c r="J57">
-        <v>0.8494188461475927</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K57">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="L57">
-        <v>3.87</v>
+        <v>3.26</v>
       </c>
       <c r="M57">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="N57">
-        <v>3.69</v>
+        <v>2.91</v>
       </c>
       <c r="O57">
         <v>1</v>
@@ -3649,46 +3646,46 @@
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B58" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C58">
-        <v>1.81278435001382</v>
+        <v>2.009416633049714</v>
       </c>
       <c r="D58" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E58">
-        <v>1.804290161552344</v>
+        <v>1.941460968937936</v>
       </c>
       <c r="F58">
         <v>-1</v>
       </c>
       <c r="G58">
-        <v>0.00556721564998618</v>
+        <v>0.006010583366950286</v>
       </c>
       <c r="H58">
-        <v>0.005575709838447656</v>
+        <v>0.005638539031062064</v>
       </c>
       <c r="I58">
-        <v>0.008494188461475982</v>
+        <v>0.067955664111778</v>
       </c>
       <c r="J58">
-        <v>0.8494188461475927</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K58">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="L58">
-        <v>3.69</v>
+        <v>4.01</v>
       </c>
       <c r="M58">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N58">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O58">
         <v>1</v>
@@ -3699,196 +3696,196 @@
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C59">
-        <v>1.778043160662217</v>
+        <v>1.989451635066732</v>
       </c>
       <c r="D59" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E59">
-        <v>1.4819325002745</v>
+        <v>1.941460968937936</v>
       </c>
       <c r="F59">
         <v>-1</v>
       </c>
       <c r="G59">
-        <v>0.004741956839337784</v>
+        <v>0.005750548364933269</v>
       </c>
       <c r="H59">
-        <v>0.004338067499725501</v>
+        <v>0.005638539031062064</v>
       </c>
       <c r="I59">
-        <v>0.2961106603877166</v>
+        <v>0.04799066612879543</v>
       </c>
       <c r="J59">
-        <v>0.898155660204717</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K59">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="L59">
-        <v>3.26</v>
+        <v>3.87</v>
       </c>
       <c r="M59">
-        <v>1.59</v>
+        <v>2.31</v>
       </c>
       <c r="N59">
-        <v>2.91</v>
+        <v>3.79</v>
       </c>
       <c r="O59">
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C60">
-        <v>1.253223538131198</v>
+        <v>1.921484303615948</v>
       </c>
       <c r="D60" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E60">
-        <v>1.508412028621273</v>
+        <v>1.941460968937936</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G60">
-        <v>0.005366776461868803</v>
+        <v>0.005458515696384052</v>
       </c>
       <c r="H60">
-        <v>0.004831587971378727</v>
+        <v>0.005638539031062064</v>
       </c>
       <c r="I60">
-        <v>0.2551884904900752</v>
+        <v>-0.01997666532198861</v>
       </c>
       <c r="J60">
-        <v>0.898155660204717</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K60">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="L60">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
       <c r="M60">
-        <v>1.85</v>
+        <v>2.31</v>
       </c>
       <c r="N60">
-        <v>3.17</v>
+        <v>3.79</v>
       </c>
       <c r="O60">
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C61">
-        <v>1.764610849488207</v>
+        <v>1.913481970148146</v>
       </c>
       <c r="D61" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E61">
-        <v>1.696094434345528</v>
+        <v>1.941460968937936</v>
       </c>
       <c r="F61">
         <v>-1</v>
       </c>
       <c r="G61">
-        <v>0.006255389150511792</v>
+        <v>0.005466518029851854</v>
       </c>
       <c r="H61">
-        <v>0.005683905565654472</v>
+        <v>0.005638539031062064</v>
       </c>
       <c r="I61">
-        <v>0.06851641514267914</v>
+        <v>-0.02797899878978982</v>
       </c>
       <c r="J61">
-        <v>0.898155660204717</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K61">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="L61">
-        <v>4.01</v>
+        <v>3.69</v>
       </c>
       <c r="M61">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N61">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O61">
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" spans="1:16">
       <c r="A62" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C62">
-        <v>1.759334198518915</v>
+        <v>1.858458903856472</v>
       </c>
       <c r="D62" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E62">
-        <v>1.696094434345528</v>
+        <v>1.559424034625328</v>
       </c>
       <c r="F62">
         <v>-1</v>
       </c>
       <c r="G62">
-        <v>0.005980665801481085</v>
+        <v>0.004661541096143528</v>
       </c>
       <c r="H62">
-        <v>0.005683905565654472</v>
+        <v>0.004260575965374673</v>
       </c>
       <c r="I62">
-        <v>0.06323976417338706</v>
+        <v>0.2990348692311444</v>
       </c>
       <c r="J62">
-        <v>0.898155660204717</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K62">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="L62">
-        <v>3.87</v>
+        <v>3.26</v>
       </c>
       <c r="M62">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="N62">
-        <v>3.69</v>
+        <v>2.91</v>
       </c>
       <c r="O62">
         <v>1</v>
@@ -3899,46 +3896,46 @@
     </row>
     <row r="63" spans="1:16">
       <c r="A63" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B63" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C63">
-        <v>1.705075990947575</v>
+        <v>1.886452884631018</v>
       </c>
       <c r="D63" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E63">
-        <v>1.696094434345528</v>
+        <v>1.827842465399061</v>
       </c>
       <c r="F63">
         <v>-1</v>
       </c>
       <c r="G63">
-        <v>0.005674924009052424</v>
+        <v>0.006133547115368982</v>
       </c>
       <c r="H63">
-        <v>0.005683905565654472</v>
+        <v>0.005752157534600939</v>
       </c>
       <c r="I63">
-        <v>0.008981556602047247</v>
+        <v>0.05861041923195698</v>
       </c>
       <c r="J63">
-        <v>0.898155660204717</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K63">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="L63">
-        <v>3.69</v>
+        <v>4.01</v>
       </c>
       <c r="M63">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N63">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O63">
         <v>1</v>
@@ -3949,196 +3946,196 @@
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C64">
-        <v>1.698438247560837</v>
+        <v>1.873865711553157</v>
       </c>
       <c r="D64" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E64">
-        <v>1.372006375010957</v>
+        <v>1.827842465399061</v>
       </c>
       <c r="F64">
         <v>-1</v>
       </c>
       <c r="G64">
-        <v>0.004821561752439162</v>
+        <v>0.005866134288446843</v>
       </c>
       <c r="H64">
-        <v>0.004267993624989043</v>
+        <v>0.005752157534600939</v>
       </c>
       <c r="I64">
-        <v>0.3264318725498792</v>
+        <v>0.04602324615409614</v>
       </c>
       <c r="J64">
-        <v>0.9464010620843414</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K64">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="L64">
-        <v>3.26</v>
+        <v>3.87</v>
       </c>
       <c r="M64">
-        <v>1.53</v>
+        <v>2.31</v>
       </c>
       <c r="N64">
-        <v>2.82</v>
+        <v>3.79</v>
       </c>
       <c r="O64">
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C65">
-        <v>1.142741567826858</v>
+        <v>1.81278435001382</v>
       </c>
       <c r="D65" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E65">
-        <v>1.419158035143968</v>
+        <v>1.827842465399061</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G65">
-        <v>0.005477258432173141</v>
+        <v>0.00556721564998618</v>
       </c>
       <c r="H65">
-        <v>0.004920841964856031</v>
+        <v>0.005752157534600939</v>
       </c>
       <c r="I65">
-        <v>0.2764164673171099</v>
+        <v>-0.01505811538524093</v>
       </c>
       <c r="J65">
-        <v>0.9464010620843414</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K65">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="L65">
-        <v>3.31</v>
+        <v>3.69</v>
       </c>
       <c r="M65">
-        <v>1.85</v>
+        <v>2.31</v>
       </c>
       <c r="N65">
-        <v>3.17</v>
+        <v>3.79</v>
       </c>
       <c r="O65">
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B66" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C66">
-        <v>1.643997344789146</v>
+        <v>1.804290161552344</v>
       </c>
       <c r="D66" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E66">
-        <v>1.588989642172762</v>
+        <v>1.827842465399061</v>
       </c>
       <c r="F66">
         <v>-1</v>
       </c>
       <c r="G66">
-        <v>0.006376002655210854</v>
+        <v>0.005575709838447656</v>
       </c>
       <c r="H66">
-        <v>0.005791010357827238</v>
+        <v>0.005752157534600939</v>
       </c>
       <c r="I66">
-        <v>0.05500770261638444</v>
+        <v>-0.02355230384671692</v>
       </c>
       <c r="J66">
-        <v>0.9464010620843414</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K66">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="L66">
-        <v>4.01</v>
+        <v>3.69</v>
       </c>
       <c r="M66">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N66">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O66">
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" spans="1:16">
       <c r="A67" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C67">
-        <v>1.645957504101798</v>
+        <v>1.778043160662217</v>
       </c>
       <c r="D67" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E67">
-        <v>1.588989642172762</v>
+        <v>1.4819325002745</v>
       </c>
       <c r="F67">
         <v>-1</v>
       </c>
       <c r="G67">
-        <v>0.006094042495898203</v>
+        <v>0.004741956839337784</v>
       </c>
       <c r="H67">
-        <v>0.005791010357827238</v>
+        <v>0.004338067499725501</v>
       </c>
       <c r="I67">
-        <v>0.05696786192903591</v>
+        <v>0.2961106603877166</v>
       </c>
       <c r="J67">
-        <v>0.9464010620843414</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K67">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="L67">
-        <v>3.87</v>
+        <v>3.26</v>
       </c>
       <c r="M67">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="N67">
-        <v>3.69</v>
+        <v>2.91</v>
       </c>
       <c r="O67">
         <v>1</v>
@@ -4149,34 +4146,34 @@
     </row>
     <row r="68" spans="1:16">
       <c r="A68" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B68" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C68">
-        <v>1.02473295176371</v>
+        <v>1.253223538131198</v>
       </c>
       <c r="D68" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E68">
-        <v>1.323823563651905</v>
+        <v>1.508412028621273</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68">
-        <v>0.005595267048236289</v>
+        <v>0.005366776461868803</v>
       </c>
       <c r="H68">
-        <v>0.005016176436348095</v>
+        <v>0.004831587971378727</v>
       </c>
       <c r="I68">
-        <v>0.2990906118881951</v>
+        <v>0.2551884904900752</v>
       </c>
       <c r="J68">
-        <v>0.9979332088368078</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K68">
         <v>2.29</v>
@@ -4194,39 +4191,39 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B69" t="s">
         <v>33</v>
       </c>
       <c r="C69">
-        <v>1.51516697790798</v>
+        <v>1.764610849488207</v>
       </c>
       <c r="D69" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E69">
-        <v>1.474588276382287</v>
+        <v>1.715260424927104</v>
       </c>
       <c r="F69">
         <v>-1</v>
       </c>
       <c r="G69">
-        <v>0.00650483302209202</v>
+        <v>0.006255389150511792</v>
       </c>
       <c r="H69">
-        <v>0.005905411723617714</v>
+        <v>0.005864739575072896</v>
       </c>
       <c r="I69">
-        <v>0.04057870152569354</v>
+        <v>0.04935042456110361</v>
       </c>
       <c r="J69">
-        <v>0.9979332088368078</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K69">
         <v>2.5</v>
@@ -4235,48 +4232,48 @@
         <v>4.01</v>
       </c>
       <c r="M69">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N69">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O69">
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B70" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C70">
-        <v>1.524856959233502</v>
+        <v>1.759334198518915</v>
       </c>
       <c r="D70" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E70">
-        <v>1.474588276382287</v>
+        <v>1.715260424927104</v>
       </c>
       <c r="F70">
         <v>-1</v>
       </c>
       <c r="G70">
-        <v>0.006215143040766499</v>
+        <v>0.005980665801481085</v>
       </c>
       <c r="H70">
-        <v>0.005905411723617714</v>
+        <v>0.005864739575072896</v>
       </c>
       <c r="I70">
-        <v>0.05026868285121511</v>
+        <v>0.04407377359181153</v>
       </c>
       <c r="J70">
-        <v>0.9979332088368078</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K70">
         <v>2.35</v>
@@ -4285,154 +4282,154 @@
         <v>3.87</v>
       </c>
       <c r="M70">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N70">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O70">
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B71" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C71">
-        <v>1.025578495611604</v>
+        <v>1.705075990947575</v>
       </c>
       <c r="D71" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E71">
-        <v>1.267956426585794</v>
+        <v>1.715260424927104</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G71">
-        <v>0.005734421504388396</v>
+        <v>0.005674924009052424</v>
       </c>
       <c r="H71">
-        <v>0.005072043573414206</v>
+        <v>0.005864739575072896</v>
       </c>
       <c r="I71">
-        <v>0.2423779309741898</v>
+        <v>-0.01018443397952828</v>
       </c>
       <c r="J71">
-        <v>1.028131661304976</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K71">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="L71">
-        <v>3.38</v>
+        <v>3.69</v>
       </c>
       <c r="M71">
-        <v>1.85</v>
+        <v>2.31</v>
       </c>
       <c r="N71">
-        <v>3.17</v>
+        <v>3.79</v>
       </c>
       <c r="O71">
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C72">
-        <v>1.453890595933306</v>
+        <v>1.698438247560837</v>
       </c>
       <c r="D72" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E72">
-        <v>1.407547711902953</v>
+        <v>1.372006375010957</v>
       </c>
       <c r="F72">
         <v>-1</v>
       </c>
       <c r="G72">
-        <v>0.006286109404066695</v>
+        <v>0.004821561752439162</v>
       </c>
       <c r="H72">
-        <v>0.005972452288097048</v>
+        <v>0.004267993624989043</v>
       </c>
       <c r="I72">
-        <v>0.04634288403035303</v>
+        <v>0.3264318725498792</v>
       </c>
       <c r="J72">
-        <v>1.028131661304976</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K72">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="L72">
-        <v>3.87</v>
+        <v>3.26</v>
       </c>
       <c r="M72">
-        <v>2.22</v>
+        <v>1.53</v>
       </c>
       <c r="N72">
-        <v>3.69</v>
+        <v>2.82</v>
       </c>
       <c r="O72">
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B73" t="s">
         <v>35</v>
       </c>
       <c r="C73">
-        <v>0.95505474527386</v>
+        <v>1.142741567826858</v>
       </c>
       <c r="D73" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E73">
-        <v>1.210983091160105</v>
+        <v>1.419158035143968</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73">
-        <v>0.00580494525472614</v>
+        <v>0.005477258432173141</v>
       </c>
       <c r="H73">
-        <v>0.005129016908839895</v>
+        <v>0.004920841964856031</v>
       </c>
       <c r="I73">
-        <v>0.2559283458862451</v>
+        <v>0.2764164673171099</v>
       </c>
       <c r="J73">
-        <v>1.058928058832376</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K73">
         <v>2.29</v>
       </c>
       <c r="L73">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="M73">
         <v>1.85</v>
@@ -4444,107 +4441,107 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="74" spans="1:16">
       <c r="A74" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B74" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C74">
-        <v>0.8997461387005035</v>
+        <v>1.643997344789146</v>
       </c>
       <c r="D74" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E74">
-        <v>1.166301465762415</v>
+        <v>1.603813546585172</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G74">
-        <v>0.005860253861299496</v>
+        <v>0.006376002655210854</v>
       </c>
       <c r="H74">
-        <v>0.005173698534237585</v>
+        <v>0.005976186453414829</v>
       </c>
       <c r="I74">
-        <v>0.2665553270619117</v>
+        <v>0.04018379820397477</v>
       </c>
       <c r="J74">
-        <v>1.083080288777073</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K74">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="L74">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="M74">
-        <v>1.85</v>
+        <v>2.31</v>
       </c>
       <c r="N74">
-        <v>3.17</v>
+        <v>3.79</v>
       </c>
       <c r="O74">
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B75" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C75">
-        <v>0.9004291893178089</v>
+        <v>1.645957504101798</v>
       </c>
       <c r="D75" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E75">
-        <v>1.166853275213077</v>
+        <v>1.603813546585172</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G75">
-        <v>0.005859570810682191</v>
+        <v>0.006094042495898203</v>
       </c>
       <c r="H75">
-        <v>0.005173146724786923</v>
+        <v>0.005976186453414829</v>
       </c>
       <c r="I75">
-        <v>0.2664240858952684</v>
+        <v>0.04214395751662625</v>
       </c>
       <c r="J75">
-        <v>1.082782013398337</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K75">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="L75">
-        <v>3.38</v>
+        <v>3.87</v>
       </c>
       <c r="M75">
-        <v>1.85</v>
+        <v>2.31</v>
       </c>
       <c r="N75">
-        <v>3.17</v>
+        <v>3.79</v>
       </c>
       <c r="O75">
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4552,87 +4549,87 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C76">
-        <v>0.8995341152947529</v>
+        <v>1.613410205419267</v>
       </c>
       <c r="D76" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E76">
-        <v>1.166130180478294</v>
+        <v>1.623410205419267</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G76">
-        <v>0.005860465884705247</v>
+        <v>0.004906589794580732</v>
       </c>
       <c r="H76">
-        <v>0.005173869819521706</v>
+        <v>0.004916589794580733</v>
       </c>
       <c r="I76">
-        <v>0.2665960651835411</v>
+        <v>-0.01000000000000023</v>
       </c>
       <c r="J76">
-        <v>1.083172875417138</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K76">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="L76">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="M76">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="N76">
-        <v>3.17</v>
+        <v>3.27</v>
       </c>
       <c r="O76">
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B77" t="s">
         <v>35</v>
       </c>
       <c r="C77">
-        <v>0.8942975364165378</v>
+        <v>1.02473295176371</v>
       </c>
       <c r="D77" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E77">
-        <v>1.161899756493709</v>
+        <v>1.323823563651905</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77">
-        <v>0.005865702463583462</v>
+        <v>0.005595267048236289</v>
       </c>
       <c r="H77">
-        <v>0.00517810024350629</v>
+        <v>0.005016176436348095</v>
       </c>
       <c r="I77">
-        <v>0.2676022200771717</v>
+        <v>0.2990906118881951</v>
       </c>
       <c r="J77">
-        <v>1.085459591084481</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K77">
         <v>2.29</v>
       </c>
       <c r="L77">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="M77">
         <v>1.85</v>
@@ -4644,107 +4641,107 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C78">
-        <v>0.823882990348408</v>
+        <v>1.51516697790798</v>
       </c>
       <c r="D78" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E78">
-        <v>1.068500891892621</v>
+        <v>1.484774287586974</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G78">
-        <v>0.005936117009651592</v>
+        <v>0.00650483302209202</v>
       </c>
       <c r="H78">
-        <v>0.005131499108107379</v>
+        <v>0.006095225712413025</v>
       </c>
       <c r="I78">
-        <v>0.2446179015442134</v>
+        <v>0.03039269032100611</v>
       </c>
       <c r="J78">
-        <v>1.1162083011579</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K78">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="L78">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="M78">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="N78">
-        <v>3.1</v>
+        <v>3.79</v>
       </c>
       <c r="O78">
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="79" spans="1:16">
       <c r="A79" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B79" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C79">
-        <v>0.7552208383877499</v>
+        <v>1.524856959233502</v>
       </c>
       <c r="D79" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E79">
-        <v>1.013930971993758</v>
+        <v>1.484774287586974</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G79">
-        <v>0.00600477916161225</v>
+        <v>0.006215143040766499</v>
       </c>
       <c r="H79">
-        <v>0.005186069028006243</v>
+        <v>0.006095225712413025</v>
       </c>
       <c r="I79">
-        <v>0.2587101336060078</v>
+        <v>0.04008267164652768</v>
       </c>
       <c r="J79">
-        <v>1.146191773629804</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K79">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="L79">
-        <v>3.38</v>
+        <v>3.87</v>
       </c>
       <c r="M79">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="N79">
-        <v>3.1</v>
+        <v>3.79</v>
       </c>
       <c r="O79">
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -4752,31 +4749,31 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C80">
-        <v>0.7164672131147527</v>
+        <v>1.025578495611604</v>
       </c>
       <c r="D80" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E80">
-        <v>0.6464672131147529</v>
+        <v>1.267956426585794</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80">
-        <v>0.006043532786885248</v>
+        <v>0.005734421504388396</v>
       </c>
       <c r="H80">
-        <v>0.005973532786885247</v>
+        <v>0.005072043573414206</v>
       </c>
       <c r="I80">
-        <v>-0.06999999999999984</v>
+        <v>0.2423779309741898</v>
       </c>
       <c r="J80">
-        <v>1.163114754098361</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K80">
         <v>2.29</v>
@@ -4785,66 +4782,66 @@
         <v>3.38</v>
       </c>
       <c r="M80">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="N80">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="O80">
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="81" spans="1:16">
       <c r="A81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B81" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C81">
-        <v>0.6498239504652852</v>
+        <v>1.453890595933306</v>
       </c>
       <c r="D81" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E81">
-        <v>0.5798239504652853</v>
+        <v>1.415015862385505</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G81">
-        <v>0.006110176049534715</v>
+        <v>0.006286109404066695</v>
       </c>
       <c r="H81">
-        <v>0.006040176049534715</v>
+        <v>0.006164984137614495</v>
       </c>
       <c r="I81">
-        <v>-0.06999999999999984</v>
+        <v>0.03887473354780102</v>
       </c>
       <c r="J81">
-        <v>1.192216615517343</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K81">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="L81">
-        <v>3.38</v>
+        <v>3.87</v>
       </c>
       <c r="M81">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="N81">
-        <v>3.31</v>
+        <v>3.79</v>
       </c>
       <c r="O81">
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -4855,78 +4852,78 @@
         <v>36</v>
       </c>
       <c r="C82">
-        <v>0.5205928926738919</v>
+        <v>0.95505474527386</v>
       </c>
       <c r="D82" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E82">
-        <v>0.4040417624885522</v>
+        <v>1.210983091160105</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82">
-        <v>0.006459407107326108</v>
+        <v>0.00580494525472614</v>
       </c>
       <c r="H82">
-        <v>0.006215958237511448</v>
+        <v>0.005129016908839895</v>
       </c>
       <c r="I82">
-        <v>-0.1165511301853397</v>
+        <v>0.2559283458862451</v>
       </c>
       <c r="J82">
-        <v>1.268977396293209</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K82">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="L82">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="M82">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="N82">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="O82">
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C83">
-        <v>0.474041762488552</v>
+        <v>0.8997461387005035</v>
       </c>
       <c r="D83" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E83">
-        <v>0.4040417624885522</v>
+        <v>1.166301465762415</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83">
-        <v>0.006285958237511447</v>
+        <v>0.005860253861299496</v>
       </c>
       <c r="H83">
-        <v>0.006215958237511448</v>
+        <v>0.005173698534237585</v>
       </c>
       <c r="I83">
-        <v>-0.06999999999999984</v>
+        <v>0.2665553270619117</v>
       </c>
       <c r="J83">
-        <v>1.268977396293209</v>
+        <v>1.083080288777073</v>
       </c>
       <c r="K83">
         <v>2.29</v>
@@ -4935,16 +4932,16 @@
         <v>3.38</v>
       </c>
       <c r="M83">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="N83">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="O83">
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -4955,78 +4952,78 @@
         <v>36</v>
       </c>
       <c r="C84">
-        <v>0.3774746016246668</v>
+        <v>0.9004291893178089</v>
       </c>
       <c r="D84" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E84">
-        <v>0.2639815545814042</v>
+        <v>1.166853275213077</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84">
-        <v>0.006602525398375333</v>
+        <v>0.005859570810682191</v>
       </c>
       <c r="H84">
-        <v>0.006356018445418596</v>
+        <v>0.005173146724786923</v>
       </c>
       <c r="I84">
-        <v>-0.1134930470432627</v>
+        <v>0.2664240858952684</v>
       </c>
       <c r="J84">
-        <v>1.330139059134758</v>
+        <v>1.082782013398337</v>
       </c>
       <c r="K84">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="L84">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="M84">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="N84">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="O84">
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
     </row>
     <row r="85" spans="1:16">
       <c r="A85" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C85">
-        <v>0.333981554581404</v>
+        <v>0.8995341152947529</v>
       </c>
       <c r="D85" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E85">
-        <v>0.2639815545814042</v>
+        <v>1.166130180478294</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85">
-        <v>0.006426018445418596</v>
+        <v>0.005860465884705247</v>
       </c>
       <c r="H85">
-        <v>0.006356018445418596</v>
+        <v>0.005173869819521706</v>
       </c>
       <c r="I85">
-        <v>-0.06999999999999984</v>
+        <v>0.2665960651835411</v>
       </c>
       <c r="J85">
-        <v>1.330139059134758</v>
+        <v>1.083172875417138</v>
       </c>
       <c r="K85">
         <v>2.29</v>
@@ -5035,66 +5032,66 @@
         <v>3.38</v>
       </c>
       <c r="M85">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="N85">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="O85">
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C86">
-        <v>0.4202010228602702</v>
+        <v>0.8942975364165378</v>
       </c>
       <c r="D86" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E86">
-        <v>0.6791469123747405</v>
+        <v>1.161899756493709</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86">
-        <v>0.00613979897713973</v>
+        <v>0.005865702463583462</v>
       </c>
       <c r="H86">
-        <v>0.00552085308762526</v>
+        <v>0.00517810024350629</v>
       </c>
       <c r="I86">
-        <v>0.2589458895144703</v>
+        <v>0.2676022200771717</v>
       </c>
       <c r="J86">
-        <v>1.330139059134758</v>
+        <v>1.085459591084481</v>
       </c>
       <c r="K86">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="L86">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="M86">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="N86">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="O86">
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5105,46 +5102,46 @@
         <v>36</v>
       </c>
       <c r="C87">
-        <v>0.2442505289553791</v>
+        <v>0.823882990348408</v>
       </c>
       <c r="D87" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="E87">
-        <v>0.1336041501315459</v>
+        <v>1.068500891892621</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87">
-        <v>0.006735749471044622</v>
+        <v>0.005936117009651592</v>
       </c>
       <c r="H87">
-        <v>0.006486395849868455</v>
+        <v>0.005131499108107379</v>
       </c>
       <c r="I87">
-        <v>-0.1106463788238332</v>
+        <v>0.2446179015442134</v>
       </c>
       <c r="J87">
-        <v>1.387072423523342</v>
+        <v>1.1162083011579</v>
       </c>
       <c r="K87">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="L87">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="M87">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="N87">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="O87">
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5152,99 +5149,99 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C88">
-        <v>2.01907486979781</v>
+        <v>0.7552208383877499</v>
       </c>
       <c r="D88" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E88">
-        <v>1.922058484380455</v>
+        <v>1.013930971993758</v>
       </c>
       <c r="F88">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G88">
-        <v>0.00600092513020219</v>
+        <v>0.00600477916161225</v>
       </c>
       <c r="H88">
-        <v>0.005457941515619545</v>
+        <v>0.005186069028006243</v>
       </c>
       <c r="I88">
-        <v>0.09701638541735469</v>
+        <v>0.2587101336060078</v>
       </c>
       <c r="J88">
-        <v>0.7963700520808761</v>
+        <v>1.146191773629804</v>
       </c>
       <c r="K88">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="L88">
-        <v>4.01</v>
+        <v>3.38</v>
       </c>
       <c r="M88">
-        <v>2.22</v>
+        <v>1.82</v>
       </c>
       <c r="N88">
-        <v>3.69</v>
+        <v>3.1</v>
       </c>
       <c r="O88">
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="89" spans="1:16">
       <c r="A89" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C89">
-        <v>1.998530377609941</v>
+        <v>0.7164672131147527</v>
       </c>
       <c r="D89" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E89">
-        <v>1.922058484380455</v>
+        <v>0.6464672131147529</v>
       </c>
       <c r="F89">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G89">
-        <v>0.005741469622390059</v>
+        <v>0.006043532786885248</v>
       </c>
       <c r="H89">
-        <v>0.005457941515619545</v>
+        <v>0.005973532786885247</v>
       </c>
       <c r="I89">
-        <v>0.07647189322948633</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J89">
-        <v>0.7963700520808761</v>
+        <v>1.163114754098361</v>
       </c>
       <c r="K89">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="L89">
-        <v>3.87</v>
+        <v>3.38</v>
       </c>
       <c r="M89">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="N89">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="O89">
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5252,299 +5249,299 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C90">
-        <v>2.009451144824672</v>
+        <v>0.6498239504652852</v>
       </c>
       <c r="D90" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E90">
-        <v>1.913512616604309</v>
+        <v>0.5798239504652853</v>
       </c>
       <c r="F90">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G90">
-        <v>0.006010548855175328</v>
+        <v>0.006110176049534715</v>
       </c>
       <c r="H90">
-        <v>0.005466487383395691</v>
+        <v>0.006040176049534715</v>
       </c>
       <c r="I90">
-        <v>0.09593852822036353</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J90">
-        <v>0.8002195420701311</v>
+        <v>1.192216615517343</v>
       </c>
       <c r="K90">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="L90">
-        <v>4.01</v>
+        <v>3.38</v>
       </c>
       <c r="M90">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="N90">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="O90">
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C91">
-        <v>1.989484076135192</v>
+        <v>0.5205928926738919</v>
       </c>
       <c r="D91" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E91">
-        <v>1.913512616604309</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F91">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G91">
-        <v>0.005750515923864809</v>
+        <v>0.006459407107326108</v>
       </c>
       <c r="H91">
-        <v>0.005466487383395691</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I91">
-        <v>0.07597145953088336</v>
+        <v>-0.1165511301853397</v>
       </c>
       <c r="J91">
-        <v>0.8002195420701311</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K91">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="L91">
-        <v>3.87</v>
+        <v>3.49</v>
       </c>
       <c r="M91">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="N91">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="O91">
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B92" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C92">
-        <v>1.996409318396163</v>
+        <v>0.474041762488552</v>
       </c>
       <c r="D92" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E92">
-        <v>1.901931474735792</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F92">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G92">
-        <v>0.006023590681603837</v>
+        <v>0.006285958237511447</v>
       </c>
       <c r="H92">
-        <v>0.005478068525264208</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I92">
-        <v>0.09447784366037015</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J92">
-        <v>0.8054362726415348</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K92">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="L92">
-        <v>4.01</v>
+        <v>3.38</v>
       </c>
       <c r="M92">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="N92">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="O92">
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93" spans="1:16">
       <c r="A93" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C93">
-        <v>1.977224759292393</v>
+        <v>0.3774746016246668</v>
       </c>
       <c r="D93" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E93">
-        <v>1.901931474735792</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F93">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G93">
-        <v>0.005762775240707607</v>
+        <v>0.006602525398375333</v>
       </c>
       <c r="H93">
-        <v>0.005478068525264208</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I93">
-        <v>0.07529328455660078</v>
+        <v>-0.1134930470432627</v>
       </c>
       <c r="J93">
-        <v>0.8054362726415348</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K93">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="L93">
-        <v>3.87</v>
+        <v>3.49</v>
       </c>
       <c r="M93">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="N93">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="O93">
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
     </row>
     <row r="94" spans="1:16">
       <c r="A94" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B94" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C94">
-        <v>1.981381467084703</v>
+        <v>0.333981554581404</v>
       </c>
       <c r="D94" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E94">
-        <v>1.888586742771217</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F94">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G94">
-        <v>0.006038618532915297</v>
+        <v>0.006426018445418596</v>
       </c>
       <c r="H94">
-        <v>0.005491413257228784</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I94">
-        <v>0.09279472431348657</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J94">
-        <v>0.8114474131661186</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K94">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="L94">
-        <v>4.01</v>
+        <v>3.38</v>
       </c>
       <c r="M94">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="N94">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="O94">
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
     </row>
     <row r="95" spans="1:16">
       <c r="A95" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C95">
-        <v>1.963098579059621</v>
+        <v>0.4202010228602702</v>
       </c>
       <c r="D95" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E95">
-        <v>1.888586742771217</v>
+        <v>0.6791469123747405</v>
       </c>
       <c r="F95">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G95">
-        <v>0.005776901420940379</v>
+        <v>0.00613979897713973</v>
       </c>
       <c r="H95">
-        <v>0.005491413257228784</v>
+        <v>0.00552085308762526</v>
       </c>
       <c r="I95">
-        <v>0.07451183628840474</v>
+        <v>0.2589458895144703</v>
       </c>
       <c r="J95">
-        <v>0.8114474131661186</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K95">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="L95">
-        <v>3.87</v>
+        <v>3.28</v>
       </c>
       <c r="M95">
-        <v>2.22</v>
+        <v>1.82</v>
       </c>
       <c r="N95">
-        <v>3.69</v>
+        <v>3.1</v>
       </c>
       <c r="O95">
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5552,349 +5549,349 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C96">
-        <v>1.977186894395391</v>
+        <v>0.2442505289553791</v>
       </c>
       <c r="D96" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E96">
-        <v>1.884861962223107</v>
+        <v>0.1336041501315459</v>
       </c>
       <c r="F96">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G96">
-        <v>0.006042813105604609</v>
+        <v>0.006735749471044622</v>
       </c>
       <c r="H96">
-        <v>0.005495138037776893</v>
+        <v>0.006486395849868455</v>
       </c>
       <c r="I96">
-        <v>0.09232493217228366</v>
+        <v>-0.1106463788238332</v>
       </c>
       <c r="J96">
-        <v>0.8131252422418436</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K96">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="L96">
-        <v>4.01</v>
+        <v>3.49</v>
       </c>
       <c r="M96">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="N96">
-        <v>3.69</v>
+        <v>3.31</v>
       </c>
       <c r="O96">
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:16">
       <c r="A97" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C97">
-        <v>1.959155680731668</v>
+        <v>2.01907486979781</v>
       </c>
       <c r="D97" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E97">
-        <v>1.884861962223107</v>
+        <v>1.950385179693176</v>
       </c>
       <c r="F97">
         <v>-1</v>
       </c>
       <c r="G97">
-        <v>0.005780844319268333</v>
+        <v>0.00600092513020219</v>
       </c>
       <c r="H97">
-        <v>0.005495138037776893</v>
+        <v>0.005629614820306824</v>
       </c>
       <c r="I97">
-        <v>0.07429371850856059</v>
+        <v>0.06868969010463344</v>
       </c>
       <c r="J97">
-        <v>0.8131252422418436</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K97">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L97">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M97">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N97">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O97">
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:16">
       <c r="A98" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B98" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C98">
-        <v>1.972128109819418</v>
+        <v>1.998530377609941</v>
       </c>
       <c r="D98" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E98">
-        <v>1.880369761519644</v>
+        <v>1.950385179693176</v>
       </c>
       <c r="F98">
         <v>-1</v>
       </c>
       <c r="G98">
-        <v>0.006047871890180582</v>
+        <v>0.005741469622390059</v>
       </c>
       <c r="H98">
-        <v>0.005499630238480356</v>
+        <v>0.005629614820306824</v>
       </c>
       <c r="I98">
-        <v>0.09175834829977458</v>
+        <v>0.04814519791676508</v>
       </c>
       <c r="J98">
-        <v>0.8151487560722326</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K98">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L98">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M98">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N98">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O98">
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C99">
-        <v>1.954400423230253</v>
+        <v>2.009451144824672</v>
       </c>
       <c r="D99" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E99">
-        <v>1.880369761519644</v>
+        <v>1.941492857817997</v>
       </c>
       <c r="F99">
         <v>-1</v>
       </c>
       <c r="G99">
-        <v>0.005785599576769747</v>
+        <v>0.006010548855175328</v>
       </c>
       <c r="H99">
-        <v>0.005499630238480356</v>
+        <v>0.005638507142182003</v>
       </c>
       <c r="I99">
-        <v>0.0740306617106099</v>
+        <v>0.06795828700667506</v>
       </c>
       <c r="J99">
-        <v>0.8151487560722326</v>
+        <v>0.8002195420701311</v>
       </c>
       <c r="K99">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L99">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M99">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N99">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O99">
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:16">
       <c r="A100" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B100" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C100">
-        <v>1.962255996565552</v>
+        <v>1.989484076135192</v>
       </c>
       <c r="D100" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E100">
-        <v>1.87160332495021</v>
+        <v>1.941492857817997</v>
       </c>
       <c r="F100">
         <v>-1</v>
       </c>
       <c r="G100">
-        <v>0.006057744003434448</v>
+        <v>0.005750515923864809</v>
       </c>
       <c r="H100">
-        <v>0.00550839667504979</v>
+        <v>0.005638507142182003</v>
       </c>
       <c r="I100">
-        <v>0.09065267161534196</v>
+        <v>0.04799121831719488</v>
       </c>
       <c r="J100">
-        <v>0.8190976013737793</v>
+        <v>0.8002195420701311</v>
       </c>
       <c r="K100">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L100">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M100">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N100">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O100">
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C101">
-        <v>1.945120636771619</v>
+        <v>1.996409318396163</v>
       </c>
       <c r="D101" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E101">
-        <v>1.87160332495021</v>
+        <v>1.929442210198055</v>
       </c>
       <c r="F101">
         <v>-1</v>
       </c>
       <c r="G101">
-        <v>0.005794879363228382</v>
+        <v>0.006023590681603837</v>
       </c>
       <c r="H101">
-        <v>0.00550839667504979</v>
+        <v>0.005650557789801946</v>
       </c>
       <c r="I101">
-        <v>0.07351731182140897</v>
+        <v>0.06696710819810803</v>
       </c>
       <c r="J101">
-        <v>0.8190976013737793</v>
+        <v>0.8054362726415348</v>
       </c>
       <c r="K101">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L101">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M101">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N101">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O101">
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:16">
       <c r="A102" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B102" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C102">
-        <v>1.879794300963948</v>
+        <v>1.977224759292393</v>
       </c>
       <c r="D102" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E102">
-        <v>1.87160332495021</v>
+        <v>1.929442210198055</v>
       </c>
       <c r="F102">
         <v>-1</v>
       </c>
       <c r="G102">
-        <v>0.005500205699036052</v>
+        <v>0.005762775240707607</v>
       </c>
       <c r="H102">
-        <v>0.00550839667504979</v>
+        <v>0.005650557789801946</v>
       </c>
       <c r="I102">
-        <v>0.008190976013737972</v>
+        <v>0.04778254909433866</v>
       </c>
       <c r="J102">
-        <v>0.8190976013737793</v>
+        <v>0.8054362726415348</v>
       </c>
       <c r="K102">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="L102">
-        <v>3.69</v>
+        <v>3.87</v>
       </c>
       <c r="M102">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N102">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O102">
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -5905,28 +5902,28 @@
         <v>33</v>
       </c>
       <c r="C103">
-        <v>1.966334427874344</v>
+        <v>1.981381467084703</v>
       </c>
       <c r="D103" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E103">
-        <v>1.875224971952417</v>
+        <v>1.915556475586266</v>
       </c>
       <c r="F103">
         <v>-1</v>
       </c>
       <c r="G103">
-        <v>0.006053665572125656</v>
+        <v>0.006038618532915297</v>
       </c>
       <c r="H103">
-        <v>0.005504775028047582</v>
+        <v>0.005664443524413735</v>
       </c>
       <c r="I103">
-        <v>0.09110945592192632</v>
+        <v>0.06582499149843701</v>
       </c>
       <c r="J103">
-        <v>0.8174662288502623</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K103">
         <v>2.5</v>
@@ -5935,16 +5932,16 @@
         <v>4.01</v>
       </c>
       <c r="M103">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N103">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O103">
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -5952,31 +5949,31 @@
         <v>1</v>
       </c>
       <c r="B104" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C104">
-        <v>1.948954362201884</v>
+        <v>1.963098579059621</v>
       </c>
       <c r="D104" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E104">
-        <v>1.875224971952417</v>
+        <v>1.915556475586266</v>
       </c>
       <c r="F104">
         <v>-1</v>
       </c>
       <c r="G104">
-        <v>0.005791045637798117</v>
+        <v>0.005776901420940379</v>
       </c>
       <c r="H104">
-        <v>0.005504775028047582</v>
+        <v>0.005664443524413735</v>
       </c>
       <c r="I104">
-        <v>0.07372939024946623</v>
+        <v>0.04754210347335519</v>
       </c>
       <c r="J104">
-        <v>0.8174662288502623</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K104">
         <v>2.35</v>
@@ -5985,16 +5982,16 @@
         <v>3.87</v>
       </c>
       <c r="M104">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N104">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O104">
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6005,28 +6002,28 @@
         <v>33</v>
       </c>
       <c r="C105">
-        <v>1.967381519350304</v>
+        <v>1.977186894395391</v>
       </c>
       <c r="D105" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E105">
-        <v>1.87615478918307</v>
+        <v>1.911680690421341</v>
       </c>
       <c r="F105">
         <v>-1</v>
       </c>
       <c r="G105">
-        <v>0.006052618480649696</v>
+        <v>0.006042813105604609</v>
       </c>
       <c r="H105">
-        <v>0.00550384521081693</v>
+        <v>0.005668319309578659</v>
       </c>
       <c r="I105">
-        <v>0.09122673016723404</v>
+        <v>0.06550620397404949</v>
       </c>
       <c r="J105">
-        <v>0.8170473922598784</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K105">
         <v>2.5</v>
@@ -6035,16 +6032,16 @@
         <v>4.01</v>
       </c>
       <c r="M105">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N105">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O105">
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6052,31 +6049,31 @@
         <v>1</v>
       </c>
       <c r="B106" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C106">
-        <v>1.949938628189286</v>
+        <v>1.959155680731668</v>
       </c>
       <c r="D106" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E106">
-        <v>1.87615478918307</v>
+        <v>1.911680690421341</v>
       </c>
       <c r="F106">
         <v>-1</v>
       </c>
       <c r="G106">
-        <v>0.005790061371810714</v>
+        <v>0.005780844319268333</v>
       </c>
       <c r="H106">
-        <v>0.00550384521081693</v>
+        <v>0.005668319309578659</v>
       </c>
       <c r="I106">
-        <v>0.07378383900621599</v>
+        <v>0.04747499031032643</v>
       </c>
       <c r="J106">
-        <v>0.8170473922598784</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K106">
         <v>2.35</v>
@@ -6085,16 +6082,16 @@
         <v>3.87</v>
       </c>
       <c r="M106">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N106">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O106">
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6105,28 +6102,28 @@
         <v>33</v>
       </c>
       <c r="C107">
-        <v>1.965836780713639</v>
+        <v>1.972128109819418</v>
       </c>
       <c r="D107" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E107">
-        <v>1.874783061273712</v>
+        <v>1.907006373473143</v>
       </c>
       <c r="F107">
         <v>-1</v>
       </c>
       <c r="G107">
-        <v>0.00605416321928636</v>
+        <v>0.006047871890180582</v>
       </c>
       <c r="H107">
-        <v>0.005505216938726289</v>
+        <v>0.005672993626526857</v>
       </c>
       <c r="I107">
-        <v>0.09105371943992768</v>
+        <v>0.06512173634627527</v>
       </c>
       <c r="J107">
-        <v>0.8176652877145442</v>
+        <v>0.8151487560722326</v>
       </c>
       <c r="K107">
         <v>2.5</v>
@@ -6135,16 +6132,16 @@
         <v>4.01</v>
       </c>
       <c r="M107">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N107">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O107">
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6152,31 +6149,31 @@
         <v>1</v>
       </c>
       <c r="B108" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C108">
-        <v>1.948486573870821</v>
+        <v>1.954400423230253</v>
       </c>
       <c r="D108" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E108">
-        <v>1.874783061273712</v>
+        <v>1.907006373473143</v>
       </c>
       <c r="F108">
         <v>-1</v>
       </c>
       <c r="G108">
-        <v>0.00579151342612918</v>
+        <v>0.005785599576769747</v>
       </c>
       <c r="H108">
-        <v>0.005505216938726289</v>
+        <v>0.005672993626526857</v>
       </c>
       <c r="I108">
-        <v>0.0737035125971095</v>
+        <v>0.04739404975711059</v>
       </c>
       <c r="J108">
-        <v>0.8176652877145442</v>
+        <v>0.8151487560722326</v>
       </c>
       <c r="K108">
         <v>2.35</v>
@@ -6185,216 +6182,216 @@
         <v>3.87</v>
       </c>
       <c r="M108">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N108">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O108">
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="109" spans="1:16">
       <c r="A109" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C109">
-        <v>1.882959714150857</v>
+        <v>1.962255996565552</v>
       </c>
       <c r="D109" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E109">
-        <v>1.874783061273712</v>
+        <v>1.89788454082657</v>
       </c>
       <c r="F109">
         <v>-1</v>
       </c>
       <c r="G109">
-        <v>0.005497040285849143</v>
+        <v>0.006057744003434448</v>
       </c>
       <c r="H109">
-        <v>0.005505216938726289</v>
+        <v>0.005682115459173431</v>
       </c>
       <c r="I109">
-        <v>0.00817665287714564</v>
+        <v>0.06437145573898184</v>
       </c>
       <c r="J109">
-        <v>0.8176652877145442</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K109">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="L109">
-        <v>3.69</v>
+        <v>4.01</v>
       </c>
       <c r="M109">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N109">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O109">
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="110" spans="1:16">
       <c r="A110" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B110" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C110">
-        <v>1.964801996006813</v>
+        <v>1.945120636771619</v>
       </c>
       <c r="D110" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E110">
-        <v>1.87386417245405</v>
+        <v>1.89788454082657</v>
       </c>
       <c r="F110">
         <v>-1</v>
       </c>
       <c r="G110">
-        <v>0.006055198003993187</v>
+        <v>0.005794879363228382</v>
       </c>
       <c r="H110">
-        <v>0.005506135827545951</v>
+        <v>0.005682115459173431</v>
       </c>
       <c r="I110">
-        <v>0.09093782355276314</v>
+        <v>0.04723609594504885</v>
       </c>
       <c r="J110">
-        <v>0.8180792015972748</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K110">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L110">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M110">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N110">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O110">
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="111" spans="1:16">
       <c r="A111" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C111">
-        <v>1.947513876246404</v>
+        <v>1.966334427874344</v>
       </c>
       <c r="D111" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E111">
-        <v>1.87386417245405</v>
+        <v>1.901653011355894</v>
       </c>
       <c r="F111">
         <v>-1</v>
       </c>
       <c r="G111">
-        <v>0.005792486123753596</v>
+        <v>0.006053665572125656</v>
       </c>
       <c r="H111">
-        <v>0.005506135827545951</v>
+        <v>0.005678346988644107</v>
       </c>
       <c r="I111">
-        <v>0.07364970379235447</v>
+        <v>0.06468141651844972</v>
       </c>
       <c r="J111">
-        <v>0.8180792015972748</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K111">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L111">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M111">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N111">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O111">
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="112" spans="1:16">
       <c r="A112" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B112" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C112">
-        <v>1.882044964470023</v>
+        <v>1.948954362201884</v>
       </c>
       <c r="D112" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E112">
-        <v>1.87386417245405</v>
+        <v>1.901653011355894</v>
       </c>
       <c r="F112">
         <v>-1</v>
       </c>
       <c r="G112">
-        <v>0.005497955035529977</v>
+        <v>0.005791045637798117</v>
       </c>
       <c r="H112">
-        <v>0.005506135827545951</v>
+        <v>0.005678346988644107</v>
       </c>
       <c r="I112">
-        <v>0.008180792015972882</v>
+        <v>0.04730135084598963</v>
       </c>
       <c r="J112">
-        <v>0.8180792015972748</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K112">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="L112">
-        <v>3.69</v>
+        <v>3.87</v>
       </c>
       <c r="M112">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N112">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O112">
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6405,28 +6402,28 @@
         <v>33</v>
       </c>
       <c r="C113">
-        <v>1.96211546833212</v>
+        <v>1.967381519350304</v>
       </c>
       <c r="D113" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E113">
-        <v>1.871478535878923</v>
+        <v>1.902620523879681</v>
       </c>
       <c r="F113">
         <v>-1</v>
       </c>
       <c r="G113">
-        <v>0.006057884531667879</v>
+        <v>0.006052618480649696</v>
       </c>
       <c r="H113">
-        <v>0.005508521464121076</v>
+        <v>0.005677379476120319</v>
       </c>
       <c r="I113">
-        <v>0.09063693245319748</v>
+        <v>0.06476099547062297</v>
       </c>
       <c r="J113">
-        <v>0.8191538126671517</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K113">
         <v>2.5</v>
@@ -6435,16 +6432,16 @@
         <v>4.01</v>
       </c>
       <c r="M113">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N113">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O113">
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6452,31 +6449,31 @@
         <v>1</v>
       </c>
       <c r="B114" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C114">
-        <v>1.944988540232194</v>
+        <v>1.949938628189286</v>
       </c>
       <c r="D114" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E114">
-        <v>1.871478535878923</v>
+        <v>1.902620523879681</v>
       </c>
       <c r="F114">
         <v>-1</v>
       </c>
       <c r="G114">
-        <v>0.005795011459767806</v>
+        <v>0.005790061371810714</v>
       </c>
       <c r="H114">
-        <v>0.005508521464121076</v>
+        <v>0.005677379476120319</v>
       </c>
       <c r="I114">
-        <v>0.0735100043532706</v>
+        <v>0.04731810430960492</v>
       </c>
       <c r="J114">
-        <v>0.8191538126671517</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K114">
         <v>2.35</v>
@@ -6485,216 +6482,216 @@
         <v>3.87</v>
       </c>
       <c r="M114">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N114">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O114">
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="115" spans="1:16">
       <c r="A115" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C115">
-        <v>1.879670074005595</v>
+        <v>1.965836780713639</v>
       </c>
       <c r="D115" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E115">
-        <v>1.871478535878923</v>
+        <v>1.901193185379403</v>
       </c>
       <c r="F115">
         <v>-1</v>
       </c>
       <c r="G115">
-        <v>0.005500329925994405</v>
+        <v>0.00605416321928636</v>
       </c>
       <c r="H115">
-        <v>0.005508521464121076</v>
+        <v>0.005678806814620596</v>
       </c>
       <c r="I115">
-        <v>0.008191538126671727</v>
+        <v>0.06464359533423636</v>
       </c>
       <c r="J115">
-        <v>0.8191538126671517</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K115">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="L115">
-        <v>3.69</v>
+        <v>4.01</v>
       </c>
       <c r="M115">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N115">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O115">
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="116" spans="1:16">
       <c r="A116" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B116" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C116">
-        <v>1.969378632640371</v>
+        <v>1.948486573870821</v>
       </c>
       <c r="D116" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E116">
-        <v>1.877928225784649</v>
+        <v>1.901193185379403</v>
       </c>
       <c r="F116">
         <v>-1</v>
       </c>
       <c r="G116">
-        <v>0.006050621367359629</v>
+        <v>0.00579151342612918</v>
       </c>
       <c r="H116">
-        <v>0.005502071774215351</v>
+        <v>0.005678806814620596</v>
       </c>
       <c r="I116">
-        <v>0.09145040685572159</v>
+        <v>0.04729338849141818</v>
       </c>
       <c r="J116">
-        <v>0.8162485469438515</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K116">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L116">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M116">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N116">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O116">
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="117" spans="1:16">
       <c r="A117" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C117">
-        <v>1.951815914681949</v>
+        <v>1.964801996006813</v>
       </c>
       <c r="D117" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E117">
-        <v>1.877928225784649</v>
+        <v>1.900237044310295</v>
       </c>
       <c r="F117">
         <v>-1</v>
       </c>
       <c r="G117">
-        <v>0.005788184085318051</v>
+        <v>0.006055198003993187</v>
       </c>
       <c r="H117">
-        <v>0.005502071774215351</v>
+        <v>0.005679762955689705</v>
       </c>
       <c r="I117">
-        <v>0.07388768889729946</v>
+        <v>0.06456495169651766</v>
       </c>
       <c r="J117">
-        <v>0.8162485469438515</v>
+        <v>0.8180792015972748</v>
       </c>
       <c r="K117">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L117">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M117">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N117">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O117">
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="118" spans="1:16">
       <c r="A118" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B118" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C118">
-        <v>1.886090711254088</v>
+        <v>1.947513876246404</v>
       </c>
       <c r="D118" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E118">
-        <v>1.877928225784649</v>
+        <v>1.900237044310295</v>
       </c>
       <c r="F118">
         <v>-1</v>
       </c>
       <c r="G118">
-        <v>0.005493909288745913</v>
+        <v>0.005792486123753596</v>
       </c>
       <c r="H118">
-        <v>0.005502071774215351</v>
+        <v>0.005679762955689705</v>
       </c>
       <c r="I118">
-        <v>0.008162485469438652</v>
+        <v>0.04727683193610899</v>
       </c>
       <c r="J118">
-        <v>0.8162485469438515</v>
+        <v>0.8180792015972748</v>
       </c>
       <c r="K118">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="L118">
-        <v>3.69</v>
+        <v>3.87</v>
       </c>
       <c r="M118">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N118">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O118">
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6705,28 +6702,28 @@
         <v>33</v>
       </c>
       <c r="C119">
-        <v>1.979025316902244</v>
+        <v>1.96211546833212</v>
       </c>
       <c r="D119" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E119">
-        <v>1.886494481409192</v>
+        <v>1.89775469273888</v>
       </c>
       <c r="F119">
         <v>-1</v>
       </c>
       <c r="G119">
-        <v>0.006040974683097756</v>
+        <v>0.006057884531667879</v>
       </c>
       <c r="H119">
-        <v>0.005493505518590808</v>
+        <v>0.005682245307261121</v>
       </c>
       <c r="I119">
-        <v>0.09253083549305141</v>
+        <v>0.06436077559324094</v>
       </c>
       <c r="J119">
-        <v>0.8123898732391025</v>
+        <v>0.8191538126671517</v>
       </c>
       <c r="K119">
         <v>2.5</v>
@@ -6735,16 +6732,16 @@
         <v>4.01</v>
       </c>
       <c r="M119">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N119">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O119">
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -6752,31 +6749,31 @@
         <v>1</v>
       </c>
       <c r="B120" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C120">
-        <v>1.960883797888109</v>
+        <v>1.944988540232194</v>
       </c>
       <c r="D120" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E120">
-        <v>1.886494481409192</v>
+        <v>1.89775469273888</v>
       </c>
       <c r="F120">
         <v>-1</v>
       </c>
       <c r="G120">
-        <v>0.005779116202111891</v>
+        <v>0.005795011459767806</v>
       </c>
       <c r="H120">
-        <v>0.005493505518590808</v>
+        <v>0.005682245307261121</v>
       </c>
       <c r="I120">
-        <v>0.07438931647891689</v>
+        <v>0.04723384749331405</v>
       </c>
       <c r="J120">
-        <v>0.8123898732391025</v>
+        <v>0.8191538126671517</v>
       </c>
       <c r="K120">
         <v>2.35</v>
@@ -6785,16 +6782,16 @@
         <v>3.87</v>
       </c>
       <c r="M120">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N120">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O120">
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -6805,28 +6802,28 @@
         <v>33</v>
       </c>
       <c r="C121">
-        <v>1.983626913195719</v>
+        <v>1.969378632640371</v>
       </c>
       <c r="D121" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E121">
-        <v>1.890580698917798</v>
+        <v>1.904465856559703</v>
       </c>
       <c r="F121">
         <v>-1</v>
       </c>
       <c r="G121">
-        <v>0.00603637308680428</v>
+        <v>0.006050621367359629</v>
       </c>
       <c r="H121">
-        <v>0.005489419301082201</v>
+        <v>0.005675534143440297</v>
       </c>
       <c r="I121">
-        <v>0.0930462142779207</v>
+        <v>0.06491277608066803</v>
       </c>
       <c r="J121">
-        <v>0.8105492347217125</v>
+        <v>0.8162485469438515</v>
       </c>
       <c r="K121">
         <v>2.5</v>
@@ -6835,16 +6832,16 @@
         <v>4.01</v>
       </c>
       <c r="M121">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N121">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O121">
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -6852,31 +6849,31 @@
         <v>1</v>
       </c>
       <c r="B122" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C122">
-        <v>1.965209298403976</v>
+        <v>1.951815914681949</v>
       </c>
       <c r="D122" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E122">
-        <v>1.890580698917798</v>
+        <v>1.904465856559703</v>
       </c>
       <c r="F122">
         <v>-1</v>
       </c>
       <c r="G122">
-        <v>0.005774790701596024</v>
+        <v>0.005788184085318051</v>
       </c>
       <c r="H122">
-        <v>0.005489419301082201</v>
+        <v>0.005675534143440297</v>
       </c>
       <c r="I122">
-        <v>0.07462859948617773</v>
+        <v>0.04735005812224591</v>
       </c>
       <c r="J122">
-        <v>0.8105492347217125</v>
+        <v>0.8162485469438515</v>
       </c>
       <c r="K122">
         <v>2.35</v>
@@ -6885,16 +6882,16 @@
         <v>3.87</v>
       </c>
       <c r="M122">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N122">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O122">
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -6905,28 +6902,28 @@
         <v>33</v>
       </c>
       <c r="C123">
-        <v>1.99070164592738</v>
+        <v>1.979025316902244</v>
       </c>
       <c r="D123" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E123">
-        <v>1.896863061583513</v>
+        <v>1.913379392817673</v>
       </c>
       <c r="F123">
         <v>-1</v>
       </c>
       <c r="G123">
-        <v>0.006029298354072619</v>
+        <v>0.006040974683097756</v>
       </c>
       <c r="H123">
-        <v>0.005483136938416486</v>
+        <v>0.005666620607182327</v>
       </c>
       <c r="I123">
-        <v>0.09383858434386672</v>
+        <v>0.06564592408457037</v>
       </c>
       <c r="J123">
-        <v>0.8077193416290479</v>
+        <v>0.8123898732391025</v>
       </c>
       <c r="K123">
         <v>2.5</v>
@@ -6935,16 +6932,16 @@
         <v>4.01</v>
       </c>
       <c r="M123">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N123">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O123">
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -6952,31 +6949,31 @@
         <v>1</v>
       </c>
       <c r="B124" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C124">
-        <v>1.971859547171738</v>
+        <v>1.960883797888109</v>
       </c>
       <c r="D124" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E124">
-        <v>1.896863061583513</v>
+        <v>1.913379392817673</v>
       </c>
       <c r="F124">
         <v>-1</v>
       </c>
       <c r="G124">
-        <v>0.005768140452828262</v>
+        <v>0.005779116202111891</v>
       </c>
       <c r="H124">
-        <v>0.005483136938416486</v>
+        <v>0.005666620607182327</v>
       </c>
       <c r="I124">
-        <v>0.07499648558822414</v>
+        <v>0.04750440507043585</v>
       </c>
       <c r="J124">
-        <v>0.8077193416290479</v>
+        <v>0.8123898732391025</v>
       </c>
       <c r="K124">
         <v>2.35</v>
@@ -6985,16 +6982,16 @@
         <v>3.87</v>
       </c>
       <c r="M124">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N124">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O124">
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7005,28 +7002,28 @@
         <v>33</v>
       </c>
       <c r="C125">
-        <v>1.995518685947181</v>
+        <v>1.983626913195719</v>
       </c>
       <c r="D125" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E125">
-        <v>1.901140593121096</v>
+        <v>1.917631267792844</v>
       </c>
       <c r="F125">
         <v>-1</v>
       </c>
       <c r="G125">
-        <v>0.006024481314052819</v>
+        <v>0.00603637308680428</v>
       </c>
       <c r="H125">
-        <v>0.005478859406878904</v>
+        <v>0.005662368732207156</v>
       </c>
       <c r="I125">
-        <v>0.09437809282608445</v>
+        <v>0.0659956454028745</v>
       </c>
       <c r="J125">
-        <v>0.8057925256211278</v>
+        <v>0.8105492347217125</v>
       </c>
       <c r="K125">
         <v>2.5</v>
@@ -7035,16 +7032,16 @@
         <v>4.01</v>
       </c>
       <c r="M125">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N125">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O125">
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7052,31 +7049,31 @@
         <v>1</v>
       </c>
       <c r="B126" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C126">
-        <v>1.97638756479035</v>
+        <v>1.965209298403976</v>
       </c>
       <c r="D126" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E126">
-        <v>1.901140593121096</v>
+        <v>1.917631267792844</v>
       </c>
       <c r="F126">
         <v>-1</v>
       </c>
       <c r="G126">
-        <v>0.005763612435209651</v>
+        <v>0.005774790701596024</v>
       </c>
       <c r="H126">
-        <v>0.005478859406878904</v>
+        <v>0.005662368732207156</v>
       </c>
       <c r="I126">
-        <v>0.07524697166925365</v>
+        <v>0.04757803061113153</v>
       </c>
       <c r="J126">
-        <v>0.8057925256211278</v>
+        <v>0.8105492347217125</v>
       </c>
       <c r="K126">
         <v>2.35</v>
@@ -7085,16 +7082,16 @@
         <v>3.87</v>
       </c>
       <c r="M126">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N126">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O126">
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7105,28 +7102,28 @@
         <v>33</v>
       </c>
       <c r="C127">
-        <v>2.001757402215216</v>
+        <v>1.99070164592738</v>
       </c>
       <c r="D127" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E127">
-        <v>1.906680573167112</v>
+        <v>1.924168320836899</v>
       </c>
       <c r="F127">
         <v>-1</v>
       </c>
       <c r="G127">
-        <v>0.006018242597784784</v>
+        <v>0.006029298354072619</v>
       </c>
       <c r="H127">
-        <v>0.005473319426832888</v>
+        <v>0.005655831679163101</v>
       </c>
       <c r="I127">
-        <v>0.09507682904810433</v>
+        <v>0.06653332509048071</v>
       </c>
       <c r="J127">
-        <v>0.8032970391139135</v>
+        <v>0.8077193416290479</v>
       </c>
       <c r="K127">
         <v>2.5</v>
@@ -7135,16 +7132,16 @@
         <v>4.01</v>
       </c>
       <c r="M127">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N127">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O127">
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7152,31 +7149,31 @@
         <v>1</v>
       </c>
       <c r="B128" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C128">
-        <v>1.982251958082303</v>
+        <v>1.971859547171738</v>
       </c>
       <c r="D128" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E128">
-        <v>1.906680573167112</v>
+        <v>1.924168320836899</v>
       </c>
       <c r="F128">
         <v>-1</v>
       </c>
       <c r="G128">
-        <v>0.005757748041917698</v>
+        <v>0.005768140452828262</v>
       </c>
       <c r="H128">
-        <v>0.005473319426832888</v>
+        <v>0.005655831679163101</v>
       </c>
       <c r="I128">
-        <v>0.07557138491519133</v>
+        <v>0.04769122633483813</v>
       </c>
       <c r="J128">
-        <v>0.8032970391139135</v>
+        <v>0.8077193416290479</v>
       </c>
       <c r="K128">
         <v>2.35</v>
@@ -7185,16 +7182,16 @@
         <v>3.87</v>
       </c>
       <c r="M128">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N128">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O128">
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7205,28 +7202,28 @@
         <v>33</v>
       </c>
       <c r="C129">
-        <v>2.008261226887488</v>
+        <v>1.995518685947181</v>
       </c>
       <c r="D129" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E129">
-        <v>1.912455969476089</v>
+        <v>1.928619265815195</v>
       </c>
       <c r="F129">
         <v>-1</v>
       </c>
       <c r="G129">
-        <v>0.006011738773112512</v>
+        <v>0.006024481314052819</v>
       </c>
       <c r="H129">
-        <v>0.005467544030523911</v>
+        <v>0.005651380734184805</v>
       </c>
       <c r="I129">
-        <v>0.09580525741139856</v>
+        <v>0.06689942013198569</v>
       </c>
       <c r="J129">
-        <v>0.8006955092450049</v>
+        <v>0.8057925256211278</v>
       </c>
       <c r="K129">
         <v>2.5</v>
@@ -7235,16 +7232,16 @@
         <v>4.01</v>
       </c>
       <c r="M129">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N129">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O129">
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7252,31 +7249,31 @@
         <v>1</v>
       </c>
       <c r="B130" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C130">
-        <v>1.988365553274239</v>
+        <v>1.97638756479035</v>
       </c>
       <c r="D130" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E130">
-        <v>1.912455969476089</v>
+        <v>1.928619265815195</v>
       </c>
       <c r="F130">
         <v>-1</v>
       </c>
       <c r="G130">
-        <v>0.005751634446725762</v>
+        <v>0.005763612435209651</v>
       </c>
       <c r="H130">
-        <v>0.005467544030523911</v>
+        <v>0.005651380734184805</v>
       </c>
       <c r="I130">
-        <v>0.0759095837981496</v>
+        <v>0.04776829897515489</v>
       </c>
       <c r="J130">
-        <v>0.8006955092450049</v>
+        <v>0.8057925256211278</v>
       </c>
       <c r="K130">
         <v>2.35</v>
@@ -7285,16 +7282,16 @@
         <v>3.87</v>
       </c>
       <c r="M130">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N130">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O130">
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7305,28 +7302,28 @@
         <v>33</v>
       </c>
       <c r="C131">
-        <v>2.013407841318734</v>
+        <v>2.001757402215216</v>
       </c>
       <c r="D131" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E131">
-        <v>1.917026163091035</v>
+        <v>1.93438383964686</v>
       </c>
       <c r="F131">
         <v>-1</v>
       </c>
       <c r="G131">
-        <v>0.006006592158681266</v>
+        <v>0.006018242597784784</v>
       </c>
       <c r="H131">
-        <v>0.005462973836908965</v>
+        <v>0.00564561616035314</v>
       </c>
       <c r="I131">
-        <v>0.0963816782276985</v>
+        <v>0.06737356256835647</v>
       </c>
       <c r="J131">
-        <v>0.7986368634725065</v>
+        <v>0.8032970391139135</v>
       </c>
       <c r="K131">
         <v>2.5</v>
@@ -7335,16 +7332,16 @@
         <v>4.01</v>
       </c>
       <c r="M131">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N131">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O131">
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7352,31 +7349,31 @@
         <v>1</v>
       </c>
       <c r="B132" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C132">
-        <v>1.99320337083961</v>
+        <v>1.982251958082303</v>
       </c>
       <c r="D132" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E132">
-        <v>1.917026163091035</v>
+        <v>1.93438383964686</v>
       </c>
       <c r="F132">
         <v>-1</v>
       </c>
       <c r="G132">
-        <v>0.005746796629160391</v>
+        <v>0.005757748041917698</v>
       </c>
       <c r="H132">
-        <v>0.005462973836908965</v>
+        <v>0.00564561616035314</v>
       </c>
       <c r="I132">
-        <v>0.0761772077485745</v>
+        <v>0.04786811843544347</v>
       </c>
       <c r="J132">
-        <v>0.7986368634725065</v>
+        <v>0.8032970391139135</v>
       </c>
       <c r="K132">
         <v>2.35</v>
@@ -7385,16 +7382,16 @@
         <v>3.87</v>
       </c>
       <c r="M132">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N132">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O132">
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7405,28 +7402,28 @@
         <v>33</v>
       </c>
       <c r="C133">
-        <v>2.024814922108121</v>
+        <v>2.008261226887488</v>
       </c>
       <c r="D133" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E133">
-        <v>1.927155650832012</v>
+        <v>1.940393373644039</v>
       </c>
       <c r="F133">
         <v>-1</v>
       </c>
       <c r="G133">
-        <v>0.005995185077891879</v>
+        <v>0.006011738773112512</v>
       </c>
       <c r="H133">
-        <v>0.005452844349167989</v>
+        <v>0.005639606626355961</v>
       </c>
       <c r="I133">
-        <v>0.09765927127610952</v>
+        <v>0.06786785324344891</v>
       </c>
       <c r="J133">
-        <v>0.7940740311567515</v>
+        <v>0.8006955092450049</v>
       </c>
       <c r="K133">
         <v>2.5</v>
@@ -7435,16 +7432,16 @@
         <v>4.01</v>
       </c>
       <c r="M133">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N133">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O133">
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7452,31 +7449,31 @@
         <v>1</v>
       </c>
       <c r="B134" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C134">
-        <v>2.003926026781634</v>
+        <v>1.988365553274239</v>
       </c>
       <c r="D134" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E134">
-        <v>1.927155650832012</v>
+        <v>1.940393373644039</v>
       </c>
       <c r="F134">
         <v>-1</v>
       </c>
       <c r="G134">
-        <v>0.005736073973218366</v>
+        <v>0.005751634446725762</v>
       </c>
       <c r="H134">
-        <v>0.005452844349167989</v>
+        <v>0.005639606626355961</v>
       </c>
       <c r="I134">
-        <v>0.07677037594962255</v>
+        <v>0.04797217963019995</v>
       </c>
       <c r="J134">
-        <v>0.7940740311567515</v>
+        <v>0.8006955092450049</v>
       </c>
       <c r="K134">
         <v>2.35</v>
@@ -7485,16 +7482,16 @@
         <v>3.87</v>
       </c>
       <c r="M134">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N134">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O134">
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7505,28 +7502,28 @@
         <v>33</v>
       </c>
       <c r="C135">
-        <v>2.037026290859836</v>
+        <v>2.013407841318734</v>
       </c>
       <c r="D135" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E135">
-        <v>1.937999346283534</v>
+        <v>1.94514884537851</v>
       </c>
       <c r="F135">
         <v>-1</v>
       </c>
       <c r="G135">
-        <v>0.005982973709140164</v>
+        <v>0.006006592158681266</v>
       </c>
       <c r="H135">
-        <v>0.005442000653716466</v>
+        <v>0.00563485115462149</v>
       </c>
       <c r="I135">
-        <v>0.09902694457630168</v>
+        <v>0.06825899594022378</v>
       </c>
       <c r="J135">
-        <v>0.7891894836560657</v>
+        <v>0.7986368634725065</v>
       </c>
       <c r="K135">
         <v>2.5</v>
@@ -7535,16 +7532,16 @@
         <v>4.01</v>
       </c>
       <c r="M135">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N135">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O135">
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7552,31 +7549,31 @@
         <v>1</v>
       </c>
       <c r="B136" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C136">
-        <v>2.015404713408246</v>
+        <v>1.99320337083961</v>
       </c>
       <c r="D136" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E136">
-        <v>1.937999346283534</v>
+        <v>1.94514884537851</v>
       </c>
       <c r="F136">
         <v>-1</v>
       </c>
       <c r="G136">
-        <v>0.005724595286591755</v>
+        <v>0.005746796629160391</v>
       </c>
       <c r="H136">
-        <v>0.005442000653716466</v>
+        <v>0.00563485115462149</v>
       </c>
       <c r="I136">
-        <v>0.07740536712471147</v>
+        <v>0.04805452546109978</v>
       </c>
       <c r="J136">
-        <v>0.7891894836560657</v>
+        <v>0.7986368634725065</v>
       </c>
       <c r="K136">
         <v>2.35</v>
@@ -7585,16 +7582,16 @@
         <v>3.87</v>
       </c>
       <c r="M136">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N136">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O136">
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7605,28 +7602,28 @@
         <v>33</v>
       </c>
       <c r="C137">
-        <v>2.040400244545683</v>
+        <v>2.024814922108121</v>
       </c>
       <c r="D137" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E137">
-        <v>1.940995417156566</v>
+        <v>1.955688988027904</v>
       </c>
       <c r="F137">
         <v>-1</v>
       </c>
       <c r="G137">
-        <v>0.005979599755454317</v>
+        <v>0.005995185077891879</v>
       </c>
       <c r="H137">
-        <v>0.005439004582843434</v>
+        <v>0.005624311011972096</v>
       </c>
       <c r="I137">
-        <v>0.0994048273891166</v>
+        <v>0.06912593408021706</v>
       </c>
       <c r="J137">
-        <v>0.7878399021817268</v>
+        <v>0.7940740311567515</v>
       </c>
       <c r="K137">
         <v>2.5</v>
@@ -7635,16 +7632,16 @@
         <v>4.01</v>
       </c>
       <c r="M137">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N137">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O137">
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7652,31 +7649,31 @@
         <v>1</v>
       </c>
       <c r="B138" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C138">
-        <v>2.018576229872942</v>
+        <v>2.003926026781634</v>
       </c>
       <c r="D138" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E138">
-        <v>1.940995417156566</v>
+        <v>1.955688988027904</v>
       </c>
       <c r="F138">
         <v>-1</v>
       </c>
       <c r="G138">
-        <v>0.005721423770127059</v>
+        <v>0.005736073973218366</v>
       </c>
       <c r="H138">
-        <v>0.005439004582843434</v>
+        <v>0.005624311011972096</v>
       </c>
       <c r="I138">
-        <v>0.07758081271637574</v>
+        <v>0.04823703875373009</v>
       </c>
       <c r="J138">
-        <v>0.7878399021817268</v>
+        <v>0.7940740311567515</v>
       </c>
       <c r="K138">
         <v>2.35</v>
@@ -7685,16 +7682,16 @@
         <v>3.87</v>
       </c>
       <c r="M138">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N138">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O138">
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7705,28 +7702,28 @@
         <v>33</v>
       </c>
       <c r="C139">
-        <v>2.040677055689185</v>
+        <v>2.037026290859836</v>
       </c>
       <c r="D139" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E139">
-        <v>1.941241225451996</v>
+        <v>1.966972292754488</v>
       </c>
       <c r="F139">
         <v>-1</v>
       </c>
       <c r="G139">
-        <v>0.005979322944310814</v>
+        <v>0.005982973709140164</v>
       </c>
       <c r="H139">
-        <v>0.005438758774548004</v>
+        <v>0.005613027707245512</v>
       </c>
       <c r="I139">
-        <v>0.09943583023718894</v>
+        <v>0.0700539981053474</v>
       </c>
       <c r="J139">
-        <v>0.7877291777243258</v>
+        <v>0.7891894836560657</v>
       </c>
       <c r="K139">
         <v>2.5</v>
@@ -7735,16 +7732,16 @@
         <v>4.01</v>
       </c>
       <c r="M139">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N139">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O139">
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -7752,31 +7749,31 @@
         <v>1</v>
       </c>
       <c r="B140" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C140">
-        <v>2.018836432347834</v>
+        <v>2.015404713408246</v>
       </c>
       <c r="D140" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E140">
-        <v>1.941241225451996</v>
+        <v>1.966972292754488</v>
       </c>
       <c r="F140">
         <v>-1</v>
       </c>
       <c r="G140">
-        <v>0.005721163567652166</v>
+        <v>0.005724595286591755</v>
       </c>
       <c r="H140">
-        <v>0.005438758774548004</v>
+        <v>0.005613027707245512</v>
       </c>
       <c r="I140">
-        <v>0.07759520689583788</v>
+        <v>0.04843242065375719</v>
       </c>
       <c r="J140">
-        <v>0.7877291777243258</v>
+        <v>0.7891894836560657</v>
       </c>
       <c r="K140">
         <v>2.35</v>
@@ -7785,16 +7782,16 @@
         <v>3.87</v>
       </c>
       <c r="M140">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N140">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O140">
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -7805,28 +7802,28 @@
         <v>33</v>
       </c>
       <c r="C141">
-        <v>2.041764709541035</v>
+        <v>2.040400244545683</v>
       </c>
       <c r="D141" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E141">
-        <v>1.94220706207244</v>
+        <v>1.970089825960211</v>
       </c>
       <c r="F141">
         <v>-1</v>
       </c>
       <c r="G141">
-        <v>0.005978235290458964</v>
+        <v>0.005979599755454317</v>
       </c>
       <c r="H141">
-        <v>0.005437792937927561</v>
+        <v>0.005609910174039789</v>
       </c>
       <c r="I141">
-        <v>0.09955764746859574</v>
+        <v>0.07031041858547171</v>
       </c>
       <c r="J141">
-        <v>0.7872941161835857</v>
+        <v>0.7878399021817268</v>
       </c>
       <c r="K141">
         <v>2.5</v>
@@ -7835,16 +7832,16 @@
         <v>4.01</v>
       </c>
       <c r="M141">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N141">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O141">
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -7852,31 +7849,31 @@
         <v>1</v>
       </c>
       <c r="B142" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C142">
-        <v>2.019858826968574</v>
+        <v>2.018576229872942</v>
       </c>
       <c r="D142" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E142">
-        <v>1.94220706207244</v>
+        <v>1.970089825960211</v>
       </c>
       <c r="F142">
         <v>-1</v>
       </c>
       <c r="G142">
-        <v>0.005720141173031427</v>
+        <v>0.005721423770127059</v>
       </c>
       <c r="H142">
-        <v>0.005437792937927561</v>
+        <v>0.005609910174039789</v>
       </c>
       <c r="I142">
-        <v>0.07765176489613412</v>
+        <v>0.04848640391273085</v>
       </c>
       <c r="J142">
-        <v>0.7872941161835857</v>
+        <v>0.7878399021817268</v>
       </c>
       <c r="K142">
         <v>2.35</v>
@@ -7885,16 +7882,16 @@
         <v>3.87</v>
       </c>
       <c r="M142">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N142">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O142">
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -7905,28 +7902,28 @@
         <v>33</v>
       </c>
       <c r="C143">
-        <v>2.038301570426869</v>
+        <v>2.040677055689185</v>
       </c>
       <c r="D143" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E143">
-        <v>1.939131794539059</v>
+        <v>1.970345599456807</v>
       </c>
       <c r="F143">
         <v>-1</v>
       </c>
       <c r="G143">
-        <v>0.005981698429573131</v>
+        <v>0.005979322944310814</v>
       </c>
       <c r="H143">
-        <v>0.005440868205460941</v>
+        <v>0.005609654400543193</v>
       </c>
       <c r="I143">
-        <v>0.0991697758878094</v>
+        <v>0.07033145623237802</v>
       </c>
       <c r="J143">
-        <v>0.7886793718292525</v>
+        <v>0.7877291777243258</v>
       </c>
       <c r="K143">
         <v>2.5</v>
@@ -7935,16 +7932,16 @@
         <v>4.01</v>
       </c>
       <c r="M143">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N143">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O143">
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -7952,31 +7949,31 @@
         <v>1</v>
       </c>
       <c r="B144" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C144">
-        <v>2.016603476201257</v>
+        <v>2.018836432347834</v>
       </c>
       <c r="D144" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E144">
-        <v>1.939131794539059</v>
+        <v>1.970345599456807</v>
       </c>
       <c r="F144">
         <v>-1</v>
       </c>
       <c r="G144">
-        <v>0.005723396523798744</v>
+        <v>0.005721163567652166</v>
       </c>
       <c r="H144">
-        <v>0.005440868205460941</v>
+        <v>0.005609654400543193</v>
       </c>
       <c r="I144">
-        <v>0.07747168166219742</v>
+        <v>0.04849083289102696</v>
       </c>
       <c r="J144">
-        <v>0.7886793718292525</v>
+        <v>0.7877291777243258</v>
       </c>
       <c r="K144">
         <v>2.35</v>
@@ -7985,16 +7982,16 @@
         <v>3.87</v>
       </c>
       <c r="M144">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N144">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O144">
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8005,28 +8002,28 @@
         <v>33</v>
       </c>
       <c r="C145">
-        <v>2.035132415564467</v>
+        <v>2.041764709541035</v>
       </c>
       <c r="D145" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E145">
-        <v>1.936317585021247</v>
+        <v>1.971350591615917</v>
       </c>
       <c r="F145">
         <v>-1</v>
       </c>
       <c r="G145">
-        <v>0.005984867584435533</v>
+        <v>0.005978235290458964</v>
       </c>
       <c r="H145">
-        <v>0.005443682414978753</v>
+        <v>0.005608649408384083</v>
       </c>
       <c r="I145">
-        <v>0.09881483054322016</v>
+        <v>0.07041411792511831</v>
       </c>
       <c r="J145">
-        <v>0.7899470337742129</v>
+        <v>0.7872941161835857</v>
       </c>
       <c r="K145">
         <v>2.5</v>
@@ -8035,16 +8032,16 @@
         <v>4.01</v>
       </c>
       <c r="M145">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N145">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O145">
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8052,31 +8049,31 @@
         <v>1</v>
       </c>
       <c r="B146" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C146">
-        <v>2.013624470630599</v>
+        <v>2.019858826968574</v>
       </c>
       <c r="D146" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E146">
-        <v>1.936317585021247</v>
+        <v>1.971350591615917</v>
       </c>
       <c r="F146">
         <v>-1</v>
       </c>
       <c r="G146">
-        <v>0.0057263755293694</v>
+        <v>0.005720141173031427</v>
       </c>
       <c r="H146">
-        <v>0.005443682414978753</v>
+        <v>0.005608649408384083</v>
       </c>
       <c r="I146">
-        <v>0.07730688560935239</v>
+        <v>0.04850823535265669</v>
       </c>
       <c r="J146">
-        <v>0.7899470337742129</v>
+        <v>0.7872941161835857</v>
       </c>
       <c r="K146">
         <v>2.35</v>
@@ -8085,16 +8082,16 @@
         <v>3.87</v>
       </c>
       <c r="M146">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N146">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O146">
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8105,28 +8102,28 @@
         <v>33</v>
       </c>
       <c r="C147">
-        <v>2.033942517186959</v>
+        <v>2.038301570426869</v>
       </c>
       <c r="D147" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E147">
-        <v>1.935260955262019</v>
+        <v>1.968150651074427</v>
       </c>
       <c r="F147">
         <v>-1</v>
       </c>
       <c r="G147">
-        <v>0.005986057482813041</v>
+        <v>0.005981698429573131</v>
       </c>
       <c r="H147">
-        <v>0.00544473904473798</v>
+        <v>0.005611849348925574</v>
       </c>
       <c r="I147">
-        <v>0.09868156192493927</v>
+        <v>0.07015091935244189</v>
       </c>
       <c r="J147">
-        <v>0.7904229931252164</v>
+        <v>0.7886793718292525</v>
       </c>
       <c r="K147">
         <v>2.5</v>
@@ -8135,16 +8132,16 @@
         <v>4.01</v>
       </c>
       <c r="M147">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N147">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O147">
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8152,31 +8149,31 @@
         <v>1</v>
       </c>
       <c r="B148" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C148">
-        <v>2.012505966155742</v>
+        <v>2.016603476201257</v>
       </c>
       <c r="D148" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E148">
-        <v>1.935260955262019</v>
+        <v>1.968150651074427</v>
       </c>
       <c r="F148">
         <v>-1</v>
       </c>
       <c r="G148">
-        <v>0.00572749403384426</v>
+        <v>0.005723396523798744</v>
       </c>
       <c r="H148">
-        <v>0.00544473904473798</v>
+        <v>0.005611849348925574</v>
       </c>
       <c r="I148">
-        <v>0.07724501089372215</v>
+        <v>0.04845282512682991</v>
       </c>
       <c r="J148">
-        <v>0.7904229931252164</v>
+        <v>0.7886793718292525</v>
       </c>
       <c r="K148">
         <v>2.35</v>
@@ -8185,16 +8182,16 @@
         <v>3.87</v>
       </c>
       <c r="M148">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N148">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O148">
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8205,28 +8202,28 @@
         <v>33</v>
       </c>
       <c r="C149">
-        <v>2.03219014170303</v>
+        <v>2.035132415564467</v>
       </c>
       <c r="D149" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E149">
-        <v>1.933704845832291</v>
+        <v>1.965222351981568</v>
       </c>
       <c r="F149">
         <v>-1</v>
       </c>
       <c r="G149">
-        <v>0.00598780985829697</v>
+        <v>0.005984867584435533</v>
       </c>
       <c r="H149">
-        <v>0.005446295154167709</v>
+        <v>0.005614777648018432</v>
       </c>
       <c r="I149">
-        <v>0.09848529587073918</v>
+        <v>0.06991006358289908</v>
       </c>
       <c r="J149">
-        <v>0.791123943318788</v>
+        <v>0.7899470337742129</v>
       </c>
       <c r="K149">
         <v>2.5</v>
@@ -8235,16 +8232,16 @@
         <v>4.01</v>
       </c>
       <c r="M149">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N149">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O149">
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8252,31 +8249,31 @@
         <v>1</v>
       </c>
       <c r="B150" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C150">
-        <v>2.010858733200848</v>
+        <v>2.013624470630599</v>
       </c>
       <c r="D150" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E150">
-        <v>1.933704845832291</v>
+        <v>1.965222351981568</v>
       </c>
       <c r="F150">
         <v>-1</v>
       </c>
       <c r="G150">
-        <v>0.005729141266799152</v>
+        <v>0.0057263755293694</v>
       </c>
       <c r="H150">
-        <v>0.005446295154167709</v>
+        <v>0.005614777648018432</v>
       </c>
       <c r="I150">
-        <v>0.07715388736855777</v>
+        <v>0.04840211864903132</v>
       </c>
       <c r="J150">
-        <v>0.791123943318788</v>
+        <v>0.7899470337742129</v>
       </c>
       <c r="K150">
         <v>2.35</v>
@@ -8285,16 +8282,16 @@
         <v>3.87</v>
       </c>
       <c r="M150">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N150">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O150">
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8305,28 +8302,28 @@
         <v>33</v>
       </c>
       <c r="C151">
-        <v>2.031041804995824</v>
+        <v>2.033942517186959</v>
       </c>
       <c r="D151" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E151">
-        <v>1.932685122836292</v>
+        <v>1.96412288588075</v>
       </c>
       <c r="F151">
         <v>-1</v>
       </c>
       <c r="G151">
-        <v>0.005988958195004175</v>
+        <v>0.005986057482813041</v>
       </c>
       <c r="H151">
-        <v>0.005447314877163708</v>
+        <v>0.005615877114119251</v>
       </c>
       <c r="I151">
-        <v>0.0983566821595323</v>
+        <v>0.0698196313062085</v>
       </c>
       <c r="J151">
-        <v>0.7915832780016702</v>
+        <v>0.7904229931252164</v>
       </c>
       <c r="K151">
         <v>2.5</v>
@@ -8335,16 +8332,16 @@
         <v>4.01</v>
       </c>
       <c r="M151">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N151">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O151">
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8352,31 +8349,31 @@
         <v>1</v>
       </c>
       <c r="B152" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C152">
-        <v>2.009779296696075</v>
+        <v>2.012505966155742</v>
       </c>
       <c r="D152" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E152">
-        <v>1.932685122836292</v>
+        <v>1.96412288588075</v>
       </c>
       <c r="F152">
         <v>-1</v>
       </c>
       <c r="G152">
-        <v>0.005730220703303925</v>
+        <v>0.00572749403384426</v>
       </c>
       <c r="H152">
-        <v>0.005447314877163708</v>
+        <v>0.005615877114119251</v>
       </c>
       <c r="I152">
-        <v>0.07709417385978323</v>
+        <v>0.04838308027499139</v>
       </c>
       <c r="J152">
-        <v>0.7915832780016702</v>
+        <v>0.7904229931252164</v>
       </c>
       <c r="K152">
         <v>2.35</v>
@@ -8385,16 +8382,16 @@
         <v>3.87</v>
       </c>
       <c r="M152">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N152">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O152">
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8405,28 +8402,28 @@
         <v>33</v>
       </c>
       <c r="C153">
-        <v>2.032225684349332</v>
+        <v>2.03219014170303</v>
       </c>
       <c r="D153" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E153">
-        <v>1.933736407702207</v>
+        <v>1.9625036909336</v>
       </c>
       <c r="F153">
         <v>-1</v>
       </c>
       <c r="G153">
-        <v>0.005987774315650668</v>
+        <v>0.00598780985829697</v>
       </c>
       <c r="H153">
-        <v>0.005446263592297793</v>
+        <v>0.005617496309066401</v>
       </c>
       <c r="I153">
-        <v>0.09848927664712526</v>
+        <v>0.06968645076942992</v>
       </c>
       <c r="J153">
-        <v>0.7911097262602672</v>
+        <v>0.791123943318788</v>
       </c>
       <c r="K153">
         <v>2.5</v>
@@ -8435,16 +8432,16 @@
         <v>4.01</v>
       </c>
       <c r="M153">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N153">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O153">
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8452,31 +8449,31 @@
         <v>1</v>
       </c>
       <c r="B154" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C154">
-        <v>2.010892143288372</v>
+        <v>2.010858733200848</v>
       </c>
       <c r="D154" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E154">
-        <v>1.933736407702207</v>
+        <v>1.9625036909336</v>
       </c>
       <c r="F154">
         <v>-1</v>
       </c>
       <c r="G154">
-        <v>0.005729107856711628</v>
+        <v>0.005729141266799152</v>
       </c>
       <c r="H154">
-        <v>0.005446263592297793</v>
+        <v>0.005617496309066401</v>
       </c>
       <c r="I154">
-        <v>0.07715573558616584</v>
+        <v>0.04835504226724852</v>
       </c>
       <c r="J154">
-        <v>0.7911097262602672</v>
+        <v>0.791123943318788</v>
       </c>
       <c r="K154">
         <v>2.35</v>
@@ -8485,16 +8482,16 @@
         <v>3.87</v>
       </c>
       <c r="M154">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N154">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O154">
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8505,28 +8502,28 @@
         <v>33</v>
       </c>
       <c r="C155">
-        <v>2.033826265263685</v>
+        <v>2.031041804995824</v>
       </c>
       <c r="D155" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E155">
-        <v>1.935157723554152</v>
+        <v>1.961442627816142</v>
       </c>
       <c r="F155">
         <v>-1</v>
       </c>
       <c r="G155">
-        <v>0.005986173734736314</v>
+        <v>0.005988958195004175</v>
       </c>
       <c r="H155">
-        <v>0.005444842276445847</v>
+        <v>0.005618557372183858</v>
       </c>
       <c r="I155">
-        <v>0.09866854170953276</v>
+        <v>0.06959917717968245</v>
       </c>
       <c r="J155">
-        <v>0.7904694938945258</v>
+        <v>0.7915832780016702</v>
       </c>
       <c r="K155">
         <v>2.5</v>
@@ -8535,16 +8532,16 @@
         <v>4.01</v>
       </c>
       <c r="M155">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N155">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O155">
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8552,31 +8549,31 @@
         <v>1</v>
       </c>
       <c r="B156" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C156">
-        <v>2.012396689347864</v>
+        <v>2.009779296696075</v>
       </c>
       <c r="D156" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E156">
-        <v>1.935157723554152</v>
+        <v>1.961442627816142</v>
       </c>
       <c r="F156">
         <v>-1</v>
       </c>
       <c r="G156">
-        <v>0.005727603310652135</v>
+        <v>0.005730220703303925</v>
       </c>
       <c r="H156">
-        <v>0.005444842276445847</v>
+        <v>0.005618557372183858</v>
       </c>
       <c r="I156">
-        <v>0.07723896579371203</v>
+        <v>0.04833666887993338</v>
       </c>
       <c r="J156">
-        <v>0.7904694938945258</v>
+        <v>0.7915832780016702</v>
       </c>
       <c r="K156">
         <v>2.35</v>
@@ -8585,16 +8582,16 @@
         <v>3.87</v>
       </c>
       <c r="M156">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N156">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O156">
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8605,28 +8602,28 @@
         <v>33</v>
       </c>
       <c r="C157">
-        <v>2.037114148133088</v>
+        <v>2.032225684349332</v>
       </c>
       <c r="D157" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E157">
-        <v>1.938077363542182</v>
+        <v>1.962536532338783</v>
       </c>
       <c r="F157">
         <v>-1</v>
       </c>
       <c r="G157">
-        <v>0.005982885851866911</v>
+        <v>0.005987774315650668</v>
       </c>
       <c r="H157">
-        <v>0.005441922636457818</v>
+        <v>0.005617463467661218</v>
       </c>
       <c r="I157">
-        <v>0.09903678459090592</v>
+        <v>0.06968915201054915</v>
       </c>
       <c r="J157">
-        <v>0.7891543407467646</v>
+        <v>0.7911097262602672</v>
       </c>
       <c r="K157">
         <v>2.5</v>
@@ -8635,16 +8632,16 @@
         <v>4.01</v>
       </c>
       <c r="M157">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N157">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O157">
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8652,31 +8649,31 @@
         <v>1</v>
       </c>
       <c r="B158" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C158">
-        <v>2.015487299245103</v>
+        <v>2.010892143288372</v>
       </c>
       <c r="D158" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E158">
-        <v>1.938077363542182</v>
+        <v>1.962536532338783</v>
       </c>
       <c r="F158">
         <v>-1</v>
       </c>
       <c r="G158">
-        <v>0.005724512700754897</v>
+        <v>0.005729107856711628</v>
       </c>
       <c r="H158">
-        <v>0.005441922636457818</v>
+        <v>0.005617463467661218</v>
       </c>
       <c r="I158">
-        <v>0.07740993570292076</v>
+        <v>0.04835561094958973</v>
       </c>
       <c r="J158">
-        <v>0.7891543407467646</v>
+        <v>0.7911097262602672</v>
       </c>
       <c r="K158">
         <v>2.35</v>
@@ -8685,16 +8682,16 @@
         <v>3.87</v>
       </c>
       <c r="M158">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N158">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O158">
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -8705,28 +8702,28 @@
         <v>33</v>
       </c>
       <c r="C159">
-        <v>2.041024370702765</v>
+        <v>2.033826265263685</v>
       </c>
       <c r="D159" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E159">
-        <v>1.941549641184055</v>
+        <v>1.964015469103645</v>
       </c>
       <c r="F159">
         <v>-1</v>
       </c>
       <c r="G159">
-        <v>0.005978975629297235</v>
+        <v>0.005986173734736314</v>
       </c>
       <c r="H159">
-        <v>0.005438450358815945</v>
+        <v>0.005615984530896355</v>
       </c>
       <c r="I159">
-        <v>0.09947472951870973</v>
+        <v>0.06981079616003982</v>
       </c>
       <c r="J159">
-        <v>0.7875902517188939</v>
+        <v>0.7904694938945258</v>
       </c>
       <c r="K159">
         <v>2.5</v>
@@ -8735,16 +8732,16 @@
         <v>4.01</v>
       </c>
       <c r="M159">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N159">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O159">
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -8752,31 +8749,31 @@
         <v>1</v>
       </c>
       <c r="B160" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C160">
-        <v>2.0191629084606</v>
+        <v>2.012396689347864</v>
       </c>
       <c r="D160" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E160">
-        <v>1.941549641184055</v>
+        <v>1.964015469103645</v>
       </c>
       <c r="F160">
         <v>-1</v>
       </c>
       <c r="G160">
-        <v>0.005720837091539401</v>
+        <v>0.005727603310652135</v>
       </c>
       <c r="H160">
-        <v>0.005438450358815945</v>
+        <v>0.005615984530896355</v>
       </c>
       <c r="I160">
-        <v>0.07761326727654438</v>
+        <v>0.04838122024421909</v>
       </c>
       <c r="J160">
-        <v>0.7875902517188939</v>
+        <v>0.7904694938945258</v>
       </c>
       <c r="K160">
         <v>2.35</v>
@@ -8785,16 +8782,16 @@
         <v>3.87</v>
       </c>
       <c r="M160">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N160">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O160">
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -8805,28 +8802,28 @@
         <v>33</v>
       </c>
       <c r="C161">
-        <v>2.042989638697718</v>
+        <v>2.037114148133088</v>
       </c>
       <c r="D161" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E161">
-        <v>1.943294799163574</v>
+        <v>1.967053472874974</v>
       </c>
       <c r="F161">
         <v>-1</v>
       </c>
       <c r="G161">
-        <v>0.005977010361302281</v>
+        <v>0.005982885851866911</v>
       </c>
       <c r="H161">
-        <v>0.005436705200836426</v>
+        <v>0.005612946527125027</v>
       </c>
       <c r="I161">
-        <v>0.09969483953414437</v>
+        <v>0.07006067525811455</v>
       </c>
       <c r="J161">
-        <v>0.7868041445209126</v>
+        <v>0.7891543407467646</v>
       </c>
       <c r="K161">
         <v>2.5</v>
@@ -8835,16 +8832,16 @@
         <v>4.01</v>
       </c>
       <c r="M161">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N161">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O161">
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -8852,31 +8849,31 @@
         <v>1</v>
       </c>
       <c r="B162" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C162">
-        <v>2.021010260375856</v>
+        <v>2.015487299245103</v>
       </c>
       <c r="D162" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E162">
-        <v>1.943294799163574</v>
+        <v>1.967053472874974</v>
       </c>
       <c r="F162">
         <v>-1</v>
       </c>
       <c r="G162">
-        <v>0.005718989739624145</v>
+        <v>0.005724512700754897</v>
       </c>
       <c r="H162">
-        <v>0.005436705200836426</v>
+        <v>0.005612946527125027</v>
       </c>
       <c r="I162">
-        <v>0.07771546121228168</v>
+        <v>0.04843382637012938</v>
       </c>
       <c r="J162">
-        <v>0.7868041445209126</v>
+        <v>0.7891543407467646</v>
       </c>
       <c r="K162">
         <v>2.35</v>
@@ -8885,16 +8882,16 @@
         <v>3.87</v>
       </c>
       <c r="M162">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N162">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O162">
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -8905,28 +8902,28 @@
         <v>33</v>
       </c>
       <c r="C163">
-        <v>2.046475047291454</v>
+        <v>2.041024370702765</v>
       </c>
       <c r="D163" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E163">
-        <v>1.946389841994811</v>
+        <v>1.970666518529355</v>
       </c>
       <c r="F163">
         <v>-1</v>
       </c>
       <c r="G163">
-        <v>0.005973524952708546</v>
+        <v>0.005978975629297235</v>
       </c>
       <c r="H163">
-        <v>0.005433610158005188</v>
+        <v>0.005609333481470645</v>
       </c>
       <c r="I163">
-        <v>0.100085205296643</v>
+        <v>0.07035785217340984</v>
       </c>
       <c r="J163">
-        <v>0.7854099810834182</v>
+        <v>0.7875902517188939</v>
       </c>
       <c r="K163">
         <v>2.5</v>
@@ -8935,16 +8932,16 @@
         <v>4.01</v>
       </c>
       <c r="M163">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N163">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O163">
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -8952,31 +8949,31 @@
         <v>1</v>
       </c>
       <c r="B164" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C164">
-        <v>2.024286544453967</v>
+        <v>2.0191629084606</v>
       </c>
       <c r="D164" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E164">
-        <v>1.946389841994811</v>
+        <v>1.970666518529355</v>
       </c>
       <c r="F164">
         <v>-1</v>
       </c>
       <c r="G164">
-        <v>0.005715713455546033</v>
+        <v>0.005720837091539401</v>
       </c>
       <c r="H164">
-        <v>0.005433610158005188</v>
+        <v>0.005609333481470645</v>
       </c>
       <c r="I164">
-        <v>0.07789670245915592</v>
+        <v>0.0484963899312445</v>
       </c>
       <c r="J164">
-        <v>0.7854099810834182</v>
+        <v>0.7875902517188939</v>
       </c>
       <c r="K164">
         <v>2.35</v>
@@ -8985,16 +8982,16 @@
         <v>3.87</v>
       </c>
       <c r="M164">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N164">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O164">
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9005,28 +9002,28 @@
         <v>33</v>
       </c>
       <c r="C165">
-        <v>2.05115387029975</v>
+        <v>2.042989638697718</v>
       </c>
       <c r="D165" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E165">
-        <v>1.950544636826178</v>
+        <v>1.972482426156692</v>
       </c>
       <c r="F165">
         <v>-1</v>
       </c>
       <c r="G165">
-        <v>0.00596884612970025</v>
+        <v>0.005977010361302281</v>
       </c>
       <c r="H165">
-        <v>0.005429455363173821</v>
+        <v>0.005607517573843309</v>
       </c>
       <c r="I165">
-        <v>0.1006092334735722</v>
+        <v>0.07050721254102643</v>
       </c>
       <c r="J165">
-        <v>0.7835384518800999</v>
+        <v>0.7868041445209126</v>
       </c>
       <c r="K165">
         <v>2.5</v>
@@ -9035,16 +9032,16 @@
         <v>4.01</v>
       </c>
       <c r="M165">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N165">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O165">
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9052,31 +9049,31 @@
         <v>1</v>
       </c>
       <c r="B166" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C166">
-        <v>2.028684638081765</v>
+        <v>2.021010260375856</v>
       </c>
       <c r="D166" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E166">
-        <v>1.950544636826178</v>
+        <v>1.972482426156692</v>
       </c>
       <c r="F166">
         <v>-1</v>
       </c>
       <c r="G166">
-        <v>0.005711315361918235</v>
+        <v>0.005718989739624145</v>
       </c>
       <c r="H166">
-        <v>0.005429455363173821</v>
+        <v>0.005607517573843309</v>
       </c>
       <c r="I166">
-        <v>0.07814000125558729</v>
+        <v>0.04852783421916373</v>
       </c>
       <c r="J166">
-        <v>0.7835384518800999</v>
+        <v>0.7868041445209126</v>
       </c>
       <c r="K166">
         <v>2.35</v>
@@ -9085,16 +9082,16 @@
         <v>3.87</v>
       </c>
       <c r="M166">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N166">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O166">
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9105,28 +9102,28 @@
         <v>33</v>
       </c>
       <c r="C167">
-        <v>2.052411570940913</v>
+        <v>2.046475047291454</v>
       </c>
       <c r="D167" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E167">
-        <v>1.95166147499553</v>
+        <v>1.975702943697304</v>
       </c>
       <c r="F167">
         <v>-1</v>
       </c>
       <c r="G167">
-        <v>0.005967588429059087</v>
+        <v>0.005973524952708546</v>
       </c>
       <c r="H167">
-        <v>0.00542833852500447</v>
+        <v>0.005604297056302696</v>
       </c>
       <c r="I167">
-        <v>0.1007500959453824</v>
+        <v>0.07077210359415043</v>
       </c>
       <c r="J167">
-        <v>0.783035371623635</v>
+        <v>0.7854099810834182</v>
       </c>
       <c r="K167">
         <v>2.5</v>
@@ -9135,16 +9132,16 @@
         <v>4.01</v>
       </c>
       <c r="M167">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N167">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O167">
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9152,31 +9149,31 @@
         <v>1</v>
       </c>
       <c r="B168" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C168">
-        <v>2.029866876684458</v>
+        <v>2.024286544453967</v>
       </c>
       <c r="D168" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E168">
-        <v>1.95166147499553</v>
+        <v>1.975702943697304</v>
       </c>
       <c r="F168">
         <v>-1</v>
       </c>
       <c r="G168">
-        <v>0.005710133123315543</v>
+        <v>0.005715713455546033</v>
       </c>
       <c r="H168">
-        <v>0.00542833852500447</v>
+        <v>0.005604297056302696</v>
       </c>
       <c r="I168">
-        <v>0.07820540168892753</v>
+        <v>0.04858360075666335</v>
       </c>
       <c r="J168">
-        <v>0.783035371623635</v>
+        <v>0.7854099810834182</v>
       </c>
       <c r="K168">
         <v>2.35</v>
@@ -9185,16 +9182,16 @@
         <v>3.87</v>
       </c>
       <c r="M168">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N168">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O168">
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9205,28 +9202,28 @@
         <v>33</v>
       </c>
       <c r="C169">
-        <v>2.054065467064709</v>
+        <v>2.05115387029975</v>
       </c>
       <c r="D169" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E169">
-        <v>1.953130134753462</v>
+        <v>1.980026176156969</v>
       </c>
       <c r="F169">
         <v>-1</v>
       </c>
       <c r="G169">
-        <v>0.005965934532935291</v>
+        <v>0.00596884612970025</v>
       </c>
       <c r="H169">
-        <v>0.005426869865246538</v>
+        <v>0.005599973823843031</v>
       </c>
       <c r="I169">
-        <v>0.1009353323112472</v>
+        <v>0.07112769414278097</v>
       </c>
       <c r="J169">
-        <v>0.7823738131741161</v>
+        <v>0.7835384518800999</v>
       </c>
       <c r="K169">
         <v>2.5</v>
@@ -9235,16 +9232,16 @@
         <v>4.01</v>
       </c>
       <c r="M169">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N169">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O169">
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9252,31 +9249,31 @@
         <v>1</v>
       </c>
       <c r="B170" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C170">
-        <v>2.031421539040827</v>
+        <v>2.028684638081765</v>
       </c>
       <c r="D170" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E170">
-        <v>1.953130134753462</v>
+        <v>1.980026176156969</v>
       </c>
       <c r="F170">
         <v>-1</v>
       </c>
       <c r="G170">
-        <v>0.005708578460959173</v>
+        <v>0.005711315361918235</v>
       </c>
       <c r="H170">
-        <v>0.005426869865246538</v>
+        <v>0.005599973823843031</v>
       </c>
       <c r="I170">
-        <v>0.07829140428736503</v>
+        <v>0.04865846192479606</v>
       </c>
       <c r="J170">
-        <v>0.7823738131741161</v>
+        <v>0.7835384518800999</v>
       </c>
       <c r="K170">
         <v>2.35</v>
@@ -9285,16 +9282,16 @@
         <v>3.87</v>
       </c>
       <c r="M170">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N170">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O170">
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9305,28 +9302,28 @@
         <v>33</v>
       </c>
       <c r="C171">
-        <v>2.057724755182126</v>
+        <v>2.052411570940913</v>
       </c>
       <c r="D171" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E171">
-        <v>1.956379582601728</v>
+        <v>1.981188291549403</v>
       </c>
       <c r="F171">
         <v>-1</v>
       </c>
       <c r="G171">
-        <v>0.005962275244817874</v>
+        <v>0.005967588429059087</v>
       </c>
       <c r="H171">
-        <v>0.005423620417398272</v>
+        <v>0.005598811708450597</v>
       </c>
       <c r="I171">
-        <v>0.1013451725803984</v>
+        <v>0.07122327939150952</v>
       </c>
       <c r="J171">
-        <v>0.7809100979271496</v>
+        <v>0.783035371623635</v>
       </c>
       <c r="K171">
         <v>2.5</v>
@@ -9335,60 +9332,60 @@
         <v>4.01</v>
       </c>
       <c r="M171">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N171">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O171">
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="172" spans="1:16">
       <c r="A172" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B172" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C172">
-        <v>2.034861269871199</v>
+        <v>2.054065467064709</v>
       </c>
       <c r="D172" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E172">
-        <v>1.956379582601728</v>
+        <v>1.982716491567792</v>
       </c>
       <c r="F172">
         <v>-1</v>
       </c>
       <c r="G172">
-        <v>0.005705138730128801</v>
+        <v>0.005965934532935291</v>
       </c>
       <c r="H172">
-        <v>0.005423620417398272</v>
+        <v>0.005597283508432208</v>
       </c>
       <c r="I172">
-        <v>0.07848168726947091</v>
+        <v>0.07134897549691743</v>
       </c>
       <c r="J172">
-        <v>0.7809100979271496</v>
+        <v>0.7823738131741161</v>
       </c>
       <c r="K172">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L172">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M172">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N172">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O172">
         <v>1</v>
@@ -9405,28 +9402,28 @@
         <v>33</v>
       </c>
       <c r="C173">
-        <v>2.059621791558839</v>
+        <v>2.057724755182126</v>
       </c>
       <c r="D173" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E173">
-        <v>1.958064150904249</v>
+        <v>1.986097673788285</v>
       </c>
       <c r="F173">
         <v>-1</v>
       </c>
       <c r="G173">
-        <v>0.005960378208441161</v>
+        <v>0.005962275244817874</v>
       </c>
       <c r="H173">
-        <v>0.005421935849095751</v>
+        <v>0.005593902326211715</v>
       </c>
       <c r="I173">
-        <v>0.1015576406545902</v>
+        <v>0.07162708139384155</v>
       </c>
       <c r="J173">
-        <v>0.7801512833764644</v>
+        <v>0.7809100979271496</v>
       </c>
       <c r="K173">
         <v>2.5</v>
@@ -9435,10 +9432,10 @@
         <v>4.01</v>
       </c>
       <c r="M173">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N173">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O173">
         <v>1</v>
@@ -9455,28 +9452,28 @@
         <v>33</v>
       </c>
       <c r="C174">
-        <v>2.060612201172958</v>
+        <v>2.059621791558839</v>
       </c>
       <c r="D174" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E174">
-        <v>1.958943634641587</v>
+        <v>1.987850535400367</v>
       </c>
       <c r="F174">
         <v>-1</v>
       </c>
       <c r="G174">
-        <v>0.005959387798827042</v>
+        <v>0.005960378208441161</v>
       </c>
       <c r="H174">
-        <v>0.005421056365358413</v>
+        <v>0.005592149464599632</v>
       </c>
       <c r="I174">
-        <v>0.1016685665313712</v>
+        <v>0.0717712561584718</v>
       </c>
       <c r="J174">
-        <v>0.7797551195308166</v>
+        <v>0.7801512833764644</v>
       </c>
       <c r="K174">
         <v>2.5</v>
@@ -9485,10 +9482,10 @@
         <v>4.01</v>
       </c>
       <c r="M174">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N174">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O174">
         <v>1</v>
@@ -9505,28 +9502,28 @@
         <v>33</v>
       </c>
       <c r="C175">
-        <v>2.062155534027272</v>
+        <v>2.060612201172958</v>
       </c>
       <c r="D175" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E175">
-        <v>1.960314114216218</v>
+        <v>1.988765673883814</v>
       </c>
       <c r="F175">
         <v>-1</v>
       </c>
       <c r="G175">
-        <v>0.005957844465972727</v>
+        <v>0.005959387798827042</v>
       </c>
       <c r="H175">
-        <v>0.005419685885783782</v>
+        <v>0.005591234326116187</v>
       </c>
       <c r="I175">
-        <v>0.1018414198110544</v>
+        <v>0.07184652728914442</v>
       </c>
       <c r="J175">
-        <v>0.7791377863890909</v>
+        <v>0.7797551195308166</v>
       </c>
       <c r="K175">
         <v>2.5</v>
@@ -9535,10 +9532,10 @@
         <v>4.01</v>
       </c>
       <c r="M175">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="N175">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="O175">
         <v>1</v>
@@ -9552,43 +9549,43 @@
         <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C176">
-        <v>2.065159805074657</v>
+        <v>1.559502895465797</v>
       </c>
       <c r="D176" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="E176">
-        <v>1.962981906906296</v>
+        <v>1.912426863301427</v>
       </c>
       <c r="F176">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G176">
-        <v>0.005954840194925343</v>
+        <v>0.004660497104534203</v>
       </c>
       <c r="H176">
-        <v>0.005417018093093704</v>
+        <v>0.005967573136698573</v>
       </c>
       <c r="I176">
-        <v>0.1021778981683614</v>
+        <v>0.35292396783563</v>
       </c>
       <c r="J176">
-        <v>0.777936077970137</v>
+        <v>0.7951267202739504</v>
       </c>
       <c r="K176">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="L176">
-        <v>4.01</v>
+        <v>3.11</v>
       </c>
       <c r="M176">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="N176">
-        <v>3.69</v>
+        <v>3.94</v>
       </c>
       <c r="O176">
         <v>1</v>
@@ -9602,99 +9599,49 @@
         <v>0</v>
       </c>
       <c r="B177" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C177">
-        <v>2.066699852252084</v>
+        <v>1.557903064751518</v>
       </c>
       <c r="D177" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="E177">
-        <v>1.96434946879985</v>
+        <v>1.910334776982754</v>
       </c>
       <c r="F177">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G177">
-        <v>0.005953300147747916</v>
+        <v>0.004662096935248481</v>
       </c>
       <c r="H177">
-        <v>0.00541565053120015</v>
+        <v>0.005969665223017246</v>
       </c>
       <c r="I177">
-        <v>0.1023503834522335</v>
+        <v>0.3524317122312364</v>
       </c>
       <c r="J177">
-        <v>0.7773200590991663</v>
+        <v>0.7959471462812728</v>
       </c>
       <c r="K177">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="L177">
-        <v>4.01</v>
+        <v>3.11</v>
       </c>
       <c r="M177">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="N177">
-        <v>3.69</v>
+        <v>3.94</v>
       </c>
       <c r="O177">
         <v>1</v>
       </c>
       <c r="P177" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="178" spans="1:16">
-      <c r="A178" s="1">
-        <v>0</v>
-      </c>
-      <c r="B178" t="s">
-        <v>38</v>
-      </c>
-      <c r="C178">
-        <v>1.557903064751518</v>
-      </c>
-      <c r="D178" t="s">
-        <v>25</v>
-      </c>
-      <c r="E178">
-        <v>1.910334776982754</v>
-      </c>
-      <c r="F178">
-        <v>1</v>
-      </c>
-      <c r="G178">
-        <v>0.004662096935248481</v>
-      </c>
-      <c r="H178">
-        <v>0.005969665223017246</v>
-      </c>
-      <c r="I178">
-        <v>0.3524317122312364</v>
-      </c>
-      <c r="J178">
-        <v>0.7959471462812728</v>
-      </c>
-      <c r="K178">
-        <v>1.95</v>
-      </c>
-      <c r="L178">
-        <v>3.11</v>
-      </c>
-      <c r="M178">
-        <v>2.55</v>
-      </c>
-      <c r="N178">
-        <v>3.94</v>
-      </c>
-      <c r="O178">
-        <v>1</v>
-      </c>
-      <c r="P178" t="s">
-        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01618-601618.xlsx
+++ b/s60_signal/position-01618-601618.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="138">
   <si>
     <t>trade_time</t>
   </si>
@@ -100,7 +100,7 @@
     <t>2021-08-06</t>
   </si>
   <si>
-    <t>2021-08-02</t>
+    <t>2021-08-11</t>
   </si>
   <si>
     <t>2021-08-03</t>
@@ -112,13 +112,10 @@
     <t>2021-01-15</t>
   </si>
   <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
     <t>2021-07-26</t>
   </si>
   <si>
-    <t>2021-08-11</t>
+    <t>2021-08-12</t>
   </si>
   <si>
     <t>2021-02-26</t>
@@ -130,12 +127,12 @@
     <t>2021-02-23</t>
   </si>
   <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
     <t>2021-07-19</t>
   </si>
   <si>
+    <t>2021-07-16</t>
+  </si>
+  <si>
     <t>2016-12-30</t>
   </si>
   <si>
@@ -163,7 +160,10 @@
     <t>2020-10-15</t>
   </si>
   <si>
-    <t>2021-08-12</t>
+    <t>2021-08-13</t>
+  </si>
+  <si>
+    <t>2021-08-16</t>
   </si>
   <si>
     <t>2021-01-20</t>
@@ -418,19 +418,10 @@
     <t>2021-05-31</t>
   </si>
   <si>
-    <t>2021-06-01</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>2021-06-07</t>
+    <t>2021-07-12</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
   </si>
   <si>
     <t>2021-07-14</t>
@@ -794,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P177"/>
+  <dimension ref="A1:P173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -855,7 +846,7 @@
         <v>2.241636620202809</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2">
         <v>2.083673377356266</v>
@@ -905,7 +896,7 @@
         <v>2.291018963074085</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3">
         <v>2.748932188801797</v>
@@ -955,7 +946,7 @@
         <v>0.1640886968569069</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E4">
         <v>0.8087275807852619</v>
@@ -1005,7 +996,7 @@
         <v>0.1567937244930127</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5">
         <v>0.8087275807852619</v>
@@ -1055,7 +1046,7 @@
         <v>0.06008199184724816</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6">
         <v>0.7118353409391309</v>
@@ -1105,7 +1096,7 @@
         <v>0.05109309920632388</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7">
         <v>0.7118353409391309</v>
@@ -1155,7 +1146,7 @@
         <v>-0.0569506423664734</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8">
         <v>0.6028081963621785</v>
@@ -1205,7 +1196,7 @@
         <v>-0.06784560396853312</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E9">
         <v>0.6028081963621785</v>
@@ -1255,7 +1246,7 @@
         <v>-0.1396452470657845</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E10">
         <v>0.5257702258605397</v>
@@ -1305,7 +1296,7 @@
         <v>-0.1518870263339567</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11">
         <v>0.5257702258605397</v>
@@ -1355,7 +1346,7 @@
         <v>-0.2479133877986754</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12">
         <v>0.424908049151723</v>
@@ -1405,7 +1396,7 @@
         <v>-0.2619184918344848</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E13">
         <v>0.424908049151723</v>
@@ -1455,7 +1446,7 @@
         <v>-0.3399965939203824</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E14">
         <v>0.3391236942630966</v>
@@ -1505,7 +1496,7 @@
         <v>0.9756011105228968</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E15">
         <v>0.8107654111102569</v>
@@ -1555,7 +1546,7 @@
         <v>1.301145679016073</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E16">
         <v>1.173416666670367</v>
@@ -1605,7 +1596,7 @@
         <v>1.296277364845049</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17">
         <v>1.230890933009092</v>
@@ -1655,7 +1646,7 @@
         <v>0.4435035626339812</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E18">
         <v>0.9439906537348826</v>
@@ -1705,7 +1696,7 @@
         <v>0.4423533289773536</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19">
         <v>0.9439906537348826</v>
@@ -1755,7 +1746,7 @@
         <v>1.507350128118183</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E20">
         <v>1.202821457299868</v>
@@ -1805,7 +1796,7 @@
         <v>1.54125697476493</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E21">
         <v>1.238224194239853</v>
@@ -1855,7 +1846,7 @@
         <v>1.573438797246031</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E22">
         <v>1.271825803006885</v>
@@ -1905,7 +1896,7 @@
         <v>1.613400857289038</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E23">
         <v>1.313550895110613</v>
@@ -1955,7 +1946,7 @@
         <v>1.593400857289038</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E24">
         <v>1.363275825771058</v>
@@ -2005,7 +1996,7 @@
         <v>1.645344720184119</v>
       </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E25">
         <v>1.346904046074595</v>
@@ -2055,7 +2046,7 @@
         <v>1.625344720184119</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E26">
         <v>1.394045281942056</v>
@@ -2105,7 +2096,7 @@
         <v>1.68180858461344</v>
       </c>
       <c r="D27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E27">
         <v>1.384976610405209</v>
@@ -2155,7 +2146,7 @@
         <v>1.66180858461344</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E28">
         <v>1.429168563120298</v>
@@ -2205,7 +2196,7 @@
         <v>1.710614904938503</v>
       </c>
       <c r="D29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29">
         <v>1.415053797803437</v>
@@ -2241,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2255,7 +2246,7 @@
         <v>1.690614904938503</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30">
         <v>1.456915827551058</v>
@@ -2291,7 +2282,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2405,7 +2396,7 @@
         <v>2.754322580645161</v>
       </c>
       <c r="D33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E33">
         <v>2.847571157495255</v>
@@ -2455,10 +2446,10 @@
         <v>2.638017457305502</v>
       </c>
       <c r="D34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E34">
-        <v>2.715915749525616</v>
+        <v>2.678463757115749</v>
       </c>
       <c r="F34">
         <v>-1</v>
@@ -2467,10 +2458,10 @@
         <v>0.004841982542694498</v>
       </c>
       <c r="H34">
-        <v>0.004864084250474385</v>
+        <v>0.004761536242884251</v>
       </c>
       <c r="I34">
-        <v>-0.07789829222011369</v>
+        <v>-0.04044629981024661</v>
       </c>
       <c r="J34">
         <v>0.4649715370018978</v>
@@ -2482,10 +2473,10 @@
         <v>3.74</v>
       </c>
       <c r="M34">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="N34">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="O34">
         <v>1</v>
@@ -2505,10 +2496,10 @@
         <v>2.662412903225806</v>
       </c>
       <c r="D35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E35">
-        <v>2.715915749525616</v>
+        <v>2.678463757115749</v>
       </c>
       <c r="F35">
         <v>-1</v>
@@ -2517,10 +2508,10 @@
         <v>0.004717587096774194</v>
       </c>
       <c r="H35">
-        <v>0.004864084250474385</v>
+        <v>0.004761536242884251</v>
       </c>
       <c r="I35">
-        <v>-0.05350284629981017</v>
+        <v>-0.0160508538899431</v>
       </c>
       <c r="J35">
         <v>0.4649715370018978</v>
@@ -2532,10 +2523,10 @@
         <v>3.69</v>
       </c>
       <c r="M35">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="N35">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="O35">
         <v>1</v>
@@ -2546,96 +2537,96 @@
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C36">
-        <v>2.644938723766401</v>
+        <v>2.657763187855787</v>
       </c>
       <c r="D36" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E36">
-        <v>2.740332082123923</v>
+        <v>2.678463757115749</v>
       </c>
       <c r="F36">
         <v>-1</v>
       </c>
       <c r="G36">
-        <v>0.005235061276233599</v>
+        <v>0.004722236812144213</v>
       </c>
       <c r="H36">
-        <v>0.005279667917876077</v>
+        <v>0.004761536242884251</v>
       </c>
       <c r="I36">
-        <v>-0.0953933583575215</v>
+        <v>-0.020700569259962</v>
       </c>
       <c r="J36">
-        <v>0.5078671671504308</v>
+        <v>0.4649715370018978</v>
       </c>
       <c r="K36">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="L36">
-        <v>3.94</v>
+        <v>3.69</v>
       </c>
       <c r="M36">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="N36">
-        <v>4.01</v>
+        <v>3.72</v>
       </c>
       <c r="O36">
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C37">
-        <v>2.536354813853479</v>
+        <v>2.644938723766401</v>
       </c>
       <c r="D37" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E37">
-        <v>2.616826843882505</v>
+        <v>2.740332082123923</v>
       </c>
       <c r="F37">
         <v>-1</v>
       </c>
       <c r="G37">
-        <v>0.004943645186146522</v>
+        <v>0.005235061276233599</v>
       </c>
       <c r="H37">
-        <v>0.004963173156117495</v>
+        <v>0.005279667917876077</v>
       </c>
       <c r="I37">
-        <v>-0.08047203002902581</v>
+        <v>-0.0953933583575215</v>
       </c>
       <c r="J37">
         <v>0.5078671671504308</v>
       </c>
       <c r="K37">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="L37">
-        <v>3.74</v>
+        <v>3.94</v>
       </c>
       <c r="M37">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="N37">
-        <v>3.79</v>
+        <v>4.01</v>
       </c>
       <c r="O37">
         <v>1</v>
@@ -2646,46 +2637,46 @@
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C38">
-        <v>2.567613560597548</v>
+        <v>2.676512157196488</v>
       </c>
       <c r="D38" t="s">
         <v>49</v>
       </c>
       <c r="E38">
-        <v>2.616826843882505</v>
+        <v>2.656669500539496</v>
       </c>
       <c r="F38">
         <v>-1</v>
       </c>
       <c r="G38">
-        <v>0.004812386439402452</v>
+        <v>0.005063487842803513</v>
       </c>
       <c r="H38">
-        <v>0.004963173156117495</v>
+        <v>0.005023330499460504</v>
       </c>
       <c r="I38">
-        <v>-0.04921328328495722</v>
+        <v>0.01984265665699159</v>
       </c>
       <c r="J38">
         <v>0.5078671671504308</v>
       </c>
       <c r="K38">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="L38">
-        <v>3.69</v>
+        <v>3.87</v>
       </c>
       <c r="M38">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N38">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O38">
         <v>1</v>
@@ -2696,146 +2687,146 @@
     </row>
     <row r="39" spans="1:16">
       <c r="A39" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C39">
-        <v>2.551891062104373</v>
+        <v>2.567613560597548</v>
       </c>
       <c r="D39" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E39">
-        <v>2.649108884416052</v>
+        <v>2.656669500539496</v>
       </c>
       <c r="F39">
         <v>-1</v>
       </c>
       <c r="G39">
-        <v>0.005328108937895627</v>
+        <v>0.004812386439402452</v>
       </c>
       <c r="H39">
-        <v>0.005370891115583948</v>
+        <v>0.005023330499460504</v>
       </c>
       <c r="I39">
-        <v>-0.09721782231167886</v>
+        <v>-0.08905593994194838</v>
       </c>
       <c r="J39">
-        <v>0.5443564462335794</v>
+        <v>0.5078671671504308</v>
       </c>
       <c r="K39">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="L39">
-        <v>3.94</v>
+        <v>3.69</v>
       </c>
       <c r="M39">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="N39">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="O39">
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B40" t="s">
         <v>28</v>
       </c>
       <c r="C40">
-        <v>2.454431657964081</v>
+        <v>2.562534888926043</v>
       </c>
       <c r="D40" t="s">
         <v>49</v>
       </c>
       <c r="E40">
-        <v>2.532536609200432</v>
+        <v>2.656669500539496</v>
       </c>
       <c r="F40">
         <v>-1</v>
       </c>
       <c r="G40">
-        <v>0.005045568342035919</v>
+        <v>0.004817465111073956</v>
       </c>
       <c r="H40">
-        <v>0.005047463390799568</v>
+        <v>0.005023330499460504</v>
       </c>
       <c r="I40">
-        <v>-0.07810495123635075</v>
+        <v>-0.09413461161345271</v>
       </c>
       <c r="J40">
-        <v>0.5443564462335794</v>
+        <v>0.5078671671504308</v>
       </c>
       <c r="K40">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="L40">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="M40">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N40">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O40">
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C41">
-        <v>2.486972253823789</v>
+        <v>2.551891062104373</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E41">
-        <v>2.532536609200432</v>
+        <v>2.649108884416052</v>
       </c>
       <c r="F41">
         <v>-1</v>
       </c>
       <c r="G41">
-        <v>0.004893027746176211</v>
+        <v>0.005328108937895627</v>
       </c>
       <c r="H41">
-        <v>0.005047463390799568</v>
+        <v>0.005370891115583948</v>
       </c>
       <c r="I41">
-        <v>-0.0455643553766425</v>
+        <v>-0.09721782231167886</v>
       </c>
       <c r="J41">
         <v>0.5443564462335794</v>
       </c>
       <c r="K41">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="L41">
-        <v>3.69</v>
+        <v>3.94</v>
       </c>
       <c r="M41">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="N41">
-        <v>3.79</v>
+        <v>4.01</v>
       </c>
       <c r="O41">
         <v>1</v>
@@ -2846,152 +2837,152 @@
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C42">
-        <v>2.433094415049971</v>
+        <v>2.590762351351088</v>
       </c>
       <c r="D42" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E42">
-        <v>2.532641583382324</v>
+        <v>2.57164948027576</v>
       </c>
       <c r="F42">
         <v>-1</v>
       </c>
       <c r="G42">
-        <v>0.005446905584950029</v>
+        <v>0.005149237648648912</v>
       </c>
       <c r="H42">
-        <v>0.005487358416617676</v>
+        <v>0.00510835051972424</v>
       </c>
       <c r="I42">
-        <v>-0.09954716833235322</v>
+        <v>0.01911287107532855</v>
       </c>
       <c r="J42">
-        <v>0.5909433666470703</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K42">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="L42">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="M42">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="N42">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="O42">
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C43">
-        <v>2.481283088379385</v>
+        <v>2.486972253823789</v>
       </c>
       <c r="D43" t="s">
         <v>49</v>
       </c>
       <c r="E43">
-        <v>2.424920823045268</v>
+        <v>2.57164948027576</v>
       </c>
       <c r="F43">
         <v>-1</v>
       </c>
       <c r="G43">
-        <v>0.005258716911620615</v>
+        <v>0.004893027746176211</v>
       </c>
       <c r="H43">
-        <v>0.005155079176954733</v>
+        <v>0.00510835051972424</v>
       </c>
       <c r="I43">
-        <v>0.05636226533411737</v>
+        <v>-0.08467722645197062</v>
       </c>
       <c r="J43">
-        <v>0.5909433666470703</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K43">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="L43">
-        <v>3.87</v>
+        <v>3.69</v>
       </c>
       <c r="M43">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N43">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C44">
-        <v>2.384015159709975</v>
+        <v>2.481528689361454</v>
       </c>
       <c r="D44" t="s">
         <v>49</v>
       </c>
       <c r="E44">
-        <v>2.424920823045268</v>
+        <v>2.57164948027576</v>
       </c>
       <c r="F44">
         <v>-1</v>
       </c>
       <c r="G44">
-        <v>0.004995984840290025</v>
+        <v>0.004898471310638547</v>
       </c>
       <c r="H44">
-        <v>0.005155079176954733</v>
+        <v>0.00510835051972424</v>
       </c>
       <c r="I44">
-        <v>-0.04090566333529289</v>
+        <v>-0.09012079091430625</v>
       </c>
       <c r="J44">
-        <v>0.5909433666470703</v>
+        <v>0.5443564462335794</v>
       </c>
       <c r="K44">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="L44">
         <v>3.69</v>
       </c>
       <c r="M44">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N44">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O44">
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3002,28 +2993,28 @@
         <v>25</v>
       </c>
       <c r="C45">
-        <v>2.311696741357657</v>
+        <v>2.433094415049971</v>
       </c>
       <c r="D45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E45">
-        <v>2.413624256232997</v>
+        <v>2.532641583382324</v>
       </c>
       <c r="F45">
         <v>-1</v>
       </c>
       <c r="G45">
-        <v>0.005568303258642344</v>
+        <v>0.005446905584950029</v>
       </c>
       <c r="H45">
-        <v>0.005606375743767004</v>
+        <v>0.005487358416617676</v>
       </c>
       <c r="I45">
-        <v>-0.10192751487534</v>
+        <v>-0.09954716833235322</v>
       </c>
       <c r="J45">
-        <v>0.6385502975068013</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K45">
         <v>2.55</v>
@@ -3041,7 +3032,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3052,28 +3043,28 @@
         <v>29</v>
       </c>
       <c r="C46">
-        <v>2.369406800859017</v>
+        <v>2.481283088379385</v>
       </c>
       <c r="D46" t="s">
         <v>49</v>
       </c>
       <c r="E46">
-        <v>2.314948812759289</v>
+        <v>2.463101955712326</v>
       </c>
       <c r="F46">
         <v>-1</v>
       </c>
       <c r="G46">
-        <v>0.005370593199140983</v>
+        <v>0.005258716911620615</v>
       </c>
       <c r="H46">
-        <v>0.005265051187240711</v>
+        <v>0.005216898044287674</v>
       </c>
       <c r="I46">
-        <v>0.05445798809972757</v>
+        <v>0.0181811326670589</v>
       </c>
       <c r="J46">
-        <v>0.6385502975068013</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K46">
         <v>2.35</v>
@@ -3082,16 +3073,16 @@
         <v>3.87</v>
       </c>
       <c r="M46">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N46">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O46">
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3102,28 +3093,28 @@
         <v>27</v>
       </c>
       <c r="C47">
-        <v>2.278803842509969</v>
+        <v>2.384015159709975</v>
       </c>
       <c r="D47" t="s">
         <v>49</v>
       </c>
       <c r="E47">
-        <v>2.314948812759289</v>
+        <v>2.463101955712326</v>
       </c>
       <c r="F47">
         <v>-1</v>
       </c>
       <c r="G47">
-        <v>0.005101196157490031</v>
+        <v>0.004995984840290025</v>
       </c>
       <c r="H47">
-        <v>0.005265051187240711</v>
+        <v>0.005216898044287674</v>
       </c>
       <c r="I47">
-        <v>-0.03614497024932017</v>
+        <v>-0.07908679600235136</v>
       </c>
       <c r="J47">
-        <v>0.6385502975068013</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K47">
         <v>2.21</v>
@@ -3132,298 +3123,298 @@
         <v>3.69</v>
       </c>
       <c r="M47">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N47">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O47">
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C48">
-        <v>2.182359258383708</v>
+        <v>2.378105726043504</v>
       </c>
       <c r="D48" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E48">
-        <v>2.286822802336969</v>
+        <v>2.463101955712326</v>
       </c>
       <c r="F48">
         <v>-1</v>
       </c>
       <c r="G48">
-        <v>0.005697640741616292</v>
+        <v>0.005001894273956496</v>
       </c>
       <c r="H48">
-        <v>0.005733177197663031</v>
+        <v>0.005216898044287674</v>
       </c>
       <c r="I48">
-        <v>-0.1044635439532606</v>
+        <v>-0.08499622966882203</v>
       </c>
       <c r="J48">
-        <v>0.6892708790652124</v>
+        <v>0.5909433666470703</v>
       </c>
       <c r="K48">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="L48">
-        <v>3.94</v>
+        <v>3.69</v>
       </c>
       <c r="M48">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="N48">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="O48">
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C49">
-        <v>2.250213434196751</v>
+        <v>2.311696741357657</v>
       </c>
       <c r="D49" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E49">
-        <v>2.197784269359359</v>
+        <v>2.413624256232997</v>
       </c>
       <c r="F49">
         <v>-1</v>
       </c>
       <c r="G49">
-        <v>0.00548978656580325</v>
+        <v>0.005568303258642344</v>
       </c>
       <c r="H49">
-        <v>0.005382215730640641</v>
+        <v>0.005606375743767004</v>
       </c>
       <c r="I49">
-        <v>0.0524291648373918</v>
+        <v>-0.10192751487534</v>
       </c>
       <c r="J49">
-        <v>0.6892708790652124</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K49">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L49">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M49">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="N49">
-        <v>3.79</v>
+        <v>4.01</v>
       </c>
       <c r="O49">
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C50">
-        <v>2.16671135726588</v>
+        <v>2.369406800859017</v>
       </c>
       <c r="D50" t="s">
         <v>49</v>
       </c>
       <c r="E50">
-        <v>2.197784269359359</v>
+        <v>2.352177806809153</v>
       </c>
       <c r="F50">
         <v>-1</v>
       </c>
       <c r="G50">
-        <v>0.005213288642734119</v>
+        <v>0.005370593199140983</v>
       </c>
       <c r="H50">
-        <v>0.005382215730640641</v>
+        <v>0.005327822193190846</v>
       </c>
       <c r="I50">
-        <v>-0.03107291209347895</v>
+        <v>0.017228994049864</v>
       </c>
       <c r="J50">
-        <v>0.6892708790652124</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K50">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="L50">
-        <v>3.69</v>
+        <v>3.87</v>
       </c>
       <c r="M50">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N50">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O50">
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C51">
-        <v>2.037699170124481</v>
+        <v>2.278803842509969</v>
       </c>
       <c r="D51" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E51">
-        <v>1.775843983402489</v>
+        <v>2.352177806809153</v>
       </c>
       <c r="F51">
         <v>-1</v>
       </c>
       <c r="G51">
-        <v>0.004482300829875518</v>
+        <v>0.005101196157490031</v>
       </c>
       <c r="H51">
-        <v>0.004324156016597511</v>
+        <v>0.005327822193190846</v>
       </c>
       <c r="I51">
-        <v>0.2618551867219918</v>
+        <v>-0.07337396429918375</v>
       </c>
       <c r="J51">
-        <v>0.7407883817427386</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K51">
-        <v>1.65</v>
+        <v>2.21</v>
       </c>
       <c r="L51">
-        <v>3.26</v>
+        <v>3.69</v>
       </c>
       <c r="M51">
-        <v>1.72</v>
+        <v>2.33</v>
       </c>
       <c r="N51">
-        <v>3.05</v>
+        <v>3.84</v>
       </c>
       <c r="O51">
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C52">
-        <v>2.047699170124481</v>
+        <v>2.272418339534901</v>
       </c>
       <c r="D52" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E52">
-        <v>1.775843983402489</v>
+        <v>2.352177806809153</v>
       </c>
       <c r="F52">
         <v>-1</v>
       </c>
       <c r="G52">
-        <v>0.004492300829875518</v>
+        <v>0.005107581660465099</v>
       </c>
       <c r="H52">
-        <v>0.004324156016597511</v>
+        <v>0.005327822193190846</v>
       </c>
       <c r="I52">
-        <v>0.271855186721992</v>
+        <v>-0.07975946727425187</v>
       </c>
       <c r="J52">
-        <v>0.7407883817427386</v>
+        <v>0.6385502975068013</v>
       </c>
       <c r="K52">
-        <v>1.65</v>
+        <v>2.22</v>
       </c>
       <c r="L52">
-        <v>3.27</v>
+        <v>3.69</v>
       </c>
       <c r="M52">
-        <v>1.72</v>
+        <v>2.33</v>
       </c>
       <c r="N52">
-        <v>3.05</v>
+        <v>3.84</v>
       </c>
       <c r="O52">
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" spans="1:16">
       <c r="A53" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B53" t="s">
         <v>25</v>
       </c>
       <c r="C53">
-        <v>2.050989626556016</v>
+        <v>2.182359258383708</v>
       </c>
       <c r="D53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E53">
-        <v>2.158029045643153</v>
+        <v>2.286822802336969</v>
       </c>
       <c r="F53">
         <v>-1</v>
       </c>
       <c r="G53">
-        <v>0.005829010373443984</v>
+        <v>0.005697640741616292</v>
       </c>
       <c r="H53">
-        <v>0.005861970954356846</v>
+        <v>0.005733177197663031</v>
       </c>
       <c r="I53">
-        <v>-0.1070394190871369</v>
+        <v>-0.1044635439532606</v>
       </c>
       <c r="J53">
-        <v>0.7407883817427386</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K53">
         <v>2.55</v>
@@ -3441,39 +3432,39 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B54" t="s">
         <v>29</v>
       </c>
       <c r="C54">
-        <v>2.129147302904564</v>
+        <v>2.250213434196751</v>
       </c>
       <c r="D54" t="s">
         <v>49</v>
       </c>
       <c r="E54">
-        <v>2.078778838174274</v>
+        <v>2.233998851778055</v>
       </c>
       <c r="F54">
         <v>-1</v>
       </c>
       <c r="G54">
-        <v>0.005610852697095436</v>
+        <v>0.00548978656580325</v>
       </c>
       <c r="H54">
-        <v>0.005501221161825726</v>
+        <v>0.005446001148221945</v>
       </c>
       <c r="I54">
-        <v>0.05036846473029044</v>
+        <v>0.01621458241869611</v>
       </c>
       <c r="J54">
-        <v>0.7407883817427386</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K54">
         <v>2.35</v>
@@ -3482,48 +3473,48 @@
         <v>3.87</v>
       </c>
       <c r="M54">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N54">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O54">
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:16">
       <c r="A55" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B55" t="s">
         <v>27</v>
       </c>
       <c r="C55">
-        <v>2.052857676348547</v>
+        <v>2.16671135726588</v>
       </c>
       <c r="D55" t="s">
         <v>49</v>
       </c>
       <c r="E55">
-        <v>2.078778838174274</v>
+        <v>2.233998851778055</v>
       </c>
       <c r="F55">
         <v>-1</v>
       </c>
       <c r="G55">
-        <v>0.005327142323651453</v>
+        <v>0.005213288642734119</v>
       </c>
       <c r="H55">
-        <v>0.005501221161825726</v>
+        <v>0.005446001148221945</v>
       </c>
       <c r="I55">
-        <v>-0.02592116182572646</v>
+        <v>-0.06728749451217464</v>
       </c>
       <c r="J55">
-        <v>0.7407883817427386</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K55">
         <v>2.21</v>
@@ -3532,66 +3523,66 @@
         <v>3.69</v>
       </c>
       <c r="M55">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N55">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O55">
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C56">
-        <v>2.027673443983402</v>
+        <v>2.159818648475228</v>
       </c>
       <c r="D56" t="s">
         <v>49</v>
       </c>
       <c r="E56">
-        <v>2.078778838174274</v>
+        <v>2.233998851778055</v>
       </c>
       <c r="F56">
         <v>-1</v>
       </c>
       <c r="G56">
-        <v>0.005272326556016598</v>
+        <v>0.005220181351524772</v>
       </c>
       <c r="H56">
-        <v>0.005501221161825726</v>
+        <v>0.005446001148221945</v>
       </c>
       <c r="I56">
-        <v>-0.05110539419087168</v>
+        <v>-0.07418020330282671</v>
       </c>
       <c r="J56">
-        <v>0.7407883817427386</v>
+        <v>0.6892708790652124</v>
       </c>
       <c r="K56">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="L56">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
       <c r="M56">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N56">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O56">
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3602,28 +3593,28 @@
         <v>30</v>
       </c>
       <c r="C57">
-        <v>1.939614977812812</v>
+        <v>2.037699170124481</v>
       </c>
       <c r="D57" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E57">
-        <v>1.637628978619619</v>
+        <v>1.775843983402489</v>
       </c>
       <c r="F57">
         <v>-1</v>
       </c>
       <c r="G57">
-        <v>0.004580385022187188</v>
+        <v>0.004482300829875518</v>
       </c>
       <c r="H57">
-        <v>0.004182371021380382</v>
+        <v>0.004324156016597511</v>
       </c>
       <c r="I57">
-        <v>0.301985999193193</v>
+        <v>0.2618551867219918</v>
       </c>
       <c r="J57">
-        <v>0.8002333467801142</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K57">
         <v>1.65</v>
@@ -3632,16 +3623,16 @@
         <v>3.26</v>
       </c>
       <c r="M57">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="N57">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="O57">
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3649,49 +3640,49 @@
         <v>1</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C58">
-        <v>2.009416633049714</v>
+        <v>2.047699170124481</v>
       </c>
       <c r="D58" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E58">
-        <v>1.941460968937936</v>
+        <v>1.775843983402489</v>
       </c>
       <c r="F58">
         <v>-1</v>
       </c>
       <c r="G58">
-        <v>0.006010583366950286</v>
+        <v>0.004492300829875518</v>
       </c>
       <c r="H58">
-        <v>0.005638539031062064</v>
+        <v>0.004324156016597511</v>
       </c>
       <c r="I58">
-        <v>0.067955664111778</v>
+        <v>0.271855186721992</v>
       </c>
       <c r="J58">
-        <v>0.8002333467801142</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K58">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="L58">
-        <v>4.01</v>
+        <v>3.27</v>
       </c>
       <c r="M58">
-        <v>2.31</v>
+        <v>1.72</v>
       </c>
       <c r="N58">
-        <v>3.79</v>
+        <v>3.05</v>
       </c>
       <c r="O58">
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3699,49 +3690,49 @@
         <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C59">
-        <v>1.989451635066732</v>
+        <v>2.050989626556016</v>
       </c>
       <c r="D59" t="s">
         <v>49</v>
       </c>
       <c r="E59">
-        <v>1.941460968937936</v>
+        <v>2.113963070539419</v>
       </c>
       <c r="F59">
         <v>-1</v>
       </c>
       <c r="G59">
-        <v>0.005750548364933269</v>
+        <v>0.005829010373443984</v>
       </c>
       <c r="H59">
-        <v>0.005638539031062064</v>
+        <v>0.005566036929460581</v>
       </c>
       <c r="I59">
-        <v>0.04799066612879543</v>
+        <v>-0.06297344398340243</v>
       </c>
       <c r="J59">
-        <v>0.8002333467801142</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K59">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L59">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M59">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N59">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O59">
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -3749,49 +3740,49 @@
         <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C60">
-        <v>1.921484303615948</v>
+        <v>2.129147302904564</v>
       </c>
       <c r="D60" t="s">
         <v>49</v>
       </c>
       <c r="E60">
-        <v>1.941460968937936</v>
+        <v>2.113963070539419</v>
       </c>
       <c r="F60">
         <v>-1</v>
       </c>
       <c r="G60">
-        <v>0.005458515696384052</v>
+        <v>0.005610852697095436</v>
       </c>
       <c r="H60">
-        <v>0.005638539031062064</v>
+        <v>0.005566036929460581</v>
       </c>
       <c r="I60">
-        <v>-0.01997666532198861</v>
+        <v>0.01518423236514543</v>
       </c>
       <c r="J60">
-        <v>0.8002333467801142</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K60">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="L60">
-        <v>3.69</v>
+        <v>3.87</v>
       </c>
       <c r="M60">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N60">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O60">
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -3799,431 +3790,431 @@
         <v>4</v>
       </c>
       <c r="B61" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C61">
-        <v>1.913481970148146</v>
+        <v>2.052857676348547</v>
       </c>
       <c r="D61" t="s">
         <v>49</v>
       </c>
       <c r="E61">
-        <v>1.941460968937936</v>
+        <v>2.113963070539419</v>
       </c>
       <c r="F61">
         <v>-1</v>
       </c>
       <c r="G61">
-        <v>0.005466518029851854</v>
+        <v>0.005327142323651453</v>
       </c>
       <c r="H61">
-        <v>0.005638539031062064</v>
+        <v>0.005566036929460581</v>
       </c>
       <c r="I61">
-        <v>-0.02797899878978982</v>
+        <v>-0.06110539419087146</v>
       </c>
       <c r="J61">
-        <v>0.8002333467801142</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K61">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="L61">
         <v>3.69</v>
       </c>
       <c r="M61">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N61">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O61">
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:16">
       <c r="A62" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B62" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C62">
-        <v>1.858458903856472</v>
+        <v>2.04544979253112</v>
       </c>
       <c r="D62" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E62">
-        <v>1.559424034625328</v>
+        <v>2.113963070539419</v>
       </c>
       <c r="F62">
         <v>-1</v>
       </c>
       <c r="G62">
-        <v>0.004661541096143528</v>
+        <v>0.005334550207468879</v>
       </c>
       <c r="H62">
-        <v>0.004260575965374673</v>
+        <v>0.005566036929460581</v>
       </c>
       <c r="I62">
-        <v>0.2990348692311444</v>
+        <v>-0.06851327800829887</v>
       </c>
       <c r="J62">
-        <v>0.8494188461475927</v>
+        <v>0.7407883817427386</v>
       </c>
       <c r="K62">
-        <v>1.65</v>
+        <v>2.22</v>
       </c>
       <c r="L62">
-        <v>3.26</v>
+        <v>3.69</v>
       </c>
       <c r="M62">
-        <v>1.59</v>
+        <v>2.33</v>
       </c>
       <c r="N62">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="O62">
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:16">
       <c r="A63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C63">
-        <v>1.886452884631018</v>
+        <v>1.939614977812812</v>
       </c>
       <c r="D63" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E63">
-        <v>1.827842465399061</v>
+        <v>1.637628978619619</v>
       </c>
       <c r="F63">
         <v>-1</v>
       </c>
       <c r="G63">
-        <v>0.006133547115368982</v>
+        <v>0.004580385022187188</v>
       </c>
       <c r="H63">
-        <v>0.005752157534600939</v>
+        <v>0.004182371021380382</v>
       </c>
       <c r="I63">
-        <v>0.05861041923195698</v>
+        <v>0.301985999193193</v>
       </c>
       <c r="J63">
-        <v>0.8494188461475927</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K63">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="L63">
-        <v>4.01</v>
+        <v>3.26</v>
       </c>
       <c r="M63">
-        <v>2.31</v>
+        <v>1.59</v>
       </c>
       <c r="N63">
-        <v>3.79</v>
+        <v>2.91</v>
       </c>
       <c r="O63">
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B64" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C64">
-        <v>1.873865711553157</v>
+        <v>2.009416633049714</v>
       </c>
       <c r="D64" t="s">
         <v>49</v>
       </c>
       <c r="E64">
-        <v>1.827842465399061</v>
+        <v>1.975456302002334</v>
       </c>
       <c r="F64">
         <v>-1</v>
       </c>
       <c r="G64">
-        <v>0.005866134288446843</v>
+        <v>0.006010583366950286</v>
       </c>
       <c r="H64">
-        <v>0.005752157534600939</v>
+        <v>0.005704543697997666</v>
       </c>
       <c r="I64">
-        <v>0.04602324615409614</v>
+        <v>0.03396033104738039</v>
       </c>
       <c r="J64">
-        <v>0.8494188461475927</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K64">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L64">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M64">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N64">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O64">
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B65" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C65">
-        <v>1.81278435001382</v>
+        <v>1.989451635066732</v>
       </c>
       <c r="D65" t="s">
         <v>49</v>
       </c>
       <c r="E65">
-        <v>1.827842465399061</v>
+        <v>1.975456302002334</v>
       </c>
       <c r="F65">
         <v>-1</v>
       </c>
       <c r="G65">
-        <v>0.00556721564998618</v>
+        <v>0.005750548364933269</v>
       </c>
       <c r="H65">
-        <v>0.005752157534600939</v>
+        <v>0.005704543697997666</v>
       </c>
       <c r="I65">
-        <v>-0.01505811538524093</v>
+        <v>0.01399533306439782</v>
       </c>
       <c r="J65">
-        <v>0.8494188461475927</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K65">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="L65">
-        <v>3.69</v>
+        <v>3.87</v>
       </c>
       <c r="M65">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N65">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O65">
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B66" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C66">
-        <v>1.804290161552344</v>
+        <v>1.921484303615948</v>
       </c>
       <c r="D66" t="s">
         <v>49</v>
       </c>
       <c r="E66">
-        <v>1.827842465399061</v>
+        <v>1.975456302002334</v>
       </c>
       <c r="F66">
         <v>-1</v>
       </c>
       <c r="G66">
-        <v>0.005575709838447656</v>
+        <v>0.005458515696384052</v>
       </c>
       <c r="H66">
-        <v>0.005752157534600939</v>
+        <v>0.005704543697997666</v>
       </c>
       <c r="I66">
-        <v>-0.02355230384671692</v>
+        <v>-0.05397199838638622</v>
       </c>
       <c r="J66">
-        <v>0.8494188461475927</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K66">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="L66">
         <v>3.69</v>
       </c>
       <c r="M66">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N66">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O66">
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:16">
       <c r="A67" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C67">
-        <v>1.778043160662217</v>
+        <v>1.913481970148146</v>
       </c>
       <c r="D67" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E67">
-        <v>1.4819325002745</v>
+        <v>1.975456302002334</v>
       </c>
       <c r="F67">
         <v>-1</v>
       </c>
       <c r="G67">
-        <v>0.004741956839337784</v>
+        <v>0.005466518029851854</v>
       </c>
       <c r="H67">
-        <v>0.004338067499725501</v>
+        <v>0.005704543697997666</v>
       </c>
       <c r="I67">
-        <v>0.2961106603877166</v>
+        <v>-0.06197433185418744</v>
       </c>
       <c r="J67">
-        <v>0.898155660204717</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K67">
-        <v>1.65</v>
+        <v>2.22</v>
       </c>
       <c r="L67">
-        <v>3.26</v>
+        <v>3.69</v>
       </c>
       <c r="M67">
-        <v>1.59</v>
+        <v>2.33</v>
       </c>
       <c r="N67">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="O67">
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:16">
       <c r="A68" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C68">
-        <v>1.253223538131198</v>
+        <v>1.858458903856472</v>
       </c>
       <c r="D68" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E68">
-        <v>1.508412028621273</v>
+        <v>1.559424034625328</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G68">
-        <v>0.005366776461868803</v>
+        <v>0.004661541096143528</v>
       </c>
       <c r="H68">
-        <v>0.004831587971378727</v>
+        <v>0.004260575965374673</v>
       </c>
       <c r="I68">
-        <v>0.2551884904900752</v>
+        <v>0.2990348692311444</v>
       </c>
       <c r="J68">
-        <v>0.898155660204717</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K68">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="L68">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="M68">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="N68">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="O68">
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C69">
-        <v>1.764610849488207</v>
+        <v>1.886452884631018</v>
       </c>
       <c r="D69" t="s">
         <v>49</v>
       </c>
       <c r="E69">
-        <v>1.715260424927104</v>
+        <v>1.860854088476109</v>
       </c>
       <c r="F69">
         <v>-1</v>
       </c>
       <c r="G69">
-        <v>0.006255389150511792</v>
+        <v>0.006133547115368982</v>
       </c>
       <c r="H69">
-        <v>0.005864739575072896</v>
+        <v>0.005819145911523891</v>
       </c>
       <c r="I69">
-        <v>0.04935042456110361</v>
+        <v>0.02559879615490912</v>
       </c>
       <c r="J69">
-        <v>0.898155660204717</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K69">
         <v>2.5</v>
@@ -4232,48 +4223,48 @@
         <v>4.01</v>
       </c>
       <c r="M69">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N69">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O69">
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B70" t="s">
         <v>29</v>
       </c>
       <c r="C70">
-        <v>1.759334198518915</v>
+        <v>1.873865711553157</v>
       </c>
       <c r="D70" t="s">
         <v>49</v>
       </c>
       <c r="E70">
-        <v>1.715260424927104</v>
+        <v>1.860854088476109</v>
       </c>
       <c r="F70">
         <v>-1</v>
       </c>
       <c r="G70">
-        <v>0.005980665801481085</v>
+        <v>0.005866134288446843</v>
       </c>
       <c r="H70">
-        <v>0.005864739575072896</v>
+        <v>0.005819145911523891</v>
       </c>
       <c r="I70">
-        <v>0.04407377359181153</v>
+        <v>0.01301162307704828</v>
       </c>
       <c r="J70">
-        <v>0.898155660204717</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K70">
         <v>2.35</v>
@@ -4282,48 +4273,48 @@
         <v>3.87</v>
       </c>
       <c r="M70">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N70">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O70">
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B71" t="s">
         <v>27</v>
       </c>
       <c r="C71">
-        <v>1.705075990947575</v>
+        <v>1.81278435001382</v>
       </c>
       <c r="D71" t="s">
         <v>49</v>
       </c>
       <c r="E71">
-        <v>1.715260424927104</v>
+        <v>1.860854088476109</v>
       </c>
       <c r="F71">
         <v>-1</v>
       </c>
       <c r="G71">
-        <v>0.005674924009052424</v>
+        <v>0.00556721564998618</v>
       </c>
       <c r="H71">
-        <v>0.005864739575072896</v>
+        <v>0.005819145911523891</v>
       </c>
       <c r="I71">
-        <v>-0.01018443397952828</v>
+        <v>-0.04806973846228879</v>
       </c>
       <c r="J71">
-        <v>0.898155660204717</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K71">
         <v>2.21</v>
@@ -4332,498 +4323,498 @@
         <v>3.69</v>
       </c>
       <c r="M71">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N71">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O71">
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C72">
-        <v>1.698438247560837</v>
+        <v>1.827842465399061</v>
       </c>
       <c r="D72" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E72">
-        <v>1.372006375010957</v>
+        <v>1.860854088476109</v>
       </c>
       <c r="F72">
         <v>-1</v>
       </c>
       <c r="G72">
-        <v>0.004821561752439162</v>
+        <v>0.005752157534600939</v>
       </c>
       <c r="H72">
-        <v>0.004267993624989043</v>
+        <v>0.005819145911523891</v>
       </c>
       <c r="I72">
-        <v>0.3264318725498792</v>
+        <v>-0.03301162307704786</v>
       </c>
       <c r="J72">
-        <v>0.9464010620843414</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K72">
-        <v>1.65</v>
+        <v>2.31</v>
       </c>
       <c r="L72">
-        <v>3.26</v>
+        <v>3.79</v>
       </c>
       <c r="M72">
-        <v>1.53</v>
+        <v>2.33</v>
       </c>
       <c r="N72">
-        <v>2.82</v>
+        <v>3.84</v>
       </c>
       <c r="O72">
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C73">
-        <v>1.142741567826858</v>
+        <v>1.778043160662217</v>
       </c>
       <c r="D73" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E73">
-        <v>1.419158035143968</v>
+        <v>1.4819325002745</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G73">
-        <v>0.005477258432173141</v>
+        <v>0.004741956839337784</v>
       </c>
       <c r="H73">
-        <v>0.004920841964856031</v>
+        <v>0.004338067499725501</v>
       </c>
       <c r="I73">
-        <v>0.2764164673171099</v>
+        <v>0.2961106603877166</v>
       </c>
       <c r="J73">
-        <v>0.9464010620843414</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K73">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="L73">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="M73">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="N73">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="O73">
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74" spans="1:16">
       <c r="A74" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B74" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C74">
-        <v>1.643997344789146</v>
+        <v>1.253223538131198</v>
       </c>
       <c r="D74" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E74">
-        <v>1.603813546585172</v>
+        <v>1.508412028621273</v>
       </c>
       <c r="F74">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G74">
-        <v>0.006376002655210854</v>
+        <v>0.005366776461868803</v>
       </c>
       <c r="H74">
-        <v>0.005976186453414829</v>
+        <v>0.004831587971378727</v>
       </c>
       <c r="I74">
-        <v>0.04018379820397477</v>
+        <v>0.2551884904900752</v>
       </c>
       <c r="J74">
-        <v>0.9464010620843414</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K74">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="L74">
-        <v>4.01</v>
+        <v>3.31</v>
       </c>
       <c r="M74">
-        <v>2.31</v>
+        <v>1.85</v>
       </c>
       <c r="N74">
-        <v>3.79</v>
+        <v>3.17</v>
       </c>
       <c r="O74">
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B75" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C75">
-        <v>1.645957504101798</v>
+        <v>1.764610849488207</v>
       </c>
       <c r="D75" t="s">
         <v>49</v>
       </c>
       <c r="E75">
-        <v>1.603813546585172</v>
+        <v>1.747297311723009</v>
       </c>
       <c r="F75">
         <v>-1</v>
       </c>
       <c r="G75">
-        <v>0.006094042495898203</v>
+        <v>0.006255389150511792</v>
       </c>
       <c r="H75">
-        <v>0.005976186453414829</v>
+        <v>0.00593270268827699</v>
       </c>
       <c r="I75">
-        <v>0.04214395751662625</v>
+        <v>0.01731353776519784</v>
       </c>
       <c r="J75">
-        <v>0.9464010620843414</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K75">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L75">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M75">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N75">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O75">
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C76">
-        <v>1.613410205419267</v>
+        <v>1.759334198518915</v>
       </c>
       <c r="D76" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E76">
-        <v>1.623410205419267</v>
+        <v>1.747297311723009</v>
       </c>
       <c r="F76">
         <v>-1</v>
       </c>
       <c r="G76">
-        <v>0.004906589794580732</v>
+        <v>0.005980665801481085</v>
       </c>
       <c r="H76">
-        <v>0.004916589794580733</v>
+        <v>0.00593270268827699</v>
       </c>
       <c r="I76">
-        <v>-0.01000000000000023</v>
+        <v>0.01203688679590575</v>
       </c>
       <c r="J76">
-        <v>0.9979332088368078</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K76">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="L76">
-        <v>3.26</v>
+        <v>3.87</v>
       </c>
       <c r="M76">
-        <v>1.65</v>
+        <v>2.33</v>
       </c>
       <c r="N76">
-        <v>3.27</v>
+        <v>3.84</v>
       </c>
       <c r="O76">
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B77" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C77">
-        <v>1.02473295176371</v>
+        <v>1.715260424927104</v>
       </c>
       <c r="D77" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E77">
-        <v>1.323823563651905</v>
+        <v>1.747297311723009</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G77">
-        <v>0.005595267048236289</v>
+        <v>0.005864739575072896</v>
       </c>
       <c r="H77">
-        <v>0.005016176436348095</v>
+        <v>0.00593270268827699</v>
       </c>
       <c r="I77">
-        <v>0.2990906118881951</v>
+        <v>-0.03203688679590577</v>
       </c>
       <c r="J77">
-        <v>0.9979332088368078</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K77">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="L77">
-        <v>3.31</v>
+        <v>3.79</v>
       </c>
       <c r="M77">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="N77">
-        <v>3.17</v>
+        <v>3.84</v>
       </c>
       <c r="O77">
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C78">
-        <v>1.51516697790798</v>
+        <v>1.698438247560837</v>
       </c>
       <c r="D78" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E78">
-        <v>1.484774287586974</v>
+        <v>1.372006375010957</v>
       </c>
       <c r="F78">
         <v>-1</v>
       </c>
       <c r="G78">
-        <v>0.00650483302209202</v>
+        <v>0.004821561752439162</v>
       </c>
       <c r="H78">
-        <v>0.006095225712413025</v>
+        <v>0.004267993624989043</v>
       </c>
       <c r="I78">
-        <v>0.03039269032100611</v>
+        <v>0.3264318725498792</v>
       </c>
       <c r="J78">
-        <v>0.9979332088368078</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K78">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="L78">
-        <v>4.01</v>
+        <v>3.26</v>
       </c>
       <c r="M78">
-        <v>2.31</v>
+        <v>1.53</v>
       </c>
       <c r="N78">
-        <v>3.79</v>
+        <v>2.82</v>
       </c>
       <c r="O78">
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="79" spans="1:16">
       <c r="A79" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B79" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C79">
-        <v>1.524856959233502</v>
+        <v>1.142741567826858</v>
       </c>
       <c r="D79" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E79">
-        <v>1.484774287586974</v>
+        <v>1.419158035143968</v>
       </c>
       <c r="F79">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G79">
-        <v>0.006215143040766499</v>
+        <v>0.005477258432173141</v>
       </c>
       <c r="H79">
-        <v>0.006095225712413025</v>
+        <v>0.004920841964856031</v>
       </c>
       <c r="I79">
-        <v>0.04008267164652768</v>
+        <v>0.2764164673171099</v>
       </c>
       <c r="J79">
-        <v>0.9979332088368078</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K79">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="L79">
-        <v>3.87</v>
+        <v>3.31</v>
       </c>
       <c r="M79">
-        <v>2.31</v>
+        <v>1.85</v>
       </c>
       <c r="N79">
-        <v>3.79</v>
+        <v>3.17</v>
       </c>
       <c r="O79">
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B80" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C80">
-        <v>1.025578495611604</v>
+        <v>1.643997344789146</v>
       </c>
       <c r="D80" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E80">
-        <v>1.267956426585794</v>
+        <v>1.634885525343484</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G80">
-        <v>0.005734421504388396</v>
+        <v>0.006376002655210854</v>
       </c>
       <c r="H80">
-        <v>0.005072043573414206</v>
+        <v>0.006045114474656515</v>
       </c>
       <c r="I80">
-        <v>0.2423779309741898</v>
+        <v>0.009111819445661862</v>
       </c>
       <c r="J80">
-        <v>1.028131661304976</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K80">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="L80">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="M80">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="N80">
-        <v>3.17</v>
+        <v>3.84</v>
       </c>
       <c r="O80">
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="81" spans="1:16">
       <c r="A81" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B81" t="s">
         <v>29</v>
       </c>
       <c r="C81">
-        <v>1.453890595933306</v>
+        <v>1.645957504101798</v>
       </c>
       <c r="D81" t="s">
         <v>49</v>
       </c>
       <c r="E81">
-        <v>1.415015862385505</v>
+        <v>1.634885525343484</v>
       </c>
       <c r="F81">
         <v>-1</v>
       </c>
       <c r="G81">
-        <v>0.006286109404066695</v>
+        <v>0.006094042495898203</v>
       </c>
       <c r="H81">
-        <v>0.006164984137614495</v>
+        <v>0.006045114474656515</v>
       </c>
       <c r="I81">
-        <v>0.03887473354780102</v>
+        <v>0.01107197875831334</v>
       </c>
       <c r="J81">
-        <v>1.028131661304976</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K81">
         <v>2.35</v>
@@ -4832,16 +4823,16 @@
         <v>3.87</v>
       </c>
       <c r="M81">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N81">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O81">
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -4849,87 +4840,87 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C82">
-        <v>0.95505474527386</v>
+        <v>1.613410205419267</v>
       </c>
       <c r="D82" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="E82">
-        <v>1.210983091160105</v>
+        <v>1.623410205419267</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G82">
-        <v>0.00580494525472614</v>
+        <v>0.004906589794580732</v>
       </c>
       <c r="H82">
-        <v>0.005129016908839895</v>
+        <v>0.004916589794580733</v>
       </c>
       <c r="I82">
-        <v>0.2559283458862451</v>
+        <v>-0.01000000000000023</v>
       </c>
       <c r="J82">
-        <v>1.058928058832376</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K82">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="L82">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="M82">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="N82">
-        <v>3.17</v>
+        <v>3.27</v>
       </c>
       <c r="O82">
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B83" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C83">
-        <v>0.8997461387005035</v>
+        <v>1.02473295176371</v>
       </c>
       <c r="D83" t="s">
         <v>52</v>
       </c>
       <c r="E83">
-        <v>1.166301465762415</v>
+        <v>1.323823563651905</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83">
-        <v>0.005860253861299496</v>
+        <v>0.005595267048236289</v>
       </c>
       <c r="H83">
-        <v>0.005173698534237585</v>
+        <v>0.005016176436348095</v>
       </c>
       <c r="I83">
-        <v>0.2665553270619117</v>
+        <v>0.2990906118881951</v>
       </c>
       <c r="J83">
-        <v>1.083080288777073</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K83">
         <v>2.29</v>
       </c>
       <c r="L83">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="M83">
         <v>1.85</v>
@@ -4941,107 +4932,107 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B84" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C84">
-        <v>0.9004291893178089</v>
+        <v>1.51516697790798</v>
       </c>
       <c r="D84" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E84">
-        <v>1.166853275213077</v>
+        <v>1.514815623410238</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G84">
-        <v>0.005859570810682191</v>
+        <v>0.00650483302209202</v>
       </c>
       <c r="H84">
-        <v>0.005173146724786923</v>
+        <v>0.006165184376589762</v>
       </c>
       <c r="I84">
-        <v>0.2664240858952684</v>
+        <v>0.0003513544977424843</v>
       </c>
       <c r="J84">
-        <v>1.082782013398337</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K84">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="L84">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="M84">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="N84">
-        <v>3.17</v>
+        <v>3.84</v>
       </c>
       <c r="O84">
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="85" spans="1:16">
       <c r="A85" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B85" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C85">
-        <v>0.8995341152947529</v>
+        <v>1.524856959233502</v>
       </c>
       <c r="D85" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E85">
-        <v>1.166130180478294</v>
+        <v>1.514815623410238</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G85">
-        <v>0.005860465884705247</v>
+        <v>0.006215143040766499</v>
       </c>
       <c r="H85">
-        <v>0.005173869819521706</v>
+        <v>0.006165184376589762</v>
       </c>
       <c r="I85">
-        <v>0.2665960651835411</v>
+        <v>0.01004133582326405</v>
       </c>
       <c r="J85">
-        <v>1.083172875417138</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K85">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="L85">
-        <v>3.38</v>
+        <v>3.87</v>
       </c>
       <c r="M85">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="N85">
-        <v>3.17</v>
+        <v>3.84</v>
       </c>
       <c r="O85">
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5049,81 +5040,81 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C86">
-        <v>0.8942975364165378</v>
+        <v>1.563582758846789</v>
       </c>
       <c r="D86" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="E86">
-        <v>1.161899756493709</v>
+        <v>1.573582758846789</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G86">
-        <v>0.005865702463583462</v>
+        <v>0.004956417241153211</v>
       </c>
       <c r="H86">
-        <v>0.00517810024350629</v>
+        <v>0.004966417241153211</v>
       </c>
       <c r="I86">
-        <v>0.2676022200771717</v>
+        <v>-0.01000000000000023</v>
       </c>
       <c r="J86">
-        <v>1.085459591084481</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K86">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="L86">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="M86">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="N86">
-        <v>3.17</v>
+        <v>3.27</v>
       </c>
       <c r="O86">
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C87">
-        <v>0.823882990348408</v>
+        <v>1.025578495611604</v>
       </c>
       <c r="D87" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E87">
-        <v>1.068500891892621</v>
+        <v>1.267956426585794</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87">
-        <v>0.005936117009651592</v>
+        <v>0.005734421504388396</v>
       </c>
       <c r="H87">
-        <v>0.005131499108107379</v>
+        <v>0.005072043573414206</v>
       </c>
       <c r="I87">
-        <v>0.2446179015442134</v>
+        <v>0.2423779309741898</v>
       </c>
       <c r="J87">
-        <v>1.1162083011579</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K87">
         <v>2.29</v>
@@ -5132,16 +5123,16 @@
         <v>3.38</v>
       </c>
       <c r="M87">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="N87">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="O87">
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5149,31 +5140,31 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C88">
-        <v>0.7552208383877499</v>
+        <v>0.95505474527386</v>
       </c>
       <c r="D88" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E88">
-        <v>1.013930971993758</v>
+        <v>1.210983091160105</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88">
-        <v>0.00600477916161225</v>
+        <v>0.00580494525472614</v>
       </c>
       <c r="H88">
-        <v>0.005186069028006243</v>
+        <v>0.005129016908839895</v>
       </c>
       <c r="I88">
-        <v>0.2587101336060078</v>
+        <v>0.2559283458862451</v>
       </c>
       <c r="J88">
-        <v>1.146191773629804</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K88">
         <v>2.29</v>
@@ -5182,16 +5173,16 @@
         <v>3.38</v>
       </c>
       <c r="M88">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="N88">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="O88">
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5199,31 +5190,31 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C89">
-        <v>0.7164672131147527</v>
+        <v>0.8997461387005035</v>
       </c>
       <c r="D89" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="E89">
-        <v>0.6464672131147529</v>
+        <v>1.166301465762415</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89">
-        <v>0.006043532786885248</v>
+        <v>0.005860253861299496</v>
       </c>
       <c r="H89">
-        <v>0.005973532786885247</v>
+        <v>0.005173698534237585</v>
       </c>
       <c r="I89">
-        <v>-0.06999999999999984</v>
+        <v>0.2665553270619117</v>
       </c>
       <c r="J89">
-        <v>1.163114754098361</v>
+        <v>1.083080288777073</v>
       </c>
       <c r="K89">
         <v>2.29</v>
@@ -5232,16 +5223,16 @@
         <v>3.38</v>
       </c>
       <c r="M89">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="N89">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="O89">
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5249,31 +5240,31 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C90">
-        <v>0.6498239504652852</v>
+        <v>0.9004291893178089</v>
       </c>
       <c r="D90" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="E90">
-        <v>0.5798239504652853</v>
+        <v>1.166853275213077</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90">
-        <v>0.006110176049534715</v>
+        <v>0.005859570810682191</v>
       </c>
       <c r="H90">
-        <v>0.006040176049534715</v>
+        <v>0.005173146724786923</v>
       </c>
       <c r="I90">
-        <v>-0.06999999999999984</v>
+        <v>0.2664240858952684</v>
       </c>
       <c r="J90">
-        <v>1.192216615517343</v>
+        <v>1.082782013398337</v>
       </c>
       <c r="K90">
         <v>2.29</v>
@@ -5282,16 +5273,16 @@
         <v>3.38</v>
       </c>
       <c r="M90">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="N90">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="O90">
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5299,81 +5290,81 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C91">
-        <v>0.5205928926738919</v>
+        <v>0.8995341152947529</v>
       </c>
       <c r="D91" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="E91">
-        <v>0.4040417624885522</v>
+        <v>1.166130180478294</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="G91">
-        <v>0.006459407107326108</v>
+        <v>0.005860465884705247</v>
       </c>
       <c r="H91">
-        <v>0.006215958237511448</v>
+        <v>0.005173869819521706</v>
       </c>
       <c r="I91">
-        <v>-0.1165511301853397</v>
+        <v>0.2665960651835411</v>
       </c>
       <c r="J91">
-        <v>1.268977396293209</v>
+        <v>1.083172875417138</v>
       </c>
       <c r="K91">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="L91">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="M91">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="N91">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="O91">
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C92">
-        <v>0.474041762488552</v>
+        <v>0.8942975364165378</v>
       </c>
       <c r="D92" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="E92">
-        <v>0.4040417624885522</v>
+        <v>1.161899756493709</v>
       </c>
       <c r="F92">
         <v>1</v>
       </c>
       <c r="G92">
-        <v>0.006285958237511447</v>
+        <v>0.005865702463583462</v>
       </c>
       <c r="H92">
-        <v>0.006215958237511448</v>
+        <v>0.00517810024350629</v>
       </c>
       <c r="I92">
-        <v>-0.06999999999999984</v>
+        <v>0.2676022200771717</v>
       </c>
       <c r="J92">
-        <v>1.268977396293209</v>
+        <v>1.085459591084481</v>
       </c>
       <c r="K92">
         <v>2.29</v>
@@ -5382,16 +5373,16 @@
         <v>3.38</v>
       </c>
       <c r="M92">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="N92">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="O92">
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5399,81 +5390,81 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C93">
-        <v>0.3774746016246668</v>
+        <v>0.823882990348408</v>
       </c>
       <c r="D93" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="E93">
-        <v>0.2639815545814042</v>
+        <v>1.105014642857884</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93">
-        <v>0.006602525398375333</v>
+        <v>0.005936117009651592</v>
       </c>
       <c r="H93">
-        <v>0.006356018445418596</v>
+        <v>0.005234985357142116</v>
       </c>
       <c r="I93">
-        <v>-0.1134930470432627</v>
+        <v>0.281131652509476</v>
       </c>
       <c r="J93">
-        <v>1.330139059134758</v>
+        <v>1.1162083011579</v>
       </c>
       <c r="K93">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="L93">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="M93">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="N93">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="O93">
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>31</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94" spans="1:16">
       <c r="A94" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C94">
-        <v>0.333981554581404</v>
+        <v>0.7552208383877499</v>
       </c>
       <c r="D94" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E94">
-        <v>0.2639815545814042</v>
+        <v>1.013930971993758</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94">
-        <v>0.006426018445418596</v>
+        <v>0.00600477916161225</v>
       </c>
       <c r="H94">
-        <v>0.006356018445418596</v>
+        <v>0.005186069028006243</v>
       </c>
       <c r="I94">
-        <v>-0.06999999999999984</v>
+        <v>0.2587101336060078</v>
       </c>
       <c r="J94">
-        <v>1.330139059134758</v>
+        <v>1.146191773629804</v>
       </c>
       <c r="K94">
         <v>2.29</v>
@@ -5482,66 +5473,66 @@
         <v>3.38</v>
       </c>
       <c r="M94">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="N94">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="O94">
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:16">
       <c r="A95" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C95">
-        <v>0.4202010228602702</v>
+        <v>0.7164672131147527</v>
       </c>
       <c r="D95" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E95">
-        <v>0.6791469123747405</v>
+        <v>0.6464672131147529</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
       <c r="G95">
-        <v>0.00613979897713973</v>
+        <v>0.006043532786885248</v>
       </c>
       <c r="H95">
-        <v>0.00552085308762526</v>
+        <v>0.005973532786885247</v>
       </c>
       <c r="I95">
-        <v>0.2589458895144703</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J95">
-        <v>1.330139059134758</v>
+        <v>1.163114754098361</v>
       </c>
       <c r="K95">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="L95">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="M95">
-        <v>1.82</v>
+        <v>2.29</v>
       </c>
       <c r="N95">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="O95">
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5549,31 +5540,31 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C96">
-        <v>0.2442505289553791</v>
+        <v>0.7002131196894186</v>
       </c>
       <c r="D96" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E96">
-        <v>0.1336041501315459</v>
+        <v>0.5798239504652853</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
       <c r="G96">
-        <v>0.006735749471044622</v>
+        <v>0.006279786880310581</v>
       </c>
       <c r="H96">
-        <v>0.006486395849868455</v>
+        <v>0.006040176049534715</v>
       </c>
       <c r="I96">
-        <v>-0.1106463788238332</v>
+        <v>-0.1203891692241332</v>
       </c>
       <c r="J96">
-        <v>1.387072423523342</v>
+        <v>1.192216615517343</v>
       </c>
       <c r="K96">
         <v>2.34</v>
@@ -5591,207 +5582,207 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
     </row>
     <row r="97" spans="1:16">
       <c r="A97" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B97" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C97">
-        <v>2.01907486979781</v>
+        <v>0.6498239504652852</v>
       </c>
       <c r="D97" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E97">
-        <v>1.950385179693176</v>
+        <v>0.5798239504652853</v>
       </c>
       <c r="F97">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G97">
-        <v>0.00600092513020219</v>
+        <v>0.006110176049534715</v>
       </c>
       <c r="H97">
-        <v>0.005629614820306824</v>
+        <v>0.006040176049534715</v>
       </c>
       <c r="I97">
-        <v>0.06868969010463344</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J97">
-        <v>0.7963700520808761</v>
+        <v>1.192216615517343</v>
       </c>
       <c r="K97">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="L97">
-        <v>4.01</v>
+        <v>3.38</v>
       </c>
       <c r="M97">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="N97">
-        <v>3.79</v>
+        <v>3.31</v>
       </c>
       <c r="O97">
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
     </row>
     <row r="98" spans="1:16">
       <c r="A98" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C98">
-        <v>1.998530377609941</v>
+        <v>0.5205928926738919</v>
       </c>
       <c r="D98" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E98">
-        <v>1.950385179693176</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F98">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G98">
-        <v>0.005741469622390059</v>
+        <v>0.006459407107326108</v>
       </c>
       <c r="H98">
-        <v>0.005629614820306824</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I98">
-        <v>0.04814519791676508</v>
+        <v>-0.1165511301853397</v>
       </c>
       <c r="J98">
-        <v>0.7963700520808761</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K98">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="L98">
-        <v>3.87</v>
+        <v>3.49</v>
       </c>
       <c r="M98">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="N98">
-        <v>3.79</v>
+        <v>3.31</v>
       </c>
       <c r="O98">
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B99" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C99">
-        <v>2.009451144824672</v>
+        <v>0.474041762488552</v>
       </c>
       <c r="D99" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E99">
-        <v>1.941492857817997</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F99">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G99">
-        <v>0.006010548855175328</v>
+        <v>0.006285958237511447</v>
       </c>
       <c r="H99">
-        <v>0.005638507142182003</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I99">
-        <v>0.06795828700667506</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J99">
-        <v>0.8002195420701311</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K99">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="L99">
-        <v>4.01</v>
+        <v>3.38</v>
       </c>
       <c r="M99">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="N99">
-        <v>3.79</v>
+        <v>3.31</v>
       </c>
       <c r="O99">
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="100" spans="1:16">
       <c r="A100" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C100">
-        <v>1.989484076135192</v>
+        <v>0.3774746016246668</v>
       </c>
       <c r="D100" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E100">
-        <v>1.941492857817997</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F100">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G100">
-        <v>0.005750515923864809</v>
+        <v>0.006602525398375333</v>
       </c>
       <c r="H100">
-        <v>0.005638507142182003</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I100">
-        <v>0.04799121831719488</v>
+        <v>-0.1134930470432627</v>
       </c>
       <c r="J100">
-        <v>0.8002195420701311</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K100">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="L100">
-        <v>3.87</v>
+        <v>3.49</v>
       </c>
       <c r="M100">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="N100">
-        <v>3.79</v>
+        <v>3.31</v>
       </c>
       <c r="O100">
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -5799,3199 +5790,3199 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C101">
-        <v>1.996409318396163</v>
+        <v>0.2442505289553791</v>
       </c>
       <c r="D101" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E101">
-        <v>1.929442210198055</v>
+        <v>0.1336041501315459</v>
       </c>
       <c r="F101">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G101">
-        <v>0.006023590681603837</v>
+        <v>0.006735749471044622</v>
       </c>
       <c r="H101">
-        <v>0.005650557789801946</v>
+        <v>0.006486395849868455</v>
       </c>
       <c r="I101">
-        <v>0.06696710819810803</v>
+        <v>-0.1106463788238332</v>
       </c>
       <c r="J101">
-        <v>0.8054362726415348</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K101">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="L101">
-        <v>4.01</v>
+        <v>3.49</v>
       </c>
       <c r="M101">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="N101">
-        <v>3.79</v>
+        <v>3.31</v>
       </c>
       <c r="O101">
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="102" spans="1:16">
       <c r="A102" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C102">
-        <v>1.977224759292393</v>
+        <v>2.01907486979781</v>
       </c>
       <c r="D102" t="s">
         <v>49</v>
       </c>
       <c r="E102">
-        <v>1.929442210198055</v>
+        <v>1.984457778651558</v>
       </c>
       <c r="F102">
         <v>-1</v>
       </c>
       <c r="G102">
-        <v>0.005762775240707607</v>
+        <v>0.00600092513020219</v>
       </c>
       <c r="H102">
-        <v>0.005650557789801946</v>
+        <v>0.005695542221348442</v>
       </c>
       <c r="I102">
-        <v>0.04778254909433866</v>
+        <v>0.03461709114625111</v>
       </c>
       <c r="J102">
-        <v>0.8054362726415348</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K102">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L102">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M102">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N102">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O102">
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="103" spans="1:16">
       <c r="A103" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B103" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C103">
-        <v>1.981381467084703</v>
+        <v>1.998530377609941</v>
       </c>
       <c r="D103" t="s">
         <v>49</v>
       </c>
       <c r="E103">
-        <v>1.915556475586266</v>
+        <v>1.984457778651558</v>
       </c>
       <c r="F103">
         <v>-1</v>
       </c>
       <c r="G103">
-        <v>0.006038618532915297</v>
+        <v>0.005741469622390059</v>
       </c>
       <c r="H103">
-        <v>0.005664443524413735</v>
+        <v>0.005695542221348442</v>
       </c>
       <c r="I103">
-        <v>0.06582499149843701</v>
+        <v>0.01407259895838275</v>
       </c>
       <c r="J103">
-        <v>0.8114474131661186</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K103">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L103">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M103">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N103">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O103">
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="104" spans="1:16">
       <c r="A104" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C104">
-        <v>1.963098579059621</v>
+        <v>2.009451144824672</v>
       </c>
       <c r="D104" t="s">
         <v>49</v>
       </c>
       <c r="E104">
-        <v>1.915556475586266</v>
+        <v>1.975488466976594</v>
       </c>
       <c r="F104">
         <v>-1</v>
       </c>
       <c r="G104">
-        <v>0.005776901420940379</v>
+        <v>0.006010548855175328</v>
       </c>
       <c r="H104">
-        <v>0.005664443524413735</v>
+        <v>0.005704511533023406</v>
       </c>
       <c r="I104">
-        <v>0.04754210347335519</v>
+        <v>0.03396267784807794</v>
       </c>
       <c r="J104">
-        <v>0.8114474131661186</v>
+        <v>0.8002195420701311</v>
       </c>
       <c r="K104">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L104">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M104">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N104">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O104">
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="105" spans="1:16">
       <c r="A105" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B105" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C105">
-        <v>1.977186894395391</v>
+        <v>1.989484076135192</v>
       </c>
       <c r="D105" t="s">
         <v>49</v>
       </c>
       <c r="E105">
-        <v>1.911680690421341</v>
+        <v>1.975488466976594</v>
       </c>
       <c r="F105">
         <v>-1</v>
       </c>
       <c r="G105">
-        <v>0.006042813105604609</v>
+        <v>0.005750515923864809</v>
       </c>
       <c r="H105">
-        <v>0.005668319309578659</v>
+        <v>0.005704511533023406</v>
       </c>
       <c r="I105">
-        <v>0.06550620397404949</v>
+        <v>0.01399560915859777</v>
       </c>
       <c r="J105">
-        <v>0.8131252422418436</v>
+        <v>0.8002195420701311</v>
       </c>
       <c r="K105">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L105">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M105">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N105">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O105">
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="106" spans="1:16">
       <c r="A106" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C106">
-        <v>1.959155680731668</v>
+        <v>1.996409318396163</v>
       </c>
       <c r="D106" t="s">
         <v>49</v>
       </c>
       <c r="E106">
-        <v>1.911680690421341</v>
+        <v>1.963333484745224</v>
       </c>
       <c r="F106">
         <v>-1</v>
       </c>
       <c r="G106">
-        <v>0.005780844319268333</v>
+        <v>0.006023590681603837</v>
       </c>
       <c r="H106">
-        <v>0.005668319309578659</v>
+        <v>0.005716666515254776</v>
       </c>
       <c r="I106">
-        <v>0.04747499031032643</v>
+        <v>0.03307583365093891</v>
       </c>
       <c r="J106">
-        <v>0.8131252422418436</v>
+        <v>0.8054362726415348</v>
       </c>
       <c r="K106">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L106">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M106">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N106">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O106">
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="107" spans="1:16">
       <c r="A107" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B107" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C107">
-        <v>1.972128109819418</v>
+        <v>1.977224759292393</v>
       </c>
       <c r="D107" t="s">
         <v>49</v>
       </c>
       <c r="E107">
-        <v>1.907006373473143</v>
+        <v>1.963333484745224</v>
       </c>
       <c r="F107">
         <v>-1</v>
       </c>
       <c r="G107">
-        <v>0.006047871890180582</v>
+        <v>0.005762775240707607</v>
       </c>
       <c r="H107">
-        <v>0.005672993626526857</v>
+        <v>0.005716666515254776</v>
       </c>
       <c r="I107">
-        <v>0.06512173634627527</v>
+        <v>0.01389127454716954</v>
       </c>
       <c r="J107">
-        <v>0.8151487560722326</v>
+        <v>0.8054362726415348</v>
       </c>
       <c r="K107">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L107">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M107">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N107">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O107">
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="108" spans="1:16">
       <c r="A108" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C108">
-        <v>1.954400423230253</v>
+        <v>1.981381467084703</v>
       </c>
       <c r="D108" t="s">
         <v>49</v>
       </c>
       <c r="E108">
-        <v>1.907006373473143</v>
+        <v>1.949327527322944</v>
       </c>
       <c r="F108">
         <v>-1</v>
       </c>
       <c r="G108">
-        <v>0.005785599576769747</v>
+        <v>0.006038618532915297</v>
       </c>
       <c r="H108">
-        <v>0.005672993626526857</v>
+        <v>0.005730672472677056</v>
       </c>
       <c r="I108">
-        <v>0.04739404975711059</v>
+        <v>0.03205393976175963</v>
       </c>
       <c r="J108">
-        <v>0.8151487560722326</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K108">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L108">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M108">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N108">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O108">
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109" spans="1:16">
       <c r="A109" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B109" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C109">
-        <v>1.962255996565552</v>
+        <v>1.963098579059621</v>
       </c>
       <c r="D109" t="s">
         <v>49</v>
       </c>
       <c r="E109">
-        <v>1.89788454082657</v>
+        <v>1.949327527322944</v>
       </c>
       <c r="F109">
         <v>-1</v>
       </c>
       <c r="G109">
-        <v>0.006057744003434448</v>
+        <v>0.005776901420940379</v>
       </c>
       <c r="H109">
-        <v>0.005682115459173431</v>
+        <v>0.005730672472677056</v>
       </c>
       <c r="I109">
-        <v>0.06437145573898184</v>
+        <v>0.01377105173667781</v>
       </c>
       <c r="J109">
-        <v>0.8190976013737793</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K109">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L109">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M109">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N109">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O109">
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="110" spans="1:16">
       <c r="A110" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C110">
-        <v>1.945120636771619</v>
+        <v>1.977186894395391</v>
       </c>
       <c r="D110" t="s">
         <v>49</v>
       </c>
       <c r="E110">
-        <v>1.89788454082657</v>
+        <v>1.945418185576504</v>
       </c>
       <c r="F110">
         <v>-1</v>
       </c>
       <c r="G110">
-        <v>0.005794879363228382</v>
+        <v>0.006042813105604609</v>
       </c>
       <c r="H110">
-        <v>0.005682115459173431</v>
+        <v>0.005734581814423496</v>
       </c>
       <c r="I110">
-        <v>0.04723609594504885</v>
+        <v>0.03176870881888649</v>
       </c>
       <c r="J110">
-        <v>0.8190976013737793</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K110">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L110">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M110">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N110">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O110">
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="111" spans="1:16">
       <c r="A111" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B111" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C111">
-        <v>1.966334427874344</v>
+        <v>1.959155680731668</v>
       </c>
       <c r="D111" t="s">
         <v>49</v>
       </c>
       <c r="E111">
-        <v>1.901653011355894</v>
+        <v>1.945418185576504</v>
       </c>
       <c r="F111">
         <v>-1</v>
       </c>
       <c r="G111">
-        <v>0.006053665572125656</v>
+        <v>0.005780844319268333</v>
       </c>
       <c r="H111">
-        <v>0.005678346988644107</v>
+        <v>0.005734581814423496</v>
       </c>
       <c r="I111">
-        <v>0.06468141651844972</v>
+        <v>0.01373749515516343</v>
       </c>
       <c r="J111">
-        <v>0.8174662288502623</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K111">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L111">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M111">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N111">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O111">
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="112" spans="1:16">
       <c r="A112" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C112">
-        <v>1.948954362201884</v>
+        <v>1.972128109819418</v>
       </c>
       <c r="D112" t="s">
         <v>49</v>
       </c>
       <c r="E112">
-        <v>1.901653011355894</v>
+        <v>1.940703398351698</v>
       </c>
       <c r="F112">
         <v>-1</v>
       </c>
       <c r="G112">
-        <v>0.005791045637798117</v>
+        <v>0.006047871890180582</v>
       </c>
       <c r="H112">
-        <v>0.005678346988644107</v>
+        <v>0.005739296601648302</v>
       </c>
       <c r="I112">
-        <v>0.04730135084598963</v>
+        <v>0.03142471146772019</v>
       </c>
       <c r="J112">
-        <v>0.8174662288502623</v>
+        <v>0.8151487560722326</v>
       </c>
       <c r="K112">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L112">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M112">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N112">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O112">
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="113" spans="1:16">
       <c r="A113" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B113" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C113">
-        <v>1.967381519350304</v>
+        <v>1.954400423230253</v>
       </c>
       <c r="D113" t="s">
         <v>49</v>
       </c>
       <c r="E113">
-        <v>1.902620523879681</v>
+        <v>1.940703398351698</v>
       </c>
       <c r="F113">
         <v>-1</v>
       </c>
       <c r="G113">
-        <v>0.006052618480649696</v>
+        <v>0.005785599576769747</v>
       </c>
       <c r="H113">
-        <v>0.005677379476120319</v>
+        <v>0.005739296601648302</v>
       </c>
       <c r="I113">
-        <v>0.06476099547062297</v>
+        <v>0.01369702487855551</v>
       </c>
       <c r="J113">
-        <v>0.8170473922598784</v>
+        <v>0.8151487560722326</v>
       </c>
       <c r="K113">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L113">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M113">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N113">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O113">
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="114" spans="1:16">
       <c r="A114" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C114">
-        <v>1.949938628189286</v>
+        <v>1.962255996565552</v>
       </c>
       <c r="D114" t="s">
         <v>49</v>
       </c>
       <c r="E114">
-        <v>1.902620523879681</v>
+        <v>1.931502588799094</v>
       </c>
       <c r="F114">
         <v>-1</v>
       </c>
       <c r="G114">
-        <v>0.005790061371810714</v>
+        <v>0.006057744003434448</v>
       </c>
       <c r="H114">
-        <v>0.005677379476120319</v>
+        <v>0.005748497411200906</v>
       </c>
       <c r="I114">
-        <v>0.04731810430960492</v>
+        <v>0.03075340776645774</v>
       </c>
       <c r="J114">
-        <v>0.8170473922598784</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K114">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L114">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M114">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N114">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O114">
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="115" spans="1:16">
       <c r="A115" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B115" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C115">
-        <v>1.965836780713639</v>
+        <v>1.945120636771619</v>
       </c>
       <c r="D115" t="s">
         <v>49</v>
       </c>
       <c r="E115">
-        <v>1.901193185379403</v>
+        <v>1.931502588799094</v>
       </c>
       <c r="F115">
         <v>-1</v>
       </c>
       <c r="G115">
-        <v>0.00605416321928636</v>
+        <v>0.005794879363228382</v>
       </c>
       <c r="H115">
-        <v>0.005678806814620596</v>
+        <v>0.005748497411200906</v>
       </c>
       <c r="I115">
-        <v>0.06464359533423636</v>
+        <v>0.01361804797252475</v>
       </c>
       <c r="J115">
-        <v>0.8176652877145442</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K115">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L115">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M115">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N115">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O115">
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="116" spans="1:16">
       <c r="A116" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C116">
-        <v>1.948486573870821</v>
+        <v>1.966334427874344</v>
       </c>
       <c r="D116" t="s">
         <v>49</v>
       </c>
       <c r="E116">
-        <v>1.901193185379403</v>
+        <v>1.935303686778889</v>
       </c>
       <c r="F116">
         <v>-1</v>
       </c>
       <c r="G116">
-        <v>0.00579151342612918</v>
+        <v>0.006053665572125656</v>
       </c>
       <c r="H116">
-        <v>0.005678806814620596</v>
+        <v>0.005744696313221111</v>
       </c>
       <c r="I116">
-        <v>0.04729338849141818</v>
+        <v>0.03103074109545512</v>
       </c>
       <c r="J116">
-        <v>0.8176652877145442</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K116">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L116">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M116">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N116">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O116">
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="117" spans="1:16">
       <c r="A117" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B117" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C117">
-        <v>1.964801996006813</v>
+        <v>1.948954362201884</v>
       </c>
       <c r="D117" t="s">
         <v>49</v>
       </c>
       <c r="E117">
-        <v>1.900237044310295</v>
+        <v>1.935303686778889</v>
       </c>
       <c r="F117">
         <v>-1</v>
       </c>
       <c r="G117">
-        <v>0.006055198003993187</v>
+        <v>0.005791045637798117</v>
       </c>
       <c r="H117">
-        <v>0.005679762955689705</v>
+        <v>0.005744696313221111</v>
       </c>
       <c r="I117">
-        <v>0.06456495169651766</v>
+        <v>0.01365067542299503</v>
       </c>
       <c r="J117">
-        <v>0.8180792015972748</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K117">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L117">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M117">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N117">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O117">
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="118" spans="1:16">
       <c r="A118" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C118">
-        <v>1.947513876246404</v>
+        <v>1.967381519350304</v>
       </c>
       <c r="D118" t="s">
         <v>49</v>
       </c>
       <c r="E118">
-        <v>1.900237044310295</v>
+        <v>1.936279576034483</v>
       </c>
       <c r="F118">
         <v>-1</v>
       </c>
       <c r="G118">
-        <v>0.005792486123753596</v>
+        <v>0.006052618480649696</v>
       </c>
       <c r="H118">
-        <v>0.005679762955689705</v>
+        <v>0.005743720423965517</v>
       </c>
       <c r="I118">
-        <v>0.04727683193610899</v>
+        <v>0.03110194331582061</v>
       </c>
       <c r="J118">
-        <v>0.8180792015972748</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K118">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L118">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M118">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N118">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O118">
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="119" spans="1:16">
       <c r="A119" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B119" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C119">
-        <v>1.96211546833212</v>
+        <v>1.949938628189286</v>
       </c>
       <c r="D119" t="s">
         <v>49</v>
       </c>
       <c r="E119">
-        <v>1.89775469273888</v>
+        <v>1.936279576034483</v>
       </c>
       <c r="F119">
         <v>-1</v>
       </c>
       <c r="G119">
-        <v>0.006057884531667879</v>
+        <v>0.005790061371810714</v>
       </c>
       <c r="H119">
-        <v>0.005682245307261121</v>
+        <v>0.005743720423965517</v>
       </c>
       <c r="I119">
-        <v>0.06436077559324094</v>
+        <v>0.01365905215480256</v>
       </c>
       <c r="J119">
-        <v>0.8191538126671517</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K119">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L119">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M119">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N119">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O119">
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="120" spans="1:16">
       <c r="A120" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C120">
-        <v>1.944988540232194</v>
+        <v>1.965836780713639</v>
       </c>
       <c r="D120" t="s">
         <v>49</v>
       </c>
       <c r="E120">
-        <v>1.89775469273888</v>
+        <v>1.934839879625112</v>
       </c>
       <c r="F120">
         <v>-1</v>
       </c>
       <c r="G120">
-        <v>0.005795011459767806</v>
+        <v>0.00605416321928636</v>
       </c>
       <c r="H120">
-        <v>0.005682245307261121</v>
+        <v>0.005745160120374888</v>
       </c>
       <c r="I120">
-        <v>0.04723384749331405</v>
+        <v>0.0309969010885276</v>
       </c>
       <c r="J120">
-        <v>0.8191538126671517</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K120">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L120">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M120">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N120">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O120">
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="121" spans="1:16">
       <c r="A121" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B121" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C121">
-        <v>1.969378632640371</v>
+        <v>1.948486573870821</v>
       </c>
       <c r="D121" t="s">
         <v>49</v>
       </c>
       <c r="E121">
-        <v>1.904465856559703</v>
+        <v>1.934839879625112</v>
       </c>
       <c r="F121">
         <v>-1</v>
       </c>
       <c r="G121">
-        <v>0.006050621367359629</v>
+        <v>0.00579151342612918</v>
       </c>
       <c r="H121">
-        <v>0.005675534143440297</v>
+        <v>0.005745160120374888</v>
       </c>
       <c r="I121">
-        <v>0.06491277608066803</v>
+        <v>0.01364669424570941</v>
       </c>
       <c r="J121">
-        <v>0.8162485469438515</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K121">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L121">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M121">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N121">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O121">
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="122" spans="1:16">
       <c r="A122" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C122">
-        <v>1.951815914681949</v>
+        <v>1.964801996006813</v>
       </c>
       <c r="D122" t="s">
         <v>49</v>
       </c>
       <c r="E122">
-        <v>1.904465856559703</v>
+        <v>1.93387546027835</v>
       </c>
       <c r="F122">
         <v>-1</v>
       </c>
       <c r="G122">
-        <v>0.005788184085318051</v>
+        <v>0.006055198003993187</v>
       </c>
       <c r="H122">
-        <v>0.005675534143440297</v>
+        <v>0.00574612453972165</v>
       </c>
       <c r="I122">
-        <v>0.04735005812224591</v>
+        <v>0.03092653572846338</v>
       </c>
       <c r="J122">
-        <v>0.8162485469438515</v>
+        <v>0.8180792015972748</v>
       </c>
       <c r="K122">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L122">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M122">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N122">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O122">
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="123" spans="1:16">
       <c r="A123" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B123" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C123">
-        <v>1.979025316902244</v>
+        <v>1.947513876246404</v>
       </c>
       <c r="D123" t="s">
         <v>49</v>
       </c>
       <c r="E123">
-        <v>1.913379392817673</v>
+        <v>1.93387546027835</v>
       </c>
       <c r="F123">
         <v>-1</v>
       </c>
       <c r="G123">
-        <v>0.006040974683097756</v>
+        <v>0.005792486123753596</v>
       </c>
       <c r="H123">
-        <v>0.005666620607182327</v>
+        <v>0.00574612453972165</v>
       </c>
       <c r="I123">
-        <v>0.06564592408457037</v>
+        <v>0.01363841596805471</v>
       </c>
       <c r="J123">
-        <v>0.8123898732391025</v>
+        <v>0.8180792015972748</v>
       </c>
       <c r="K123">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L123">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M123">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N123">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O123">
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="124" spans="1:16">
       <c r="A124" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C124">
-        <v>1.960883797888109</v>
+        <v>1.96211546833212</v>
       </c>
       <c r="D124" t="s">
         <v>49</v>
       </c>
       <c r="E124">
-        <v>1.913379392817673</v>
+        <v>1.931371616485536</v>
       </c>
       <c r="F124">
         <v>-1</v>
       </c>
       <c r="G124">
-        <v>0.005779116202111891</v>
+        <v>0.006057884531667879</v>
       </c>
       <c r="H124">
-        <v>0.005666620607182327</v>
+        <v>0.005748628383514463</v>
       </c>
       <c r="I124">
-        <v>0.04750440507043585</v>
+        <v>0.03074385184658412</v>
       </c>
       <c r="J124">
-        <v>0.8123898732391025</v>
+        <v>0.8191538126671517</v>
       </c>
       <c r="K124">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L124">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M124">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N124">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O124">
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="125" spans="1:16">
       <c r="A125" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B125" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C125">
-        <v>1.983626913195719</v>
+        <v>1.944988540232194</v>
       </c>
       <c r="D125" t="s">
         <v>49</v>
       </c>
       <c r="E125">
-        <v>1.917631267792844</v>
+        <v>1.931371616485536</v>
       </c>
       <c r="F125">
         <v>-1</v>
       </c>
       <c r="G125">
-        <v>0.00603637308680428</v>
+        <v>0.005795011459767806</v>
       </c>
       <c r="H125">
-        <v>0.005662368732207156</v>
+        <v>0.005748628383514463</v>
       </c>
       <c r="I125">
-        <v>0.0659956454028745</v>
+        <v>0.01361692374665724</v>
       </c>
       <c r="J125">
-        <v>0.8105492347217125</v>
+        <v>0.8191538126671517</v>
       </c>
       <c r="K125">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L125">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M125">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N125">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O125">
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="126" spans="1:16">
       <c r="A126" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C126">
-        <v>1.965209298403976</v>
+        <v>1.969378632640371</v>
       </c>
       <c r="D126" t="s">
         <v>49</v>
       </c>
       <c r="E126">
-        <v>1.917631267792844</v>
+        <v>1.938140885620826</v>
       </c>
       <c r="F126">
         <v>-1</v>
       </c>
       <c r="G126">
-        <v>0.005774790701596024</v>
+        <v>0.006050621367359629</v>
       </c>
       <c r="H126">
-        <v>0.005662368732207156</v>
+        <v>0.005741859114379175</v>
       </c>
       <c r="I126">
-        <v>0.04757803061113153</v>
+        <v>0.03123774701954529</v>
       </c>
       <c r="J126">
-        <v>0.8105492347217125</v>
+        <v>0.8162485469438515</v>
       </c>
       <c r="K126">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L126">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M126">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N126">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O126">
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="127" spans="1:16">
       <c r="A127" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B127" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C127">
-        <v>1.99070164592738</v>
+        <v>1.951815914681949</v>
       </c>
       <c r="D127" t="s">
         <v>49</v>
       </c>
       <c r="E127">
-        <v>1.924168320836899</v>
+        <v>1.938140885620826</v>
       </c>
       <c r="F127">
         <v>-1</v>
       </c>
       <c r="G127">
-        <v>0.006029298354072619</v>
+        <v>0.005788184085318051</v>
       </c>
       <c r="H127">
-        <v>0.005655831679163101</v>
+        <v>0.005741859114379175</v>
       </c>
       <c r="I127">
-        <v>0.06653332509048071</v>
+        <v>0.01367502906112317</v>
       </c>
       <c r="J127">
-        <v>0.8077193416290479</v>
+        <v>0.8162485469438515</v>
       </c>
       <c r="K127">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L127">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M127">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N127">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O127">
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="128" spans="1:16">
       <c r="A128" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C128">
-        <v>1.971859547171738</v>
+        <v>1.979025316902244</v>
       </c>
       <c r="D128" t="s">
         <v>49</v>
       </c>
       <c r="E128">
-        <v>1.924168320836899</v>
+        <v>1.947131595352891</v>
       </c>
       <c r="F128">
         <v>-1</v>
       </c>
       <c r="G128">
-        <v>0.005768140452828262</v>
+        <v>0.006040974683097756</v>
       </c>
       <c r="H128">
-        <v>0.005655831679163101</v>
+        <v>0.005732868404647109</v>
       </c>
       <c r="I128">
-        <v>0.04769122633483813</v>
+        <v>0.03189372154935266</v>
       </c>
       <c r="J128">
-        <v>0.8077193416290479</v>
+        <v>0.8123898732391025</v>
       </c>
       <c r="K128">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L128">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M128">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N128">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O128">
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="129" spans="1:16">
       <c r="A129" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B129" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C129">
-        <v>1.995518685947181</v>
+        <v>1.960883797888109</v>
       </c>
       <c r="D129" t="s">
         <v>49</v>
       </c>
       <c r="E129">
-        <v>1.928619265815195</v>
+        <v>1.947131595352891</v>
       </c>
       <c r="F129">
         <v>-1</v>
       </c>
       <c r="G129">
-        <v>0.006024481314052819</v>
+        <v>0.005779116202111891</v>
       </c>
       <c r="H129">
-        <v>0.005651380734184805</v>
+        <v>0.005732868404647109</v>
       </c>
       <c r="I129">
-        <v>0.06689942013198569</v>
+        <v>0.01375220253521814</v>
       </c>
       <c r="J129">
-        <v>0.8057925256211278</v>
+        <v>0.8123898732391025</v>
       </c>
       <c r="K129">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L129">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M129">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N129">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O129">
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="130" spans="1:16">
       <c r="A130" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C130">
-        <v>1.97638756479035</v>
+        <v>1.983626913195719</v>
       </c>
       <c r="D130" t="s">
         <v>49</v>
       </c>
       <c r="E130">
-        <v>1.928619265815195</v>
+        <v>1.95142028309841</v>
       </c>
       <c r="F130">
         <v>-1</v>
       </c>
       <c r="G130">
-        <v>0.005763612435209651</v>
+        <v>0.00603637308680428</v>
       </c>
       <c r="H130">
-        <v>0.005651380734184805</v>
+        <v>0.00572857971690159</v>
       </c>
       <c r="I130">
-        <v>0.04776829897515489</v>
+        <v>0.03220663009730895</v>
       </c>
       <c r="J130">
-        <v>0.8057925256211278</v>
+        <v>0.8105492347217125</v>
       </c>
       <c r="K130">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L130">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M130">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N130">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O130">
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="131" spans="1:16">
       <c r="A131" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B131" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C131">
-        <v>2.001757402215216</v>
+        <v>1.965209298403976</v>
       </c>
       <c r="D131" t="s">
         <v>49</v>
       </c>
       <c r="E131">
-        <v>1.93438383964686</v>
+        <v>1.95142028309841</v>
       </c>
       <c r="F131">
         <v>-1</v>
       </c>
       <c r="G131">
-        <v>0.006018242597784784</v>
+        <v>0.005774790701596024</v>
       </c>
       <c r="H131">
-        <v>0.00564561616035314</v>
+        <v>0.00572857971690159</v>
       </c>
       <c r="I131">
-        <v>0.06737356256835647</v>
+        <v>0.01378901530556598</v>
       </c>
       <c r="J131">
-        <v>0.8032970391139135</v>
+        <v>0.8105492347217125</v>
       </c>
       <c r="K131">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L131">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M131">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N131">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O131">
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="132" spans="1:16">
       <c r="A132" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C132">
-        <v>1.982251958082303</v>
+        <v>1.99070164592738</v>
       </c>
       <c r="D132" t="s">
         <v>49</v>
       </c>
       <c r="E132">
-        <v>1.93438383964686</v>
+        <v>1.958013934004318</v>
       </c>
       <c r="F132">
         <v>-1</v>
       </c>
       <c r="G132">
-        <v>0.005757748041917698</v>
+        <v>0.006029298354072619</v>
       </c>
       <c r="H132">
-        <v>0.00564561616035314</v>
+        <v>0.005721986065995681</v>
       </c>
       <c r="I132">
-        <v>0.04786811843544347</v>
+        <v>0.03268771192306197</v>
       </c>
       <c r="J132">
-        <v>0.8032970391139135</v>
+        <v>0.8077193416290479</v>
       </c>
       <c r="K132">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L132">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M132">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N132">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O132">
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="133" spans="1:16">
       <c r="A133" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B133" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C133">
-        <v>2.008261226887488</v>
+        <v>1.971859547171738</v>
       </c>
       <c r="D133" t="s">
         <v>49</v>
       </c>
       <c r="E133">
-        <v>1.940393373644039</v>
+        <v>1.958013934004318</v>
       </c>
       <c r="F133">
         <v>-1</v>
       </c>
       <c r="G133">
-        <v>0.006011738773112512</v>
+        <v>0.005768140452828262</v>
       </c>
       <c r="H133">
-        <v>0.005639606626355961</v>
+        <v>0.005721986065995681</v>
       </c>
       <c r="I133">
-        <v>0.06786785324344891</v>
+        <v>0.01384561316741939</v>
       </c>
       <c r="J133">
-        <v>0.8006955092450049</v>
+        <v>0.8077193416290479</v>
       </c>
       <c r="K133">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L133">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M133">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N133">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O133">
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="134" spans="1:16">
       <c r="A134" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C134">
-        <v>1.988365553274239</v>
+        <v>1.995518685947181</v>
       </c>
       <c r="D134" t="s">
         <v>49</v>
       </c>
       <c r="E134">
-        <v>1.940393373644039</v>
+        <v>1.962503415302772</v>
       </c>
       <c r="F134">
         <v>-1</v>
       </c>
       <c r="G134">
-        <v>0.005751634446725762</v>
+        <v>0.006024481314052819</v>
       </c>
       <c r="H134">
-        <v>0.005639606626355961</v>
+        <v>0.005717496584697228</v>
       </c>
       <c r="I134">
-        <v>0.04797217963019995</v>
+        <v>0.03301527064440846</v>
       </c>
       <c r="J134">
-        <v>0.8006955092450049</v>
+        <v>0.8057925256211278</v>
       </c>
       <c r="K134">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L134">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M134">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N134">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O134">
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="135" spans="1:16">
       <c r="A135" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B135" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C135">
-        <v>2.013407841318734</v>
+        <v>1.97638756479035</v>
       </c>
       <c r="D135" t="s">
         <v>49</v>
       </c>
       <c r="E135">
-        <v>1.94514884537851</v>
+        <v>1.962503415302772</v>
       </c>
       <c r="F135">
         <v>-1</v>
       </c>
       <c r="G135">
-        <v>0.006006592158681266</v>
+        <v>0.005763612435209651</v>
       </c>
       <c r="H135">
-        <v>0.00563485115462149</v>
+        <v>0.005717496584697228</v>
       </c>
       <c r="I135">
-        <v>0.06825899594022378</v>
+        <v>0.01388414948757766</v>
       </c>
       <c r="J135">
-        <v>0.7986368634725065</v>
+        <v>0.8057925256211278</v>
       </c>
       <c r="K135">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L135">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M135">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N135">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O135">
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="136" spans="1:16">
       <c r="A136" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C136">
-        <v>1.99320337083961</v>
+        <v>2.001757402215216</v>
       </c>
       <c r="D136" t="s">
         <v>49</v>
       </c>
       <c r="E136">
-        <v>1.94514884537851</v>
+        <v>1.968317898864581</v>
       </c>
       <c r="F136">
         <v>-1</v>
       </c>
       <c r="G136">
-        <v>0.005746796629160391</v>
+        <v>0.006018242597784784</v>
       </c>
       <c r="H136">
-        <v>0.00563485115462149</v>
+        <v>0.005711682101135418</v>
       </c>
       <c r="I136">
-        <v>0.04805452546109978</v>
+        <v>0.03343950335063495</v>
       </c>
       <c r="J136">
-        <v>0.7986368634725065</v>
+        <v>0.8032970391139135</v>
       </c>
       <c r="K136">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L136">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M136">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N136">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O136">
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="137" spans="1:16">
       <c r="A137" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B137" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C137">
-        <v>2.024814922108121</v>
+        <v>1.982251958082303</v>
       </c>
       <c r="D137" t="s">
         <v>49</v>
       </c>
       <c r="E137">
-        <v>1.955688988027904</v>
+        <v>1.968317898864581</v>
       </c>
       <c r="F137">
         <v>-1</v>
       </c>
       <c r="G137">
-        <v>0.005995185077891879</v>
+        <v>0.005757748041917698</v>
       </c>
       <c r="H137">
-        <v>0.005624311011972096</v>
+        <v>0.005711682101135418</v>
       </c>
       <c r="I137">
-        <v>0.06912593408021706</v>
+        <v>0.01393405921772195</v>
       </c>
       <c r="J137">
-        <v>0.7940740311567515</v>
+        <v>0.8032970391139135</v>
       </c>
       <c r="K137">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L137">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M137">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N137">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O137">
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="138" spans="1:16">
       <c r="A138" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C138">
-        <v>2.003926026781634</v>
+        <v>2.008261226887488</v>
       </c>
       <c r="D138" t="s">
         <v>49</v>
       </c>
       <c r="E138">
-        <v>1.955688988027904</v>
+        <v>1.974379463459139</v>
       </c>
       <c r="F138">
         <v>-1</v>
       </c>
       <c r="G138">
-        <v>0.005736073973218366</v>
+        <v>0.006011738773112512</v>
       </c>
       <c r="H138">
-        <v>0.005624311011972096</v>
+        <v>0.005705620536540861</v>
       </c>
       <c r="I138">
-        <v>0.04823703875373009</v>
+        <v>0.03388176342834903</v>
       </c>
       <c r="J138">
-        <v>0.7940740311567515</v>
+        <v>0.8006955092450049</v>
       </c>
       <c r="K138">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L138">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M138">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N138">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O138">
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="139" spans="1:16">
       <c r="A139" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B139" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C139">
-        <v>2.037026290859836</v>
+        <v>1.988365553274239</v>
       </c>
       <c r="D139" t="s">
         <v>49</v>
       </c>
       <c r="E139">
-        <v>1.966972292754488</v>
+        <v>1.974379463459139</v>
       </c>
       <c r="F139">
         <v>-1</v>
       </c>
       <c r="G139">
-        <v>0.005982973709140164</v>
+        <v>0.005751634446725762</v>
       </c>
       <c r="H139">
-        <v>0.005613027707245512</v>
+        <v>0.005705620536540861</v>
       </c>
       <c r="I139">
-        <v>0.0700539981053474</v>
+        <v>0.01398608981510008</v>
       </c>
       <c r="J139">
-        <v>0.7891894836560657</v>
+        <v>0.8006955092450049</v>
       </c>
       <c r="K139">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L139">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M139">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N139">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O139">
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="140" spans="1:16">
       <c r="A140" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C140">
-        <v>2.015404713408246</v>
+        <v>2.013407841318734</v>
       </c>
       <c r="D140" t="s">
         <v>49</v>
       </c>
       <c r="E140">
-        <v>1.966972292754488</v>
+        <v>1.97917610810906</v>
       </c>
       <c r="F140">
         <v>-1</v>
       </c>
       <c r="G140">
-        <v>0.005724595286591755</v>
+        <v>0.006006592158681266</v>
       </c>
       <c r="H140">
-        <v>0.005613027707245512</v>
+        <v>0.00570082389189094</v>
       </c>
       <c r="I140">
-        <v>0.04843242065375719</v>
+        <v>0.03423173320967421</v>
       </c>
       <c r="J140">
-        <v>0.7891894836560657</v>
+        <v>0.7986368634725065</v>
       </c>
       <c r="K140">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L140">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M140">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N140">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O140">
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="141" spans="1:16">
       <c r="A141" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B141" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C141">
-        <v>2.040400244545683</v>
+        <v>1.99320337083961</v>
       </c>
       <c r="D141" t="s">
         <v>49</v>
       </c>
       <c r="E141">
-        <v>1.970089825960211</v>
+        <v>1.97917610810906</v>
       </c>
       <c r="F141">
         <v>-1</v>
       </c>
       <c r="G141">
-        <v>0.005979599755454317</v>
+        <v>0.005746796629160391</v>
       </c>
       <c r="H141">
-        <v>0.005609910174039789</v>
+        <v>0.00570082389189094</v>
       </c>
       <c r="I141">
-        <v>0.07031041858547171</v>
+        <v>0.01402726273055022</v>
       </c>
       <c r="J141">
-        <v>0.7878399021817268</v>
+        <v>0.7986368634725065</v>
       </c>
       <c r="K141">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L141">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M141">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N141">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O141">
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="142" spans="1:16">
       <c r="A142" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B142" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C142">
-        <v>2.018576229872942</v>
+        <v>2.024814922108121</v>
       </c>
       <c r="D142" t="s">
         <v>49</v>
       </c>
       <c r="E142">
-        <v>1.970089825960211</v>
+        <v>1.989807507404769</v>
       </c>
       <c r="F142">
         <v>-1</v>
       </c>
       <c r="G142">
-        <v>0.005721423770127059</v>
+        <v>0.005995185077891879</v>
       </c>
       <c r="H142">
-        <v>0.005609910174039789</v>
+        <v>0.005690192492595231</v>
       </c>
       <c r="I142">
-        <v>0.04848640391273085</v>
+        <v>0.03500741470335211</v>
       </c>
       <c r="J142">
-        <v>0.7878399021817268</v>
+        <v>0.7940740311567515</v>
       </c>
       <c r="K142">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L142">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M142">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N142">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O142">
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="143" spans="1:16">
       <c r="A143" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B143" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C143">
-        <v>2.040677055689185</v>
+        <v>2.003926026781634</v>
       </c>
       <c r="D143" t="s">
         <v>49</v>
       </c>
       <c r="E143">
-        <v>1.970345599456807</v>
+        <v>1.989807507404769</v>
       </c>
       <c r="F143">
         <v>-1</v>
       </c>
       <c r="G143">
-        <v>0.005979322944310814</v>
+        <v>0.005736073973218366</v>
       </c>
       <c r="H143">
-        <v>0.005609654400543193</v>
+        <v>0.005690192492595231</v>
       </c>
       <c r="I143">
-        <v>0.07033145623237802</v>
+        <v>0.01411851937686515</v>
       </c>
       <c r="J143">
-        <v>0.7877291777243258</v>
+        <v>0.7940740311567515</v>
       </c>
       <c r="K143">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L143">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M143">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N143">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O143">
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="144" spans="1:16">
       <c r="A144" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B144" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C144">
-        <v>2.018836432347834</v>
+        <v>2.037026290859836</v>
       </c>
       <c r="D144" t="s">
         <v>49</v>
       </c>
       <c r="E144">
-        <v>1.970345599456807</v>
+        <v>2.001188503081367</v>
       </c>
       <c r="F144">
         <v>-1</v>
       </c>
       <c r="G144">
-        <v>0.005721163567652166</v>
+        <v>0.005982973709140164</v>
       </c>
       <c r="H144">
-        <v>0.005609654400543193</v>
+        <v>0.005678811496918633</v>
       </c>
       <c r="I144">
-        <v>0.04849083289102696</v>
+        <v>0.03583778777846902</v>
       </c>
       <c r="J144">
-        <v>0.7877291777243258</v>
+        <v>0.7891894836560657</v>
       </c>
       <c r="K144">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L144">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M144">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N144">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O144">
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="145" spans="1:16">
       <c r="A145" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B145" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C145">
-        <v>2.041764709541035</v>
+        <v>2.015404713408246</v>
       </c>
       <c r="D145" t="s">
         <v>49</v>
       </c>
       <c r="E145">
-        <v>1.971350591615917</v>
+        <v>2.001188503081367</v>
       </c>
       <c r="F145">
         <v>-1</v>
       </c>
       <c r="G145">
-        <v>0.005978235290458964</v>
+        <v>0.005724595286591755</v>
       </c>
       <c r="H145">
-        <v>0.005608649408384083</v>
+        <v>0.005678811496918633</v>
       </c>
       <c r="I145">
-        <v>0.07041411792511831</v>
+        <v>0.01421621032687881</v>
       </c>
       <c r="J145">
-        <v>0.7872941161835857</v>
+        <v>0.7891894836560657</v>
       </c>
       <c r="K145">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L145">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M145">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N145">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O145">
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="146" spans="1:16">
       <c r="A146" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B146" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C146">
-        <v>2.019858826968574</v>
+        <v>2.040400244545683</v>
       </c>
       <c r="D146" t="s">
         <v>49</v>
       </c>
       <c r="E146">
-        <v>1.971350591615917</v>
+        <v>2.004333027916577</v>
       </c>
       <c r="F146">
         <v>-1</v>
       </c>
       <c r="G146">
-        <v>0.005720141173031427</v>
+        <v>0.005979599755454317</v>
       </c>
       <c r="H146">
-        <v>0.005608649408384083</v>
+        <v>0.005675666972083424</v>
       </c>
       <c r="I146">
-        <v>0.04850823535265669</v>
+        <v>0.03606721662910628</v>
       </c>
       <c r="J146">
-        <v>0.7872941161835857</v>
+        <v>0.7878399021817268</v>
       </c>
       <c r="K146">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L146">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M146">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N146">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O146">
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="147" spans="1:16">
       <c r="A147" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B147" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C147">
-        <v>2.038301570426869</v>
+        <v>2.018576229872942</v>
       </c>
       <c r="D147" t="s">
         <v>49</v>
       </c>
       <c r="E147">
-        <v>1.968150651074427</v>
+        <v>2.004333027916577</v>
       </c>
       <c r="F147">
         <v>-1</v>
       </c>
       <c r="G147">
-        <v>0.005981698429573131</v>
+        <v>0.005721423770127059</v>
       </c>
       <c r="H147">
-        <v>0.005611849348925574</v>
+        <v>0.005675666972083424</v>
       </c>
       <c r="I147">
-        <v>0.07015091935244189</v>
+        <v>0.01424320195636541</v>
       </c>
       <c r="J147">
-        <v>0.7886793718292525</v>
+        <v>0.7878399021817268</v>
       </c>
       <c r="K147">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L147">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M147">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N147">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O147">
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="148" spans="1:16">
       <c r="A148" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B148" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C148">
-        <v>2.016603476201257</v>
+        <v>2.040677055689185</v>
       </c>
       <c r="D148" t="s">
         <v>49</v>
       </c>
       <c r="E148">
-        <v>1.968150651074427</v>
+        <v>2.004591015902321</v>
       </c>
       <c r="F148">
         <v>-1</v>
       </c>
       <c r="G148">
-        <v>0.005723396523798744</v>
+        <v>0.005979322944310814</v>
       </c>
       <c r="H148">
-        <v>0.005611849348925574</v>
+        <v>0.005675408984097679</v>
       </c>
       <c r="I148">
-        <v>0.04845282512682991</v>
+        <v>0.03608603978686453</v>
       </c>
       <c r="J148">
-        <v>0.7886793718292525</v>
+        <v>0.7877291777243258</v>
       </c>
       <c r="K148">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L148">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M148">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N148">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O148">
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="149" spans="1:16">
       <c r="A149" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B149" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C149">
-        <v>2.035132415564467</v>
+        <v>2.018836432347834</v>
       </c>
       <c r="D149" t="s">
         <v>49</v>
       </c>
       <c r="E149">
-        <v>1.965222351981568</v>
+        <v>2.004591015902321</v>
       </c>
       <c r="F149">
         <v>-1</v>
       </c>
       <c r="G149">
-        <v>0.005984867584435533</v>
+        <v>0.005721163567652166</v>
       </c>
       <c r="H149">
-        <v>0.005614777648018432</v>
+        <v>0.005675408984097679</v>
       </c>
       <c r="I149">
-        <v>0.06991006358289908</v>
+        <v>0.01424541644551347</v>
       </c>
       <c r="J149">
-        <v>0.7899470337742129</v>
+        <v>0.7877291777243258</v>
       </c>
       <c r="K149">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L149">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M149">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N149">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O149">
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="150" spans="1:16">
       <c r="A150" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B150" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C150">
-        <v>2.013624470630599</v>
+        <v>2.041764709541035</v>
       </c>
       <c r="D150" t="s">
         <v>49</v>
       </c>
       <c r="E150">
-        <v>1.965222351981568</v>
+        <v>2.005604709292245</v>
       </c>
       <c r="F150">
         <v>-1</v>
       </c>
       <c r="G150">
-        <v>0.0057263755293694</v>
+        <v>0.005978235290458964</v>
       </c>
       <c r="H150">
-        <v>0.005614777648018432</v>
+        <v>0.005674395290707754</v>
       </c>
       <c r="I150">
-        <v>0.04840211864903132</v>
+        <v>0.03616000024879007</v>
       </c>
       <c r="J150">
-        <v>0.7899470337742129</v>
+        <v>0.7872941161835857</v>
       </c>
       <c r="K150">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L150">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M150">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N150">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O150">
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="151" spans="1:16">
       <c r="A151" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B151" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C151">
-        <v>2.033942517186959</v>
+        <v>2.019858826968574</v>
       </c>
       <c r="D151" t="s">
         <v>49</v>
       </c>
       <c r="E151">
-        <v>1.96412288588075</v>
+        <v>2.005604709292245</v>
       </c>
       <c r="F151">
         <v>-1</v>
       </c>
       <c r="G151">
-        <v>0.005986057482813041</v>
+        <v>0.005720141173031427</v>
       </c>
       <c r="H151">
-        <v>0.005615877114119251</v>
+        <v>0.005674395290707754</v>
       </c>
       <c r="I151">
-        <v>0.0698196313062085</v>
+        <v>0.01425411767632845</v>
       </c>
       <c r="J151">
-        <v>0.7904229931252164</v>
+        <v>0.7872941161835857</v>
       </c>
       <c r="K151">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L151">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M151">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N151">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O151">
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="152" spans="1:16">
       <c r="A152" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B152" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C152">
-        <v>2.012505966155742</v>
+        <v>2.038301570426869</v>
       </c>
       <c r="D152" t="s">
         <v>49</v>
       </c>
       <c r="E152">
-        <v>1.96412288588075</v>
+        <v>2.002377063637842</v>
       </c>
       <c r="F152">
         <v>-1</v>
       </c>
       <c r="G152">
-        <v>0.00572749403384426</v>
+        <v>0.005981698429573131</v>
       </c>
       <c r="H152">
-        <v>0.005615877114119251</v>
+        <v>0.005677622936362158</v>
       </c>
       <c r="I152">
-        <v>0.04838308027499139</v>
+        <v>0.03592450678902681</v>
       </c>
       <c r="J152">
-        <v>0.7904229931252164</v>
+        <v>0.7886793718292525</v>
       </c>
       <c r="K152">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L152">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M152">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N152">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O152">
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="153" spans="1:16">
       <c r="A153" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B153" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C153">
-        <v>2.03219014170303</v>
+        <v>2.016603476201257</v>
       </c>
       <c r="D153" t="s">
         <v>49</v>
       </c>
       <c r="E153">
-        <v>1.9625036909336</v>
+        <v>2.002377063637842</v>
       </c>
       <c r="F153">
         <v>-1</v>
       </c>
       <c r="G153">
-        <v>0.00598780985829697</v>
+        <v>0.005723396523798744</v>
       </c>
       <c r="H153">
-        <v>0.005617496309066401</v>
+        <v>0.005677622936362158</v>
       </c>
       <c r="I153">
-        <v>0.06968645076942992</v>
+        <v>0.01422641256341484</v>
       </c>
       <c r="J153">
-        <v>0.791123943318788</v>
+        <v>0.7886793718292525</v>
       </c>
       <c r="K153">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L153">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M153">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N153">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O153">
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="154" spans="1:16">
       <c r="A154" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B154" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C154">
-        <v>2.010858733200848</v>
+        <v>2.035132415564467</v>
       </c>
       <c r="D154" t="s">
         <v>49</v>
       </c>
       <c r="E154">
-        <v>1.9625036909336</v>
+        <v>1.999423411306084</v>
       </c>
       <c r="F154">
         <v>-1</v>
       </c>
       <c r="G154">
-        <v>0.005729141266799152</v>
+        <v>0.005984867584435533</v>
       </c>
       <c r="H154">
-        <v>0.005617496309066401</v>
+        <v>0.005680576588693916</v>
       </c>
       <c r="I154">
-        <v>0.04835504226724852</v>
+        <v>0.03570900425838364</v>
       </c>
       <c r="J154">
-        <v>0.791123943318788</v>
+        <v>0.7899470337742129</v>
       </c>
       <c r="K154">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L154">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M154">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N154">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O154">
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="155" spans="1:16">
       <c r="A155" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B155" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C155">
-        <v>2.031041804995824</v>
+        <v>2.013624470630599</v>
       </c>
       <c r="D155" t="s">
         <v>49</v>
       </c>
       <c r="E155">
-        <v>1.961442627816142</v>
+        <v>1.999423411306084</v>
       </c>
       <c r="F155">
         <v>-1</v>
       </c>
       <c r="G155">
-        <v>0.005988958195004175</v>
+        <v>0.0057263755293694</v>
       </c>
       <c r="H155">
-        <v>0.005618557372183858</v>
+        <v>0.005680576588693916</v>
       </c>
       <c r="I155">
-        <v>0.06959917717968245</v>
+        <v>0.01420105932451587</v>
       </c>
       <c r="J155">
-        <v>0.7915832780016702</v>
+        <v>0.7899470337742129</v>
       </c>
       <c r="K155">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L155">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M155">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N155">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O155">
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="156" spans="1:16">
       <c r="A156" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B156" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C156">
-        <v>2.009779296696075</v>
+        <v>2.033942517186959</v>
       </c>
       <c r="D156" t="s">
         <v>49</v>
       </c>
       <c r="E156">
-        <v>1.961442627816142</v>
+        <v>1.998314426018246</v>
       </c>
       <c r="F156">
         <v>-1</v>
       </c>
       <c r="G156">
-        <v>0.005730220703303925</v>
+        <v>0.005986057482813041</v>
       </c>
       <c r="H156">
-        <v>0.005618557372183858</v>
+        <v>0.005681685573981754</v>
       </c>
       <c r="I156">
-        <v>0.04833666887993338</v>
+        <v>0.03562809116871302</v>
       </c>
       <c r="J156">
-        <v>0.7915832780016702</v>
+        <v>0.7904229931252164</v>
       </c>
       <c r="K156">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L156">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M156">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N156">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O156">
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="157" spans="1:16">
       <c r="A157" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B157" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C157">
-        <v>2.032225684349332</v>
+        <v>2.012505966155742</v>
       </c>
       <c r="D157" t="s">
         <v>49</v>
       </c>
       <c r="E157">
-        <v>1.962536532338783</v>
+        <v>1.998314426018246</v>
       </c>
       <c r="F157">
         <v>-1</v>
       </c>
       <c r="G157">
-        <v>0.005987774315650668</v>
+        <v>0.00572749403384426</v>
       </c>
       <c r="H157">
-        <v>0.005617463467661218</v>
+        <v>0.005681685573981754</v>
       </c>
       <c r="I157">
-        <v>0.06968915201054915</v>
+        <v>0.01419154013749591</v>
       </c>
       <c r="J157">
-        <v>0.7911097262602672</v>
+        <v>0.7904229931252164</v>
       </c>
       <c r="K157">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L157">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M157">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N157">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O157">
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="158" spans="1:16">
       <c r="A158" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B158" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C158">
-        <v>2.010892143288372</v>
+        <v>2.03219014170303</v>
       </c>
       <c r="D158" t="s">
         <v>49</v>
       </c>
       <c r="E158">
-        <v>1.962536532338783</v>
+        <v>1.996681212067224</v>
       </c>
       <c r="F158">
         <v>-1</v>
       </c>
       <c r="G158">
-        <v>0.005729107856711628</v>
+        <v>0.00598780985829697</v>
       </c>
       <c r="H158">
-        <v>0.005617463467661218</v>
+        <v>0.005683318787932776</v>
       </c>
       <c r="I158">
-        <v>0.04835561094958973</v>
+        <v>0.03550892963580599</v>
       </c>
       <c r="J158">
-        <v>0.7911097262602672</v>
+        <v>0.791123943318788</v>
       </c>
       <c r="K158">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L158">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M158">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N158">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O158">
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="159" spans="1:16">
       <c r="A159" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B159" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C159">
-        <v>2.033826265263685</v>
+        <v>2.010858733200848</v>
       </c>
       <c r="D159" t="s">
         <v>49</v>
       </c>
       <c r="E159">
-        <v>1.964015469103645</v>
+        <v>1.996681212067224</v>
       </c>
       <c r="F159">
         <v>-1</v>
       </c>
       <c r="G159">
-        <v>0.005986173734736314</v>
+        <v>0.005729141266799152</v>
       </c>
       <c r="H159">
-        <v>0.005615984530896355</v>
+        <v>0.005683318787932776</v>
       </c>
       <c r="I159">
-        <v>0.06981079616003982</v>
+        <v>0.01417752113362458</v>
       </c>
       <c r="J159">
-        <v>0.7904694938945258</v>
+        <v>0.791123943318788</v>
       </c>
       <c r="K159">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L159">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M159">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N159">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O159">
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="160" spans="1:16">
       <c r="A160" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B160" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C160">
-        <v>2.012396689347864</v>
+        <v>2.031041804995824</v>
       </c>
       <c r="D160" t="s">
         <v>49</v>
       </c>
       <c r="E160">
-        <v>1.964015469103645</v>
+        <v>1.995610962256108</v>
       </c>
       <c r="F160">
         <v>-1</v>
       </c>
       <c r="G160">
-        <v>0.005727603310652135</v>
+        <v>0.005988958195004175</v>
       </c>
       <c r="H160">
-        <v>0.005615984530896355</v>
+        <v>0.005684389037743891</v>
       </c>
       <c r="I160">
-        <v>0.04838122024421909</v>
+        <v>0.03543084273971608</v>
       </c>
       <c r="J160">
-        <v>0.7904694938945258</v>
+        <v>0.7915832780016702</v>
       </c>
       <c r="K160">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L160">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M160">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N160">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O160">
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="161" spans="1:16">
       <c r="A161" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B161" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C161">
-        <v>2.037114148133088</v>
+        <v>2.009779296696075</v>
       </c>
       <c r="D161" t="s">
         <v>49</v>
       </c>
       <c r="E161">
-        <v>1.967053472874974</v>
+        <v>1.995610962256108</v>
       </c>
       <c r="F161">
         <v>-1</v>
       </c>
       <c r="G161">
-        <v>0.005982885851866911</v>
+        <v>0.005730220703303925</v>
       </c>
       <c r="H161">
-        <v>0.005612946527125027</v>
+        <v>0.005684389037743891</v>
       </c>
       <c r="I161">
-        <v>0.07006067525811455</v>
+        <v>0.01416833443996701</v>
       </c>
       <c r="J161">
-        <v>0.7891543407467646</v>
+        <v>0.7915832780016702</v>
       </c>
       <c r="K161">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L161">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M161">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N161">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O161">
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="162" spans="1:16">
       <c r="A162" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B162" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C162">
-        <v>2.015487299245103</v>
+        <v>2.032225684349332</v>
       </c>
       <c r="D162" t="s">
         <v>49</v>
       </c>
       <c r="E162">
-        <v>1.967053472874974</v>
+        <v>1.996714337813577</v>
       </c>
       <c r="F162">
         <v>-1</v>
       </c>
       <c r="G162">
-        <v>0.005724512700754897</v>
+        <v>0.005987774315650668</v>
       </c>
       <c r="H162">
-        <v>0.005612946527125027</v>
+        <v>0.005683285662186423</v>
       </c>
       <c r="I162">
-        <v>0.04843382637012938</v>
+        <v>0.03551134653575461</v>
       </c>
       <c r="J162">
-        <v>0.7891543407467646</v>
+        <v>0.7911097262602672</v>
       </c>
       <c r="K162">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L162">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M162">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N162">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O162">
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="163" spans="1:16">
       <c r="A163" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B163" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C163">
-        <v>2.041024370702765</v>
+        <v>2.010892143288372</v>
       </c>
       <c r="D163" t="s">
         <v>49</v>
       </c>
       <c r="E163">
-        <v>1.970666518529355</v>
+        <v>1.996714337813577</v>
       </c>
       <c r="F163">
         <v>-1</v>
       </c>
       <c r="G163">
-        <v>0.005978975629297235</v>
+        <v>0.005729107856711628</v>
       </c>
       <c r="H163">
-        <v>0.005609333481470645</v>
+        <v>0.005683285662186423</v>
       </c>
       <c r="I163">
-        <v>0.07035785217340984</v>
+        <v>0.01417780547479519</v>
       </c>
       <c r="J163">
-        <v>0.7875902517188939</v>
+        <v>0.7911097262602672</v>
       </c>
       <c r="K163">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L163">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M163">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N163">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O163">
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="164" spans="1:16">
       <c r="A164" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B164" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C164">
-        <v>2.0191629084606</v>
+        <v>2.033826265263685</v>
       </c>
       <c r="D164" t="s">
         <v>49</v>
       </c>
       <c r="E164">
-        <v>1.970666518529355</v>
+        <v>1.998206079225755</v>
       </c>
       <c r="F164">
         <v>-1</v>
       </c>
       <c r="G164">
-        <v>0.005720837091539401</v>
+        <v>0.005986173734736314</v>
       </c>
       <c r="H164">
-        <v>0.005609333481470645</v>
+        <v>0.005681793920774245</v>
       </c>
       <c r="I164">
-        <v>0.0484963899312445</v>
+        <v>0.03562018603793038</v>
       </c>
       <c r="J164">
-        <v>0.7875902517188939</v>
+        <v>0.7904694938945258</v>
       </c>
       <c r="K164">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L164">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M164">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N164">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O164">
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -8999,31 +8990,31 @@
         <v>0</v>
       </c>
       <c r="B165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C165">
-        <v>2.042989638697718</v>
+        <v>2.037114148133088</v>
       </c>
       <c r="D165" t="s">
         <v>49</v>
       </c>
       <c r="E165">
-        <v>1.972482426156692</v>
+        <v>2.001270386060038</v>
       </c>
       <c r="F165">
         <v>-1</v>
       </c>
       <c r="G165">
-        <v>0.005977010361302281</v>
+        <v>0.005982885851866911</v>
       </c>
       <c r="H165">
-        <v>0.005607517573843309</v>
+        <v>0.005678729613939962</v>
       </c>
       <c r="I165">
-        <v>0.07050721254102643</v>
+        <v>0.03584376207305029</v>
       </c>
       <c r="J165">
-        <v>0.7868041445209126</v>
+        <v>0.7891543407467646</v>
       </c>
       <c r="K165">
         <v>2.5</v>
@@ -9032,66 +9023,66 @@
         <v>4.01</v>
       </c>
       <c r="M165">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N165">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O165">
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="166" spans="1:16">
       <c r="A166" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B166" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C166">
-        <v>2.021010260375856</v>
+        <v>2.041024370702765</v>
       </c>
       <c r="D166" t="s">
         <v>49</v>
       </c>
       <c r="E166">
-        <v>1.972482426156692</v>
+        <v>2.004914713494977</v>
       </c>
       <c r="F166">
         <v>-1</v>
       </c>
       <c r="G166">
-        <v>0.005718989739624145</v>
+        <v>0.005978975629297235</v>
       </c>
       <c r="H166">
-        <v>0.005607517573843309</v>
+        <v>0.005675085286505023</v>
       </c>
       <c r="I166">
-        <v>0.04852783421916373</v>
+        <v>0.03610965720778792</v>
       </c>
       <c r="J166">
-        <v>0.7868041445209126</v>
+        <v>0.7875902517188939</v>
       </c>
       <c r="K166">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L166">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M166">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N166">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O166">
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9099,31 +9090,31 @@
         <v>0</v>
       </c>
       <c r="B167" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C167">
-        <v>2.046475047291454</v>
+        <v>2.042989638697718</v>
       </c>
       <c r="D167" t="s">
         <v>49</v>
       </c>
       <c r="E167">
-        <v>1.975702943697304</v>
+        <v>2.006746343266273</v>
       </c>
       <c r="F167">
         <v>-1</v>
       </c>
       <c r="G167">
-        <v>0.005973524952708546</v>
+        <v>0.005977010361302281</v>
       </c>
       <c r="H167">
-        <v>0.005604297056302696</v>
+        <v>0.005673253656733726</v>
       </c>
       <c r="I167">
-        <v>0.07077210359415043</v>
+        <v>0.03624329543144489</v>
       </c>
       <c r="J167">
-        <v>0.7854099810834182</v>
+        <v>0.7868041445209126</v>
       </c>
       <c r="K167">
         <v>2.5</v>
@@ -9132,60 +9123,60 @@
         <v>4.01</v>
       </c>
       <c r="M167">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N167">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O167">
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="168" spans="1:16">
       <c r="A168" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B168" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C168">
-        <v>2.024286544453967</v>
+        <v>2.046475047291454</v>
       </c>
       <c r="D168" t="s">
         <v>49</v>
       </c>
       <c r="E168">
-        <v>1.975702943697304</v>
+        <v>2.009994744075636</v>
       </c>
       <c r="F168">
         <v>-1</v>
       </c>
       <c r="G168">
-        <v>0.005715713455546033</v>
+        <v>0.005973524952708546</v>
       </c>
       <c r="H168">
-        <v>0.005604297056302696</v>
+        <v>0.005670005255924364</v>
       </c>
       <c r="I168">
-        <v>0.04858360075666335</v>
+        <v>0.03648030321581874</v>
       </c>
       <c r="J168">
         <v>0.7854099810834182</v>
       </c>
       <c r="K168">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L168">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M168">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N168">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O168">
         <v>1</v>
@@ -9199,7 +9190,7 @@
         <v>0</v>
       </c>
       <c r="B169" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C169">
         <v>2.05115387029975</v>
@@ -9208,7 +9199,7 @@
         <v>49</v>
       </c>
       <c r="E169">
-        <v>1.980026176156969</v>
+        <v>2.014355407119367</v>
       </c>
       <c r="F169">
         <v>-1</v>
@@ -9217,10 +9208,10 @@
         <v>0.00596884612970025</v>
       </c>
       <c r="H169">
-        <v>0.005599973823843031</v>
+        <v>0.005665644592880632</v>
       </c>
       <c r="I169">
-        <v>0.07112769414278097</v>
+        <v>0.03679846318038305</v>
       </c>
       <c r="J169">
         <v>0.7835384518800999</v>
@@ -9232,10 +9223,10 @@
         <v>4.01</v>
       </c>
       <c r="M169">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N169">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="O169">
         <v>1</v>
@@ -9246,52 +9237,52 @@
     </row>
     <row r="170" spans="1:16">
       <c r="A170" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B170" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C170">
-        <v>2.028684638081765</v>
+        <v>1.569608330766713</v>
       </c>
       <c r="D170" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E170">
-        <v>1.980026176156969</v>
+        <v>1.925641663310317</v>
       </c>
       <c r="F170">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G170">
-        <v>0.005711315361918235</v>
+        <v>0.004650391669233286</v>
       </c>
       <c r="H170">
-        <v>0.005599973823843031</v>
+        <v>0.005954358336689684</v>
       </c>
       <c r="I170">
-        <v>0.04865846192479606</v>
+        <v>0.3560333325436043</v>
       </c>
       <c r="J170">
-        <v>0.7835384518800999</v>
+        <v>0.78994444576066</v>
       </c>
       <c r="K170">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="L170">
-        <v>3.87</v>
+        <v>3.11</v>
       </c>
       <c r="M170">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="N170">
-        <v>3.79</v>
+        <v>3.94</v>
       </c>
       <c r="O170">
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9299,49 +9290,49 @@
         <v>0</v>
       </c>
       <c r="B171" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C171">
-        <v>2.052411570940913</v>
+        <v>1.563290930299889</v>
       </c>
       <c r="D171" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E171">
-        <v>1.981188291549403</v>
+        <v>1.91738044731524</v>
       </c>
       <c r="F171">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G171">
-        <v>0.005967588429059087</v>
+        <v>0.00465670906970011</v>
       </c>
       <c r="H171">
-        <v>0.005598811708450597</v>
+        <v>0.005962619552684761</v>
       </c>
       <c r="I171">
-        <v>0.07122327939150952</v>
+        <v>0.3540895170153506</v>
       </c>
       <c r="J171">
-        <v>0.783035371623635</v>
+        <v>0.7931841383077493</v>
       </c>
       <c r="K171">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="L171">
-        <v>4.01</v>
+        <v>3.11</v>
       </c>
       <c r="M171">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="N171">
-        <v>3.79</v>
+        <v>3.94</v>
       </c>
       <c r="O171">
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9349,49 +9340,49 @@
         <v>0</v>
       </c>
       <c r="B172" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C172">
-        <v>2.054065467064709</v>
+        <v>1.559502895465797</v>
       </c>
       <c r="D172" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E172">
-        <v>1.982716491567792</v>
+        <v>1.912426863301427</v>
       </c>
       <c r="F172">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G172">
-        <v>0.005965934532935291</v>
+        <v>0.004660497104534203</v>
       </c>
       <c r="H172">
-        <v>0.005597283508432208</v>
+        <v>0.005967573136698573</v>
       </c>
       <c r="I172">
-        <v>0.07134897549691743</v>
+        <v>0.35292396783563</v>
       </c>
       <c r="J172">
-        <v>0.7823738131741161</v>
+        <v>0.7951267202739504</v>
       </c>
       <c r="K172">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="L172">
-        <v>4.01</v>
+        <v>3.11</v>
       </c>
       <c r="M172">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="N172">
-        <v>3.79</v>
+        <v>3.94</v>
       </c>
       <c r="O172">
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9399,249 +9390,49 @@
         <v>0</v>
       </c>
       <c r="B173" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C173">
-        <v>2.057724755182126</v>
+        <v>1.590146235974642</v>
       </c>
       <c r="D173" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E173">
-        <v>1.986097673788285</v>
+        <v>1.910334776982754</v>
       </c>
       <c r="F173">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G173">
-        <v>0.005962275244817874</v>
+        <v>0.004789853764025359</v>
       </c>
       <c r="H173">
-        <v>0.005593902326211715</v>
+        <v>0.005969665223017246</v>
       </c>
       <c r="I173">
-        <v>0.07162708139384155</v>
+        <v>0.3201885410081127</v>
       </c>
       <c r="J173">
-        <v>0.7809100979271496</v>
+        <v>0.7959471462812728</v>
       </c>
       <c r="K173">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="L173">
-        <v>4.01</v>
+        <v>3.19</v>
       </c>
       <c r="M173">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="N173">
-        <v>3.79</v>
+        <v>3.94</v>
       </c>
       <c r="O173">
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="174" spans="1:16">
-      <c r="A174" s="1">
-        <v>0</v>
-      </c>
-      <c r="B174" t="s">
-        <v>33</v>
-      </c>
-      <c r="C174">
-        <v>2.059621791558839</v>
-      </c>
-      <c r="D174" t="s">
-        <v>49</v>
-      </c>
-      <c r="E174">
-        <v>1.987850535400367</v>
-      </c>
-      <c r="F174">
-        <v>-1</v>
-      </c>
-      <c r="G174">
-        <v>0.005960378208441161</v>
-      </c>
-      <c r="H174">
-        <v>0.005592149464599632</v>
-      </c>
-      <c r="I174">
-        <v>0.0717712561584718</v>
-      </c>
-      <c r="J174">
-        <v>0.7801512833764644</v>
-      </c>
-      <c r="K174">
-        <v>2.5</v>
-      </c>
-      <c r="L174">
-        <v>4.01</v>
-      </c>
-      <c r="M174">
-        <v>2.31</v>
-      </c>
-      <c r="N174">
-        <v>3.79</v>
-      </c>
-      <c r="O174">
-        <v>1</v>
-      </c>
-      <c r="P174" t="s">
         <v>137</v>
-      </c>
-    </row>
-    <row r="175" spans="1:16">
-      <c r="A175" s="1">
-        <v>0</v>
-      </c>
-      <c r="B175" t="s">
-        <v>33</v>
-      </c>
-      <c r="C175">
-        <v>2.060612201172958</v>
-      </c>
-      <c r="D175" t="s">
-        <v>49</v>
-      </c>
-      <c r="E175">
-        <v>1.988765673883814</v>
-      </c>
-      <c r="F175">
-        <v>-1</v>
-      </c>
-      <c r="G175">
-        <v>0.005959387798827042</v>
-      </c>
-      <c r="H175">
-        <v>0.005591234326116187</v>
-      </c>
-      <c r="I175">
-        <v>0.07184652728914442</v>
-      </c>
-      <c r="J175">
-        <v>0.7797551195308166</v>
-      </c>
-      <c r="K175">
-        <v>2.5</v>
-      </c>
-      <c r="L175">
-        <v>4.01</v>
-      </c>
-      <c r="M175">
-        <v>2.31</v>
-      </c>
-      <c r="N175">
-        <v>3.79</v>
-      </c>
-      <c r="O175">
-        <v>1</v>
-      </c>
-      <c r="P175" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="176" spans="1:16">
-      <c r="A176" s="1">
-        <v>0</v>
-      </c>
-      <c r="B176" t="s">
-        <v>39</v>
-      </c>
-      <c r="C176">
-        <v>1.559502895465797</v>
-      </c>
-      <c r="D176" t="s">
-        <v>25</v>
-      </c>
-      <c r="E176">
-        <v>1.912426863301427</v>
-      </c>
-      <c r="F176">
-        <v>1</v>
-      </c>
-      <c r="G176">
-        <v>0.004660497104534203</v>
-      </c>
-      <c r="H176">
-        <v>0.005967573136698573</v>
-      </c>
-      <c r="I176">
-        <v>0.35292396783563</v>
-      </c>
-      <c r="J176">
-        <v>0.7951267202739504</v>
-      </c>
-      <c r="K176">
-        <v>1.95</v>
-      </c>
-      <c r="L176">
-        <v>3.11</v>
-      </c>
-      <c r="M176">
-        <v>2.55</v>
-      </c>
-      <c r="N176">
-        <v>3.94</v>
-      </c>
-      <c r="O176">
-        <v>1</v>
-      </c>
-      <c r="P176" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="177" spans="1:16">
-      <c r="A177" s="1">
-        <v>0</v>
-      </c>
-      <c r="B177" t="s">
-        <v>39</v>
-      </c>
-      <c r="C177">
-        <v>1.557903064751518</v>
-      </c>
-      <c r="D177" t="s">
-        <v>25</v>
-      </c>
-      <c r="E177">
-        <v>1.910334776982754</v>
-      </c>
-      <c r="F177">
-        <v>1</v>
-      </c>
-      <c r="G177">
-        <v>0.004662096935248481</v>
-      </c>
-      <c r="H177">
-        <v>0.005969665223017246</v>
-      </c>
-      <c r="I177">
-        <v>0.3524317122312364</v>
-      </c>
-      <c r="J177">
-        <v>0.7959471462812728</v>
-      </c>
-      <c r="K177">
-        <v>1.95</v>
-      </c>
-      <c r="L177">
-        <v>3.11</v>
-      </c>
-      <c r="M177">
-        <v>2.55</v>
-      </c>
-      <c r="N177">
-        <v>3.94</v>
-      </c>
-      <c r="O177">
-        <v>1</v>
-      </c>
-      <c r="P177" t="s">
-        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01618-601618.xlsx
+++ b/s60_signal/position-01618-601618.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="129">
   <si>
     <t>trade_time</t>
   </si>
@@ -106,6 +106,9 @@
     <t>2021-08-03</t>
   </si>
   <si>
+    <t>2021-08-12</t>
+  </si>
+  <si>
     <t>2021-01-13</t>
   </si>
   <si>
@@ -115,7 +118,7 @@
     <t>2021-07-26</t>
   </si>
   <si>
-    <t>2021-08-12</t>
+    <t>2021-08-16</t>
   </si>
   <si>
     <t>2021-02-26</t>
@@ -130,9 +133,6 @@
     <t>2021-07-19</t>
   </si>
   <si>
-    <t>2021-07-16</t>
-  </si>
-  <si>
     <t>2016-12-30</t>
   </si>
   <si>
@@ -163,7 +163,7 @@
     <t>2021-08-13</t>
   </si>
   <si>
-    <t>2021-08-16</t>
+    <t>2021-08-17</t>
   </si>
   <si>
     <t>2021-01-20</t>
@@ -178,6 +178,9 @@
     <t>2021-02-03</t>
   </si>
   <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
     <t>2021-03-09</t>
   </si>
   <si>
@@ -392,36 +395,6 @@
   </si>
   <si>
     <t>2021-05-18</t>
-  </si>
-  <si>
-    <t>2021-05-20</t>
-  </si>
-  <si>
-    <t>2021-05-21</t>
-  </si>
-  <si>
-    <t>2021-05-24</t>
-  </si>
-  <si>
-    <t>2021-05-25</t>
-  </si>
-  <si>
-    <t>2021-05-26</t>
-  </si>
-  <si>
-    <t>2021-05-27</t>
-  </si>
-  <si>
-    <t>2021-05-28</t>
-  </si>
-  <si>
-    <t>2021-05-31</t>
-  </si>
-  <si>
-    <t>2021-07-12</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
   </si>
   <si>
     <t>2021-07-14</t>
@@ -785,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P173"/>
+  <dimension ref="A1:P165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -882,7 +855,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -932,7 +905,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -982,7 +955,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1032,7 +1005,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1082,7 +1055,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1132,7 +1105,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1182,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1232,7 +1205,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1282,7 +1255,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1332,7 +1305,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1382,7 +1355,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1432,7 +1405,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1482,7 +1455,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1532,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1582,7 +1555,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1632,7 +1605,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1682,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1732,7 +1705,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1782,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -1832,7 +1805,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -1882,7 +1855,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -1932,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -1982,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2032,7 +2005,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2082,7 +2055,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2132,7 +2105,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2182,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2332,7 +2305,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2382,7 +2355,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2396,7 +2369,7 @@
         <v>2.754322580645161</v>
       </c>
       <c r="D33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E33">
         <v>2.847571157495255</v>
@@ -2432,7 +2405,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2482,7 +2455,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2532,7 +2505,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2582,7 +2555,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2596,7 +2569,7 @@
         <v>2.644938723766401</v>
       </c>
       <c r="D37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E37">
         <v>2.740332082123923</v>
@@ -2632,7 +2605,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2646,7 +2619,7 @@
         <v>2.676512157196488</v>
       </c>
       <c r="D38" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E38">
         <v>2.656669500539496</v>
@@ -2682,7 +2655,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2696,7 +2669,7 @@
         <v>2.567613560597548</v>
       </c>
       <c r="D39" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E39">
         <v>2.656669500539496</v>
@@ -2732,7 +2705,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -2746,7 +2719,7 @@
         <v>2.562534888926043</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E40">
         <v>2.656669500539496</v>
@@ -2782,7 +2755,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -2796,7 +2769,7 @@
         <v>2.551891062104373</v>
       </c>
       <c r="D41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E41">
         <v>2.649108884416052</v>
@@ -2832,7 +2805,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -2849,7 +2822,7 @@
         <v>49</v>
       </c>
       <c r="E42">
-        <v>2.57164948027576</v>
+        <v>2.738100964577074</v>
       </c>
       <c r="F42">
         <v>-1</v>
@@ -2858,10 +2831,10 @@
         <v>0.005149237648648912</v>
       </c>
       <c r="H42">
-        <v>0.00510835051972424</v>
+        <v>0.005361899035422927</v>
       </c>
       <c r="I42">
-        <v>0.01911287107532855</v>
+        <v>-0.1473386132259851</v>
       </c>
       <c r="J42">
         <v>0.5443564462335794</v>
@@ -2873,16 +2846,16 @@
         <v>3.87</v>
       </c>
       <c r="M42">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N42">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O42">
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -2899,7 +2872,7 @@
         <v>49</v>
       </c>
       <c r="E43">
-        <v>2.57164948027576</v>
+        <v>2.738100964577074</v>
       </c>
       <c r="F43">
         <v>-1</v>
@@ -2908,10 +2881,10 @@
         <v>0.004893027746176211</v>
       </c>
       <c r="H43">
-        <v>0.00510835051972424</v>
+        <v>0.005361899035422927</v>
       </c>
       <c r="I43">
-        <v>-0.08467722645197062</v>
+        <v>-0.2511287107532842</v>
       </c>
       <c r="J43">
         <v>0.5443564462335794</v>
@@ -2923,16 +2896,16 @@
         <v>3.69</v>
       </c>
       <c r="M43">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N43">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -2940,49 +2913,49 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C44">
-        <v>2.481528689361454</v>
+        <v>2.532536609200432</v>
       </c>
       <c r="D44" t="s">
         <v>49</v>
       </c>
       <c r="E44">
-        <v>2.57164948027576</v>
+        <v>2.738100964577074</v>
       </c>
       <c r="F44">
         <v>-1</v>
       </c>
       <c r="G44">
-        <v>0.004898471310638547</v>
+        <v>0.005047463390799568</v>
       </c>
       <c r="H44">
-        <v>0.00510835051972424</v>
+        <v>0.005361899035422927</v>
       </c>
       <c r="I44">
-        <v>-0.09012079091430625</v>
+        <v>-0.2055643553766417</v>
       </c>
       <c r="J44">
         <v>0.5443564462335794</v>
       </c>
       <c r="K44">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="L44">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="M44">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N44">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O44">
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -2996,10 +2969,10 @@
         <v>2.433094415049971</v>
       </c>
       <c r="D45" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E45">
-        <v>2.532641583382324</v>
+        <v>2.625826486380561</v>
       </c>
       <c r="F45">
         <v>-1</v>
@@ -3008,10 +2981,10 @@
         <v>0.005446905584950029</v>
       </c>
       <c r="H45">
-        <v>0.005487358416617676</v>
+        <v>0.005474173513619439</v>
       </c>
       <c r="I45">
-        <v>-0.09954716833235322</v>
+        <v>-0.1927320713305898</v>
       </c>
       <c r="J45">
         <v>0.5909433666470703</v>
@@ -3023,16 +2996,16 @@
         <v>3.94</v>
       </c>
       <c r="M45">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="N45">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="O45">
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3049,7 +3022,7 @@
         <v>49</v>
       </c>
       <c r="E46">
-        <v>2.463101955712326</v>
+        <v>2.625826486380561</v>
       </c>
       <c r="F46">
         <v>-1</v>
@@ -3058,10 +3031,10 @@
         <v>0.005258716911620615</v>
       </c>
       <c r="H46">
-        <v>0.005216898044287674</v>
+        <v>0.005474173513619439</v>
       </c>
       <c r="I46">
-        <v>0.0181811326670589</v>
+        <v>-0.1445433980011757</v>
       </c>
       <c r="J46">
         <v>0.5909433666470703</v>
@@ -3073,16 +3046,16 @@
         <v>3.87</v>
       </c>
       <c r="M46">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N46">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O46">
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3099,7 +3072,7 @@
         <v>49</v>
       </c>
       <c r="E47">
-        <v>2.463101955712326</v>
+        <v>2.625826486380561</v>
       </c>
       <c r="F47">
         <v>-1</v>
@@ -3108,10 +3081,10 @@
         <v>0.004995984840290025</v>
       </c>
       <c r="H47">
-        <v>0.005216898044287674</v>
+        <v>0.005474173513619439</v>
       </c>
       <c r="I47">
-        <v>-0.07908679600235136</v>
+        <v>-0.2418113266705859</v>
       </c>
       <c r="J47">
         <v>0.5909433666470703</v>
@@ -3123,16 +3096,16 @@
         <v>3.69</v>
       </c>
       <c r="M47">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N47">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O47">
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3149,7 +3122,7 @@
         <v>49</v>
       </c>
       <c r="E48">
-        <v>2.463101955712326</v>
+        <v>2.625826486380561</v>
       </c>
       <c r="F48">
         <v>-1</v>
@@ -3158,10 +3131,10 @@
         <v>0.005001894273956496</v>
       </c>
       <c r="H48">
-        <v>0.005216898044287674</v>
+        <v>0.005474173513619439</v>
       </c>
       <c r="I48">
-        <v>-0.08499622966882203</v>
+        <v>-0.2477207603370566</v>
       </c>
       <c r="J48">
         <v>0.5909433666470703</v>
@@ -3173,16 +3146,16 @@
         <v>3.69</v>
       </c>
       <c r="M48">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N48">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O48">
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3196,10 +3169,10 @@
         <v>2.311696741357657</v>
       </c>
       <c r="D49" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E49">
-        <v>2.413624256232997</v>
+        <v>2.511093783008609</v>
       </c>
       <c r="F49">
         <v>-1</v>
@@ -3208,10 +3181,10 @@
         <v>0.005568303258642344</v>
       </c>
       <c r="H49">
-        <v>0.005606375743767004</v>
+        <v>0.005588906216991391</v>
       </c>
       <c r="I49">
-        <v>-0.10192751487534</v>
+        <v>-0.1993970416509523</v>
       </c>
       <c r="J49">
         <v>0.6385502975068013</v>
@@ -3223,16 +3196,16 @@
         <v>3.94</v>
       </c>
       <c r="M49">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="N49">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="O49">
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3249,7 +3222,7 @@
         <v>49</v>
       </c>
       <c r="E50">
-        <v>2.352177806809153</v>
+        <v>2.511093783008609</v>
       </c>
       <c r="F50">
         <v>-1</v>
@@ -3258,10 +3231,10 @@
         <v>0.005370593199140983</v>
       </c>
       <c r="H50">
-        <v>0.005327822193190846</v>
+        <v>0.005588906216991391</v>
       </c>
       <c r="I50">
-        <v>0.017228994049864</v>
+        <v>-0.1416869821495919</v>
       </c>
       <c r="J50">
         <v>0.6385502975068013</v>
@@ -3273,16 +3246,16 @@
         <v>3.87</v>
       </c>
       <c r="M50">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N50">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O50">
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3299,7 +3272,7 @@
         <v>49</v>
       </c>
       <c r="E51">
-        <v>2.352177806809153</v>
+        <v>2.511093783008609</v>
       </c>
       <c r="F51">
         <v>-1</v>
@@ -3308,10 +3281,10 @@
         <v>0.005101196157490031</v>
       </c>
       <c r="H51">
-        <v>0.005327822193190846</v>
+        <v>0.005588906216991391</v>
       </c>
       <c r="I51">
-        <v>-0.07337396429918375</v>
+        <v>-0.2322899404986396</v>
       </c>
       <c r="J51">
         <v>0.6385502975068013</v>
@@ -3323,16 +3296,16 @@
         <v>3.69</v>
       </c>
       <c r="M51">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N51">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O51">
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3349,7 +3322,7 @@
         <v>49</v>
       </c>
       <c r="E52">
-        <v>2.352177806809153</v>
+        <v>2.511093783008609</v>
       </c>
       <c r="F52">
         <v>-1</v>
@@ -3358,10 +3331,10 @@
         <v>0.005107581660465099</v>
       </c>
       <c r="H52">
-        <v>0.005327822193190846</v>
+        <v>0.005588906216991391</v>
       </c>
       <c r="I52">
-        <v>-0.07975946727425187</v>
+        <v>-0.2386754434737077</v>
       </c>
       <c r="J52">
         <v>0.6385502975068013</v>
@@ -3373,16 +3346,16 @@
         <v>3.69</v>
       </c>
       <c r="M52">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N52">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O52">
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3396,10 +3369,10 @@
         <v>2.182359258383708</v>
       </c>
       <c r="D53" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E53">
-        <v>2.286822802336969</v>
+        <v>2.388857181452837</v>
       </c>
       <c r="F53">
         <v>-1</v>
@@ -3408,10 +3381,10 @@
         <v>0.005697640741616292</v>
       </c>
       <c r="H53">
-        <v>0.005733177197663031</v>
+        <v>0.005711142818547162</v>
       </c>
       <c r="I53">
-        <v>-0.1044635439532606</v>
+        <v>-0.2064979230691293</v>
       </c>
       <c r="J53">
         <v>0.6892708790652124</v>
@@ -3423,16 +3396,16 @@
         <v>3.94</v>
       </c>
       <c r="M53">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="N53">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="O53">
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3449,7 +3422,7 @@
         <v>49</v>
       </c>
       <c r="E54">
-        <v>2.233998851778055</v>
+        <v>2.388857181452837</v>
       </c>
       <c r="F54">
         <v>-1</v>
@@ -3458,10 +3431,10 @@
         <v>0.00548978656580325</v>
       </c>
       <c r="H54">
-        <v>0.005446001148221945</v>
+        <v>0.005711142818547162</v>
       </c>
       <c r="I54">
-        <v>0.01621458241869611</v>
+        <v>-0.1386437472560864</v>
       </c>
       <c r="J54">
         <v>0.6892708790652124</v>
@@ -3473,16 +3446,16 @@
         <v>3.87</v>
       </c>
       <c r="M54">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N54">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O54">
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3499,7 +3472,7 @@
         <v>49</v>
       </c>
       <c r="E55">
-        <v>2.233998851778055</v>
+        <v>2.388857181452837</v>
       </c>
       <c r="F55">
         <v>-1</v>
@@ -3508,10 +3481,10 @@
         <v>0.005213288642734119</v>
       </c>
       <c r="H55">
-        <v>0.005446001148221945</v>
+        <v>0.005711142818547162</v>
       </c>
       <c r="I55">
-        <v>-0.06728749451217464</v>
+        <v>-0.2221458241869572</v>
       </c>
       <c r="J55">
         <v>0.6892708790652124</v>
@@ -3523,16 +3496,16 @@
         <v>3.69</v>
       </c>
       <c r="M55">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N55">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O55">
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3540,49 +3513,49 @@
         <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C56">
-        <v>2.159818648475228</v>
+        <v>2.197784269359359</v>
       </c>
       <c r="D56" t="s">
         <v>49</v>
       </c>
       <c r="E56">
-        <v>2.233998851778055</v>
+        <v>2.388857181452837</v>
       </c>
       <c r="F56">
         <v>-1</v>
       </c>
       <c r="G56">
-        <v>0.005220181351524772</v>
+        <v>0.005382215730640641</v>
       </c>
       <c r="H56">
-        <v>0.005446001148221945</v>
+        <v>0.005711142818547162</v>
       </c>
       <c r="I56">
-        <v>-0.07418020330282671</v>
+        <v>-0.1910729120934782</v>
       </c>
       <c r="J56">
         <v>0.6892708790652124</v>
       </c>
       <c r="K56">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="L56">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="M56">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N56">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O56">
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3590,49 +3563,49 @@
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C57">
-        <v>2.037699170124481</v>
+        <v>2.050989626556016</v>
       </c>
       <c r="D57" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E57">
-        <v>1.775843983402489</v>
+        <v>2.264699999999999</v>
       </c>
       <c r="F57">
         <v>-1</v>
       </c>
       <c r="G57">
-        <v>0.004482300829875518</v>
+        <v>0.005829010373443984</v>
       </c>
       <c r="H57">
-        <v>0.004324156016597511</v>
+        <v>0.0058353</v>
       </c>
       <c r="I57">
-        <v>0.2618551867219918</v>
+        <v>-0.2137103734439831</v>
       </c>
       <c r="J57">
         <v>0.7407883817427386</v>
       </c>
       <c r="K57">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="L57">
-        <v>3.26</v>
+        <v>3.94</v>
       </c>
       <c r="M57">
-        <v>1.72</v>
+        <v>2.41</v>
       </c>
       <c r="N57">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="O57">
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3640,49 +3613,49 @@
         <v>1</v>
       </c>
       <c r="B58" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C58">
-        <v>2.047699170124481</v>
+        <v>2.129147302904564</v>
       </c>
       <c r="D58" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E58">
-        <v>1.775843983402489</v>
+        <v>2.264699999999999</v>
       </c>
       <c r="F58">
         <v>-1</v>
       </c>
       <c r="G58">
-        <v>0.004492300829875518</v>
+        <v>0.005610852697095436</v>
       </c>
       <c r="H58">
-        <v>0.004324156016597511</v>
+        <v>0.0058353</v>
       </c>
       <c r="I58">
-        <v>0.271855186721992</v>
+        <v>-0.1355526970954353</v>
       </c>
       <c r="J58">
         <v>0.7407883817427386</v>
       </c>
       <c r="K58">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="L58">
-        <v>3.27</v>
+        <v>3.87</v>
       </c>
       <c r="M58">
-        <v>1.72</v>
+        <v>2.41</v>
       </c>
       <c r="N58">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="O58">
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3690,49 +3663,49 @@
         <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C59">
-        <v>2.050989626556016</v>
+        <v>2.052857676348547</v>
       </c>
       <c r="D59" t="s">
         <v>49</v>
       </c>
       <c r="E59">
-        <v>2.113963070539419</v>
+        <v>2.264699999999999</v>
       </c>
       <c r="F59">
         <v>-1</v>
       </c>
       <c r="G59">
-        <v>0.005829010373443984</v>
+        <v>0.005327142323651453</v>
       </c>
       <c r="H59">
-        <v>0.005566036929460581</v>
+        <v>0.0058353</v>
       </c>
       <c r="I59">
-        <v>-0.06297344398340243</v>
+        <v>-0.2118423236514522</v>
       </c>
       <c r="J59">
         <v>0.7407883817427386</v>
       </c>
       <c r="K59">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="L59">
-        <v>3.94</v>
+        <v>3.69</v>
       </c>
       <c r="M59">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N59">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O59">
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -3740,1299 +3713,1299 @@
         <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C60">
-        <v>2.129147302904564</v>
+        <v>2.078778838174274</v>
       </c>
       <c r="D60" t="s">
         <v>49</v>
       </c>
       <c r="E60">
-        <v>2.113963070539419</v>
+        <v>2.264699999999999</v>
       </c>
       <c r="F60">
         <v>-1</v>
       </c>
       <c r="G60">
-        <v>0.005610852697095436</v>
+        <v>0.005501221161825726</v>
       </c>
       <c r="H60">
-        <v>0.005566036929460581</v>
+        <v>0.0058353</v>
       </c>
       <c r="I60">
-        <v>0.01518423236514543</v>
+        <v>-0.1859211618257257</v>
       </c>
       <c r="J60">
         <v>0.7407883817427386</v>
       </c>
       <c r="K60">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="L60">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="M60">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N60">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O60">
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C61">
-        <v>2.052857676348547</v>
+        <v>1.939614977812812</v>
       </c>
       <c r="D61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E61">
-        <v>2.113963070539419</v>
+        <v>1.673598643538204</v>
       </c>
       <c r="F61">
         <v>-1</v>
       </c>
       <c r="G61">
-        <v>0.005327142323651453</v>
+        <v>0.004580385022187188</v>
       </c>
       <c r="H61">
-        <v>0.005566036929460581</v>
+        <v>0.004426401356461797</v>
       </c>
       <c r="I61">
-        <v>-0.06110539419087146</v>
+        <v>0.266016334274608</v>
       </c>
       <c r="J61">
-        <v>0.7407883817427386</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K61">
-        <v>2.21</v>
+        <v>1.65</v>
       </c>
       <c r="L61">
-        <v>3.69</v>
+        <v>3.26</v>
       </c>
       <c r="M61">
-        <v>2.33</v>
+        <v>1.72</v>
       </c>
       <c r="N61">
-        <v>3.84</v>
+        <v>3.05</v>
       </c>
       <c r="O61">
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:16">
       <c r="A62" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C62">
-        <v>2.04544979253112</v>
+        <v>1.949614977812812</v>
       </c>
       <c r="D62" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E62">
-        <v>2.113963070539419</v>
+        <v>1.673598643538204</v>
       </c>
       <c r="F62">
         <v>-1</v>
       </c>
       <c r="G62">
-        <v>0.005334550207468879</v>
+        <v>0.004590385022187188</v>
       </c>
       <c r="H62">
-        <v>0.005566036929460581</v>
+        <v>0.004426401356461797</v>
       </c>
       <c r="I62">
-        <v>-0.06851327800829887</v>
+        <v>0.2760163342746083</v>
       </c>
       <c r="J62">
-        <v>0.7407883817427386</v>
+        <v>0.8002333467801142</v>
       </c>
       <c r="K62">
-        <v>2.22</v>
+        <v>1.65</v>
       </c>
       <c r="L62">
-        <v>3.69</v>
+        <v>3.27</v>
       </c>
       <c r="M62">
-        <v>2.33</v>
+        <v>1.72</v>
       </c>
       <c r="N62">
-        <v>3.84</v>
+        <v>3.05</v>
       </c>
       <c r="O62">
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63" spans="1:16">
       <c r="A63" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B63" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C63">
-        <v>1.939614977812812</v>
+        <v>2.009416633049714</v>
       </c>
       <c r="D63" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E63">
-        <v>1.637628978619619</v>
+        <v>2.121437634259925</v>
       </c>
       <c r="F63">
         <v>-1</v>
       </c>
       <c r="G63">
-        <v>0.004580385022187188</v>
+        <v>0.006010583366950286</v>
       </c>
       <c r="H63">
-        <v>0.004182371021380382</v>
+        <v>0.005978562365740075</v>
       </c>
       <c r="I63">
-        <v>0.301985999193193</v>
+        <v>-0.1120210012102105</v>
       </c>
       <c r="J63">
         <v>0.8002333467801142</v>
       </c>
       <c r="K63">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="L63">
-        <v>3.26</v>
+        <v>4.01</v>
       </c>
       <c r="M63">
-        <v>1.59</v>
+        <v>2.41</v>
       </c>
       <c r="N63">
-        <v>2.91</v>
+        <v>4.05</v>
       </c>
       <c r="O63">
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C64">
-        <v>2.009416633049714</v>
+        <v>1.989451635066732</v>
       </c>
       <c r="D64" t="s">
         <v>49</v>
       </c>
       <c r="E64">
-        <v>1.975456302002334</v>
+        <v>2.121437634259925</v>
       </c>
       <c r="F64">
         <v>-1</v>
       </c>
       <c r="G64">
-        <v>0.006010583366950286</v>
+        <v>0.005750548364933269</v>
       </c>
       <c r="H64">
-        <v>0.005704543697997666</v>
+        <v>0.005978562365740075</v>
       </c>
       <c r="I64">
-        <v>0.03396033104738039</v>
+        <v>-0.1319859991931931</v>
       </c>
       <c r="J64">
         <v>0.8002333467801142</v>
       </c>
       <c r="K64">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L64">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M64">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N64">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O64">
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B65" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C65">
-        <v>1.989451635066732</v>
+        <v>1.941460968937936</v>
       </c>
       <c r="D65" t="s">
         <v>49</v>
       </c>
       <c r="E65">
-        <v>1.975456302002334</v>
+        <v>2.121437634259925</v>
       </c>
       <c r="F65">
         <v>-1</v>
       </c>
       <c r="G65">
-        <v>0.005750548364933269</v>
+        <v>0.005638539031062064</v>
       </c>
       <c r="H65">
-        <v>0.005704543697997666</v>
+        <v>0.005978562365740075</v>
       </c>
       <c r="I65">
-        <v>0.01399533306439782</v>
+        <v>-0.1799766653219885</v>
       </c>
       <c r="J65">
         <v>0.8002333467801142</v>
       </c>
       <c r="K65">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="L65">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="M65">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N65">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O65">
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C66">
-        <v>1.921484303615948</v>
+        <v>1.858458903856472</v>
       </c>
       <c r="D66" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E66">
-        <v>1.975456302002334</v>
+        <v>1.559424034625328</v>
       </c>
       <c r="F66">
         <v>-1</v>
       </c>
       <c r="G66">
-        <v>0.005458515696384052</v>
+        <v>0.004661541096143528</v>
       </c>
       <c r="H66">
-        <v>0.005704543697997666</v>
+        <v>0.004260575965374673</v>
       </c>
       <c r="I66">
-        <v>-0.05397199838638622</v>
+        <v>0.2990348692311444</v>
       </c>
       <c r="J66">
-        <v>0.8002333467801142</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K66">
-        <v>2.21</v>
+        <v>1.65</v>
       </c>
       <c r="L66">
-        <v>3.69</v>
+        <v>3.26</v>
       </c>
       <c r="M66">
-        <v>2.33</v>
+        <v>1.59</v>
       </c>
       <c r="N66">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="O66">
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="1:16">
       <c r="A67" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B67" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C67">
-        <v>1.913481970148146</v>
+        <v>1.886452884631018</v>
       </c>
       <c r="D67" t="s">
         <v>49</v>
       </c>
       <c r="E67">
-        <v>1.975456302002334</v>
+        <v>2.002900580784301</v>
       </c>
       <c r="F67">
         <v>-1</v>
       </c>
       <c r="G67">
-        <v>0.005466518029851854</v>
+        <v>0.006133547115368982</v>
       </c>
       <c r="H67">
-        <v>0.005704543697997666</v>
+        <v>0.006097099419215699</v>
       </c>
       <c r="I67">
-        <v>-0.06197433185418744</v>
+        <v>-0.1164476961532834</v>
       </c>
       <c r="J67">
-        <v>0.8002333467801142</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K67">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="L67">
-        <v>3.69</v>
+        <v>4.01</v>
       </c>
       <c r="M67">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N67">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O67">
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68" spans="1:16">
       <c r="A68" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C68">
-        <v>1.858458903856472</v>
+        <v>1.873865711553157</v>
       </c>
       <c r="D68" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E68">
-        <v>1.559424034625328</v>
+        <v>2.002900580784301</v>
       </c>
       <c r="F68">
         <v>-1</v>
       </c>
       <c r="G68">
-        <v>0.004661541096143528</v>
+        <v>0.005866134288446843</v>
       </c>
       <c r="H68">
-        <v>0.004260575965374673</v>
+        <v>0.006097099419215699</v>
       </c>
       <c r="I68">
-        <v>0.2990348692311444</v>
+        <v>-0.1290348692311443</v>
       </c>
       <c r="J68">
         <v>0.8494188461475927</v>
       </c>
       <c r="K68">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="L68">
-        <v>3.26</v>
+        <v>3.87</v>
       </c>
       <c r="M68">
-        <v>1.59</v>
+        <v>2.41</v>
       </c>
       <c r="N68">
-        <v>2.91</v>
+        <v>4.05</v>
       </c>
       <c r="O68">
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B69" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C69">
-        <v>1.886452884631018</v>
+        <v>1.827842465399061</v>
       </c>
       <c r="D69" t="s">
         <v>49</v>
       </c>
       <c r="E69">
-        <v>1.860854088476109</v>
+        <v>2.002900580784301</v>
       </c>
       <c r="F69">
         <v>-1</v>
       </c>
       <c r="G69">
-        <v>0.006133547115368982</v>
+        <v>0.005752157534600939</v>
       </c>
       <c r="H69">
-        <v>0.005819145911523891</v>
+        <v>0.006097099419215699</v>
       </c>
       <c r="I69">
-        <v>0.02559879615490912</v>
+        <v>-0.1750581153852404</v>
       </c>
       <c r="J69">
         <v>0.8494188461475927</v>
       </c>
       <c r="K69">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="L69">
-        <v>4.01</v>
+        <v>3.79</v>
       </c>
       <c r="M69">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N69">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O69">
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B70" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C70">
-        <v>1.873865711553157</v>
+        <v>1.860854088476109</v>
       </c>
       <c r="D70" t="s">
         <v>49</v>
       </c>
       <c r="E70">
-        <v>1.860854088476109</v>
+        <v>2.002900580784301</v>
       </c>
       <c r="F70">
         <v>-1</v>
       </c>
       <c r="G70">
-        <v>0.005866134288446843</v>
+        <v>0.005819145911523891</v>
       </c>
       <c r="H70">
-        <v>0.005819145911523891</v>
+        <v>0.006097099419215699</v>
       </c>
       <c r="I70">
-        <v>0.01301162307704828</v>
+        <v>-0.1420464923081926</v>
       </c>
       <c r="J70">
         <v>0.8494188461475927</v>
       </c>
       <c r="K70">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="L70">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="M70">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N70">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O70">
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C71">
-        <v>1.81278435001382</v>
+        <v>1.778043160662217</v>
       </c>
       <c r="D71" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E71">
-        <v>1.860854088476109</v>
+        <v>1.4819325002745</v>
       </c>
       <c r="F71">
         <v>-1</v>
       </c>
       <c r="G71">
-        <v>0.00556721564998618</v>
+        <v>0.004741956839337784</v>
       </c>
       <c r="H71">
-        <v>0.005819145911523891</v>
+        <v>0.004338067499725501</v>
       </c>
       <c r="I71">
-        <v>-0.04806973846228879</v>
+        <v>0.2961106603877166</v>
       </c>
       <c r="J71">
-        <v>0.8494188461475927</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K71">
-        <v>2.21</v>
+        <v>1.65</v>
       </c>
       <c r="L71">
-        <v>3.69</v>
+        <v>3.26</v>
       </c>
       <c r="M71">
-        <v>2.33</v>
+        <v>1.59</v>
       </c>
       <c r="N71">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="O71">
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B72" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C72">
-        <v>1.827842465399061</v>
+        <v>1.253223538131198</v>
       </c>
       <c r="D72" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E72">
-        <v>1.860854088476109</v>
+        <v>1.508412028621273</v>
       </c>
       <c r="F72">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G72">
-        <v>0.005752157534600939</v>
+        <v>0.005366776461868803</v>
       </c>
       <c r="H72">
-        <v>0.005819145911523891</v>
+        <v>0.004831587971378727</v>
       </c>
       <c r="I72">
-        <v>-0.03301162307704786</v>
+        <v>0.2551884904900752</v>
       </c>
       <c r="J72">
-        <v>0.8494188461475927</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K72">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="L72">
-        <v>3.79</v>
+        <v>3.31</v>
       </c>
       <c r="M72">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="N72">
-        <v>3.84</v>
+        <v>3.17</v>
       </c>
       <c r="O72">
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C73">
-        <v>1.778043160662217</v>
+        <v>1.764610849488207</v>
       </c>
       <c r="D73" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E73">
-        <v>1.4819325002745</v>
+        <v>1.885444858906632</v>
       </c>
       <c r="F73">
         <v>-1</v>
       </c>
       <c r="G73">
-        <v>0.004741956839337784</v>
+        <v>0.006255389150511792</v>
       </c>
       <c r="H73">
-        <v>0.004338067499725501</v>
+        <v>0.006214555141093368</v>
       </c>
       <c r="I73">
-        <v>0.2961106603877166</v>
+        <v>-0.1208340094184246</v>
       </c>
       <c r="J73">
         <v>0.898155660204717</v>
       </c>
       <c r="K73">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="L73">
-        <v>3.26</v>
+        <v>4.01</v>
       </c>
       <c r="M73">
-        <v>1.59</v>
+        <v>2.41</v>
       </c>
       <c r="N73">
-        <v>2.91</v>
+        <v>4.05</v>
       </c>
       <c r="O73">
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="74" spans="1:16">
       <c r="A74" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B74" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C74">
-        <v>1.253223538131198</v>
+        <v>1.759334198518915</v>
       </c>
       <c r="D74" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E74">
-        <v>1.508412028621273</v>
+        <v>1.885444858906632</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G74">
-        <v>0.005366776461868803</v>
+        <v>0.005980665801481085</v>
       </c>
       <c r="H74">
-        <v>0.004831587971378727</v>
+        <v>0.006214555141093368</v>
       </c>
       <c r="I74">
-        <v>0.2551884904900752</v>
+        <v>-0.1261106603877167</v>
       </c>
       <c r="J74">
         <v>0.898155660204717</v>
       </c>
       <c r="K74">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="L74">
-        <v>3.31</v>
+        <v>3.87</v>
       </c>
       <c r="M74">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="N74">
-        <v>3.17</v>
+        <v>4.05</v>
       </c>
       <c r="O74">
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B75" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C75">
-        <v>1.764610849488207</v>
+        <v>1.747297311723009</v>
       </c>
       <c r="D75" t="s">
         <v>49</v>
       </c>
       <c r="E75">
-        <v>1.747297311723009</v>
+        <v>1.885444858906632</v>
       </c>
       <c r="F75">
         <v>-1</v>
       </c>
       <c r="G75">
-        <v>0.006255389150511792</v>
+        <v>0.00593270268827699</v>
       </c>
       <c r="H75">
-        <v>0.00593270268827699</v>
+        <v>0.006214555141093368</v>
       </c>
       <c r="I75">
-        <v>0.01731353776519784</v>
+        <v>-0.1381475471836224</v>
       </c>
       <c r="J75">
         <v>0.898155660204717</v>
       </c>
       <c r="K75">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="L75">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="M75">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N75">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O75">
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C76">
-        <v>1.759334198518915</v>
+        <v>1.698438247560837</v>
       </c>
       <c r="D76" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E76">
-        <v>1.747297311723009</v>
+        <v>1.372006375010957</v>
       </c>
       <c r="F76">
         <v>-1</v>
       </c>
       <c r="G76">
-        <v>0.005980665801481085</v>
+        <v>0.004821561752439162</v>
       </c>
       <c r="H76">
-        <v>0.00593270268827699</v>
+        <v>0.004267993624989043</v>
       </c>
       <c r="I76">
-        <v>0.01203688679590575</v>
+        <v>0.3264318725498792</v>
       </c>
       <c r="J76">
-        <v>0.898155660204717</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K76">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="L76">
-        <v>3.87</v>
+        <v>3.26</v>
       </c>
       <c r="M76">
-        <v>2.33</v>
+        <v>1.53</v>
       </c>
       <c r="N76">
-        <v>3.84</v>
+        <v>2.82</v>
       </c>
       <c r="O76">
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B77" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C77">
-        <v>1.715260424927104</v>
+        <v>1.142741567826858</v>
       </c>
       <c r="D77" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E77">
-        <v>1.747297311723009</v>
+        <v>1.419158035143968</v>
       </c>
       <c r="F77">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>0.005864739575072896</v>
+        <v>0.005477258432173141</v>
       </c>
       <c r="H77">
-        <v>0.00593270268827699</v>
+        <v>0.004920841964856031</v>
       </c>
       <c r="I77">
-        <v>-0.03203688679590577</v>
+        <v>0.2764164673171099</v>
       </c>
       <c r="J77">
-        <v>0.898155660204717</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K77">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="L77">
-        <v>3.79</v>
+        <v>3.31</v>
       </c>
       <c r="M77">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="N77">
-        <v>3.84</v>
+        <v>3.17</v>
       </c>
       <c r="O77">
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C78">
-        <v>1.698438247560837</v>
+        <v>1.643997344789146</v>
       </c>
       <c r="D78" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E78">
-        <v>1.372006375010957</v>
+        <v>1.769173440376737</v>
       </c>
       <c r="F78">
         <v>-1</v>
       </c>
       <c r="G78">
-        <v>0.004821561752439162</v>
+        <v>0.006376002655210854</v>
       </c>
       <c r="H78">
-        <v>0.004267993624989043</v>
+        <v>0.006330826559623264</v>
       </c>
       <c r="I78">
-        <v>0.3264318725498792</v>
+        <v>-0.1251760955875905</v>
       </c>
       <c r="J78">
         <v>0.9464010620843414</v>
       </c>
       <c r="K78">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="L78">
-        <v>3.26</v>
+        <v>4.01</v>
       </c>
       <c r="M78">
-        <v>1.53</v>
+        <v>2.41</v>
       </c>
       <c r="N78">
-        <v>2.82</v>
+        <v>4.05</v>
       </c>
       <c r="O78">
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="79" spans="1:16">
       <c r="A79" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B79" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C79">
-        <v>1.142741567826858</v>
+        <v>1.645957504101798</v>
       </c>
       <c r="D79" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E79">
-        <v>1.419158035143968</v>
+        <v>1.769173440376737</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G79">
-        <v>0.005477258432173141</v>
+        <v>0.006094042495898203</v>
       </c>
       <c r="H79">
-        <v>0.004920841964856031</v>
+        <v>0.006330826559623264</v>
       </c>
       <c r="I79">
-        <v>0.2764164673171099</v>
+        <v>-0.123215936274939</v>
       </c>
       <c r="J79">
         <v>0.9464010620843414</v>
       </c>
       <c r="K79">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="L79">
-        <v>3.31</v>
+        <v>3.87</v>
       </c>
       <c r="M79">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="N79">
-        <v>3.17</v>
+        <v>4.05</v>
       </c>
       <c r="O79">
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B80" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C80">
-        <v>1.643997344789146</v>
+        <v>1.634885525343484</v>
       </c>
       <c r="D80" t="s">
         <v>49</v>
       </c>
       <c r="E80">
-        <v>1.634885525343484</v>
+        <v>1.769173440376737</v>
       </c>
       <c r="F80">
         <v>-1</v>
       </c>
       <c r="G80">
-        <v>0.006376002655210854</v>
+        <v>0.006045114474656515</v>
       </c>
       <c r="H80">
-        <v>0.006045114474656515</v>
+        <v>0.006330826559623264</v>
       </c>
       <c r="I80">
-        <v>0.009111819445661862</v>
+        <v>-0.1342879150332523</v>
       </c>
       <c r="J80">
         <v>0.9464010620843414</v>
       </c>
       <c r="K80">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="L80">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="M80">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N80">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O80">
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="81" spans="1:16">
       <c r="A81" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C81">
-        <v>1.645957504101798</v>
+        <v>1.613410205419267</v>
       </c>
       <c r="D81" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E81">
-        <v>1.634885525343484</v>
+        <v>1.293162190479684</v>
       </c>
       <c r="F81">
         <v>-1</v>
       </c>
       <c r="G81">
-        <v>0.006094042495898203</v>
+        <v>0.004906589794580732</v>
       </c>
       <c r="H81">
-        <v>0.006045114474656515</v>
+        <v>0.004346837809520315</v>
       </c>
       <c r="I81">
-        <v>0.01107197875831334</v>
+        <v>0.320248014939583</v>
       </c>
       <c r="J81">
-        <v>0.9464010620843414</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K81">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="L81">
-        <v>3.87</v>
+        <v>3.26</v>
       </c>
       <c r="M81">
-        <v>2.33</v>
+        <v>1.53</v>
       </c>
       <c r="N81">
-        <v>3.84</v>
+        <v>2.82</v>
       </c>
       <c r="O81">
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="82" spans="1:16">
       <c r="A82" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C82">
-        <v>1.613410205419267</v>
+        <v>1.02473295176371</v>
       </c>
       <c r="D82" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E82">
-        <v>1.623410205419267</v>
+        <v>1.323823563651905</v>
       </c>
       <c r="F82">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G82">
-        <v>0.004906589794580732</v>
+        <v>0.005595267048236289</v>
       </c>
       <c r="H82">
-        <v>0.004916589794580733</v>
+        <v>0.005016176436348095</v>
       </c>
       <c r="I82">
-        <v>-0.01000000000000023</v>
+        <v>0.2990906118881951</v>
       </c>
       <c r="J82">
         <v>0.9979332088368078</v>
       </c>
       <c r="K82">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="L82">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="M82">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="N82">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="O82">
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B83" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C83">
-        <v>1.02473295176371</v>
+        <v>1.524856959233502</v>
       </c>
       <c r="D83" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E83">
-        <v>1.323823563651905</v>
+        <v>1.644980966703293</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G83">
-        <v>0.005595267048236289</v>
+        <v>0.006215143040766499</v>
       </c>
       <c r="H83">
-        <v>0.005016176436348095</v>
+        <v>0.006455019033296707</v>
       </c>
       <c r="I83">
-        <v>0.2990906118881951</v>
+        <v>-0.1201240074697911</v>
       </c>
       <c r="J83">
         <v>0.9979332088368078</v>
       </c>
       <c r="K83">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="L83">
-        <v>3.31</v>
+        <v>3.87</v>
       </c>
       <c r="M83">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="N83">
-        <v>3.17</v>
+        <v>4.05</v>
       </c>
       <c r="O83">
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C84">
-        <v>1.51516697790798</v>
+        <v>1.563582758846789</v>
       </c>
       <c r="D84" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E84">
-        <v>1.514815623410238</v>
+        <v>1.198083824655585</v>
       </c>
       <c r="F84">
         <v>-1</v>
       </c>
       <c r="G84">
-        <v>0.00650483302209202</v>
+        <v>0.004956417241153211</v>
       </c>
       <c r="H84">
-        <v>0.006165184376589762</v>
+        <v>0.004261916175344414</v>
       </c>
       <c r="I84">
-        <v>0.0003513544977424843</v>
+        <v>0.3654989341912036</v>
       </c>
       <c r="J84">
-        <v>0.9979332088368078</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K84">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="L84">
-        <v>4.01</v>
+        <v>3.26</v>
       </c>
       <c r="M84">
-        <v>2.33</v>
+        <v>1.49</v>
       </c>
       <c r="N84">
-        <v>3.84</v>
+        <v>2.73</v>
       </c>
       <c r="O84">
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" spans="1:16">
       <c r="A85" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B85" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C85">
-        <v>1.524856959233502</v>
+        <v>0.9555784956116042</v>
       </c>
       <c r="D85" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E85">
-        <v>1.514815623410238</v>
+        <v>1.267956426585794</v>
       </c>
       <c r="F85">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G85">
-        <v>0.006215143040766499</v>
+        <v>0.005664421504388396</v>
       </c>
       <c r="H85">
-        <v>0.006165184376589762</v>
+        <v>0.005072043573414206</v>
       </c>
       <c r="I85">
-        <v>0.01004133582326405</v>
+        <v>0.3123779309741896</v>
       </c>
       <c r="J85">
-        <v>0.9979332088368078</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K85">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="L85">
-        <v>3.87</v>
+        <v>3.31</v>
       </c>
       <c r="M85">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="N85">
-        <v>3.84</v>
+        <v>3.17</v>
       </c>
       <c r="O85">
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5040,31 +5013,31 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C86">
-        <v>1.563582758846789</v>
+        <v>1.51276870292658</v>
       </c>
       <c r="D86" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E86">
-        <v>1.573582758846789</v>
+        <v>1.522768702926581</v>
       </c>
       <c r="F86">
         <v>-1</v>
       </c>
       <c r="G86">
-        <v>0.004956417241153211</v>
+        <v>0.00500723129707342</v>
       </c>
       <c r="H86">
-        <v>0.004966417241153211</v>
+        <v>0.005017231297073419</v>
       </c>
       <c r="I86">
         <v>-0.01000000000000023</v>
       </c>
       <c r="J86">
-        <v>1.028131661304976</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K86">
         <v>1.65</v>
@@ -5082,7 +5055,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5090,31 +5063,31 @@
         <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C87">
-        <v>1.025578495611604</v>
+        <v>0.95505474527386</v>
       </c>
       <c r="D87" t="s">
         <v>52</v>
       </c>
       <c r="E87">
-        <v>1.267956426585794</v>
+        <v>1.210983091160105</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87">
-        <v>0.005734421504388396</v>
+        <v>0.00580494525472614</v>
       </c>
       <c r="H87">
-        <v>0.005072043573414206</v>
+        <v>0.005129016908839895</v>
       </c>
       <c r="I87">
-        <v>0.2423779309741898</v>
+        <v>0.2559283458862451</v>
       </c>
       <c r="J87">
-        <v>1.028131661304976</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K87">
         <v>2.29</v>
@@ -5132,7 +5105,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5140,31 +5113,31 @@
         <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C88">
-        <v>0.95505474527386</v>
+        <v>0.8997461387005035</v>
       </c>
       <c r="D88" t="s">
         <v>52</v>
       </c>
       <c r="E88">
-        <v>1.210983091160105</v>
+        <v>1.166301465762415</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88">
-        <v>0.00580494525472614</v>
+        <v>0.005860253861299496</v>
       </c>
       <c r="H88">
-        <v>0.005129016908839895</v>
+        <v>0.005173698534237585</v>
       </c>
       <c r="I88">
-        <v>0.2559283458862451</v>
+        <v>0.2665553270619117</v>
       </c>
       <c r="J88">
-        <v>1.058928058832376</v>
+        <v>1.083080288777073</v>
       </c>
       <c r="K88">
         <v>2.29</v>
@@ -5182,7 +5155,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5190,31 +5163,31 @@
         <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C89">
-        <v>0.8997461387005035</v>
+        <v>0.9004291893178089</v>
       </c>
       <c r="D89" t="s">
         <v>52</v>
       </c>
       <c r="E89">
-        <v>1.166301465762415</v>
+        <v>1.166853275213077</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89">
-        <v>0.005860253861299496</v>
+        <v>0.005859570810682191</v>
       </c>
       <c r="H89">
-        <v>0.005173698534237585</v>
+        <v>0.005173146724786923</v>
       </c>
       <c r="I89">
-        <v>0.2665553270619117</v>
+        <v>0.2664240858952684</v>
       </c>
       <c r="J89">
-        <v>1.083080288777073</v>
+        <v>1.082782013398337</v>
       </c>
       <c r="K89">
         <v>2.29</v>
@@ -5232,7 +5205,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5240,31 +5213,31 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C90">
-        <v>0.9004291893178089</v>
+        <v>0.8995341152947529</v>
       </c>
       <c r="D90" t="s">
         <v>52</v>
       </c>
       <c r="E90">
-        <v>1.166853275213077</v>
+        <v>1.166130180478294</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90">
-        <v>0.005859570810682191</v>
+        <v>0.005860465884705247</v>
       </c>
       <c r="H90">
-        <v>0.005173146724786923</v>
+        <v>0.005173869819521706</v>
       </c>
       <c r="I90">
-        <v>0.2664240858952684</v>
+        <v>0.2665960651835411</v>
       </c>
       <c r="J90">
-        <v>1.082782013398337</v>
+        <v>1.083172875417138</v>
       </c>
       <c r="K90">
         <v>2.29</v>
@@ -5282,7 +5255,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5290,31 +5263,31 @@
         <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C91">
-        <v>0.8995341152947529</v>
+        <v>0.8942975364165378</v>
       </c>
       <c r="D91" t="s">
         <v>52</v>
       </c>
       <c r="E91">
-        <v>1.166130180478294</v>
+        <v>1.161899756493709</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="G91">
-        <v>0.005860465884705247</v>
+        <v>0.005865702463583462</v>
       </c>
       <c r="H91">
-        <v>0.005173869819521706</v>
+        <v>0.00517810024350629</v>
       </c>
       <c r="I91">
-        <v>0.2665960651835411</v>
+        <v>0.2676022200771717</v>
       </c>
       <c r="J91">
-        <v>1.083172875417138</v>
+        <v>1.085459591084481</v>
       </c>
       <c r="K91">
         <v>2.29</v>
@@ -5332,7 +5305,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5340,31 +5313,31 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C92">
-        <v>0.8942975364165378</v>
+        <v>0.823882990348408</v>
       </c>
       <c r="D92" t="s">
         <v>52</v>
       </c>
       <c r="E92">
-        <v>1.161899756493709</v>
+        <v>1.105014642857884</v>
       </c>
       <c r="F92">
         <v>1</v>
       </c>
       <c r="G92">
-        <v>0.005865702463583462</v>
+        <v>0.005936117009651592</v>
       </c>
       <c r="H92">
-        <v>0.00517810024350629</v>
+        <v>0.005234985357142116</v>
       </c>
       <c r="I92">
-        <v>0.2676022200771717</v>
+        <v>0.281131652509476</v>
       </c>
       <c r="J92">
-        <v>1.085459591084481</v>
+        <v>1.1162083011579</v>
       </c>
       <c r="K92">
         <v>2.29</v>
@@ -5382,7 +5355,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5390,31 +5363,31 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C93">
-        <v>0.823882990348408</v>
+        <v>0.7552208383877499</v>
       </c>
       <c r="D93" t="s">
         <v>52</v>
       </c>
       <c r="E93">
-        <v>1.105014642857884</v>
+        <v>1.049545218784863</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93">
-        <v>0.005936117009651592</v>
+        <v>0.00600477916161225</v>
       </c>
       <c r="H93">
-        <v>0.005234985357142116</v>
+        <v>0.005290454781215137</v>
       </c>
       <c r="I93">
-        <v>0.281131652509476</v>
+        <v>0.2943243803971134</v>
       </c>
       <c r="J93">
-        <v>1.1162083011579</v>
+        <v>1.146191773629804</v>
       </c>
       <c r="K93">
         <v>2.29</v>
@@ -5432,7 +5405,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5440,31 +5413,31 @@
         <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C94">
-        <v>0.7552208383877499</v>
+        <v>0.7164672131147527</v>
       </c>
       <c r="D94" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E94">
-        <v>1.013930971993758</v>
+        <v>0.9831311475409823</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94">
-        <v>0.00600477916161225</v>
+        <v>0.006043532786885248</v>
       </c>
       <c r="H94">
-        <v>0.005186069028006243</v>
+        <v>0.005216868852459018</v>
       </c>
       <c r="I94">
-        <v>0.2587101336060078</v>
+        <v>0.2666639344262296</v>
       </c>
       <c r="J94">
-        <v>1.146191773629804</v>
+        <v>1.163114754098361</v>
       </c>
       <c r="K94">
         <v>2.29</v>
@@ -5482,7 +5455,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5490,31 +5463,31 @@
         <v>0</v>
       </c>
       <c r="B95" t="s">
+        <v>36</v>
+      </c>
+      <c r="C95">
+        <v>0.6498239504652852</v>
+      </c>
+      <c r="D95" t="s">
         <v>35</v>
       </c>
-      <c r="C95">
-        <v>0.7164672131147527</v>
-      </c>
-      <c r="D95" t="s">
-        <v>34</v>
-      </c>
       <c r="E95">
-        <v>0.6464672131147529</v>
+        <v>0.5798239504652853</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
       <c r="G95">
-        <v>0.006043532786885248</v>
+        <v>0.006110176049534715</v>
       </c>
       <c r="H95">
-        <v>0.005973532786885247</v>
+        <v>0.006040176049534715</v>
       </c>
       <c r="I95">
         <v>-0.06999999999999984</v>
       </c>
       <c r="J95">
-        <v>1.163114754098361</v>
+        <v>1.192216615517343</v>
       </c>
       <c r="K95">
         <v>2.29</v>
@@ -5532,7 +5505,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5540,31 +5513,31 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C96">
-        <v>0.7002131196894186</v>
+        <v>0.5205928926738919</v>
       </c>
       <c r="D96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E96">
-        <v>0.5798239504652853</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
       <c r="G96">
-        <v>0.006279786880310581</v>
+        <v>0.006459407107326108</v>
       </c>
       <c r="H96">
-        <v>0.006040176049534715</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I96">
-        <v>-0.1203891692241332</v>
+        <v>-0.1165511301853397</v>
       </c>
       <c r="J96">
-        <v>1.192216615517343</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K96">
         <v>2.34</v>
@@ -5582,7 +5555,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5590,31 +5563,31 @@
         <v>1</v>
       </c>
       <c r="B97" t="s">
+        <v>36</v>
+      </c>
+      <c r="C97">
+        <v>0.474041762488552</v>
+      </c>
+      <c r="D97" t="s">
         <v>35</v>
       </c>
-      <c r="C97">
-        <v>0.6498239504652852</v>
-      </c>
-      <c r="D97" t="s">
-        <v>34</v>
-      </c>
       <c r="E97">
-        <v>0.5798239504652853</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
       <c r="G97">
-        <v>0.006110176049534715</v>
+        <v>0.006285958237511447</v>
       </c>
       <c r="H97">
-        <v>0.006040176049534715</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I97">
         <v>-0.06999999999999984</v>
       </c>
       <c r="J97">
-        <v>1.192216615517343</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K97">
         <v>2.29</v>
@@ -5632,7 +5605,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5640,31 +5613,31 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C98">
-        <v>0.5205928926738919</v>
+        <v>0.3774746016246668</v>
       </c>
       <c r="D98" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E98">
-        <v>0.4040417624885522</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
       <c r="G98">
-        <v>0.006459407107326108</v>
+        <v>0.006602525398375333</v>
       </c>
       <c r="H98">
-        <v>0.006215958237511448</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I98">
-        <v>-0.1165511301853397</v>
+        <v>-0.1134930470432627</v>
       </c>
       <c r="J98">
-        <v>1.268977396293209</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K98">
         <v>2.34</v>
@@ -5682,45 +5655,45 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B99" t="s">
+        <v>37</v>
+      </c>
+      <c r="C99">
+        <v>0.2442505289553791</v>
+      </c>
+      <c r="D99" t="s">
         <v>35</v>
       </c>
-      <c r="C99">
-        <v>0.474041762488552</v>
-      </c>
-      <c r="D99" t="s">
-        <v>34</v>
-      </c>
       <c r="E99">
-        <v>0.4040417624885522</v>
+        <v>0.1336041501315459</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
       <c r="G99">
-        <v>0.006285958237511447</v>
+        <v>0.006735749471044622</v>
       </c>
       <c r="H99">
-        <v>0.006215958237511448</v>
+        <v>0.006486395849868455</v>
       </c>
       <c r="I99">
-        <v>-0.06999999999999984</v>
+        <v>-0.1106463788238332</v>
       </c>
       <c r="J99">
-        <v>1.268977396293209</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K99">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="L99">
-        <v>3.38</v>
+        <v>3.49</v>
       </c>
       <c r="M99">
         <v>2.29</v>
@@ -5732,7 +5705,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -5740,299 +5713,299 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C100">
-        <v>0.3774746016246668</v>
+        <v>2.01907486979781</v>
       </c>
       <c r="D100" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E100">
-        <v>0.2639815545814042</v>
+        <v>2.130748174485088</v>
       </c>
       <c r="F100">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G100">
-        <v>0.006602525398375333</v>
+        <v>0.00600092513020219</v>
       </c>
       <c r="H100">
-        <v>0.006356018445418596</v>
+        <v>0.005969251825514912</v>
       </c>
       <c r="I100">
-        <v>-0.1134930470432627</v>
+        <v>-0.1116733046872787</v>
       </c>
       <c r="J100">
-        <v>1.330139059134758</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K100">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="L100">
-        <v>3.49</v>
+        <v>4.01</v>
       </c>
       <c r="M100">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="N100">
-        <v>3.31</v>
+        <v>4.05</v>
       </c>
       <c r="O100">
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B101" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C101">
-        <v>0.2442505289553791</v>
+        <v>1.998530377609941</v>
       </c>
       <c r="D101" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E101">
-        <v>0.1336041501315459</v>
+        <v>2.130748174485088</v>
       </c>
       <c r="F101">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G101">
-        <v>0.006735749471044622</v>
+        <v>0.005741469622390059</v>
       </c>
       <c r="H101">
-        <v>0.006486395849868455</v>
+        <v>0.005969251825514912</v>
       </c>
       <c r="I101">
-        <v>-0.1106463788238332</v>
+        <v>-0.132217796875147</v>
       </c>
       <c r="J101">
-        <v>1.387072423523342</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K101">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="L101">
-        <v>3.49</v>
+        <v>3.87</v>
       </c>
       <c r="M101">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="N101">
-        <v>3.31</v>
+        <v>4.05</v>
       </c>
       <c r="O101">
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="102" spans="1:16">
       <c r="A102" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B102" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C102">
-        <v>2.01907486979781</v>
+        <v>1.984457778651558</v>
       </c>
       <c r="D102" t="s">
         <v>49</v>
       </c>
       <c r="E102">
-        <v>1.984457778651558</v>
+        <v>2.130748174485088</v>
       </c>
       <c r="F102">
         <v>-1</v>
       </c>
       <c r="G102">
-        <v>0.00600092513020219</v>
+        <v>0.005695542221348442</v>
       </c>
       <c r="H102">
-        <v>0.005695542221348442</v>
+        <v>0.005969251825514912</v>
       </c>
       <c r="I102">
-        <v>0.03461709114625111</v>
+        <v>-0.1462903958335298</v>
       </c>
       <c r="J102">
         <v>0.7963700520808761</v>
       </c>
       <c r="K102">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="L102">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="M102">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N102">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O102">
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103" spans="1:16">
       <c r="A103" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C103">
-        <v>1.998530377609941</v>
+        <v>2.009451144824672</v>
       </c>
       <c r="D103" t="s">
         <v>49</v>
       </c>
       <c r="E103">
-        <v>1.984457778651558</v>
+        <v>2.121470903610984</v>
       </c>
       <c r="F103">
         <v>-1</v>
       </c>
       <c r="G103">
-        <v>0.005741469622390059</v>
+        <v>0.006010548855175328</v>
       </c>
       <c r="H103">
-        <v>0.005695542221348442</v>
+        <v>0.005978529096389016</v>
       </c>
       <c r="I103">
-        <v>0.01407259895838275</v>
+        <v>-0.1120197587863117</v>
       </c>
       <c r="J103">
-        <v>0.7963700520808761</v>
+        <v>0.8002195420701311</v>
       </c>
       <c r="K103">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L103">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M103">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N103">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O103">
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="104" spans="1:16">
       <c r="A104" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B104" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C104">
-        <v>2.009451144824672</v>
+        <v>1.989484076135192</v>
       </c>
       <c r="D104" t="s">
         <v>49</v>
       </c>
       <c r="E104">
-        <v>1.975488466976594</v>
+        <v>2.121470903610984</v>
       </c>
       <c r="F104">
         <v>-1</v>
       </c>
       <c r="G104">
-        <v>0.006010548855175328</v>
+        <v>0.005750515923864809</v>
       </c>
       <c r="H104">
-        <v>0.005704511533023406</v>
+        <v>0.005978529096389016</v>
       </c>
       <c r="I104">
-        <v>0.03396267784807794</v>
+        <v>-0.1319868274757918</v>
       </c>
       <c r="J104">
         <v>0.8002195420701311</v>
       </c>
       <c r="K104">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L104">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M104">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N104">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O104">
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="105" spans="1:16">
       <c r="A105" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B105" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C105">
-        <v>1.989484076135192</v>
+        <v>1.975488466976594</v>
       </c>
       <c r="D105" t="s">
         <v>49</v>
       </c>
       <c r="E105">
-        <v>1.975488466976594</v>
+        <v>2.121470903610984</v>
       </c>
       <c r="F105">
         <v>-1</v>
       </c>
       <c r="G105">
-        <v>0.005750515923864809</v>
+        <v>0.005704511533023406</v>
       </c>
       <c r="H105">
-        <v>0.005704511533023406</v>
+        <v>0.005978529096389016</v>
       </c>
       <c r="I105">
-        <v>0.01399560915859777</v>
+        <v>-0.1459824366343896</v>
       </c>
       <c r="J105">
         <v>0.8002195420701311</v>
       </c>
       <c r="K105">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="L105">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="M105">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N105">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O105">
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6040,7 +6013,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C106">
         <v>1.996409318396163</v>
@@ -6049,7 +6022,7 @@
         <v>49</v>
       </c>
       <c r="E106">
-        <v>1.963333484745224</v>
+        <v>2.108898582933901</v>
       </c>
       <c r="F106">
         <v>-1</v>
@@ -6058,10 +6031,10 @@
         <v>0.006023590681603837</v>
       </c>
       <c r="H106">
-        <v>0.005716666515254776</v>
+        <v>0.005991101417066099</v>
       </c>
       <c r="I106">
-        <v>0.03307583365093891</v>
+        <v>-0.1124892645377384</v>
       </c>
       <c r="J106">
         <v>0.8054362726415348</v>
@@ -6073,16 +6046,16 @@
         <v>4.01</v>
       </c>
       <c r="M106">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N106">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O106">
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6099,7 +6072,7 @@
         <v>49</v>
       </c>
       <c r="E107">
-        <v>1.963333484745224</v>
+        <v>2.108898582933901</v>
       </c>
       <c r="F107">
         <v>-1</v>
@@ -6108,10 +6081,10 @@
         <v>0.005762775240707607</v>
       </c>
       <c r="H107">
-        <v>0.005716666515254776</v>
+        <v>0.005991101417066099</v>
       </c>
       <c r="I107">
-        <v>0.01389127454716954</v>
+        <v>-0.1316738236415078</v>
       </c>
       <c r="J107">
         <v>0.8054362726415348</v>
@@ -6123,60 +6096,60 @@
         <v>3.87</v>
       </c>
       <c r="M107">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N107">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O107">
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108" spans="1:16">
       <c r="A108" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B108" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C108">
-        <v>1.981381467084703</v>
+        <v>1.963333484745224</v>
       </c>
       <c r="D108" t="s">
         <v>49</v>
       </c>
       <c r="E108">
-        <v>1.949327527322944</v>
+        <v>2.108898582933901</v>
       </c>
       <c r="F108">
         <v>-1</v>
       </c>
       <c r="G108">
-        <v>0.006038618532915297</v>
+        <v>0.005716666515254776</v>
       </c>
       <c r="H108">
-        <v>0.005730672472677056</v>
+        <v>0.005991101417066099</v>
       </c>
       <c r="I108">
-        <v>0.03205393976175963</v>
+        <v>-0.1455650981886774</v>
       </c>
       <c r="J108">
-        <v>0.8114474131661186</v>
+        <v>0.8054362726415348</v>
       </c>
       <c r="K108">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="L108">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="M108">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N108">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O108">
         <v>1</v>
@@ -6187,96 +6160,96 @@
     </row>
     <row r="109" spans="1:16">
       <c r="A109" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C109">
-        <v>1.963098579059621</v>
+        <v>1.981381467084703</v>
       </c>
       <c r="D109" t="s">
         <v>49</v>
       </c>
       <c r="E109">
-        <v>1.949327527322944</v>
+        <v>2.094411734269654</v>
       </c>
       <c r="F109">
         <v>-1</v>
       </c>
       <c r="G109">
-        <v>0.005776901420940379</v>
+        <v>0.006038618532915297</v>
       </c>
       <c r="H109">
-        <v>0.005730672472677056</v>
+        <v>0.006005588265730346</v>
       </c>
       <c r="I109">
-        <v>0.01377105173667781</v>
+        <v>-0.1130302671849508</v>
       </c>
       <c r="J109">
         <v>0.8114474131661186</v>
       </c>
       <c r="K109">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L109">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M109">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N109">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O109">
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="110" spans="1:16">
       <c r="A110" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B110" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C110">
-        <v>1.977186894395391</v>
+        <v>1.963098579059621</v>
       </c>
       <c r="D110" t="s">
         <v>49</v>
       </c>
       <c r="E110">
-        <v>1.945418185576504</v>
+        <v>2.094411734269654</v>
       </c>
       <c r="F110">
         <v>-1</v>
       </c>
       <c r="G110">
-        <v>0.006042813105604609</v>
+        <v>0.005776901420940379</v>
       </c>
       <c r="H110">
-        <v>0.005734581814423496</v>
+        <v>0.006005588265730346</v>
       </c>
       <c r="I110">
-        <v>0.03176870881888649</v>
+        <v>-0.1313131552100326</v>
       </c>
       <c r="J110">
-        <v>0.8131252422418436</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K110">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L110">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M110">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N110">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O110">
         <v>1</v>
@@ -6287,46 +6260,46 @@
     </row>
     <row r="111" spans="1:16">
       <c r="A111" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B111" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C111">
-        <v>1.959155680731668</v>
+        <v>1.949327527322944</v>
       </c>
       <c r="D111" t="s">
         <v>49</v>
       </c>
       <c r="E111">
-        <v>1.945418185576504</v>
+        <v>2.094411734269654</v>
       </c>
       <c r="F111">
         <v>-1</v>
       </c>
       <c r="G111">
-        <v>0.005780844319268333</v>
+        <v>0.005730672472677056</v>
       </c>
       <c r="H111">
-        <v>0.005734581814423496</v>
+        <v>0.006005588265730346</v>
       </c>
       <c r="I111">
-        <v>0.01373749515516343</v>
+        <v>-0.1450842069467104</v>
       </c>
       <c r="J111">
-        <v>0.8131252422418436</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K111">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="L111">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="M111">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N111">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O111">
         <v>1</v>
@@ -6340,31 +6313,31 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C112">
-        <v>1.972128109819418</v>
+        <v>1.977186894395391</v>
       </c>
       <c r="D112" t="s">
         <v>49</v>
       </c>
       <c r="E112">
-        <v>1.940703398351698</v>
+        <v>2.090368166197157</v>
       </c>
       <c r="F112">
         <v>-1</v>
       </c>
       <c r="G112">
-        <v>0.006047871890180582</v>
+        <v>0.006042813105604609</v>
       </c>
       <c r="H112">
-        <v>0.005739296601648302</v>
+        <v>0.006009631833802842</v>
       </c>
       <c r="I112">
-        <v>0.03142471146772019</v>
+        <v>-0.113181271801766</v>
       </c>
       <c r="J112">
-        <v>0.8151487560722326</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K112">
         <v>2.5</v>
@@ -6373,10 +6346,10 @@
         <v>4.01</v>
       </c>
       <c r="M112">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N112">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O112">
         <v>1</v>
@@ -6393,28 +6366,28 @@
         <v>29</v>
       </c>
       <c r="C113">
-        <v>1.954400423230253</v>
+        <v>1.959155680731668</v>
       </c>
       <c r="D113" t="s">
         <v>49</v>
       </c>
       <c r="E113">
-        <v>1.940703398351698</v>
+        <v>2.090368166197157</v>
       </c>
       <c r="F113">
         <v>-1</v>
       </c>
       <c r="G113">
-        <v>0.005785599576769747</v>
+        <v>0.005780844319268333</v>
       </c>
       <c r="H113">
-        <v>0.005739296601648302</v>
+        <v>0.006009631833802842</v>
       </c>
       <c r="I113">
-        <v>0.01369702487855551</v>
+        <v>-0.131212485465489</v>
       </c>
       <c r="J113">
-        <v>0.8151487560722326</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K113">
         <v>2.35</v>
@@ -6423,10 +6396,10 @@
         <v>3.87</v>
       </c>
       <c r="M113">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N113">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O113">
         <v>1</v>
@@ -6437,96 +6410,96 @@
     </row>
     <row r="114" spans="1:16">
       <c r="A114" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B114" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C114">
-        <v>1.962255996565552</v>
+        <v>1.945418185576504</v>
       </c>
       <c r="D114" t="s">
         <v>49</v>
       </c>
       <c r="E114">
-        <v>1.931502588799094</v>
+        <v>2.090368166197157</v>
       </c>
       <c r="F114">
         <v>-1</v>
       </c>
       <c r="G114">
-        <v>0.006057744003434448</v>
+        <v>0.005734581814423496</v>
       </c>
       <c r="H114">
-        <v>0.005748497411200906</v>
+        <v>0.006009631833802842</v>
       </c>
       <c r="I114">
-        <v>0.03075340776645774</v>
+        <v>-0.1449499806206525</v>
       </c>
       <c r="J114">
-        <v>0.8190976013737793</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K114">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="L114">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="M114">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N114">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O114">
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="115" spans="1:16">
       <c r="A115" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C115">
-        <v>1.945120636771619</v>
+        <v>1.972128109819418</v>
       </c>
       <c r="D115" t="s">
         <v>49</v>
       </c>
       <c r="E115">
-        <v>1.931502588799094</v>
+        <v>2.085491497865919</v>
       </c>
       <c r="F115">
         <v>-1</v>
       </c>
       <c r="G115">
-        <v>0.005794879363228382</v>
+        <v>0.006047871890180582</v>
       </c>
       <c r="H115">
-        <v>0.005748497411200906</v>
+        <v>0.00601450850213408</v>
       </c>
       <c r="I115">
-        <v>0.01361804797252475</v>
+        <v>-0.1133633880465013</v>
       </c>
       <c r="J115">
-        <v>0.8190976013737793</v>
+        <v>0.8151487560722326</v>
       </c>
       <c r="K115">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L115">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M115">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N115">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O115">
         <v>1</v>
@@ -6537,102 +6510,102 @@
     </row>
     <row r="116" spans="1:16">
       <c r="A116" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B116" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C116">
-        <v>1.966334427874344</v>
+        <v>1.954400423230253</v>
       </c>
       <c r="D116" t="s">
         <v>49</v>
       </c>
       <c r="E116">
-        <v>1.935303686778889</v>
+        <v>2.085491497865919</v>
       </c>
       <c r="F116">
         <v>-1</v>
       </c>
       <c r="G116">
-        <v>0.006053665572125656</v>
+        <v>0.005785599576769747</v>
       </c>
       <c r="H116">
-        <v>0.005744696313221111</v>
+        <v>0.00601450850213408</v>
       </c>
       <c r="I116">
-        <v>0.03103074109545512</v>
+        <v>-0.1310910746356659</v>
       </c>
       <c r="J116">
-        <v>0.8174662288502623</v>
+        <v>0.8151487560722326</v>
       </c>
       <c r="K116">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L116">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M116">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N116">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O116">
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="117" spans="1:16">
       <c r="A117" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B117" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C117">
-        <v>1.948954362201884</v>
+        <v>1.940703398351698</v>
       </c>
       <c r="D117" t="s">
         <v>49</v>
       </c>
       <c r="E117">
-        <v>1.935303686778889</v>
+        <v>2.085491497865919</v>
       </c>
       <c r="F117">
         <v>-1</v>
       </c>
       <c r="G117">
-        <v>0.005791045637798117</v>
+        <v>0.005739296601648302</v>
       </c>
       <c r="H117">
-        <v>0.005744696313221111</v>
+        <v>0.00601450850213408</v>
       </c>
       <c r="I117">
-        <v>0.01365067542299503</v>
+        <v>-0.1447880995142214</v>
       </c>
       <c r="J117">
-        <v>0.8174662288502623</v>
+        <v>0.8151487560722326</v>
       </c>
       <c r="K117">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="L117">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="M117">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N117">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O117">
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6640,31 +6613,31 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C118">
-        <v>1.967381519350304</v>
+        <v>1.962255996565552</v>
       </c>
       <c r="D118" t="s">
         <v>49</v>
       </c>
       <c r="E118">
-        <v>1.936279576034483</v>
+        <v>2.075974780689192</v>
       </c>
       <c r="F118">
         <v>-1</v>
       </c>
       <c r="G118">
-        <v>0.006052618480649696</v>
+        <v>0.006057744003434448</v>
       </c>
       <c r="H118">
-        <v>0.005743720423965517</v>
+        <v>0.006024025219310808</v>
       </c>
       <c r="I118">
-        <v>0.03110194331582061</v>
+        <v>-0.1137187841236398</v>
       </c>
       <c r="J118">
-        <v>0.8170473922598784</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K118">
         <v>2.5</v>
@@ -6673,16 +6646,16 @@
         <v>4.01</v>
       </c>
       <c r="M118">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N118">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O118">
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6693,28 +6666,28 @@
         <v>29</v>
       </c>
       <c r="C119">
-        <v>1.949938628189286</v>
+        <v>1.945120636771619</v>
       </c>
       <c r="D119" t="s">
         <v>49</v>
       </c>
       <c r="E119">
-        <v>1.936279576034483</v>
+        <v>2.075974780689192</v>
       </c>
       <c r="F119">
         <v>-1</v>
       </c>
       <c r="G119">
-        <v>0.005790061371810714</v>
+        <v>0.005794879363228382</v>
       </c>
       <c r="H119">
-        <v>0.005743720423965517</v>
+        <v>0.006024025219310808</v>
       </c>
       <c r="I119">
-        <v>0.01365905215480256</v>
+        <v>-0.1308541439175728</v>
       </c>
       <c r="J119">
-        <v>0.8170473922598784</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K119">
         <v>2.35</v>
@@ -6723,216 +6696,216 @@
         <v>3.87</v>
       </c>
       <c r="M119">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N119">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O119">
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="120" spans="1:16">
       <c r="A120" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B120" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C120">
-        <v>1.965836780713639</v>
+        <v>1.931502588799094</v>
       </c>
       <c r="D120" t="s">
         <v>49</v>
       </c>
       <c r="E120">
-        <v>1.934839879625112</v>
+        <v>2.075974780689192</v>
       </c>
       <c r="F120">
         <v>-1</v>
       </c>
       <c r="G120">
-        <v>0.00605416321928636</v>
+        <v>0.005748497411200906</v>
       </c>
       <c r="H120">
-        <v>0.005745160120374888</v>
+        <v>0.006024025219310808</v>
       </c>
       <c r="I120">
-        <v>0.0309969010885276</v>
+        <v>-0.1444721918900975</v>
       </c>
       <c r="J120">
-        <v>0.8176652877145442</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K120">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="L120">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="M120">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N120">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O120">
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="121" spans="1:16">
       <c r="A121" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C121">
-        <v>1.948486573870821</v>
+        <v>1.966334427874344</v>
       </c>
       <c r="D121" t="s">
         <v>49</v>
       </c>
       <c r="E121">
-        <v>1.934839879625112</v>
+        <v>2.079906388470867</v>
       </c>
       <c r="F121">
         <v>-1</v>
       </c>
       <c r="G121">
-        <v>0.00579151342612918</v>
+        <v>0.006053665572125656</v>
       </c>
       <c r="H121">
-        <v>0.005745160120374888</v>
+        <v>0.006020093611529133</v>
       </c>
       <c r="I121">
-        <v>0.01364669424570941</v>
+        <v>-0.1135719605965235</v>
       </c>
       <c r="J121">
-        <v>0.8176652877145442</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K121">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L121">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M121">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N121">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O121">
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="122" spans="1:16">
       <c r="A122" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B122" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C122">
-        <v>1.964801996006813</v>
+        <v>1.948954362201884</v>
       </c>
       <c r="D122" t="s">
         <v>49</v>
       </c>
       <c r="E122">
-        <v>1.93387546027835</v>
+        <v>2.079906388470867</v>
       </c>
       <c r="F122">
         <v>-1</v>
       </c>
       <c r="G122">
-        <v>0.006055198003993187</v>
+        <v>0.005791045637798117</v>
       </c>
       <c r="H122">
-        <v>0.00574612453972165</v>
+        <v>0.006020093611529133</v>
       </c>
       <c r="I122">
-        <v>0.03092653572846338</v>
+        <v>-0.1309520262689836</v>
       </c>
       <c r="J122">
-        <v>0.8180792015972748</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K122">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L122">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M122">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N122">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O122">
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="123" spans="1:16">
       <c r="A123" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B123" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C123">
-        <v>1.947513876246404</v>
+        <v>1.935303686778889</v>
       </c>
       <c r="D123" t="s">
         <v>49</v>
       </c>
       <c r="E123">
-        <v>1.93387546027835</v>
+        <v>2.079906388470867</v>
       </c>
       <c r="F123">
         <v>-1</v>
       </c>
       <c r="G123">
-        <v>0.005792486123753596</v>
+        <v>0.005744696313221111</v>
       </c>
       <c r="H123">
-        <v>0.00574612453972165</v>
+        <v>0.006020093611529133</v>
       </c>
       <c r="I123">
-        <v>0.01363841596805471</v>
+        <v>-0.1446027016919786</v>
       </c>
       <c r="J123">
-        <v>0.8180792015972748</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K123">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="L123">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="M123">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N123">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O123">
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -6940,31 +6913,31 @@
         <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C124">
-        <v>1.96211546833212</v>
+        <v>1.967381519350304</v>
       </c>
       <c r="D124" t="s">
         <v>49</v>
       </c>
       <c r="E124">
-        <v>1.931371616485536</v>
+        <v>2.080915784653693</v>
       </c>
       <c r="F124">
         <v>-1</v>
       </c>
       <c r="G124">
-        <v>0.006057884531667879</v>
+        <v>0.006052618480649696</v>
       </c>
       <c r="H124">
-        <v>0.005748628383514463</v>
+        <v>0.006019084215346308</v>
       </c>
       <c r="I124">
-        <v>0.03074385184658412</v>
+        <v>-0.1135342653033891</v>
       </c>
       <c r="J124">
-        <v>0.8191538126671517</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K124">
         <v>2.5</v>
@@ -6973,16 +6946,16 @@
         <v>4.01</v>
       </c>
       <c r="M124">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N124">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O124">
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -6993,28 +6966,28 @@
         <v>29</v>
       </c>
       <c r="C125">
-        <v>1.944988540232194</v>
+        <v>1.949938628189286</v>
       </c>
       <c r="D125" t="s">
         <v>49</v>
       </c>
       <c r="E125">
-        <v>1.931371616485536</v>
+        <v>2.080915784653693</v>
       </c>
       <c r="F125">
         <v>-1</v>
       </c>
       <c r="G125">
-        <v>0.005795011459767806</v>
+        <v>0.005790061371810714</v>
       </c>
       <c r="H125">
-        <v>0.005748628383514463</v>
+        <v>0.006019084215346308</v>
       </c>
       <c r="I125">
-        <v>0.01361692374665724</v>
+        <v>-0.1309771564644071</v>
       </c>
       <c r="J125">
-        <v>0.8191538126671517</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K125">
         <v>2.35</v>
@@ -7023,216 +6996,216 @@
         <v>3.87</v>
       </c>
       <c r="M125">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N125">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O125">
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="126" spans="1:16">
       <c r="A126" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B126" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C126">
-        <v>1.969378632640371</v>
+        <v>1.936279576034483</v>
       </c>
       <c r="D126" t="s">
         <v>49</v>
       </c>
       <c r="E126">
-        <v>1.938140885620826</v>
+        <v>2.080915784653693</v>
       </c>
       <c r="F126">
         <v>-1</v>
       </c>
       <c r="G126">
-        <v>0.006050621367359629</v>
+        <v>0.005743720423965517</v>
       </c>
       <c r="H126">
-        <v>0.005741859114379175</v>
+        <v>0.006019084215346308</v>
       </c>
       <c r="I126">
-        <v>0.03123774701954529</v>
+        <v>-0.1446362086192097</v>
       </c>
       <c r="J126">
-        <v>0.8162485469438515</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K126">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="L126">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="M126">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N126">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O126">
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="127" spans="1:16">
       <c r="A127" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C127">
-        <v>1.951815914681949</v>
+        <v>1.965836780713639</v>
       </c>
       <c r="D127" t="s">
         <v>49</v>
       </c>
       <c r="E127">
-        <v>1.938140885620826</v>
+        <v>2.079426656607948</v>
       </c>
       <c r="F127">
         <v>-1</v>
       </c>
       <c r="G127">
-        <v>0.005788184085318051</v>
+        <v>0.00605416321928636</v>
       </c>
       <c r="H127">
-        <v>0.005741859114379175</v>
+        <v>0.006020573343392051</v>
       </c>
       <c r="I127">
-        <v>0.01367502906112317</v>
+        <v>-0.1135898758943088</v>
       </c>
       <c r="J127">
-        <v>0.8162485469438515</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K127">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L127">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M127">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N127">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O127">
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="128" spans="1:16">
       <c r="A128" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B128" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C128">
-        <v>1.979025316902244</v>
+        <v>1.948486573870821</v>
       </c>
       <c r="D128" t="s">
         <v>49</v>
       </c>
       <c r="E128">
-        <v>1.947131595352891</v>
+        <v>2.079426656607948</v>
       </c>
       <c r="F128">
         <v>-1</v>
       </c>
       <c r="G128">
-        <v>0.006040974683097756</v>
+        <v>0.00579151342612918</v>
       </c>
       <c r="H128">
-        <v>0.005732868404647109</v>
+        <v>0.006020573343392051</v>
       </c>
       <c r="I128">
-        <v>0.03189372154935266</v>
+        <v>-0.130940082737127</v>
       </c>
       <c r="J128">
-        <v>0.8123898732391025</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K128">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L128">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M128">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N128">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O128">
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="129" spans="1:16">
       <c r="A129" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B129" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C129">
-        <v>1.960883797888109</v>
+        <v>1.934839879625112</v>
       </c>
       <c r="D129" t="s">
         <v>49</v>
       </c>
       <c r="E129">
-        <v>1.947131595352891</v>
+        <v>2.079426656607948</v>
       </c>
       <c r="F129">
         <v>-1</v>
       </c>
       <c r="G129">
-        <v>0.005779116202111891</v>
+        <v>0.005745160120374888</v>
       </c>
       <c r="H129">
-        <v>0.005732868404647109</v>
+        <v>0.006020573343392051</v>
       </c>
       <c r="I129">
-        <v>0.01375220253521814</v>
+        <v>-0.1445867769828364</v>
       </c>
       <c r="J129">
-        <v>0.8123898732391025</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K129">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="L129">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="M129">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N129">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O129">
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7240,31 +7213,31 @@
         <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C130">
-        <v>1.983626913195719</v>
+        <v>1.964801996006813</v>
       </c>
       <c r="D130" t="s">
         <v>49</v>
       </c>
       <c r="E130">
-        <v>1.95142028309841</v>
+        <v>2.078429124150567</v>
       </c>
       <c r="F130">
         <v>-1</v>
       </c>
       <c r="G130">
-        <v>0.00603637308680428</v>
+        <v>0.006055198003993187</v>
       </c>
       <c r="H130">
-        <v>0.00572857971690159</v>
+        <v>0.006021570875849432</v>
       </c>
       <c r="I130">
-        <v>0.03220663009730895</v>
+        <v>-0.1136271281437544</v>
       </c>
       <c r="J130">
-        <v>0.8105492347217125</v>
+        <v>0.8180792015972748</v>
       </c>
       <c r="K130">
         <v>2.5</v>
@@ -7273,16 +7246,16 @@
         <v>4.01</v>
       </c>
       <c r="M130">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N130">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O130">
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7293,28 +7266,28 @@
         <v>29</v>
       </c>
       <c r="C131">
-        <v>1.965209298403976</v>
+        <v>1.947513876246404</v>
       </c>
       <c r="D131" t="s">
         <v>49</v>
       </c>
       <c r="E131">
-        <v>1.95142028309841</v>
+        <v>2.078429124150567</v>
       </c>
       <c r="F131">
         <v>-1</v>
       </c>
       <c r="G131">
-        <v>0.005774790701596024</v>
+        <v>0.005792486123753596</v>
       </c>
       <c r="H131">
-        <v>0.00572857971690159</v>
+        <v>0.006021570875849432</v>
       </c>
       <c r="I131">
-        <v>0.01378901530556598</v>
+        <v>-0.1309152479041631</v>
       </c>
       <c r="J131">
-        <v>0.8105492347217125</v>
+        <v>0.8180792015972748</v>
       </c>
       <c r="K131">
         <v>2.35</v>
@@ -7323,216 +7296,216 @@
         <v>3.87</v>
       </c>
       <c r="M131">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N131">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O131">
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="132" spans="1:16">
       <c r="A132" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B132" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C132">
-        <v>1.99070164592738</v>
+        <v>1.93387546027835</v>
       </c>
       <c r="D132" t="s">
         <v>49</v>
       </c>
       <c r="E132">
-        <v>1.958013934004318</v>
+        <v>2.078429124150567</v>
       </c>
       <c r="F132">
         <v>-1</v>
       </c>
       <c r="G132">
-        <v>0.006029298354072619</v>
+        <v>0.00574612453972165</v>
       </c>
       <c r="H132">
-        <v>0.005721986065995681</v>
+        <v>0.006021570875849432</v>
       </c>
       <c r="I132">
-        <v>0.03268771192306197</v>
+        <v>-0.1445536638722178</v>
       </c>
       <c r="J132">
-        <v>0.8077193416290479</v>
+        <v>0.8180792015972748</v>
       </c>
       <c r="K132">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="L132">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="M132">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N132">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O132">
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="133" spans="1:16">
       <c r="A133" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C133">
-        <v>1.971859547171738</v>
+        <v>1.96211546833212</v>
       </c>
       <c r="D133" t="s">
         <v>49</v>
       </c>
       <c r="E133">
-        <v>1.958013934004318</v>
+        <v>2.075839311472164</v>
       </c>
       <c r="F133">
         <v>-1</v>
       </c>
       <c r="G133">
-        <v>0.005768140452828262</v>
+        <v>0.006057884531667879</v>
       </c>
       <c r="H133">
-        <v>0.005721986065995681</v>
+        <v>0.006024160688527836</v>
       </c>
       <c r="I133">
-        <v>0.01384561316741939</v>
+        <v>-0.1137238431400434</v>
       </c>
       <c r="J133">
-        <v>0.8077193416290479</v>
+        <v>0.8191538126671517</v>
       </c>
       <c r="K133">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L133">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M133">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N133">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O133">
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="134" spans="1:16">
       <c r="A134" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B134" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C134">
-        <v>1.995518685947181</v>
+        <v>1.944988540232194</v>
       </c>
       <c r="D134" t="s">
         <v>49</v>
       </c>
       <c r="E134">
-        <v>1.962503415302772</v>
+        <v>2.075839311472164</v>
       </c>
       <c r="F134">
         <v>-1</v>
       </c>
       <c r="G134">
-        <v>0.006024481314052819</v>
+        <v>0.005795011459767806</v>
       </c>
       <c r="H134">
-        <v>0.005717496584697228</v>
+        <v>0.006024160688527836</v>
       </c>
       <c r="I134">
-        <v>0.03301527064440846</v>
+        <v>-0.1308507712399702</v>
       </c>
       <c r="J134">
-        <v>0.8057925256211278</v>
+        <v>0.8191538126671517</v>
       </c>
       <c r="K134">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L134">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M134">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N134">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O134">
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="135" spans="1:16">
       <c r="A135" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B135" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C135">
-        <v>1.97638756479035</v>
+        <v>1.931371616485536</v>
       </c>
       <c r="D135" t="s">
         <v>49</v>
       </c>
       <c r="E135">
-        <v>1.962503415302772</v>
+        <v>2.075839311472164</v>
       </c>
       <c r="F135">
         <v>-1</v>
       </c>
       <c r="G135">
-        <v>0.005763612435209651</v>
+        <v>0.005748628383514463</v>
       </c>
       <c r="H135">
-        <v>0.005717496584697228</v>
+        <v>0.006024160688527836</v>
       </c>
       <c r="I135">
-        <v>0.01388414948757766</v>
+        <v>-0.1444676949866275</v>
       </c>
       <c r="J135">
-        <v>0.8057925256211278</v>
+        <v>0.8191538126671517</v>
       </c>
       <c r="K135">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="L135">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="M135">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N135">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O135">
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7540,31 +7513,31 @@
         <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C136">
-        <v>2.001757402215216</v>
+        <v>1.969378632640371</v>
       </c>
       <c r="D136" t="s">
         <v>49</v>
       </c>
       <c r="E136">
-        <v>1.968317898864581</v>
+        <v>2.082841001865318</v>
       </c>
       <c r="F136">
         <v>-1</v>
       </c>
       <c r="G136">
-        <v>0.006018242597784784</v>
+        <v>0.006050621367359629</v>
       </c>
       <c r="H136">
-        <v>0.005711682101135418</v>
+        <v>0.006017158998134682</v>
       </c>
       <c r="I136">
-        <v>0.03343950335063495</v>
+        <v>-0.1134623692249468</v>
       </c>
       <c r="J136">
-        <v>0.8032970391139135</v>
+        <v>0.8162485469438515</v>
       </c>
       <c r="K136">
         <v>2.5</v>
@@ -7573,16 +7546,16 @@
         <v>4.01</v>
       </c>
       <c r="M136">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N136">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O136">
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7593,28 +7566,28 @@
         <v>29</v>
       </c>
       <c r="C137">
-        <v>1.982251958082303</v>
+        <v>1.951815914681949</v>
       </c>
       <c r="D137" t="s">
         <v>49</v>
       </c>
       <c r="E137">
-        <v>1.968317898864581</v>
+        <v>2.082841001865318</v>
       </c>
       <c r="F137">
         <v>-1</v>
       </c>
       <c r="G137">
-        <v>0.005757748041917698</v>
+        <v>0.005788184085318051</v>
       </c>
       <c r="H137">
-        <v>0.005711682101135418</v>
+        <v>0.006017158998134682</v>
       </c>
       <c r="I137">
-        <v>0.01393405921772195</v>
+        <v>-0.1310250871833689</v>
       </c>
       <c r="J137">
-        <v>0.8032970391139135</v>
+        <v>0.8162485469438515</v>
       </c>
       <c r="K137">
         <v>2.35</v>
@@ -7623,216 +7596,216 @@
         <v>3.87</v>
       </c>
       <c r="M137">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N137">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O137">
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="138" spans="1:16">
       <c r="A138" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B138" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C138">
-        <v>2.008261226887488</v>
+        <v>1.938140885620826</v>
       </c>
       <c r="D138" t="s">
         <v>49</v>
       </c>
       <c r="E138">
-        <v>1.974379463459139</v>
+        <v>2.082841001865318</v>
       </c>
       <c r="F138">
         <v>-1</v>
       </c>
       <c r="G138">
-        <v>0.006011738773112512</v>
+        <v>0.005741859114379175</v>
       </c>
       <c r="H138">
-        <v>0.005705620536540861</v>
+        <v>0.006017158998134682</v>
       </c>
       <c r="I138">
-        <v>0.03388176342834903</v>
+        <v>-0.1447001162444921</v>
       </c>
       <c r="J138">
-        <v>0.8006955092450049</v>
+        <v>0.8162485469438515</v>
       </c>
       <c r="K138">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="L138">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="M138">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N138">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O138">
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="139" spans="1:16">
       <c r="A139" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C139">
-        <v>1.988365553274239</v>
+        <v>1.979025316902244</v>
       </c>
       <c r="D139" t="s">
         <v>49</v>
       </c>
       <c r="E139">
-        <v>1.974379463459139</v>
+        <v>2.092140405493763</v>
       </c>
       <c r="F139">
         <v>-1</v>
       </c>
       <c r="G139">
-        <v>0.005751634446725762</v>
+        <v>0.006040974683097756</v>
       </c>
       <c r="H139">
-        <v>0.005705620536540861</v>
+        <v>0.006007859594506237</v>
       </c>
       <c r="I139">
-        <v>0.01398608981510008</v>
+        <v>-0.1131150885915191</v>
       </c>
       <c r="J139">
-        <v>0.8006955092450049</v>
+        <v>0.8123898732391025</v>
       </c>
       <c r="K139">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L139">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M139">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N139">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O139">
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="140" spans="1:16">
       <c r="A140" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B140" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C140">
-        <v>2.013407841318734</v>
+        <v>1.960883797888109</v>
       </c>
       <c r="D140" t="s">
         <v>49</v>
       </c>
       <c r="E140">
-        <v>1.97917610810906</v>
+        <v>2.092140405493763</v>
       </c>
       <c r="F140">
         <v>-1</v>
       </c>
       <c r="G140">
-        <v>0.006006592158681266</v>
+        <v>0.005779116202111891</v>
       </c>
       <c r="H140">
-        <v>0.00570082389189094</v>
+        <v>0.006007859594506237</v>
       </c>
       <c r="I140">
-        <v>0.03423173320967421</v>
+        <v>-0.1312566076056536</v>
       </c>
       <c r="J140">
-        <v>0.7986368634725065</v>
+        <v>0.8123898732391025</v>
       </c>
       <c r="K140">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L140">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M140">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N140">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O140">
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="141" spans="1:16">
       <c r="A141" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B141" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C141">
-        <v>1.99320337083961</v>
+        <v>1.947131595352891</v>
       </c>
       <c r="D141" t="s">
         <v>49</v>
       </c>
       <c r="E141">
-        <v>1.97917610810906</v>
+        <v>2.092140405493763</v>
       </c>
       <c r="F141">
         <v>-1</v>
       </c>
       <c r="G141">
-        <v>0.005746796629160391</v>
+        <v>0.005732868404647109</v>
       </c>
       <c r="H141">
-        <v>0.00570082389189094</v>
+        <v>0.006007859594506237</v>
       </c>
       <c r="I141">
-        <v>0.01402726273055022</v>
+        <v>-0.1450088101408717</v>
       </c>
       <c r="J141">
-        <v>0.7986368634725065</v>
+        <v>0.8123898732391025</v>
       </c>
       <c r="K141">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="L141">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="M141">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N141">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O141">
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -7840,31 +7813,31 @@
         <v>0</v>
       </c>
       <c r="B142" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C142">
-        <v>2.024814922108121</v>
+        <v>1.983626913195719</v>
       </c>
       <c r="D142" t="s">
         <v>49</v>
       </c>
       <c r="E142">
-        <v>1.989807507404769</v>
+        <v>2.096576344320673</v>
       </c>
       <c r="F142">
         <v>-1</v>
       </c>
       <c r="G142">
-        <v>0.005995185077891879</v>
+        <v>0.00603637308680428</v>
       </c>
       <c r="H142">
-        <v>0.005690192492595231</v>
+        <v>0.006003423655679328</v>
       </c>
       <c r="I142">
-        <v>0.03500741470335211</v>
+        <v>-0.1129494311249539</v>
       </c>
       <c r="J142">
-        <v>0.7940740311567515</v>
+        <v>0.8105492347217125</v>
       </c>
       <c r="K142">
         <v>2.5</v>
@@ -7873,16 +7846,16 @@
         <v>4.01</v>
       </c>
       <c r="M142">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N142">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O142">
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -7893,28 +7866,28 @@
         <v>29</v>
       </c>
       <c r="C143">
-        <v>2.003926026781634</v>
+        <v>1.965209298403976</v>
       </c>
       <c r="D143" t="s">
         <v>49</v>
       </c>
       <c r="E143">
-        <v>1.989807507404769</v>
+        <v>2.096576344320673</v>
       </c>
       <c r="F143">
         <v>-1</v>
       </c>
       <c r="G143">
-        <v>0.005736073973218366</v>
+        <v>0.005774790701596024</v>
       </c>
       <c r="H143">
-        <v>0.005690192492595231</v>
+        <v>0.006003423655679328</v>
       </c>
       <c r="I143">
-        <v>0.01411851937686515</v>
+        <v>-0.1313670459166969</v>
       </c>
       <c r="J143">
-        <v>0.7940740311567515</v>
+        <v>0.8105492347217125</v>
       </c>
       <c r="K143">
         <v>2.35</v>
@@ -7923,16 +7896,16 @@
         <v>3.87</v>
       </c>
       <c r="M143">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N143">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O143">
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -7940,31 +7913,31 @@
         <v>0</v>
       </c>
       <c r="B144" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C144">
-        <v>2.037026290859836</v>
+        <v>1.99070164592738</v>
       </c>
       <c r="D144" t="s">
         <v>49</v>
       </c>
       <c r="E144">
-        <v>2.001188503081367</v>
+        <v>2.103396386673994</v>
       </c>
       <c r="F144">
         <v>-1</v>
       </c>
       <c r="G144">
-        <v>0.005982973709140164</v>
+        <v>0.006029298354072619</v>
       </c>
       <c r="H144">
-        <v>0.005678811496918633</v>
+        <v>0.005996603613326006</v>
       </c>
       <c r="I144">
-        <v>0.03583778777846902</v>
+        <v>-0.1126947407466141</v>
       </c>
       <c r="J144">
-        <v>0.7891894836560657</v>
+        <v>0.8077193416290479</v>
       </c>
       <c r="K144">
         <v>2.5</v>
@@ -7973,16 +7946,16 @@
         <v>4.01</v>
       </c>
       <c r="M144">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N144">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O144">
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -7993,28 +7966,28 @@
         <v>29</v>
       </c>
       <c r="C145">
-        <v>2.015404713408246</v>
+        <v>1.971859547171738</v>
       </c>
       <c r="D145" t="s">
         <v>49</v>
       </c>
       <c r="E145">
-        <v>2.001188503081367</v>
+        <v>2.103396386673994</v>
       </c>
       <c r="F145">
         <v>-1</v>
       </c>
       <c r="G145">
-        <v>0.005724595286591755</v>
+        <v>0.005768140452828262</v>
       </c>
       <c r="H145">
-        <v>0.005678811496918633</v>
+        <v>0.005996603613326006</v>
       </c>
       <c r="I145">
-        <v>0.01421621032687881</v>
+        <v>-0.1315368395022567</v>
       </c>
       <c r="J145">
-        <v>0.7891894836560657</v>
+        <v>0.8077193416290479</v>
       </c>
       <c r="K145">
         <v>2.35</v>
@@ -8023,16 +7996,16 @@
         <v>3.87</v>
       </c>
       <c r="M145">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N145">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O145">
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8040,31 +8013,31 @@
         <v>0</v>
       </c>
       <c r="B146" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C146">
-        <v>2.040400244545683</v>
+        <v>1.995518685947181</v>
       </c>
       <c r="D146" t="s">
         <v>49</v>
       </c>
       <c r="E146">
-        <v>2.004333027916577</v>
+        <v>2.108040013253082</v>
       </c>
       <c r="F146">
         <v>-1</v>
       </c>
       <c r="G146">
-        <v>0.005979599755454317</v>
+        <v>0.006024481314052819</v>
       </c>
       <c r="H146">
-        <v>0.005675666972083424</v>
+        <v>0.005991959986746918</v>
       </c>
       <c r="I146">
-        <v>0.03606721662910628</v>
+        <v>-0.1125213273059011</v>
       </c>
       <c r="J146">
-        <v>0.7878399021817268</v>
+        <v>0.8057925256211278</v>
       </c>
       <c r="K146">
         <v>2.5</v>
@@ -8073,16 +8046,16 @@
         <v>4.01</v>
       </c>
       <c r="M146">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N146">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O146">
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8093,28 +8066,28 @@
         <v>29</v>
       </c>
       <c r="C147">
-        <v>2.018576229872942</v>
+        <v>1.97638756479035</v>
       </c>
       <c r="D147" t="s">
         <v>49</v>
       </c>
       <c r="E147">
-        <v>2.004333027916577</v>
+        <v>2.108040013253082</v>
       </c>
       <c r="F147">
         <v>-1</v>
       </c>
       <c r="G147">
-        <v>0.005721423770127059</v>
+        <v>0.005763612435209651</v>
       </c>
       <c r="H147">
-        <v>0.005675666972083424</v>
+        <v>0.005991959986746918</v>
       </c>
       <c r="I147">
-        <v>0.01424320195636541</v>
+        <v>-0.1316524484627319</v>
       </c>
       <c r="J147">
-        <v>0.7878399021817268</v>
+        <v>0.8057925256211278</v>
       </c>
       <c r="K147">
         <v>2.35</v>
@@ -8123,16 +8096,16 @@
         <v>3.87</v>
       </c>
       <c r="M147">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N147">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O147">
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8140,31 +8113,31 @@
         <v>0</v>
       </c>
       <c r="B148" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C148">
-        <v>2.040677055689185</v>
+        <v>2.001757402215216</v>
       </c>
       <c r="D148" t="s">
         <v>49</v>
       </c>
       <c r="E148">
-        <v>2.004591015902321</v>
+        <v>2.114054135735469</v>
       </c>
       <c r="F148">
         <v>-1</v>
       </c>
       <c r="G148">
-        <v>0.005979322944310814</v>
+        <v>0.006018242597784784</v>
       </c>
       <c r="H148">
-        <v>0.005675408984097679</v>
+        <v>0.005985945864264531</v>
       </c>
       <c r="I148">
-        <v>0.03608603978686453</v>
+        <v>-0.1122967335202523</v>
       </c>
       <c r="J148">
-        <v>0.7877291777243258</v>
+        <v>0.8032970391139135</v>
       </c>
       <c r="K148">
         <v>2.5</v>
@@ -8173,16 +8146,16 @@
         <v>4.01</v>
       </c>
       <c r="M148">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N148">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O148">
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8193,28 +8166,28 @@
         <v>29</v>
       </c>
       <c r="C149">
-        <v>2.018836432347834</v>
+        <v>1.982251958082303</v>
       </c>
       <c r="D149" t="s">
         <v>49</v>
       </c>
       <c r="E149">
-        <v>2.004591015902321</v>
+        <v>2.114054135735469</v>
       </c>
       <c r="F149">
         <v>-1</v>
       </c>
       <c r="G149">
-        <v>0.005721163567652166</v>
+        <v>0.005757748041917698</v>
       </c>
       <c r="H149">
-        <v>0.005675408984097679</v>
+        <v>0.005985945864264531</v>
       </c>
       <c r="I149">
-        <v>0.01424541644551347</v>
+        <v>-0.1318021776531653</v>
       </c>
       <c r="J149">
-        <v>0.7877291777243258</v>
+        <v>0.8032970391139135</v>
       </c>
       <c r="K149">
         <v>2.35</v>
@@ -8223,16 +8196,16 @@
         <v>3.87</v>
       </c>
       <c r="M149">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N149">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O149">
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8240,31 +8213,31 @@
         <v>0</v>
       </c>
       <c r="B150" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C150">
-        <v>2.041764709541035</v>
+        <v>2.008261226887488</v>
       </c>
       <c r="D150" t="s">
         <v>49</v>
       </c>
       <c r="E150">
-        <v>2.005604709292245</v>
+        <v>2.120323822719538</v>
       </c>
       <c r="F150">
         <v>-1</v>
       </c>
       <c r="G150">
-        <v>0.005978235290458964</v>
+        <v>0.006011738773112512</v>
       </c>
       <c r="H150">
-        <v>0.005674395290707754</v>
+        <v>0.005979676177280462</v>
       </c>
       <c r="I150">
-        <v>0.03616000024879007</v>
+        <v>-0.1120625958320502</v>
       </c>
       <c r="J150">
-        <v>0.7872941161835857</v>
+        <v>0.8006955092450049</v>
       </c>
       <c r="K150">
         <v>2.5</v>
@@ -8273,16 +8246,16 @@
         <v>4.01</v>
       </c>
       <c r="M150">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N150">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O150">
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8293,28 +8266,28 @@
         <v>29</v>
       </c>
       <c r="C151">
-        <v>2.019858826968574</v>
+        <v>1.988365553274239</v>
       </c>
       <c r="D151" t="s">
         <v>49</v>
       </c>
       <c r="E151">
-        <v>2.005604709292245</v>
+        <v>2.120323822719538</v>
       </c>
       <c r="F151">
         <v>-1</v>
       </c>
       <c r="G151">
-        <v>0.005720141173031427</v>
+        <v>0.005751634446725762</v>
       </c>
       <c r="H151">
-        <v>0.005674395290707754</v>
+        <v>0.005979676177280462</v>
       </c>
       <c r="I151">
-        <v>0.01425411767632845</v>
+        <v>-0.1319582694452992</v>
       </c>
       <c r="J151">
-        <v>0.7872941161835857</v>
+        <v>0.8006955092450049</v>
       </c>
       <c r="K151">
         <v>2.35</v>
@@ -8323,16 +8296,16 @@
         <v>3.87</v>
       </c>
       <c r="M151">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N151">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O151">
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8340,31 +8313,31 @@
         <v>0</v>
       </c>
       <c r="B152" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C152">
-        <v>2.038301570426869</v>
+        <v>2.013407841318734</v>
       </c>
       <c r="D152" t="s">
         <v>49</v>
       </c>
       <c r="E152">
-        <v>2.002377063637842</v>
+        <v>2.125285159031259</v>
       </c>
       <c r="F152">
         <v>-1</v>
       </c>
       <c r="G152">
-        <v>0.005981698429573131</v>
+        <v>0.006006592158681266</v>
       </c>
       <c r="H152">
-        <v>0.005677622936362158</v>
+        <v>0.005974714840968741</v>
       </c>
       <c r="I152">
-        <v>0.03592450678902681</v>
+        <v>-0.1118773177125254</v>
       </c>
       <c r="J152">
-        <v>0.7886793718292525</v>
+        <v>0.7986368634725065</v>
       </c>
       <c r="K152">
         <v>2.5</v>
@@ -8373,16 +8346,16 @@
         <v>4.01</v>
       </c>
       <c r="M152">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N152">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O152">
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8393,28 +8366,28 @@
         <v>29</v>
       </c>
       <c r="C153">
-        <v>2.016603476201257</v>
+        <v>1.99320337083961</v>
       </c>
       <c r="D153" t="s">
         <v>49</v>
       </c>
       <c r="E153">
-        <v>2.002377063637842</v>
+        <v>2.125285159031259</v>
       </c>
       <c r="F153">
         <v>-1</v>
       </c>
       <c r="G153">
-        <v>0.005723396523798744</v>
+        <v>0.005746796629160391</v>
       </c>
       <c r="H153">
-        <v>0.005677622936362158</v>
+        <v>0.005974714840968741</v>
       </c>
       <c r="I153">
-        <v>0.01422641256341484</v>
+        <v>-0.1320817881916494</v>
       </c>
       <c r="J153">
-        <v>0.7886793718292525</v>
+        <v>0.7986368634725065</v>
       </c>
       <c r="K153">
         <v>2.35</v>
@@ -8423,16 +8396,16 @@
         <v>3.87</v>
       </c>
       <c r="M153">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N153">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O153">
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8440,31 +8413,31 @@
         <v>0</v>
       </c>
       <c r="B154" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C154">
-        <v>2.035132415564467</v>
+        <v>2.024814922108121</v>
       </c>
       <c r="D154" t="s">
         <v>49</v>
       </c>
       <c r="E154">
-        <v>1.999423411306084</v>
+        <v>2.136281584912229</v>
       </c>
       <c r="F154">
         <v>-1</v>
       </c>
       <c r="G154">
-        <v>0.005984867584435533</v>
+        <v>0.005995185077891879</v>
       </c>
       <c r="H154">
-        <v>0.005680576588693916</v>
+        <v>0.00596371841508777</v>
       </c>
       <c r="I154">
-        <v>0.03570900425838364</v>
+        <v>-0.1114666628041077</v>
       </c>
       <c r="J154">
-        <v>0.7899470337742129</v>
+        <v>0.7940740311567515</v>
       </c>
       <c r="K154">
         <v>2.5</v>
@@ -8473,16 +8446,16 @@
         <v>4.01</v>
       </c>
       <c r="M154">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N154">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O154">
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8493,28 +8466,28 @@
         <v>29</v>
       </c>
       <c r="C155">
-        <v>2.013624470630599</v>
+        <v>2.003926026781634</v>
       </c>
       <c r="D155" t="s">
         <v>49</v>
       </c>
       <c r="E155">
-        <v>1.999423411306084</v>
+        <v>2.136281584912229</v>
       </c>
       <c r="F155">
         <v>-1</v>
       </c>
       <c r="G155">
-        <v>0.0057263755293694</v>
+        <v>0.005736073973218366</v>
       </c>
       <c r="H155">
-        <v>0.005680576588693916</v>
+        <v>0.00596371841508777</v>
       </c>
       <c r="I155">
-        <v>0.01420105932451587</v>
+        <v>-0.1323555581305946</v>
       </c>
       <c r="J155">
-        <v>0.7899470337742129</v>
+        <v>0.7940740311567515</v>
       </c>
       <c r="K155">
         <v>2.35</v>
@@ -8523,16 +8496,16 @@
         <v>3.87</v>
       </c>
       <c r="M155">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N155">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O155">
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8540,31 +8513,31 @@
         <v>0</v>
       </c>
       <c r="B156" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C156">
-        <v>2.033942517186959</v>
+        <v>2.037026290859836</v>
       </c>
       <c r="D156" t="s">
         <v>49</v>
       </c>
       <c r="E156">
-        <v>1.998314426018246</v>
+        <v>2.148053344388881</v>
       </c>
       <c r="F156">
         <v>-1</v>
       </c>
       <c r="G156">
-        <v>0.005986057482813041</v>
+        <v>0.005982973709140164</v>
       </c>
       <c r="H156">
-        <v>0.005681685573981754</v>
+        <v>0.005951946655611119</v>
       </c>
       <c r="I156">
-        <v>0.03562809116871302</v>
+        <v>-0.1110270535290456</v>
       </c>
       <c r="J156">
-        <v>0.7904229931252164</v>
+        <v>0.7891894836560657</v>
       </c>
       <c r="K156">
         <v>2.5</v>
@@ -8573,66 +8546,66 @@
         <v>4.01</v>
       </c>
       <c r="M156">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N156">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O156">
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="157" spans="1:16">
       <c r="A157" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C157">
-        <v>2.012505966155742</v>
+        <v>2.040400244545683</v>
       </c>
       <c r="D157" t="s">
         <v>49</v>
       </c>
       <c r="E157">
-        <v>1.998314426018246</v>
+        <v>2.151305835742038</v>
       </c>
       <c r="F157">
         <v>-1</v>
       </c>
       <c r="G157">
-        <v>0.00572749403384426</v>
+        <v>0.005979599755454317</v>
       </c>
       <c r="H157">
-        <v>0.005681685573981754</v>
+        <v>0.005948694164257961</v>
       </c>
       <c r="I157">
-        <v>0.01419154013749591</v>
+        <v>-0.1109055911963552</v>
       </c>
       <c r="J157">
-        <v>0.7904229931252164</v>
+        <v>0.7878399021817268</v>
       </c>
       <c r="K157">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L157">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M157">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N157">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O157">
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8640,31 +8613,31 @@
         <v>0</v>
       </c>
       <c r="B158" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C158">
-        <v>2.03219014170303</v>
+        <v>2.040677055689185</v>
       </c>
       <c r="D158" t="s">
         <v>49</v>
       </c>
       <c r="E158">
-        <v>1.996681212067224</v>
+        <v>2.151572681684375</v>
       </c>
       <c r="F158">
         <v>-1</v>
       </c>
       <c r="G158">
-        <v>0.00598780985829697</v>
+        <v>0.005979322944310814</v>
       </c>
       <c r="H158">
-        <v>0.005683318787932776</v>
+        <v>0.005948427318315626</v>
       </c>
       <c r="I158">
-        <v>0.03550892963580599</v>
+        <v>-0.1108956259951892</v>
       </c>
       <c r="J158">
-        <v>0.791123943318788</v>
+        <v>0.7877291777243258</v>
       </c>
       <c r="K158">
         <v>2.5</v>
@@ -8673,66 +8646,66 @@
         <v>4.01</v>
       </c>
       <c r="M158">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N158">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O158">
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="159" spans="1:16">
       <c r="A159" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B159" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C159">
-        <v>2.010858733200848</v>
+        <v>2.041764709541035</v>
       </c>
       <c r="D159" t="s">
         <v>49</v>
       </c>
       <c r="E159">
-        <v>1.996681212067224</v>
+        <v>2.152621179997558</v>
       </c>
       <c r="F159">
         <v>-1</v>
       </c>
       <c r="G159">
-        <v>0.005729141266799152</v>
+        <v>0.005978235290458964</v>
       </c>
       <c r="H159">
-        <v>0.005683318787932776</v>
+        <v>0.005947378820002442</v>
       </c>
       <c r="I159">
-        <v>0.01417752113362458</v>
+        <v>-0.1108564704565227</v>
       </c>
       <c r="J159">
-        <v>0.791123943318788</v>
+        <v>0.7872941161835857</v>
       </c>
       <c r="K159">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L159">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M159">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N159">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O159">
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -8740,31 +8713,31 @@
         <v>0</v>
       </c>
       <c r="B160" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C160">
-        <v>2.031041804995824</v>
+        <v>2.038301570426869</v>
       </c>
       <c r="D160" t="s">
         <v>49</v>
       </c>
       <c r="E160">
-        <v>1.995610962256108</v>
+        <v>2.149282713891501</v>
       </c>
       <c r="F160">
         <v>-1</v>
       </c>
       <c r="G160">
-        <v>0.005988958195004175</v>
+        <v>0.005981698429573131</v>
       </c>
       <c r="H160">
-        <v>0.005684389037743891</v>
+        <v>0.005950717286108499</v>
       </c>
       <c r="I160">
-        <v>0.03543084273971608</v>
+        <v>-0.1109811434646324</v>
       </c>
       <c r="J160">
-        <v>0.7915832780016702</v>
+        <v>0.7886793718292525</v>
       </c>
       <c r="K160">
         <v>2.5</v>
@@ -8773,66 +8746,66 @@
         <v>4.01</v>
       </c>
       <c r="M160">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N160">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O160">
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="161" spans="1:16">
       <c r="A161" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B161" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C161">
-        <v>2.009779296696075</v>
+        <v>2.035132415564467</v>
       </c>
       <c r="D161" t="s">
         <v>49</v>
       </c>
       <c r="E161">
-        <v>1.995610962256108</v>
+        <v>2.146227648604146</v>
       </c>
       <c r="F161">
         <v>-1</v>
       </c>
       <c r="G161">
-        <v>0.005730220703303925</v>
+        <v>0.005984867584435533</v>
       </c>
       <c r="H161">
-        <v>0.005684389037743891</v>
+        <v>0.005953772351395854</v>
       </c>
       <c r="I161">
-        <v>0.01416833443996701</v>
+        <v>-0.1110952330396793</v>
       </c>
       <c r="J161">
-        <v>0.7915832780016702</v>
+        <v>0.7899470337742129</v>
       </c>
       <c r="K161">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L161">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M161">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N161">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O161">
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -8840,31 +8813,31 @@
         <v>0</v>
       </c>
       <c r="B162" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C162">
-        <v>2.032225684349332</v>
+        <v>2.033942517186959</v>
       </c>
       <c r="D162" t="s">
         <v>49</v>
       </c>
       <c r="E162">
-        <v>1.996714337813577</v>
+        <v>2.145080586568228</v>
       </c>
       <c r="F162">
         <v>-1</v>
       </c>
       <c r="G162">
-        <v>0.005987774315650668</v>
+        <v>0.005986057482813041</v>
       </c>
       <c r="H162">
-        <v>0.005683285662186423</v>
+        <v>0.005954919413431771</v>
       </c>
       <c r="I162">
-        <v>0.03551134653575461</v>
+        <v>-0.1111380693812696</v>
       </c>
       <c r="J162">
-        <v>0.7911097262602672</v>
+        <v>0.7904229931252164</v>
       </c>
       <c r="K162">
         <v>2.5</v>
@@ -8873,66 +8846,66 @@
         <v>4.01</v>
       </c>
       <c r="M162">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N162">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O162">
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="163" spans="1:16">
       <c r="A163" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B163" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C163">
-        <v>2.010892143288372</v>
+        <v>2.03219014170303</v>
       </c>
       <c r="D163" t="s">
         <v>49</v>
       </c>
       <c r="E163">
-        <v>1.996714337813577</v>
+        <v>2.14339129660172</v>
       </c>
       <c r="F163">
         <v>-1</v>
       </c>
       <c r="G163">
-        <v>0.005729107856711628</v>
+        <v>0.00598780985829697</v>
       </c>
       <c r="H163">
-        <v>0.005683285662186423</v>
+        <v>0.005956608703398279</v>
       </c>
       <c r="I163">
-        <v>0.01417780547479519</v>
+        <v>-0.1112011548986906</v>
       </c>
       <c r="J163">
-        <v>0.7911097262602672</v>
+        <v>0.791123943318788</v>
       </c>
       <c r="K163">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="L163">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="M163">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N163">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="O163">
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -8940,49 +8913,49 @@
         <v>0</v>
       </c>
       <c r="B164" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C164">
-        <v>2.033826265263685</v>
+        <v>1.559502895465797</v>
       </c>
       <c r="D164" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E164">
-        <v>1.998206079225755</v>
+        <v>1.912426863301427</v>
       </c>
       <c r="F164">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G164">
-        <v>0.005986173734736314</v>
+        <v>0.004660497104534203</v>
       </c>
       <c r="H164">
-        <v>0.005681793920774245</v>
+        <v>0.005967573136698573</v>
       </c>
       <c r="I164">
-        <v>0.03562018603793038</v>
+        <v>0.35292396783563</v>
       </c>
       <c r="J164">
-        <v>0.7904694938945258</v>
+        <v>0.7951267202739504</v>
       </c>
       <c r="K164">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="L164">
-        <v>4.01</v>
+        <v>3.11</v>
       </c>
       <c r="M164">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="N164">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="O164">
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -8990,449 +8963,49 @@
         <v>0</v>
       </c>
       <c r="B165" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C165">
-        <v>2.037114148133088</v>
+        <v>1.557903064751518</v>
       </c>
       <c r="D165" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E165">
-        <v>2.001270386060038</v>
+        <v>1.910334776982754</v>
       </c>
       <c r="F165">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G165">
-        <v>0.005982885851866911</v>
+        <v>0.004662096935248481</v>
       </c>
       <c r="H165">
-        <v>0.005678729613939962</v>
+        <v>0.005969665223017246</v>
       </c>
       <c r="I165">
-        <v>0.03584376207305029</v>
+        <v>0.3524317122312364</v>
       </c>
       <c r="J165">
-        <v>0.7891543407467646</v>
+        <v>0.7959471462812728</v>
       </c>
       <c r="K165">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="L165">
-        <v>4.01</v>
+        <v>3.11</v>
       </c>
       <c r="M165">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="N165">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="O165">
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="166" spans="1:16">
-      <c r="A166" s="1">
-        <v>0</v>
-      </c>
-      <c r="B166" t="s">
-        <v>32</v>
-      </c>
-      <c r="C166">
-        <v>2.041024370702765</v>
-      </c>
-      <c r="D166" t="s">
-        <v>49</v>
-      </c>
-      <c r="E166">
-        <v>2.004914713494977</v>
-      </c>
-      <c r="F166">
-        <v>-1</v>
-      </c>
-      <c r="G166">
-        <v>0.005978975629297235</v>
-      </c>
-      <c r="H166">
-        <v>0.005675085286505023</v>
-      </c>
-      <c r="I166">
-        <v>0.03610965720778792</v>
-      </c>
-      <c r="J166">
-        <v>0.7875902517188939</v>
-      </c>
-      <c r="K166">
-        <v>2.5</v>
-      </c>
-      <c r="L166">
-        <v>4.01</v>
-      </c>
-      <c r="M166">
-        <v>2.33</v>
-      </c>
-      <c r="N166">
-        <v>3.84</v>
-      </c>
-      <c r="O166">
-        <v>1</v>
-      </c>
-      <c r="P166" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="167" spans="1:16">
-      <c r="A167" s="1">
-        <v>0</v>
-      </c>
-      <c r="B167" t="s">
-        <v>32</v>
-      </c>
-      <c r="C167">
-        <v>2.042989638697718</v>
-      </c>
-      <c r="D167" t="s">
-        <v>49</v>
-      </c>
-      <c r="E167">
-        <v>2.006746343266273</v>
-      </c>
-      <c r="F167">
-        <v>-1</v>
-      </c>
-      <c r="G167">
-        <v>0.005977010361302281</v>
-      </c>
-      <c r="H167">
-        <v>0.005673253656733726</v>
-      </c>
-      <c r="I167">
-        <v>0.03624329543144489</v>
-      </c>
-      <c r="J167">
-        <v>0.7868041445209126</v>
-      </c>
-      <c r="K167">
-        <v>2.5</v>
-      </c>
-      <c r="L167">
-        <v>4.01</v>
-      </c>
-      <c r="M167">
-        <v>2.33</v>
-      </c>
-      <c r="N167">
-        <v>3.84</v>
-      </c>
-      <c r="O167">
-        <v>1</v>
-      </c>
-      <c r="P167" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="168" spans="1:16">
-      <c r="A168" s="1">
-        <v>0</v>
-      </c>
-      <c r="B168" t="s">
-        <v>32</v>
-      </c>
-      <c r="C168">
-        <v>2.046475047291454</v>
-      </c>
-      <c r="D168" t="s">
-        <v>49</v>
-      </c>
-      <c r="E168">
-        <v>2.009994744075636</v>
-      </c>
-      <c r="F168">
-        <v>-1</v>
-      </c>
-      <c r="G168">
-        <v>0.005973524952708546</v>
-      </c>
-      <c r="H168">
-        <v>0.005670005255924364</v>
-      </c>
-      <c r="I168">
-        <v>0.03648030321581874</v>
-      </c>
-      <c r="J168">
-        <v>0.7854099810834182</v>
-      </c>
-      <c r="K168">
-        <v>2.5</v>
-      </c>
-      <c r="L168">
-        <v>4.01</v>
-      </c>
-      <c r="M168">
-        <v>2.33</v>
-      </c>
-      <c r="N168">
-        <v>3.84</v>
-      </c>
-      <c r="O168">
-        <v>1</v>
-      </c>
-      <c r="P168" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="169" spans="1:16">
-      <c r="A169" s="1">
-        <v>0</v>
-      </c>
-      <c r="B169" t="s">
-        <v>32</v>
-      </c>
-      <c r="C169">
-        <v>2.05115387029975</v>
-      </c>
-      <c r="D169" t="s">
-        <v>49</v>
-      </c>
-      <c r="E169">
-        <v>2.014355407119367</v>
-      </c>
-      <c r="F169">
-        <v>-1</v>
-      </c>
-      <c r="G169">
-        <v>0.00596884612970025</v>
-      </c>
-      <c r="H169">
-        <v>0.005665644592880632</v>
-      </c>
-      <c r="I169">
-        <v>0.03679846318038305</v>
-      </c>
-      <c r="J169">
-        <v>0.7835384518800999</v>
-      </c>
-      <c r="K169">
-        <v>2.5</v>
-      </c>
-      <c r="L169">
-        <v>4.01</v>
-      </c>
-      <c r="M169">
-        <v>2.33</v>
-      </c>
-      <c r="N169">
-        <v>3.84</v>
-      </c>
-      <c r="O169">
-        <v>1</v>
-      </c>
-      <c r="P169" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="170" spans="1:16">
-      <c r="A170" s="1">
-        <v>0</v>
-      </c>
-      <c r="B170" t="s">
-        <v>37</v>
-      </c>
-      <c r="C170">
-        <v>1.569608330766713</v>
-      </c>
-      <c r="D170" t="s">
-        <v>25</v>
-      </c>
-      <c r="E170">
-        <v>1.925641663310317</v>
-      </c>
-      <c r="F170">
-        <v>1</v>
-      </c>
-      <c r="G170">
-        <v>0.004650391669233286</v>
-      </c>
-      <c r="H170">
-        <v>0.005954358336689684</v>
-      </c>
-      <c r="I170">
-        <v>0.3560333325436043</v>
-      </c>
-      <c r="J170">
-        <v>0.78994444576066</v>
-      </c>
-      <c r="K170">
-        <v>1.95</v>
-      </c>
-      <c r="L170">
-        <v>3.11</v>
-      </c>
-      <c r="M170">
-        <v>2.55</v>
-      </c>
-      <c r="N170">
-        <v>3.94</v>
-      </c>
-      <c r="O170">
-        <v>1</v>
-      </c>
-      <c r="P170" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="171" spans="1:16">
-      <c r="A171" s="1">
-        <v>0</v>
-      </c>
-      <c r="B171" t="s">
-        <v>37</v>
-      </c>
-      <c r="C171">
-        <v>1.563290930299889</v>
-      </c>
-      <c r="D171" t="s">
-        <v>25</v>
-      </c>
-      <c r="E171">
-        <v>1.91738044731524</v>
-      </c>
-      <c r="F171">
-        <v>1</v>
-      </c>
-      <c r="G171">
-        <v>0.00465670906970011</v>
-      </c>
-      <c r="H171">
-        <v>0.005962619552684761</v>
-      </c>
-      <c r="I171">
-        <v>0.3540895170153506</v>
-      </c>
-      <c r="J171">
-        <v>0.7931841383077493</v>
-      </c>
-      <c r="K171">
-        <v>1.95</v>
-      </c>
-      <c r="L171">
-        <v>3.11</v>
-      </c>
-      <c r="M171">
-        <v>2.55</v>
-      </c>
-      <c r="N171">
-        <v>3.94</v>
-      </c>
-      <c r="O171">
-        <v>1</v>
-      </c>
-      <c r="P171" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="172" spans="1:16">
-      <c r="A172" s="1">
-        <v>0</v>
-      </c>
-      <c r="B172" t="s">
-        <v>37</v>
-      </c>
-      <c r="C172">
-        <v>1.559502895465797</v>
-      </c>
-      <c r="D172" t="s">
-        <v>25</v>
-      </c>
-      <c r="E172">
-        <v>1.912426863301427</v>
-      </c>
-      <c r="F172">
-        <v>1</v>
-      </c>
-      <c r="G172">
-        <v>0.004660497104534203</v>
-      </c>
-      <c r="H172">
-        <v>0.005967573136698573</v>
-      </c>
-      <c r="I172">
-        <v>0.35292396783563</v>
-      </c>
-      <c r="J172">
-        <v>0.7951267202739504</v>
-      </c>
-      <c r="K172">
-        <v>1.95</v>
-      </c>
-      <c r="L172">
-        <v>3.11</v>
-      </c>
-      <c r="M172">
-        <v>2.55</v>
-      </c>
-      <c r="N172">
-        <v>3.94</v>
-      </c>
-      <c r="O172">
-        <v>1</v>
-      </c>
-      <c r="P172" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="173" spans="1:16">
-      <c r="A173" s="1">
-        <v>0</v>
-      </c>
-      <c r="B173" t="s">
-        <v>38</v>
-      </c>
-      <c r="C173">
-        <v>1.590146235974642</v>
-      </c>
-      <c r="D173" t="s">
-        <v>25</v>
-      </c>
-      <c r="E173">
-        <v>1.910334776982754</v>
-      </c>
-      <c r="F173">
-        <v>1</v>
-      </c>
-      <c r="G173">
-        <v>0.004789853764025359</v>
-      </c>
-      <c r="H173">
-        <v>0.005969665223017246</v>
-      </c>
-      <c r="I173">
-        <v>0.3201885410081127</v>
-      </c>
-      <c r="J173">
-        <v>0.7959471462812728</v>
-      </c>
-      <c r="K173">
-        <v>2.01</v>
-      </c>
-      <c r="L173">
-        <v>3.19</v>
-      </c>
-      <c r="M173">
-        <v>2.55</v>
-      </c>
-      <c r="N173">
-        <v>3.94</v>
-      </c>
-      <c r="O173">
-        <v>1</v>
-      </c>
-      <c r="P173" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01618-601618.xlsx
+++ b/s60_signal/position-01618-601618.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="167">
   <si>
     <t>trade_time</t>
   </si>
@@ -115,12 +115,12 @@
     <t>2021-07-26</t>
   </si>
   <si>
+    <t>2021-01-15</t>
+  </si>
+  <si>
     <t>2021-01-13</t>
   </si>
   <si>
-    <t>2021-01-15</t>
-  </si>
-  <si>
     <t>2021-02-26</t>
   </si>
   <si>
@@ -133,6 +133,9 @@
     <t>2021-02-23</t>
   </si>
   <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
     <t>2021-07-19</t>
   </si>
   <si>
@@ -184,12 +187,18 @@
     <t>2021-02-03</t>
   </si>
   <si>
+    <t>2021-08-23</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>2021-03-09</t>
+  </si>
+  <si>
     <t>2021-08-19</t>
   </si>
   <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
     <t>2016-12-23</t>
   </si>
   <si>
@@ -466,13 +475,7 @@
     <t>2021-06-18</t>
   </si>
   <si>
-    <t>2021-06-21</t>
-  </si>
-  <si>
-    <t>2021-06-22</t>
-  </si>
-  <si>
-    <t>2021-06-23</t>
+    <t>2021-07-09</t>
   </si>
   <si>
     <t>2021-07-12</t>
@@ -509,6 +512,9 @@
   </si>
   <si>
     <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
   </si>
 </sst>
 </file>
@@ -866,7 +872,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P203"/>
+  <dimension ref="A1:P196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -927,7 +933,7 @@
         <v>2.241636620202809</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E2">
         <v>2.083673377356266</v>
@@ -963,7 +969,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -977,7 +983,7 @@
         <v>2.291018963074085</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3">
         <v>2.748932188801797</v>
@@ -1013,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1027,7 +1033,7 @@
         <v>0.1640886968569069</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E4">
         <v>0.8087275807852619</v>
@@ -1063,7 +1069,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1077,7 +1083,7 @@
         <v>0.1567937244930127</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E5">
         <v>0.8087275807852619</v>
@@ -1113,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1127,7 +1133,7 @@
         <v>0.06008199184724816</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6">
         <v>0.7118353409391309</v>
@@ -1163,7 +1169,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1177,7 +1183,7 @@
         <v>0.05109309920632388</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7">
         <v>0.7118353409391309</v>
@@ -1213,7 +1219,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1227,7 +1233,7 @@
         <v>-0.0569506423664734</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8">
         <v>0.6028081963621785</v>
@@ -1263,7 +1269,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1277,7 +1283,7 @@
         <v>-0.06784560396853312</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9">
         <v>0.6028081963621785</v>
@@ -1313,7 +1319,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1327,7 +1333,7 @@
         <v>-0.1396452470657845</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10">
         <v>0.5257702258605397</v>
@@ -1363,7 +1369,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1377,7 +1383,7 @@
         <v>-0.1518870263339567</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E11">
         <v>0.5257702258605397</v>
@@ -1413,7 +1419,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1427,7 +1433,7 @@
         <v>-0.2479133877986754</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E12">
         <v>0.424908049151723</v>
@@ -1463,7 +1469,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1477,7 +1483,7 @@
         <v>-0.2619184918344848</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E13">
         <v>0.424908049151723</v>
@@ -1513,7 +1519,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1527,7 +1533,7 @@
         <v>-0.3399965939203824</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E14">
         <v>0.3391236942630966</v>
@@ -1563,7 +1569,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1577,7 +1583,7 @@
         <v>0.9756011105228968</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15">
         <v>0.8107654111102569</v>
@@ -1613,7 +1619,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1627,7 +1633,7 @@
         <v>1.301145679016073</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E16">
         <v>1.173416666670367</v>
@@ -1663,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1677,7 +1683,7 @@
         <v>1.296277364845049</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E17">
         <v>1.230890933009092</v>
@@ -1713,7 +1719,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1727,7 +1733,7 @@
         <v>0.4435035626339812</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E18">
         <v>0.9439906537348826</v>
@@ -1763,7 +1769,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1777,7 +1783,7 @@
         <v>0.4423533289773536</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E19">
         <v>0.9439906537348826</v>
@@ -1813,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1827,7 +1833,7 @@
         <v>1.507350128118183</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E20">
         <v>1.202821457299868</v>
@@ -1863,7 +1869,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -1877,7 +1883,7 @@
         <v>1.54125697476493</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E21">
         <v>1.238224194239853</v>
@@ -1913,7 +1919,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -1927,7 +1933,7 @@
         <v>1.573438797246031</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E22">
         <v>1.271825803006885</v>
@@ -1963,7 +1969,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -1977,7 +1983,7 @@
         <v>1.613400857289038</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E23">
         <v>1.313550895110613</v>
@@ -2013,7 +2019,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2027,7 +2033,7 @@
         <v>1.593400857289038</v>
       </c>
       <c r="D24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E24">
         <v>1.363275825771058</v>
@@ -2063,7 +2069,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2077,7 +2083,7 @@
         <v>1.645344720184119</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E25">
         <v>1.346904046074595</v>
@@ -2113,7 +2119,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2127,7 +2133,7 @@
         <v>1.625344720184119</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E26">
         <v>1.394045281942056</v>
@@ -2163,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2177,7 +2183,7 @@
         <v>1.68180858461344</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E27">
         <v>1.384976610405209</v>
@@ -2213,7 +2219,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2227,7 +2233,7 @@
         <v>1.66180858461344</v>
       </c>
       <c r="D28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E28">
         <v>1.429168563120298</v>
@@ -2263,7 +2269,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2277,7 +2283,7 @@
         <v>1.710614904938503</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E29">
         <v>1.415053797803437</v>
@@ -2313,7 +2319,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2327,7 +2333,7 @@
         <v>1.690614904938503</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E30">
         <v>1.456915827551058</v>
@@ -2363,7 +2369,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2413,7 +2419,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2463,7 +2469,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2513,7 +2519,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2527,7 +2533,7 @@
         <v>2.638017457305502</v>
       </c>
       <c r="D34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E34">
         <v>2.678463757115749</v>
@@ -2563,7 +2569,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2577,7 +2583,7 @@
         <v>2.662412903225806</v>
       </c>
       <c r="D35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E35">
         <v>2.678463757115749</v>
@@ -2613,7 +2619,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2627,7 +2633,7 @@
         <v>2.657763187855787</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E36">
         <v>2.678463757115749</v>
@@ -2663,7 +2669,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2713,7 +2719,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2763,7 +2769,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2813,7 +2819,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -2863,7 +2869,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -2913,7 +2919,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -2963,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3013,7 +3019,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3063,7 +3069,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3113,7 +3119,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3163,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3213,7 +3219,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3263,7 +3269,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3313,7 +3319,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3363,7 +3369,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3413,7 +3419,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3421,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C52">
-        <v>2.182359258383708</v>
+        <v>2.286822802336969</v>
       </c>
       <c r="D52" t="s">
         <v>36</v>
@@ -3436,22 +3442,22 @@
         <v>-1</v>
       </c>
       <c r="G52">
-        <v>0.005697640741616292</v>
+        <v>0.005733177197663031</v>
       </c>
       <c r="H52">
         <v>0.005711142818547162</v>
       </c>
       <c r="I52">
-        <v>-0.2064979230691293</v>
+        <v>-0.1020343791158687</v>
       </c>
       <c r="J52">
         <v>0.6892708790652124</v>
       </c>
       <c r="K52">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="L52">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="M52">
         <v>2.41</v>
@@ -3463,7 +3469,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3513,7 +3519,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3563,7 +3569,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3613,7 +3619,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3663,7 +3669,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3713,7 +3719,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3763,7 +3769,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3813,7 +3819,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -3824,10 +3830,10 @@
         <v>33</v>
       </c>
       <c r="C60">
-        <v>1.939614977812812</v>
+        <v>1.949614977812812</v>
       </c>
       <c r="D60" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E60">
         <v>1.673598643538204</v>
@@ -3836,13 +3842,13 @@
         <v>-1</v>
       </c>
       <c r="G60">
-        <v>0.004580385022187188</v>
+        <v>0.004590385022187188</v>
       </c>
       <c r="H60">
         <v>0.004426401356461797</v>
       </c>
       <c r="I60">
-        <v>0.266016334274608</v>
+        <v>0.2760163342746083</v>
       </c>
       <c r="J60">
         <v>0.8002333467801142</v>
@@ -3851,7 +3857,7 @@
         <v>1.65</v>
       </c>
       <c r="L60">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="M60">
         <v>1.72</v>
@@ -3863,7 +3869,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -3871,49 +3877,49 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C61">
-        <v>1.949614977812812</v>
+        <v>2.009416633049714</v>
       </c>
       <c r="D61" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E61">
-        <v>1.673598643538204</v>
+        <v>2.121437634259925</v>
       </c>
       <c r="F61">
         <v>-1</v>
       </c>
       <c r="G61">
-        <v>0.004590385022187188</v>
+        <v>0.006010583366950286</v>
       </c>
       <c r="H61">
-        <v>0.004426401356461797</v>
+        <v>0.005978562365740075</v>
       </c>
       <c r="I61">
-        <v>0.2760163342746083</v>
+        <v>-0.1120210012102105</v>
       </c>
       <c r="J61">
         <v>0.8002333467801142</v>
       </c>
       <c r="K61">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="L61">
-        <v>3.27</v>
+        <v>4.01</v>
       </c>
       <c r="M61">
-        <v>1.72</v>
+        <v>2.41</v>
       </c>
       <c r="N61">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="O61">
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -3921,10 +3927,10 @@
         <v>2</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C62">
-        <v>2.009416633049714</v>
+        <v>1.989451635066732</v>
       </c>
       <c r="D62" t="s">
         <v>36</v>
@@ -3936,22 +3942,22 @@
         <v>-1</v>
       </c>
       <c r="G62">
-        <v>0.006010583366950286</v>
+        <v>0.005750548364933269</v>
       </c>
       <c r="H62">
         <v>0.005978562365740075</v>
       </c>
       <c r="I62">
-        <v>-0.1120210012102105</v>
+        <v>-0.1319859991931931</v>
       </c>
       <c r="J62">
         <v>0.8002333467801142</v>
       </c>
       <c r="K62">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L62">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M62">
         <v>2.41</v>
@@ -3963,7 +3969,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -3971,10 +3977,10 @@
         <v>3</v>
       </c>
       <c r="B63" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C63">
-        <v>1.989451635066732</v>
+        <v>1.975456302002334</v>
       </c>
       <c r="D63" t="s">
         <v>36</v>
@@ -3986,22 +3992,22 @@
         <v>-1</v>
       </c>
       <c r="G63">
-        <v>0.005750548364933269</v>
+        <v>0.005704543697997666</v>
       </c>
       <c r="H63">
         <v>0.005978562365740075</v>
       </c>
       <c r="I63">
-        <v>-0.1319859991931931</v>
+        <v>-0.1459813322575909</v>
       </c>
       <c r="J63">
         <v>0.8002333467801142</v>
       </c>
       <c r="K63">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="L63">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="M63">
         <v>2.41</v>
@@ -4013,168 +4019,168 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C64">
-        <v>1.941460968937936</v>
+        <v>1.858458903856472</v>
       </c>
       <c r="D64" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E64">
-        <v>2.121437634259925</v>
+        <v>1.58899958462614</v>
       </c>
       <c r="F64">
         <v>-1</v>
       </c>
       <c r="G64">
-        <v>0.005638539031062064</v>
+        <v>0.004661541096143528</v>
       </c>
       <c r="H64">
-        <v>0.005978562365740075</v>
+        <v>0.004511000415373859</v>
       </c>
       <c r="I64">
-        <v>-0.1799766653219885</v>
+        <v>0.2694593192303316</v>
       </c>
       <c r="J64">
-        <v>0.8002333467801142</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K64">
-        <v>2.31</v>
+        <v>1.65</v>
       </c>
       <c r="L64">
-        <v>3.79</v>
+        <v>3.26</v>
       </c>
       <c r="M64">
-        <v>2.41</v>
+        <v>1.72</v>
       </c>
       <c r="N64">
-        <v>4.05</v>
+        <v>3.05</v>
       </c>
       <c r="O64">
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B65" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C65">
-        <v>1.975456302002334</v>
+        <v>1.868458903856472</v>
       </c>
       <c r="D65" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E65">
-        <v>2.121437634259925</v>
+        <v>1.58899958462614</v>
       </c>
       <c r="F65">
         <v>-1</v>
       </c>
       <c r="G65">
-        <v>0.005704543697997666</v>
+        <v>0.004671541096143528</v>
       </c>
       <c r="H65">
-        <v>0.005978562365740075</v>
+        <v>0.004511000415373859</v>
       </c>
       <c r="I65">
-        <v>-0.1459813322575909</v>
+        <v>0.2794593192303318</v>
       </c>
       <c r="J65">
-        <v>0.8002333467801142</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K65">
-        <v>2.33</v>
+        <v>1.65</v>
       </c>
       <c r="L65">
-        <v>3.84</v>
+        <v>3.27</v>
       </c>
       <c r="M65">
-        <v>2.41</v>
+        <v>1.72</v>
       </c>
       <c r="N65">
-        <v>4.05</v>
+        <v>3.05</v>
       </c>
       <c r="O65">
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C66">
-        <v>1.858458903856472</v>
+        <v>1.886452884631018</v>
       </c>
       <c r="D66" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E66">
-        <v>1.559424034625328</v>
+        <v>2.002900580784301</v>
       </c>
       <c r="F66">
         <v>-1</v>
       </c>
       <c r="G66">
-        <v>0.004661541096143528</v>
+        <v>0.006133547115368982</v>
       </c>
       <c r="H66">
-        <v>0.004260575965374673</v>
+        <v>0.006097099419215699</v>
       </c>
       <c r="I66">
-        <v>0.2990348692311444</v>
+        <v>-0.1164476961532834</v>
       </c>
       <c r="J66">
         <v>0.8494188461475927</v>
       </c>
       <c r="K66">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="L66">
-        <v>3.26</v>
+        <v>4.01</v>
       </c>
       <c r="M66">
-        <v>1.59</v>
+        <v>2.41</v>
       </c>
       <c r="N66">
-        <v>2.91</v>
+        <v>4.05</v>
       </c>
       <c r="O66">
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="1:16">
       <c r="A67" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B67" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C67">
-        <v>1.886452884631018</v>
+        <v>1.873865711553157</v>
       </c>
       <c r="D67" t="s">
         <v>36</v>
@@ -4186,22 +4192,22 @@
         <v>-1</v>
       </c>
       <c r="G67">
-        <v>0.006133547115368982</v>
+        <v>0.005866134288446843</v>
       </c>
       <c r="H67">
         <v>0.006097099419215699</v>
       </c>
       <c r="I67">
-        <v>-0.1164476961532834</v>
+        <v>-0.1290348692311443</v>
       </c>
       <c r="J67">
         <v>0.8494188461475927</v>
       </c>
       <c r="K67">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L67">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M67">
         <v>2.41</v>
@@ -4213,18 +4219,18 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:16">
       <c r="A68" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B68" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C68">
-        <v>1.873865711553157</v>
+        <v>1.860854088476109</v>
       </c>
       <c r="D68" t="s">
         <v>36</v>
@@ -4236,22 +4242,22 @@
         <v>-1</v>
       </c>
       <c r="G68">
-        <v>0.005866134288446843</v>
+        <v>0.005819145911523891</v>
       </c>
       <c r="H68">
         <v>0.006097099419215699</v>
       </c>
       <c r="I68">
-        <v>-0.1290348692311443</v>
+        <v>-0.1420464923081926</v>
       </c>
       <c r="J68">
         <v>0.8494188461475927</v>
       </c>
       <c r="K68">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="L68">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="M68">
         <v>2.41</v>
@@ -4263,168 +4269,168 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C69">
-        <v>1.860854088476109</v>
+        <v>1.778043160662217</v>
       </c>
       <c r="D69" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="E69">
-        <v>2.002900580784301</v>
+        <v>1.4819325002745</v>
       </c>
       <c r="F69">
         <v>-1</v>
       </c>
       <c r="G69">
-        <v>0.005819145911523891</v>
+        <v>0.004741956839337784</v>
       </c>
       <c r="H69">
-        <v>0.006097099419215699</v>
+        <v>0.004338067499725501</v>
       </c>
       <c r="I69">
-        <v>-0.1420464923081926</v>
+        <v>0.2961106603877166</v>
       </c>
       <c r="J69">
-        <v>0.8494188461475927</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K69">
-        <v>2.33</v>
+        <v>1.65</v>
       </c>
       <c r="L69">
-        <v>3.84</v>
+        <v>3.26</v>
       </c>
       <c r="M69">
-        <v>2.41</v>
+        <v>1.59</v>
       </c>
       <c r="N69">
-        <v>4.05</v>
+        <v>2.91</v>
       </c>
       <c r="O69">
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B70" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C70">
-        <v>1.778043160662217</v>
+        <v>1.253223538131198</v>
       </c>
       <c r="D70" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E70">
-        <v>1.4819325002745</v>
+        <v>1.508412028621273</v>
       </c>
       <c r="F70">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G70">
-        <v>0.004741956839337784</v>
+        <v>0.005366776461868803</v>
       </c>
       <c r="H70">
-        <v>0.004338067499725501</v>
+        <v>0.004831587971378727</v>
       </c>
       <c r="I70">
-        <v>0.2961106603877166</v>
+        <v>0.2551884904900752</v>
       </c>
       <c r="J70">
         <v>0.898155660204717</v>
       </c>
       <c r="K70">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="L70">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="M70">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="N70">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="O70">
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B71" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C71">
-        <v>1.253223538131198</v>
+        <v>1.764610849488207</v>
       </c>
       <c r="D71" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E71">
-        <v>1.508412028621273</v>
+        <v>1.885444858906632</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G71">
-        <v>0.005366776461868803</v>
+        <v>0.006255389150511792</v>
       </c>
       <c r="H71">
-        <v>0.004831587971378727</v>
+        <v>0.006214555141093368</v>
       </c>
       <c r="I71">
-        <v>0.2551884904900752</v>
+        <v>-0.1208340094184246</v>
       </c>
       <c r="J71">
         <v>0.898155660204717</v>
       </c>
       <c r="K71">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="L71">
-        <v>3.31</v>
+        <v>4.01</v>
       </c>
       <c r="M71">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="N71">
-        <v>3.17</v>
+        <v>4.05</v>
       </c>
       <c r="O71">
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C72">
-        <v>1.764610849488207</v>
+        <v>1.759334198518915</v>
       </c>
       <c r="D72" t="s">
         <v>36</v>
@@ -4436,22 +4442,22 @@
         <v>-1</v>
       </c>
       <c r="G72">
-        <v>0.006255389150511792</v>
+        <v>0.005980665801481085</v>
       </c>
       <c r="H72">
         <v>0.006214555141093368</v>
       </c>
       <c r="I72">
-        <v>-0.1208340094184246</v>
+        <v>-0.1261106603877167</v>
       </c>
       <c r="J72">
         <v>0.898155660204717</v>
       </c>
       <c r="K72">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L72">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M72">
         <v>2.41</v>
@@ -4463,18 +4469,18 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B73" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C73">
-        <v>1.759334198518915</v>
+        <v>1.747297311723009</v>
       </c>
       <c r="D73" t="s">
         <v>36</v>
@@ -4486,22 +4492,22 @@
         <v>-1</v>
       </c>
       <c r="G73">
-        <v>0.005980665801481085</v>
+        <v>0.00593270268827699</v>
       </c>
       <c r="H73">
         <v>0.006214555141093368</v>
       </c>
       <c r="I73">
-        <v>-0.1261106603877167</v>
+        <v>-0.1381475471836224</v>
       </c>
       <c r="J73">
         <v>0.898155660204717</v>
       </c>
       <c r="K73">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="L73">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="M73">
         <v>2.41</v>
@@ -4513,168 +4519,168 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74" spans="1:16">
       <c r="A74" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C74">
-        <v>1.747297311723009</v>
+        <v>1.698438247560837</v>
       </c>
       <c r="D74" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E74">
-        <v>1.885444858906632</v>
+        <v>1.400398406873488</v>
       </c>
       <c r="F74">
         <v>-1</v>
       </c>
       <c r="G74">
-        <v>0.00593270268827699</v>
+        <v>0.004821561752439162</v>
       </c>
       <c r="H74">
-        <v>0.006214555141093368</v>
+        <v>0.004239601593126512</v>
       </c>
       <c r="I74">
-        <v>-0.1381475471836224</v>
+        <v>0.2980398406873488</v>
       </c>
       <c r="J74">
-        <v>0.898155660204717</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K74">
-        <v>2.33</v>
+        <v>1.65</v>
       </c>
       <c r="L74">
-        <v>3.84</v>
+        <v>3.26</v>
       </c>
       <c r="M74">
-        <v>2.41</v>
+        <v>1.5</v>
       </c>
       <c r="N74">
-        <v>4.05</v>
+        <v>2.82</v>
       </c>
       <c r="O74">
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B75" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C75">
-        <v>1.698438247560837</v>
+        <v>1.142741567826858</v>
       </c>
       <c r="D75" t="s">
         <v>54</v>
       </c>
       <c r="E75">
-        <v>1.400398406873488</v>
+        <v>1.419158035143968</v>
       </c>
       <c r="F75">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G75">
-        <v>0.004821561752439162</v>
+        <v>0.005477258432173141</v>
       </c>
       <c r="H75">
-        <v>0.004239601593126512</v>
+        <v>0.004920841964856031</v>
       </c>
       <c r="I75">
-        <v>0.2980398406873488</v>
+        <v>0.2764164673171099</v>
       </c>
       <c r="J75">
         <v>0.9464010620843414</v>
       </c>
       <c r="K75">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="L75">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="M75">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="N75">
-        <v>2.82</v>
+        <v>3.17</v>
       </c>
       <c r="O75">
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B76" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C76">
-        <v>1.142741567826858</v>
+        <v>1.643997344789146</v>
       </c>
       <c r="D76" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E76">
-        <v>1.419158035143968</v>
+        <v>1.769173440376737</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G76">
-        <v>0.005477258432173141</v>
+        <v>0.006376002655210854</v>
       </c>
       <c r="H76">
-        <v>0.004920841964856031</v>
+        <v>0.006330826559623264</v>
       </c>
       <c r="I76">
-        <v>0.2764164673171099</v>
+        <v>-0.1251760955875905</v>
       </c>
       <c r="J76">
         <v>0.9464010620843414</v>
       </c>
       <c r="K76">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="L76">
-        <v>3.31</v>
+        <v>4.01</v>
       </c>
       <c r="M76">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="N76">
-        <v>3.17</v>
+        <v>4.05</v>
       </c>
       <c r="O76">
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B77" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C77">
-        <v>1.643997344789146</v>
+        <v>1.645957504101798</v>
       </c>
       <c r="D77" t="s">
         <v>36</v>
@@ -4686,22 +4692,22 @@
         <v>-1</v>
       </c>
       <c r="G77">
-        <v>0.006376002655210854</v>
+        <v>0.006094042495898203</v>
       </c>
       <c r="H77">
         <v>0.006330826559623264</v>
       </c>
       <c r="I77">
-        <v>-0.1251760955875905</v>
+        <v>-0.123215936274939</v>
       </c>
       <c r="J77">
         <v>0.9464010620843414</v>
       </c>
       <c r="K77">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L77">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M77">
         <v>2.41</v>
@@ -4713,1412 +4719,1412 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C78">
-        <v>1.645957504101798</v>
+        <v>1.613410205419267</v>
       </c>
       <c r="D78" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="E78">
-        <v>1.769173440376737</v>
+        <v>1.293162190479684</v>
       </c>
       <c r="F78">
         <v>-1</v>
       </c>
       <c r="G78">
-        <v>0.006094042495898203</v>
+        <v>0.004906589794580732</v>
       </c>
       <c r="H78">
-        <v>0.006330826559623264</v>
+        <v>0.004346837809520315</v>
       </c>
       <c r="I78">
-        <v>-0.123215936274939</v>
+        <v>0.320248014939583</v>
       </c>
       <c r="J78">
-        <v>0.9464010620843414</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K78">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="L78">
-        <v>3.87</v>
+        <v>3.26</v>
       </c>
       <c r="M78">
-        <v>2.41</v>
+        <v>1.53</v>
       </c>
       <c r="N78">
-        <v>4.05</v>
+        <v>2.82</v>
       </c>
       <c r="O78">
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:16">
       <c r="A79" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B79" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C79">
-        <v>1.634885525343484</v>
+        <v>1.02473295176371</v>
       </c>
       <c r="D79" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="E79">
-        <v>1.769173440376737</v>
+        <v>1.323823563651905</v>
       </c>
       <c r="F79">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G79">
-        <v>0.006045114474656515</v>
+        <v>0.005595267048236289</v>
       </c>
       <c r="H79">
-        <v>0.006330826559623264</v>
+        <v>0.005016176436348095</v>
       </c>
       <c r="I79">
-        <v>-0.1342879150332523</v>
+        <v>0.2990906118881951</v>
       </c>
       <c r="J79">
-        <v>0.9464010620843414</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K79">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="L79">
-        <v>3.84</v>
+        <v>3.31</v>
       </c>
       <c r="M79">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="N79">
-        <v>4.05</v>
+        <v>3.17</v>
       </c>
       <c r="O79">
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B80" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C80">
-        <v>1.613410205419267</v>
+        <v>1.644980966703293</v>
       </c>
       <c r="D80" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E80">
-        <v>1.293162190479684</v>
+        <v>1.454815623410238</v>
       </c>
       <c r="F80">
         <v>-1</v>
       </c>
       <c r="G80">
-        <v>0.004906589794580732</v>
+        <v>0.006455019033296707</v>
       </c>
       <c r="H80">
-        <v>0.004346837809520315</v>
+        <v>0.006105184376589762</v>
       </c>
       <c r="I80">
-        <v>0.320248014939583</v>
+        <v>0.1901653432930552</v>
       </c>
       <c r="J80">
         <v>0.9979332088368078</v>
       </c>
       <c r="K80">
-        <v>1.65</v>
+        <v>2.41</v>
       </c>
       <c r="L80">
-        <v>3.26</v>
+        <v>4.05</v>
       </c>
       <c r="M80">
-        <v>1.53</v>
+        <v>2.33</v>
       </c>
       <c r="N80">
-        <v>2.82</v>
+        <v>3.78</v>
       </c>
       <c r="O80">
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="81" spans="1:16">
       <c r="A81" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C81">
-        <v>1.02473295176371</v>
+        <v>1.563582758846789</v>
       </c>
       <c r="D81" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E81">
-        <v>1.323823563651905</v>
+        <v>1.246958558203386</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G81">
-        <v>0.005595267048236289</v>
+        <v>0.004956417241153211</v>
       </c>
       <c r="H81">
-        <v>0.005016176436348095</v>
+        <v>0.004393041441796613</v>
       </c>
       <c r="I81">
-        <v>0.2990906118881951</v>
+        <v>0.3166242006434028</v>
       </c>
       <c r="J81">
-        <v>0.9979332088368078</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K81">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="L81">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="M81">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="N81">
-        <v>3.17</v>
+        <v>2.82</v>
       </c>
       <c r="O81">
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="82" spans="1:16">
       <c r="A82" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C82">
-        <v>1.563582758846789</v>
+        <v>0.9555784956116042</v>
       </c>
       <c r="D82" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E82">
-        <v>1.246958558203386</v>
+        <v>1.267956426585794</v>
       </c>
       <c r="F82">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G82">
-        <v>0.004956417241153211</v>
+        <v>0.005664421504388396</v>
       </c>
       <c r="H82">
-        <v>0.004393041441796613</v>
+        <v>0.005072043573414206</v>
       </c>
       <c r="I82">
-        <v>0.3166242006434028</v>
+        <v>0.3123779309741896</v>
       </c>
       <c r="J82">
         <v>1.028131661304976</v>
       </c>
       <c r="K82">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="L82">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="M82">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="N82">
-        <v>2.82</v>
+        <v>3.17</v>
       </c>
       <c r="O82">
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B83" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C83">
-        <v>0.9555784956116042</v>
+        <v>1.572202696255007</v>
       </c>
       <c r="D83" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E83">
-        <v>1.267956426585794</v>
+        <v>1.384453229159405</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G83">
-        <v>0.005664421504388396</v>
+        <v>0.006527797303744994</v>
       </c>
       <c r="H83">
-        <v>0.005072043573414206</v>
+        <v>0.006175546770840595</v>
       </c>
       <c r="I83">
-        <v>0.3123779309741896</v>
+        <v>0.1877494670956019</v>
       </c>
       <c r="J83">
         <v>1.028131661304976</v>
       </c>
       <c r="K83">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="L83">
-        <v>3.31</v>
+        <v>4.05</v>
       </c>
       <c r="M83">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="N83">
-        <v>3.17</v>
+        <v>3.78</v>
       </c>
       <c r="O83">
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C84">
-        <v>1.572202696255007</v>
+        <v>1.51276870292658</v>
       </c>
       <c r="D84" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E84">
-        <v>1.423327962707206</v>
+        <v>1.15219719233976</v>
       </c>
       <c r="F84">
         <v>-1</v>
       </c>
       <c r="G84">
-        <v>0.006527797303744994</v>
+        <v>0.00500723129707342</v>
       </c>
       <c r="H84">
-        <v>0.006296672037292794</v>
+        <v>0.004307802807660239</v>
       </c>
       <c r="I84">
-        <v>0.1488747335478009</v>
+        <v>0.3605715105868199</v>
       </c>
       <c r="J84">
-        <v>1.028131661304976</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K84">
-        <v>2.41</v>
+        <v>1.65</v>
       </c>
       <c r="L84">
-        <v>4.05</v>
+        <v>3.26</v>
       </c>
       <c r="M84">
-        <v>2.37</v>
+        <v>1.49</v>
       </c>
       <c r="N84">
-        <v>3.86</v>
+        <v>2.73</v>
       </c>
       <c r="O84">
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="85" spans="1:16">
       <c r="A85" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B85" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C85">
-        <v>1.51276870292658</v>
+        <v>0.95505474527386</v>
       </c>
       <c r="D85" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E85">
-        <v>1.15219719233976</v>
+        <v>1.210983091160105</v>
       </c>
       <c r="F85">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G85">
-        <v>0.00500723129707342</v>
+        <v>0.00580494525472614</v>
       </c>
       <c r="H85">
-        <v>0.004307802807660239</v>
+        <v>0.005129016908839895</v>
       </c>
       <c r="I85">
-        <v>0.3605715105868199</v>
+        <v>0.2559283458862451</v>
       </c>
       <c r="J85">
         <v>1.058928058832376</v>
       </c>
       <c r="K85">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="L85">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="M85">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="N85">
-        <v>2.73</v>
+        <v>3.17</v>
       </c>
       <c r="O85">
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B86" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C86">
-        <v>0.95505474527386</v>
+        <v>1.497983378213975</v>
       </c>
       <c r="D86" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E86">
-        <v>1.210983091160105</v>
+        <v>1.312697622920565</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G86">
-        <v>0.00580494525472614</v>
+        <v>0.006602016621786024</v>
       </c>
       <c r="H86">
-        <v>0.005129016908839895</v>
+        <v>0.006247302377079435</v>
       </c>
       <c r="I86">
-        <v>0.2559283458862451</v>
+        <v>0.18528575529341</v>
       </c>
       <c r="J86">
         <v>1.058928058832376</v>
       </c>
       <c r="K86">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="L86">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="M86">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="N86">
-        <v>3.17</v>
+        <v>3.78</v>
       </c>
       <c r="O86">
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C87">
-        <v>1.497983378213975</v>
+        <v>1.47291752351783</v>
       </c>
       <c r="D87" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E87">
-        <v>1.35034050056727</v>
+        <v>1.48291752351783</v>
       </c>
       <c r="F87">
         <v>-1</v>
       </c>
       <c r="G87">
-        <v>0.006602016621786024</v>
+        <v>0.00504708247648217</v>
       </c>
       <c r="H87">
-        <v>0.00636965949943273</v>
+        <v>0.005057082476482171</v>
       </c>
       <c r="I87">
-        <v>0.1476428776467049</v>
+        <v>-0.01000000000000023</v>
       </c>
       <c r="J87">
-        <v>1.058928058832376</v>
+        <v>1.083080288777073</v>
       </c>
       <c r="K87">
-        <v>2.41</v>
+        <v>1.65</v>
       </c>
       <c r="L87">
-        <v>4.05</v>
+        <v>3.26</v>
       </c>
       <c r="M87">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="N87">
-        <v>3.86</v>
+        <v>3.27</v>
       </c>
       <c r="O87">
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C88">
-        <v>1.47291752351783</v>
+        <v>0.8997461387005035</v>
       </c>
       <c r="D88" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="E88">
-        <v>1.48291752351783</v>
+        <v>1.166301465762415</v>
       </c>
       <c r="F88">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G88">
-        <v>0.00504708247648217</v>
+        <v>0.005860253861299496</v>
       </c>
       <c r="H88">
-        <v>0.005057082476482171</v>
+        <v>0.005173698534237585</v>
       </c>
       <c r="I88">
-        <v>-0.01000000000000023</v>
+        <v>0.2665553270619117</v>
       </c>
       <c r="J88">
         <v>1.083080288777073</v>
       </c>
       <c r="K88">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="L88">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="M88">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="N88">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="O88">
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89" spans="1:16">
       <c r="A89" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B89" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C89">
-        <v>0.8997461387005035</v>
+        <v>1.439776504047254</v>
       </c>
       <c r="D89" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E89">
-        <v>1.166301465762415</v>
+        <v>1.25642292714942</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G89">
-        <v>0.005860253861299496</v>
+        <v>0.006660223495952746</v>
       </c>
       <c r="H89">
-        <v>0.005173698534237585</v>
+        <v>0.00630357707285058</v>
       </c>
       <c r="I89">
-        <v>0.2665553270619117</v>
+        <v>0.1833535768978343</v>
       </c>
       <c r="J89">
         <v>1.083080288777073</v>
       </c>
       <c r="K89">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="L89">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="M89">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="N89">
-        <v>3.17</v>
+        <v>3.78</v>
       </c>
       <c r="O89">
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C90">
-        <v>1.439776504047254</v>
+        <v>1.473409677892745</v>
       </c>
       <c r="D90" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E90">
-        <v>1.293099715598337</v>
+        <v>1.483409677892745</v>
       </c>
       <c r="F90">
         <v>-1</v>
       </c>
       <c r="G90">
-        <v>0.006660223495952746</v>
+        <v>0.005046590322107255</v>
       </c>
       <c r="H90">
-        <v>0.006426900284401663</v>
+        <v>0.005056590322107255</v>
       </c>
       <c r="I90">
-        <v>0.1466767884489171</v>
+        <v>-0.01000000000000023</v>
       </c>
       <c r="J90">
-        <v>1.083080288777073</v>
+        <v>1.082782013398337</v>
       </c>
       <c r="K90">
-        <v>2.41</v>
+        <v>1.65</v>
       </c>
       <c r="L90">
-        <v>4.05</v>
+        <v>3.26</v>
       </c>
       <c r="M90">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="N90">
-        <v>3.86</v>
+        <v>3.27</v>
       </c>
       <c r="O90">
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B91" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C91">
-        <v>1.473409677892745</v>
+        <v>0.9004291893178089</v>
       </c>
       <c r="D91" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="E91">
-        <v>1.483409677892745</v>
+        <v>1.166853275213077</v>
       </c>
       <c r="F91">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G91">
-        <v>0.005046590322107255</v>
+        <v>0.005859570810682191</v>
       </c>
       <c r="H91">
-        <v>0.005056590322107255</v>
+        <v>0.005173146724786923</v>
       </c>
       <c r="I91">
-        <v>-0.01000000000000023</v>
+        <v>0.2664240858952684</v>
       </c>
       <c r="J91">
         <v>1.082782013398337</v>
       </c>
       <c r="K91">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="L91">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="M91">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="N91">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="O91">
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B92" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C92">
-        <v>0.9004291893178089</v>
+        <v>1.440495347710009</v>
       </c>
       <c r="D92" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E92">
-        <v>1.166853275213077</v>
+        <v>1.257117908781876</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G92">
-        <v>0.005859570810682191</v>
+        <v>0.006659504652289991</v>
       </c>
       <c r="H92">
-        <v>0.005173146724786923</v>
+        <v>0.006302882091218124</v>
       </c>
       <c r="I92">
-        <v>0.2664240858952684</v>
+        <v>0.1833774389281331</v>
       </c>
       <c r="J92">
         <v>1.082782013398337</v>
       </c>
       <c r="K92">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="L92">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="M92">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="N92">
-        <v>3.17</v>
+        <v>3.78</v>
       </c>
       <c r="O92">
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93" spans="1:16">
       <c r="A93" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C93">
-        <v>1.440495347710009</v>
+        <v>1.472764755561722</v>
       </c>
       <c r="D93" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E93">
-        <v>1.293806628245942</v>
+        <v>1.482764755561722</v>
       </c>
       <c r="F93">
         <v>-1</v>
       </c>
       <c r="G93">
-        <v>0.006659504652289991</v>
+        <v>0.005047235244438278</v>
       </c>
       <c r="H93">
-        <v>0.006426193371754058</v>
+        <v>0.005057235244438278</v>
       </c>
       <c r="I93">
-        <v>0.1466887194640667</v>
+        <v>-0.01000000000000023</v>
       </c>
       <c r="J93">
-        <v>1.082782013398337</v>
+        <v>1.083172875417138</v>
       </c>
       <c r="K93">
-        <v>2.41</v>
+        <v>1.65</v>
       </c>
       <c r="L93">
-        <v>4.05</v>
+        <v>3.26</v>
       </c>
       <c r="M93">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="N93">
-        <v>3.86</v>
+        <v>3.27</v>
       </c>
       <c r="O93">
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94" spans="1:16">
       <c r="A94" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B94" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C94">
-        <v>1.472764755561722</v>
+        <v>0.8995341152947529</v>
       </c>
       <c r="D94" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="E94">
-        <v>1.482764755561722</v>
+        <v>1.166130180478294</v>
       </c>
       <c r="F94">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G94">
-        <v>0.005047235244438278</v>
+        <v>0.005860465884705247</v>
       </c>
       <c r="H94">
-        <v>0.005057235244438278</v>
+        <v>0.005173869819521706</v>
       </c>
       <c r="I94">
-        <v>-0.01000000000000023</v>
+        <v>0.2665960651835411</v>
       </c>
       <c r="J94">
         <v>1.083172875417138</v>
       </c>
       <c r="K94">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="L94">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="M94">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="N94">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="O94">
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95" spans="1:16">
       <c r="A95" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C95">
-        <v>0.8995341152947529</v>
+        <v>1.439553370244696</v>
       </c>
       <c r="D95" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E95">
-        <v>1.166130180478294</v>
+        <v>1.256207200278067</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G95">
-        <v>0.005860465884705247</v>
+        <v>0.006660446629755304</v>
       </c>
       <c r="H95">
-        <v>0.005173869819521706</v>
+        <v>0.006303792799721933</v>
       </c>
       <c r="I95">
-        <v>0.2665960651835411</v>
+        <v>0.183346169966629</v>
       </c>
       <c r="J95">
         <v>1.083172875417138</v>
       </c>
       <c r="K95">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="L95">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="M95">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="N95">
-        <v>3.17</v>
+        <v>3.78</v>
       </c>
       <c r="O95">
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="96" spans="1:16">
       <c r="A96" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C96">
-        <v>1.439553370244696</v>
+        <v>1.468991674710606</v>
       </c>
       <c r="D96" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E96">
-        <v>1.292880285261382</v>
+        <v>1.478991674710606</v>
       </c>
       <c r="F96">
         <v>-1</v>
       </c>
       <c r="G96">
-        <v>0.006660446629755304</v>
+        <v>0.005051008325289394</v>
       </c>
       <c r="H96">
-        <v>0.006427119714738618</v>
+        <v>0.005061008325289394</v>
       </c>
       <c r="I96">
-        <v>0.1466730849833144</v>
+        <v>-0.01000000000000023</v>
       </c>
       <c r="J96">
-        <v>1.083172875417138</v>
+        <v>1.085459591084481</v>
       </c>
       <c r="K96">
-        <v>2.41</v>
+        <v>1.65</v>
       </c>
       <c r="L96">
-        <v>4.05</v>
+        <v>3.26</v>
       </c>
       <c r="M96">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="N96">
-        <v>3.86</v>
+        <v>3.27</v>
       </c>
       <c r="O96">
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="97" spans="1:16">
       <c r="A97" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B97" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C97">
-        <v>1.468991674710606</v>
+        <v>0.8942975364165378</v>
       </c>
       <c r="D97" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="E97">
-        <v>1.478991674710606</v>
+        <v>1.161899756493709</v>
       </c>
       <c r="F97">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G97">
-        <v>0.005051008325289394</v>
+        <v>0.005865702463583462</v>
       </c>
       <c r="H97">
-        <v>0.005061008325289394</v>
+        <v>0.00517810024350629</v>
       </c>
       <c r="I97">
-        <v>-0.01000000000000023</v>
+        <v>0.2676022200771717</v>
       </c>
       <c r="J97">
         <v>1.085459591084481</v>
       </c>
       <c r="K97">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="L97">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="M97">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="N97">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="O97">
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:16">
       <c r="A98" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B98" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C98">
-        <v>0.8942975364165378</v>
+        <v>1.4340423854864</v>
       </c>
       <c r="D98" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E98">
-        <v>1.161899756493709</v>
+        <v>1.250879152773158</v>
       </c>
       <c r="F98">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G98">
-        <v>0.005865702463583462</v>
+        <v>0.0066659576145136</v>
       </c>
       <c r="H98">
-        <v>0.00517810024350629</v>
+        <v>0.006309120847226842</v>
       </c>
       <c r="I98">
-        <v>0.2676022200771717</v>
+        <v>0.1831632327132411</v>
       </c>
       <c r="J98">
         <v>1.085459591084481</v>
       </c>
       <c r="K98">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="L98">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="M98">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="N98">
-        <v>3.17</v>
+        <v>3.78</v>
       </c>
       <c r="O98">
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C99">
-        <v>1.4340423854864</v>
+        <v>0.823882990348408</v>
       </c>
       <c r="D99" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E99">
-        <v>1.287460769129779</v>
+        <v>1.105014642857884</v>
       </c>
       <c r="F99">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G99">
-        <v>0.0066659576145136</v>
+        <v>0.005936117009651592</v>
       </c>
       <c r="H99">
-        <v>0.006432539230870221</v>
+        <v>0.005234985357142116</v>
       </c>
       <c r="I99">
-        <v>0.1465816163566203</v>
+        <v>0.281131652509476</v>
       </c>
       <c r="J99">
-        <v>1.085459591084481</v>
+        <v>1.1162083011579</v>
       </c>
       <c r="K99">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="L99">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="M99">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="N99">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="O99">
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:16">
       <c r="A100" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B100" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C100">
-        <v>0.823882990348408</v>
+        <v>1.35993799420946</v>
       </c>
       <c r="D100" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E100">
-        <v>1.105014642857884</v>
+        <v>1.179234658302092</v>
       </c>
       <c r="F100">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G100">
-        <v>0.005936117009651592</v>
+        <v>0.00674006200579054</v>
       </c>
       <c r="H100">
-        <v>0.005234985357142116</v>
+        <v>0.006380765341697908</v>
       </c>
       <c r="I100">
-        <v>0.281131652509476</v>
+        <v>0.180703335907368</v>
       </c>
       <c r="J100">
         <v>1.1162083011579</v>
       </c>
       <c r="K100">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="L100">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="M100">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="N100">
-        <v>3.17</v>
+        <v>3.78</v>
       </c>
       <c r="O100">
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C101">
-        <v>1.35993799420946</v>
+        <v>0.7552208383877499</v>
       </c>
       <c r="D101" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E101">
-        <v>1.214586326255775</v>
+        <v>1.049545218784863</v>
       </c>
       <c r="F101">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G101">
-        <v>0.00674006200579054</v>
+        <v>0.00600477916161225</v>
       </c>
       <c r="H101">
-        <v>0.006505413673744224</v>
+        <v>0.005290454781215137</v>
       </c>
       <c r="I101">
-        <v>0.1453516679536841</v>
+        <v>0.2943243803971134</v>
       </c>
       <c r="J101">
-        <v>1.1162083011579</v>
+        <v>1.146191773629804</v>
       </c>
       <c r="K101">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="L101">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="M101">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="N101">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="O101">
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:16">
       <c r="A102" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B102" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C102">
-        <v>0.7552208383877499</v>
+        <v>1.287677825552173</v>
       </c>
       <c r="D102" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E102">
-        <v>1.049545218784863</v>
+        <v>1.109373167442558</v>
       </c>
       <c r="F102">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G102">
-        <v>0.00600477916161225</v>
+        <v>0.006812322174447827</v>
       </c>
       <c r="H102">
-        <v>0.005290454781215137</v>
+        <v>0.006450626832557441</v>
       </c>
       <c r="I102">
-        <v>0.2943243803971134</v>
+        <v>0.1783046581096155</v>
       </c>
       <c r="J102">
         <v>1.146191773629804</v>
       </c>
       <c r="K102">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="L102">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="M102">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="N102">
-        <v>3.17</v>
+        <v>3.78</v>
       </c>
       <c r="O102">
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:16">
       <c r="A103" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C103">
-        <v>1.287677825552173</v>
+        <v>0.7164672131147527</v>
       </c>
       <c r="D103" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E103">
-        <v>1.143525496497365</v>
+        <v>1.018237704918032</v>
       </c>
       <c r="F103">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G103">
-        <v>0.006812322174447827</v>
+        <v>0.006043532786885248</v>
       </c>
       <c r="H103">
-        <v>0.006576474503502634</v>
+        <v>0.005321762295081968</v>
       </c>
       <c r="I103">
-        <v>0.1441523290548079</v>
+        <v>0.3017704918032789</v>
       </c>
       <c r="J103">
-        <v>1.146191773629804</v>
+        <v>1.163114754098361</v>
       </c>
       <c r="K103">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="L103">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="M103">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="N103">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="O103">
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104" spans="1:16">
       <c r="A104" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B104" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C104">
-        <v>0.7164672131147527</v>
+        <v>1.246893442622949</v>
       </c>
       <c r="D104" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E104">
-        <v>1.018237704918032</v>
+        <v>1.069942622950818</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G104">
-        <v>0.006043532786885248</v>
+        <v>0.006853106557377051</v>
       </c>
       <c r="H104">
-        <v>0.005321762295081968</v>
+        <v>0.006490057377049181</v>
       </c>
       <c r="I104">
-        <v>0.3017704918032789</v>
+        <v>0.1769508196721312</v>
       </c>
       <c r="J104">
         <v>1.163114754098361</v>
       </c>
       <c r="K104">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="L104">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="M104">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="N104">
-        <v>3.17</v>
+        <v>3.78</v>
       </c>
       <c r="O104">
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:16">
       <c r="A105" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C105">
-        <v>1.246893442622949</v>
+        <v>0.7002131196894186</v>
       </c>
       <c r="D105" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="E105">
-        <v>1.103418032786883</v>
+        <v>0.5798239504652853</v>
       </c>
       <c r="F105">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G105">
-        <v>0.006853106557377051</v>
+        <v>0.006279786880310581</v>
       </c>
       <c r="H105">
-        <v>0.006616581967213117</v>
+        <v>0.006040176049534715</v>
       </c>
       <c r="I105">
-        <v>0.1434754098360655</v>
+        <v>-0.1203891692241332</v>
       </c>
       <c r="J105">
-        <v>1.163114754098361</v>
+        <v>1.192216615517343</v>
       </c>
       <c r="K105">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="L105">
-        <v>4.05</v>
+        <v>3.49</v>
       </c>
       <c r="M105">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="N105">
-        <v>3.86</v>
+        <v>3.31</v>
       </c>
       <c r="O105">
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
     </row>
     <row r="106" spans="1:16">
       <c r="A106" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B106" t="s">
         <v>37</v>
@@ -6163,12 +6169,12 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="107" spans="1:16">
       <c r="A107" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B107" t="s">
         <v>36</v>
@@ -6177,10 +6183,10 @@
         <v>1.176757956603204</v>
       </c>
       <c r="D107" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E107">
-        <v>1.034446621223898</v>
+        <v>1.002135285844592</v>
       </c>
       <c r="F107">
         <v>-1</v>
@@ -6189,10 +6195,10 @@
         <v>0.006923242043396796</v>
       </c>
       <c r="H107">
-        <v>0.006685553378776103</v>
+        <v>0.006557864714155408</v>
       </c>
       <c r="I107">
-        <v>0.1423113353793064</v>
+        <v>0.1746226707586125</v>
       </c>
       <c r="J107">
         <v>1.192216615517343</v>
@@ -6204,16 +6210,16 @@
         <v>4.05</v>
       </c>
       <c r="M107">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N107">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O107">
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6263,7 +6269,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6313,57 +6319,57 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="110" spans="1:16">
       <c r="A110" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B110" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C110">
-        <v>0.3774746016246668</v>
+        <v>0.551698597969601</v>
       </c>
       <c r="D110" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="E110">
-        <v>0.2639815545814042</v>
+        <v>0.7904611387463603</v>
       </c>
       <c r="F110">
         <v>1</v>
       </c>
       <c r="G110">
-        <v>0.006602525398375333</v>
+        <v>0.006008301402030399</v>
       </c>
       <c r="H110">
-        <v>0.006356018445418596</v>
+        <v>0.005409538861253641</v>
       </c>
       <c r="I110">
-        <v>-0.1134930470432627</v>
+        <v>0.2387625407767593</v>
       </c>
       <c r="J110">
-        <v>1.330139059134758</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K110">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="L110">
-        <v>3.49</v>
+        <v>3.28</v>
       </c>
       <c r="M110">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="N110">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="O110">
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6374,28 +6380,28 @@
         <v>38</v>
       </c>
       <c r="C111">
-        <v>0.2442505289553791</v>
+        <v>0.3774746016246668</v>
       </c>
       <c r="D111" t="s">
         <v>35</v>
       </c>
       <c r="E111">
-        <v>0.1336041501315459</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
       <c r="G111">
-        <v>0.006735749471044622</v>
+        <v>0.006602525398375333</v>
       </c>
       <c r="H111">
-        <v>0.006486395849868455</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I111">
-        <v>-0.1106463788238332</v>
+        <v>-0.1134930470432627</v>
       </c>
       <c r="J111">
-        <v>1.387072423523342</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K111">
         <v>2.34</v>
@@ -6413,7 +6419,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6421,1354 +6427,1354 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C112">
-        <v>2.01907486979781</v>
+        <v>0.2442505289553791</v>
       </c>
       <c r="D112" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E112">
-        <v>1.972602976568324</v>
+        <v>0.2036041501315458</v>
       </c>
       <c r="F112">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G112">
-        <v>0.00600092513020219</v>
+        <v>0.006735749471044622</v>
       </c>
       <c r="H112">
-        <v>0.005747397023431676</v>
+        <v>0.006556395849868454</v>
       </c>
       <c r="I112">
-        <v>0.04647189322948608</v>
+        <v>-0.04064637882383337</v>
       </c>
       <c r="J112">
-        <v>0.7963700520808761</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K112">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="L112">
-        <v>4.01</v>
+        <v>3.49</v>
       </c>
       <c r="M112">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="N112">
-        <v>3.86</v>
+        <v>3.38</v>
       </c>
       <c r="O112">
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="113" spans="1:16">
       <c r="A113" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C113">
-        <v>2.130748174485088</v>
+        <v>2.01907486979781</v>
       </c>
       <c r="D113" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E113">
-        <v>1.972602976568324</v>
+        <v>1.924457778651558</v>
       </c>
       <c r="F113">
         <v>-1</v>
       </c>
       <c r="G113">
-        <v>0.005969251825514912</v>
+        <v>0.00600092513020219</v>
       </c>
       <c r="H113">
-        <v>0.005747397023431676</v>
+        <v>0.005635542221348441</v>
       </c>
       <c r="I113">
-        <v>0.1581451979167647</v>
+        <v>0.09461709114625116</v>
       </c>
       <c r="J113">
         <v>0.7963700520808761</v>
       </c>
       <c r="K113">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="L113">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M113">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N113">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O113">
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="114" spans="1:16">
       <c r="A114" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B114" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C114">
-        <v>2.009451144824672</v>
+        <v>2.130748174485088</v>
       </c>
       <c r="D114" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E114">
-        <v>1.963479685293789</v>
+        <v>1.924457778651558</v>
       </c>
       <c r="F114">
         <v>-1</v>
       </c>
       <c r="G114">
-        <v>0.006010548855175328</v>
+        <v>0.005969251825514912</v>
       </c>
       <c r="H114">
-        <v>0.005756520314706211</v>
+        <v>0.005635542221348441</v>
       </c>
       <c r="I114">
-        <v>0.04597145953088311</v>
+        <v>0.2062903958335298</v>
       </c>
       <c r="J114">
-        <v>0.8002195420701311</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K114">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L114">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M114">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N114">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O114">
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="115" spans="1:16">
       <c r="A115" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C115">
-        <v>2.121470903610984</v>
+        <v>2.009451144824672</v>
       </c>
       <c r="D115" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E115">
-        <v>1.963479685293789</v>
+        <v>1.915488466976594</v>
       </c>
       <c r="F115">
         <v>-1</v>
       </c>
       <c r="G115">
-        <v>0.005978529096389016</v>
+        <v>0.006010548855175328</v>
       </c>
       <c r="H115">
-        <v>0.005756520314706211</v>
+        <v>0.005644511533023405</v>
       </c>
       <c r="I115">
-        <v>0.1579912183171948</v>
+        <v>0.09396267784807799</v>
       </c>
       <c r="J115">
         <v>0.8002195420701311</v>
       </c>
       <c r="K115">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="L115">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M115">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N115">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O115">
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="116" spans="1:16">
       <c r="A116" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B116" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C116">
-        <v>1.996409318396163</v>
+        <v>2.121470903610984</v>
       </c>
       <c r="D116" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E116">
-        <v>1.951116033839562</v>
+        <v>1.915488466976594</v>
       </c>
       <c r="F116">
         <v>-1</v>
       </c>
       <c r="G116">
-        <v>0.006023590681603837</v>
+        <v>0.005978529096389016</v>
       </c>
       <c r="H116">
-        <v>0.005768883966160438</v>
+        <v>0.005644511533023405</v>
       </c>
       <c r="I116">
-        <v>0.04529328455660031</v>
+        <v>0.2059824366343896</v>
       </c>
       <c r="J116">
-        <v>0.8054362726415348</v>
+        <v>0.8002195420701311</v>
       </c>
       <c r="K116">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L116">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M116">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N116">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O116">
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="117" spans="1:16">
       <c r="A117" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C117">
-        <v>2.108898582933901</v>
+        <v>1.996409318396163</v>
       </c>
       <c r="D117" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E117">
-        <v>1.951116033839562</v>
+        <v>1.903333484745224</v>
       </c>
       <c r="F117">
         <v>-1</v>
       </c>
       <c r="G117">
-        <v>0.005991101417066099</v>
+        <v>0.006023590681603837</v>
       </c>
       <c r="H117">
-        <v>0.005768883966160438</v>
+        <v>0.005656666515254777</v>
       </c>
       <c r="I117">
-        <v>0.1577825490943388</v>
+        <v>0.09307583365093897</v>
       </c>
       <c r="J117">
         <v>0.8054362726415348</v>
       </c>
       <c r="K117">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="L117">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M117">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N117">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O117">
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="118" spans="1:16">
       <c r="A118" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B118" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C118">
-        <v>1.981381467084703</v>
+        <v>2.108898582933901</v>
       </c>
       <c r="D118" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E118">
-        <v>1.936869630796299</v>
+        <v>1.903333484745224</v>
       </c>
       <c r="F118">
         <v>-1</v>
       </c>
       <c r="G118">
-        <v>0.006038618532915297</v>
+        <v>0.005991101417066099</v>
       </c>
       <c r="H118">
-        <v>0.005783130369203702</v>
+        <v>0.005656666515254777</v>
       </c>
       <c r="I118">
-        <v>0.04451183628840449</v>
+        <v>0.2055650981886774</v>
       </c>
       <c r="J118">
-        <v>0.8114474131661186</v>
+        <v>0.8054362726415348</v>
       </c>
       <c r="K118">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L118">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M118">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N118">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O118">
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="119" spans="1:16">
       <c r="A119" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C119">
-        <v>2.094411734269654</v>
+        <v>1.981381467084703</v>
       </c>
       <c r="D119" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E119">
-        <v>1.936869630796299</v>
+        <v>1.889327527322944</v>
       </c>
       <c r="F119">
         <v>-1</v>
       </c>
       <c r="G119">
-        <v>0.006005588265730346</v>
+        <v>0.006038618532915297</v>
       </c>
       <c r="H119">
-        <v>0.005783130369203702</v>
+        <v>0.005670672472677056</v>
       </c>
       <c r="I119">
-        <v>0.1575421034733553</v>
+        <v>0.09205393976175968</v>
       </c>
       <c r="J119">
         <v>0.8114474131661186</v>
       </c>
       <c r="K119">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="L119">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M119">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N119">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O119">
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="120" spans="1:16">
       <c r="A120" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B120" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C120">
-        <v>1.977186894395391</v>
+        <v>2.094411734269654</v>
       </c>
       <c r="D120" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E120">
-        <v>1.932893175886831</v>
+        <v>1.889327527322944</v>
       </c>
       <c r="F120">
         <v>-1</v>
       </c>
       <c r="G120">
-        <v>0.006042813105604609</v>
+        <v>0.006005588265730346</v>
       </c>
       <c r="H120">
-        <v>0.005787106824113169</v>
+        <v>0.005670672472677056</v>
       </c>
       <c r="I120">
-        <v>0.04429371850856012</v>
+        <v>0.2050842069467105</v>
       </c>
       <c r="J120">
-        <v>0.8131252422418436</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K120">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L120">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M120">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N120">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O120">
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="121" spans="1:16">
       <c r="A121" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C121">
-        <v>2.090368166197157</v>
+        <v>1.977186894395391</v>
       </c>
       <c r="D121" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E121">
-        <v>1.932893175886831</v>
+        <v>1.885418185576504</v>
       </c>
       <c r="F121">
         <v>-1</v>
       </c>
       <c r="G121">
-        <v>0.006009631833802842</v>
+        <v>0.006042813105604609</v>
       </c>
       <c r="H121">
-        <v>0.005787106824113169</v>
+        <v>0.005674581814423495</v>
       </c>
       <c r="I121">
-        <v>0.1574749903103261</v>
+        <v>0.09176870881888655</v>
       </c>
       <c r="J121">
         <v>0.8131252422418436</v>
       </c>
       <c r="K121">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="L121">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M121">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N121">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O121">
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="122" spans="1:16">
       <c r="A122" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B122" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C122">
-        <v>1.972128109819418</v>
+        <v>2.090368166197157</v>
       </c>
       <c r="D122" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E122">
-        <v>1.928097448108809</v>
+        <v>1.885418185576504</v>
       </c>
       <c r="F122">
         <v>-1</v>
       </c>
       <c r="G122">
-        <v>0.006047871890180582</v>
+        <v>0.006009631833802842</v>
       </c>
       <c r="H122">
-        <v>0.005791902551891191</v>
+        <v>0.005674581814423495</v>
       </c>
       <c r="I122">
-        <v>0.04403066171060943</v>
+        <v>0.2049499806206525</v>
       </c>
       <c r="J122">
-        <v>0.8151487560722326</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K122">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L122">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M122">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N122">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O122">
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="123" spans="1:16">
       <c r="A123" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C123">
-        <v>2.085491497865919</v>
+        <v>1.972128109819418</v>
       </c>
       <c r="D123" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E123">
-        <v>1.928097448108809</v>
+        <v>1.880703398351698</v>
       </c>
       <c r="F123">
         <v>-1</v>
       </c>
       <c r="G123">
-        <v>0.00601450850213408</v>
+        <v>0.006047871890180582</v>
       </c>
       <c r="H123">
-        <v>0.005791902551891191</v>
+        <v>0.005679296601648302</v>
       </c>
       <c r="I123">
-        <v>0.1573940497571107</v>
+        <v>0.09142471146772024</v>
       </c>
       <c r="J123">
         <v>0.8151487560722326</v>
       </c>
       <c r="K123">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="L123">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M123">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N123">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O123">
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="124" spans="1:16">
       <c r="A124" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B124" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C124">
-        <v>1.962255996565552</v>
+        <v>2.085491497865919</v>
       </c>
       <c r="D124" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E124">
-        <v>1.918738684744143</v>
+        <v>1.880703398351698</v>
       </c>
       <c r="F124">
         <v>-1</v>
       </c>
       <c r="G124">
-        <v>0.006057744003434448</v>
+        <v>0.00601450850213408</v>
       </c>
       <c r="H124">
-        <v>0.005801261315255857</v>
+        <v>0.005679296601648302</v>
       </c>
       <c r="I124">
-        <v>0.04351731182140894</v>
+        <v>0.2047880995142215</v>
       </c>
       <c r="J124">
-        <v>0.8190976013737793</v>
+        <v>0.8151487560722326</v>
       </c>
       <c r="K124">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L124">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M124">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N124">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O124">
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="125" spans="1:16">
       <c r="A125" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C125">
-        <v>2.075974780689192</v>
+        <v>1.962255996565552</v>
       </c>
       <c r="D125" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E125">
-        <v>1.918738684744143</v>
+        <v>1.871502588799094</v>
       </c>
       <c r="F125">
         <v>-1</v>
       </c>
       <c r="G125">
-        <v>0.006024025219310808</v>
+        <v>0.006057744003434448</v>
       </c>
       <c r="H125">
-        <v>0.005801261315255857</v>
+        <v>0.005688497411200906</v>
       </c>
       <c r="I125">
-        <v>0.1572360959450487</v>
+        <v>0.09075340776645779</v>
       </c>
       <c r="J125">
         <v>0.8190976013737793</v>
       </c>
       <c r="K125">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="L125">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M125">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N125">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O125">
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="126" spans="1:16">
       <c r="A126" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B126" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C126">
-        <v>1.966334427874344</v>
+        <v>2.075974780689192</v>
       </c>
       <c r="D126" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E126">
-        <v>1.922605037624878</v>
+        <v>1.871502588799094</v>
       </c>
       <c r="F126">
         <v>-1</v>
       </c>
       <c r="G126">
-        <v>0.006053665572125656</v>
+        <v>0.006024025219310808</v>
       </c>
       <c r="H126">
-        <v>0.005797394962375121</v>
+        <v>0.005688497411200906</v>
       </c>
       <c r="I126">
-        <v>0.04372939024946576</v>
+        <v>0.2044721918900976</v>
       </c>
       <c r="J126">
-        <v>0.8174662288502623</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K126">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L126">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M126">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N126">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O126">
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="127" spans="1:16">
       <c r="A127" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C127">
-        <v>2.079906388470867</v>
+        <v>1.966334427874344</v>
       </c>
       <c r="D127" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E127">
-        <v>1.922605037624878</v>
+        <v>1.875303686778889</v>
       </c>
       <c r="F127">
         <v>-1</v>
       </c>
       <c r="G127">
-        <v>0.006020093611529133</v>
+        <v>0.006053665572125656</v>
       </c>
       <c r="H127">
-        <v>0.005797394962375121</v>
+        <v>0.005684696313221111</v>
       </c>
       <c r="I127">
-        <v>0.1573013508459893</v>
+        <v>0.09103074109545517</v>
       </c>
       <c r="J127">
         <v>0.8174662288502623</v>
       </c>
       <c r="K127">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="L127">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M127">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N127">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O127">
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="128" spans="1:16">
       <c r="A128" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B128" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C128">
-        <v>1.967381519350304</v>
+        <v>2.079906388470867</v>
       </c>
       <c r="D128" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E128">
-        <v>1.923597680344088</v>
+        <v>1.875303686778889</v>
       </c>
       <c r="F128">
         <v>-1</v>
       </c>
       <c r="G128">
-        <v>0.006052618480649696</v>
+        <v>0.006020093611529133</v>
       </c>
       <c r="H128">
-        <v>0.005796402319655912</v>
+        <v>0.005684696313221111</v>
       </c>
       <c r="I128">
-        <v>0.04378383900621574</v>
+        <v>0.2046027016919787</v>
       </c>
       <c r="J128">
-        <v>0.8170473922598784</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K128">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L128">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M128">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N128">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O128">
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="129" spans="1:16">
       <c r="A129" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C129">
-        <v>2.080915784653693</v>
+        <v>1.967381519350304</v>
       </c>
       <c r="D129" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E129">
-        <v>1.923597680344088</v>
+        <v>1.876279576034483</v>
       </c>
       <c r="F129">
         <v>-1</v>
       </c>
       <c r="G129">
-        <v>0.006019084215346308</v>
+        <v>0.006052618480649696</v>
       </c>
       <c r="H129">
-        <v>0.005796402319655912</v>
+        <v>0.005683720423965516</v>
       </c>
       <c r="I129">
-        <v>0.1573181043096048</v>
+        <v>0.09110194331582067</v>
       </c>
       <c r="J129">
         <v>0.8170473922598784</v>
       </c>
       <c r="K129">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="L129">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M129">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N129">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O129">
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="130" spans="1:16">
       <c r="A130" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B130" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C130">
-        <v>1.965836780713639</v>
+        <v>2.080915784653693</v>
       </c>
       <c r="D130" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E130">
-        <v>1.92213326811653</v>
+        <v>1.876279576034483</v>
       </c>
       <c r="F130">
         <v>-1</v>
       </c>
       <c r="G130">
-        <v>0.00605416321928636</v>
+        <v>0.006019084215346308</v>
       </c>
       <c r="H130">
-        <v>0.005797866731883469</v>
+        <v>0.005683720423965516</v>
       </c>
       <c r="I130">
-        <v>0.04370351259710925</v>
+        <v>0.2046362086192097</v>
       </c>
       <c r="J130">
-        <v>0.8176652877145442</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K130">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L130">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M130">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N130">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O130">
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="131" spans="1:16">
       <c r="A131" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C131">
-        <v>2.079426656607948</v>
+        <v>1.965836780713639</v>
       </c>
       <c r="D131" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E131">
-        <v>1.92213326811653</v>
+        <v>1.874839879625112</v>
       </c>
       <c r="F131">
         <v>-1</v>
       </c>
       <c r="G131">
-        <v>0.006020573343392051</v>
+        <v>0.00605416321928636</v>
       </c>
       <c r="H131">
-        <v>0.005797866731883469</v>
+        <v>0.005685160120374888</v>
       </c>
       <c r="I131">
-        <v>0.1572933884914181</v>
+        <v>0.09099690108852765</v>
       </c>
       <c r="J131">
         <v>0.8176652877145442</v>
       </c>
       <c r="K131">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="L131">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M131">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N131">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O131">
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="132" spans="1:16">
       <c r="A132" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B132" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C132">
-        <v>1.964801996006813</v>
+        <v>2.079426656607948</v>
       </c>
       <c r="D132" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E132">
-        <v>1.921152292214459</v>
+        <v>1.874839879625112</v>
       </c>
       <c r="F132">
         <v>-1</v>
       </c>
       <c r="G132">
-        <v>0.006055198003993187</v>
+        <v>0.006020573343392051</v>
       </c>
       <c r="H132">
-        <v>0.00579884770778554</v>
+        <v>0.005685160120374888</v>
       </c>
       <c r="I132">
-        <v>0.04364970379235444</v>
+        <v>0.2045867769828364</v>
       </c>
       <c r="J132">
-        <v>0.8180792015972748</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K132">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L132">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M132">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N132">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O132">
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="133" spans="1:16">
       <c r="A133" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C133">
-        <v>2.078429124150567</v>
+        <v>1.964801996006813</v>
       </c>
       <c r="D133" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E133">
-        <v>1.921152292214459</v>
+        <v>1.87387546027835</v>
       </c>
       <c r="F133">
         <v>-1</v>
       </c>
       <c r="G133">
-        <v>0.006021570875849432</v>
+        <v>0.006055198003993187</v>
       </c>
       <c r="H133">
-        <v>0.00579884770778554</v>
+        <v>0.00568612453972165</v>
       </c>
       <c r="I133">
-        <v>0.1572768319361089</v>
+        <v>0.09092653572846343</v>
       </c>
       <c r="J133">
         <v>0.8180792015972748</v>
       </c>
       <c r="K133">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="L133">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M133">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N133">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O133">
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="134" spans="1:16">
       <c r="A134" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B134" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C134">
-        <v>1.96211546833212</v>
+        <v>2.078429124150567</v>
       </c>
       <c r="D134" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E134">
-        <v>1.91860546397885</v>
+        <v>1.87387546027835</v>
       </c>
       <c r="F134">
         <v>-1</v>
       </c>
       <c r="G134">
-        <v>0.006057884531667879</v>
+        <v>0.006021570875849432</v>
       </c>
       <c r="H134">
-        <v>0.00580139453602115</v>
+        <v>0.00568612453972165</v>
       </c>
       <c r="I134">
-        <v>0.04351000435327013</v>
+        <v>0.2045536638722179</v>
       </c>
       <c r="J134">
-        <v>0.8191538126671517</v>
+        <v>0.8180792015972748</v>
       </c>
       <c r="K134">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L134">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M134">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N134">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O134">
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="135" spans="1:16">
       <c r="A135" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C135">
-        <v>2.075839311472164</v>
+        <v>1.96211546833212</v>
       </c>
       <c r="D135" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E135">
-        <v>1.91860546397885</v>
+        <v>1.871371616485536</v>
       </c>
       <c r="F135">
         <v>-1</v>
       </c>
       <c r="G135">
-        <v>0.006024160688527836</v>
+        <v>0.006057884531667879</v>
       </c>
       <c r="H135">
-        <v>0.00580139453602115</v>
+        <v>0.005688628383514464</v>
       </c>
       <c r="I135">
-        <v>0.1572338474933135</v>
+        <v>0.09074385184658418</v>
       </c>
       <c r="J135">
         <v>0.8191538126671517</v>
       </c>
       <c r="K135">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="L135">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M135">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N135">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O135">
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="136" spans="1:16">
       <c r="A136" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B136" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C136">
-        <v>1.969378632640371</v>
+        <v>2.075839311472164</v>
       </c>
       <c r="D136" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E136">
-        <v>1.925490943743072</v>
+        <v>1.871371616485536</v>
       </c>
       <c r="F136">
         <v>-1</v>
       </c>
       <c r="G136">
-        <v>0.006050621367359629</v>
+        <v>0.006024160688527836</v>
       </c>
       <c r="H136">
-        <v>0.005794509056256928</v>
+        <v>0.005688628383514464</v>
       </c>
       <c r="I136">
-        <v>0.04388768889729944</v>
+        <v>0.2044676949866275</v>
       </c>
       <c r="J136">
-        <v>0.8162485469438515</v>
+        <v>0.8191538126671517</v>
       </c>
       <c r="K136">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L136">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M136">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N136">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O136">
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="137" spans="1:16">
       <c r="A137" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B137" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C137">
-        <v>2.082841001865318</v>
+        <v>1.969378632640371</v>
       </c>
       <c r="D137" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E137">
-        <v>1.925490943743072</v>
+        <v>1.878140885620826</v>
       </c>
       <c r="F137">
         <v>-1</v>
       </c>
       <c r="G137">
-        <v>0.006017158998134682</v>
+        <v>0.006050621367359629</v>
       </c>
       <c r="H137">
-        <v>0.005794509056256928</v>
+        <v>0.005681859114379174</v>
       </c>
       <c r="I137">
-        <v>0.1573500581222462</v>
+        <v>0.09123774701954535</v>
       </c>
       <c r="J137">
         <v>0.8162485469438515</v>
       </c>
       <c r="K137">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="L137">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="M137">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N137">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O137">
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="138" spans="1:16">
       <c r="A138" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B138" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C138">
-        <v>1.979025316902244</v>
+        <v>2.082841001865318</v>
       </c>
       <c r="D138" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E138">
-        <v>1.934636000423327</v>
+        <v>1.878140885620826</v>
       </c>
       <c r="F138">
         <v>-1</v>
       </c>
       <c r="G138">
-        <v>0.006040974683097756</v>
+        <v>0.006017158998134682</v>
       </c>
       <c r="H138">
-        <v>0.005785363999576672</v>
+        <v>0.005681859114379174</v>
       </c>
       <c r="I138">
-        <v>0.04438931647891664</v>
+        <v>0.2047001162444921</v>
       </c>
       <c r="J138">
-        <v>0.8123898732391025</v>
+        <v>0.8162485469438515</v>
       </c>
       <c r="K138">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L138">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M138">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N138">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O138">
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="139" spans="1:16">
       <c r="A139" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B139" t="s">
         <v>36</v>
@@ -7777,10 +7783,10 @@
         <v>2.092140405493763</v>
       </c>
       <c r="D139" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E139">
-        <v>1.934636000423327</v>
+        <v>1.887131595352891</v>
       </c>
       <c r="F139">
         <v>-1</v>
@@ -7789,10 +7795,10 @@
         <v>0.006007859594506237</v>
       </c>
       <c r="H139">
-        <v>0.005785363999576672</v>
+        <v>0.005672868404647109</v>
       </c>
       <c r="I139">
-        <v>0.1575044050704357</v>
+        <v>0.2050088101408718</v>
       </c>
       <c r="J139">
         <v>0.8123898732391025</v>
@@ -7804,16 +7810,16 @@
         <v>4.05</v>
       </c>
       <c r="M139">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N139">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O139">
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -7821,81 +7827,81 @@
         <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C140">
-        <v>1.983626913195719</v>
+        <v>2.096576344320673</v>
       </c>
       <c r="D140" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E140">
-        <v>1.938998313709541</v>
+        <v>1.89142028309841</v>
       </c>
       <c r="F140">
         <v>-1</v>
       </c>
       <c r="G140">
-        <v>0.00603637308680428</v>
+        <v>0.006003423655679328</v>
       </c>
       <c r="H140">
-        <v>0.005781001686290459</v>
+        <v>0.00566857971690159</v>
       </c>
       <c r="I140">
-        <v>0.04462859948617748</v>
+        <v>0.2051560612222629</v>
       </c>
       <c r="J140">
         <v>0.8105492347217125</v>
       </c>
       <c r="K140">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L140">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M140">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N140">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O140">
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="141" spans="1:16">
       <c r="A141" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B141" t="s">
         <v>36</v>
       </c>
       <c r="C141">
-        <v>2.096576344320673</v>
+        <v>2.103396386673994</v>
       </c>
       <c r="D141" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E141">
-        <v>1.938998313709541</v>
+        <v>1.898013934004318</v>
       </c>
       <c r="F141">
         <v>-1</v>
       </c>
       <c r="G141">
-        <v>0.006003423655679328</v>
+        <v>0.005996603613326006</v>
       </c>
       <c r="H141">
-        <v>0.005781001686290459</v>
+        <v>0.005661986065995682</v>
       </c>
       <c r="I141">
-        <v>0.1575780306111314</v>
+        <v>0.2053824526696761</v>
       </c>
       <c r="J141">
-        <v>0.8105492347217125</v>
+        <v>0.8077193416290479</v>
       </c>
       <c r="K141">
         <v>2.41</v>
@@ -7904,16 +7910,16 @@
         <v>4.05</v>
       </c>
       <c r="M141">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N141">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O141">
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -7921,81 +7927,81 @@
         <v>0</v>
       </c>
       <c r="B142" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C142">
-        <v>1.99070164592738</v>
+        <v>2.108040013253082</v>
       </c>
       <c r="D142" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E142">
-        <v>1.945705160339156</v>
+        <v>1.902503415302772</v>
       </c>
       <c r="F142">
         <v>-1</v>
       </c>
       <c r="G142">
-        <v>0.006029298354072619</v>
+        <v>0.005991959986746918</v>
       </c>
       <c r="H142">
-        <v>0.005774294839660844</v>
+        <v>0.005657496584697228</v>
       </c>
       <c r="I142">
-        <v>0.04499648558822389</v>
+        <v>0.2055365979503097</v>
       </c>
       <c r="J142">
-        <v>0.8077193416290479</v>
+        <v>0.8057925256211278</v>
       </c>
       <c r="K142">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L142">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M142">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N142">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O142">
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="143" spans="1:16">
       <c r="A143" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B143" t="s">
         <v>36</v>
       </c>
       <c r="C143">
-        <v>2.103396386673994</v>
+        <v>2.114054135735469</v>
       </c>
       <c r="D143" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E143">
-        <v>1.945705160339156</v>
+        <v>1.908317898864581</v>
       </c>
       <c r="F143">
         <v>-1</v>
       </c>
       <c r="G143">
-        <v>0.005996603613326006</v>
+        <v>0.005985945864264531</v>
       </c>
       <c r="H143">
-        <v>0.005774294839660844</v>
+        <v>0.005651682101135419</v>
       </c>
       <c r="I143">
-        <v>0.157691226334838</v>
+        <v>0.2057362368708873</v>
       </c>
       <c r="J143">
-        <v>0.8077193416290479</v>
+        <v>0.8032970391139135</v>
       </c>
       <c r="K143">
         <v>2.41</v>
@@ -8004,16 +8010,16 @@
         <v>4.05</v>
       </c>
       <c r="M143">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N143">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O143">
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8021,81 +8027,81 @@
         <v>0</v>
       </c>
       <c r="B144" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C144">
-        <v>1.995518685947181</v>
+        <v>2.120323822719538</v>
       </c>
       <c r="D144" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E144">
-        <v>1.950271714277927</v>
+        <v>1.914379463459138</v>
       </c>
       <c r="F144">
         <v>-1</v>
       </c>
       <c r="G144">
-        <v>0.006024481314052819</v>
+        <v>0.005979676177280462</v>
       </c>
       <c r="H144">
-        <v>0.005769728285722073</v>
+        <v>0.005645620536540861</v>
       </c>
       <c r="I144">
-        <v>0.04524697166925362</v>
+        <v>0.2059443592603993</v>
       </c>
       <c r="J144">
-        <v>0.8057925256211278</v>
+        <v>0.8006955092450049</v>
       </c>
       <c r="K144">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L144">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M144">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N144">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O144">
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="145" spans="1:16">
       <c r="A145" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B145" t="s">
         <v>36</v>
       </c>
       <c r="C145">
-        <v>2.108040013253082</v>
+        <v>2.125285159031259</v>
       </c>
       <c r="D145" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E145">
-        <v>1.950271714277927</v>
+        <v>1.919176108109059</v>
       </c>
       <c r="F145">
         <v>-1</v>
       </c>
       <c r="G145">
-        <v>0.005991959986746918</v>
+        <v>0.005974714840968741</v>
       </c>
       <c r="H145">
-        <v>0.005769728285722073</v>
+        <v>0.00564082389189094</v>
       </c>
       <c r="I145">
-        <v>0.1577682989751548</v>
+        <v>0.2061090509221997</v>
       </c>
       <c r="J145">
-        <v>0.8057925256211278</v>
+        <v>0.7986368634725065</v>
       </c>
       <c r="K145">
         <v>2.41</v>
@@ -8104,16 +8110,16 @@
         <v>4.05</v>
       </c>
       <c r="M145">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N145">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O145">
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8121,81 +8127,81 @@
         <v>0</v>
       </c>
       <c r="B146" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C146">
-        <v>2.001757402215216</v>
+        <v>2.136281584912229</v>
       </c>
       <c r="D146" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E146">
-        <v>1.956186017300025</v>
+        <v>1.929807507404769</v>
       </c>
       <c r="F146">
         <v>-1</v>
       </c>
       <c r="G146">
-        <v>0.006018242597784784</v>
+        <v>0.00596371841508777</v>
       </c>
       <c r="H146">
-        <v>0.005763813982699975</v>
+        <v>0.00563019249259523</v>
       </c>
       <c r="I146">
-        <v>0.0455713849151913</v>
+        <v>0.2064740775074598</v>
       </c>
       <c r="J146">
-        <v>0.8032970391139135</v>
+        <v>0.7940740311567515</v>
       </c>
       <c r="K146">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L146">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M146">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N146">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O146">
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="147" spans="1:16">
       <c r="A147" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B147" t="s">
         <v>36</v>
       </c>
       <c r="C147">
-        <v>2.114054135735469</v>
+        <v>2.148053344388881</v>
       </c>
       <c r="D147" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E147">
-        <v>1.956186017300025</v>
+        <v>1.941188503081367</v>
       </c>
       <c r="F147">
         <v>-1</v>
       </c>
       <c r="G147">
-        <v>0.005985945864264531</v>
+        <v>0.005951946655611119</v>
       </c>
       <c r="H147">
-        <v>0.005763813982699975</v>
+        <v>0.005618811496918633</v>
       </c>
       <c r="I147">
-        <v>0.1578681184354436</v>
+        <v>0.2068648413075147</v>
       </c>
       <c r="J147">
-        <v>0.8032970391139135</v>
+        <v>0.7891894836560657</v>
       </c>
       <c r="K147">
         <v>2.41</v>
@@ -8204,16 +8210,16 @@
         <v>4.05</v>
       </c>
       <c r="M147">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N147">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O147">
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8221,81 +8227,81 @@
         <v>0</v>
       </c>
       <c r="B148" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C148">
-        <v>2.008261226887488</v>
+        <v>2.151305835742038</v>
       </c>
       <c r="D148" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E148">
-        <v>1.962351643089338</v>
+        <v>1.944333027916576</v>
       </c>
       <c r="F148">
         <v>-1</v>
       </c>
       <c r="G148">
-        <v>0.006011738773112512</v>
+        <v>0.005948694164257961</v>
       </c>
       <c r="H148">
-        <v>0.005757648356910661</v>
+        <v>0.005615666972083423</v>
       </c>
       <c r="I148">
-        <v>0.04590958379814936</v>
+        <v>0.2069728078254618</v>
       </c>
       <c r="J148">
-        <v>0.8006955092450049</v>
+        <v>0.7878399021817268</v>
       </c>
       <c r="K148">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L148">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M148">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N148">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O148">
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="149" spans="1:16">
       <c r="A149" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B149" t="s">
         <v>36</v>
       </c>
       <c r="C149">
-        <v>2.120323822719538</v>
+        <v>2.151572681684375</v>
       </c>
       <c r="D149" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E149">
-        <v>1.962351643089338</v>
+        <v>1.944591015902321</v>
       </c>
       <c r="F149">
         <v>-1</v>
       </c>
       <c r="G149">
-        <v>0.005979676177280462</v>
+        <v>0.005948427318315626</v>
       </c>
       <c r="H149">
-        <v>0.005757648356910661</v>
+        <v>0.00561540898409768</v>
       </c>
       <c r="I149">
-        <v>0.1579721796301996</v>
+        <v>0.206981665782054</v>
       </c>
       <c r="J149">
-        <v>0.8006955092450049</v>
+        <v>0.7877291777243258</v>
       </c>
       <c r="K149">
         <v>2.41</v>
@@ -8304,16 +8310,16 @@
         <v>4.05</v>
       </c>
       <c r="M149">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N149">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O149">
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8321,81 +8327,81 @@
         <v>0</v>
       </c>
       <c r="B150" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C150">
-        <v>2.013407841318734</v>
+        <v>2.152621179997558</v>
       </c>
       <c r="D150" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E150">
-        <v>1.967230633570159</v>
+        <v>1.945604709292245</v>
       </c>
       <c r="F150">
         <v>-1</v>
       </c>
       <c r="G150">
-        <v>0.006006592158681266</v>
+        <v>0.005947378820002442</v>
       </c>
       <c r="H150">
-        <v>0.00575276936642984</v>
+        <v>0.005614395290707755</v>
       </c>
       <c r="I150">
-        <v>0.04617720774857448</v>
+        <v>0.207016470705313</v>
       </c>
       <c r="J150">
-        <v>0.7986368634725065</v>
+        <v>0.7872941161835857</v>
       </c>
       <c r="K150">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L150">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M150">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N150">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O150">
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="151" spans="1:16">
       <c r="A151" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B151" t="s">
         <v>36</v>
       </c>
       <c r="C151">
-        <v>2.125285159031259</v>
+        <v>2.149282713891501</v>
       </c>
       <c r="D151" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E151">
-        <v>1.967230633570159</v>
+        <v>1.942377063637841</v>
       </c>
       <c r="F151">
         <v>-1</v>
       </c>
       <c r="G151">
-        <v>0.005974714840968741</v>
+        <v>0.005950717286108499</v>
       </c>
       <c r="H151">
-        <v>0.00575276936642984</v>
+        <v>0.005617622936362159</v>
       </c>
       <c r="I151">
-        <v>0.1580545254610999</v>
+        <v>0.2069056502536595</v>
       </c>
       <c r="J151">
-        <v>0.7986368634725065</v>
+        <v>0.7886793718292525</v>
       </c>
       <c r="K151">
         <v>2.41</v>
@@ -8404,16 +8410,16 @@
         <v>4.05</v>
       </c>
       <c r="M151">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N151">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O151">
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8424,28 +8430,28 @@
         <v>36</v>
       </c>
       <c r="C152">
-        <v>2.136281584912229</v>
+        <v>2.146227648604146</v>
       </c>
       <c r="D152" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E152">
-        <v>1.978044546158499</v>
+        <v>1.939423411306084</v>
       </c>
       <c r="F152">
         <v>-1</v>
       </c>
       <c r="G152">
-        <v>0.00596371841508777</v>
+        <v>0.005953772351395854</v>
       </c>
       <c r="H152">
-        <v>0.005741955453841502</v>
+        <v>0.005620576588693917</v>
       </c>
       <c r="I152">
-        <v>0.15823703875373</v>
+        <v>0.206804237298063</v>
       </c>
       <c r="J152">
-        <v>0.7940740311567515</v>
+        <v>0.7899470337742129</v>
       </c>
       <c r="K152">
         <v>2.41</v>
@@ -8454,16 +8460,16 @@
         <v>4.05</v>
       </c>
       <c r="M152">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N152">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O152">
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8474,28 +8480,28 @@
         <v>36</v>
       </c>
       <c r="C153">
-        <v>2.148053344388881</v>
+        <v>2.145080586568228</v>
       </c>
       <c r="D153" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E153">
-        <v>1.989620923735124</v>
+        <v>1.938314426018246</v>
       </c>
       <c r="F153">
         <v>-1</v>
       </c>
       <c r="G153">
-        <v>0.005951946655611119</v>
+        <v>0.005954919413431771</v>
       </c>
       <c r="H153">
-        <v>0.005730379076264875</v>
+        <v>0.005621685573981754</v>
       </c>
       <c r="I153">
-        <v>0.1584324206537573</v>
+        <v>0.2067661605499826</v>
       </c>
       <c r="J153">
-        <v>0.7891894836560657</v>
+        <v>0.7904229931252164</v>
       </c>
       <c r="K153">
         <v>2.41</v>
@@ -8504,16 +8510,16 @@
         <v>4.05</v>
       </c>
       <c r="M153">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N153">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O153">
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8524,28 +8530,28 @@
         <v>36</v>
       </c>
       <c r="C154">
-        <v>2.151305835742038</v>
+        <v>2.14339129660172</v>
       </c>
       <c r="D154" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E154">
-        <v>1.992819431829307</v>
+        <v>1.936681212067224</v>
       </c>
       <c r="F154">
         <v>-1</v>
       </c>
       <c r="G154">
-        <v>0.005948694164257961</v>
+        <v>0.005956608703398279</v>
       </c>
       <c r="H154">
-        <v>0.005727180568170693</v>
+        <v>0.005623318787932776</v>
       </c>
       <c r="I154">
-        <v>0.1584864039127309</v>
+        <v>0.2067100845344967</v>
       </c>
       <c r="J154">
-        <v>0.7878399021817268</v>
+        <v>0.791123943318788</v>
       </c>
       <c r="K154">
         <v>2.41</v>
@@ -8554,16 +8560,16 @@
         <v>4.05</v>
       </c>
       <c r="M154">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N154">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O154">
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8574,28 +8580,28 @@
         <v>36</v>
       </c>
       <c r="C155">
-        <v>2.151572681684375</v>
+        <v>2.142284300015975</v>
       </c>
       <c r="D155" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E155">
-        <v>1.993081848793347</v>
+        <v>1.935610962256108</v>
       </c>
       <c r="F155">
         <v>-1</v>
       </c>
       <c r="G155">
-        <v>0.005948427318315626</v>
+        <v>0.005957715699984025</v>
       </c>
       <c r="H155">
-        <v>0.005726918151206652</v>
+        <v>0.005624389037743892</v>
       </c>
       <c r="I155">
-        <v>0.1584908328910271</v>
+        <v>0.2066733377598666</v>
       </c>
       <c r="J155">
-        <v>0.7877291777243258</v>
+        <v>0.7915832780016702</v>
       </c>
       <c r="K155">
         <v>2.41</v>
@@ -8604,16 +8610,16 @@
         <v>4.05</v>
       </c>
       <c r="M155">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N155">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O155">
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8624,28 +8630,28 @@
         <v>36</v>
       </c>
       <c r="C156">
-        <v>2.152621179997558</v>
+        <v>2.143425559712756</v>
       </c>
       <c r="D156" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E156">
-        <v>1.994112944644902</v>
+        <v>1.936714337813577</v>
       </c>
       <c r="F156">
         <v>-1</v>
       </c>
       <c r="G156">
-        <v>0.005947378820002442</v>
+        <v>0.005956574440287244</v>
       </c>
       <c r="H156">
-        <v>0.005725887055355099</v>
+        <v>0.005623285662186422</v>
       </c>
       <c r="I156">
-        <v>0.1585082353526563</v>
+        <v>0.2067112218991787</v>
       </c>
       <c r="J156">
-        <v>0.7872941161835857</v>
+        <v>0.7911097262602672</v>
       </c>
       <c r="K156">
         <v>2.41</v>
@@ -8654,16 +8660,16 @@
         <v>4.05</v>
       </c>
       <c r="M156">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N156">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O156">
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8674,28 +8680,28 @@
         <v>36</v>
       </c>
       <c r="C157">
-        <v>2.149282713891501</v>
+        <v>2.144968519714193</v>
       </c>
       <c r="D157" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E157">
-        <v>1.990829888764671</v>
+        <v>1.938206079225755</v>
       </c>
       <c r="F157">
         <v>-1</v>
       </c>
       <c r="G157">
-        <v>0.005950717286108499</v>
+        <v>0.005955031480285808</v>
       </c>
       <c r="H157">
-        <v>0.005729170111235329</v>
+        <v>0.005621793920774245</v>
       </c>
       <c r="I157">
-        <v>0.1584528251268296</v>
+        <v>0.2067624404884378</v>
       </c>
       <c r="J157">
-        <v>0.7886793718292525</v>
+        <v>0.7904694938945258</v>
       </c>
       <c r="K157">
         <v>2.41</v>
@@ -8704,16 +8710,16 @@
         <v>4.05</v>
       </c>
       <c r="M157">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N157">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O157">
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8724,28 +8730,28 @@
         <v>36</v>
       </c>
       <c r="C158">
-        <v>2.146227648604146</v>
+        <v>2.148138038800297</v>
       </c>
       <c r="D158" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E158">
-        <v>1.987825529955115</v>
+        <v>1.941270386060038</v>
       </c>
       <c r="F158">
         <v>-1</v>
       </c>
       <c r="G158">
-        <v>0.005953772351395854</v>
+        <v>0.005951861961199702</v>
       </c>
       <c r="H158">
-        <v>0.005732174470044885</v>
+        <v>0.005618729613939962</v>
       </c>
       <c r="I158">
-        <v>0.1584021186490314</v>
+        <v>0.2068676527402589</v>
       </c>
       <c r="J158">
-        <v>0.7899470337742129</v>
+        <v>0.7891543407467646</v>
       </c>
       <c r="K158">
         <v>2.41</v>
@@ -8754,16 +8760,16 @@
         <v>4.05</v>
       </c>
       <c r="M158">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N158">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O158">
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -8774,28 +8780,28 @@
         <v>36</v>
       </c>
       <c r="C159">
-        <v>2.145080586568228</v>
+        <v>2.151907493357466</v>
       </c>
       <c r="D159" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E159">
-        <v>1.986697506293237</v>
+        <v>1.944914713494977</v>
       </c>
       <c r="F159">
         <v>-1</v>
       </c>
       <c r="G159">
-        <v>0.005954919413431771</v>
+        <v>0.005948092506642534</v>
       </c>
       <c r="H159">
-        <v>0.005733302493706763</v>
+        <v>0.005615085286505023</v>
       </c>
       <c r="I159">
-        <v>0.1583830802749913</v>
+        <v>0.2069927798624884</v>
       </c>
       <c r="J159">
-        <v>0.7904229931252164</v>
+        <v>0.7875902517188939</v>
       </c>
       <c r="K159">
         <v>2.41</v>
@@ -8804,16 +8810,16 @@
         <v>4.05</v>
       </c>
       <c r="M159">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N159">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O159">
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -8824,28 +8830,28 @@
         <v>36</v>
       </c>
       <c r="C160">
-        <v>2.14339129660172</v>
+        <v>2.1538020117046</v>
       </c>
       <c r="D160" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E160">
-        <v>1.985036254334472</v>
+        <v>1.946746343266273</v>
       </c>
       <c r="F160">
         <v>-1</v>
       </c>
       <c r="G160">
-        <v>0.005956608703398279</v>
+        <v>0.005946197988295399</v>
       </c>
       <c r="H160">
-        <v>0.005734963745665528</v>
+        <v>0.005613253656733727</v>
       </c>
       <c r="I160">
-        <v>0.1583550422672482</v>
+        <v>0.2070556684383269</v>
       </c>
       <c r="J160">
-        <v>0.791123943318788</v>
+        <v>0.7868041445209126</v>
       </c>
       <c r="K160">
         <v>2.41</v>
@@ -8854,16 +8860,16 @@
         <v>4.05</v>
       </c>
       <c r="M160">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N160">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O160">
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -8874,28 +8880,28 @@
         <v>36</v>
       </c>
       <c r="C161">
-        <v>2.142284300015975</v>
+        <v>2.157161945588962</v>
       </c>
       <c r="D161" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E161">
-        <v>1.983947631136042</v>
+        <v>1.949994744075635</v>
       </c>
       <c r="F161">
         <v>-1</v>
       </c>
       <c r="G161">
-        <v>0.005957715699984025</v>
+        <v>0.005942838054411038</v>
       </c>
       <c r="H161">
-        <v>0.005736052368863958</v>
+        <v>0.005610005255924365</v>
       </c>
       <c r="I161">
-        <v>0.1583366688799333</v>
+        <v>0.2071672015133268</v>
       </c>
       <c r="J161">
-        <v>0.7915832780016702</v>
+        <v>0.7854099810834182</v>
       </c>
       <c r="K161">
         <v>2.41</v>
@@ -8904,16 +8910,16 @@
         <v>4.05</v>
       </c>
       <c r="M161">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N161">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O161">
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -8924,28 +8930,28 @@
         <v>36</v>
       </c>
       <c r="C162">
-        <v>2.143425559712756</v>
+        <v>2.161672330968959</v>
       </c>
       <c r="D162" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E162">
-        <v>1.985069948763166</v>
+        <v>1.954355407119367</v>
       </c>
       <c r="F162">
         <v>-1</v>
       </c>
       <c r="G162">
-        <v>0.005956574440287244</v>
+        <v>0.005938327669031041</v>
       </c>
       <c r="H162">
-        <v>0.005734930051236834</v>
+        <v>0.005605644592880633</v>
       </c>
       <c r="I162">
-        <v>0.1583556109495894</v>
+        <v>0.207316923849592</v>
       </c>
       <c r="J162">
-        <v>0.7911097262602672</v>
+        <v>0.7835384518800999</v>
       </c>
       <c r="K162">
         <v>2.41</v>
@@ -8954,16 +8960,16 @@
         <v>4.05</v>
       </c>
       <c r="M162">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N162">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O162">
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -8974,28 +8980,28 @@
         <v>36</v>
       </c>
       <c r="C163">
-        <v>2.144968519714193</v>
+        <v>2.162884754387039</v>
       </c>
       <c r="D163" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E163">
-        <v>1.986587299469974</v>
+        <v>1.95552758411693</v>
       </c>
       <c r="F163">
         <v>-1</v>
       </c>
       <c r="G163">
-        <v>0.005955031480285808</v>
+        <v>0.00593711524561296</v>
       </c>
       <c r="H163">
-        <v>0.005733412700530027</v>
+        <v>0.005604472415883069</v>
       </c>
       <c r="I163">
-        <v>0.158381220244219</v>
+        <v>0.2073571702701089</v>
       </c>
       <c r="J163">
-        <v>0.7904694938945258</v>
+        <v>0.783035371623635</v>
       </c>
       <c r="K163">
         <v>2.41</v>
@@ -9004,16 +9010,16 @@
         <v>4.05</v>
       </c>
       <c r="M163">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N163">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O163">
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9024,28 +9030,28 @@
         <v>36</v>
       </c>
       <c r="C164">
-        <v>2.148138038800297</v>
+        <v>2.16447911025038</v>
       </c>
       <c r="D164" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E164">
-        <v>1.989704212430168</v>
+        <v>1.957069015304309</v>
       </c>
       <c r="F164">
         <v>-1</v>
       </c>
       <c r="G164">
-        <v>0.005951861961199702</v>
+        <v>0.00593552088974962</v>
       </c>
       <c r="H164">
-        <v>0.005730295787569832</v>
+        <v>0.005602930984695691</v>
       </c>
       <c r="I164">
-        <v>0.1584338263701295</v>
+        <v>0.2074100949460704</v>
       </c>
       <c r="J164">
-        <v>0.7891543407467646</v>
+        <v>0.7823738131741161</v>
       </c>
       <c r="K164">
         <v>2.41</v>
@@ -9054,16 +9060,16 @@
         <v>4.05</v>
       </c>
       <c r="M164">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N164">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O164">
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9074,28 +9080,28 @@
         <v>36</v>
       </c>
       <c r="C165">
-        <v>2.151907493357466</v>
+        <v>2.168006663995569</v>
       </c>
       <c r="D165" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E165">
-        <v>1.993411103426221</v>
+        <v>1.960479471829741</v>
       </c>
       <c r="F165">
         <v>-1</v>
       </c>
       <c r="G165">
-        <v>0.005948092506642534</v>
+        <v>0.005931993336004431</v>
       </c>
       <c r="H165">
-        <v>0.005726588896573778</v>
+        <v>0.005599520528170259</v>
       </c>
       <c r="I165">
-        <v>0.1584963899312442</v>
+        <v>0.2075271921658277</v>
       </c>
       <c r="J165">
-        <v>0.7875902517188939</v>
+        <v>0.7809100979271496</v>
       </c>
       <c r="K165">
         <v>2.41</v>
@@ -9104,16 +9110,16 @@
         <v>4.05</v>
       </c>
       <c r="M165">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N165">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O165">
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9124,28 +9130,28 @@
         <v>36</v>
       </c>
       <c r="C166">
-        <v>2.1538020117046</v>
+        <v>2.16983540706272</v>
       </c>
       <c r="D166" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E166">
-        <v>1.995274177485437</v>
+        <v>1.962247509732838</v>
       </c>
       <c r="F166">
         <v>-1</v>
       </c>
       <c r="G166">
-        <v>0.005946197988295399</v>
+        <v>0.005930164592937279</v>
       </c>
       <c r="H166">
-        <v>0.005724725822514562</v>
+        <v>0.005597752490267162</v>
       </c>
       <c r="I166">
-        <v>0.1585278342191634</v>
+        <v>0.2075878973298828</v>
       </c>
       <c r="J166">
-        <v>0.7868041445209126</v>
+        <v>0.7801512833764644</v>
       </c>
       <c r="K166">
         <v>2.41</v>
@@ -9154,16 +9160,16 @@
         <v>4.05</v>
       </c>
       <c r="M166">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N166">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O166">
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9174,28 +9180,28 @@
         <v>36</v>
       </c>
       <c r="C167">
-        <v>2.157161945588962</v>
+        <v>2.170790161930732</v>
       </c>
       <c r="D167" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E167">
-        <v>1.998578344832299</v>
+        <v>1.963170571493197</v>
       </c>
       <c r="F167">
         <v>-1</v>
       </c>
       <c r="G167">
-        <v>0.005942838054411038</v>
+        <v>0.005929209838069268</v>
       </c>
       <c r="H167">
-        <v>0.005721421655167701</v>
+        <v>0.005596829428506803</v>
       </c>
       <c r="I167">
-        <v>0.1585836007566634</v>
+        <v>0.2076195904375346</v>
       </c>
       <c r="J167">
-        <v>0.7854099810834182</v>
+        <v>0.7797551195308166</v>
       </c>
       <c r="K167">
         <v>2.41</v>
@@ -9204,16 +9210,16 @@
         <v>4.05</v>
       </c>
       <c r="M167">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N167">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O167">
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9224,28 +9230,28 @@
         <v>36</v>
       </c>
       <c r="C168">
-        <v>2.161672330968959</v>
+        <v>2.17227793480229</v>
       </c>
       <c r="D168" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E168">
-        <v>2.003013869044163</v>
+        <v>1.964608957713418</v>
       </c>
       <c r="F168">
         <v>-1</v>
       </c>
       <c r="G168">
-        <v>0.005938327669031041</v>
+        <v>0.00592772206519771</v>
       </c>
       <c r="H168">
-        <v>0.005716986130955837</v>
+        <v>0.005595391042286581</v>
       </c>
       <c r="I168">
-        <v>0.1586584619247962</v>
+        <v>0.2076689770888727</v>
       </c>
       <c r="J168">
-        <v>0.7835384518800999</v>
+        <v>0.7791377863890909</v>
       </c>
       <c r="K168">
         <v>2.41</v>
@@ -9254,16 +9260,16 @@
         <v>4.05</v>
       </c>
       <c r="M168">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N168">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O168">
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9274,28 +9280,28 @@
         <v>36</v>
       </c>
       <c r="C169">
-        <v>2.162884754387039</v>
+        <v>2.17517405209197</v>
       </c>
       <c r="D169" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E169">
-        <v>2.004206169251985</v>
+        <v>1.967408938329581</v>
       </c>
       <c r="F169">
         <v>-1</v>
       </c>
       <c r="G169">
-        <v>0.00593711524561296</v>
+        <v>0.00592482594790803</v>
       </c>
       <c r="H169">
-        <v>0.005715793830748015</v>
+        <v>0.005592591061670419</v>
       </c>
       <c r="I169">
-        <v>0.1586785851350543</v>
+        <v>0.207765113762389</v>
       </c>
       <c r="J169">
-        <v>0.783035371623635</v>
+        <v>0.777936077970137</v>
       </c>
       <c r="K169">
         <v>2.41</v>
@@ -9304,16 +9310,16 @@
         <v>4.05</v>
       </c>
       <c r="M169">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N169">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O169">
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9324,28 +9330,28 @@
         <v>36</v>
       </c>
       <c r="C170">
-        <v>2.16447911025038</v>
+        <v>2.176658657571009</v>
       </c>
       <c r="D170" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E170">
-        <v>2.005774062777345</v>
+        <v>1.968844262298942</v>
       </c>
       <c r="F170">
         <v>-1</v>
       </c>
       <c r="G170">
-        <v>0.00593552088974962</v>
+        <v>0.005923341342428991</v>
       </c>
       <c r="H170">
-        <v>0.005714225937222655</v>
+        <v>0.005591155737701057</v>
       </c>
       <c r="I170">
-        <v>0.1587050474730347</v>
+        <v>0.2078143952720668</v>
       </c>
       <c r="J170">
-        <v>0.7823738131741161</v>
+        <v>0.7773200590991663</v>
       </c>
       <c r="K170">
         <v>2.41</v>
@@ -9354,16 +9360,16 @@
         <v>4.05</v>
       </c>
       <c r="M170">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N170">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O170">
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9374,28 +9380,28 @@
         <v>36</v>
       </c>
       <c r="C171">
-        <v>2.168006663995569</v>
+        <v>2.179386080861772</v>
       </c>
       <c r="D171" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E171">
-        <v>2.009243067912655</v>
+        <v>1.971481148716983</v>
       </c>
       <c r="F171">
         <v>-1</v>
       </c>
       <c r="G171">
-        <v>0.005931993336004431</v>
+        <v>0.005920613919138227</v>
       </c>
       <c r="H171">
-        <v>0.005710756932087344</v>
+        <v>0.005588518851283016</v>
       </c>
       <c r="I171">
-        <v>0.1587635960829137</v>
+        <v>0.2079049321447892</v>
       </c>
       <c r="J171">
-        <v>0.7809100979271496</v>
+        <v>0.7761883481901358</v>
       </c>
       <c r="K171">
         <v>2.41</v>
@@ -9404,16 +9410,16 @@
         <v>4.05</v>
       </c>
       <c r="M171">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N171">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O171">
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9424,28 +9430,28 @@
         <v>36</v>
       </c>
       <c r="C172">
-        <v>2.16983540706272</v>
+        <v>2.182571074608897</v>
       </c>
       <c r="D172" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E172">
-        <v>2.011041458397779</v>
+        <v>1.974560416530593</v>
       </c>
       <c r="F172">
         <v>-1</v>
       </c>
       <c r="G172">
-        <v>0.005930164592937279</v>
+        <v>0.005917428925391103</v>
       </c>
       <c r="H172">
-        <v>0.005708958541602221</v>
+        <v>0.005585439583469407</v>
       </c>
       <c r="I172">
-        <v>0.1587939486649415</v>
+        <v>0.2080106580783037</v>
       </c>
       <c r="J172">
-        <v>0.7801512833764644</v>
+        <v>0.7748667740212044</v>
       </c>
       <c r="K172">
         <v>2.41</v>
@@ -9454,16 +9460,16 @@
         <v>4.05</v>
       </c>
       <c r="M172">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N172">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O172">
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9474,28 +9480,28 @@
         <v>36</v>
       </c>
       <c r="C173">
-        <v>2.170790161930732</v>
+        <v>2.185730109854243</v>
       </c>
       <c r="D173" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E173">
-        <v>2.011980366711964</v>
+        <v>1.97761458753543</v>
       </c>
       <c r="F173">
         <v>-1</v>
       </c>
       <c r="G173">
-        <v>0.005929209838069268</v>
+        <v>0.005914269890145757</v>
       </c>
       <c r="H173">
-        <v>0.005708019633288036</v>
+        <v>0.00558238541246457</v>
       </c>
       <c r="I173">
-        <v>0.1588097952187675</v>
+        <v>0.2081155223188127</v>
       </c>
       <c r="J173">
-        <v>0.7797551195308166</v>
+        <v>0.7735559710148369</v>
       </c>
       <c r="K173">
         <v>2.41</v>
@@ -9504,16 +9510,16 @@
         <v>4.05</v>
       </c>
       <c r="M173">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N173">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O173">
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9524,28 +9530,28 @@
         <v>36</v>
       </c>
       <c r="C174">
-        <v>2.17227793480229</v>
+        <v>2.187649692044639</v>
       </c>
       <c r="D174" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E174">
-        <v>2.013443446257854</v>
+        <v>1.979470449155191</v>
       </c>
       <c r="F174">
         <v>-1</v>
       </c>
       <c r="G174">
-        <v>0.00592772206519771</v>
+        <v>0.005912350307955361</v>
       </c>
       <c r="H174">
-        <v>0.005706556553742146</v>
+        <v>0.005580529550844809</v>
       </c>
       <c r="I174">
-        <v>0.1588344885444362</v>
+        <v>0.2081792428894487</v>
       </c>
       <c r="J174">
-        <v>0.7791377863890909</v>
+        <v>0.7727594638818923</v>
       </c>
       <c r="K174">
         <v>2.41</v>
@@ -9554,16 +9560,16 @@
         <v>4.05</v>
       </c>
       <c r="M174">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N174">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O174">
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9574,28 +9580,28 @@
         <v>36</v>
       </c>
       <c r="C175">
-        <v>2.17517405209197</v>
+        <v>2.18845970117501</v>
       </c>
       <c r="D175" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E175">
-        <v>2.016291495210775</v>
+        <v>1.980253570015674</v>
       </c>
       <c r="F175">
         <v>-1</v>
       </c>
       <c r="G175">
-        <v>0.00592482594790803</v>
+        <v>0.005911540298824991</v>
       </c>
       <c r="H175">
-        <v>0.005703708504789224</v>
+        <v>0.005579746429984326</v>
       </c>
       <c r="I175">
-        <v>0.1588825568811942</v>
+        <v>0.2082061311593364</v>
       </c>
       <c r="J175">
-        <v>0.777936077970137</v>
+        <v>0.7724233605082945</v>
       </c>
       <c r="K175">
         <v>2.41</v>
@@ -9604,16 +9610,16 @@
         <v>4.05</v>
       </c>
       <c r="M175">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N175">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O175">
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9621,49 +9627,49 @@
         <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C176">
-        <v>2.176658657571009</v>
+        <v>1.57348881425233</v>
       </c>
       <c r="D176" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="E176">
-        <v>2.017751459934976</v>
+        <v>1.930716141714586</v>
       </c>
       <c r="F176">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G176">
-        <v>0.005923341342428991</v>
+        <v>0.004646511185747669</v>
       </c>
       <c r="H176">
-        <v>0.005702248540065025</v>
+        <v>0.005949283858285414</v>
       </c>
       <c r="I176">
-        <v>0.1589071976360334</v>
+        <v>0.3572273274622557</v>
       </c>
       <c r="J176">
-        <v>0.7773200590991663</v>
+        <v>0.7879544542295741</v>
       </c>
       <c r="K176">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="L176">
-        <v>4.05</v>
+        <v>3.11</v>
       </c>
       <c r="M176">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="N176">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="O176">
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9671,49 +9677,49 @@
         <v>0</v>
       </c>
       <c r="B177" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C177">
-        <v>2.179386080861772</v>
+        <v>1.569608330766713</v>
       </c>
       <c r="D177" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="E177">
-        <v>2.020433614789378</v>
+        <v>1.925641663310317</v>
       </c>
       <c r="F177">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G177">
-        <v>0.005920613919138227</v>
+        <v>0.004650391669233286</v>
       </c>
       <c r="H177">
-        <v>0.005699566385210622</v>
+        <v>0.005954358336689684</v>
       </c>
       <c r="I177">
-        <v>0.1589524660723942</v>
+        <v>0.3560333325436043</v>
       </c>
       <c r="J177">
-        <v>0.7761883481901358</v>
+        <v>0.78994444576066</v>
       </c>
       <c r="K177">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="L177">
-        <v>4.05</v>
+        <v>3.11</v>
       </c>
       <c r="M177">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="N177">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="O177">
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9721,49 +9727,49 @@
         <v>0</v>
       </c>
       <c r="B178" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C178">
-        <v>2.182571074608897</v>
+        <v>1.563290930299889</v>
       </c>
       <c r="D178" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="E178">
-        <v>2.023565745569745</v>
+        <v>1.91738044731524</v>
       </c>
       <c r="F178">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G178">
-        <v>0.005917428925391103</v>
+        <v>0.00465670906970011</v>
       </c>
       <c r="H178">
-        <v>0.005696434254430255</v>
+        <v>0.005962619552684761</v>
       </c>
       <c r="I178">
-        <v>0.159005329039152</v>
+        <v>0.3540895170153506</v>
       </c>
       <c r="J178">
-        <v>0.7748667740212044</v>
+        <v>0.7931841383077493</v>
       </c>
       <c r="K178">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="L178">
-        <v>4.05</v>
+        <v>3.11</v>
       </c>
       <c r="M178">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="N178">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="O178">
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9771,49 +9777,49 @@
         <v>0</v>
       </c>
       <c r="B179" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C179">
-        <v>2.185730109854243</v>
+        <v>1.559502895465797</v>
       </c>
       <c r="D179" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="E179">
-        <v>2.026672348694836</v>
+        <v>1.912426863301427</v>
       </c>
       <c r="F179">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G179">
-        <v>0.005914269890145757</v>
+        <v>0.004660497104534203</v>
       </c>
       <c r="H179">
-        <v>0.005693327651305164</v>
+        <v>0.005967573136698573</v>
       </c>
       <c r="I179">
-        <v>0.1590577611594064</v>
+        <v>0.35292396783563</v>
       </c>
       <c r="J179">
-        <v>0.7735559710148369</v>
+        <v>0.7951267202739504</v>
       </c>
       <c r="K179">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="L179">
-        <v>4.05</v>
+        <v>3.11</v>
       </c>
       <c r="M179">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="N179">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="O179">
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -9821,49 +9827,49 @@
         <v>0</v>
       </c>
       <c r="B180" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C180">
-        <v>2.187649692044639</v>
+        <v>1.590146235974642</v>
       </c>
       <c r="D180" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="E180">
-        <v>2.028560070599915</v>
+        <v>1.910334776982754</v>
       </c>
       <c r="F180">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G180">
-        <v>0.005912350307955361</v>
+        <v>0.004789853764025359</v>
       </c>
       <c r="H180">
-        <v>0.005691439929400085</v>
+        <v>0.005969665223017246</v>
       </c>
       <c r="I180">
-        <v>0.1590896214447244</v>
+        <v>0.3201885410081127</v>
       </c>
       <c r="J180">
-        <v>0.7727594638818923</v>
+        <v>0.7959471462812728</v>
       </c>
       <c r="K180">
-        <v>2.41</v>
+        <v>2.01</v>
       </c>
       <c r="L180">
-        <v>4.05</v>
+        <v>3.19</v>
       </c>
       <c r="M180">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="N180">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="O180">
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -9874,28 +9880,28 @@
         <v>36</v>
       </c>
       <c r="C181">
-        <v>2.18845970117501</v>
+        <v>2.134728112347791</v>
       </c>
       <c r="D181" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E181">
-        <v>2.029356635595342</v>
+        <v>1.928305602394337</v>
       </c>
       <c r="F181">
         <v>-1</v>
       </c>
       <c r="G181">
-        <v>0.005911540298824991</v>
+        <v>0.005965271887652209</v>
       </c>
       <c r="H181">
-        <v>0.005690643364404658</v>
+        <v>0.005631694397605662</v>
       </c>
       <c r="I181">
-        <v>0.1591030655796684</v>
+        <v>0.2064225099534538</v>
       </c>
       <c r="J181">
-        <v>0.7724233605082945</v>
+        <v>0.7947186255818296</v>
       </c>
       <c r="K181">
         <v>2.41</v>
@@ -9904,16 +9910,16 @@
         <v>4.05</v>
       </c>
       <c r="M181">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N181">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O181">
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -9924,28 +9930,28 @@
         <v>36</v>
       </c>
       <c r="C182">
-        <v>2.188849869028743</v>
+        <v>2.126802703854744</v>
       </c>
       <c r="D182" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E182">
-        <v>2.029740327634074</v>
+        <v>1.920643278000645</v>
       </c>
       <c r="F182">
         <v>-1</v>
       </c>
       <c r="G182">
-        <v>0.005911150130971257</v>
+        <v>0.005973197296145255</v>
       </c>
       <c r="H182">
-        <v>0.005690259672365926</v>
+        <v>0.005639356721999355</v>
       </c>
       <c r="I182">
-        <v>0.1591095413946682</v>
+        <v>0.2061594258540995</v>
       </c>
       <c r="J182">
-        <v>0.7722614651333018</v>
+        <v>0.7980071768237574</v>
       </c>
       <c r="K182">
         <v>2.41</v>
@@ -9954,16 +9960,16 @@
         <v>4.05</v>
       </c>
       <c r="M182">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N182">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O182">
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -9974,28 +9980,28 @@
         <v>36</v>
       </c>
       <c r="C183">
-        <v>2.187755446155108</v>
+        <v>2.118150939933342</v>
       </c>
       <c r="D183" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E183">
-        <v>2.028664069455438</v>
+        <v>1.912278709562111</v>
       </c>
       <c r="F183">
         <v>-1</v>
       </c>
       <c r="G183">
-        <v>0.005912244553844892</v>
+        <v>0.005981849060066658</v>
       </c>
       <c r="H183">
-        <v>0.005691335930544562</v>
+        <v>0.00564772129043789</v>
       </c>
       <c r="I183">
-        <v>0.1590913766996698</v>
+        <v>0.2058722303712313</v>
       </c>
       <c r="J183">
-        <v>0.772715582508254</v>
+        <v>0.8015971203596091</v>
       </c>
       <c r="K183">
         <v>2.41</v>
@@ -10004,16 +10010,16 @@
         <v>4.05</v>
       </c>
       <c r="M183">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N183">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O183">
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10024,28 +10030,28 @@
         <v>36</v>
       </c>
       <c r="C184">
-        <v>2.185506499177827</v>
+        <v>2.102390273794673</v>
       </c>
       <c r="D184" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E184">
-        <v>2.026452449398942</v>
+        <v>1.8970412190629</v>
       </c>
       <c r="F184">
         <v>-1</v>
       </c>
       <c r="G184">
-        <v>0.005914493500822173</v>
+        <v>0.005997609726205327</v>
       </c>
       <c r="H184">
-        <v>0.005693547550601058</v>
+        <v>0.0056629587809371</v>
       </c>
       <c r="I184">
-        <v>0.1590540497788853</v>
+        <v>0.2053490547317733</v>
       </c>
       <c r="J184">
-        <v>0.7736487555278725</v>
+        <v>0.8081368158528327</v>
       </c>
       <c r="K184">
         <v>2.41</v>
@@ -10054,16 +10060,16 @@
         <v>4.05</v>
       </c>
       <c r="M184">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N184">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O184">
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>152</v>
+        <v>25</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10071,49 +10077,49 @@
         <v>0</v>
       </c>
       <c r="B185" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C185">
-        <v>1.569608330766713</v>
+        <v>2.068262994068838</v>
       </c>
       <c r="D185" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E185">
-        <v>1.925641663310317</v>
+        <v>1.864046795095599</v>
       </c>
       <c r="F185">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G185">
-        <v>0.004650391669233286</v>
+        <v>0.006031737005931162</v>
       </c>
       <c r="H185">
-        <v>0.005954358336689684</v>
+        <v>0.005695953204904402</v>
       </c>
       <c r="I185">
-        <v>0.3560333325436043</v>
+        <v>0.2042161989732392</v>
       </c>
       <c r="J185">
-        <v>0.78994444576066</v>
+        <v>0.8222975128345069</v>
       </c>
       <c r="K185">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="L185">
-        <v>3.11</v>
+        <v>4.05</v>
       </c>
       <c r="M185">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="N185">
-        <v>3.94</v>
+        <v>3.78</v>
       </c>
       <c r="O185">
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>153</v>
+        <v>32</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10121,49 +10127,49 @@
         <v>0</v>
       </c>
       <c r="B186" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C186">
-        <v>1.563290930299889</v>
+        <v>2.026595514500883</v>
       </c>
       <c r="D186" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E186">
-        <v>1.91738044731524</v>
+        <v>1.823762468376372</v>
       </c>
       <c r="F186">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G186">
-        <v>0.00465670906970011</v>
+        <v>0.006073404485499117</v>
       </c>
       <c r="H186">
-        <v>0.005962619552684761</v>
+        <v>0.005736237531623627</v>
       </c>
       <c r="I186">
-        <v>0.3540895170153506</v>
+        <v>0.2028330461245107</v>
       </c>
       <c r="J186">
-        <v>0.7931841383077493</v>
+        <v>0.8395869234436169</v>
       </c>
       <c r="K186">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="L186">
-        <v>3.11</v>
+        <v>4.05</v>
       </c>
       <c r="M186">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="N186">
-        <v>3.94</v>
+        <v>3.78</v>
       </c>
       <c r="O186">
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10171,49 +10177,49 @@
         <v>0</v>
       </c>
       <c r="B187" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C187">
-        <v>1.559502895465797</v>
+        <v>2.00904612221926</v>
       </c>
       <c r="D187" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E187">
-        <v>1.912426863301427</v>
+        <v>1.806795628535633</v>
       </c>
       <c r="F187">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G187">
-        <v>0.004660497104534203</v>
+        <v>0.006090953877780739</v>
       </c>
       <c r="H187">
-        <v>0.005967573136698573</v>
+        <v>0.005753204371464368</v>
       </c>
       <c r="I187">
-        <v>0.35292396783563</v>
+        <v>0.2022504936836271</v>
       </c>
       <c r="J187">
-        <v>0.7951267202739504</v>
+        <v>0.846868828954664</v>
       </c>
       <c r="K187">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="L187">
-        <v>3.11</v>
+        <v>4.05</v>
       </c>
       <c r="M187">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="N187">
-        <v>3.94</v>
+        <v>3.78</v>
       </c>
       <c r="O187">
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10221,49 +10227,49 @@
         <v>0</v>
       </c>
       <c r="B188" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C188">
-        <v>1.590146235974642</v>
+        <v>1.99410787626086</v>
       </c>
       <c r="D188" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E188">
-        <v>1.910334776982754</v>
+        <v>1.792353257961744</v>
       </c>
       <c r="F188">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G188">
-        <v>0.004789853764025359</v>
+        <v>0.00610589212373914</v>
       </c>
       <c r="H188">
-        <v>0.005969665223017246</v>
+        <v>0.005767646742038256</v>
       </c>
       <c r="I188">
-        <v>0.3201885410081127</v>
+        <v>0.2017546182991157</v>
       </c>
       <c r="J188">
-        <v>0.7959471462812728</v>
+        <v>0.8530672712610541</v>
       </c>
       <c r="K188">
-        <v>2.01</v>
+        <v>2.41</v>
       </c>
       <c r="L188">
-        <v>3.19</v>
+        <v>4.05</v>
       </c>
       <c r="M188">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="N188">
-        <v>3.94</v>
+        <v>3.78</v>
       </c>
       <c r="O188">
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>156</v>
+        <v>24</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10274,28 +10280,28 @@
         <v>36</v>
       </c>
       <c r="C189">
-        <v>2.134728112347791</v>
+        <v>1.97566667479463</v>
       </c>
       <c r="D189" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E189">
-        <v>1.976516857371064</v>
+        <v>1.774524212560784</v>
       </c>
       <c r="F189">
         <v>-1</v>
       </c>
       <c r="G189">
-        <v>0.005965271887652209</v>
+        <v>0.00612433332520537</v>
       </c>
       <c r="H189">
-        <v>0.005743483142628936</v>
+        <v>0.005785475787439216</v>
       </c>
       <c r="I189">
-        <v>0.1582112549767269</v>
+        <v>0.2011424622338467</v>
       </c>
       <c r="J189">
-        <v>0.7947186255818296</v>
+        <v>0.8607192220769168</v>
       </c>
       <c r="K189">
         <v>2.41</v>
@@ -10304,16 +10310,16 @@
         <v>4.05</v>
       </c>
       <c r="M189">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N189">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O189">
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>157</v>
+        <v>26</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10324,28 +10330,28 @@
         <v>36</v>
       </c>
       <c r="C190">
-        <v>2.126802703854744</v>
+        <v>1.955884214730955</v>
       </c>
       <c r="D190" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E190">
-        <v>1.968722990927695</v>
+        <v>1.755398431669347</v>
       </c>
       <c r="F190">
         <v>-1</v>
       </c>
       <c r="G190">
-        <v>0.005973197296145255</v>
+        <v>0.006144115785269044</v>
       </c>
       <c r="H190">
-        <v>0.005751277009072305</v>
+        <v>0.005804601568330653</v>
       </c>
       <c r="I190">
-        <v>0.1580797129270497</v>
+        <v>0.2004857830616085</v>
       </c>
       <c r="J190">
-        <v>0.7980071768237574</v>
+        <v>0.8689277117298939</v>
       </c>
       <c r="K190">
         <v>2.41</v>
@@ -10354,16 +10360,16 @@
         <v>4.05</v>
       </c>
       <c r="M190">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N190">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O190">
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10374,28 +10380,28 @@
         <v>36</v>
       </c>
       <c r="C191">
-        <v>2.118150939933342</v>
+        <v>1.938792565740484</v>
       </c>
       <c r="D191" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E191">
-        <v>1.960214824747726</v>
+        <v>1.738874140321713</v>
       </c>
       <c r="F191">
         <v>-1</v>
       </c>
       <c r="G191">
-        <v>0.005981849060066658</v>
+        <v>0.006161207434259517</v>
       </c>
       <c r="H191">
-        <v>0.005759785175252274</v>
+        <v>0.005821125859678287</v>
       </c>
       <c r="I191">
-        <v>0.1579361151856156</v>
+        <v>0.1999184254187711</v>
       </c>
       <c r="J191">
-        <v>0.8015971203596091</v>
+        <v>0.8760196822653594</v>
       </c>
       <c r="K191">
         <v>2.41</v>
@@ -10404,16 +10410,16 @@
         <v>4.05</v>
       </c>
       <c r="M191">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N191">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O191">
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10424,28 +10430,28 @@
         <v>36</v>
       </c>
       <c r="C192">
-        <v>2.102390273794673</v>
+        <v>1.907679309834471</v>
       </c>
       <c r="D192" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E192">
-        <v>1.944715746428786</v>
+        <v>1.708793689591003</v>
       </c>
       <c r="F192">
         <v>-1</v>
       </c>
       <c r="G192">
-        <v>0.005997609726205327</v>
+        <v>0.006192320690165529</v>
       </c>
       <c r="H192">
-        <v>0.005775284253571213</v>
+        <v>0.005851206310408996</v>
       </c>
       <c r="I192">
-        <v>0.1576745273658866</v>
+        <v>0.1988856202434679</v>
       </c>
       <c r="J192">
-        <v>0.8081368158528327</v>
+        <v>0.8889297469566507</v>
       </c>
       <c r="K192">
         <v>2.41</v>
@@ -10454,16 +10460,16 @@
         <v>4.05</v>
       </c>
       <c r="M192">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N192">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O192">
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>25</v>
+        <v>163</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10474,28 +10480,28 @@
         <v>36</v>
       </c>
       <c r="C193">
-        <v>2.068262994068838</v>
+        <v>1.884046836214932</v>
       </c>
       <c r="D193" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E193">
-        <v>1.911154894582218</v>
+        <v>1.685945696423565</v>
       </c>
       <c r="F193">
         <v>-1</v>
       </c>
       <c r="G193">
-        <v>0.006031737005931162</v>
+        <v>0.006215953163785068</v>
       </c>
       <c r="H193">
-        <v>0.005808845105417781</v>
+        <v>0.005874054303576434</v>
       </c>
       <c r="I193">
-        <v>0.1571080994866194</v>
+        <v>0.1981011397913668</v>
       </c>
       <c r="J193">
-        <v>0.8222975128345069</v>
+        <v>0.8987357526079118</v>
       </c>
       <c r="K193">
         <v>2.41</v>
@@ -10504,16 +10510,16 @@
         <v>4.05</v>
       </c>
       <c r="M193">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="N193">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="O193">
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10524,28 +10530,28 @@
         <v>36</v>
       </c>
       <c r="C194">
-        <v>2.026595514500883</v>
+        <v>1.866414391842988</v>
       </c>
       <c r="D194" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E194">
-        <v>1.870178991438628</v>
+        <v>1.712656476625677</v>
       </c>
       <c r="F194">
         <v>-1</v>
       </c>
       <c r="G194">
-        <v>0.006073404485499117</v>
+        <v>0.006233585608157012</v>
       </c>
       <c r="H194">
-        <v>0.005849821008561373</v>
+        <v>0.006007343523374323</v>
       </c>
       <c r="I194">
-        <v>0.1564165230622554</v>
+        <v>0.153757915217311</v>
       </c>
       <c r="J194">
-        <v>0.8395869234436169</v>
+        <v>0.906052119567225</v>
       </c>
       <c r="K194">
         <v>2.41</v>
@@ -10563,7 +10569,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>159</v>
+        <v>27</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10574,28 +10580,28 @@
         <v>36</v>
       </c>
       <c r="C195">
-        <v>2.00904612221926</v>
+        <v>1.846516388844341</v>
       </c>
       <c r="D195" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E195">
-        <v>1.852920875377446</v>
+        <v>1.693088730938211</v>
       </c>
       <c r="F195">
         <v>-1</v>
       </c>
       <c r="G195">
-        <v>0.006090953877780739</v>
+        <v>0.006253483611155659</v>
       </c>
       <c r="H195">
-        <v>0.005867079124622553</v>
+        <v>0.006026911269061789</v>
       </c>
       <c r="I195">
-        <v>0.1561252468418135</v>
+        <v>0.1534276579061298</v>
       </c>
       <c r="J195">
-        <v>0.846868828954664</v>
+        <v>0.9143085523467465</v>
       </c>
       <c r="K195">
         <v>2.41</v>
@@ -10613,7 +10619,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10624,28 +10630,28 @@
         <v>36</v>
       </c>
       <c r="C196">
-        <v>1.99410787626086</v>
+        <v>1.830119753165329</v>
       </c>
       <c r="D196" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E196">
-        <v>1.838230567111302</v>
+        <v>1.67696423858997</v>
       </c>
       <c r="F196">
         <v>-1</v>
       </c>
       <c r="G196">
-        <v>0.00610589212373914</v>
+        <v>0.006269880246834671</v>
       </c>
       <c r="H196">
-        <v>0.005881769432888697</v>
+        <v>0.00604303576141003</v>
       </c>
       <c r="I196">
-        <v>0.1558773091495578</v>
+        <v>0.1531555145753583</v>
       </c>
       <c r="J196">
-        <v>0.8530672712610541</v>
+        <v>0.9211121356160461</v>
       </c>
       <c r="K196">
         <v>2.41</v>
@@ -10663,357 +10669,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="197" spans="1:16">
-      <c r="A197" s="1">
-        <v>0</v>
-      </c>
-      <c r="B197" t="s">
-        <v>36</v>
-      </c>
-      <c r="C197">
-        <v>1.97566667479463</v>
-      </c>
-      <c r="D197" t="s">
-        <v>56</v>
-      </c>
-      <c r="E197">
-        <v>1.820095443677707</v>
-      </c>
-      <c r="F197">
-        <v>-1</v>
-      </c>
-      <c r="G197">
-        <v>0.00612433332520537</v>
-      </c>
-      <c r="H197">
-        <v>0.005899904556322293</v>
-      </c>
-      <c r="I197">
-        <v>0.1555712311169231</v>
-      </c>
-      <c r="J197">
-        <v>0.8607192220769168</v>
-      </c>
-      <c r="K197">
-        <v>2.41</v>
-      </c>
-      <c r="L197">
-        <v>4.05</v>
-      </c>
-      <c r="M197">
-        <v>2.37</v>
-      </c>
-      <c r="N197">
-        <v>3.86</v>
-      </c>
-      <c r="O197">
-        <v>1</v>
-      </c>
-      <c r="P197" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="198" spans="1:16">
-      <c r="A198" s="1">
-        <v>0</v>
-      </c>
-      <c r="B198" t="s">
-        <v>36</v>
-      </c>
-      <c r="C198">
-        <v>1.955884214730955</v>
-      </c>
-      <c r="D198" t="s">
-        <v>56</v>
-      </c>
-      <c r="E198">
-        <v>1.800641323200151</v>
-      </c>
-      <c r="F198">
-        <v>-1</v>
-      </c>
-      <c r="G198">
-        <v>0.006144115785269044</v>
-      </c>
-      <c r="H198">
-        <v>0.005919358676799849</v>
-      </c>
-      <c r="I198">
-        <v>0.1552428915308042</v>
-      </c>
-      <c r="J198">
-        <v>0.8689277117298939</v>
-      </c>
-      <c r="K198">
-        <v>2.41</v>
-      </c>
-      <c r="L198">
-        <v>4.05</v>
-      </c>
-      <c r="M198">
-        <v>2.37</v>
-      </c>
-      <c r="N198">
-        <v>3.86</v>
-      </c>
-      <c r="O198">
-        <v>1</v>
-      </c>
-      <c r="P198" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="199" spans="1:16">
-      <c r="A199" s="1">
-        <v>0</v>
-      </c>
-      <c r="B199" t="s">
-        <v>36</v>
-      </c>
-      <c r="C199">
-        <v>1.938792565740484</v>
-      </c>
-      <c r="D199" t="s">
-        <v>56</v>
-      </c>
-      <c r="E199">
-        <v>1.783833353031098</v>
-      </c>
-      <c r="F199">
-        <v>-1</v>
-      </c>
-      <c r="G199">
-        <v>0.006161207434259517</v>
-      </c>
-      <c r="H199">
-        <v>0.005936166646968902</v>
-      </c>
-      <c r="I199">
-        <v>0.1549592127093855</v>
-      </c>
-      <c r="J199">
-        <v>0.8760196822653594</v>
-      </c>
-      <c r="K199">
-        <v>2.41</v>
-      </c>
-      <c r="L199">
-        <v>4.05</v>
-      </c>
-      <c r="M199">
-        <v>2.37</v>
-      </c>
-      <c r="N199">
-        <v>3.86</v>
-      </c>
-      <c r="O199">
-        <v>1</v>
-      </c>
-      <c r="P199" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="200" spans="1:16">
-      <c r="A200" s="1">
-        <v>0</v>
-      </c>
-      <c r="B200" t="s">
-        <v>36</v>
-      </c>
-      <c r="C200">
-        <v>1.907679309834471</v>
-      </c>
-      <c r="D200" t="s">
-        <v>56</v>
-      </c>
-      <c r="E200">
-        <v>1.753236499712738</v>
-      </c>
-      <c r="F200">
-        <v>-1</v>
-      </c>
-      <c r="G200">
-        <v>0.006192320690165529</v>
-      </c>
-      <c r="H200">
-        <v>0.005966763500287263</v>
-      </c>
-      <c r="I200">
-        <v>0.1544428101217337</v>
-      </c>
-      <c r="J200">
-        <v>0.8889297469566507</v>
-      </c>
-      <c r="K200">
-        <v>2.41</v>
-      </c>
-      <c r="L200">
-        <v>4.05</v>
-      </c>
-      <c r="M200">
-        <v>2.37</v>
-      </c>
-      <c r="N200">
-        <v>3.86</v>
-      </c>
-      <c r="O200">
-        <v>1</v>
-      </c>
-      <c r="P200" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="201" spans="1:16">
-      <c r="A201" s="1">
-        <v>0</v>
-      </c>
-      <c r="B201" t="s">
-        <v>36</v>
-      </c>
-      <c r="C201">
-        <v>1.884046836214932</v>
-      </c>
-      <c r="D201" t="s">
-        <v>56</v>
-      </c>
-      <c r="E201">
-        <v>1.729996266319249</v>
-      </c>
-      <c r="F201">
-        <v>-1</v>
-      </c>
-      <c r="G201">
-        <v>0.006215953163785068</v>
-      </c>
-      <c r="H201">
-        <v>0.005990003733680751</v>
-      </c>
-      <c r="I201">
-        <v>0.1540505698956833</v>
-      </c>
-      <c r="J201">
-        <v>0.8987357526079118</v>
-      </c>
-      <c r="K201">
-        <v>2.41</v>
-      </c>
-      <c r="L201">
-        <v>4.05</v>
-      </c>
-      <c r="M201">
-        <v>2.37</v>
-      </c>
-      <c r="N201">
-        <v>3.86</v>
-      </c>
-      <c r="O201">
-        <v>1</v>
-      </c>
-      <c r="P201" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="202" spans="1:16">
-      <c r="A202" s="1">
-        <v>0</v>
-      </c>
-      <c r="B202" t="s">
-        <v>36</v>
-      </c>
-      <c r="C202">
-        <v>1.866414391842988</v>
-      </c>
-      <c r="D202" t="s">
-        <v>56</v>
-      </c>
-      <c r="E202">
-        <v>1.712656476625677</v>
-      </c>
-      <c r="F202">
-        <v>-1</v>
-      </c>
-      <c r="G202">
-        <v>0.006233585608157012</v>
-      </c>
-      <c r="H202">
-        <v>0.006007343523374323</v>
-      </c>
-      <c r="I202">
-        <v>0.153757915217311</v>
-      </c>
-      <c r="J202">
-        <v>0.906052119567225</v>
-      </c>
-      <c r="K202">
-        <v>2.41</v>
-      </c>
-      <c r="L202">
-        <v>4.05</v>
-      </c>
-      <c r="M202">
-        <v>2.37</v>
-      </c>
-      <c r="N202">
-        <v>3.86</v>
-      </c>
-      <c r="O202">
-        <v>1</v>
-      </c>
-      <c r="P202" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="203" spans="1:16">
-      <c r="A203" s="1">
-        <v>0</v>
-      </c>
-      <c r="B203" t="s">
-        <v>36</v>
-      </c>
-      <c r="C203">
-        <v>1.846516388844341</v>
-      </c>
-      <c r="D203" t="s">
-        <v>56</v>
-      </c>
-      <c r="E203">
-        <v>1.693088730938211</v>
-      </c>
-      <c r="F203">
-        <v>-1</v>
-      </c>
-      <c r="G203">
-        <v>0.006253483611155659</v>
-      </c>
-      <c r="H203">
-        <v>0.006026911269061789</v>
-      </c>
-      <c r="I203">
-        <v>0.1534276579061298</v>
-      </c>
-      <c r="J203">
-        <v>0.9143085523467465</v>
-      </c>
-      <c r="K203">
-        <v>2.41</v>
-      </c>
-      <c r="L203">
-        <v>4.05</v>
-      </c>
-      <c r="M203">
-        <v>2.37</v>
-      </c>
-      <c r="N203">
-        <v>3.86</v>
-      </c>
-      <c r="O203">
-        <v>1</v>
-      </c>
-      <c r="P203" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01618-601618.xlsx
+++ b/s60_signal/position-01618-601618.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="161">
   <si>
     <t>trade_time</t>
   </si>
@@ -115,12 +115,12 @@
     <t>2021-07-26</t>
   </si>
   <si>
+    <t>2021-01-13</t>
+  </si>
+  <si>
     <t>2021-01-15</t>
   </si>
   <si>
-    <t>2021-01-13</t>
-  </si>
-  <si>
     <t>2021-02-26</t>
   </si>
   <si>
@@ -181,21 +181,21 @@
     <t>2021-03-12</t>
   </si>
   <si>
-    <t>2021-01-29</t>
-  </si>
-  <si>
     <t>2021-02-03</t>
   </si>
   <si>
+    <t>2021-08-24</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>2021-03-09</t>
+  </si>
+  <si>
     <t>2021-08-23</t>
   </si>
   <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>2021-03-09</t>
-  </si>
-  <si>
     <t>2021-08-19</t>
   </si>
   <si>
@@ -460,21 +460,6 @@
     <t>2021-06-10</t>
   </si>
   <si>
-    <t>2021-06-11</t>
-  </si>
-  <si>
-    <t>2021-06-15</t>
-  </si>
-  <si>
-    <t>2021-06-16</t>
-  </si>
-  <si>
-    <t>2021-06-17</t>
-  </si>
-  <si>
-    <t>2021-06-18</t>
-  </si>
-  <si>
     <t>2021-07-09</t>
   </si>
   <si>
@@ -512,9 +497,6 @@
   </si>
   <si>
     <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
   </si>
 </sst>
 </file>
@@ -872,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P196"/>
+  <dimension ref="A1:P175"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -3827,43 +3809,43 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C60">
-        <v>1.949614977812812</v>
+        <v>2.009416633049714</v>
       </c>
       <c r="D60" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E60">
-        <v>1.673598643538204</v>
+        <v>2.121437634259925</v>
       </c>
       <c r="F60">
         <v>-1</v>
       </c>
       <c r="G60">
-        <v>0.004590385022187188</v>
+        <v>0.006010583366950286</v>
       </c>
       <c r="H60">
-        <v>0.004426401356461797</v>
+        <v>0.005978562365740075</v>
       </c>
       <c r="I60">
-        <v>0.2760163342746083</v>
+        <v>-0.1120210012102105</v>
       </c>
       <c r="J60">
         <v>0.8002333467801142</v>
       </c>
       <c r="K60">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="L60">
-        <v>3.27</v>
+        <v>4.01</v>
       </c>
       <c r="M60">
-        <v>1.72</v>
+        <v>2.41</v>
       </c>
       <c r="N60">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="O60">
         <v>1</v>
@@ -3877,10 +3859,10 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C61">
-        <v>2.009416633049714</v>
+        <v>1.989451635066732</v>
       </c>
       <c r="D61" t="s">
         <v>36</v>
@@ -3892,22 +3874,22 @@
         <v>-1</v>
       </c>
       <c r="G61">
-        <v>0.006010583366950286</v>
+        <v>0.005750548364933269</v>
       </c>
       <c r="H61">
         <v>0.005978562365740075</v>
       </c>
       <c r="I61">
-        <v>-0.1120210012102105</v>
+        <v>-0.1319859991931931</v>
       </c>
       <c r="J61">
         <v>0.8002333467801142</v>
       </c>
       <c r="K61">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L61">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M61">
         <v>2.41</v>
@@ -3927,10 +3909,10 @@
         <v>2</v>
       </c>
       <c r="B62" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C62">
-        <v>1.989451635066732</v>
+        <v>1.975456302002334</v>
       </c>
       <c r="D62" t="s">
         <v>36</v>
@@ -3942,22 +3924,22 @@
         <v>-1</v>
       </c>
       <c r="G62">
-        <v>0.005750548364933269</v>
+        <v>0.005704543697997666</v>
       </c>
       <c r="H62">
         <v>0.005978562365740075</v>
       </c>
       <c r="I62">
-        <v>-0.1319859991931931</v>
+        <v>-0.1459813322575909</v>
       </c>
       <c r="J62">
         <v>0.8002333467801142</v>
       </c>
       <c r="K62">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="L62">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="M62">
         <v>2.41</v>
@@ -3974,63 +3956,63 @@
     </row>
     <row r="63" spans="1:16">
       <c r="A63" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C63">
-        <v>1.975456302002334</v>
+        <v>1.858458903856472</v>
       </c>
       <c r="D63" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E63">
-        <v>2.121437634259925</v>
+        <v>1.58899958462614</v>
       </c>
       <c r="F63">
         <v>-1</v>
       </c>
       <c r="G63">
-        <v>0.005704543697997666</v>
+        <v>0.004661541096143528</v>
       </c>
       <c r="H63">
-        <v>0.005978562365740075</v>
+        <v>0.004511000415373859</v>
       </c>
       <c r="I63">
-        <v>-0.1459813322575909</v>
+        <v>0.2694593192303316</v>
       </c>
       <c r="J63">
-        <v>0.8002333467801142</v>
+        <v>0.8494188461475927</v>
       </c>
       <c r="K63">
-        <v>2.33</v>
+        <v>1.65</v>
       </c>
       <c r="L63">
-        <v>3.84</v>
+        <v>3.26</v>
       </c>
       <c r="M63">
-        <v>2.41</v>
+        <v>1.72</v>
       </c>
       <c r="N63">
-        <v>4.05</v>
+        <v>3.05</v>
       </c>
       <c r="O63">
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B64" t="s">
         <v>34</v>
       </c>
       <c r="C64">
-        <v>1.858458903856472</v>
+        <v>1.868458903856472</v>
       </c>
       <c r="D64" t="s">
         <v>52</v>
@@ -4042,13 +4024,13 @@
         <v>-1</v>
       </c>
       <c r="G64">
-        <v>0.004661541096143528</v>
+        <v>0.004671541096143528</v>
       </c>
       <c r="H64">
         <v>0.004511000415373859</v>
       </c>
       <c r="I64">
-        <v>0.2694593192303316</v>
+        <v>0.2794593192303318</v>
       </c>
       <c r="J64">
         <v>0.8494188461475927</v>
@@ -4057,7 +4039,7 @@
         <v>1.65</v>
       </c>
       <c r="L64">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="M64">
         <v>1.72</v>
@@ -4074,46 +4056,46 @@
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C65">
-        <v>1.868458903856472</v>
+        <v>1.886452884631018</v>
       </c>
       <c r="D65" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E65">
-        <v>1.58899958462614</v>
+        <v>2.002900580784301</v>
       </c>
       <c r="F65">
         <v>-1</v>
       </c>
       <c r="G65">
-        <v>0.004671541096143528</v>
+        <v>0.006133547115368982</v>
       </c>
       <c r="H65">
-        <v>0.004511000415373859</v>
+        <v>0.006097099419215699</v>
       </c>
       <c r="I65">
-        <v>0.2794593192303318</v>
+        <v>-0.1164476961532834</v>
       </c>
       <c r="J65">
         <v>0.8494188461475927</v>
       </c>
       <c r="K65">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="L65">
-        <v>3.27</v>
+        <v>4.01</v>
       </c>
       <c r="M65">
-        <v>1.72</v>
+        <v>2.41</v>
       </c>
       <c r="N65">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="O65">
         <v>1</v>
@@ -4124,13 +4106,13 @@
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B66" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C66">
-        <v>1.886452884631018</v>
+        <v>1.873865711553157</v>
       </c>
       <c r="D66" t="s">
         <v>36</v>
@@ -4142,22 +4124,22 @@
         <v>-1</v>
       </c>
       <c r="G66">
-        <v>0.006133547115368982</v>
+        <v>0.005866134288446843</v>
       </c>
       <c r="H66">
         <v>0.006097099419215699</v>
       </c>
       <c r="I66">
-        <v>-0.1164476961532834</v>
+        <v>-0.1290348692311443</v>
       </c>
       <c r="J66">
         <v>0.8494188461475927</v>
       </c>
       <c r="K66">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L66">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M66">
         <v>2.41</v>
@@ -4174,13 +4156,13 @@
     </row>
     <row r="67" spans="1:16">
       <c r="A67" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B67" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C67">
-        <v>1.873865711553157</v>
+        <v>1.860854088476109</v>
       </c>
       <c r="D67" t="s">
         <v>36</v>
@@ -4192,22 +4174,22 @@
         <v>-1</v>
       </c>
       <c r="G67">
-        <v>0.005866134288446843</v>
+        <v>0.005819145911523891</v>
       </c>
       <c r="H67">
         <v>0.006097099419215699</v>
       </c>
       <c r="I67">
-        <v>-0.1290348692311443</v>
+        <v>-0.1420464923081926</v>
       </c>
       <c r="J67">
         <v>0.8494188461475927</v>
       </c>
       <c r="K67">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="L67">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="M67">
         <v>2.41</v>
@@ -4224,96 +4206,96 @@
     </row>
     <row r="68" spans="1:16">
       <c r="A68" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C68">
-        <v>1.860854088476109</v>
+        <v>1.778043160662217</v>
       </c>
       <c r="D68" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="E68">
-        <v>2.002900580784301</v>
+        <v>1.4819325002745</v>
       </c>
       <c r="F68">
         <v>-1</v>
       </c>
       <c r="G68">
-        <v>0.005819145911523891</v>
+        <v>0.004741956839337784</v>
       </c>
       <c r="H68">
-        <v>0.006097099419215699</v>
+        <v>0.004338067499725501</v>
       </c>
       <c r="I68">
-        <v>-0.1420464923081926</v>
+        <v>0.2961106603877166</v>
       </c>
       <c r="J68">
-        <v>0.8494188461475927</v>
+        <v>0.898155660204717</v>
       </c>
       <c r="K68">
-        <v>2.33</v>
+        <v>1.65</v>
       </c>
       <c r="L68">
-        <v>3.84</v>
+        <v>3.26</v>
       </c>
       <c r="M68">
-        <v>2.41</v>
+        <v>1.59</v>
       </c>
       <c r="N68">
-        <v>4.05</v>
+        <v>2.91</v>
       </c>
       <c r="O68">
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B69" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C69">
-        <v>1.778043160662217</v>
+        <v>1.764610849488207</v>
       </c>
       <c r="D69" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E69">
-        <v>1.4819325002745</v>
+        <v>1.885444858906632</v>
       </c>
       <c r="F69">
         <v>-1</v>
       </c>
       <c r="G69">
-        <v>0.004741956839337784</v>
+        <v>0.006255389150511792</v>
       </c>
       <c r="H69">
-        <v>0.004338067499725501</v>
+        <v>0.006214555141093368</v>
       </c>
       <c r="I69">
-        <v>0.2961106603877166</v>
+        <v>-0.1208340094184246</v>
       </c>
       <c r="J69">
         <v>0.898155660204717</v>
       </c>
       <c r="K69">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="L69">
-        <v>3.26</v>
+        <v>4.01</v>
       </c>
       <c r="M69">
-        <v>1.59</v>
+        <v>2.41</v>
       </c>
       <c r="N69">
-        <v>2.91</v>
+        <v>4.05</v>
       </c>
       <c r="O69">
         <v>1</v>
@@ -4324,46 +4306,46 @@
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B70" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C70">
-        <v>1.253223538131198</v>
+        <v>1.759334198518915</v>
       </c>
       <c r="D70" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="E70">
-        <v>1.508412028621273</v>
+        <v>1.885444858906632</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G70">
-        <v>0.005366776461868803</v>
+        <v>0.005980665801481085</v>
       </c>
       <c r="H70">
-        <v>0.004831587971378727</v>
+        <v>0.006214555141093368</v>
       </c>
       <c r="I70">
-        <v>0.2551884904900752</v>
+        <v>-0.1261106603877167</v>
       </c>
       <c r="J70">
         <v>0.898155660204717</v>
       </c>
       <c r="K70">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="L70">
-        <v>3.31</v>
+        <v>3.87</v>
       </c>
       <c r="M70">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="N70">
-        <v>3.17</v>
+        <v>4.05</v>
       </c>
       <c r="O70">
         <v>1</v>
@@ -4374,13 +4356,13 @@
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B71" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C71">
-        <v>1.764610849488207</v>
+        <v>1.747297311723009</v>
       </c>
       <c r="D71" t="s">
         <v>36</v>
@@ -4392,22 +4374,22 @@
         <v>-1</v>
       </c>
       <c r="G71">
-        <v>0.006255389150511792</v>
+        <v>0.00593270268827699</v>
       </c>
       <c r="H71">
         <v>0.006214555141093368</v>
       </c>
       <c r="I71">
-        <v>-0.1208340094184246</v>
+        <v>-0.1381475471836224</v>
       </c>
       <c r="J71">
         <v>0.898155660204717</v>
       </c>
       <c r="K71">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="L71">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="M71">
         <v>2.41</v>
@@ -4424,146 +4406,146 @@
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C72">
-        <v>1.759334198518915</v>
+        <v>1.698438247560837</v>
       </c>
       <c r="D72" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="E72">
-        <v>1.885444858906632</v>
+        <v>1.405222311285897</v>
       </c>
       <c r="F72">
         <v>-1</v>
       </c>
       <c r="G72">
-        <v>0.005980665801481085</v>
+        <v>0.004821561752439162</v>
       </c>
       <c r="H72">
-        <v>0.006214555141093368</v>
+        <v>0.004414777688714104</v>
       </c>
       <c r="I72">
-        <v>-0.1261106603877167</v>
+        <v>0.2932159362749394</v>
       </c>
       <c r="J72">
-        <v>0.898155660204717</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K72">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="L72">
-        <v>3.87</v>
+        <v>3.26</v>
       </c>
       <c r="M72">
-        <v>2.41</v>
+        <v>1.59</v>
       </c>
       <c r="N72">
-        <v>4.05</v>
+        <v>2.91</v>
       </c>
       <c r="O72">
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B73" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C73">
-        <v>1.747297311723009</v>
+        <v>1.142741567826858</v>
       </c>
       <c r="D73" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="E73">
-        <v>1.885444858906632</v>
+        <v>1.419158035143968</v>
       </c>
       <c r="F73">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>0.00593270268827699</v>
+        <v>0.005477258432173141</v>
       </c>
       <c r="H73">
-        <v>0.006214555141093368</v>
+        <v>0.004920841964856031</v>
       </c>
       <c r="I73">
-        <v>-0.1381475471836224</v>
+        <v>0.2764164673171099</v>
       </c>
       <c r="J73">
-        <v>0.898155660204717</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K73">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="L73">
-        <v>3.84</v>
+        <v>3.31</v>
       </c>
       <c r="M73">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="N73">
-        <v>4.05</v>
+        <v>3.17</v>
       </c>
       <c r="O73">
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="74" spans="1:16">
       <c r="A74" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B74" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C74">
-        <v>1.698438247560837</v>
+        <v>1.645957504101798</v>
       </c>
       <c r="D74" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E74">
-        <v>1.400398406873488</v>
+        <v>1.769173440376737</v>
       </c>
       <c r="F74">
         <v>-1</v>
       </c>
       <c r="G74">
-        <v>0.004821561752439162</v>
+        <v>0.006094042495898203</v>
       </c>
       <c r="H74">
-        <v>0.004239601593126512</v>
+        <v>0.006330826559623264</v>
       </c>
       <c r="I74">
-        <v>0.2980398406873488</v>
+        <v>-0.123215936274939</v>
       </c>
       <c r="J74">
         <v>0.9464010620843414</v>
       </c>
       <c r="K74">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="L74">
-        <v>3.26</v>
+        <v>3.87</v>
       </c>
       <c r="M74">
-        <v>1.5</v>
+        <v>2.41</v>
       </c>
       <c r="N74">
-        <v>2.82</v>
+        <v>4.05</v>
       </c>
       <c r="O74">
         <v>1</v>
@@ -4574,152 +4556,152 @@
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C75">
-        <v>1.142741567826858</v>
+        <v>1.613410205419267</v>
       </c>
       <c r="D75" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E75">
-        <v>1.419158035143968</v>
+        <v>1.293162190479684</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G75">
-        <v>0.005477258432173141</v>
+        <v>0.004906589794580732</v>
       </c>
       <c r="H75">
-        <v>0.004920841964856031</v>
+        <v>0.004346837809520315</v>
       </c>
       <c r="I75">
-        <v>0.2764164673171099</v>
+        <v>0.320248014939583</v>
       </c>
       <c r="J75">
-        <v>0.9464010620843414</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K75">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="L75">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="M75">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="N75">
-        <v>3.17</v>
+        <v>2.82</v>
       </c>
       <c r="O75">
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B76" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C76">
-        <v>1.643997344789146</v>
+        <v>1.02473295176371</v>
       </c>
       <c r="D76" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="E76">
-        <v>1.769173440376737</v>
+        <v>1.323823563651905</v>
       </c>
       <c r="F76">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G76">
-        <v>0.006376002655210854</v>
+        <v>0.005595267048236289</v>
       </c>
       <c r="H76">
-        <v>0.006330826559623264</v>
+        <v>0.005016176436348095</v>
       </c>
       <c r="I76">
-        <v>-0.1251760955875905</v>
+        <v>0.2990906118881951</v>
       </c>
       <c r="J76">
-        <v>0.9464010620843414</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K76">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="L76">
-        <v>4.01</v>
+        <v>3.31</v>
       </c>
       <c r="M76">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="N76">
-        <v>4.05</v>
+        <v>3.17</v>
       </c>
       <c r="O76">
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B77" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C77">
-        <v>1.645957504101798</v>
+        <v>1.644980966703293</v>
       </c>
       <c r="D77" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="E77">
-        <v>1.769173440376737</v>
+        <v>1.574980966703293</v>
       </c>
       <c r="F77">
         <v>-1</v>
       </c>
       <c r="G77">
-        <v>0.006094042495898203</v>
+        <v>0.006455019033296707</v>
       </c>
       <c r="H77">
-        <v>0.006330826559623264</v>
+        <v>0.006385019033296708</v>
       </c>
       <c r="I77">
-        <v>-0.123215936274939</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J77">
-        <v>0.9464010620843414</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K77">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="L77">
-        <v>3.87</v>
+        <v>4.05</v>
       </c>
       <c r="M77">
         <v>2.41</v>
       </c>
       <c r="N77">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="O77">
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4727,31 +4709,31 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C78">
-        <v>1.613410205419267</v>
+        <v>1.563582758846789</v>
       </c>
       <c r="D78" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E78">
-        <v>1.293162190479684</v>
+        <v>1.246958558203386</v>
       </c>
       <c r="F78">
         <v>-1</v>
       </c>
       <c r="G78">
-        <v>0.004906589794580732</v>
+        <v>0.004956417241153211</v>
       </c>
       <c r="H78">
-        <v>0.004346837809520315</v>
+        <v>0.004393041441796613</v>
       </c>
       <c r="I78">
-        <v>0.320248014939583</v>
+        <v>0.3166242006434028</v>
       </c>
       <c r="J78">
-        <v>0.9979332088368078</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K78">
         <v>1.65</v>
@@ -4769,7 +4751,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -4780,28 +4762,28 @@
         <v>35</v>
       </c>
       <c r="C79">
-        <v>1.02473295176371</v>
+        <v>0.9555784956116042</v>
       </c>
       <c r="D79" t="s">
         <v>54</v>
       </c>
       <c r="E79">
-        <v>1.323823563651905</v>
+        <v>1.267956426585794</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="G79">
-        <v>0.005595267048236289</v>
+        <v>0.005664421504388396</v>
       </c>
       <c r="H79">
-        <v>0.005016176436348095</v>
+        <v>0.005072043573414206</v>
       </c>
       <c r="I79">
-        <v>0.2990906118881951</v>
+        <v>0.3123779309741896</v>
       </c>
       <c r="J79">
-        <v>0.9979332088368078</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K79">
         <v>2.29</v>
@@ -4819,7 +4801,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -4830,28 +4812,28 @@
         <v>36</v>
       </c>
       <c r="C80">
-        <v>1.644980966703293</v>
+        <v>1.572202696255007</v>
       </c>
       <c r="D80" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E80">
-        <v>1.454815623410238</v>
+        <v>1.502202696255007</v>
       </c>
       <c r="F80">
         <v>-1</v>
       </c>
       <c r="G80">
-        <v>0.006455019033296707</v>
+        <v>0.006527797303744994</v>
       </c>
       <c r="H80">
-        <v>0.006105184376589762</v>
+        <v>0.006457797303744993</v>
       </c>
       <c r="I80">
-        <v>0.1901653432930552</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J80">
-        <v>0.9979332088368078</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K80">
         <v>2.41</v>
@@ -4860,16 +4842,16 @@
         <v>4.05</v>
       </c>
       <c r="M80">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N80">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O80">
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -4877,31 +4859,31 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C81">
-        <v>1.563582758846789</v>
+        <v>1.51276870292658</v>
       </c>
       <c r="D81" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E81">
-        <v>1.246958558203386</v>
+        <v>1.15219719233976</v>
       </c>
       <c r="F81">
         <v>-1</v>
       </c>
       <c r="G81">
-        <v>0.004956417241153211</v>
+        <v>0.00500723129707342</v>
       </c>
       <c r="H81">
-        <v>0.004393041441796613</v>
+        <v>0.004307802807660239</v>
       </c>
       <c r="I81">
-        <v>0.3166242006434028</v>
+        <v>0.3605715105868199</v>
       </c>
       <c r="J81">
-        <v>1.028131661304976</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K81">
         <v>1.65</v>
@@ -4910,16 +4892,16 @@
         <v>3.26</v>
       </c>
       <c r="M81">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="N81">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="O81">
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -4927,37 +4909,37 @@
         <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C82">
-        <v>0.9555784956116042</v>
+        <v>0.95505474527386</v>
       </c>
       <c r="D82" t="s">
         <v>54</v>
       </c>
       <c r="E82">
-        <v>1.267956426585794</v>
+        <v>1.210983091160105</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82">
-        <v>0.005664421504388396</v>
+        <v>0.00580494525472614</v>
       </c>
       <c r="H82">
-        <v>0.005072043573414206</v>
+        <v>0.005129016908839895</v>
       </c>
       <c r="I82">
-        <v>0.3123779309741896</v>
+        <v>0.2559283458862451</v>
       </c>
       <c r="J82">
-        <v>1.028131661304976</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K82">
         <v>2.29</v>
       </c>
       <c r="L82">
-        <v>3.31</v>
+        <v>3.38</v>
       </c>
       <c r="M82">
         <v>1.85</v>
@@ -4969,7 +4951,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -4980,28 +4962,28 @@
         <v>36</v>
       </c>
       <c r="C83">
-        <v>1.572202696255007</v>
+        <v>1.497983378213975</v>
       </c>
       <c r="D83" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E83">
-        <v>1.384453229159405</v>
+        <v>1.427983378213975</v>
       </c>
       <c r="F83">
         <v>-1</v>
       </c>
       <c r="G83">
-        <v>0.006527797303744994</v>
+        <v>0.006602016621786024</v>
       </c>
       <c r="H83">
-        <v>0.006175546770840595</v>
+        <v>0.006532016621786025</v>
       </c>
       <c r="I83">
-        <v>0.1877494670956019</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J83">
-        <v>1.028131661304976</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K83">
         <v>2.41</v>
@@ -5010,16 +4992,16 @@
         <v>4.05</v>
       </c>
       <c r="M83">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N83">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O83">
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5027,31 +5009,31 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C84">
-        <v>1.51276870292658</v>
+        <v>1.47291752351783</v>
       </c>
       <c r="D84" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E84">
-        <v>1.15219719233976</v>
+        <v>1.116210369722162</v>
       </c>
       <c r="F84">
         <v>-1</v>
       </c>
       <c r="G84">
-        <v>0.00500723129707342</v>
+        <v>0.00504708247648217</v>
       </c>
       <c r="H84">
-        <v>0.004307802807660239</v>
+        <v>0.004343789630277838</v>
       </c>
       <c r="I84">
-        <v>0.3605715105868199</v>
+        <v>0.3567071537956681</v>
       </c>
       <c r="J84">
-        <v>1.058928058832376</v>
+        <v>1.083080288777073</v>
       </c>
       <c r="K84">
         <v>1.65</v>
@@ -5069,7 +5051,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5080,28 +5062,28 @@
         <v>37</v>
       </c>
       <c r="C85">
-        <v>0.95505474527386</v>
+        <v>0.8997461387005035</v>
       </c>
       <c r="D85" t="s">
         <v>54</v>
       </c>
       <c r="E85">
-        <v>1.210983091160105</v>
+        <v>1.166301465762415</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85">
-        <v>0.00580494525472614</v>
+        <v>0.005860253861299496</v>
       </c>
       <c r="H85">
-        <v>0.005129016908839895</v>
+        <v>0.005173698534237585</v>
       </c>
       <c r="I85">
-        <v>0.2559283458862451</v>
+        <v>0.2665553270619117</v>
       </c>
       <c r="J85">
-        <v>1.058928058832376</v>
+        <v>1.083080288777073</v>
       </c>
       <c r="K85">
         <v>2.29</v>
@@ -5119,7 +5101,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5130,28 +5112,28 @@
         <v>36</v>
       </c>
       <c r="C86">
-        <v>1.497983378213975</v>
+        <v>1.439776504047254</v>
       </c>
       <c r="D86" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E86">
-        <v>1.312697622920565</v>
+        <v>1.369776504047254</v>
       </c>
       <c r="F86">
         <v>-1</v>
       </c>
       <c r="G86">
-        <v>0.006602016621786024</v>
+        <v>0.006660223495952746</v>
       </c>
       <c r="H86">
-        <v>0.006247302377079435</v>
+        <v>0.006590223495952746</v>
       </c>
       <c r="I86">
-        <v>0.18528575529341</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J86">
-        <v>1.058928058832376</v>
+        <v>1.083080288777073</v>
       </c>
       <c r="K86">
         <v>2.41</v>
@@ -5160,16 +5142,16 @@
         <v>4.05</v>
       </c>
       <c r="M86">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N86">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O86">
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5177,31 +5159,31 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C87">
-        <v>1.47291752351783</v>
+        <v>1.473409677892745</v>
       </c>
       <c r="D87" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="E87">
-        <v>1.48291752351783</v>
+        <v>1.116654800036478</v>
       </c>
       <c r="F87">
         <v>-1</v>
       </c>
       <c r="G87">
-        <v>0.00504708247648217</v>
+        <v>0.005046590322107255</v>
       </c>
       <c r="H87">
-        <v>0.005057082476482171</v>
+        <v>0.004343345199963522</v>
       </c>
       <c r="I87">
-        <v>-0.01000000000000023</v>
+        <v>0.3567548778562661</v>
       </c>
       <c r="J87">
-        <v>1.083080288777073</v>
+        <v>1.082782013398337</v>
       </c>
       <c r="K87">
         <v>1.65</v>
@@ -5210,16 +5192,16 @@
         <v>3.26</v>
       </c>
       <c r="M87">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="N87">
-        <v>3.27</v>
+        <v>2.73</v>
       </c>
       <c r="O87">
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5230,28 +5212,28 @@
         <v>37</v>
       </c>
       <c r="C88">
-        <v>0.8997461387005035</v>
+        <v>0.9004291893178089</v>
       </c>
       <c r="D88" t="s">
         <v>54</v>
       </c>
       <c r="E88">
-        <v>1.166301465762415</v>
+        <v>1.166853275213077</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88">
-        <v>0.005860253861299496</v>
+        <v>0.005859570810682191</v>
       </c>
       <c r="H88">
-        <v>0.005173698534237585</v>
+        <v>0.005173146724786923</v>
       </c>
       <c r="I88">
-        <v>0.2665553270619117</v>
+        <v>0.2664240858952684</v>
       </c>
       <c r="J88">
-        <v>1.083080288777073</v>
+        <v>1.082782013398337</v>
       </c>
       <c r="K88">
         <v>2.29</v>
@@ -5269,7 +5251,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5280,28 +5262,28 @@
         <v>36</v>
       </c>
       <c r="C89">
-        <v>1.439776504047254</v>
+        <v>1.440495347710009</v>
       </c>
       <c r="D89" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E89">
-        <v>1.25642292714942</v>
+        <v>1.370495347710009</v>
       </c>
       <c r="F89">
         <v>-1</v>
       </c>
       <c r="G89">
-        <v>0.006660223495952746</v>
+        <v>0.006659504652289991</v>
       </c>
       <c r="H89">
-        <v>0.00630357707285058</v>
+        <v>0.006589504652289991</v>
       </c>
       <c r="I89">
-        <v>0.1833535768978343</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J89">
-        <v>1.083080288777073</v>
+        <v>1.082782013398337</v>
       </c>
       <c r="K89">
         <v>2.41</v>
@@ -5310,16 +5292,16 @@
         <v>4.05</v>
       </c>
       <c r="M89">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N89">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O89">
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5327,31 +5309,31 @@
         <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C90">
-        <v>1.473409677892745</v>
+        <v>1.472764755561722</v>
       </c>
       <c r="D90" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="E90">
-        <v>1.483409677892745</v>
+        <v>1.116072415628464</v>
       </c>
       <c r="F90">
         <v>-1</v>
       </c>
       <c r="G90">
-        <v>0.005046590322107255</v>
+        <v>0.005047235244438278</v>
       </c>
       <c r="H90">
-        <v>0.005056590322107255</v>
+        <v>0.004343927584371536</v>
       </c>
       <c r="I90">
-        <v>-0.01000000000000023</v>
+        <v>0.3566923399332578</v>
       </c>
       <c r="J90">
-        <v>1.082782013398337</v>
+        <v>1.083172875417138</v>
       </c>
       <c r="K90">
         <v>1.65</v>
@@ -5360,16 +5342,16 @@
         <v>3.26</v>
       </c>
       <c r="M90">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="N90">
-        <v>3.27</v>
+        <v>2.73</v>
       </c>
       <c r="O90">
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5380,28 +5362,28 @@
         <v>37</v>
       </c>
       <c r="C91">
-        <v>0.9004291893178089</v>
+        <v>0.8995341152947529</v>
       </c>
       <c r="D91" t="s">
         <v>54</v>
       </c>
       <c r="E91">
-        <v>1.166853275213077</v>
+        <v>1.166130180478294</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="G91">
-        <v>0.005859570810682191</v>
+        <v>0.005860465884705247</v>
       </c>
       <c r="H91">
-        <v>0.005173146724786923</v>
+        <v>0.005173869819521706</v>
       </c>
       <c r="I91">
-        <v>0.2664240858952684</v>
+        <v>0.2665960651835411</v>
       </c>
       <c r="J91">
-        <v>1.082782013398337</v>
+        <v>1.083172875417138</v>
       </c>
       <c r="K91">
         <v>2.29</v>
@@ -5419,7 +5401,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5430,28 +5412,28 @@
         <v>36</v>
       </c>
       <c r="C92">
-        <v>1.440495347710009</v>
+        <v>1.439553370244696</v>
       </c>
       <c r="D92" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E92">
-        <v>1.257117908781876</v>
+        <v>1.369553370244696</v>
       </c>
       <c r="F92">
         <v>-1</v>
       </c>
       <c r="G92">
-        <v>0.006659504652289991</v>
+        <v>0.006660446629755304</v>
       </c>
       <c r="H92">
-        <v>0.006302882091218124</v>
+        <v>0.006590446629755304</v>
       </c>
       <c r="I92">
-        <v>0.1833774389281331</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J92">
-        <v>1.082782013398337</v>
+        <v>1.083172875417138</v>
       </c>
       <c r="K92">
         <v>2.41</v>
@@ -5460,16 +5442,16 @@
         <v>4.05</v>
       </c>
       <c r="M92">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N92">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O92">
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5477,31 +5459,31 @@
         <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C93">
-        <v>1.472764755561722</v>
+        <v>1.468991674710606</v>
       </c>
       <c r="D93" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="E93">
-        <v>1.482764755561722</v>
+        <v>1.112665209284123</v>
       </c>
       <c r="F93">
         <v>-1</v>
       </c>
       <c r="G93">
-        <v>0.005047235244438278</v>
+        <v>0.005051008325289394</v>
       </c>
       <c r="H93">
-        <v>0.005057235244438278</v>
+        <v>0.004347334790715877</v>
       </c>
       <c r="I93">
-        <v>-0.01000000000000023</v>
+        <v>0.3563264654264828</v>
       </c>
       <c r="J93">
-        <v>1.083172875417138</v>
+        <v>1.085459591084481</v>
       </c>
       <c r="K93">
         <v>1.65</v>
@@ -5510,16 +5492,16 @@
         <v>3.26</v>
       </c>
       <c r="M93">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="N93">
-        <v>3.27</v>
+        <v>2.73</v>
       </c>
       <c r="O93">
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5530,28 +5512,28 @@
         <v>37</v>
       </c>
       <c r="C94">
-        <v>0.8995341152947529</v>
+        <v>0.8942975364165378</v>
       </c>
       <c r="D94" t="s">
         <v>54</v>
       </c>
       <c r="E94">
-        <v>1.166130180478294</v>
+        <v>1.161899756493709</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94">
-        <v>0.005860465884705247</v>
+        <v>0.005865702463583462</v>
       </c>
       <c r="H94">
-        <v>0.005173869819521706</v>
+        <v>0.00517810024350629</v>
       </c>
       <c r="I94">
-        <v>0.2665960651835411</v>
+        <v>0.2676022200771717</v>
       </c>
       <c r="J94">
-        <v>1.083172875417138</v>
+        <v>1.085459591084481</v>
       </c>
       <c r="K94">
         <v>2.29</v>
@@ -5569,7 +5551,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5580,28 +5562,28 @@
         <v>36</v>
       </c>
       <c r="C95">
-        <v>1.439553370244696</v>
+        <v>1.4340423854864</v>
       </c>
       <c r="D95" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E95">
-        <v>1.256207200278067</v>
+        <v>1.3640423854864</v>
       </c>
       <c r="F95">
         <v>-1</v>
       </c>
       <c r="G95">
-        <v>0.006660446629755304</v>
+        <v>0.0066659576145136</v>
       </c>
       <c r="H95">
-        <v>0.006303792799721933</v>
+        <v>0.0065959576145136</v>
       </c>
       <c r="I95">
-        <v>0.183346169966629</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J95">
-        <v>1.083172875417138</v>
+        <v>1.085459591084481</v>
       </c>
       <c r="K95">
         <v>2.41</v>
@@ -5610,16 +5592,16 @@
         <v>4.05</v>
       </c>
       <c r="M95">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N95">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O95">
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5627,31 +5609,31 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
+        <v>33</v>
+      </c>
+      <c r="C96">
+        <v>1.418256303089464</v>
+      </c>
+      <c r="D96" t="s">
         <v>34</v>
       </c>
-      <c r="C96">
-        <v>1.468991674710606</v>
-      </c>
-      <c r="D96" t="s">
-        <v>33</v>
-      </c>
       <c r="E96">
-        <v>1.478991674710606</v>
+        <v>1.428256303089464</v>
       </c>
       <c r="F96">
         <v>-1</v>
       </c>
       <c r="G96">
-        <v>0.005051008325289394</v>
+        <v>0.005101743696910536</v>
       </c>
       <c r="H96">
-        <v>0.005061008325289394</v>
+        <v>0.005111743696910536</v>
       </c>
       <c r="I96">
         <v>-0.01000000000000023</v>
       </c>
       <c r="J96">
-        <v>1.085459591084481</v>
+        <v>1.1162083011579</v>
       </c>
       <c r="K96">
         <v>1.65</v>
@@ -5669,7 +5651,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5680,28 +5662,28 @@
         <v>37</v>
       </c>
       <c r="C97">
-        <v>0.8942975364165378</v>
+        <v>0.823882990348408</v>
       </c>
       <c r="D97" t="s">
         <v>54</v>
       </c>
       <c r="E97">
-        <v>1.161899756493709</v>
+        <v>1.105014642857884</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
       <c r="G97">
-        <v>0.005865702463583462</v>
+        <v>0.005936117009651592</v>
       </c>
       <c r="H97">
-        <v>0.00517810024350629</v>
+        <v>0.005234985357142116</v>
       </c>
       <c r="I97">
-        <v>0.2676022200771717</v>
+        <v>0.281131652509476</v>
       </c>
       <c r="J97">
-        <v>1.085459591084481</v>
+        <v>1.1162083011579</v>
       </c>
       <c r="K97">
         <v>2.29</v>
@@ -5719,7 +5701,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5730,28 +5712,28 @@
         <v>36</v>
       </c>
       <c r="C98">
-        <v>1.4340423854864</v>
+        <v>1.35993799420946</v>
       </c>
       <c r="D98" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E98">
-        <v>1.250879152773158</v>
+        <v>1.28993799420946</v>
       </c>
       <c r="F98">
         <v>-1</v>
       </c>
       <c r="G98">
-        <v>0.0066659576145136</v>
+        <v>0.00674006200579054</v>
       </c>
       <c r="H98">
-        <v>0.006309120847226842</v>
+        <v>0.00667006200579054</v>
       </c>
       <c r="I98">
-        <v>0.1831632327132411</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J98">
-        <v>1.085459591084481</v>
+        <v>1.1162083011579</v>
       </c>
       <c r="K98">
         <v>2.41</v>
@@ -5760,16 +5742,16 @@
         <v>4.05</v>
       </c>
       <c r="M98">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N98">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O98">
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5780,28 +5762,28 @@
         <v>37</v>
       </c>
       <c r="C99">
-        <v>0.823882990348408</v>
+        <v>0.7552208383877499</v>
       </c>
       <c r="D99" t="s">
         <v>54</v>
       </c>
       <c r="E99">
-        <v>1.105014642857884</v>
+        <v>1.049545218784863</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
       <c r="G99">
-        <v>0.005936117009651592</v>
+        <v>0.00600477916161225</v>
       </c>
       <c r="H99">
-        <v>0.005234985357142116</v>
+        <v>0.005290454781215137</v>
       </c>
       <c r="I99">
-        <v>0.281131652509476</v>
+        <v>0.2943243803971134</v>
       </c>
       <c r="J99">
-        <v>1.1162083011579</v>
+        <v>1.146191773629804</v>
       </c>
       <c r="K99">
         <v>2.29</v>
@@ -5819,7 +5801,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -5830,28 +5812,28 @@
         <v>36</v>
       </c>
       <c r="C100">
-        <v>1.35993799420946</v>
+        <v>1.287677825552173</v>
       </c>
       <c r="D100" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E100">
-        <v>1.179234658302092</v>
+        <v>1.217677825552173</v>
       </c>
       <c r="F100">
         <v>-1</v>
       </c>
       <c r="G100">
-        <v>0.00674006200579054</v>
+        <v>0.006812322174447827</v>
       </c>
       <c r="H100">
-        <v>0.006380765341697908</v>
+        <v>0.006742322174447827</v>
       </c>
       <c r="I100">
-        <v>0.180703335907368</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J100">
-        <v>1.1162083011579</v>
+        <v>1.146191773629804</v>
       </c>
       <c r="K100">
         <v>2.41</v>
@@ -5860,16 +5842,16 @@
         <v>4.05</v>
       </c>
       <c r="M100">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N100">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O100">
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -5880,28 +5862,28 @@
         <v>37</v>
       </c>
       <c r="C101">
-        <v>0.7552208383877499</v>
+        <v>0.7164672131147527</v>
       </c>
       <c r="D101" t="s">
         <v>54</v>
       </c>
       <c r="E101">
-        <v>1.049545218784863</v>
+        <v>1.018237704918032</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
       <c r="G101">
-        <v>0.00600477916161225</v>
+        <v>0.006043532786885248</v>
       </c>
       <c r="H101">
-        <v>0.005290454781215137</v>
+        <v>0.005321762295081968</v>
       </c>
       <c r="I101">
-        <v>0.2943243803971134</v>
+        <v>0.3017704918032789</v>
       </c>
       <c r="J101">
-        <v>1.146191773629804</v>
+        <v>1.163114754098361</v>
       </c>
       <c r="K101">
         <v>2.29</v>
@@ -5919,7 +5901,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -5930,28 +5912,28 @@
         <v>36</v>
       </c>
       <c r="C102">
-        <v>1.287677825552173</v>
+        <v>1.246893442622949</v>
       </c>
       <c r="D102" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E102">
-        <v>1.109373167442558</v>
+        <v>1.176893442622949</v>
       </c>
       <c r="F102">
         <v>-1</v>
       </c>
       <c r="G102">
-        <v>0.006812322174447827</v>
+        <v>0.006853106557377051</v>
       </c>
       <c r="H102">
-        <v>0.006450626832557441</v>
+        <v>0.006783106557377051</v>
       </c>
       <c r="I102">
-        <v>0.1783046581096155</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J102">
-        <v>1.146191773629804</v>
+        <v>1.163114754098361</v>
       </c>
       <c r="K102">
         <v>2.41</v>
@@ -5960,16 +5942,16 @@
         <v>4.05</v>
       </c>
       <c r="M102">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N102">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O102">
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -5977,49 +5959,49 @@
         <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C103">
-        <v>0.7164672131147527</v>
+        <v>0.7002131196894186</v>
       </c>
       <c r="D103" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E103">
-        <v>1.018237704918032</v>
+        <v>0.5798239504652853</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
       <c r="G103">
-        <v>0.006043532786885248</v>
+        <v>0.006279786880310581</v>
       </c>
       <c r="H103">
-        <v>0.005321762295081968</v>
+        <v>0.006040176049534715</v>
       </c>
       <c r="I103">
-        <v>0.3017704918032789</v>
+        <v>-0.1203891692241332</v>
       </c>
       <c r="J103">
-        <v>1.163114754098361</v>
+        <v>1.192216615517343</v>
       </c>
       <c r="K103">
+        <v>2.34</v>
+      </c>
+      <c r="L103">
+        <v>3.49</v>
+      </c>
+      <c r="M103">
         <v>2.29</v>
       </c>
-      <c r="L103">
-        <v>3.38</v>
-      </c>
-      <c r="M103">
-        <v>1.85</v>
-      </c>
       <c r="N103">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="O103">
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6027,137 +6009,137 @@
         <v>1</v>
       </c>
       <c r="B104" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C104">
-        <v>1.246893442622949</v>
+        <v>0.6498239504652852</v>
       </c>
       <c r="D104" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="E104">
-        <v>1.069942622950818</v>
+        <v>0.5798239504652853</v>
       </c>
       <c r="F104">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G104">
-        <v>0.006853106557377051</v>
+        <v>0.006110176049534715</v>
       </c>
       <c r="H104">
-        <v>0.006490057377049181</v>
+        <v>0.006040176049534715</v>
       </c>
       <c r="I104">
-        <v>0.1769508196721312</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J104">
-        <v>1.163114754098361</v>
+        <v>1.192216615517343</v>
       </c>
       <c r="K104">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="L104">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="M104">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="N104">
-        <v>3.78</v>
+        <v>3.31</v>
       </c>
       <c r="O104">
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
     </row>
     <row r="105" spans="1:16">
       <c r="A105" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B105" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C105">
-        <v>0.7002131196894186</v>
+        <v>1.176757956603204</v>
       </c>
       <c r="D105" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E105">
-        <v>0.5798239504652853</v>
+        <v>1.106757956603204</v>
       </c>
       <c r="F105">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G105">
-        <v>0.006279786880310581</v>
+        <v>0.006923242043396796</v>
       </c>
       <c r="H105">
-        <v>0.006040176049534715</v>
+        <v>0.006853242043396796</v>
       </c>
       <c r="I105">
-        <v>-0.1203891692241332</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J105">
         <v>1.192216615517343</v>
       </c>
       <c r="K105">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="L105">
-        <v>3.49</v>
+        <v>4.05</v>
       </c>
       <c r="M105">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="N105">
-        <v>3.31</v>
+        <v>3.98</v>
       </c>
       <c r="O105">
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106" spans="1:16">
       <c r="A106" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C106">
-        <v>0.6498239504652852</v>
+        <v>0.5205928926738919</v>
       </c>
       <c r="D106" t="s">
         <v>35</v>
       </c>
       <c r="E106">
-        <v>0.5798239504652853</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
       <c r="G106">
-        <v>0.006110176049534715</v>
+        <v>0.006459407107326108</v>
       </c>
       <c r="H106">
-        <v>0.006040176049534715</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I106">
-        <v>-0.06999999999999984</v>
+        <v>-0.1165511301853397</v>
       </c>
       <c r="J106">
-        <v>1.192216615517343</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K106">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="L106">
-        <v>3.38</v>
+        <v>3.49</v>
       </c>
       <c r="M106">
         <v>2.29</v>
@@ -6169,101 +6151,101 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
     </row>
     <row r="107" spans="1:16">
       <c r="A107" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B107" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C107">
-        <v>1.176757956603204</v>
+        <v>0.474041762488552</v>
       </c>
       <c r="D107" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="E107">
-        <v>1.002135285844592</v>
+        <v>0.4040417624885522</v>
       </c>
       <c r="F107">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G107">
-        <v>0.006923242043396796</v>
+        <v>0.006285958237511447</v>
       </c>
       <c r="H107">
-        <v>0.006557864714155408</v>
+        <v>0.006215958237511448</v>
       </c>
       <c r="I107">
-        <v>0.1746226707586125</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J107">
-        <v>1.192216615517343</v>
+        <v>1.268977396293209</v>
       </c>
       <c r="K107">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="L107">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="M107">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="N107">
-        <v>3.78</v>
+        <v>3.31</v>
       </c>
       <c r="O107">
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
     </row>
     <row r="108" spans="1:16">
       <c r="A108" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B108" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C108">
-        <v>0.5205928926738919</v>
+        <v>0.551698597969601</v>
       </c>
       <c r="D108" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E108">
-        <v>0.4040417624885522</v>
+        <v>0.7904611387463603</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
       <c r="G108">
-        <v>0.006459407107326108</v>
+        <v>0.006008301402030399</v>
       </c>
       <c r="H108">
-        <v>0.006215958237511448</v>
+        <v>0.005409538861253641</v>
       </c>
       <c r="I108">
-        <v>-0.1165511301853397</v>
+        <v>0.2387625407767593</v>
       </c>
       <c r="J108">
         <v>1.268977396293209</v>
       </c>
       <c r="K108">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="L108">
-        <v>3.49</v>
+        <v>3.28</v>
       </c>
       <c r="M108">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="N108">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="O108">
         <v>1</v>
@@ -6274,40 +6256,40 @@
     </row>
     <row r="109" spans="1:16">
       <c r="A109" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C109">
-        <v>0.474041762488552</v>
+        <v>0.3774746016246668</v>
       </c>
       <c r="D109" t="s">
         <v>35</v>
       </c>
       <c r="E109">
-        <v>0.4040417624885522</v>
+        <v>0.2639815545814042</v>
       </c>
       <c r="F109">
         <v>1</v>
       </c>
       <c r="G109">
-        <v>0.006285958237511447</v>
+        <v>0.006602525398375333</v>
       </c>
       <c r="H109">
-        <v>0.006215958237511448</v>
+        <v>0.006356018445418596</v>
       </c>
       <c r="I109">
-        <v>-0.06999999999999984</v>
+        <v>-0.1134930470432627</v>
       </c>
       <c r="J109">
-        <v>1.268977396293209</v>
+        <v>1.330139059134758</v>
       </c>
       <c r="K109">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="L109">
-        <v>3.38</v>
+        <v>3.49</v>
       </c>
       <c r="M109">
         <v>2.29</v>
@@ -6319,57 +6301,57 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
     </row>
     <row r="110" spans="1:16">
       <c r="A110" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C110">
-        <v>0.551698597969601</v>
+        <v>0.2442505289553791</v>
       </c>
       <c r="D110" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="E110">
-        <v>0.7904611387463603</v>
+        <v>0.2036041501315458</v>
       </c>
       <c r="F110">
         <v>1</v>
       </c>
       <c r="G110">
-        <v>0.006008301402030399</v>
+        <v>0.006735749471044622</v>
       </c>
       <c r="H110">
-        <v>0.005409538861253641</v>
+        <v>0.006556395849868454</v>
       </c>
       <c r="I110">
-        <v>0.2387625407767593</v>
+        <v>-0.04064637882383337</v>
       </c>
       <c r="J110">
-        <v>1.268977396293209</v>
+        <v>1.387072423523342</v>
       </c>
       <c r="K110">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="L110">
-        <v>3.28</v>
+        <v>3.49</v>
       </c>
       <c r="M110">
-        <v>1.82</v>
+        <v>2.29</v>
       </c>
       <c r="N110">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="O110">
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6377,49 +6359,49 @@
         <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C111">
-        <v>0.3774746016246668</v>
+        <v>2.130748174485088</v>
       </c>
       <c r="D111" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E111">
-        <v>0.2639815545814042</v>
+        <v>2.060748174485089</v>
       </c>
       <c r="F111">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G111">
-        <v>0.006602525398375333</v>
+        <v>0.005969251825514912</v>
       </c>
       <c r="H111">
-        <v>0.006356018445418596</v>
+        <v>0.005899251825514911</v>
       </c>
       <c r="I111">
-        <v>-0.1134930470432627</v>
+        <v>0.0699999999999994</v>
       </c>
       <c r="J111">
-        <v>1.330139059134758</v>
+        <v>0.7963700520808761</v>
       </c>
       <c r="K111">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="L111">
-        <v>3.49</v>
+        <v>4.05</v>
       </c>
       <c r="M111">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="N111">
-        <v>3.31</v>
+        <v>3.98</v>
       </c>
       <c r="O111">
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6427,49 +6409,49 @@
         <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C112">
-        <v>0.2442505289553791</v>
+        <v>2.121470903610984</v>
       </c>
       <c r="D112" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="E112">
-        <v>0.2036041501315458</v>
+        <v>2.051470903610984</v>
       </c>
       <c r="F112">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G112">
-        <v>0.006735749471044622</v>
+        <v>0.005978529096389016</v>
       </c>
       <c r="H112">
-        <v>0.006556395849868454</v>
+        <v>0.005908529096389016</v>
       </c>
       <c r="I112">
-        <v>-0.04064637882383337</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J112">
-        <v>1.387072423523342</v>
+        <v>0.8002195420701311</v>
       </c>
       <c r="K112">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="L112">
-        <v>3.49</v>
+        <v>4.05</v>
       </c>
       <c r="M112">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="N112">
-        <v>3.38</v>
+        <v>3.98</v>
       </c>
       <c r="O112">
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6477,81 +6459,81 @@
         <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C113">
-        <v>2.01907486979781</v>
+        <v>2.108898582933901</v>
       </c>
       <c r="D113" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E113">
-        <v>1.924457778651558</v>
+        <v>2.038898582933901</v>
       </c>
       <c r="F113">
         <v>-1</v>
       </c>
       <c r="G113">
-        <v>0.00600092513020219</v>
+        <v>0.005991101417066099</v>
       </c>
       <c r="H113">
-        <v>0.005635542221348441</v>
+        <v>0.005921101417066099</v>
       </c>
       <c r="I113">
-        <v>0.09461709114625116</v>
+        <v>0.07000000000000028</v>
       </c>
       <c r="J113">
-        <v>0.7963700520808761</v>
+        <v>0.8054362726415348</v>
       </c>
       <c r="K113">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L113">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M113">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N113">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O113">
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="114" spans="1:16">
       <c r="A114" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B114" t="s">
         <v>36</v>
       </c>
       <c r="C114">
-        <v>2.130748174485088</v>
+        <v>2.094411734269654</v>
       </c>
       <c r="D114" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E114">
-        <v>1.924457778651558</v>
+        <v>2.024411734269654</v>
       </c>
       <c r="F114">
         <v>-1</v>
       </c>
       <c r="G114">
-        <v>0.005969251825514912</v>
+        <v>0.006005588265730346</v>
       </c>
       <c r="H114">
-        <v>0.005635542221348441</v>
+        <v>0.005935588265730345</v>
       </c>
       <c r="I114">
-        <v>0.2062903958335298</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J114">
-        <v>0.7963700520808761</v>
+        <v>0.8114474131661186</v>
       </c>
       <c r="K114">
         <v>2.41</v>
@@ -6560,16 +6542,16 @@
         <v>4.05</v>
       </c>
       <c r="M114">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N114">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O114">
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6577,81 +6559,81 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C115">
-        <v>2.009451144824672</v>
+        <v>2.090368166197157</v>
       </c>
       <c r="D115" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E115">
-        <v>1.915488466976594</v>
+        <v>2.020368166197157</v>
       </c>
       <c r="F115">
         <v>-1</v>
       </c>
       <c r="G115">
-        <v>0.006010548855175328</v>
+        <v>0.006009631833802842</v>
       </c>
       <c r="H115">
-        <v>0.005644511533023405</v>
+        <v>0.005939631833802844</v>
       </c>
       <c r="I115">
-        <v>0.09396267784807799</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J115">
-        <v>0.8002195420701311</v>
+        <v>0.8131252422418436</v>
       </c>
       <c r="K115">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L115">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M115">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N115">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O115">
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="116" spans="1:16">
       <c r="A116" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B116" t="s">
         <v>36</v>
       </c>
       <c r="C116">
-        <v>2.121470903610984</v>
+        <v>2.085491497865919</v>
       </c>
       <c r="D116" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E116">
-        <v>1.915488466976594</v>
+        <v>2.015491497865919</v>
       </c>
       <c r="F116">
         <v>-1</v>
       </c>
       <c r="G116">
-        <v>0.005978529096389016</v>
+        <v>0.00601450850213408</v>
       </c>
       <c r="H116">
-        <v>0.005644511533023405</v>
+        <v>0.005944508502134081</v>
       </c>
       <c r="I116">
-        <v>0.2059824366343896</v>
+        <v>0.07000000000000028</v>
       </c>
       <c r="J116">
-        <v>0.8002195420701311</v>
+        <v>0.8151487560722326</v>
       </c>
       <c r="K116">
         <v>2.41</v>
@@ -6660,16 +6642,16 @@
         <v>4.05</v>
       </c>
       <c r="M116">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N116">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O116">
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6677,81 +6659,81 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C117">
-        <v>1.996409318396163</v>
+        <v>2.075974780689192</v>
       </c>
       <c r="D117" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E117">
-        <v>1.903333484745224</v>
+        <v>2.005974780689192</v>
       </c>
       <c r="F117">
         <v>-1</v>
       </c>
       <c r="G117">
-        <v>0.006023590681603837</v>
+        <v>0.006024025219310808</v>
       </c>
       <c r="H117">
-        <v>0.005656666515254777</v>
+        <v>0.005954025219310808</v>
       </c>
       <c r="I117">
-        <v>0.09307583365093897</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J117">
-        <v>0.8054362726415348</v>
+        <v>0.8190976013737793</v>
       </c>
       <c r="K117">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L117">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M117">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N117">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O117">
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="118" spans="1:16">
       <c r="A118" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B118" t="s">
         <v>36</v>
       </c>
       <c r="C118">
-        <v>2.108898582933901</v>
+        <v>2.079906388470867</v>
       </c>
       <c r="D118" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E118">
-        <v>1.903333484745224</v>
+        <v>2.009906388470868</v>
       </c>
       <c r="F118">
         <v>-1</v>
       </c>
       <c r="G118">
-        <v>0.005991101417066099</v>
+        <v>0.006020093611529133</v>
       </c>
       <c r="H118">
-        <v>0.005656666515254777</v>
+        <v>0.005950093611529132</v>
       </c>
       <c r="I118">
-        <v>0.2055650981886774</v>
+        <v>0.0699999999999994</v>
       </c>
       <c r="J118">
-        <v>0.8054362726415348</v>
+        <v>0.8174662288502623</v>
       </c>
       <c r="K118">
         <v>2.41</v>
@@ -6760,16 +6742,16 @@
         <v>4.05</v>
       </c>
       <c r="M118">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N118">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O118">
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6777,81 +6759,81 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C119">
-        <v>1.981381467084703</v>
+        <v>2.080915784653693</v>
       </c>
       <c r="D119" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E119">
-        <v>1.889327527322944</v>
+        <v>2.010915784653693</v>
       </c>
       <c r="F119">
         <v>-1</v>
       </c>
       <c r="G119">
-        <v>0.006038618532915297</v>
+        <v>0.006019084215346308</v>
       </c>
       <c r="H119">
-        <v>0.005670672472677056</v>
+        <v>0.005949084215346307</v>
       </c>
       <c r="I119">
-        <v>0.09205393976175968</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J119">
-        <v>0.8114474131661186</v>
+        <v>0.8170473922598784</v>
       </c>
       <c r="K119">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L119">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M119">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N119">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O119">
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="120" spans="1:16">
       <c r="A120" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B120" t="s">
         <v>36</v>
       </c>
       <c r="C120">
-        <v>2.094411734269654</v>
+        <v>2.079426656607948</v>
       </c>
       <c r="D120" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E120">
-        <v>1.889327527322944</v>
+        <v>2.009426656607948</v>
       </c>
       <c r="F120">
         <v>-1</v>
       </c>
       <c r="G120">
-        <v>0.006005588265730346</v>
+        <v>0.006020573343392051</v>
       </c>
       <c r="H120">
-        <v>0.005670672472677056</v>
+        <v>0.005950573343392052</v>
       </c>
       <c r="I120">
-        <v>0.2050842069467105</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J120">
-        <v>0.8114474131661186</v>
+        <v>0.8176652877145442</v>
       </c>
       <c r="K120">
         <v>2.41</v>
@@ -6860,16 +6842,16 @@
         <v>4.05</v>
       </c>
       <c r="M120">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N120">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O120">
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -6877,81 +6859,81 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C121">
-        <v>1.977186894395391</v>
+        <v>2.078429124150567</v>
       </c>
       <c r="D121" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E121">
-        <v>1.885418185576504</v>
+        <v>2.008429124150568</v>
       </c>
       <c r="F121">
         <v>-1</v>
       </c>
       <c r="G121">
-        <v>0.006042813105604609</v>
+        <v>0.006021570875849432</v>
       </c>
       <c r="H121">
-        <v>0.005674581814423495</v>
+        <v>0.005951570875849433</v>
       </c>
       <c r="I121">
-        <v>0.09176870881888655</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J121">
-        <v>0.8131252422418436</v>
+        <v>0.8180792015972748</v>
       </c>
       <c r="K121">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L121">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M121">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N121">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O121">
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="122" spans="1:16">
       <c r="A122" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B122" t="s">
         <v>36</v>
       </c>
       <c r="C122">
-        <v>2.090368166197157</v>
+        <v>2.075839311472164</v>
       </c>
       <c r="D122" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E122">
-        <v>1.885418185576504</v>
+        <v>2.005839311472164</v>
       </c>
       <c r="F122">
         <v>-1</v>
       </c>
       <c r="G122">
-        <v>0.006009631833802842</v>
+        <v>0.006024160688527836</v>
       </c>
       <c r="H122">
-        <v>0.005674581814423495</v>
+        <v>0.005954160688527835</v>
       </c>
       <c r="I122">
-        <v>0.2049499806206525</v>
+        <v>0.0699999999999994</v>
       </c>
       <c r="J122">
-        <v>0.8131252422418436</v>
+        <v>0.8191538126671517</v>
       </c>
       <c r="K122">
         <v>2.41</v>
@@ -6960,16 +6942,16 @@
         <v>4.05</v>
       </c>
       <c r="M122">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N122">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O122">
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -6977,81 +6959,81 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C123">
-        <v>1.972128109819418</v>
+        <v>2.082841001865318</v>
       </c>
       <c r="D123" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E123">
-        <v>1.880703398351698</v>
+        <v>2.012841001865318</v>
       </c>
       <c r="F123">
         <v>-1</v>
       </c>
       <c r="G123">
-        <v>0.006047871890180582</v>
+        <v>0.006017158998134682</v>
       </c>
       <c r="H123">
-        <v>0.005679296601648302</v>
+        <v>0.005947158998134683</v>
       </c>
       <c r="I123">
-        <v>0.09142471146772024</v>
+        <v>0.07000000000000028</v>
       </c>
       <c r="J123">
-        <v>0.8151487560722326</v>
+        <v>0.8162485469438515</v>
       </c>
       <c r="K123">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L123">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M123">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N123">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O123">
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="124" spans="1:16">
       <c r="A124" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B124" t="s">
         <v>36</v>
       </c>
       <c r="C124">
-        <v>2.085491497865919</v>
+        <v>2.092140405493763</v>
       </c>
       <c r="D124" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E124">
-        <v>1.880703398351698</v>
+        <v>2.022140405493763</v>
       </c>
       <c r="F124">
         <v>-1</v>
       </c>
       <c r="G124">
-        <v>0.00601450850213408</v>
+        <v>0.006007859594506237</v>
       </c>
       <c r="H124">
-        <v>0.005679296601648302</v>
+        <v>0.005937859594506238</v>
       </c>
       <c r="I124">
-        <v>0.2047880995142215</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J124">
-        <v>0.8151487560722326</v>
+        <v>0.8123898732391025</v>
       </c>
       <c r="K124">
         <v>2.41</v>
@@ -7060,16 +7042,16 @@
         <v>4.05</v>
       </c>
       <c r="M124">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N124">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O124">
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7077,81 +7059,81 @@
         <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C125">
-        <v>1.962255996565552</v>
+        <v>2.096576344320673</v>
       </c>
       <c r="D125" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E125">
-        <v>1.871502588799094</v>
+        <v>2.026576344320673</v>
       </c>
       <c r="F125">
         <v>-1</v>
       </c>
       <c r="G125">
-        <v>0.006057744003434448</v>
+        <v>0.006003423655679328</v>
       </c>
       <c r="H125">
-        <v>0.005688497411200906</v>
+        <v>0.005933423655679327</v>
       </c>
       <c r="I125">
-        <v>0.09075340776645779</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J125">
-        <v>0.8190976013737793</v>
+        <v>0.8105492347217125</v>
       </c>
       <c r="K125">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L125">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M125">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N125">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O125">
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="126" spans="1:16">
       <c r="A126" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B126" t="s">
         <v>36</v>
       </c>
       <c r="C126">
-        <v>2.075974780689192</v>
+        <v>2.103396386673994</v>
       </c>
       <c r="D126" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E126">
-        <v>1.871502588799094</v>
+        <v>2.033396386673994</v>
       </c>
       <c r="F126">
         <v>-1</v>
       </c>
       <c r="G126">
-        <v>0.006024025219310808</v>
+        <v>0.005996603613326006</v>
       </c>
       <c r="H126">
-        <v>0.005688497411200906</v>
+        <v>0.005926603613326005</v>
       </c>
       <c r="I126">
-        <v>0.2044721918900976</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J126">
-        <v>0.8190976013737793</v>
+        <v>0.8077193416290479</v>
       </c>
       <c r="K126">
         <v>2.41</v>
@@ -7160,16 +7142,16 @@
         <v>4.05</v>
       </c>
       <c r="M126">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N126">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O126">
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7177,81 +7159,81 @@
         <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C127">
-        <v>1.966334427874344</v>
+        <v>2.108040013253082</v>
       </c>
       <c r="D127" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E127">
-        <v>1.875303686778889</v>
+        <v>2.038040013253082</v>
       </c>
       <c r="F127">
         <v>-1</v>
       </c>
       <c r="G127">
-        <v>0.006053665572125656</v>
+        <v>0.005991959986746918</v>
       </c>
       <c r="H127">
-        <v>0.005684696313221111</v>
+        <v>0.005921959986746919</v>
       </c>
       <c r="I127">
-        <v>0.09103074109545517</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J127">
-        <v>0.8174662288502623</v>
+        <v>0.8057925256211278</v>
       </c>
       <c r="K127">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L127">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M127">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N127">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O127">
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="128" spans="1:16">
       <c r="A128" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B128" t="s">
         <v>36</v>
       </c>
       <c r="C128">
-        <v>2.079906388470867</v>
+        <v>2.114054135735469</v>
       </c>
       <c r="D128" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E128">
-        <v>1.875303686778889</v>
+        <v>2.044054135735468</v>
       </c>
       <c r="F128">
         <v>-1</v>
       </c>
       <c r="G128">
-        <v>0.006020093611529133</v>
+        <v>0.005985945864264531</v>
       </c>
       <c r="H128">
-        <v>0.005684696313221111</v>
+        <v>0.005915945864264532</v>
       </c>
       <c r="I128">
-        <v>0.2046027016919787</v>
+        <v>0.07000000000000028</v>
       </c>
       <c r="J128">
-        <v>0.8174662288502623</v>
+        <v>0.8032970391139135</v>
       </c>
       <c r="K128">
         <v>2.41</v>
@@ -7260,16 +7242,16 @@
         <v>4.05</v>
       </c>
       <c r="M128">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N128">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O128">
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7277,81 +7259,81 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C129">
-        <v>1.967381519350304</v>
+        <v>2.120323822719538</v>
       </c>
       <c r="D129" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E129">
-        <v>1.876279576034483</v>
+        <v>2.050323822719538</v>
       </c>
       <c r="F129">
         <v>-1</v>
       </c>
       <c r="G129">
-        <v>0.006052618480649696</v>
+        <v>0.005979676177280462</v>
       </c>
       <c r="H129">
-        <v>0.005683720423965516</v>
+        <v>0.005909676177280462</v>
       </c>
       <c r="I129">
-        <v>0.09110194331582067</v>
+        <v>0.0699999999999994</v>
       </c>
       <c r="J129">
-        <v>0.8170473922598784</v>
+        <v>0.8006955092450049</v>
       </c>
       <c r="K129">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L129">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M129">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N129">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O129">
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="130" spans="1:16">
       <c r="A130" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B130" t="s">
         <v>36</v>
       </c>
       <c r="C130">
-        <v>2.080915784653693</v>
+        <v>2.125285159031259</v>
       </c>
       <c r="D130" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E130">
-        <v>1.876279576034483</v>
+        <v>2.055285159031259</v>
       </c>
       <c r="F130">
         <v>-1</v>
       </c>
       <c r="G130">
-        <v>0.006019084215346308</v>
+        <v>0.005974714840968741</v>
       </c>
       <c r="H130">
-        <v>0.005683720423965516</v>
+        <v>0.005904714840968741</v>
       </c>
       <c r="I130">
-        <v>0.2046362086192097</v>
+        <v>0.07000000000000028</v>
       </c>
       <c r="J130">
-        <v>0.8170473922598784</v>
+        <v>0.7986368634725065</v>
       </c>
       <c r="K130">
         <v>2.41</v>
@@ -7360,16 +7342,16 @@
         <v>4.05</v>
       </c>
       <c r="M130">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N130">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O130">
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7377,81 +7359,81 @@
         <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C131">
-        <v>1.965836780713639</v>
+        <v>2.136281584912229</v>
       </c>
       <c r="D131" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E131">
-        <v>1.874839879625112</v>
+        <v>2.066281584912229</v>
       </c>
       <c r="F131">
         <v>-1</v>
       </c>
       <c r="G131">
-        <v>0.00605416321928636</v>
+        <v>0.00596371841508777</v>
       </c>
       <c r="H131">
-        <v>0.005685160120374888</v>
+        <v>0.005893718415087771</v>
       </c>
       <c r="I131">
-        <v>0.09099690108852765</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J131">
-        <v>0.8176652877145442</v>
+        <v>0.7940740311567515</v>
       </c>
       <c r="K131">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L131">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M131">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N131">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O131">
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
     </row>
     <row r="132" spans="1:16">
       <c r="A132" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B132" t="s">
         <v>36</v>
       </c>
       <c r="C132">
-        <v>2.079426656607948</v>
+        <v>2.148053344388881</v>
       </c>
       <c r="D132" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E132">
-        <v>1.874839879625112</v>
+        <v>2.078053344388882</v>
       </c>
       <c r="F132">
         <v>-1</v>
       </c>
       <c r="G132">
-        <v>0.006020573343392051</v>
+        <v>0.005951946655611119</v>
       </c>
       <c r="H132">
-        <v>0.005685160120374888</v>
+        <v>0.005881946655611118</v>
       </c>
       <c r="I132">
-        <v>0.2045867769828364</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J132">
-        <v>0.8176652877145442</v>
+        <v>0.7891894836560657</v>
       </c>
       <c r="K132">
         <v>2.41</v>
@@ -7460,16 +7442,16 @@
         <v>4.05</v>
       </c>
       <c r="M132">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N132">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O132">
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7477,81 +7459,81 @@
         <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C133">
-        <v>1.964801996006813</v>
+        <v>2.151305835742038</v>
       </c>
       <c r="D133" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E133">
-        <v>1.87387546027835</v>
+        <v>2.081305835742038</v>
       </c>
       <c r="F133">
         <v>-1</v>
       </c>
       <c r="G133">
-        <v>0.006055198003993187</v>
+        <v>0.005948694164257961</v>
       </c>
       <c r="H133">
-        <v>0.00568612453972165</v>
+        <v>0.005878694164257962</v>
       </c>
       <c r="I133">
-        <v>0.09092653572846343</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J133">
-        <v>0.8180792015972748</v>
+        <v>0.7878399021817268</v>
       </c>
       <c r="K133">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L133">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M133">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N133">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O133">
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="134" spans="1:16">
       <c r="A134" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B134" t="s">
         <v>36</v>
       </c>
       <c r="C134">
-        <v>2.078429124150567</v>
+        <v>2.151572681684375</v>
       </c>
       <c r="D134" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E134">
-        <v>1.87387546027835</v>
+        <v>2.081572681684375</v>
       </c>
       <c r="F134">
         <v>-1</v>
       </c>
       <c r="G134">
-        <v>0.006021570875849432</v>
+        <v>0.005948427318315626</v>
       </c>
       <c r="H134">
-        <v>0.00568612453972165</v>
+        <v>0.005878427318315625</v>
       </c>
       <c r="I134">
-        <v>0.2045536638722179</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J134">
-        <v>0.8180792015972748</v>
+        <v>0.7877291777243258</v>
       </c>
       <c r="K134">
         <v>2.41</v>
@@ -7560,16 +7542,16 @@
         <v>4.05</v>
       </c>
       <c r="M134">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N134">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O134">
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7577,81 +7559,81 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C135">
-        <v>1.96211546833212</v>
+        <v>2.152621179997558</v>
       </c>
       <c r="D135" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E135">
-        <v>1.871371616485536</v>
+        <v>2.082621179997558</v>
       </c>
       <c r="F135">
         <v>-1</v>
       </c>
       <c r="G135">
-        <v>0.006057884531667879</v>
+        <v>0.005947378820002442</v>
       </c>
       <c r="H135">
-        <v>0.005688628383514464</v>
+        <v>0.005877378820002442</v>
       </c>
       <c r="I135">
-        <v>0.09074385184658418</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J135">
-        <v>0.8191538126671517</v>
+        <v>0.7872941161835857</v>
       </c>
       <c r="K135">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L135">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M135">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N135">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O135">
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="136" spans="1:16">
       <c r="A136" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B136" t="s">
         <v>36</v>
       </c>
       <c r="C136">
-        <v>2.075839311472164</v>
+        <v>2.149282713891501</v>
       </c>
       <c r="D136" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E136">
-        <v>1.871371616485536</v>
+        <v>2.079282713891502</v>
       </c>
       <c r="F136">
         <v>-1</v>
       </c>
       <c r="G136">
-        <v>0.006024160688527836</v>
+        <v>0.005950717286108499</v>
       </c>
       <c r="H136">
-        <v>0.005688628383514464</v>
+        <v>0.005880717286108499</v>
       </c>
       <c r="I136">
-        <v>0.2044676949866275</v>
+        <v>0.0699999999999994</v>
       </c>
       <c r="J136">
-        <v>0.8191538126671517</v>
+        <v>0.7886793718292525</v>
       </c>
       <c r="K136">
         <v>2.41</v>
@@ -7660,16 +7642,16 @@
         <v>4.05</v>
       </c>
       <c r="M136">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N136">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O136">
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7677,81 +7659,81 @@
         <v>0</v>
       </c>
       <c r="B137" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C137">
-        <v>1.969378632640371</v>
+        <v>2.146227648604146</v>
       </c>
       <c r="D137" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E137">
-        <v>1.878140885620826</v>
+        <v>2.076227648604147</v>
       </c>
       <c r="F137">
         <v>-1</v>
       </c>
       <c r="G137">
-        <v>0.006050621367359629</v>
+        <v>0.005953772351395854</v>
       </c>
       <c r="H137">
-        <v>0.005681859114379174</v>
+        <v>0.005883772351395853</v>
       </c>
       <c r="I137">
-        <v>0.09123774701954535</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J137">
-        <v>0.8162485469438515</v>
+        <v>0.7899470337742129</v>
       </c>
       <c r="K137">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="L137">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="M137">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N137">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O137">
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
     </row>
     <row r="138" spans="1:16">
       <c r="A138" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B138" t="s">
         <v>36</v>
       </c>
       <c r="C138">
-        <v>2.082841001865318</v>
+        <v>2.145080586568228</v>
       </c>
       <c r="D138" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E138">
-        <v>1.878140885620826</v>
+        <v>2.075080586568228</v>
       </c>
       <c r="F138">
         <v>-1</v>
       </c>
       <c r="G138">
-        <v>0.006017158998134682</v>
+        <v>0.005954919413431771</v>
       </c>
       <c r="H138">
-        <v>0.005681859114379174</v>
+        <v>0.005884919413431771</v>
       </c>
       <c r="I138">
-        <v>0.2047001162444921</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J138">
-        <v>0.8162485469438515</v>
+        <v>0.7904229931252164</v>
       </c>
       <c r="K138">
         <v>2.41</v>
@@ -7760,16 +7742,16 @@
         <v>4.05</v>
       </c>
       <c r="M138">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N138">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O138">
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7780,28 +7762,28 @@
         <v>36</v>
       </c>
       <c r="C139">
-        <v>2.092140405493763</v>
+        <v>2.14339129660172</v>
       </c>
       <c r="D139" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E139">
-        <v>1.887131595352891</v>
+        <v>2.073391296601721</v>
       </c>
       <c r="F139">
         <v>-1</v>
       </c>
       <c r="G139">
-        <v>0.006007859594506237</v>
+        <v>0.005956608703398279</v>
       </c>
       <c r="H139">
-        <v>0.005672868404647109</v>
+        <v>0.005886608703398279</v>
       </c>
       <c r="I139">
-        <v>0.2050088101408718</v>
+        <v>0.0699999999999994</v>
       </c>
       <c r="J139">
-        <v>0.8123898732391025</v>
+        <v>0.791123943318788</v>
       </c>
       <c r="K139">
         <v>2.41</v>
@@ -7810,16 +7792,16 @@
         <v>4.05</v>
       </c>
       <c r="M139">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N139">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O139">
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -7830,28 +7812,28 @@
         <v>36</v>
       </c>
       <c r="C140">
-        <v>2.096576344320673</v>
+        <v>2.142284300015975</v>
       </c>
       <c r="D140" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E140">
-        <v>1.89142028309841</v>
+        <v>2.072284300015975</v>
       </c>
       <c r="F140">
         <v>-1</v>
       </c>
       <c r="G140">
-        <v>0.006003423655679328</v>
+        <v>0.005957715699984025</v>
       </c>
       <c r="H140">
-        <v>0.00566857971690159</v>
+        <v>0.005887715699984026</v>
       </c>
       <c r="I140">
-        <v>0.2051560612222629</v>
+        <v>0.07000000000000028</v>
       </c>
       <c r="J140">
-        <v>0.8105492347217125</v>
+        <v>0.7915832780016702</v>
       </c>
       <c r="K140">
         <v>2.41</v>
@@ -7860,16 +7842,16 @@
         <v>4.05</v>
       </c>
       <c r="M140">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N140">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O140">
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -7880,28 +7862,28 @@
         <v>36</v>
       </c>
       <c r="C141">
-        <v>2.103396386673994</v>
+        <v>2.143425559712756</v>
       </c>
       <c r="D141" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E141">
-        <v>1.898013934004318</v>
+        <v>2.073425559712756</v>
       </c>
       <c r="F141">
         <v>-1</v>
       </c>
       <c r="G141">
-        <v>0.005996603613326006</v>
+        <v>0.005956574440287244</v>
       </c>
       <c r="H141">
-        <v>0.005661986065995682</v>
+        <v>0.005886574440287244</v>
       </c>
       <c r="I141">
-        <v>0.2053824526696761</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J141">
-        <v>0.8077193416290479</v>
+        <v>0.7911097262602672</v>
       </c>
       <c r="K141">
         <v>2.41</v>
@@ -7910,16 +7892,16 @@
         <v>4.05</v>
       </c>
       <c r="M141">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N141">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O141">
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -7930,28 +7912,28 @@
         <v>36</v>
       </c>
       <c r="C142">
-        <v>2.108040013253082</v>
+        <v>2.144968519714193</v>
       </c>
       <c r="D142" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E142">
-        <v>1.902503415302772</v>
+        <v>2.074968519714193</v>
       </c>
       <c r="F142">
         <v>-1</v>
       </c>
       <c r="G142">
-        <v>0.005991959986746918</v>
+        <v>0.005955031480285808</v>
       </c>
       <c r="H142">
-        <v>0.005657496584697228</v>
+        <v>0.005885031480285807</v>
       </c>
       <c r="I142">
-        <v>0.2055365979503097</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J142">
-        <v>0.8057925256211278</v>
+        <v>0.7904694938945258</v>
       </c>
       <c r="K142">
         <v>2.41</v>
@@ -7960,16 +7942,16 @@
         <v>4.05</v>
       </c>
       <c r="M142">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N142">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O142">
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -7980,28 +7962,28 @@
         <v>36</v>
       </c>
       <c r="C143">
-        <v>2.114054135735469</v>
+        <v>2.148138038800297</v>
       </c>
       <c r="D143" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E143">
-        <v>1.908317898864581</v>
+        <v>2.078138038800297</v>
       </c>
       <c r="F143">
         <v>-1</v>
       </c>
       <c r="G143">
-        <v>0.005985945864264531</v>
+        <v>0.005951861961199702</v>
       </c>
       <c r="H143">
-        <v>0.005651682101135419</v>
+        <v>0.005881861961199703</v>
       </c>
       <c r="I143">
-        <v>0.2057362368708873</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J143">
-        <v>0.8032970391139135</v>
+        <v>0.7891543407467646</v>
       </c>
       <c r="K143">
         <v>2.41</v>
@@ -8010,16 +7992,16 @@
         <v>4.05</v>
       </c>
       <c r="M143">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N143">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O143">
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8030,28 +8012,28 @@
         <v>36</v>
       </c>
       <c r="C144">
-        <v>2.120323822719538</v>
+        <v>2.151907493357466</v>
       </c>
       <c r="D144" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E144">
-        <v>1.914379463459138</v>
+        <v>2.081907493357466</v>
       </c>
       <c r="F144">
         <v>-1</v>
       </c>
       <c r="G144">
-        <v>0.005979676177280462</v>
+        <v>0.005948092506642534</v>
       </c>
       <c r="H144">
-        <v>0.005645620536540861</v>
+        <v>0.005878092506642535</v>
       </c>
       <c r="I144">
-        <v>0.2059443592603993</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J144">
-        <v>0.8006955092450049</v>
+        <v>0.7875902517188939</v>
       </c>
       <c r="K144">
         <v>2.41</v>
@@ -8060,16 +8042,16 @@
         <v>4.05</v>
       </c>
       <c r="M144">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N144">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O144">
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8080,28 +8062,28 @@
         <v>36</v>
       </c>
       <c r="C145">
-        <v>2.125285159031259</v>
+        <v>2.1538020117046</v>
       </c>
       <c r="D145" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E145">
-        <v>1.919176108109059</v>
+        <v>2.0838020117046</v>
       </c>
       <c r="F145">
         <v>-1</v>
       </c>
       <c r="G145">
-        <v>0.005974714840968741</v>
+        <v>0.005946197988295399</v>
       </c>
       <c r="H145">
-        <v>0.00564082389189094</v>
+        <v>0.0058761979882954</v>
       </c>
       <c r="I145">
-        <v>0.2061090509221997</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J145">
-        <v>0.7986368634725065</v>
+        <v>0.7868041445209126</v>
       </c>
       <c r="K145">
         <v>2.41</v>
@@ -8110,16 +8092,16 @@
         <v>4.05</v>
       </c>
       <c r="M145">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N145">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O145">
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8130,28 +8112,28 @@
         <v>36</v>
       </c>
       <c r="C146">
-        <v>2.136281584912229</v>
+        <v>2.157161945588962</v>
       </c>
       <c r="D146" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E146">
-        <v>1.929807507404769</v>
+        <v>2.087161945588962</v>
       </c>
       <c r="F146">
         <v>-1</v>
       </c>
       <c r="G146">
-        <v>0.00596371841508777</v>
+        <v>0.005942838054411038</v>
       </c>
       <c r="H146">
-        <v>0.00563019249259523</v>
+        <v>0.005872838054411038</v>
       </c>
       <c r="I146">
-        <v>0.2064740775074598</v>
+        <v>0.07000000000000028</v>
       </c>
       <c r="J146">
-        <v>0.7940740311567515</v>
+        <v>0.7854099810834182</v>
       </c>
       <c r="K146">
         <v>2.41</v>
@@ -8160,16 +8142,16 @@
         <v>4.05</v>
       </c>
       <c r="M146">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N146">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O146">
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8180,28 +8162,28 @@
         <v>36</v>
       </c>
       <c r="C147">
-        <v>2.148053344388881</v>
+        <v>2.161672330968959</v>
       </c>
       <c r="D147" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E147">
-        <v>1.941188503081367</v>
+        <v>2.091672330968959</v>
       </c>
       <c r="F147">
         <v>-1</v>
       </c>
       <c r="G147">
-        <v>0.005951946655611119</v>
+        <v>0.005938327669031041</v>
       </c>
       <c r="H147">
-        <v>0.005618811496918633</v>
+        <v>0.005868327669031041</v>
       </c>
       <c r="I147">
-        <v>0.2068648413075147</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J147">
-        <v>0.7891894836560657</v>
+        <v>0.7835384518800999</v>
       </c>
       <c r="K147">
         <v>2.41</v>
@@ -8210,16 +8192,16 @@
         <v>4.05</v>
       </c>
       <c r="M147">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N147">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O147">
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8230,28 +8212,28 @@
         <v>36</v>
       </c>
       <c r="C148">
-        <v>2.151305835742038</v>
+        <v>2.162884754387039</v>
       </c>
       <c r="D148" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E148">
-        <v>1.944333027916576</v>
+        <v>2.09288475438704</v>
       </c>
       <c r="F148">
         <v>-1</v>
       </c>
       <c r="G148">
-        <v>0.005948694164257961</v>
+        <v>0.00593711524561296</v>
       </c>
       <c r="H148">
-        <v>0.005615666972083423</v>
+        <v>0.005867115245612961</v>
       </c>
       <c r="I148">
-        <v>0.2069728078254618</v>
+        <v>0.0699999999999994</v>
       </c>
       <c r="J148">
-        <v>0.7878399021817268</v>
+        <v>0.783035371623635</v>
       </c>
       <c r="K148">
         <v>2.41</v>
@@ -8260,16 +8242,16 @@
         <v>4.05</v>
       </c>
       <c r="M148">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N148">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O148">
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8280,28 +8262,28 @@
         <v>36</v>
       </c>
       <c r="C149">
-        <v>2.151572681684375</v>
+        <v>2.16447911025038</v>
       </c>
       <c r="D149" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E149">
-        <v>1.944591015902321</v>
+        <v>2.09447911025038</v>
       </c>
       <c r="F149">
         <v>-1</v>
       </c>
       <c r="G149">
-        <v>0.005948427318315626</v>
+        <v>0.00593552088974962</v>
       </c>
       <c r="H149">
-        <v>0.00561540898409768</v>
+        <v>0.00586552088974962</v>
       </c>
       <c r="I149">
-        <v>0.206981665782054</v>
+        <v>0.0699999999999994</v>
       </c>
       <c r="J149">
-        <v>0.7877291777243258</v>
+        <v>0.7823738131741161</v>
       </c>
       <c r="K149">
         <v>2.41</v>
@@ -8310,16 +8292,16 @@
         <v>4.05</v>
       </c>
       <c r="M149">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N149">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O149">
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8330,28 +8312,28 @@
         <v>36</v>
       </c>
       <c r="C150">
-        <v>2.152621179997558</v>
+        <v>2.168006663995569</v>
       </c>
       <c r="D150" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E150">
-        <v>1.945604709292245</v>
+        <v>2.098006663995569</v>
       </c>
       <c r="F150">
         <v>-1</v>
       </c>
       <c r="G150">
-        <v>0.005947378820002442</v>
+        <v>0.005931993336004431</v>
       </c>
       <c r="H150">
-        <v>0.005614395290707755</v>
+        <v>0.00586199333600443</v>
       </c>
       <c r="I150">
-        <v>0.207016470705313</v>
+        <v>0.0699999999999994</v>
       </c>
       <c r="J150">
-        <v>0.7872941161835857</v>
+        <v>0.7809100979271496</v>
       </c>
       <c r="K150">
         <v>2.41</v>
@@ -8360,16 +8342,16 @@
         <v>4.05</v>
       </c>
       <c r="M150">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N150">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O150">
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8380,28 +8362,28 @@
         <v>36</v>
       </c>
       <c r="C151">
-        <v>2.149282713891501</v>
+        <v>2.16983540706272</v>
       </c>
       <c r="D151" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E151">
-        <v>1.942377063637841</v>
+        <v>2.099835407062721</v>
       </c>
       <c r="F151">
         <v>-1</v>
       </c>
       <c r="G151">
-        <v>0.005950717286108499</v>
+        <v>0.005930164592937279</v>
       </c>
       <c r="H151">
-        <v>0.005617622936362159</v>
+        <v>0.005860164592937279</v>
       </c>
       <c r="I151">
-        <v>0.2069056502536595</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J151">
-        <v>0.7886793718292525</v>
+        <v>0.7801512833764644</v>
       </c>
       <c r="K151">
         <v>2.41</v>
@@ -8410,16 +8392,16 @@
         <v>4.05</v>
       </c>
       <c r="M151">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N151">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O151">
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8430,28 +8412,28 @@
         <v>36</v>
       </c>
       <c r="C152">
-        <v>2.146227648604146</v>
+        <v>2.170790161930732</v>
       </c>
       <c r="D152" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E152">
-        <v>1.939423411306084</v>
+        <v>2.100790161930732</v>
       </c>
       <c r="F152">
         <v>-1</v>
       </c>
       <c r="G152">
-        <v>0.005953772351395854</v>
+        <v>0.005929209838069268</v>
       </c>
       <c r="H152">
-        <v>0.005620576588693917</v>
+        <v>0.005859209838069268</v>
       </c>
       <c r="I152">
-        <v>0.206804237298063</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J152">
-        <v>0.7899470337742129</v>
+        <v>0.7797551195308166</v>
       </c>
       <c r="K152">
         <v>2.41</v>
@@ -8460,16 +8442,16 @@
         <v>4.05</v>
       </c>
       <c r="M152">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N152">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O152">
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8480,28 +8462,28 @@
         <v>36</v>
       </c>
       <c r="C153">
-        <v>2.145080586568228</v>
+        <v>2.17227793480229</v>
       </c>
       <c r="D153" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E153">
-        <v>1.938314426018246</v>
+        <v>2.102277934802291</v>
       </c>
       <c r="F153">
         <v>-1</v>
       </c>
       <c r="G153">
-        <v>0.005954919413431771</v>
+        <v>0.00592772206519771</v>
       </c>
       <c r="H153">
-        <v>0.005621685573981754</v>
+        <v>0.005857722065197709</v>
       </c>
       <c r="I153">
-        <v>0.2067661605499826</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J153">
-        <v>0.7904229931252164</v>
+        <v>0.7791377863890909</v>
       </c>
       <c r="K153">
         <v>2.41</v>
@@ -8510,16 +8492,16 @@
         <v>4.05</v>
       </c>
       <c r="M153">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N153">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O153">
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8530,28 +8512,28 @@
         <v>36</v>
       </c>
       <c r="C154">
-        <v>2.14339129660172</v>
+        <v>2.17517405209197</v>
       </c>
       <c r="D154" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E154">
-        <v>1.936681212067224</v>
+        <v>2.10517405209197</v>
       </c>
       <c r="F154">
         <v>-1</v>
       </c>
       <c r="G154">
-        <v>0.005956608703398279</v>
+        <v>0.00592482594790803</v>
       </c>
       <c r="H154">
-        <v>0.005623318787932776</v>
+        <v>0.00585482594790803</v>
       </c>
       <c r="I154">
-        <v>0.2067100845344967</v>
+        <v>0.06999999999999984</v>
       </c>
       <c r="J154">
-        <v>0.791123943318788</v>
+        <v>0.777936077970137</v>
       </c>
       <c r="K154">
         <v>2.41</v>
@@ -8560,16 +8542,16 @@
         <v>4.05</v>
       </c>
       <c r="M154">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N154">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O154">
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8580,28 +8562,28 @@
         <v>36</v>
       </c>
       <c r="C155">
-        <v>2.142284300015975</v>
+        <v>2.176658657571009</v>
       </c>
       <c r="D155" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E155">
-        <v>1.935610962256108</v>
+        <v>2.106658657571009</v>
       </c>
       <c r="F155">
         <v>-1</v>
       </c>
       <c r="G155">
-        <v>0.005957715699984025</v>
+        <v>0.005923341342428991</v>
       </c>
       <c r="H155">
-        <v>0.005624389037743892</v>
+        <v>0.005853341342428991</v>
       </c>
       <c r="I155">
-        <v>0.2066733377598666</v>
+        <v>0.07000000000000028</v>
       </c>
       <c r="J155">
-        <v>0.7915832780016702</v>
+        <v>0.7773200590991663</v>
       </c>
       <c r="K155">
         <v>2.41</v>
@@ -8610,16 +8592,16 @@
         <v>4.05</v>
       </c>
       <c r="M155">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N155">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O155">
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8627,49 +8609,49 @@
         <v>0</v>
       </c>
       <c r="B156" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C156">
-        <v>2.143425559712756</v>
+        <v>1.57348881425233</v>
       </c>
       <c r="D156" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="E156">
-        <v>1.936714337813577</v>
+        <v>1.930716141714586</v>
       </c>
       <c r="F156">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G156">
-        <v>0.005956574440287244</v>
+        <v>0.004646511185747669</v>
       </c>
       <c r="H156">
-        <v>0.005623285662186422</v>
+        <v>0.005949283858285414</v>
       </c>
       <c r="I156">
-        <v>0.2067112218991787</v>
+        <v>0.3572273274622557</v>
       </c>
       <c r="J156">
-        <v>0.7911097262602672</v>
+        <v>0.7879544542295741</v>
       </c>
       <c r="K156">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="L156">
-        <v>4.05</v>
+        <v>3.11</v>
       </c>
       <c r="M156">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="N156">
-        <v>3.78</v>
+        <v>3.94</v>
       </c>
       <c r="O156">
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8677,49 +8659,49 @@
         <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C157">
-        <v>2.144968519714193</v>
+        <v>1.569608330766713</v>
       </c>
       <c r="D157" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="E157">
-        <v>1.938206079225755</v>
+        <v>1.925641663310317</v>
       </c>
       <c r="F157">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G157">
-        <v>0.005955031480285808</v>
+        <v>0.004650391669233286</v>
       </c>
       <c r="H157">
-        <v>0.005621793920774245</v>
+        <v>0.005954358336689684</v>
       </c>
       <c r="I157">
-        <v>0.2067624404884378</v>
+        <v>0.3560333325436043</v>
       </c>
       <c r="J157">
-        <v>0.7904694938945258</v>
+        <v>0.78994444576066</v>
       </c>
       <c r="K157">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="L157">
-        <v>4.05</v>
+        <v>3.11</v>
       </c>
       <c r="M157">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="N157">
-        <v>3.78</v>
+        <v>3.94</v>
       </c>
       <c r="O157">
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8727,49 +8709,49 @@
         <v>0</v>
       </c>
       <c r="B158" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C158">
-        <v>2.148138038800297</v>
+        <v>1.563290930299889</v>
       </c>
       <c r="D158" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="E158">
-        <v>1.941270386060038</v>
+        <v>1.91738044731524</v>
       </c>
       <c r="F158">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G158">
-        <v>0.005951861961199702</v>
+        <v>0.00465670906970011</v>
       </c>
       <c r="H158">
-        <v>0.005618729613939962</v>
+        <v>0.005962619552684761</v>
       </c>
       <c r="I158">
-        <v>0.2068676527402589</v>
+        <v>0.3540895170153506</v>
       </c>
       <c r="J158">
-        <v>0.7891543407467646</v>
+        <v>0.7931841383077493</v>
       </c>
       <c r="K158">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="L158">
-        <v>4.05</v>
+        <v>3.11</v>
       </c>
       <c r="M158">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="N158">
-        <v>3.78</v>
+        <v>3.94</v>
       </c>
       <c r="O158">
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -8777,49 +8759,49 @@
         <v>0</v>
       </c>
       <c r="B159" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C159">
-        <v>2.151907493357466</v>
+        <v>1.59179529224936</v>
       </c>
       <c r="D159" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="E159">
-        <v>1.944914713494977</v>
+        <v>1.912426863301427</v>
       </c>
       <c r="F159">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G159">
-        <v>0.005948092506642534</v>
+        <v>0.00478820470775064</v>
       </c>
       <c r="H159">
-        <v>0.005615085286505023</v>
+        <v>0.005967573136698573</v>
       </c>
       <c r="I159">
-        <v>0.2069927798624884</v>
+        <v>0.3206315710520669</v>
       </c>
       <c r="J159">
-        <v>0.7875902517188939</v>
+        <v>0.7951267202739504</v>
       </c>
       <c r="K159">
-        <v>2.41</v>
+        <v>2.01</v>
       </c>
       <c r="L159">
-        <v>4.05</v>
+        <v>3.19</v>
       </c>
       <c r="M159">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="N159">
-        <v>3.78</v>
+        <v>3.94</v>
       </c>
       <c r="O159">
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -8827,49 +8809,49 @@
         <v>0</v>
       </c>
       <c r="B160" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C160">
-        <v>2.1538020117046</v>
+        <v>1.590146235974642</v>
       </c>
       <c r="D160" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="E160">
-        <v>1.946746343266273</v>
+        <v>1.910334776982754</v>
       </c>
       <c r="F160">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G160">
-        <v>0.005946197988295399</v>
+        <v>0.004789853764025359</v>
       </c>
       <c r="H160">
-        <v>0.005613253656733727</v>
+        <v>0.005969665223017246</v>
       </c>
       <c r="I160">
-        <v>0.2070556684383269</v>
+        <v>0.3201885410081127</v>
       </c>
       <c r="J160">
-        <v>0.7868041445209126</v>
+        <v>0.7959471462812728</v>
       </c>
       <c r="K160">
-        <v>2.41</v>
+        <v>2.01</v>
       </c>
       <c r="L160">
-        <v>4.05</v>
+        <v>3.19</v>
       </c>
       <c r="M160">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="N160">
-        <v>3.78</v>
+        <v>3.94</v>
       </c>
       <c r="O160">
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -8880,28 +8862,28 @@
         <v>36</v>
       </c>
       <c r="C161">
-        <v>2.157161945588962</v>
+        <v>2.134728112347791</v>
       </c>
       <c r="D161" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E161">
-        <v>1.949994744075635</v>
+        <v>2.06472811234779</v>
       </c>
       <c r="F161">
         <v>-1</v>
       </c>
       <c r="G161">
-        <v>0.005942838054411038</v>
+        <v>0.005965271887652209</v>
       </c>
       <c r="H161">
-        <v>0.005610005255924365</v>
+        <v>0.00589527188765221</v>
       </c>
       <c r="I161">
-        <v>0.2071672015133268</v>
+        <v>0.07000000000000028</v>
       </c>
       <c r="J161">
-        <v>0.7854099810834182</v>
+        <v>0.7947186255818296</v>
       </c>
       <c r="K161">
         <v>2.41</v>
@@ -8910,16 +8892,16 @@
         <v>4.05</v>
       </c>
       <c r="M161">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="N161">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="O161">
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -8930,28 +8912,28 @@
         <v>36</v>
       </c>
       <c r="C162">
-        <v>2.161672330968959</v>
+        <v>2.126802703854744</v>
       </c>
       <c r="D162" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E162">
-        <v>1.954355407119367</v>
+        <v>1.920643278000645</v>
       </c>
       <c r="F162">
         <v>-1</v>
       </c>
       <c r="G162">
-        <v>0.005938327669031041</v>
+        <v>0.005973197296145255</v>
       </c>
       <c r="H162">
-        <v>0.005605644592880633</v>
+        <v>0.005639356721999355</v>
       </c>
       <c r="I162">
-        <v>0.207316923849592</v>
+        <v>0.2061594258540995</v>
       </c>
       <c r="J162">
-        <v>0.7835384518800999</v>
+        <v>0.7980071768237574</v>
       </c>
       <c r="K162">
         <v>2.41</v>
@@ -8969,7 +8951,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -8980,28 +8962,28 @@
         <v>36</v>
       </c>
       <c r="C163">
-        <v>2.162884754387039</v>
+        <v>2.118150939933342</v>
       </c>
       <c r="D163" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E163">
-        <v>1.95552758411693</v>
+        <v>1.912278709562111</v>
       </c>
       <c r="F163">
         <v>-1</v>
       </c>
       <c r="G163">
-        <v>0.00593711524561296</v>
+        <v>0.005981849060066658</v>
       </c>
       <c r="H163">
-        <v>0.005604472415883069</v>
+        <v>0.00564772129043789</v>
       </c>
       <c r="I163">
-        <v>0.2073571702701089</v>
+        <v>0.2058722303712313</v>
       </c>
       <c r="J163">
-        <v>0.783035371623635</v>
+        <v>0.8015971203596091</v>
       </c>
       <c r="K163">
         <v>2.41</v>
@@ -9019,7 +9001,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9030,28 +9012,28 @@
         <v>36</v>
       </c>
       <c r="C164">
-        <v>2.16447911025038</v>
+        <v>2.102390273794673</v>
       </c>
       <c r="D164" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E164">
-        <v>1.957069015304309</v>
+        <v>1.8970412190629</v>
       </c>
       <c r="F164">
         <v>-1</v>
       </c>
       <c r="G164">
-        <v>0.00593552088974962</v>
+        <v>0.005997609726205327</v>
       </c>
       <c r="H164">
-        <v>0.005602930984695691</v>
+        <v>0.0056629587809371</v>
       </c>
       <c r="I164">
-        <v>0.2074100949460704</v>
+        <v>0.2053490547317733</v>
       </c>
       <c r="J164">
-        <v>0.7823738131741161</v>
+        <v>0.8081368158528327</v>
       </c>
       <c r="K164">
         <v>2.41</v>
@@ -9069,7 +9051,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9080,28 +9062,28 @@
         <v>36</v>
       </c>
       <c r="C165">
-        <v>2.168006663995569</v>
+        <v>2.068262994068838</v>
       </c>
       <c r="D165" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E165">
-        <v>1.960479471829741</v>
+        <v>1.864046795095599</v>
       </c>
       <c r="F165">
         <v>-1</v>
       </c>
       <c r="G165">
-        <v>0.005931993336004431</v>
+        <v>0.006031737005931162</v>
       </c>
       <c r="H165">
-        <v>0.005599520528170259</v>
+        <v>0.005695953204904402</v>
       </c>
       <c r="I165">
-        <v>0.2075271921658277</v>
+        <v>0.2042161989732392</v>
       </c>
       <c r="J165">
-        <v>0.7809100979271496</v>
+        <v>0.8222975128345069</v>
       </c>
       <c r="K165">
         <v>2.41</v>
@@ -9119,7 +9101,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>142</v>
+        <v>32</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9130,28 +9112,28 @@
         <v>36</v>
       </c>
       <c r="C166">
-        <v>2.16983540706272</v>
+        <v>2.026595514500883</v>
       </c>
       <c r="D166" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E166">
-        <v>1.962247509732838</v>
+        <v>1.823762468376372</v>
       </c>
       <c r="F166">
         <v>-1</v>
       </c>
       <c r="G166">
-        <v>0.005930164592937279</v>
+        <v>0.006073404485499117</v>
       </c>
       <c r="H166">
-        <v>0.005597752490267162</v>
+        <v>0.005736237531623627</v>
       </c>
       <c r="I166">
-        <v>0.2075878973298828</v>
+        <v>0.2028330461245107</v>
       </c>
       <c r="J166">
-        <v>0.7801512833764644</v>
+        <v>0.8395869234436169</v>
       </c>
       <c r="K166">
         <v>2.41</v>
@@ -9169,7 +9151,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9180,28 +9162,28 @@
         <v>36</v>
       </c>
       <c r="C167">
-        <v>2.170790161930732</v>
+        <v>2.00904612221926</v>
       </c>
       <c r="D167" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E167">
-        <v>1.963170571493197</v>
+        <v>1.806795628535633</v>
       </c>
       <c r="F167">
         <v>-1</v>
       </c>
       <c r="G167">
-        <v>0.005929209838069268</v>
+        <v>0.006090953877780739</v>
       </c>
       <c r="H167">
-        <v>0.005596829428506803</v>
+        <v>0.005753204371464368</v>
       </c>
       <c r="I167">
-        <v>0.2076195904375346</v>
+        <v>0.2022504936836271</v>
       </c>
       <c r="J167">
-        <v>0.7797551195308166</v>
+        <v>0.846868828954664</v>
       </c>
       <c r="K167">
         <v>2.41</v>
@@ -9219,7 +9201,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9230,28 +9212,28 @@
         <v>36</v>
       </c>
       <c r="C168">
-        <v>2.17227793480229</v>
+        <v>1.99410787626086</v>
       </c>
       <c r="D168" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E168">
-        <v>1.964608957713418</v>
+        <v>1.792353257961744</v>
       </c>
       <c r="F168">
         <v>-1</v>
       </c>
       <c r="G168">
-        <v>0.00592772206519771</v>
+        <v>0.00610589212373914</v>
       </c>
       <c r="H168">
-        <v>0.005595391042286581</v>
+        <v>0.005767646742038256</v>
       </c>
       <c r="I168">
-        <v>0.2076689770888727</v>
+        <v>0.2017546182991157</v>
       </c>
       <c r="J168">
-        <v>0.7791377863890909</v>
+        <v>0.8530672712610541</v>
       </c>
       <c r="K168">
         <v>2.41</v>
@@ -9269,7 +9251,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>145</v>
+        <v>24</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9280,28 +9262,28 @@
         <v>36</v>
       </c>
       <c r="C169">
-        <v>2.17517405209197</v>
+        <v>1.97566667479463</v>
       </c>
       <c r="D169" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E169">
-        <v>1.967408938329581</v>
+        <v>1.774524212560784</v>
       </c>
       <c r="F169">
         <v>-1</v>
       </c>
       <c r="G169">
-        <v>0.00592482594790803</v>
+        <v>0.00612433332520537</v>
       </c>
       <c r="H169">
-        <v>0.005592591061670419</v>
+        <v>0.005785475787439216</v>
       </c>
       <c r="I169">
-        <v>0.207765113762389</v>
+        <v>0.2011424622338467</v>
       </c>
       <c r="J169">
-        <v>0.777936077970137</v>
+        <v>0.8607192220769168</v>
       </c>
       <c r="K169">
         <v>2.41</v>
@@ -9319,7 +9301,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>146</v>
+        <v>26</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9330,28 +9312,28 @@
         <v>36</v>
       </c>
       <c r="C170">
-        <v>2.176658657571009</v>
+        <v>1.955884214730955</v>
       </c>
       <c r="D170" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E170">
-        <v>1.968844262298942</v>
+        <v>1.755398431669347</v>
       </c>
       <c r="F170">
         <v>-1</v>
       </c>
       <c r="G170">
-        <v>0.005923341342428991</v>
+        <v>0.006144115785269044</v>
       </c>
       <c r="H170">
-        <v>0.005591155737701057</v>
+        <v>0.005804601568330653</v>
       </c>
       <c r="I170">
-        <v>0.2078143952720668</v>
+        <v>0.2004857830616085</v>
       </c>
       <c r="J170">
-        <v>0.7773200590991663</v>
+        <v>0.8689277117298939</v>
       </c>
       <c r="K170">
         <v>2.41</v>
@@ -9369,7 +9351,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9380,28 +9362,28 @@
         <v>36</v>
       </c>
       <c r="C171">
-        <v>2.179386080861772</v>
+        <v>1.938792565740484</v>
       </c>
       <c r="D171" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E171">
-        <v>1.971481148716983</v>
+        <v>1.783833353031098</v>
       </c>
       <c r="F171">
         <v>-1</v>
       </c>
       <c r="G171">
-        <v>0.005920613919138227</v>
+        <v>0.006161207434259517</v>
       </c>
       <c r="H171">
-        <v>0.005588518851283016</v>
+        <v>0.005936166646968902</v>
       </c>
       <c r="I171">
-        <v>0.2079049321447892</v>
+        <v>0.1549592127093855</v>
       </c>
       <c r="J171">
-        <v>0.7761883481901358</v>
+        <v>0.8760196822653594</v>
       </c>
       <c r="K171">
         <v>2.41</v>
@@ -9410,16 +9392,16 @@
         <v>4.05</v>
       </c>
       <c r="M171">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="N171">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="O171">
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>148</v>
+        <v>29</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9430,28 +9412,28 @@
         <v>36</v>
       </c>
       <c r="C172">
-        <v>2.182571074608897</v>
+        <v>1.907679309834471</v>
       </c>
       <c r="D172" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E172">
-        <v>1.974560416530593</v>
+        <v>1.753236499712738</v>
       </c>
       <c r="F172">
         <v>-1</v>
       </c>
       <c r="G172">
-        <v>0.005917428925391103</v>
+        <v>0.006192320690165529</v>
       </c>
       <c r="H172">
-        <v>0.005585439583469407</v>
+        <v>0.005966763500287263</v>
       </c>
       <c r="I172">
-        <v>0.2080106580783037</v>
+        <v>0.1544428101217337</v>
       </c>
       <c r="J172">
-        <v>0.7748667740212044</v>
+        <v>0.8889297469566507</v>
       </c>
       <c r="K172">
         <v>2.41</v>
@@ -9460,16 +9442,16 @@
         <v>4.05</v>
       </c>
       <c r="M172">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="N172">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="O172">
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9480,28 +9462,28 @@
         <v>36</v>
       </c>
       <c r="C173">
-        <v>2.185730109854243</v>
+        <v>1.884046836214932</v>
       </c>
       <c r="D173" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E173">
-        <v>1.97761458753543</v>
+        <v>1.729996266319249</v>
       </c>
       <c r="F173">
         <v>-1</v>
       </c>
       <c r="G173">
-        <v>0.005914269890145757</v>
+        <v>0.006215953163785068</v>
       </c>
       <c r="H173">
-        <v>0.00558238541246457</v>
+        <v>0.005990003733680751</v>
       </c>
       <c r="I173">
-        <v>0.2081155223188127</v>
+        <v>0.1540505698956833</v>
       </c>
       <c r="J173">
-        <v>0.7735559710148369</v>
+        <v>0.8987357526079118</v>
       </c>
       <c r="K173">
         <v>2.41</v>
@@ -9510,16 +9492,16 @@
         <v>4.05</v>
       </c>
       <c r="M173">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="N173">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="O173">
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9530,28 +9512,28 @@
         <v>36</v>
       </c>
       <c r="C174">
-        <v>2.187649692044639</v>
+        <v>1.866414391842988</v>
       </c>
       <c r="D174" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E174">
-        <v>1.979470449155191</v>
+        <v>1.712656476625677</v>
       </c>
       <c r="F174">
         <v>-1</v>
       </c>
       <c r="G174">
-        <v>0.005912350307955361</v>
+        <v>0.006233585608157012</v>
       </c>
       <c r="H174">
-        <v>0.005580529550844809</v>
+        <v>0.006007343523374323</v>
       </c>
       <c r="I174">
-        <v>0.2081792428894487</v>
+        <v>0.153757915217311</v>
       </c>
       <c r="J174">
-        <v>0.7727594638818923</v>
+        <v>0.906052119567225</v>
       </c>
       <c r="K174">
         <v>2.41</v>
@@ -9560,16 +9542,16 @@
         <v>4.05</v>
       </c>
       <c r="M174">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="N174">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="O174">
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>151</v>
+        <v>27</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9580,28 +9562,28 @@
         <v>36</v>
       </c>
       <c r="C175">
-        <v>2.18845970117501</v>
+        <v>1.846516388844341</v>
       </c>
       <c r="D175" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E175">
-        <v>1.980253570015674</v>
+        <v>1.693088730938211</v>
       </c>
       <c r="F175">
         <v>-1</v>
       </c>
       <c r="G175">
-        <v>0.005911540298824991</v>
+        <v>0.006253483611155659</v>
       </c>
       <c r="H175">
-        <v>0.005579746429984326</v>
+        <v>0.006026911269061789</v>
       </c>
       <c r="I175">
-        <v>0.2082061311593364</v>
+        <v>0.1534276579061298</v>
       </c>
       <c r="J175">
-        <v>0.7724233605082945</v>
+        <v>0.9143085523467465</v>
       </c>
       <c r="K175">
         <v>2.41</v>
@@ -9610,1066 +9592,16 @@
         <v>4.05</v>
       </c>
       <c r="M175">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="N175">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="O175">
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="176" spans="1:16">
-      <c r="A176" s="1">
-        <v>0</v>
-      </c>
-      <c r="B176" t="s">
-        <v>40</v>
-      </c>
-      <c r="C176">
-        <v>1.57348881425233</v>
-      </c>
-      <c r="D176" t="s">
-        <v>25</v>
-      </c>
-      <c r="E176">
-        <v>1.930716141714586</v>
-      </c>
-      <c r="F176">
-        <v>1</v>
-      </c>
-      <c r="G176">
-        <v>0.004646511185747669</v>
-      </c>
-      <c r="H176">
-        <v>0.005949283858285414</v>
-      </c>
-      <c r="I176">
-        <v>0.3572273274622557</v>
-      </c>
-      <c r="J176">
-        <v>0.7879544542295741</v>
-      </c>
-      <c r="K176">
-        <v>1.95</v>
-      </c>
-      <c r="L176">
-        <v>3.11</v>
-      </c>
-      <c r="M176">
-        <v>2.55</v>
-      </c>
-      <c r="N176">
-        <v>3.94</v>
-      </c>
-      <c r="O176">
-        <v>1</v>
-      </c>
-      <c r="P176" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="177" spans="1:16">
-      <c r="A177" s="1">
-        <v>0</v>
-      </c>
-      <c r="B177" t="s">
-        <v>40</v>
-      </c>
-      <c r="C177">
-        <v>1.569608330766713</v>
-      </c>
-      <c r="D177" t="s">
-        <v>25</v>
-      </c>
-      <c r="E177">
-        <v>1.925641663310317</v>
-      </c>
-      <c r="F177">
-        <v>1</v>
-      </c>
-      <c r="G177">
-        <v>0.004650391669233286</v>
-      </c>
-      <c r="H177">
-        <v>0.005954358336689684</v>
-      </c>
-      <c r="I177">
-        <v>0.3560333325436043</v>
-      </c>
-      <c r="J177">
-        <v>0.78994444576066</v>
-      </c>
-      <c r="K177">
-        <v>1.95</v>
-      </c>
-      <c r="L177">
-        <v>3.11</v>
-      </c>
-      <c r="M177">
-        <v>2.55</v>
-      </c>
-      <c r="N177">
-        <v>3.94</v>
-      </c>
-      <c r="O177">
-        <v>1</v>
-      </c>
-      <c r="P177" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="178" spans="1:16">
-      <c r="A178" s="1">
-        <v>0</v>
-      </c>
-      <c r="B178" t="s">
-        <v>40</v>
-      </c>
-      <c r="C178">
-        <v>1.563290930299889</v>
-      </c>
-      <c r="D178" t="s">
-        <v>25</v>
-      </c>
-      <c r="E178">
-        <v>1.91738044731524</v>
-      </c>
-      <c r="F178">
-        <v>1</v>
-      </c>
-      <c r="G178">
-        <v>0.00465670906970011</v>
-      </c>
-      <c r="H178">
-        <v>0.005962619552684761</v>
-      </c>
-      <c r="I178">
-        <v>0.3540895170153506</v>
-      </c>
-      <c r="J178">
-        <v>0.7931841383077493</v>
-      </c>
-      <c r="K178">
-        <v>1.95</v>
-      </c>
-      <c r="L178">
-        <v>3.11</v>
-      </c>
-      <c r="M178">
-        <v>2.55</v>
-      </c>
-      <c r="N178">
-        <v>3.94</v>
-      </c>
-      <c r="O178">
-        <v>1</v>
-      </c>
-      <c r="P178" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="179" spans="1:16">
-      <c r="A179" s="1">
-        <v>0</v>
-      </c>
-      <c r="B179" t="s">
-        <v>40</v>
-      </c>
-      <c r="C179">
-        <v>1.559502895465797</v>
-      </c>
-      <c r="D179" t="s">
-        <v>25</v>
-      </c>
-      <c r="E179">
-        <v>1.912426863301427</v>
-      </c>
-      <c r="F179">
-        <v>1</v>
-      </c>
-      <c r="G179">
-        <v>0.004660497104534203</v>
-      </c>
-      <c r="H179">
-        <v>0.005967573136698573</v>
-      </c>
-      <c r="I179">
-        <v>0.35292396783563</v>
-      </c>
-      <c r="J179">
-        <v>0.7951267202739504</v>
-      </c>
-      <c r="K179">
-        <v>1.95</v>
-      </c>
-      <c r="L179">
-        <v>3.11</v>
-      </c>
-      <c r="M179">
-        <v>2.55</v>
-      </c>
-      <c r="N179">
-        <v>3.94</v>
-      </c>
-      <c r="O179">
-        <v>1</v>
-      </c>
-      <c r="P179" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="180" spans="1:16">
-      <c r="A180" s="1">
-        <v>0</v>
-      </c>
-      <c r="B180" t="s">
-        <v>41</v>
-      </c>
-      <c r="C180">
-        <v>1.590146235974642</v>
-      </c>
-      <c r="D180" t="s">
-        <v>25</v>
-      </c>
-      <c r="E180">
-        <v>1.910334776982754</v>
-      </c>
-      <c r="F180">
-        <v>1</v>
-      </c>
-      <c r="G180">
-        <v>0.004789853764025359</v>
-      </c>
-      <c r="H180">
-        <v>0.005969665223017246</v>
-      </c>
-      <c r="I180">
-        <v>0.3201885410081127</v>
-      </c>
-      <c r="J180">
-        <v>0.7959471462812728</v>
-      </c>
-      <c r="K180">
-        <v>2.01</v>
-      </c>
-      <c r="L180">
-        <v>3.19</v>
-      </c>
-      <c r="M180">
-        <v>2.55</v>
-      </c>
-      <c r="N180">
-        <v>3.94</v>
-      </c>
-      <c r="O180">
-        <v>1</v>
-      </c>
-      <c r="P180" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="181" spans="1:16">
-      <c r="A181" s="1">
-        <v>0</v>
-      </c>
-      <c r="B181" t="s">
-        <v>36</v>
-      </c>
-      <c r="C181">
-        <v>2.134728112347791</v>
-      </c>
-      <c r="D181" t="s">
-        <v>57</v>
-      </c>
-      <c r="E181">
-        <v>1.928305602394337</v>
-      </c>
-      <c r="F181">
-        <v>-1</v>
-      </c>
-      <c r="G181">
-        <v>0.005965271887652209</v>
-      </c>
-      <c r="H181">
-        <v>0.005631694397605662</v>
-      </c>
-      <c r="I181">
-        <v>0.2064225099534538</v>
-      </c>
-      <c r="J181">
-        <v>0.7947186255818296</v>
-      </c>
-      <c r="K181">
-        <v>2.41</v>
-      </c>
-      <c r="L181">
-        <v>4.05</v>
-      </c>
-      <c r="M181">
-        <v>2.33</v>
-      </c>
-      <c r="N181">
-        <v>3.78</v>
-      </c>
-      <c r="O181">
-        <v>1</v>
-      </c>
-      <c r="P181" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="182" spans="1:16">
-      <c r="A182" s="1">
-        <v>0</v>
-      </c>
-      <c r="B182" t="s">
-        <v>36</v>
-      </c>
-      <c r="C182">
-        <v>2.126802703854744</v>
-      </c>
-      <c r="D182" t="s">
-        <v>57</v>
-      </c>
-      <c r="E182">
-        <v>1.920643278000645</v>
-      </c>
-      <c r="F182">
-        <v>-1</v>
-      </c>
-      <c r="G182">
-        <v>0.005973197296145255</v>
-      </c>
-      <c r="H182">
-        <v>0.005639356721999355</v>
-      </c>
-      <c r="I182">
-        <v>0.2061594258540995</v>
-      </c>
-      <c r="J182">
-        <v>0.7980071768237574</v>
-      </c>
-      <c r="K182">
-        <v>2.41</v>
-      </c>
-      <c r="L182">
-        <v>4.05</v>
-      </c>
-      <c r="M182">
-        <v>2.33</v>
-      </c>
-      <c r="N182">
-        <v>3.78</v>
-      </c>
-      <c r="O182">
-        <v>1</v>
-      </c>
-      <c r="P182" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="183" spans="1:16">
-      <c r="A183" s="1">
-        <v>0</v>
-      </c>
-      <c r="B183" t="s">
-        <v>36</v>
-      </c>
-      <c r="C183">
-        <v>2.118150939933342</v>
-      </c>
-      <c r="D183" t="s">
-        <v>57</v>
-      </c>
-      <c r="E183">
-        <v>1.912278709562111</v>
-      </c>
-      <c r="F183">
-        <v>-1</v>
-      </c>
-      <c r="G183">
-        <v>0.005981849060066658</v>
-      </c>
-      <c r="H183">
-        <v>0.00564772129043789</v>
-      </c>
-      <c r="I183">
-        <v>0.2058722303712313</v>
-      </c>
-      <c r="J183">
-        <v>0.8015971203596091</v>
-      </c>
-      <c r="K183">
-        <v>2.41</v>
-      </c>
-      <c r="L183">
-        <v>4.05</v>
-      </c>
-      <c r="M183">
-        <v>2.33</v>
-      </c>
-      <c r="N183">
-        <v>3.78</v>
-      </c>
-      <c r="O183">
-        <v>1</v>
-      </c>
-      <c r="P183" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="184" spans="1:16">
-      <c r="A184" s="1">
-        <v>0</v>
-      </c>
-      <c r="B184" t="s">
-        <v>36</v>
-      </c>
-      <c r="C184">
-        <v>2.102390273794673</v>
-      </c>
-      <c r="D184" t="s">
-        <v>57</v>
-      </c>
-      <c r="E184">
-        <v>1.8970412190629</v>
-      </c>
-      <c r="F184">
-        <v>-1</v>
-      </c>
-      <c r="G184">
-        <v>0.005997609726205327</v>
-      </c>
-      <c r="H184">
-        <v>0.0056629587809371</v>
-      </c>
-      <c r="I184">
-        <v>0.2053490547317733</v>
-      </c>
-      <c r="J184">
-        <v>0.8081368158528327</v>
-      </c>
-      <c r="K184">
-        <v>2.41</v>
-      </c>
-      <c r="L184">
-        <v>4.05</v>
-      </c>
-      <c r="M184">
-        <v>2.33</v>
-      </c>
-      <c r="N184">
-        <v>3.78</v>
-      </c>
-      <c r="O184">
-        <v>1</v>
-      </c>
-      <c r="P184" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="185" spans="1:16">
-      <c r="A185" s="1">
-        <v>0</v>
-      </c>
-      <c r="B185" t="s">
-        <v>36</v>
-      </c>
-      <c r="C185">
-        <v>2.068262994068838</v>
-      </c>
-      <c r="D185" t="s">
-        <v>57</v>
-      </c>
-      <c r="E185">
-        <v>1.864046795095599</v>
-      </c>
-      <c r="F185">
-        <v>-1</v>
-      </c>
-      <c r="G185">
-        <v>0.006031737005931162</v>
-      </c>
-      <c r="H185">
-        <v>0.005695953204904402</v>
-      </c>
-      <c r="I185">
-        <v>0.2042161989732392</v>
-      </c>
-      <c r="J185">
-        <v>0.8222975128345069</v>
-      </c>
-      <c r="K185">
-        <v>2.41</v>
-      </c>
-      <c r="L185">
-        <v>4.05</v>
-      </c>
-      <c r="M185">
-        <v>2.33</v>
-      </c>
-      <c r="N185">
-        <v>3.78</v>
-      </c>
-      <c r="O185">
-        <v>1</v>
-      </c>
-      <c r="P185" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="186" spans="1:16">
-      <c r="A186" s="1">
-        <v>0</v>
-      </c>
-      <c r="B186" t="s">
-        <v>36</v>
-      </c>
-      <c r="C186">
-        <v>2.026595514500883</v>
-      </c>
-      <c r="D186" t="s">
-        <v>57</v>
-      </c>
-      <c r="E186">
-        <v>1.823762468376372</v>
-      </c>
-      <c r="F186">
-        <v>-1</v>
-      </c>
-      <c r="G186">
-        <v>0.006073404485499117</v>
-      </c>
-      <c r="H186">
-        <v>0.005736237531623627</v>
-      </c>
-      <c r="I186">
-        <v>0.2028330461245107</v>
-      </c>
-      <c r="J186">
-        <v>0.8395869234436169</v>
-      </c>
-      <c r="K186">
-        <v>2.41</v>
-      </c>
-      <c r="L186">
-        <v>4.05</v>
-      </c>
-      <c r="M186">
-        <v>2.33</v>
-      </c>
-      <c r="N186">
-        <v>3.78</v>
-      </c>
-      <c r="O186">
-        <v>1</v>
-      </c>
-      <c r="P186" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="187" spans="1:16">
-      <c r="A187" s="1">
-        <v>0</v>
-      </c>
-      <c r="B187" t="s">
-        <v>36</v>
-      </c>
-      <c r="C187">
-        <v>2.00904612221926</v>
-      </c>
-      <c r="D187" t="s">
-        <v>57</v>
-      </c>
-      <c r="E187">
-        <v>1.806795628535633</v>
-      </c>
-      <c r="F187">
-        <v>-1</v>
-      </c>
-      <c r="G187">
-        <v>0.006090953877780739</v>
-      </c>
-      <c r="H187">
-        <v>0.005753204371464368</v>
-      </c>
-      <c r="I187">
-        <v>0.2022504936836271</v>
-      </c>
-      <c r="J187">
-        <v>0.846868828954664</v>
-      </c>
-      <c r="K187">
-        <v>2.41</v>
-      </c>
-      <c r="L187">
-        <v>4.05</v>
-      </c>
-      <c r="M187">
-        <v>2.33</v>
-      </c>
-      <c r="N187">
-        <v>3.78</v>
-      </c>
-      <c r="O187">
-        <v>1</v>
-      </c>
-      <c r="P187" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="188" spans="1:16">
-      <c r="A188" s="1">
-        <v>0</v>
-      </c>
-      <c r="B188" t="s">
-        <v>36</v>
-      </c>
-      <c r="C188">
-        <v>1.99410787626086</v>
-      </c>
-      <c r="D188" t="s">
-        <v>57</v>
-      </c>
-      <c r="E188">
-        <v>1.792353257961744</v>
-      </c>
-      <c r="F188">
-        <v>-1</v>
-      </c>
-      <c r="G188">
-        <v>0.00610589212373914</v>
-      </c>
-      <c r="H188">
-        <v>0.005767646742038256</v>
-      </c>
-      <c r="I188">
-        <v>0.2017546182991157</v>
-      </c>
-      <c r="J188">
-        <v>0.8530672712610541</v>
-      </c>
-      <c r="K188">
-        <v>2.41</v>
-      </c>
-      <c r="L188">
-        <v>4.05</v>
-      </c>
-      <c r="M188">
-        <v>2.33</v>
-      </c>
-      <c r="N188">
-        <v>3.78</v>
-      </c>
-      <c r="O188">
-        <v>1</v>
-      </c>
-      <c r="P188" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="189" spans="1:16">
-      <c r="A189" s="1">
-        <v>0</v>
-      </c>
-      <c r="B189" t="s">
-        <v>36</v>
-      </c>
-      <c r="C189">
-        <v>1.97566667479463</v>
-      </c>
-      <c r="D189" t="s">
-        <v>57</v>
-      </c>
-      <c r="E189">
-        <v>1.774524212560784</v>
-      </c>
-      <c r="F189">
-        <v>-1</v>
-      </c>
-      <c r="G189">
-        <v>0.00612433332520537</v>
-      </c>
-      <c r="H189">
-        <v>0.005785475787439216</v>
-      </c>
-      <c r="I189">
-        <v>0.2011424622338467</v>
-      </c>
-      <c r="J189">
-        <v>0.8607192220769168</v>
-      </c>
-      <c r="K189">
-        <v>2.41</v>
-      </c>
-      <c r="L189">
-        <v>4.05</v>
-      </c>
-      <c r="M189">
-        <v>2.33</v>
-      </c>
-      <c r="N189">
-        <v>3.78</v>
-      </c>
-      <c r="O189">
-        <v>1</v>
-      </c>
-      <c r="P189" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="190" spans="1:16">
-      <c r="A190" s="1">
-        <v>0</v>
-      </c>
-      <c r="B190" t="s">
-        <v>36</v>
-      </c>
-      <c r="C190">
-        <v>1.955884214730955</v>
-      </c>
-      <c r="D190" t="s">
-        <v>57</v>
-      </c>
-      <c r="E190">
-        <v>1.755398431669347</v>
-      </c>
-      <c r="F190">
-        <v>-1</v>
-      </c>
-      <c r="G190">
-        <v>0.006144115785269044</v>
-      </c>
-      <c r="H190">
-        <v>0.005804601568330653</v>
-      </c>
-      <c r="I190">
-        <v>0.2004857830616085</v>
-      </c>
-      <c r="J190">
-        <v>0.8689277117298939</v>
-      </c>
-      <c r="K190">
-        <v>2.41</v>
-      </c>
-      <c r="L190">
-        <v>4.05</v>
-      </c>
-      <c r="M190">
-        <v>2.33</v>
-      </c>
-      <c r="N190">
-        <v>3.78</v>
-      </c>
-      <c r="O190">
-        <v>1</v>
-      </c>
-      <c r="P190" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="191" spans="1:16">
-      <c r="A191" s="1">
-        <v>0</v>
-      </c>
-      <c r="B191" t="s">
-        <v>36</v>
-      </c>
-      <c r="C191">
-        <v>1.938792565740484</v>
-      </c>
-      <c r="D191" t="s">
-        <v>57</v>
-      </c>
-      <c r="E191">
-        <v>1.738874140321713</v>
-      </c>
-      <c r="F191">
-        <v>-1</v>
-      </c>
-      <c r="G191">
-        <v>0.006161207434259517</v>
-      </c>
-      <c r="H191">
-        <v>0.005821125859678287</v>
-      </c>
-      <c r="I191">
-        <v>0.1999184254187711</v>
-      </c>
-      <c r="J191">
-        <v>0.8760196822653594</v>
-      </c>
-      <c r="K191">
-        <v>2.41</v>
-      </c>
-      <c r="L191">
-        <v>4.05</v>
-      </c>
-      <c r="M191">
-        <v>2.33</v>
-      </c>
-      <c r="N191">
-        <v>3.78</v>
-      </c>
-      <c r="O191">
-        <v>1</v>
-      </c>
-      <c r="P191" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="192" spans="1:16">
-      <c r="A192" s="1">
-        <v>0</v>
-      </c>
-      <c r="B192" t="s">
-        <v>36</v>
-      </c>
-      <c r="C192">
-        <v>1.907679309834471</v>
-      </c>
-      <c r="D192" t="s">
-        <v>57</v>
-      </c>
-      <c r="E192">
-        <v>1.708793689591003</v>
-      </c>
-      <c r="F192">
-        <v>-1</v>
-      </c>
-      <c r="G192">
-        <v>0.006192320690165529</v>
-      </c>
-      <c r="H192">
-        <v>0.005851206310408996</v>
-      </c>
-      <c r="I192">
-        <v>0.1988856202434679</v>
-      </c>
-      <c r="J192">
-        <v>0.8889297469566507</v>
-      </c>
-      <c r="K192">
-        <v>2.41</v>
-      </c>
-      <c r="L192">
-        <v>4.05</v>
-      </c>
-      <c r="M192">
-        <v>2.33</v>
-      </c>
-      <c r="N192">
-        <v>3.78</v>
-      </c>
-      <c r="O192">
-        <v>1</v>
-      </c>
-      <c r="P192" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="193" spans="1:16">
-      <c r="A193" s="1">
-        <v>0</v>
-      </c>
-      <c r="B193" t="s">
-        <v>36</v>
-      </c>
-      <c r="C193">
-        <v>1.884046836214932</v>
-      </c>
-      <c r="D193" t="s">
-        <v>57</v>
-      </c>
-      <c r="E193">
-        <v>1.685945696423565</v>
-      </c>
-      <c r="F193">
-        <v>-1</v>
-      </c>
-      <c r="G193">
-        <v>0.006215953163785068</v>
-      </c>
-      <c r="H193">
-        <v>0.005874054303576434</v>
-      </c>
-      <c r="I193">
-        <v>0.1981011397913668</v>
-      </c>
-      <c r="J193">
-        <v>0.8987357526079118</v>
-      </c>
-      <c r="K193">
-        <v>2.41</v>
-      </c>
-      <c r="L193">
-        <v>4.05</v>
-      </c>
-      <c r="M193">
-        <v>2.33</v>
-      </c>
-      <c r="N193">
-        <v>3.78</v>
-      </c>
-      <c r="O193">
-        <v>1</v>
-      </c>
-      <c r="P193" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="194" spans="1:16">
-      <c r="A194" s="1">
-        <v>0</v>
-      </c>
-      <c r="B194" t="s">
-        <v>36</v>
-      </c>
-      <c r="C194">
-        <v>1.866414391842988</v>
-      </c>
-      <c r="D194" t="s">
-        <v>60</v>
-      </c>
-      <c r="E194">
-        <v>1.712656476625677</v>
-      </c>
-      <c r="F194">
-        <v>-1</v>
-      </c>
-      <c r="G194">
-        <v>0.006233585608157012</v>
-      </c>
-      <c r="H194">
-        <v>0.006007343523374323</v>
-      </c>
-      <c r="I194">
-        <v>0.153757915217311</v>
-      </c>
-      <c r="J194">
-        <v>0.906052119567225</v>
-      </c>
-      <c r="K194">
-        <v>2.41</v>
-      </c>
-      <c r="L194">
-        <v>4.05</v>
-      </c>
-      <c r="M194">
-        <v>2.37</v>
-      </c>
-      <c r="N194">
-        <v>3.86</v>
-      </c>
-      <c r="O194">
-        <v>1</v>
-      </c>
-      <c r="P194" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="195" spans="1:16">
-      <c r="A195" s="1">
-        <v>0</v>
-      </c>
-      <c r="B195" t="s">
-        <v>36</v>
-      </c>
-      <c r="C195">
-        <v>1.846516388844341</v>
-      </c>
-      <c r="D195" t="s">
-        <v>60</v>
-      </c>
-      <c r="E195">
-        <v>1.693088730938211</v>
-      </c>
-      <c r="F195">
-        <v>-1</v>
-      </c>
-      <c r="G195">
-        <v>0.006253483611155659</v>
-      </c>
-      <c r="H195">
-        <v>0.006026911269061789</v>
-      </c>
-      <c r="I195">
-        <v>0.1534276579061298</v>
-      </c>
-      <c r="J195">
-        <v>0.9143085523467465</v>
-      </c>
-      <c r="K195">
-        <v>2.41</v>
-      </c>
-      <c r="L195">
-        <v>4.05</v>
-      </c>
-      <c r="M195">
-        <v>2.37</v>
-      </c>
-      <c r="N195">
-        <v>3.86</v>
-      </c>
-      <c r="O195">
-        <v>1</v>
-      </c>
-      <c r="P195" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="196" spans="1:16">
-      <c r="A196" s="1">
-        <v>0</v>
-      </c>
-      <c r="B196" t="s">
-        <v>36</v>
-      </c>
-      <c r="C196">
-        <v>1.830119753165329</v>
-      </c>
-      <c r="D196" t="s">
-        <v>60</v>
-      </c>
-      <c r="E196">
-        <v>1.67696423858997</v>
-      </c>
-      <c r="F196">
-        <v>-1</v>
-      </c>
-      <c r="G196">
-        <v>0.006269880246834671</v>
-      </c>
-      <c r="H196">
-        <v>0.00604303576141003</v>
-      </c>
-      <c r="I196">
-        <v>0.1531555145753583</v>
-      </c>
-      <c r="J196">
-        <v>0.9211121356160461</v>
-      </c>
-      <c r="K196">
-        <v>2.41</v>
-      </c>
-      <c r="L196">
-        <v>4.05</v>
-      </c>
-      <c r="M196">
-        <v>2.37</v>
-      </c>
-      <c r="N196">
-        <v>3.86</v>
-      </c>
-      <c r="O196">
-        <v>1</v>
-      </c>
-      <c r="P196" t="s">
-        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01618-601618.xlsx
+++ b/s60_signal/position-01618-601618.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="152">
   <si>
     <t>trade_time</t>
   </si>
@@ -115,12 +115,15 @@
     <t>2021-07-26</t>
   </si>
   <si>
+    <t>2021-01-15</t>
+  </si>
+  <si>
+    <t>2021-08-24</t>
+  </si>
+  <si>
     <t>2021-01-13</t>
   </si>
   <si>
-    <t>2021-01-15</t>
-  </si>
-  <si>
     <t>2021-02-26</t>
   </si>
   <si>
@@ -133,9 +136,6 @@
     <t>2021-02-23</t>
   </si>
   <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
     <t>2021-07-19</t>
   </si>
   <si>
@@ -175,6 +175,9 @@
     <t>2021-01-20</t>
   </si>
   <si>
+    <t>2021-08-25</t>
+  </si>
+  <si>
     <t>2021-01-26</t>
   </si>
   <si>
@@ -184,18 +187,15 @@
     <t>2021-02-03</t>
   </si>
   <si>
-    <t>2021-08-24</t>
-  </si>
-  <si>
     <t>2021-02-04</t>
   </si>
   <si>
-    <t>2021-03-09</t>
-  </si>
-  <si>
     <t>2021-08-23</t>
   </si>
   <si>
+    <t>2021-08-20</t>
+  </si>
+  <si>
     <t>2021-08-19</t>
   </si>
   <si>
@@ -445,24 +445,6 @@
     <t>2021-06-03</t>
   </si>
   <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>2021-06-07</t>
-  </si>
-  <si>
-    <t>2021-06-08</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>2021-06-10</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
     <t>2021-07-12</t>
   </si>
   <si>
@@ -475,12 +457,6 @@
     <t>2021-07-15</t>
   </si>
   <si>
-    <t>2021-07-20</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
     <t>2021-07-27</t>
   </si>
   <si>
@@ -494,9 +470,6 @@
   </si>
   <si>
     <t>2021-08-05</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
   </si>
 </sst>
 </file>
@@ -854,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P175"/>
+  <dimension ref="A1:P187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2915,7 +2888,7 @@
         <v>2.590762351351088</v>
       </c>
       <c r="D42" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E42">
         <v>2.738100964577074</v>
@@ -2965,7 +2938,7 @@
         <v>2.486972253823789</v>
       </c>
       <c r="D43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E43">
         <v>2.738100964577074</v>
@@ -3015,7 +2988,7 @@
         <v>2.532536609200432</v>
       </c>
       <c r="D44" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E44">
         <v>2.738100964577074</v>
@@ -3065,7 +3038,7 @@
         <v>2.433094415049971</v>
       </c>
       <c r="D45" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E45">
         <v>2.625826486380561</v>
@@ -3115,7 +3088,7 @@
         <v>2.481283088379385</v>
       </c>
       <c r="D46" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E46">
         <v>2.625826486380561</v>
@@ -3165,7 +3138,7 @@
         <v>2.424920823045268</v>
       </c>
       <c r="D47" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E47">
         <v>2.625826486380561</v>
@@ -3215,7 +3188,7 @@
         <v>2.311696741357657</v>
       </c>
       <c r="D48" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E48">
         <v>2.511093783008609</v>
@@ -3265,7 +3238,7 @@
         <v>2.369406800859017</v>
       </c>
       <c r="D49" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E49">
         <v>2.511093783008609</v>
@@ -3315,7 +3288,7 @@
         <v>2.314948812759289</v>
       </c>
       <c r="D50" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E50">
         <v>2.511093783008609</v>
@@ -3365,7 +3338,7 @@
         <v>2.352177806809153</v>
       </c>
       <c r="D51" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E51">
         <v>2.511093783008609</v>
@@ -3415,7 +3388,7 @@
         <v>2.286822802336969</v>
       </c>
       <c r="D52" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E52">
         <v>2.388857181452837</v>
@@ -3465,7 +3438,7 @@
         <v>2.250213434196751</v>
       </c>
       <c r="D53" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E53">
         <v>2.388857181452837</v>
@@ -3515,7 +3488,7 @@
         <v>2.197784269359359</v>
       </c>
       <c r="D54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E54">
         <v>2.388857181452837</v>
@@ -3565,7 +3538,7 @@
         <v>2.233998851778055</v>
       </c>
       <c r="D55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E55">
         <v>2.388857181452837</v>
@@ -3615,7 +3588,7 @@
         <v>2.158029045643153</v>
       </c>
       <c r="D56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E56">
         <v>2.264699999999999</v>
@@ -3665,7 +3638,7 @@
         <v>2.129147302904564</v>
       </c>
       <c r="D57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E57">
         <v>2.264699999999999</v>
@@ -3715,7 +3688,7 @@
         <v>2.078778838174274</v>
       </c>
       <c r="D58" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E58">
         <v>2.264699999999999</v>
@@ -3765,7 +3738,7 @@
         <v>2.113963070539419</v>
       </c>
       <c r="D59" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E59">
         <v>2.264699999999999</v>
@@ -3815,7 +3788,7 @@
         <v>2.009416633049714</v>
       </c>
       <c r="D60" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E60">
         <v>2.121437634259925</v>
@@ -3865,7 +3838,7 @@
         <v>1.989451635066732</v>
       </c>
       <c r="D61" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E61">
         <v>2.121437634259925</v>
@@ -3915,7 +3888,7 @@
         <v>1.975456302002334</v>
       </c>
       <c r="D62" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E62">
         <v>2.121437634259925</v>
@@ -3962,7 +3935,7 @@
         <v>33</v>
       </c>
       <c r="C63">
-        <v>1.858458903856472</v>
+        <v>1.868458903856472</v>
       </c>
       <c r="D63" t="s">
         <v>52</v>
@@ -3974,13 +3947,13 @@
         <v>-1</v>
       </c>
       <c r="G63">
-        <v>0.004661541096143528</v>
+        <v>0.004671541096143528</v>
       </c>
       <c r="H63">
         <v>0.004511000415373859</v>
       </c>
       <c r="I63">
-        <v>0.2694593192303316</v>
+        <v>0.2794593192303318</v>
       </c>
       <c r="J63">
         <v>0.8494188461475927</v>
@@ -3989,7 +3962,7 @@
         <v>1.65</v>
       </c>
       <c r="L63">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="M63">
         <v>1.72</v>
@@ -4009,43 +3982,43 @@
         <v>1</v>
       </c>
       <c r="B64" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C64">
-        <v>1.868458903856472</v>
+        <v>1.886452884631018</v>
       </c>
       <c r="D64" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E64">
-        <v>1.58899958462614</v>
+        <v>2.002900580784301</v>
       </c>
       <c r="F64">
         <v>-1</v>
       </c>
       <c r="G64">
-        <v>0.004671541096143528</v>
+        <v>0.006133547115368982</v>
       </c>
       <c r="H64">
-        <v>0.004511000415373859</v>
+        <v>0.006097099419215699</v>
       </c>
       <c r="I64">
-        <v>0.2794593192303318</v>
+        <v>-0.1164476961532834</v>
       </c>
       <c r="J64">
         <v>0.8494188461475927</v>
       </c>
       <c r="K64">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="L64">
-        <v>3.27</v>
+        <v>4.01</v>
       </c>
       <c r="M64">
-        <v>1.72</v>
+        <v>2.41</v>
       </c>
       <c r="N64">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="O64">
         <v>1</v>
@@ -4059,13 +4032,13 @@
         <v>2</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C65">
-        <v>1.886452884631018</v>
+        <v>1.873865711553157</v>
       </c>
       <c r="D65" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E65">
         <v>2.002900580784301</v>
@@ -4074,22 +4047,22 @@
         <v>-1</v>
       </c>
       <c r="G65">
-        <v>0.006133547115368982</v>
+        <v>0.005866134288446843</v>
       </c>
       <c r="H65">
         <v>0.006097099419215699</v>
       </c>
       <c r="I65">
-        <v>-0.1164476961532834</v>
+        <v>-0.1290348692311443</v>
       </c>
       <c r="J65">
         <v>0.8494188461475927</v>
       </c>
       <c r="K65">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="L65">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="M65">
         <v>2.41</v>
@@ -4109,13 +4082,13 @@
         <v>3</v>
       </c>
       <c r="B66" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C66">
-        <v>1.873865711553157</v>
+        <v>1.860854088476109</v>
       </c>
       <c r="D66" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E66">
         <v>2.002900580784301</v>
@@ -4124,22 +4097,22 @@
         <v>-1</v>
       </c>
       <c r="G66">
-        <v>0.005866134288446843</v>
+        <v>0.005819145911523891</v>
       </c>
       <c r="H66">
         <v>0.006097099419215699</v>
       </c>
       <c r="I66">
-        <v>-0.1290348692311443</v>
+        <v>-0.1420464923081926</v>
       </c>
       <c r="J66">
         <v>0.8494188461475927</v>
       </c>
       <c r="K66">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="L66">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="M66">
         <v>2.41</v>
@@ -4159,43 +4132,43 @@
         <v>4</v>
       </c>
       <c r="B67" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C67">
-        <v>1.860854088476109</v>
+        <v>1.932900580784302</v>
       </c>
       <c r="D67" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="E67">
-        <v>2.002900580784301</v>
+        <v>2.010121419248216</v>
       </c>
       <c r="F67">
         <v>-1</v>
       </c>
       <c r="G67">
-        <v>0.005819145911523891</v>
+        <v>0.006027099419215699</v>
       </c>
       <c r="H67">
-        <v>0.006097099419215699</v>
+        <v>0.006749878580751783</v>
       </c>
       <c r="I67">
-        <v>-0.1420464923081926</v>
+        <v>-0.07722083846391481</v>
       </c>
       <c r="J67">
         <v>0.8494188461475927</v>
       </c>
       <c r="K67">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="L67">
-        <v>3.84</v>
+        <v>3.98</v>
       </c>
       <c r="M67">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="N67">
-        <v>4.05</v>
+        <v>4.38</v>
       </c>
       <c r="O67">
         <v>1</v>
@@ -4209,13 +4182,13 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C68">
         <v>1.778043160662217</v>
       </c>
       <c r="D68" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E68">
         <v>1.4819325002745</v>
@@ -4265,7 +4238,7 @@
         <v>1.764610849488207</v>
       </c>
       <c r="D69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E69">
         <v>1.885444858906632</v>
@@ -4315,7 +4288,7 @@
         <v>1.759334198518915</v>
       </c>
       <c r="D70" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E70">
         <v>1.885444858906632</v>
@@ -4359,43 +4332,43 @@
         <v>3</v>
       </c>
       <c r="B71" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C71">
-        <v>1.747297311723009</v>
+        <v>1.815444858906632</v>
       </c>
       <c r="D71" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="E71">
-        <v>1.885444858906632</v>
+        <v>1.87414570802884</v>
       </c>
       <c r="F71">
         <v>-1</v>
       </c>
       <c r="G71">
-        <v>0.00593270268827699</v>
+        <v>0.006144555141093369</v>
       </c>
       <c r="H71">
-        <v>0.006214555141093368</v>
+        <v>0.00688585429197116</v>
       </c>
       <c r="I71">
-        <v>-0.1381475471836224</v>
+        <v>-0.05870084912220763</v>
       </c>
       <c r="J71">
         <v>0.898155660204717</v>
       </c>
       <c r="K71">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="L71">
-        <v>3.84</v>
+        <v>3.98</v>
       </c>
       <c r="M71">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="N71">
-        <v>4.05</v>
+        <v>4.38</v>
       </c>
       <c r="O71">
         <v>1</v>
@@ -4409,13 +4382,13 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C72">
         <v>1.698438247560837</v>
       </c>
       <c r="D72" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E72">
         <v>1.405222311285897</v>
@@ -4459,13 +4432,13 @@
         <v>1</v>
       </c>
       <c r="B73" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C73">
         <v>1.142741567826858</v>
       </c>
       <c r="D73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E73">
         <v>1.419158035143968</v>
@@ -4509,43 +4482,43 @@
         <v>2</v>
       </c>
       <c r="B74" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C74">
-        <v>1.645957504101798</v>
+        <v>1.769173440376737</v>
       </c>
       <c r="D74" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="E74">
-        <v>1.769173440376737</v>
+        <v>1.739541036784687</v>
       </c>
       <c r="F74">
         <v>-1</v>
       </c>
       <c r="G74">
-        <v>0.006094042495898203</v>
+        <v>0.006330826559623264</v>
       </c>
       <c r="H74">
-        <v>0.006330826559623264</v>
+        <v>0.007020458963215312</v>
       </c>
       <c r="I74">
-        <v>-0.123215936274939</v>
+        <v>0.02963240359204944</v>
       </c>
       <c r="J74">
         <v>0.9464010620843414</v>
       </c>
       <c r="K74">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="L74">
-        <v>3.87</v>
+        <v>4.05</v>
       </c>
       <c r="M74">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="N74">
-        <v>4.05</v>
+        <v>4.38</v>
       </c>
       <c r="O74">
         <v>1</v>
@@ -4556,96 +4529,96 @@
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B75" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C75">
-        <v>1.613410205419267</v>
+        <v>1.699173440376737</v>
       </c>
       <c r="D75" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E75">
-        <v>1.293162190479684</v>
+        <v>1.739541036784687</v>
       </c>
       <c r="F75">
         <v>-1</v>
       </c>
       <c r="G75">
-        <v>0.004906589794580732</v>
+        <v>0.006260826559623263</v>
       </c>
       <c r="H75">
-        <v>0.004346837809520315</v>
+        <v>0.007020458963215312</v>
       </c>
       <c r="I75">
-        <v>0.320248014939583</v>
+        <v>-0.0403675964079504</v>
       </c>
       <c r="J75">
-        <v>0.9979332088368078</v>
+        <v>0.9464010620843414</v>
       </c>
       <c r="K75">
-        <v>1.65</v>
+        <v>2.41</v>
       </c>
       <c r="L75">
-        <v>3.26</v>
+        <v>3.98</v>
       </c>
       <c r="M75">
-        <v>1.53</v>
+        <v>2.79</v>
       </c>
       <c r="N75">
-        <v>2.82</v>
+        <v>4.38</v>
       </c>
       <c r="O75">
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B76" t="s">
         <v>35</v>
       </c>
       <c r="C76">
-        <v>1.02473295176371</v>
+        <v>1.613410205419267</v>
       </c>
       <c r="D76" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E76">
-        <v>1.323823563651905</v>
+        <v>1.293162190479684</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G76">
-        <v>0.005595267048236289</v>
+        <v>0.004906589794580732</v>
       </c>
       <c r="H76">
-        <v>0.005016176436348095</v>
+        <v>0.004346837809520315</v>
       </c>
       <c r="I76">
-        <v>0.2990906118881951</v>
+        <v>0.320248014939583</v>
       </c>
       <c r="J76">
         <v>0.9979332088368078</v>
       </c>
       <c r="K76">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="L76">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="M76">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="N76">
-        <v>3.17</v>
+        <v>2.82</v>
       </c>
       <c r="O76">
         <v>1</v>
@@ -4656,46 +4629,46 @@
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B77" t="s">
         <v>36</v>
       </c>
       <c r="C77">
-        <v>1.644980966703293</v>
+        <v>1.02473295176371</v>
       </c>
       <c r="D77" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E77">
-        <v>1.574980966703293</v>
+        <v>1.323823563651905</v>
       </c>
       <c r="F77">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>0.006455019033296707</v>
+        <v>0.005595267048236289</v>
       </c>
       <c r="H77">
-        <v>0.006385019033296708</v>
+        <v>0.005016176436348095</v>
       </c>
       <c r="I77">
-        <v>0.06999999999999984</v>
+        <v>0.2990906118881951</v>
       </c>
       <c r="J77">
         <v>0.9979332088368078</v>
       </c>
       <c r="K77">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="L77">
-        <v>4.05</v>
+        <v>3.31</v>
       </c>
       <c r="M77">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="N77">
-        <v>3.98</v>
+        <v>3.17</v>
       </c>
       <c r="O77">
         <v>1</v>
@@ -4706,146 +4679,146 @@
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C78">
-        <v>1.563582758846789</v>
+        <v>1.644980966703293</v>
       </c>
       <c r="D78" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E78">
-        <v>1.246958558203386</v>
+        <v>1.595766347345306</v>
       </c>
       <c r="F78">
         <v>-1</v>
       </c>
       <c r="G78">
-        <v>0.004956417241153211</v>
+        <v>0.006455019033296707</v>
       </c>
       <c r="H78">
-        <v>0.004393041441796613</v>
+        <v>0.007164233652654694</v>
       </c>
       <c r="I78">
-        <v>0.3166242006434028</v>
+        <v>0.04921461935798677</v>
       </c>
       <c r="J78">
-        <v>1.028131661304976</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K78">
-        <v>1.65</v>
+        <v>2.41</v>
       </c>
       <c r="L78">
-        <v>3.26</v>
+        <v>4.05</v>
       </c>
       <c r="M78">
-        <v>1.53</v>
+        <v>2.79</v>
       </c>
       <c r="N78">
-        <v>2.82</v>
+        <v>4.38</v>
       </c>
       <c r="O78">
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:16">
       <c r="A79" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B79" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C79">
-        <v>0.9555784956116042</v>
+        <v>1.574980966703293</v>
       </c>
       <c r="D79" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E79">
-        <v>1.267956426585794</v>
+        <v>1.595766347345306</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G79">
-        <v>0.005664421504388396</v>
+        <v>0.006385019033296708</v>
       </c>
       <c r="H79">
-        <v>0.005072043573414206</v>
+        <v>0.007164233652654694</v>
       </c>
       <c r="I79">
-        <v>0.3123779309741896</v>
+        <v>-0.02078538064201307</v>
       </c>
       <c r="J79">
-        <v>1.028131661304976</v>
+        <v>0.9979332088368078</v>
       </c>
       <c r="K79">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="L79">
-        <v>3.31</v>
+        <v>3.98</v>
       </c>
       <c r="M79">
-        <v>1.85</v>
+        <v>2.79</v>
       </c>
       <c r="N79">
-        <v>3.17</v>
+        <v>4.38</v>
       </c>
       <c r="O79">
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C80">
-        <v>1.572202696255007</v>
+        <v>1.563582758846789</v>
       </c>
       <c r="D80" t="s">
         <v>56</v>
       </c>
       <c r="E80">
-        <v>1.502202696255007</v>
+        <v>1.246958558203386</v>
       </c>
       <c r="F80">
         <v>-1</v>
       </c>
       <c r="G80">
-        <v>0.006527797303744994</v>
+        <v>0.004956417241153211</v>
       </c>
       <c r="H80">
-        <v>0.006457797303744993</v>
+        <v>0.004393041441796613</v>
       </c>
       <c r="I80">
-        <v>0.06999999999999984</v>
+        <v>0.3166242006434028</v>
       </c>
       <c r="J80">
         <v>1.028131661304976</v>
       </c>
       <c r="K80">
-        <v>2.41</v>
+        <v>1.65</v>
       </c>
       <c r="L80">
-        <v>4.05</v>
+        <v>3.26</v>
       </c>
       <c r="M80">
-        <v>2.41</v>
+        <v>1.53</v>
       </c>
       <c r="N80">
-        <v>3.98</v>
+        <v>2.82</v>
       </c>
       <c r="O80">
         <v>1</v>
@@ -4856,152 +4829,152 @@
     </row>
     <row r="81" spans="1:16">
       <c r="A81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B81" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C81">
-        <v>1.51276870292658</v>
+        <v>0.9555784956116042</v>
       </c>
       <c r="D81" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E81">
-        <v>1.15219719233976</v>
+        <v>1.267956426585794</v>
       </c>
       <c r="F81">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G81">
-        <v>0.00500723129707342</v>
+        <v>0.005664421504388396</v>
       </c>
       <c r="H81">
-        <v>0.004307802807660239</v>
+        <v>0.005072043573414206</v>
       </c>
       <c r="I81">
-        <v>0.3605715105868199</v>
+        <v>0.3123779309741896</v>
       </c>
       <c r="J81">
-        <v>1.058928058832376</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K81">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="L81">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="M81">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="N81">
-        <v>2.73</v>
+        <v>3.17</v>
       </c>
       <c r="O81">
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="82" spans="1:16">
       <c r="A82" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B82" t="s">
         <v>37</v>
       </c>
       <c r="C82">
-        <v>0.95505474527386</v>
+        <v>1.572202696255007</v>
       </c>
       <c r="D82" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E82">
-        <v>1.210983091160105</v>
+        <v>1.511512664959116</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G82">
-        <v>0.00580494525472614</v>
+        <v>0.006527797303744994</v>
       </c>
       <c r="H82">
-        <v>0.005129016908839895</v>
+        <v>0.007248487335040884</v>
       </c>
       <c r="I82">
-        <v>0.2559283458862451</v>
+        <v>0.0606900312958909</v>
       </c>
       <c r="J82">
-        <v>1.058928058832376</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K82">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="L82">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="M82">
-        <v>1.85</v>
+        <v>2.79</v>
       </c>
       <c r="N82">
-        <v>3.17</v>
+        <v>4.38</v>
       </c>
       <c r="O82">
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B83" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C83">
-        <v>1.497983378213975</v>
+        <v>1.502202696255007</v>
       </c>
       <c r="D83" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E83">
-        <v>1.427983378213975</v>
+        <v>1.511512664959116</v>
       </c>
       <c r="F83">
         <v>-1</v>
       </c>
       <c r="G83">
-        <v>0.006602016621786024</v>
+        <v>0.006457797303744993</v>
       </c>
       <c r="H83">
-        <v>0.006532016621786025</v>
+        <v>0.007248487335040884</v>
       </c>
       <c r="I83">
-        <v>0.06999999999999984</v>
+        <v>-0.00930996870410894</v>
       </c>
       <c r="J83">
-        <v>1.058928058832376</v>
+        <v>1.028131661304976</v>
       </c>
       <c r="K83">
         <v>2.41</v>
       </c>
       <c r="L83">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="M83">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="N83">
-        <v>3.98</v>
+        <v>4.38</v>
       </c>
       <c r="O83">
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5009,31 +4982,31 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C84">
-        <v>1.47291752351783</v>
+        <v>1.51276870292658</v>
       </c>
       <c r="D84" t="s">
         <v>57</v>
       </c>
       <c r="E84">
-        <v>1.116210369722162</v>
+        <v>1.15219719233976</v>
       </c>
       <c r="F84">
         <v>-1</v>
       </c>
       <c r="G84">
-        <v>0.00504708247648217</v>
+        <v>0.00500723129707342</v>
       </c>
       <c r="H84">
-        <v>0.004343789630277838</v>
+        <v>0.004307802807660239</v>
       </c>
       <c r="I84">
-        <v>0.3567071537956681</v>
+        <v>0.3605715105868199</v>
       </c>
       <c r="J84">
-        <v>1.083080288777073</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K84">
         <v>1.65</v>
@@ -5051,7 +5024,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5059,31 +5032,31 @@
         <v>1</v>
       </c>
       <c r="B85" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C85">
-        <v>0.8997461387005035</v>
+        <v>0.95505474527386</v>
       </c>
       <c r="D85" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E85">
-        <v>1.166301465762415</v>
+        <v>1.210983091160105</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85">
-        <v>0.005860253861299496</v>
+        <v>0.00580494525472614</v>
       </c>
       <c r="H85">
-        <v>0.005173698534237585</v>
+        <v>0.005129016908839895</v>
       </c>
       <c r="I85">
-        <v>0.2665553270619117</v>
+        <v>0.2559283458862451</v>
       </c>
       <c r="J85">
-        <v>1.083080288777073</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K85">
         <v>2.29</v>
@@ -5101,7 +5074,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5109,31 +5082,31 @@
         <v>2</v>
       </c>
       <c r="B86" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C86">
-        <v>1.439776504047254</v>
+        <v>1.497983378213975</v>
       </c>
       <c r="D86" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E86">
-        <v>1.369776504047254</v>
+        <v>1.425590715857672</v>
       </c>
       <c r="F86">
         <v>-1</v>
       </c>
       <c r="G86">
-        <v>0.006660223495952746</v>
+        <v>0.006602016621786024</v>
       </c>
       <c r="H86">
-        <v>0.006590223495952746</v>
+        <v>0.007334409284142328</v>
       </c>
       <c r="I86">
-        <v>0.06999999999999984</v>
+        <v>0.07239266235630248</v>
       </c>
       <c r="J86">
-        <v>1.083080288777073</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K86">
         <v>2.41</v>
@@ -5142,748 +5115,748 @@
         <v>4.05</v>
       </c>
       <c r="M86">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="N86">
-        <v>3.98</v>
+        <v>4.38</v>
       </c>
       <c r="O86">
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B87" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C87">
-        <v>1.473409677892745</v>
+        <v>1.427983378213975</v>
       </c>
       <c r="D87" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E87">
-        <v>1.116654800036478</v>
+        <v>1.425590715857672</v>
       </c>
       <c r="F87">
         <v>-1</v>
       </c>
       <c r="G87">
-        <v>0.005046590322107255</v>
+        <v>0.006532016621786025</v>
       </c>
       <c r="H87">
-        <v>0.004343345199963522</v>
+        <v>0.007334409284142328</v>
       </c>
       <c r="I87">
-        <v>0.3567548778562661</v>
+        <v>0.002392662356302644</v>
       </c>
       <c r="J87">
-        <v>1.082782013398337</v>
+        <v>1.058928058832376</v>
       </c>
       <c r="K87">
-        <v>1.65</v>
+        <v>2.41</v>
       </c>
       <c r="L87">
-        <v>3.26</v>
+        <v>3.98</v>
       </c>
       <c r="M87">
-        <v>1.49</v>
+        <v>2.79</v>
       </c>
       <c r="N87">
-        <v>2.73</v>
+        <v>4.38</v>
       </c>
       <c r="O87">
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C88">
-        <v>0.9004291893178089</v>
+        <v>1.47291752351783</v>
       </c>
       <c r="D88" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E88">
-        <v>1.166853275213077</v>
+        <v>1.116210369722162</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G88">
-        <v>0.005859570810682191</v>
+        <v>0.00504708247648217</v>
       </c>
       <c r="H88">
-        <v>0.005173146724786923</v>
+        <v>0.004343789630277838</v>
       </c>
       <c r="I88">
-        <v>0.2664240858952684</v>
+        <v>0.3567071537956681</v>
       </c>
       <c r="J88">
-        <v>1.082782013398337</v>
+        <v>1.083080288777073</v>
       </c>
       <c r="K88">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="L88">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="M88">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="N88">
-        <v>3.17</v>
+        <v>2.73</v>
       </c>
       <c r="O88">
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89" spans="1:16">
       <c r="A89" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B89" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C89">
-        <v>1.440495347710009</v>
+        <v>0.8997461387005035</v>
       </c>
       <c r="D89" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E89">
-        <v>1.370495347710009</v>
+        <v>1.166301465762415</v>
       </c>
       <c r="F89">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G89">
-        <v>0.006659504652289991</v>
+        <v>0.005860253861299496</v>
       </c>
       <c r="H89">
-        <v>0.006589504652289991</v>
+        <v>0.005173698534237585</v>
       </c>
       <c r="I89">
-        <v>0.06999999999999984</v>
+        <v>0.2665553270619117</v>
       </c>
       <c r="J89">
-        <v>1.082782013398337</v>
+        <v>1.083080288777073</v>
       </c>
       <c r="K89">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="L89">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="M89">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="N89">
-        <v>3.98</v>
+        <v>3.17</v>
       </c>
       <c r="O89">
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B90" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C90">
-        <v>1.472764755561722</v>
+        <v>1.439776504047254</v>
       </c>
       <c r="D90" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E90">
-        <v>1.116072415628464</v>
+        <v>1.358205994311967</v>
       </c>
       <c r="F90">
         <v>-1</v>
       </c>
       <c r="G90">
-        <v>0.005047235244438278</v>
+        <v>0.006660223495952746</v>
       </c>
       <c r="H90">
-        <v>0.004343927584371536</v>
+        <v>0.007401794005688033</v>
       </c>
       <c r="I90">
-        <v>0.3566923399332578</v>
+        <v>0.08157050973528746</v>
       </c>
       <c r="J90">
-        <v>1.083172875417138</v>
+        <v>1.083080288777073</v>
       </c>
       <c r="K90">
-        <v>1.65</v>
+        <v>2.41</v>
       </c>
       <c r="L90">
-        <v>3.26</v>
+        <v>4.05</v>
       </c>
       <c r="M90">
-        <v>1.49</v>
+        <v>2.79</v>
       </c>
       <c r="N90">
-        <v>2.73</v>
+        <v>4.38</v>
       </c>
       <c r="O90">
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C91">
-        <v>0.8995341152947529</v>
+        <v>1.473409677892745</v>
       </c>
       <c r="D91" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E91">
-        <v>1.166130180478294</v>
+        <v>1.116654800036478</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G91">
-        <v>0.005860465884705247</v>
+        <v>0.005046590322107255</v>
       </c>
       <c r="H91">
-        <v>0.005173869819521706</v>
+        <v>0.004343345199963522</v>
       </c>
       <c r="I91">
-        <v>0.2665960651835411</v>
+        <v>0.3567548778562661</v>
       </c>
       <c r="J91">
-        <v>1.083172875417138</v>
+        <v>1.082782013398337</v>
       </c>
       <c r="K91">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="L91">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="M91">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="N91">
-        <v>3.17</v>
+        <v>2.73</v>
       </c>
       <c r="O91">
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B92" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C92">
-        <v>1.439553370244696</v>
+        <v>0.9004291893178089</v>
       </c>
       <c r="D92" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E92">
-        <v>1.369553370244696</v>
+        <v>1.166853275213077</v>
       </c>
       <c r="F92">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G92">
-        <v>0.006660446629755304</v>
+        <v>0.005859570810682191</v>
       </c>
       <c r="H92">
-        <v>0.006590446629755304</v>
+        <v>0.005173146724786923</v>
       </c>
       <c r="I92">
-        <v>0.06999999999999984</v>
+        <v>0.2664240858952684</v>
       </c>
       <c r="J92">
-        <v>1.083172875417138</v>
+        <v>1.082782013398337</v>
       </c>
       <c r="K92">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="L92">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="M92">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="N92">
-        <v>3.98</v>
+        <v>3.17</v>
       </c>
       <c r="O92">
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93" spans="1:16">
       <c r="A93" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C93">
-        <v>1.468991674710606</v>
+        <v>1.440495347710009</v>
       </c>
       <c r="D93" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E93">
-        <v>1.112665209284123</v>
+        <v>1.359038182618641</v>
       </c>
       <c r="F93">
         <v>-1</v>
       </c>
       <c r="G93">
-        <v>0.005051008325289394</v>
+        <v>0.006659504652289991</v>
       </c>
       <c r="H93">
-        <v>0.004347334790715877</v>
+        <v>0.00740096181738136</v>
       </c>
       <c r="I93">
-        <v>0.3563264654264828</v>
+        <v>0.08145716509136802</v>
       </c>
       <c r="J93">
-        <v>1.085459591084481</v>
+        <v>1.082782013398337</v>
       </c>
       <c r="K93">
-        <v>1.65</v>
+        <v>2.41</v>
       </c>
       <c r="L93">
-        <v>3.26</v>
+        <v>4.05</v>
       </c>
       <c r="M93">
-        <v>1.49</v>
+        <v>2.79</v>
       </c>
       <c r="N93">
-        <v>2.73</v>
+        <v>4.38</v>
       </c>
       <c r="O93">
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94" spans="1:16">
       <c r="A94" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C94">
-        <v>0.8942975364165378</v>
+        <v>1.472764755561722</v>
       </c>
       <c r="D94" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E94">
-        <v>1.161899756493709</v>
+        <v>1.116072415628464</v>
       </c>
       <c r="F94">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G94">
-        <v>0.005865702463583462</v>
+        <v>0.005047235244438278</v>
       </c>
       <c r="H94">
-        <v>0.00517810024350629</v>
+        <v>0.004343927584371536</v>
       </c>
       <c r="I94">
-        <v>0.2676022200771717</v>
+        <v>0.3566923399332578</v>
       </c>
       <c r="J94">
-        <v>1.085459591084481</v>
+        <v>1.083172875417138</v>
       </c>
       <c r="K94">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="L94">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="M94">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="N94">
-        <v>3.17</v>
+        <v>2.73</v>
       </c>
       <c r="O94">
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95" spans="1:16">
       <c r="A95" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B95" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C95">
-        <v>1.4340423854864</v>
+        <v>0.8995341152947529</v>
       </c>
       <c r="D95" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E95">
-        <v>1.3640423854864</v>
+        <v>1.166130180478294</v>
       </c>
       <c r="F95">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G95">
-        <v>0.0066659576145136</v>
+        <v>0.005860465884705247</v>
       </c>
       <c r="H95">
-        <v>0.0065959576145136</v>
+        <v>0.005173869819521706</v>
       </c>
       <c r="I95">
-        <v>0.06999999999999984</v>
+        <v>0.2665960651835411</v>
       </c>
       <c r="J95">
-        <v>1.085459591084481</v>
+        <v>1.083172875417138</v>
       </c>
       <c r="K95">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="L95">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="M95">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="N95">
-        <v>3.98</v>
+        <v>3.17</v>
       </c>
       <c r="O95">
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="96" spans="1:16">
       <c r="A96" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B96" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C96">
-        <v>1.418256303089464</v>
+        <v>1.439553370244696</v>
       </c>
       <c r="D96" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E96">
-        <v>1.428256303089464</v>
+        <v>1.357947677586184</v>
       </c>
       <c r="F96">
         <v>-1</v>
       </c>
       <c r="G96">
-        <v>0.005101743696910536</v>
+        <v>0.006660446629755304</v>
       </c>
       <c r="H96">
-        <v>0.005111743696910536</v>
+        <v>0.007402052322413816</v>
       </c>
       <c r="I96">
-        <v>-0.01000000000000023</v>
+        <v>0.08160569265851247</v>
       </c>
       <c r="J96">
-        <v>1.1162083011579</v>
+        <v>1.083172875417138</v>
       </c>
       <c r="K96">
-        <v>1.65</v>
+        <v>2.41</v>
       </c>
       <c r="L96">
-        <v>3.26</v>
+        <v>4.05</v>
       </c>
       <c r="M96">
-        <v>1.65</v>
+        <v>2.79</v>
       </c>
       <c r="N96">
-        <v>3.27</v>
+        <v>4.38</v>
       </c>
       <c r="O96">
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:16">
       <c r="A97" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C97">
-        <v>0.823882990348408</v>
+        <v>1.468991674710606</v>
       </c>
       <c r="D97" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E97">
-        <v>1.105014642857884</v>
+        <v>1.112665209284123</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G97">
-        <v>0.005936117009651592</v>
+        <v>0.005051008325289394</v>
       </c>
       <c r="H97">
-        <v>0.005234985357142116</v>
+        <v>0.004347334790715877</v>
       </c>
       <c r="I97">
-        <v>0.281131652509476</v>
+        <v>0.3563264654264828</v>
       </c>
       <c r="J97">
-        <v>1.1162083011579</v>
+        <v>1.085459591084481</v>
       </c>
       <c r="K97">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="L97">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="M97">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="N97">
-        <v>3.17</v>
+        <v>2.73</v>
       </c>
       <c r="O97">
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:16">
       <c r="A98" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B98" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C98">
-        <v>1.35993799420946</v>
+        <v>0.8942975364165378</v>
       </c>
       <c r="D98" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E98">
-        <v>1.28993799420946</v>
+        <v>1.161899756493709</v>
       </c>
       <c r="F98">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G98">
-        <v>0.00674006200579054</v>
+        <v>0.005865702463583462</v>
       </c>
       <c r="H98">
-        <v>0.00667006200579054</v>
+        <v>0.00517810024350629</v>
       </c>
       <c r="I98">
-        <v>0.06999999999999984</v>
+        <v>0.2676022200771717</v>
       </c>
       <c r="J98">
-        <v>1.1162083011579</v>
+        <v>1.085459591084481</v>
       </c>
       <c r="K98">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="L98">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="M98">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="N98">
-        <v>3.98</v>
+        <v>3.17</v>
       </c>
       <c r="O98">
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B99" t="s">
         <v>37</v>
       </c>
       <c r="C99">
-        <v>0.7552208383877499</v>
+        <v>1.4340423854864</v>
       </c>
       <c r="D99" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E99">
-        <v>1.049545218784863</v>
+        <v>1.351567740874297</v>
       </c>
       <c r="F99">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G99">
-        <v>0.00600477916161225</v>
+        <v>0.0066659576145136</v>
       </c>
       <c r="H99">
-        <v>0.005290454781215137</v>
+        <v>0.007408432259125703</v>
       </c>
       <c r="I99">
-        <v>0.2943243803971134</v>
+        <v>0.0824746446121023</v>
       </c>
       <c r="J99">
-        <v>1.146191773629804</v>
+        <v>1.085459591084481</v>
       </c>
       <c r="K99">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="L99">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="M99">
-        <v>1.85</v>
+        <v>2.79</v>
       </c>
       <c r="N99">
-        <v>3.17</v>
+        <v>4.38</v>
       </c>
       <c r="O99">
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="100" spans="1:16">
       <c r="A100" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C100">
-        <v>1.287677825552173</v>
+        <v>1.418256303089464</v>
       </c>
       <c r="D100" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E100">
-        <v>1.217677825552173</v>
+        <v>1.428256303089464</v>
       </c>
       <c r="F100">
         <v>-1</v>
       </c>
       <c r="G100">
-        <v>0.006812322174447827</v>
+        <v>0.005101743696910536</v>
       </c>
       <c r="H100">
-        <v>0.006742322174447827</v>
+        <v>0.005111743696910536</v>
       </c>
       <c r="I100">
-        <v>0.06999999999999984</v>
+        <v>-0.01000000000000023</v>
       </c>
       <c r="J100">
-        <v>1.146191773629804</v>
+        <v>1.1162083011579</v>
       </c>
       <c r="K100">
-        <v>2.41</v>
+        <v>1.65</v>
       </c>
       <c r="L100">
-        <v>4.05</v>
+        <v>3.26</v>
       </c>
       <c r="M100">
-        <v>2.41</v>
+        <v>1.65</v>
       </c>
       <c r="N100">
-        <v>3.98</v>
+        <v>3.27</v>
       </c>
       <c r="O100">
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B101" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C101">
-        <v>0.7164672131147527</v>
+        <v>0.823882990348408</v>
       </c>
       <c r="D101" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E101">
-        <v>1.018237704918032</v>
+        <v>1.105014642857884</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
       <c r="G101">
-        <v>0.006043532786885248</v>
+        <v>0.005936117009651592</v>
       </c>
       <c r="H101">
-        <v>0.005321762295081968</v>
+        <v>0.005234985357142116</v>
       </c>
       <c r="I101">
-        <v>0.3017704918032789</v>
+        <v>0.281131652509476</v>
       </c>
       <c r="J101">
-        <v>1.163114754098361</v>
+        <v>1.1162083011579</v>
       </c>
       <c r="K101">
         <v>2.29</v>
@@ -5901,39 +5874,39 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="102" spans="1:16">
       <c r="A102" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B102" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C102">
-        <v>1.246893442622949</v>
+        <v>1.35993799420946</v>
       </c>
       <c r="D102" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E102">
-        <v>1.176893442622949</v>
+        <v>1.265778839769458</v>
       </c>
       <c r="F102">
         <v>-1</v>
       </c>
       <c r="G102">
-        <v>0.006853106557377051</v>
+        <v>0.00674006200579054</v>
       </c>
       <c r="H102">
-        <v>0.006783106557377051</v>
+        <v>0.007494221160230542</v>
       </c>
       <c r="I102">
-        <v>0.06999999999999984</v>
+        <v>0.094159154440002</v>
       </c>
       <c r="J102">
-        <v>1.163114754098361</v>
+        <v>1.1162083011579</v>
       </c>
       <c r="K102">
         <v>2.41</v>
@@ -5942,16 +5915,16 @@
         <v>4.05</v>
       </c>
       <c r="M102">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="N102">
-        <v>3.98</v>
+        <v>4.38</v>
       </c>
       <c r="O102">
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -5962,46 +5935,46 @@
         <v>38</v>
       </c>
       <c r="C103">
-        <v>0.7002131196894186</v>
+        <v>0.7552208383877499</v>
       </c>
       <c r="D103" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E103">
-        <v>0.5798239504652853</v>
+        <v>1.049545218784863</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
       <c r="G103">
-        <v>0.006279786880310581</v>
+        <v>0.00600477916161225</v>
       </c>
       <c r="H103">
-        <v>0.006040176049534715</v>
+        <v>0.005290454781215137</v>
       </c>
       <c r="I103">
-        <v>-0.1203891692241332</v>
+        <v>0.2943243803971134</v>
       </c>
       <c r="J103">
-        <v>1.192216615517343</v>
+        <v>1.146191773629804</v>
       </c>
       <c r="K103">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="L103">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="M103">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="N103">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="O103">
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6012,184 +5985,184 @@
         <v>37</v>
       </c>
       <c r="C104">
-        <v>0.6498239504652852</v>
+        <v>1.287677825552173</v>
       </c>
       <c r="D104" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E104">
-        <v>0.5798239504652853</v>
+        <v>1.182124951572848</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G104">
-        <v>0.006110176049534715</v>
+        <v>0.006812322174447827</v>
       </c>
       <c r="H104">
-        <v>0.006040176049534715</v>
+        <v>0.007577875048427152</v>
       </c>
       <c r="I104">
-        <v>-0.06999999999999984</v>
+        <v>0.1055528739793252</v>
       </c>
       <c r="J104">
-        <v>1.192216615517343</v>
+        <v>1.146191773629804</v>
       </c>
       <c r="K104">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="L104">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="M104">
-        <v>2.29</v>
+        <v>2.79</v>
       </c>
       <c r="N104">
-        <v>3.31</v>
+        <v>4.38</v>
       </c>
       <c r="O104">
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
     </row>
     <row r="105" spans="1:16">
       <c r="A105" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C105">
-        <v>1.176757956603204</v>
+        <v>0.7164672131147527</v>
       </c>
       <c r="D105" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E105">
-        <v>1.106757956603204</v>
+        <v>1.018237704918032</v>
       </c>
       <c r="F105">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G105">
-        <v>0.006923242043396796</v>
+        <v>0.006043532786885248</v>
       </c>
       <c r="H105">
-        <v>0.006853242043396796</v>
+        <v>0.005321762295081968</v>
       </c>
       <c r="I105">
-        <v>0.06999999999999984</v>
+        <v>0.3017704918032789</v>
       </c>
       <c r="J105">
-        <v>1.192216615517343</v>
+        <v>1.163114754098361</v>
       </c>
       <c r="K105">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="L105">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="M105">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="N105">
-        <v>3.98</v>
+        <v>3.17</v>
       </c>
       <c r="O105">
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106" spans="1:16">
       <c r="A106" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B106" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C106">
-        <v>0.5205928926738919</v>
+        <v>1.246893442622949</v>
       </c>
       <c r="D106" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E106">
-        <v>0.4040417624885522</v>
+        <v>1.134909836065572</v>
       </c>
       <c r="F106">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G106">
-        <v>0.006459407107326108</v>
+        <v>0.006853106557377051</v>
       </c>
       <c r="H106">
-        <v>0.006215958237511448</v>
+        <v>0.007625090163934428</v>
       </c>
       <c r="I106">
-        <v>-0.1165511301853397</v>
+        <v>0.1119836065573772</v>
       </c>
       <c r="J106">
-        <v>1.268977396293209</v>
+        <v>1.163114754098361</v>
       </c>
       <c r="K106">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="L106">
-        <v>3.49</v>
+        <v>4.05</v>
       </c>
       <c r="M106">
-        <v>2.29</v>
+        <v>2.79</v>
       </c>
       <c r="N106">
-        <v>3.31</v>
+        <v>4.38</v>
       </c>
       <c r="O106">
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:16">
       <c r="A107" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C107">
-        <v>0.474041762488552</v>
+        <v>0.7002131196894186</v>
       </c>
       <c r="D107" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E107">
-        <v>0.4040417624885522</v>
+        <v>0.5798239504652853</v>
       </c>
       <c r="F107">
         <v>1</v>
       </c>
       <c r="G107">
-        <v>0.006285958237511447</v>
+        <v>0.006279786880310581</v>
       </c>
       <c r="H107">
-        <v>0.006215958237511448</v>
+        <v>0.006040176049534715</v>
       </c>
       <c r="I107">
-        <v>-0.06999999999999984</v>
+        <v>-0.1203891692241332</v>
       </c>
       <c r="J107">
-        <v>1.268977396293209</v>
+        <v>1.192216615517343</v>
       </c>
       <c r="K107">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="L107">
-        <v>3.38</v>
+        <v>3.49</v>
       </c>
       <c r="M107">
         <v>2.29</v>
@@ -6201,107 +6174,107 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
     </row>
     <row r="108" spans="1:16">
       <c r="A108" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B108" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C108">
-        <v>0.551698597969601</v>
+        <v>0.6498239504652852</v>
       </c>
       <c r="D108" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="E108">
-        <v>0.7904611387463603</v>
+        <v>0.5798239504652853</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
       <c r="G108">
-        <v>0.006008301402030399</v>
+        <v>0.006110176049534715</v>
       </c>
       <c r="H108">
-        <v>0.005409538861253641</v>
+        <v>0.006040176049534715</v>
       </c>
       <c r="I108">
-        <v>0.2387625407767593</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="J108">
-        <v>1.268977396293209</v>
+        <v>1.192216615517343</v>
       </c>
       <c r="K108">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="L108">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="M108">
-        <v>1.82</v>
+        <v>2.29</v>
       </c>
       <c r="N108">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="O108">
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
     </row>
     <row r="109" spans="1:16">
       <c r="A109" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B109" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C109">
-        <v>0.3774746016246668</v>
+        <v>1.176757956603204</v>
       </c>
       <c r="D109" t="s">
+        <v>53</v>
+      </c>
+      <c r="E109">
+        <v>1.053715642706614</v>
+      </c>
+      <c r="F109">
+        <v>-1</v>
+      </c>
+      <c r="G109">
+        <v>0.006923242043396796</v>
+      </c>
+      <c r="H109">
+        <v>0.007706284357293387</v>
+      </c>
+      <c r="I109">
+        <v>0.1230423138965899</v>
+      </c>
+      <c r="J109">
+        <v>1.192216615517343</v>
+      </c>
+      <c r="K109">
+        <v>2.41</v>
+      </c>
+      <c r="L109">
+        <v>4.05</v>
+      </c>
+      <c r="M109">
+        <v>2.79</v>
+      </c>
+      <c r="N109">
+        <v>4.38</v>
+      </c>
+      <c r="O109">
+        <v>1</v>
+    